--- a/reports/dashboard.xlsx
+++ b/reports/dashboard.xlsx
@@ -7,8 +7,11 @@
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Monthly Returns" sheetId="1" state="visible" r:id="rId1"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Statistics" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Summary" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="NIFTY" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="BANKNIFTY" sheetId="3" state="visible" r:id="rId3"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="FINNIFTY" sheetId="4" state="visible" r:id="rId4"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="ALL INDICES" sheetId="5" state="visible" r:id="rId5"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -18,7 +21,7 @@
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <numFmts count="0"/>
-  <fonts count="3">
+  <fonts count="6">
     <font>
       <name val="Calibri"/>
       <family val="2"/>
@@ -33,18 +36,38 @@
     </font>
     <font>
       <name val="Arial"/>
+      <b val="1"/>
+      <color rgb="00FFFFFF"/>
+    </font>
+    <font>
+      <name val="Arial"/>
+      <b val="1"/>
+    </font>
+    <font>
+      <name val="Arial"/>
+    </font>
+    <font>
+      <name val="Arial"/>
       <i val="1"/>
+      <color rgb="00666666"/>
+      <sz val="9"/>
     </font>
   </fonts>
-  <fills count="2">
+  <fills count="3">
     <fill>
       <patternFill/>
     </fill>
     <fill>
       <patternFill patternType="gray125"/>
     </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="001F4E78"/>
+        <bgColor rgb="001F4E78"/>
+      </patternFill>
+    </fill>
   </fills>
-  <borders count="1">
+  <borders count="2">
     <border>
       <left/>
       <right/>
@@ -52,14 +75,33 @@
       <bottom/>
       <diagonal/>
     </border>
+    <border>
+      <left style="thin">
+        <color rgb="00B7B7B7"/>
+      </left>
+      <right style="thin">
+        <color rgb="00B7B7B7"/>
+      </right>
+      <top style="thin">
+        <color rgb="00B7B7B7"/>
+      </top>
+      <bottom style="thin">
+        <color rgb="00B7B7B7"/>
+      </bottom>
+    </border>
   </borders>
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="3">
+  <cellXfs count="6">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="2" fillId="2" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0" hidden="0"/>
@@ -423,27 +465,214 @@
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr>
     <outlinePr summaryBelow="1" summaryRight="1"/>
-    <pageSetUpPr/>
+    <pageSetUpPr fitToPage="1"/>
   </sheetPr>
-  <dimension ref="A1:A3"/>
+  <dimension ref="A1:G9"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <cols>
+    <col width="15" customWidth="1" min="1" max="1"/>
+    <col width="15" customWidth="1" min="2" max="2"/>
+    <col width="15" customWidth="1" min="3" max="3"/>
+    <col width="15" customWidth="1" min="4" max="4"/>
+    <col width="15" customWidth="1" min="5" max="5"/>
+    <col width="15" customWidth="1" min="6" max="6"/>
+    <col width="22" customWidth="1" min="7" max="7"/>
+  </cols>
   <sheetData>
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Monthly Returns (%) -- PAPER TRADE, NOT REAL MONEY</t>
+          <t>Summary by index -- PAPER TRADE, NOT REAL MONEY</t>
         </is>
       </c>
     </row>
     <row r="3">
       <c r="A3" s="2" t="inlineStr">
         <is>
-          <t>No trades yet -- this fills in automatically as the bot trades.</t>
+          <t>Index</t>
+        </is>
+      </c>
+      <c r="B3" s="2" t="inlineStr">
+        <is>
+          <t>Trades</t>
+        </is>
+      </c>
+      <c r="C3" s="2" t="inlineStr">
+        <is>
+          <t>Win %</t>
+        </is>
+      </c>
+      <c r="D3" s="2" t="inlineStr">
+        <is>
+          <t>Net P&amp;L (Rs)</t>
+        </is>
+      </c>
+      <c r="E3" s="2" t="inlineStr">
+        <is>
+          <t>Profit Factor</t>
+        </is>
+      </c>
+      <c r="F3" s="2" t="inlineStr">
+        <is>
+          <t>Max DD (%)</t>
+        </is>
+      </c>
+      <c r="G3" s="2" t="inlineStr">
+        <is>
+          <t>Avg P/L per trade (Rs)</t>
+        </is>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" s="3" t="inlineStr">
+        <is>
+          <t>NIFTY</t>
+        </is>
+      </c>
+      <c r="B4" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="C4" s="4" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="D4" s="4" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="E4" s="4" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="F4" s="4" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="G4" s="4" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" s="3" t="inlineStr">
+        <is>
+          <t>BANKNIFTY</t>
+        </is>
+      </c>
+      <c r="B5" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="C5" s="4" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="D5" s="4" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="E5" s="4" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="F5" s="4" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="G5" s="4" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" s="3" t="inlineStr">
+        <is>
+          <t>FINNIFTY</t>
+        </is>
+      </c>
+      <c r="B6" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="C6" s="4" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="D6" s="4" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="E6" s="4" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="F6" s="4" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="G6" s="4" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" s="3" t="inlineStr">
+        <is>
+          <t>ALL INDICES</t>
+        </is>
+      </c>
+      <c r="B7" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="C7" s="4" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="D7" s="4" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="E7" s="4" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="F7" s="4" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="G7" s="4" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" s="5" t="inlineStr">
+        <is>
+          <t>Each index has its own sheet with the monthly-returns grid and full statistics.</t>
         </is>
       </c>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+  <pageSetup orientation="landscape" fitToHeight="0" fitToWidth="1"/>
 </worksheet>
 </file>
 
@@ -451,26 +680,182 @@
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr>
     <outlinePr summaryBelow="1" summaryRight="1"/>
-    <pageSetUpPr/>
+    <pageSetUpPr fitToPage="1"/>
   </sheetPr>
   <dimension ref="A1:A3"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <cols>
+    <col width="40" customWidth="1" min="1" max="1"/>
+    <col width="10" customWidth="1" min="2" max="2"/>
+    <col width="10" customWidth="1" min="3" max="3"/>
+    <col width="10" customWidth="1" min="4" max="4"/>
+    <col width="10" customWidth="1" min="5" max="5"/>
+    <col width="10" customWidth="1" min="6" max="6"/>
+    <col width="10" customWidth="1" min="7" max="7"/>
+    <col width="15" customWidth="1" min="8" max="8"/>
+    <col width="15" customWidth="1" min="9" max="9"/>
+    <col width="10" customWidth="1" min="10" max="10"/>
+    <col width="10" customWidth="1" min="11" max="11"/>
+    <col width="10" customWidth="1" min="12" max="12"/>
+    <col width="10" customWidth="1" min="13" max="13"/>
+    <col width="10" customWidth="1" min="14" max="14"/>
+    <col width="15" customWidth="1" min="15" max="15"/>
+  </cols>
   <sheetData>
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Trade Statistics -- PAPER TRADE, NOT REAL MONEY</t>
+          <t>NIFTY -- PAPER TRADE, NOT REAL MONEY</t>
         </is>
       </c>
     </row>
     <row r="3">
-      <c r="A3" s="2" t="inlineStr">
-        <is>
-          <t>No trades yet.</t>
+      <c r="A3" s="5" t="inlineStr">
+        <is>
+          <t>No trades yet for this index -- this fills in automatically as the bot trades.</t>
         </is>
       </c>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+  <pageSetup orientation="landscape" fitToHeight="0" fitToWidth="1"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr fitToPage="1"/>
+  </sheetPr>
+  <dimension ref="A1:A3"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <cols>
+    <col width="40" customWidth="1" min="1" max="1"/>
+    <col width="10" customWidth="1" min="2" max="2"/>
+    <col width="10" customWidth="1" min="3" max="3"/>
+    <col width="10" customWidth="1" min="4" max="4"/>
+    <col width="10" customWidth="1" min="5" max="5"/>
+    <col width="10" customWidth="1" min="6" max="6"/>
+    <col width="10" customWidth="1" min="7" max="7"/>
+    <col width="15" customWidth="1" min="8" max="8"/>
+    <col width="15" customWidth="1" min="9" max="9"/>
+    <col width="10" customWidth="1" min="10" max="10"/>
+    <col width="10" customWidth="1" min="11" max="11"/>
+    <col width="10" customWidth="1" min="12" max="12"/>
+    <col width="10" customWidth="1" min="13" max="13"/>
+    <col width="10" customWidth="1" min="14" max="14"/>
+    <col width="15" customWidth="1" min="15" max="15"/>
+  </cols>
+  <sheetData>
+    <row r="1">
+      <c r="A1" s="1" t="inlineStr">
+        <is>
+          <t>BANKNIFTY -- PAPER TRADE, NOT REAL MONEY</t>
+        </is>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" s="5" t="inlineStr">
+        <is>
+          <t>No trades yet for this index -- this fills in automatically as the bot trades.</t>
+        </is>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+  <pageSetup orientation="landscape" fitToHeight="0" fitToWidth="1"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr fitToPage="1"/>
+  </sheetPr>
+  <dimension ref="A1:A3"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <cols>
+    <col width="40" customWidth="1" min="1" max="1"/>
+    <col width="10" customWidth="1" min="2" max="2"/>
+    <col width="10" customWidth="1" min="3" max="3"/>
+    <col width="10" customWidth="1" min="4" max="4"/>
+    <col width="10" customWidth="1" min="5" max="5"/>
+    <col width="10" customWidth="1" min="6" max="6"/>
+    <col width="10" customWidth="1" min="7" max="7"/>
+    <col width="15" customWidth="1" min="8" max="8"/>
+    <col width="15" customWidth="1" min="9" max="9"/>
+    <col width="10" customWidth="1" min="10" max="10"/>
+    <col width="10" customWidth="1" min="11" max="11"/>
+    <col width="10" customWidth="1" min="12" max="12"/>
+    <col width="10" customWidth="1" min="13" max="13"/>
+    <col width="10" customWidth="1" min="14" max="14"/>
+    <col width="15" customWidth="1" min="15" max="15"/>
+  </cols>
+  <sheetData>
+    <row r="1">
+      <c r="A1" s="1" t="inlineStr">
+        <is>
+          <t>FINNIFTY -- PAPER TRADE, NOT REAL MONEY</t>
+        </is>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" s="5" t="inlineStr">
+        <is>
+          <t>No trades yet for this index -- this fills in automatically as the bot trades.</t>
+        </is>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+  <pageSetup orientation="landscape" fitToHeight="0" fitToWidth="1"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr fitToPage="1"/>
+  </sheetPr>
+  <dimension ref="A1:A3"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <cols>
+    <col width="40" customWidth="1" min="1" max="1"/>
+    <col width="10" customWidth="1" min="2" max="2"/>
+    <col width="10" customWidth="1" min="3" max="3"/>
+    <col width="10" customWidth="1" min="4" max="4"/>
+    <col width="10" customWidth="1" min="5" max="5"/>
+    <col width="10" customWidth="1" min="6" max="6"/>
+    <col width="10" customWidth="1" min="7" max="7"/>
+    <col width="15" customWidth="1" min="8" max="8"/>
+    <col width="15" customWidth="1" min="9" max="9"/>
+    <col width="10" customWidth="1" min="10" max="10"/>
+    <col width="10" customWidth="1" min="11" max="11"/>
+    <col width="10" customWidth="1" min="12" max="12"/>
+    <col width="10" customWidth="1" min="13" max="13"/>
+    <col width="10" customWidth="1" min="14" max="14"/>
+    <col width="15" customWidth="1" min="15" max="15"/>
+  </cols>
+  <sheetData>
+    <row r="1">
+      <c r="A1" s="1" t="inlineStr">
+        <is>
+          <t>ALL INDICES -- PAPER TRADE, NOT REAL MONEY</t>
+        </is>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" s="5" t="inlineStr">
+        <is>
+          <t>No trades yet for this index -- this fills in automatically as the bot trades.</t>
+        </is>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+  <pageSetup orientation="landscape" fitToHeight="0" fitToWidth="1"/>
 </worksheet>
 </file>
--- a/reports/dashboard.xlsx
+++ b/reports/dashboard.xlsx
@@ -12,6 +12,11 @@
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="BANKNIFTY" sheetId="3" state="visible" r:id="rId3"/>
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="FINNIFTY" sheetId="4" state="visible" r:id="rId4"/>
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="ALL INDICES" sheetId="5" state="visible" r:id="rId5"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="BT-Summary" sheetId="6" state="visible" r:id="rId6"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="BT-NIFTY" sheetId="7" state="visible" r:id="rId7"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="BT-BANKNIFTY" sheetId="8" state="visible" r:id="rId8"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="BT-FINNIFTY" sheetId="9" state="visible" r:id="rId9"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="BT-ALL INDICES" sheetId="10" state="visible" r:id="rId10"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -20,8 +25,13 @@
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <numFmts count="0"/>
-  <fonts count="6">
+  <numFmts count="4">
+    <numFmt numFmtId="164" formatCode="0.0%"/>
+    <numFmt numFmtId="165" formatCode="#,##0.00;-#,##0.00"/>
+    <numFmt numFmtId="166" formatCode="#,##0;-#,##0"/>
+    <numFmt numFmtId="167" formatCode="0.00&quot;%&quot;"/>
+  </numFmts>
+  <fonts count="10">
     <font>
       <name val="Calibri"/>
       <family val="2"/>
@@ -52,8 +62,26 @@
       <color rgb="00666666"/>
       <sz val="9"/>
     </font>
+    <font>
+      <name val="Arial"/>
+      <color rgb="000B8A00"/>
+    </font>
+    <font>
+      <name val="Arial"/>
+      <color rgb="00C00000"/>
+    </font>
+    <font>
+      <name val="Arial"/>
+      <b val="1"/>
+      <color rgb="000B8A00"/>
+    </font>
+    <font>
+      <name val="Arial"/>
+      <b val="1"/>
+      <color rgb="00C00000"/>
+    </font>
   </fonts>
-  <fills count="3">
+  <fills count="5">
     <fill>
       <patternFill/>
     </fill>
@@ -66,8 +94,20 @@
         <bgColor rgb="001F4E78"/>
       </patternFill>
     </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="00E6F4EA"/>
+        <bgColor rgb="00E6F4EA"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="00FDE8E8"/>
+        <bgColor rgb="00FDE8E8"/>
+      </patternFill>
+    </fill>
   </fills>
-  <borders count="2">
+  <borders count="6">
     <border>
       <left/>
       <right/>
@@ -89,11 +129,55 @@
         <color rgb="00B7B7B7"/>
       </bottom>
     </border>
+    <border>
+      <left/>
+      <right/>
+      <top style="thin">
+        <color rgb="00B7B7B7"/>
+      </top>
+      <bottom/>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right style="thin">
+        <color rgb="00B7B7B7"/>
+      </right>
+      <top style="thin">
+        <color rgb="00B7B7B7"/>
+      </top>
+      <bottom/>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right/>
+      <top style="thin">
+        <color rgb="00B7B7B7"/>
+      </top>
+      <bottom style="thin">
+        <color rgb="00B7B7B7"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right style="thin">
+        <color rgb="00B7B7B7"/>
+      </right>
+      <top style="thin">
+        <color rgb="00B7B7B7"/>
+      </top>
+      <bottom style="thin">
+        <color rgb="00B7B7B7"/>
+      </bottom>
+      <diagonal/>
+    </border>
   </borders>
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="6">
+  <cellXfs count="33">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="2" fillId="2" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
@@ -102,6 +186,51 @@
     <xf numFmtId="0" fontId="3" fillId="0" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="4" fillId="0" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="5" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="1" fontId="4" fillId="0" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="164" fontId="4" fillId="0" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="165" fontId="6" fillId="0" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="2" fontId="4" fillId="0" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="10" fontId="4" fillId="0" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="165" fontId="7" fillId="0" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="164" fontId="6" fillId="3" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="164" fontId="7" fillId="4" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="164" fontId="7" fillId="0" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="166" fontId="7" fillId="0" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="164" fontId="6" fillId="0" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="166" fontId="6" fillId="0" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="164" fontId="8" fillId="3" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="164" fontId="9" fillId="4" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="1" fontId="4" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="right"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="4" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="5" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="right"/>
+    </xf>
+    <xf numFmtId="165" fontId="6" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="right"/>
+    </xf>
+    <xf numFmtId="165" fontId="7" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="right"/>
+    </xf>
+    <xf numFmtId="165" fontId="4" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="right"/>
+    </xf>
+    <xf numFmtId="167" fontId="4" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="right"/>
+    </xf>
+    <xf numFmtId="167" fontId="6" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="right"/>
+    </xf>
+    <xf numFmtId="167" fontId="7" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="right"/>
+    </xf>
+    <xf numFmtId="2" fontId="4" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="right"/>
+    </xf>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0" hidden="0"/>
@@ -676,6 +805,1148 @@
 </worksheet>
 </file>
 
+<file path=xl/worksheets/sheet10.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr fitToPage="1"/>
+  </sheetPr>
+  <dimension ref="A1:O64"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <cols>
+    <col width="40" customWidth="1" min="1" max="1"/>
+    <col width="10" customWidth="1" min="2" max="2"/>
+    <col width="10" customWidth="1" min="3" max="3"/>
+    <col width="10" customWidth="1" min="4" max="4"/>
+    <col width="10" customWidth="1" min="5" max="5"/>
+    <col width="10" customWidth="1" min="6" max="6"/>
+    <col width="10" customWidth="1" min="7" max="7"/>
+    <col width="15" customWidth="1" min="8" max="8"/>
+    <col width="15" customWidth="1" min="9" max="9"/>
+    <col width="10" customWidth="1" min="10" max="10"/>
+    <col width="10" customWidth="1" min="11" max="11"/>
+    <col width="10" customWidth="1" min="12" max="12"/>
+    <col width="10" customWidth="1" min="13" max="13"/>
+    <col width="10" customWidth="1" min="14" max="14"/>
+    <col width="15" customWidth="1" min="15" max="15"/>
+  </cols>
+  <sheetData>
+    <row r="1">
+      <c r="A1" s="1" t="inlineStr">
+        <is>
+          <t>BACKTEST ALL INDICES -- PAPER TRADE, NOT REAL MONEY</t>
+        </is>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" s="13" t="inlineStr">
+        <is>
+          <t>MONTHLY returns (% of capital at start of month)</t>
+        </is>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" s="2" t="inlineStr">
+        <is>
+          <t>Year</t>
+        </is>
+      </c>
+      <c r="B4" s="2" t="inlineStr">
+        <is>
+          <t>Jan</t>
+        </is>
+      </c>
+      <c r="C4" s="2" t="inlineStr">
+        <is>
+          <t>Feb</t>
+        </is>
+      </c>
+      <c r="D4" s="2" t="inlineStr">
+        <is>
+          <t>Mar</t>
+        </is>
+      </c>
+      <c r="E4" s="2" t="inlineStr">
+        <is>
+          <t>Apr</t>
+        </is>
+      </c>
+      <c r="F4" s="2" t="inlineStr">
+        <is>
+          <t>May</t>
+        </is>
+      </c>
+      <c r="G4" s="2" t="inlineStr">
+        <is>
+          <t>Jun</t>
+        </is>
+      </c>
+      <c r="H4" s="2" t="inlineStr">
+        <is>
+          <t>Jul</t>
+        </is>
+      </c>
+      <c r="I4" s="2" t="inlineStr">
+        <is>
+          <t>Aug</t>
+        </is>
+      </c>
+      <c r="J4" s="2" t="inlineStr">
+        <is>
+          <t>Sep</t>
+        </is>
+      </c>
+      <c r="K4" s="2" t="inlineStr">
+        <is>
+          <t>Oct</t>
+        </is>
+      </c>
+      <c r="L4" s="2" t="inlineStr">
+        <is>
+          <t>Nov</t>
+        </is>
+      </c>
+      <c r="M4" s="2" t="inlineStr">
+        <is>
+          <t>Dec</t>
+        </is>
+      </c>
+      <c r="N4" s="2" t="inlineStr">
+        <is>
+          <t>Yr %</t>
+        </is>
+      </c>
+      <c r="O4" s="2" t="inlineStr">
+        <is>
+          <t>Yr P&amp;L (Rs)</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" s="3" t="n">
+        <v>2025</v>
+      </c>
+      <c r="B5" s="6" t="n"/>
+      <c r="C5" s="6" t="n"/>
+      <c r="D5" s="6" t="n"/>
+      <c r="E5" s="6" t="n"/>
+      <c r="F5" s="6" t="n"/>
+      <c r="G5" s="6" t="n"/>
+      <c r="H5" s="6" t="n"/>
+      <c r="I5" s="6" t="n"/>
+      <c r="J5" s="6" t="n"/>
+      <c r="K5" s="14" t="n">
+        <v>0.001868000000000001</v>
+      </c>
+      <c r="L5" s="15" t="n">
+        <v>-0.01919514347199431</v>
+      </c>
+      <c r="M5" s="15" t="n">
+        <v>-0.06368475846116115</v>
+      </c>
+      <c r="N5" s="16" t="n">
+        <v>-0.07994200000000007</v>
+      </c>
+      <c r="O5" s="17" t="n">
+        <v>-1598.84</v>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" s="3" t="n">
+        <v>2026</v>
+      </c>
+      <c r="B6" s="15" t="n">
+        <v>-0.03431848861702198</v>
+      </c>
+      <c r="C6" s="14" t="n">
+        <v>0.02423287783784272</v>
+      </c>
+      <c r="D6" s="6" t="n"/>
+      <c r="E6" s="15" t="n">
+        <v>-0.01347122872352993</v>
+      </c>
+      <c r="F6" s="6" t="n"/>
+      <c r="G6" s="14" t="n">
+        <v>0.03094387162637448</v>
+      </c>
+      <c r="H6" s="6" t="n"/>
+      <c r="I6" s="15" t="n">
+        <v>-0.05060049085150257</v>
+      </c>
+      <c r="J6" s="15" t="n">
+        <v>-0.01316202762711363</v>
+      </c>
+      <c r="K6" s="6" t="n"/>
+      <c r="L6" s="6" t="n"/>
+      <c r="M6" s="6" t="n"/>
+      <c r="N6" s="16" t="n">
+        <v>-0.05751974332052978</v>
+      </c>
+      <c r="O6" s="17" t="n">
+        <v>-1058.43</v>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" s="3" t="inlineStr">
+        <is>
+          <t>Avg</t>
+        </is>
+      </c>
+      <c r="B7" s="16" t="n">
+        <v>-0.03431848861702198</v>
+      </c>
+      <c r="C7" s="18" t="n">
+        <v>0.02423287783784272</v>
+      </c>
+      <c r="D7" s="6" t="n"/>
+      <c r="E7" s="16" t="n">
+        <v>-0.01347122872352993</v>
+      </c>
+      <c r="F7" s="6" t="n"/>
+      <c r="G7" s="18" t="n">
+        <v>0.03094387162637448</v>
+      </c>
+      <c r="H7" s="6" t="n"/>
+      <c r="I7" s="16" t="n">
+        <v>-0.05060049085150257</v>
+      </c>
+      <c r="J7" s="16" t="n">
+        <v>-0.01316202762711363</v>
+      </c>
+      <c r="K7" s="18" t="n">
+        <v>0.001868000000000001</v>
+      </c>
+      <c r="L7" s="16" t="n">
+        <v>-0.01919514347199431</v>
+      </c>
+      <c r="M7" s="16" t="n">
+        <v>-0.06368475846116115</v>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" s="13" t="inlineStr">
+        <is>
+          <t>WEEKLY returns (% of capital at start of that week; weeks split at month edges)</t>
+        </is>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" s="2" t="inlineStr">
+        <is>
+          <t>Month</t>
+        </is>
+      </c>
+      <c r="B10" s="2" t="inlineStr">
+        <is>
+          <t>W1</t>
+        </is>
+      </c>
+      <c r="C10" s="2" t="inlineStr">
+        <is>
+          <t>W2</t>
+        </is>
+      </c>
+      <c r="D10" s="2" t="inlineStr">
+        <is>
+          <t>W3</t>
+        </is>
+      </c>
+      <c r="E10" s="2" t="inlineStr">
+        <is>
+          <t>W4</t>
+        </is>
+      </c>
+      <c r="F10" s="2" t="inlineStr">
+        <is>
+          <t>W5</t>
+        </is>
+      </c>
+      <c r="G10" s="2" t="inlineStr">
+        <is>
+          <t>W6</t>
+        </is>
+      </c>
+      <c r="H10" s="2" t="inlineStr">
+        <is>
+          <t>Month %</t>
+        </is>
+      </c>
+      <c r="I10" s="2" t="inlineStr">
+        <is>
+          <t>Month P&amp;L (Rs)</t>
+        </is>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" s="3" t="inlineStr">
+        <is>
+          <t>2025-Oct</t>
+        </is>
+      </c>
+      <c r="B11" s="14" t="n">
+        <v>0.0154865</v>
+      </c>
+      <c r="C11" s="15" t="n">
+        <v>-0.0134108134376971</v>
+      </c>
+      <c r="D11" s="6" t="n"/>
+      <c r="E11" s="6" t="n"/>
+      <c r="F11" s="6" t="n"/>
+      <c r="G11" s="6" t="n"/>
+      <c r="H11" s="20" t="n">
+        <v>0.001868000000000001</v>
+      </c>
+      <c r="I11" s="19" t="n">
+        <v>37.36</v>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" s="3" t="inlineStr">
+        <is>
+          <t>2025-Nov</t>
+        </is>
+      </c>
+      <c r="B12" s="15" t="n">
+        <v>-0.01630703845217134</v>
+      </c>
+      <c r="C12" s="15" t="n">
+        <v>-0.002935982194361311</v>
+      </c>
+      <c r="D12" s="6" t="n"/>
+      <c r="E12" s="6" t="n"/>
+      <c r="F12" s="6" t="n"/>
+      <c r="G12" s="6" t="n"/>
+      <c r="H12" s="21" t="n">
+        <v>-0.01919514347199431</v>
+      </c>
+      <c r="I12" s="17" t="n">
+        <v>-384.62</v>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" s="3" t="inlineStr">
+        <is>
+          <t>2025-Dec</t>
+        </is>
+      </c>
+      <c r="B13" s="15" t="n">
+        <v>-0.02755290102041751</v>
+      </c>
+      <c r="C13" s="15" t="n">
+        <v>-0.03715560206684546</v>
+      </c>
+      <c r="D13" s="6" t="n"/>
+      <c r="E13" s="6" t="n"/>
+      <c r="F13" s="6" t="n"/>
+      <c r="G13" s="6" t="n"/>
+      <c r="H13" s="21" t="n">
+        <v>-0.06368475846116115</v>
+      </c>
+      <c r="I13" s="17" t="n">
+        <v>-1251.58</v>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" s="3" t="inlineStr">
+        <is>
+          <t>2026-Jan</t>
+        </is>
+      </c>
+      <c r="B14" s="14" t="n">
+        <v>0.01397574935493198</v>
+      </c>
+      <c r="C14" s="15" t="n">
+        <v>-0.04762859269827473</v>
+      </c>
+      <c r="D14" s="6" t="n"/>
+      <c r="E14" s="6" t="n"/>
+      <c r="F14" s="6" t="n"/>
+      <c r="G14" s="6" t="n"/>
+      <c r="H14" s="21" t="n">
+        <v>-0.03431848861702198</v>
+      </c>
+      <c r="I14" s="17" t="n">
+        <v>-631.5</v>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" s="3" t="inlineStr">
+        <is>
+          <t>2026-Feb</t>
+        </is>
+      </c>
+      <c r="B15" s="14" t="n">
+        <v>0.02423287783784272</v>
+      </c>
+      <c r="C15" s="6" t="n"/>
+      <c r="D15" s="6" t="n"/>
+      <c r="E15" s="6" t="n"/>
+      <c r="F15" s="6" t="n"/>
+      <c r="G15" s="6" t="n"/>
+      <c r="H15" s="20" t="n">
+        <v>0.02423287783784272</v>
+      </c>
+      <c r="I15" s="19" t="n">
+        <v>430.61</v>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" s="3" t="inlineStr">
+        <is>
+          <t>2026-Apr</t>
+        </is>
+      </c>
+      <c r="B16" s="15" t="n">
+        <v>-0.01347122872352993</v>
+      </c>
+      <c r="C16" s="6" t="n"/>
+      <c r="D16" s="6" t="n"/>
+      <c r="E16" s="6" t="n"/>
+      <c r="F16" s="6" t="n"/>
+      <c r="G16" s="6" t="n"/>
+      <c r="H16" s="21" t="n">
+        <v>-0.01347122872352993</v>
+      </c>
+      <c r="I16" s="17" t="n">
+        <v>-245.18</v>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" s="3" t="inlineStr">
+        <is>
+          <t>2026-Jun</t>
+        </is>
+      </c>
+      <c r="B17" s="14" t="n">
+        <v>0.01436417194232945</v>
+      </c>
+      <c r="C17" s="14" t="n">
+        <v>0.01634491846483281</v>
+      </c>
+      <c r="D17" s="6" t="n"/>
+      <c r="E17" s="6" t="n"/>
+      <c r="F17" s="6" t="n"/>
+      <c r="G17" s="6" t="n"/>
+      <c r="H17" s="20" t="n">
+        <v>0.03094387162637448</v>
+      </c>
+      <c r="I17" s="19" t="n">
+        <v>555.6</v>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" s="3" t="inlineStr">
+        <is>
+          <t>2026-Aug</t>
+        </is>
+      </c>
+      <c r="B18" s="15" t="n">
+        <v>-0.03910335055041169</v>
+      </c>
+      <c r="C18" s="15" t="n">
+        <v>-0.01196501237430328</v>
+      </c>
+      <c r="D18" s="6" t="n"/>
+      <c r="E18" s="6" t="n"/>
+      <c r="F18" s="6" t="n"/>
+      <c r="G18" s="6" t="n"/>
+      <c r="H18" s="21" t="n">
+        <v>-0.05060049085150257</v>
+      </c>
+      <c r="I18" s="17" t="n">
+        <v>-936.65</v>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" s="3" t="inlineStr">
+        <is>
+          <t>2026-Sep</t>
+        </is>
+      </c>
+      <c r="B19" s="15" t="n">
+        <v>-0.01316202762711363</v>
+      </c>
+      <c r="C19" s="6" t="n"/>
+      <c r="D19" s="6" t="n"/>
+      <c r="E19" s="6" t="n"/>
+      <c r="F19" s="6" t="n"/>
+      <c r="G19" s="6" t="n"/>
+      <c r="H19" s="21" t="n">
+        <v>-0.01316202762711363</v>
+      </c>
+      <c r="I19" s="17" t="n">
+        <v>-231.31</v>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" s="13" t="inlineStr">
+        <is>
+          <t>DAILY returns (% of capital at start of that day; blank = no trade that day)</t>
+        </is>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" s="2" t="inlineStr">
+        <is>
+          <t>Week starting (Mon)</t>
+        </is>
+      </c>
+      <c r="B22" s="2" t="inlineStr">
+        <is>
+          <t>Mon</t>
+        </is>
+      </c>
+      <c r="C22" s="2" t="inlineStr">
+        <is>
+          <t>Tue</t>
+        </is>
+      </c>
+      <c r="D22" s="2" t="inlineStr">
+        <is>
+          <t>Wed</t>
+        </is>
+      </c>
+      <c r="E22" s="2" t="inlineStr">
+        <is>
+          <t>Thu</t>
+        </is>
+      </c>
+      <c r="F22" s="2" t="inlineStr">
+        <is>
+          <t>Fri</t>
+        </is>
+      </c>
+      <c r="G22" s="2" t="inlineStr">
+        <is>
+          <t>Week %</t>
+        </is>
+      </c>
+      <c r="H22" s="2" t="inlineStr">
+        <is>
+          <t>Week P&amp;L (Rs)</t>
+        </is>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" s="3" t="inlineStr">
+        <is>
+          <t>06-Oct-2025</t>
+        </is>
+      </c>
+      <c r="B23" s="14" t="n">
+        <v>0.0154865</v>
+      </c>
+      <c r="C23" s="6" t="n"/>
+      <c r="D23" s="6" t="n"/>
+      <c r="E23" s="6" t="n"/>
+      <c r="F23" s="6" t="n"/>
+      <c r="G23" s="20" t="n">
+        <v>0.0154865</v>
+      </c>
+      <c r="H23" s="19" t="n">
+        <v>309.73</v>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24" s="3" t="inlineStr">
+        <is>
+          <t>13-Oct-2025</t>
+        </is>
+      </c>
+      <c r="B24" s="6" t="n"/>
+      <c r="C24" s="15" t="n">
+        <v>-0.0134108134376971</v>
+      </c>
+      <c r="D24" s="6" t="n"/>
+      <c r="E24" s="6" t="n"/>
+      <c r="F24" s="6" t="n"/>
+      <c r="G24" s="21" t="n">
+        <v>-0.0134108134376971</v>
+      </c>
+      <c r="H24" s="17" t="n">
+        <v>-272.37</v>
+      </c>
+    </row>
+    <row r="25">
+      <c r="A25" s="3" t="inlineStr">
+        <is>
+          <t>10-Nov-2025</t>
+        </is>
+      </c>
+      <c r="B25" s="6" t="n"/>
+      <c r="C25" s="15" t="n">
+        <v>-0.01630703845217134</v>
+      </c>
+      <c r="D25" s="6" t="n"/>
+      <c r="E25" s="6" t="n"/>
+      <c r="F25" s="6" t="n"/>
+      <c r="G25" s="21" t="n">
+        <v>-0.01630703845217134</v>
+      </c>
+      <c r="H25" s="17" t="n">
+        <v>-326.75</v>
+      </c>
+    </row>
+    <row r="26">
+      <c r="A26" s="3" t="inlineStr">
+        <is>
+          <t>24-Nov-2025</t>
+        </is>
+      </c>
+      <c r="B26" s="14" t="n">
+        <v>0.01547187022623856</v>
+      </c>
+      <c r="C26" s="15" t="n">
+        <v>-0.01812738782857545</v>
+      </c>
+      <c r="D26" s="6" t="n"/>
+      <c r="E26" s="6" t="n"/>
+      <c r="F26" s="6" t="n"/>
+      <c r="G26" s="21" t="n">
+        <v>-0.002935982194361311</v>
+      </c>
+      <c r="H26" s="17" t="n">
+        <v>-57.87</v>
+      </c>
+    </row>
+    <row r="27">
+      <c r="A27" s="3" t="inlineStr">
+        <is>
+          <t>08-Dec-2025</t>
+        </is>
+      </c>
+      <c r="B27" s="6" t="n"/>
+      <c r="C27" s="15" t="n">
+        <v>-0.02755290102041751</v>
+      </c>
+      <c r="D27" s="6" t="n"/>
+      <c r="E27" s="6" t="n"/>
+      <c r="F27" s="6" t="n"/>
+      <c r="G27" s="21" t="n">
+        <v>-0.02755290102041751</v>
+      </c>
+      <c r="H27" s="17" t="n">
+        <v>-541.49</v>
+      </c>
+    </row>
+    <row r="28">
+      <c r="A28" s="3" t="inlineStr">
+        <is>
+          <t>29-Dec-2025</t>
+        </is>
+      </c>
+      <c r="B28" s="6" t="n"/>
+      <c r="C28" s="15" t="n">
+        <v>-0.03715560206684546</v>
+      </c>
+      <c r="D28" s="6" t="n"/>
+      <c r="E28" s="6" t="n"/>
+      <c r="F28" s="6" t="n"/>
+      <c r="G28" s="21" t="n">
+        <v>-0.03715560206684546</v>
+      </c>
+      <c r="H28" s="17" t="n">
+        <v>-710.09</v>
+      </c>
+    </row>
+    <row r="29">
+      <c r="A29" s="3" t="inlineStr">
+        <is>
+          <t>12-Jan-2026</t>
+        </is>
+      </c>
+      <c r="B29" s="14" t="n">
+        <v>0.01397574935493198</v>
+      </c>
+      <c r="C29" s="6" t="n"/>
+      <c r="D29" s="6" t="n"/>
+      <c r="E29" s="6" t="n"/>
+      <c r="F29" s="6" t="n"/>
+      <c r="G29" s="20" t="n">
+        <v>0.01397574935493198</v>
+      </c>
+      <c r="H29" s="19" t="n">
+        <v>257.17</v>
+      </c>
+    </row>
+    <row r="30">
+      <c r="A30" s="3" t="inlineStr">
+        <is>
+          <t>26-Jan-2026</t>
+        </is>
+      </c>
+      <c r="B30" s="6" t="n"/>
+      <c r="C30" s="15" t="n">
+        <v>-0.04762859269827473</v>
+      </c>
+      <c r="D30" s="6" t="n"/>
+      <c r="E30" s="6" t="n"/>
+      <c r="F30" s="6" t="n"/>
+      <c r="G30" s="21" t="n">
+        <v>-0.02454989272887767</v>
+      </c>
+      <c r="H30" s="17" t="n">
+        <v>-458.06</v>
+      </c>
+    </row>
+    <row r="31">
+      <c r="A31" s="3" t="inlineStr">
+        <is>
+          <t>20-Apr-2026</t>
+        </is>
+      </c>
+      <c r="B31" s="15" t="n">
+        <v>-0.01347122872352993</v>
+      </c>
+      <c r="C31" s="6" t="n"/>
+      <c r="D31" s="6" t="n"/>
+      <c r="E31" s="6" t="n"/>
+      <c r="F31" s="6" t="n"/>
+      <c r="G31" s="21" t="n">
+        <v>-0.01347122872352993</v>
+      </c>
+      <c r="H31" s="17" t="n">
+        <v>-245.18</v>
+      </c>
+    </row>
+    <row r="32">
+      <c r="A32" s="3" t="inlineStr">
+        <is>
+          <t>01-Jun-2026</t>
+        </is>
+      </c>
+      <c r="B32" s="14" t="n">
+        <v>0.01436417194232945</v>
+      </c>
+      <c r="C32" s="6" t="n"/>
+      <c r="D32" s="6" t="n"/>
+      <c r="E32" s="6" t="n"/>
+      <c r="F32" s="6" t="n"/>
+      <c r="G32" s="20" t="n">
+        <v>0.01436417194232945</v>
+      </c>
+      <c r="H32" s="19" t="n">
+        <v>257.91</v>
+      </c>
+    </row>
+    <row r="33">
+      <c r="A33" s="3" t="inlineStr">
+        <is>
+          <t>29-Jun-2026</t>
+        </is>
+      </c>
+      <c r="B33" s="14" t="n">
+        <v>0.01634491846483281</v>
+      </c>
+      <c r="C33" s="6" t="n"/>
+      <c r="D33" s="6" t="n"/>
+      <c r="E33" s="6" t="n"/>
+      <c r="F33" s="6" t="n"/>
+      <c r="G33" s="20" t="n">
+        <v>0.01634491846483281</v>
+      </c>
+      <c r="H33" s="19" t="n">
+        <v>297.69</v>
+      </c>
+    </row>
+    <row r="34">
+      <c r="A34" s="3" t="inlineStr">
+        <is>
+          <t>10-Aug-2026</t>
+        </is>
+      </c>
+      <c r="B34" s="6" t="n"/>
+      <c r="C34" s="15" t="n">
+        <v>-0.03910335055041169</v>
+      </c>
+      <c r="D34" s="6" t="n"/>
+      <c r="E34" s="6" t="n"/>
+      <c r="F34" s="6" t="n"/>
+      <c r="G34" s="21" t="n">
+        <v>-0.03910335055041169</v>
+      </c>
+      <c r="H34" s="17" t="n">
+        <v>-723.83</v>
+      </c>
+    </row>
+    <row r="35">
+      <c r="A35" s="3" t="inlineStr">
+        <is>
+          <t>24-Aug-2026</t>
+        </is>
+      </c>
+      <c r="B35" s="6" t="n"/>
+      <c r="C35" s="15" t="n">
+        <v>-0.01196501237430328</v>
+      </c>
+      <c r="D35" s="6" t="n"/>
+      <c r="E35" s="6" t="n"/>
+      <c r="F35" s="6" t="n"/>
+      <c r="G35" s="21" t="n">
+        <v>-0.01196501237430328</v>
+      </c>
+      <c r="H35" s="17" t="n">
+        <v>-212.82</v>
+      </c>
+    </row>
+    <row r="36">
+      <c r="A36" s="3" t="inlineStr">
+        <is>
+          <t>07-Sep-2026</t>
+        </is>
+      </c>
+      <c r="B36" s="6" t="n"/>
+      <c r="C36" s="15" t="n">
+        <v>-0.01316202762711363</v>
+      </c>
+      <c r="D36" s="6" t="n"/>
+      <c r="E36" s="6" t="n"/>
+      <c r="F36" s="6" t="n"/>
+      <c r="G36" s="21" t="n">
+        <v>-0.01316202762711363</v>
+      </c>
+      <c r="H36" s="17" t="n">
+        <v>-231.31</v>
+      </c>
+    </row>
+    <row r="38">
+      <c r="A38" s="13" t="inlineStr">
+        <is>
+          <t>STATISTICS (all trades for this index)</t>
+        </is>
+      </c>
+    </row>
+    <row r="39">
+      <c r="A39" s="3" t="inlineStr">
+        <is>
+          <t>All trades</t>
+        </is>
+      </c>
+      <c r="B39" s="22" t="n">
+        <v>23</v>
+      </c>
+      <c r="C39" s="23" t="n"/>
+      <c r="D39" s="24" t="n"/>
+    </row>
+    <row r="40">
+      <c r="A40" s="3" t="inlineStr">
+        <is>
+          <t>Winners</t>
+        </is>
+      </c>
+      <c r="B40" s="25" t="inlineStr">
+        <is>
+          <t>7 (30.4%)</t>
+        </is>
+      </c>
+      <c r="C40" s="23" t="n"/>
+      <c r="D40" s="24" t="n"/>
+    </row>
+    <row r="41">
+      <c r="A41" s="3" t="inlineStr">
+        <is>
+          <t>Losers</t>
+        </is>
+      </c>
+      <c r="B41" s="25" t="inlineStr">
+        <is>
+          <t>16 (69.6%)</t>
+        </is>
+      </c>
+      <c r="C41" s="23" t="n"/>
+      <c r="D41" s="24" t="n"/>
+    </row>
+    <row r="42">
+      <c r="A42" s="3" t="inlineStr">
+        <is>
+          <t>Net P&amp;L (Rs)</t>
+        </is>
+      </c>
+      <c r="B42" s="27" t="n">
+        <v>-2657.27</v>
+      </c>
+      <c r="C42" s="23" t="n"/>
+      <c r="D42" s="24" t="n"/>
+    </row>
+    <row r="43">
+      <c r="A43" s="3" t="inlineStr">
+        <is>
+          <t>Total Profit (Rs)</t>
+        </is>
+      </c>
+      <c r="B43" s="26" t="n">
+        <v>2174.65</v>
+      </c>
+      <c r="C43" s="23" t="n"/>
+      <c r="D43" s="24" t="n"/>
+    </row>
+    <row r="44">
+      <c r="A44" s="3" t="inlineStr">
+        <is>
+          <t>Total Loss (Rs)</t>
+        </is>
+      </c>
+      <c r="B44" s="27" t="n">
+        <v>-4831.92</v>
+      </c>
+      <c r="C44" s="23" t="n"/>
+      <c r="D44" s="24" t="n"/>
+    </row>
+    <row r="45">
+      <c r="A45" s="3" t="inlineStr">
+        <is>
+          <t>Transaction costs (Rs)</t>
+        </is>
+      </c>
+      <c r="B45" s="28" t="n">
+        <v>1462.97</v>
+      </c>
+      <c r="C45" s="23" t="n"/>
+      <c r="D45" s="24" t="n"/>
+    </row>
+    <row r="46">
+      <c r="A46" s="3" t="inlineStr">
+        <is>
+          <t>Avg Profit/Loss per trade (Rs)</t>
+        </is>
+      </c>
+      <c r="B46" s="27" t="n">
+        <v>-115.53</v>
+      </c>
+      <c r="C46" s="23" t="n"/>
+      <c r="D46" s="24" t="n"/>
+    </row>
+    <row r="47">
+      <c r="A47" s="3" t="inlineStr">
+        <is>
+          <t>Avg Profit/Loss per trade (% of premium)</t>
+        </is>
+      </c>
+      <c r="B47" s="29" t="n">
+        <v>-5.45</v>
+      </c>
+      <c r="C47" s="23" t="n"/>
+      <c r="D47" s="24" t="n"/>
+    </row>
+    <row r="48">
+      <c r="A48" s="3" t="inlineStr">
+        <is>
+          <t>Avg Win (Rs)</t>
+        </is>
+      </c>
+      <c r="B48" s="26" t="n">
+        <v>310.66</v>
+      </c>
+      <c r="C48" s="23" t="n"/>
+      <c r="D48" s="24" t="n"/>
+    </row>
+    <row r="49">
+      <c r="A49" s="3" t="inlineStr">
+        <is>
+          <t>Avg Win (% of premium)</t>
+        </is>
+      </c>
+      <c r="B49" s="30" t="n">
+        <v>16.01</v>
+      </c>
+      <c r="C49" s="23" t="n"/>
+      <c r="D49" s="24" t="n"/>
+    </row>
+    <row r="50">
+      <c r="A50" s="3" t="inlineStr">
+        <is>
+          <t>Avg Loss (Rs)</t>
+        </is>
+      </c>
+      <c r="B50" s="27" t="n">
+        <v>-302</v>
+      </c>
+      <c r="C50" s="23" t="n"/>
+      <c r="D50" s="24" t="n"/>
+    </row>
+    <row r="51">
+      <c r="A51" s="3" t="inlineStr">
+        <is>
+          <t>Avg Loss (% of premium)</t>
+        </is>
+      </c>
+      <c r="B51" s="31" t="n">
+        <v>-14.84</v>
+      </c>
+      <c r="C51" s="23" t="n"/>
+      <c r="D51" s="24" t="n"/>
+    </row>
+    <row r="52">
+      <c r="A52" s="3" t="inlineStr">
+        <is>
+          <t>Largest Win (Rs)</t>
+        </is>
+      </c>
+      <c r="B52" s="26" t="n">
+        <v>406.75</v>
+      </c>
+      <c r="C52" s="23" t="n"/>
+      <c r="D52" s="24" t="n"/>
+    </row>
+    <row r="53">
+      <c r="A53" s="3" t="inlineStr">
+        <is>
+          <t>Largest Loss (Rs)</t>
+        </is>
+      </c>
+      <c r="B53" s="27" t="n">
+        <v>-368.93</v>
+      </c>
+      <c r="C53" s="23" t="n"/>
+      <c r="D53" s="24" t="n"/>
+    </row>
+    <row r="54">
+      <c r="A54" s="3" t="inlineStr">
+        <is>
+          <t>Max Consecutive Wins</t>
+        </is>
+      </c>
+      <c r="B54" s="22" t="n">
+        <v>2</v>
+      </c>
+      <c r="C54" s="23" t="n"/>
+      <c r="D54" s="24" t="n"/>
+    </row>
+    <row r="55">
+      <c r="A55" s="3" t="inlineStr">
+        <is>
+          <t>Max Consecutive Losses</t>
+        </is>
+      </c>
+      <c r="B55" s="22" t="n">
+        <v>11</v>
+      </c>
+      <c r="C55" s="23" t="n"/>
+      <c r="D55" s="24" t="n"/>
+    </row>
+    <row r="56">
+      <c r="A56" s="3" t="inlineStr">
+        <is>
+          <t>Max trade drawdown (Rs)</t>
+        </is>
+      </c>
+      <c r="B56" s="27" t="n">
+        <v>-368.93</v>
+      </c>
+      <c r="C56" s="23" t="n"/>
+      <c r="D56" s="24" t="n"/>
+    </row>
+    <row r="57">
+      <c r="A57" s="3" t="inlineStr">
+        <is>
+          <t>Max system drawdown (Rs)</t>
+        </is>
+      </c>
+      <c r="B57" s="27" t="n">
+        <v>-3321.99</v>
+      </c>
+      <c r="C57" s="23" t="n"/>
+      <c r="D57" s="24" t="n"/>
+    </row>
+    <row r="58">
+      <c r="A58" s="3" t="inlineStr">
+        <is>
+          <t>Max system drawdown (%)</t>
+        </is>
+      </c>
+      <c r="B58" s="31" t="n">
+        <v>-16.08</v>
+      </c>
+      <c r="C58" s="23" t="n"/>
+      <c r="D58" s="24" t="n"/>
+    </row>
+    <row r="59">
+      <c r="A59" s="3" t="inlineStr">
+        <is>
+          <t>Recovery Factor</t>
+        </is>
+      </c>
+      <c r="B59" s="32" t="n">
+        <v>-0.8</v>
+      </c>
+      <c r="C59" s="23" t="n"/>
+      <c r="D59" s="24" t="n"/>
+    </row>
+    <row r="60">
+      <c r="A60" s="3" t="inlineStr">
+        <is>
+          <t>Profit Factor</t>
+        </is>
+      </c>
+      <c r="B60" s="32" t="n">
+        <v>0.45</v>
+      </c>
+      <c r="C60" s="23" t="n"/>
+      <c r="D60" s="24" t="n"/>
+    </row>
+    <row r="61">
+      <c r="A61" s="3" t="inlineStr">
+        <is>
+          <t>Payoff Ratio (avg win / avg loss)</t>
+        </is>
+      </c>
+      <c r="B61" s="32" t="n">
+        <v>1.03</v>
+      </c>
+      <c r="C61" s="23" t="n"/>
+      <c r="D61" s="24" t="n"/>
+    </row>
+    <row r="62">
+      <c r="A62" s="3" t="inlineStr">
+        <is>
+          <t>Sharpe Ratio (annualized)</t>
+        </is>
+      </c>
+      <c r="B62" s="32" t="n">
+        <v>-6.22</v>
+      </c>
+      <c r="C62" s="23" t="n"/>
+      <c r="D62" s="24" t="n"/>
+    </row>
+    <row r="64">
+      <c r="A64" s="5" t="inlineStr">
+        <is>
+          <t>Caveat: with only a handful of trades these numbers (Sharpe, profit factor, drawdown %) are not statistically reliable. Watch this over weeks/months before drawing conclusions.</t>
+        </is>
+      </c>
+    </row>
+  </sheetData>
+  <mergeCells count="24">
+    <mergeCell ref="B42:D42"/>
+    <mergeCell ref="B60:D60"/>
+    <mergeCell ref="B61:D61"/>
+    <mergeCell ref="B57:D57"/>
+    <mergeCell ref="B44:D44"/>
+    <mergeCell ref="B53:D53"/>
+    <mergeCell ref="B49:D49"/>
+    <mergeCell ref="B40:D40"/>
+    <mergeCell ref="B55:D55"/>
+    <mergeCell ref="B51:D51"/>
+    <mergeCell ref="B45:D45"/>
+    <mergeCell ref="B41:D41"/>
+    <mergeCell ref="B50:D50"/>
+    <mergeCell ref="B62:D62"/>
+    <mergeCell ref="B47:D47"/>
+    <mergeCell ref="B54:D54"/>
+    <mergeCell ref="B59:D59"/>
+    <mergeCell ref="B46:D46"/>
+    <mergeCell ref="B56:D56"/>
+    <mergeCell ref="B58:D58"/>
+    <mergeCell ref="B52:D52"/>
+    <mergeCell ref="B43:D43"/>
+    <mergeCell ref="B39:D39"/>
+    <mergeCell ref="B48:D48"/>
+  </mergeCells>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+  <pageSetup orientation="landscape" fitToHeight="0" fitToWidth="1"/>
+</worksheet>
+</file>
+
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr>
@@ -858,4 +2129,2760 @@
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
   <pageSetup orientation="landscape" fitToHeight="0" fitToWidth="1"/>
 </worksheet>
+</file>
+
+<file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr fitToPage="1"/>
+  </sheetPr>
+  <dimension ref="A1:G9"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <cols>
+    <col width="15" customWidth="1" min="1" max="1"/>
+    <col width="22" customWidth="1" min="2" max="2"/>
+    <col width="15" customWidth="1" min="3" max="3"/>
+    <col width="15" customWidth="1" min="4" max="4"/>
+    <col width="15" customWidth="1" min="5" max="5"/>
+    <col width="15" customWidth="1" min="6" max="6"/>
+    <col width="15" customWidth="1" min="7" max="7"/>
+  </cols>
+  <sheetData>
+    <row r="1">
+      <c r="A1" s="1" t="inlineStr">
+        <is>
+          <t>BACKTEST summary by index (best strategy per index) -- PAPER TRADE, NOT REAL MONEY</t>
+        </is>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" s="2" t="inlineStr">
+        <is>
+          <t>Index</t>
+        </is>
+      </c>
+      <c r="B3" s="2" t="inlineStr">
+        <is>
+          <t>Best Strategy</t>
+        </is>
+      </c>
+      <c r="C3" s="2" t="inlineStr">
+        <is>
+          <t>Trades</t>
+        </is>
+      </c>
+      <c r="D3" s="2" t="inlineStr">
+        <is>
+          <t>Win %</t>
+        </is>
+      </c>
+      <c r="E3" s="2" t="inlineStr">
+        <is>
+          <t>Net P&amp;L (Rs)</t>
+        </is>
+      </c>
+      <c r="F3" s="2" t="inlineStr">
+        <is>
+          <t>Profit Factor</t>
+        </is>
+      </c>
+      <c r="G3" s="2" t="inlineStr">
+        <is>
+          <t>Max DD (%)</t>
+        </is>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" s="3" t="inlineStr">
+        <is>
+          <t>NIFTY</t>
+        </is>
+      </c>
+      <c r="B4" s="6" t="inlineStr">
+        <is>
+          <t>trend_scalp_nw (EMA5/21) [5m]</t>
+        </is>
+      </c>
+      <c r="C4" s="7" t="n">
+        <v>13</v>
+      </c>
+      <c r="D4" s="8" t="n">
+        <v>0.5384615384615384</v>
+      </c>
+      <c r="E4" s="9" t="n">
+        <v>289.63</v>
+      </c>
+      <c r="F4" s="10" t="n">
+        <v>1.15</v>
+      </c>
+      <c r="G4" s="11" t="n">
+        <v>-0.02718449608801872</v>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" s="3" t="inlineStr">
+        <is>
+          <t>BANKNIFTY</t>
+        </is>
+      </c>
+      <c r="B5" s="6" t="inlineStr">
+        <is>
+          <t>trend_scalp_nw (EMA5/21) [5m]</t>
+        </is>
+      </c>
+      <c r="C5" s="7" t="n">
+        <v>5</v>
+      </c>
+      <c r="D5" s="8" t="n">
+        <v>0</v>
+      </c>
+      <c r="E5" s="12" t="n">
+        <v>-1614.72</v>
+      </c>
+      <c r="F5" s="10" t="n">
+        <v>0</v>
+      </c>
+      <c r="G5" s="11" t="n">
+        <v>-0.08073600000000006</v>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" s="3" t="inlineStr">
+        <is>
+          <t>FINNIFTY</t>
+        </is>
+      </c>
+      <c r="B6" s="6" t="inlineStr">
+        <is>
+          <t>trend_scalp_nw (EMA8/21) [5m]</t>
+        </is>
+      </c>
+      <c r="C6" s="7" t="n">
+        <v>5</v>
+      </c>
+      <c r="D6" s="8" t="n">
+        <v>0</v>
+      </c>
+      <c r="E6" s="12" t="n">
+        <v>-1332.18</v>
+      </c>
+      <c r="F6" s="10" t="n">
+        <v>0</v>
+      </c>
+      <c r="G6" s="11" t="n">
+        <v>-0.06660900000000002</v>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" s="3" t="inlineStr">
+        <is>
+          <t>ALL INDICES</t>
+        </is>
+      </c>
+      <c r="B7" s="6" t="inlineStr">
+        <is>
+          <t>(combined)</t>
+        </is>
+      </c>
+      <c r="C7" s="7" t="n">
+        <v>23</v>
+      </c>
+      <c r="D7" s="8" t="n">
+        <v>0.3043478260869565</v>
+      </c>
+      <c r="E7" s="12" t="n">
+        <v>-2657.27</v>
+      </c>
+      <c r="F7" s="10" t="n">
+        <v>0.45</v>
+      </c>
+      <c r="G7" s="11" t="n">
+        <v>-0.1607565938469046</v>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" s="5" t="inlineStr">
+        <is>
+          <t>BT- sheets are from the BACKTEST (each index's single best combo, so time periods aren't double-counted across competing strategies). Plain-named sheets are LIVE paper trades. See latest_backtest_summary.xlsx for every combo tested.</t>
+        </is>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+  <pageSetup orientation="landscape" fitToHeight="0" fitToWidth="1"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet7.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr fitToPage="1"/>
+  </sheetPr>
+  <dimension ref="A1:O57"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <cols>
+    <col width="40" customWidth="1" min="1" max="1"/>
+    <col width="10" customWidth="1" min="2" max="2"/>
+    <col width="10" customWidth="1" min="3" max="3"/>
+    <col width="10" customWidth="1" min="4" max="4"/>
+    <col width="10" customWidth="1" min="5" max="5"/>
+    <col width="10" customWidth="1" min="6" max="6"/>
+    <col width="10" customWidth="1" min="7" max="7"/>
+    <col width="15" customWidth="1" min="8" max="8"/>
+    <col width="15" customWidth="1" min="9" max="9"/>
+    <col width="10" customWidth="1" min="10" max="10"/>
+    <col width="10" customWidth="1" min="11" max="11"/>
+    <col width="10" customWidth="1" min="12" max="12"/>
+    <col width="10" customWidth="1" min="13" max="13"/>
+    <col width="10" customWidth="1" min="14" max="14"/>
+    <col width="15" customWidth="1" min="15" max="15"/>
+  </cols>
+  <sheetData>
+    <row r="1">
+      <c r="A1" s="1" t="inlineStr">
+        <is>
+          <t>BACKTEST NIFTY -- best: trend_scalp_nw (EMA5/21) [5m] -- PAPER TRADE, NOT REAL MONEY</t>
+        </is>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" s="13" t="inlineStr">
+        <is>
+          <t>MONTHLY returns (% of capital at start of month)</t>
+        </is>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" s="2" t="inlineStr">
+        <is>
+          <t>Year</t>
+        </is>
+      </c>
+      <c r="B4" s="2" t="inlineStr">
+        <is>
+          <t>Jan</t>
+        </is>
+      </c>
+      <c r="C4" s="2" t="inlineStr">
+        <is>
+          <t>Feb</t>
+        </is>
+      </c>
+      <c r="D4" s="2" t="inlineStr">
+        <is>
+          <t>Mar</t>
+        </is>
+      </c>
+      <c r="E4" s="2" t="inlineStr">
+        <is>
+          <t>Apr</t>
+        </is>
+      </c>
+      <c r="F4" s="2" t="inlineStr">
+        <is>
+          <t>May</t>
+        </is>
+      </c>
+      <c r="G4" s="2" t="inlineStr">
+        <is>
+          <t>Jun</t>
+        </is>
+      </c>
+      <c r="H4" s="2" t="inlineStr">
+        <is>
+          <t>Jul</t>
+        </is>
+      </c>
+      <c r="I4" s="2" t="inlineStr">
+        <is>
+          <t>Aug</t>
+        </is>
+      </c>
+      <c r="J4" s="2" t="inlineStr">
+        <is>
+          <t>Sep</t>
+        </is>
+      </c>
+      <c r="K4" s="2" t="inlineStr">
+        <is>
+          <t>Oct</t>
+        </is>
+      </c>
+      <c r="L4" s="2" t="inlineStr">
+        <is>
+          <t>Nov</t>
+        </is>
+      </c>
+      <c r="M4" s="2" t="inlineStr">
+        <is>
+          <t>Dec</t>
+        </is>
+      </c>
+      <c r="N4" s="2" t="inlineStr">
+        <is>
+          <t>Yr %</t>
+        </is>
+      </c>
+      <c r="O4" s="2" t="inlineStr">
+        <is>
+          <t>Yr P&amp;L (Rs)</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" s="3" t="n">
+        <v>2025</v>
+      </c>
+      <c r="B5" s="6" t="n"/>
+      <c r="C5" s="6" t="n"/>
+      <c r="D5" s="6" t="n"/>
+      <c r="E5" s="6" t="n"/>
+      <c r="F5" s="6" t="n"/>
+      <c r="G5" s="6" t="n"/>
+      <c r="H5" s="6" t="n"/>
+      <c r="I5" s="6" t="n"/>
+      <c r="J5" s="6" t="n"/>
+      <c r="K5" s="14" t="n">
+        <v>0.0154865</v>
+      </c>
+      <c r="L5" s="15" t="n">
+        <v>-0.01893772098398157</v>
+      </c>
+      <c r="M5" s="6" t="n"/>
+      <c r="N5" s="16" t="n">
+        <v>-0.003744500000000039</v>
+      </c>
+      <c r="O5" s="17" t="n">
+        <v>-74.89</v>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" s="3" t="n">
+        <v>2026</v>
+      </c>
+      <c r="B6" s="15" t="n">
+        <v>-0.0003804244995385213</v>
+      </c>
+      <c r="C6" s="14" t="n">
+        <v>0.02161964862108907</v>
+      </c>
+      <c r="D6" s="6" t="n"/>
+      <c r="E6" s="15" t="n">
+        <v>-0.01204925855631031</v>
+      </c>
+      <c r="F6" s="6" t="n"/>
+      <c r="G6" s="14" t="n">
+        <v>0.02763772101222905</v>
+      </c>
+      <c r="H6" s="6" t="n"/>
+      <c r="I6" s="15" t="n">
+        <v>-0.01785845673657797</v>
+      </c>
+      <c r="J6" s="6" t="n"/>
+      <c r="K6" s="6" t="n"/>
+      <c r="L6" s="6" t="n"/>
+      <c r="M6" s="6" t="n"/>
+      <c r="N6" s="18" t="n">
+        <v>0.01829450376936426</v>
+      </c>
+      <c r="O6" s="19" t="n">
+        <v>364.52</v>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" s="3" t="inlineStr">
+        <is>
+          <t>Avg</t>
+        </is>
+      </c>
+      <c r="B7" s="16" t="n">
+        <v>-0.0003804244995385213</v>
+      </c>
+      <c r="C7" s="18" t="n">
+        <v>0.02161964862108907</v>
+      </c>
+      <c r="D7" s="6" t="n"/>
+      <c r="E7" s="16" t="n">
+        <v>-0.01204925855631031</v>
+      </c>
+      <c r="F7" s="6" t="n"/>
+      <c r="G7" s="18" t="n">
+        <v>0.02763772101222905</v>
+      </c>
+      <c r="H7" s="6" t="n"/>
+      <c r="I7" s="16" t="n">
+        <v>-0.01785845673657797</v>
+      </c>
+      <c r="J7" s="6" t="n"/>
+      <c r="K7" s="18" t="n">
+        <v>0.0154865</v>
+      </c>
+      <c r="L7" s="16" t="n">
+        <v>-0.01893772098398157</v>
+      </c>
+      <c r="M7" s="6" t="n"/>
+    </row>
+    <row r="9">
+      <c r="A9" s="13" t="inlineStr">
+        <is>
+          <t>WEEKLY returns (% of capital at start of that week; weeks split at month edges)</t>
+        </is>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" s="2" t="inlineStr">
+        <is>
+          <t>Month</t>
+        </is>
+      </c>
+      <c r="B10" s="2" t="inlineStr">
+        <is>
+          <t>W1</t>
+        </is>
+      </c>
+      <c r="C10" s="2" t="inlineStr">
+        <is>
+          <t>W2</t>
+        </is>
+      </c>
+      <c r="D10" s="2" t="inlineStr">
+        <is>
+          <t>W3</t>
+        </is>
+      </c>
+      <c r="E10" s="2" t="inlineStr">
+        <is>
+          <t>W4</t>
+        </is>
+      </c>
+      <c r="F10" s="2" t="inlineStr">
+        <is>
+          <t>W5</t>
+        </is>
+      </c>
+      <c r="G10" s="2" t="inlineStr">
+        <is>
+          <t>W6</t>
+        </is>
+      </c>
+      <c r="H10" s="2" t="inlineStr">
+        <is>
+          <t>Month %</t>
+        </is>
+      </c>
+      <c r="I10" s="2" t="inlineStr">
+        <is>
+          <t>Month P&amp;L (Rs)</t>
+        </is>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" s="3" t="inlineStr">
+        <is>
+          <t>2025-Oct</t>
+        </is>
+      </c>
+      <c r="B11" s="14" t="n">
+        <v>0.0154865</v>
+      </c>
+      <c r="C11" s="6" t="n"/>
+      <c r="D11" s="6" t="n"/>
+      <c r="E11" s="6" t="n"/>
+      <c r="F11" s="6" t="n"/>
+      <c r="G11" s="6" t="n"/>
+      <c r="H11" s="20" t="n">
+        <v>0.0154865</v>
+      </c>
+      <c r="I11" s="19" t="n">
+        <v>309.73</v>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" s="3" t="inlineStr">
+        <is>
+          <t>2025-Nov</t>
+        </is>
+      </c>
+      <c r="B12" s="15" t="n">
+        <v>-0.01608834780176792</v>
+      </c>
+      <c r="C12" s="15" t="n">
+        <v>-0.002895964465760363</v>
+      </c>
+      <c r="D12" s="6" t="n"/>
+      <c r="E12" s="6" t="n"/>
+      <c r="F12" s="6" t="n"/>
+      <c r="G12" s="6" t="n"/>
+      <c r="H12" s="21" t="n">
+        <v>-0.01893772098398157</v>
+      </c>
+      <c r="I12" s="17" t="n">
+        <v>-384.62</v>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" s="3" t="inlineStr">
+        <is>
+          <t>2026-Jan</t>
+        </is>
+      </c>
+      <c r="B13" s="14" t="n">
+        <v>0.01290682962352529</v>
+      </c>
+      <c r="C13" s="15" t="n">
+        <v>-0.01311794306688838</v>
+      </c>
+      <c r="D13" s="6" t="n"/>
+      <c r="E13" s="6" t="n"/>
+      <c r="F13" s="6" t="n"/>
+      <c r="G13" s="6" t="n"/>
+      <c r="H13" s="21" t="n">
+        <v>-0.0003804244995385213</v>
+      </c>
+      <c r="I13" s="17" t="n">
+        <v>-7.58</v>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" s="3" t="inlineStr">
+        <is>
+          <t>2026-Feb</t>
+        </is>
+      </c>
+      <c r="B14" s="14" t="n">
+        <v>0.02161964862108907</v>
+      </c>
+      <c r="C14" s="6" t="n"/>
+      <c r="D14" s="6" t="n"/>
+      <c r="E14" s="6" t="n"/>
+      <c r="F14" s="6" t="n"/>
+      <c r="G14" s="6" t="n"/>
+      <c r="H14" s="20" t="n">
+        <v>0.02161964862108907</v>
+      </c>
+      <c r="I14" s="19" t="n">
+        <v>430.61</v>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" s="3" t="inlineStr">
+        <is>
+          <t>2026-Apr</t>
+        </is>
+      </c>
+      <c r="B15" s="15" t="n">
+        <v>-0.01204925855631031</v>
+      </c>
+      <c r="C15" s="6" t="n"/>
+      <c r="D15" s="6" t="n"/>
+      <c r="E15" s="6" t="n"/>
+      <c r="F15" s="6" t="n"/>
+      <c r="G15" s="6" t="n"/>
+      <c r="H15" s="21" t="n">
+        <v>-0.01204925855631031</v>
+      </c>
+      <c r="I15" s="17" t="n">
+        <v>-245.18</v>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" s="3" t="inlineStr">
+        <is>
+          <t>2026-Jun</t>
+        </is>
+      </c>
+      <c r="B16" s="14" t="n">
+        <v>0.01282945397095752</v>
+      </c>
+      <c r="C16" s="14" t="n">
+        <v>0.01462069155198182</v>
+      </c>
+      <c r="D16" s="6" t="n"/>
+      <c r="E16" s="6" t="n"/>
+      <c r="F16" s="6" t="n"/>
+      <c r="G16" s="6" t="n"/>
+      <c r="H16" s="20" t="n">
+        <v>0.02763772101222905</v>
+      </c>
+      <c r="I16" s="19" t="n">
+        <v>555.6</v>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" s="3" t="inlineStr">
+        <is>
+          <t>2026-Aug</t>
+        </is>
+      </c>
+      <c r="B17" s="15" t="n">
+        <v>-0.01785845673657797</v>
+      </c>
+      <c r="C17" s="6" t="n"/>
+      <c r="D17" s="6" t="n"/>
+      <c r="E17" s="6" t="n"/>
+      <c r="F17" s="6" t="n"/>
+      <c r="G17" s="6" t="n"/>
+      <c r="H17" s="21" t="n">
+        <v>-0.01785845673657797</v>
+      </c>
+      <c r="I17" s="17" t="n">
+        <v>-368.93</v>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" s="13" t="inlineStr">
+        <is>
+          <t>DAILY returns (% of capital at start of that day; blank = no trade that day)</t>
+        </is>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" s="2" t="inlineStr">
+        <is>
+          <t>Week starting (Mon)</t>
+        </is>
+      </c>
+      <c r="B20" s="2" t="inlineStr">
+        <is>
+          <t>Mon</t>
+        </is>
+      </c>
+      <c r="C20" s="2" t="inlineStr">
+        <is>
+          <t>Tue</t>
+        </is>
+      </c>
+      <c r="D20" s="2" t="inlineStr">
+        <is>
+          <t>Wed</t>
+        </is>
+      </c>
+      <c r="E20" s="2" t="inlineStr">
+        <is>
+          <t>Thu</t>
+        </is>
+      </c>
+      <c r="F20" s="2" t="inlineStr">
+        <is>
+          <t>Fri</t>
+        </is>
+      </c>
+      <c r="G20" s="2" t="inlineStr">
+        <is>
+          <t>Week %</t>
+        </is>
+      </c>
+      <c r="H20" s="2" t="inlineStr">
+        <is>
+          <t>Week P&amp;L (Rs)</t>
+        </is>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" s="3" t="inlineStr">
+        <is>
+          <t>06-Oct-2025</t>
+        </is>
+      </c>
+      <c r="B21" s="14" t="n">
+        <v>0.0154865</v>
+      </c>
+      <c r="C21" s="6" t="n"/>
+      <c r="D21" s="6" t="n"/>
+      <c r="E21" s="6" t="n"/>
+      <c r="F21" s="6" t="n"/>
+      <c r="G21" s="20" t="n">
+        <v>0.0154865</v>
+      </c>
+      <c r="H21" s="19" t="n">
+        <v>309.73</v>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" s="3" t="inlineStr">
+        <is>
+          <t>10-Nov-2025</t>
+        </is>
+      </c>
+      <c r="B22" s="6" t="n"/>
+      <c r="C22" s="15" t="n">
+        <v>-0.01608834780176792</v>
+      </c>
+      <c r="D22" s="6" t="n"/>
+      <c r="E22" s="6" t="n"/>
+      <c r="F22" s="6" t="n"/>
+      <c r="G22" s="21" t="n">
+        <v>-0.01608834780176792</v>
+      </c>
+      <c r="H22" s="17" t="n">
+        <v>-326.75</v>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" s="3" t="inlineStr">
+        <is>
+          <t>24-Nov-2025</t>
+        </is>
+      </c>
+      <c r="B23" s="14" t="n">
+        <v>0.01526098710002212</v>
+      </c>
+      <c r="C23" s="15" t="n">
+        <v>-0.01788402371063795</v>
+      </c>
+      <c r="D23" s="6" t="n"/>
+      <c r="E23" s="6" t="n"/>
+      <c r="F23" s="6" t="n"/>
+      <c r="G23" s="21" t="n">
+        <v>-0.002895964465760363</v>
+      </c>
+      <c r="H23" s="17" t="n">
+        <v>-57.87</v>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24" s="3" t="inlineStr">
+        <is>
+          <t>12-Jan-2026</t>
+        </is>
+      </c>
+      <c r="B24" s="14" t="n">
+        <v>0.01290682962352529</v>
+      </c>
+      <c r="C24" s="6" t="n"/>
+      <c r="D24" s="6" t="n"/>
+      <c r="E24" s="6" t="n"/>
+      <c r="F24" s="6" t="n"/>
+      <c r="G24" s="20" t="n">
+        <v>0.01290682962352529</v>
+      </c>
+      <c r="H24" s="19" t="n">
+        <v>257.17</v>
+      </c>
+    </row>
+    <row r="25">
+      <c r="A25" s="3" t="inlineStr">
+        <is>
+          <t>26-Jan-2026</t>
+        </is>
+      </c>
+      <c r="B25" s="6" t="n"/>
+      <c r="C25" s="15" t="n">
+        <v>-0.01311794306688838</v>
+      </c>
+      <c r="D25" s="6" t="n"/>
+      <c r="E25" s="6" t="n"/>
+      <c r="F25" s="6" t="n"/>
+      <c r="G25" s="20" t="n">
+        <v>0.008218100234463109</v>
+      </c>
+      <c r="H25" s="19" t="n">
+        <v>165.86</v>
+      </c>
+    </row>
+    <row r="26">
+      <c r="A26" s="3" t="inlineStr">
+        <is>
+          <t>20-Apr-2026</t>
+        </is>
+      </c>
+      <c r="B26" s="15" t="n">
+        <v>-0.01204925855631031</v>
+      </c>
+      <c r="C26" s="6" t="n"/>
+      <c r="D26" s="6" t="n"/>
+      <c r="E26" s="6" t="n"/>
+      <c r="F26" s="6" t="n"/>
+      <c r="G26" s="21" t="n">
+        <v>-0.01204925855631031</v>
+      </c>
+      <c r="H26" s="17" t="n">
+        <v>-245.18</v>
+      </c>
+    </row>
+    <row r="27">
+      <c r="A27" s="3" t="inlineStr">
+        <is>
+          <t>01-Jun-2026</t>
+        </is>
+      </c>
+      <c r="B27" s="14" t="n">
+        <v>0.01282945397095752</v>
+      </c>
+      <c r="C27" s="6" t="n"/>
+      <c r="D27" s="6" t="n"/>
+      <c r="E27" s="6" t="n"/>
+      <c r="F27" s="6" t="n"/>
+      <c r="G27" s="20" t="n">
+        <v>0.01282945397095752</v>
+      </c>
+      <c r="H27" s="19" t="n">
+        <v>257.91</v>
+      </c>
+    </row>
+    <row r="28">
+      <c r="A28" s="3" t="inlineStr">
+        <is>
+          <t>29-Jun-2026</t>
+        </is>
+      </c>
+      <c r="B28" s="14" t="n">
+        <v>0.01462069155198182</v>
+      </c>
+      <c r="C28" s="6" t="n"/>
+      <c r="D28" s="6" t="n"/>
+      <c r="E28" s="6" t="n"/>
+      <c r="F28" s="6" t="n"/>
+      <c r="G28" s="20" t="n">
+        <v>0.01462069155198182</v>
+      </c>
+      <c r="H28" s="19" t="n">
+        <v>297.69</v>
+      </c>
+    </row>
+    <row r="29">
+      <c r="A29" s="3" t="inlineStr">
+        <is>
+          <t>10-Aug-2026</t>
+        </is>
+      </c>
+      <c r="B29" s="6" t="n"/>
+      <c r="C29" s="15" t="n">
+        <v>-0.01785845673657797</v>
+      </c>
+      <c r="D29" s="6" t="n"/>
+      <c r="E29" s="6" t="n"/>
+      <c r="F29" s="6" t="n"/>
+      <c r="G29" s="21" t="n">
+        <v>-0.01785845673657797</v>
+      </c>
+      <c r="H29" s="17" t="n">
+        <v>-368.93</v>
+      </c>
+    </row>
+    <row r="31">
+      <c r="A31" s="13" t="inlineStr">
+        <is>
+          <t>STATISTICS (all trades for this index)</t>
+        </is>
+      </c>
+    </row>
+    <row r="32">
+      <c r="A32" s="3" t="inlineStr">
+        <is>
+          <t>All trades</t>
+        </is>
+      </c>
+      <c r="B32" s="22" t="n">
+        <v>13</v>
+      </c>
+      <c r="C32" s="23" t="n"/>
+      <c r="D32" s="24" t="n"/>
+    </row>
+    <row r="33">
+      <c r="A33" s="3" t="inlineStr">
+        <is>
+          <t>Winners</t>
+        </is>
+      </c>
+      <c r="B33" s="25" t="inlineStr">
+        <is>
+          <t>7 (53.8%)</t>
+        </is>
+      </c>
+      <c r="C33" s="23" t="n"/>
+      <c r="D33" s="24" t="n"/>
+    </row>
+    <row r="34">
+      <c r="A34" s="3" t="inlineStr">
+        <is>
+          <t>Losers</t>
+        </is>
+      </c>
+      <c r="B34" s="25" t="inlineStr">
+        <is>
+          <t>6 (46.2%)</t>
+        </is>
+      </c>
+      <c r="C34" s="23" t="n"/>
+      <c r="D34" s="24" t="n"/>
+    </row>
+    <row r="35">
+      <c r="A35" s="3" t="inlineStr">
+        <is>
+          <t>Net P&amp;L (Rs)</t>
+        </is>
+      </c>
+      <c r="B35" s="26" t="n">
+        <v>289.63</v>
+      </c>
+      <c r="C35" s="23" t="n"/>
+      <c r="D35" s="24" t="n"/>
+    </row>
+    <row r="36">
+      <c r="A36" s="3" t="inlineStr">
+        <is>
+          <t>Total Profit (Rs)</t>
+        </is>
+      </c>
+      <c r="B36" s="26" t="n">
+        <v>2174.65</v>
+      </c>
+      <c r="C36" s="23" t="n"/>
+      <c r="D36" s="24" t="n"/>
+    </row>
+    <row r="37">
+      <c r="A37" s="3" t="inlineStr">
+        <is>
+          <t>Total Loss (Rs)</t>
+        </is>
+      </c>
+      <c r="B37" s="27" t="n">
+        <v>-1885.02</v>
+      </c>
+      <c r="C37" s="23" t="n"/>
+      <c r="D37" s="24" t="n"/>
+    </row>
+    <row r="38">
+      <c r="A38" s="3" t="inlineStr">
+        <is>
+          <t>Transaction costs (Rs)</t>
+        </is>
+      </c>
+      <c r="B38" s="28" t="n">
+        <v>863.12</v>
+      </c>
+      <c r="C38" s="23" t="n"/>
+      <c r="D38" s="24" t="n"/>
+    </row>
+    <row r="39">
+      <c r="A39" s="3" t="inlineStr">
+        <is>
+          <t>Avg Profit/Loss per trade (Rs)</t>
+        </is>
+      </c>
+      <c r="B39" s="26" t="n">
+        <v>22.28</v>
+      </c>
+      <c r="C39" s="23" t="n"/>
+      <c r="D39" s="24" t="n"/>
+    </row>
+    <row r="40">
+      <c r="A40" s="3" t="inlineStr">
+        <is>
+          <t>Avg Profit/Loss per trade (% of premium)</t>
+        </is>
+      </c>
+      <c r="B40" s="29" t="n">
+        <v>1.77</v>
+      </c>
+      <c r="C40" s="23" t="n"/>
+      <c r="D40" s="24" t="n"/>
+    </row>
+    <row r="41">
+      <c r="A41" s="3" t="inlineStr">
+        <is>
+          <t>Avg Win (Rs)</t>
+        </is>
+      </c>
+      <c r="B41" s="26" t="n">
+        <v>310.66</v>
+      </c>
+      <c r="C41" s="23" t="n"/>
+      <c r="D41" s="24" t="n"/>
+    </row>
+    <row r="42">
+      <c r="A42" s="3" t="inlineStr">
+        <is>
+          <t>Avg Win (% of premium)</t>
+        </is>
+      </c>
+      <c r="B42" s="30" t="n">
+        <v>16.01</v>
+      </c>
+      <c r="C42" s="23" t="n"/>
+      <c r="D42" s="24" t="n"/>
+    </row>
+    <row r="43">
+      <c r="A43" s="3" t="inlineStr">
+        <is>
+          <t>Avg Loss (Rs)</t>
+        </is>
+      </c>
+      <c r="B43" s="27" t="n">
+        <v>-314.17</v>
+      </c>
+      <c r="C43" s="23" t="n"/>
+      <c r="D43" s="24" t="n"/>
+    </row>
+    <row r="44">
+      <c r="A44" s="3" t="inlineStr">
+        <is>
+          <t>Avg Loss (% of premium)</t>
+        </is>
+      </c>
+      <c r="B44" s="31" t="n">
+        <v>-14.84</v>
+      </c>
+      <c r="C44" s="23" t="n"/>
+      <c r="D44" s="24" t="n"/>
+    </row>
+    <row r="45">
+      <c r="A45" s="3" t="inlineStr">
+        <is>
+          <t>Largest Win (Rs)</t>
+        </is>
+      </c>
+      <c r="B45" s="26" t="n">
+        <v>406.75</v>
+      </c>
+      <c r="C45" s="23" t="n"/>
+      <c r="D45" s="24" t="n"/>
+    </row>
+    <row r="46">
+      <c r="A46" s="3" t="inlineStr">
+        <is>
+          <t>Largest Loss (Rs)</t>
+        </is>
+      </c>
+      <c r="B46" s="27" t="n">
+        <v>-368.93</v>
+      </c>
+      <c r="C46" s="23" t="n"/>
+      <c r="D46" s="24" t="n"/>
+    </row>
+    <row r="47">
+      <c r="A47" s="3" t="inlineStr">
+        <is>
+          <t>Max Consecutive Wins</t>
+        </is>
+      </c>
+      <c r="B47" s="22" t="n">
+        <v>2</v>
+      </c>
+      <c r="C47" s="23" t="n"/>
+      <c r="D47" s="24" t="n"/>
+    </row>
+    <row r="48">
+      <c r="A48" s="3" t="inlineStr">
+        <is>
+          <t>Max Consecutive Losses</t>
+        </is>
+      </c>
+      <c r="B48" s="22" t="n">
+        <v>2</v>
+      </c>
+      <c r="C48" s="23" t="n"/>
+      <c r="D48" s="24" t="n"/>
+    </row>
+    <row r="49">
+      <c r="A49" s="3" t="inlineStr">
+        <is>
+          <t>Max trade drawdown (Rs)</t>
+        </is>
+      </c>
+      <c r="B49" s="27" t="n">
+        <v>-368.93</v>
+      </c>
+      <c r="C49" s="23" t="n"/>
+      <c r="D49" s="24" t="n"/>
+    </row>
+    <row r="50">
+      <c r="A50" s="3" t="inlineStr">
+        <is>
+          <t>Max system drawdown (Rs)</t>
+        </is>
+      </c>
+      <c r="B50" s="27" t="n">
+        <v>-561.76</v>
+      </c>
+      <c r="C50" s="23" t="n"/>
+      <c r="D50" s="24" t="n"/>
+    </row>
+    <row r="51">
+      <c r="A51" s="3" t="inlineStr">
+        <is>
+          <t>Max system drawdown (%)</t>
+        </is>
+      </c>
+      <c r="B51" s="31" t="n">
+        <v>-2.72</v>
+      </c>
+      <c r="C51" s="23" t="n"/>
+      <c r="D51" s="24" t="n"/>
+    </row>
+    <row r="52">
+      <c r="A52" s="3" t="inlineStr">
+        <is>
+          <t>Recovery Factor</t>
+        </is>
+      </c>
+      <c r="B52" s="32" t="n">
+        <v>0.52</v>
+      </c>
+      <c r="C52" s="23" t="n"/>
+      <c r="D52" s="24" t="n"/>
+    </row>
+    <row r="53">
+      <c r="A53" s="3" t="inlineStr">
+        <is>
+          <t>Profit Factor</t>
+        </is>
+      </c>
+      <c r="B53" s="32" t="n">
+        <v>1.15</v>
+      </c>
+      <c r="C53" s="23" t="n"/>
+      <c r="D53" s="24" t="n"/>
+    </row>
+    <row r="54">
+      <c r="A54" s="3" t="inlineStr">
+        <is>
+          <t>Payoff Ratio (avg win / avg loss)</t>
+        </is>
+      </c>
+      <c r="B54" s="32" t="n">
+        <v>0.99</v>
+      </c>
+      <c r="C54" s="23" t="n"/>
+      <c r="D54" s="24" t="n"/>
+    </row>
+    <row r="55">
+      <c r="A55" s="3" t="inlineStr">
+        <is>
+          <t>Sharpe Ratio (annualized)</t>
+        </is>
+      </c>
+      <c r="B55" s="32" t="n">
+        <v>1.45</v>
+      </c>
+      <c r="C55" s="23" t="n"/>
+      <c r="D55" s="24" t="n"/>
+    </row>
+    <row r="57">
+      <c r="A57" s="5" t="inlineStr">
+        <is>
+          <t>Caveat: with only a handful of trades these numbers (Sharpe, profit factor, drawdown %) are not statistically reliable. Watch this over weeks/months before drawing conclusions.</t>
+        </is>
+      </c>
+    </row>
+  </sheetData>
+  <mergeCells count="24">
+    <mergeCell ref="B42:D42"/>
+    <mergeCell ref="B44:D44"/>
+    <mergeCell ref="B53:D53"/>
+    <mergeCell ref="B38:D38"/>
+    <mergeCell ref="B34:D34"/>
+    <mergeCell ref="B37:D37"/>
+    <mergeCell ref="B49:D49"/>
+    <mergeCell ref="B40:D40"/>
+    <mergeCell ref="B55:D55"/>
+    <mergeCell ref="B51:D51"/>
+    <mergeCell ref="B33:D33"/>
+    <mergeCell ref="B36:D36"/>
+    <mergeCell ref="B45:D45"/>
+    <mergeCell ref="B41:D41"/>
+    <mergeCell ref="B35:D35"/>
+    <mergeCell ref="B32:D32"/>
+    <mergeCell ref="B50:D50"/>
+    <mergeCell ref="B47:D47"/>
+    <mergeCell ref="B54:D54"/>
+    <mergeCell ref="B46:D46"/>
+    <mergeCell ref="B52:D52"/>
+    <mergeCell ref="B43:D43"/>
+    <mergeCell ref="B39:D39"/>
+    <mergeCell ref="B48:D48"/>
+  </mergeCells>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+  <pageSetup orientation="landscape" fitToHeight="0" fitToWidth="1"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet8.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr fitToPage="1"/>
+  </sheetPr>
+  <dimension ref="A1:O48"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <cols>
+    <col width="40" customWidth="1" min="1" max="1"/>
+    <col width="10" customWidth="1" min="2" max="2"/>
+    <col width="10" customWidth="1" min="3" max="3"/>
+    <col width="10" customWidth="1" min="4" max="4"/>
+    <col width="10" customWidth="1" min="5" max="5"/>
+    <col width="10" customWidth="1" min="6" max="6"/>
+    <col width="10" customWidth="1" min="7" max="7"/>
+    <col width="15" customWidth="1" min="8" max="8"/>
+    <col width="15" customWidth="1" min="9" max="9"/>
+    <col width="10" customWidth="1" min="10" max="10"/>
+    <col width="10" customWidth="1" min="11" max="11"/>
+    <col width="10" customWidth="1" min="12" max="12"/>
+    <col width="10" customWidth="1" min="13" max="13"/>
+    <col width="10" customWidth="1" min="14" max="14"/>
+    <col width="15" customWidth="1" min="15" max="15"/>
+  </cols>
+  <sheetData>
+    <row r="1">
+      <c r="A1" s="1" t="inlineStr">
+        <is>
+          <t>BACKTEST BANKNIFTY -- best: trend_scalp_nw (EMA5/21) [5m] -- PAPER TRADE, NOT REAL MONEY</t>
+        </is>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" s="13" t="inlineStr">
+        <is>
+          <t>MONTHLY returns (% of capital at start of month)</t>
+        </is>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" s="2" t="inlineStr">
+        <is>
+          <t>Year</t>
+        </is>
+      </c>
+      <c r="B4" s="2" t="inlineStr">
+        <is>
+          <t>Jan</t>
+        </is>
+      </c>
+      <c r="C4" s="2" t="inlineStr">
+        <is>
+          <t>Feb</t>
+        </is>
+      </c>
+      <c r="D4" s="2" t="inlineStr">
+        <is>
+          <t>Mar</t>
+        </is>
+      </c>
+      <c r="E4" s="2" t="inlineStr">
+        <is>
+          <t>Apr</t>
+        </is>
+      </c>
+      <c r="F4" s="2" t="inlineStr">
+        <is>
+          <t>May</t>
+        </is>
+      </c>
+      <c r="G4" s="2" t="inlineStr">
+        <is>
+          <t>Jun</t>
+        </is>
+      </c>
+      <c r="H4" s="2" t="inlineStr">
+        <is>
+          <t>Jul</t>
+        </is>
+      </c>
+      <c r="I4" s="2" t="inlineStr">
+        <is>
+          <t>Aug</t>
+        </is>
+      </c>
+      <c r="J4" s="2" t="inlineStr">
+        <is>
+          <t>Sep</t>
+        </is>
+      </c>
+      <c r="K4" s="2" t="inlineStr">
+        <is>
+          <t>Oct</t>
+        </is>
+      </c>
+      <c r="L4" s="2" t="inlineStr">
+        <is>
+          <t>Nov</t>
+        </is>
+      </c>
+      <c r="M4" s="2" t="inlineStr">
+        <is>
+          <t>Dec</t>
+        </is>
+      </c>
+      <c r="N4" s="2" t="inlineStr">
+        <is>
+          <t>Yr %</t>
+        </is>
+      </c>
+      <c r="O4" s="2" t="inlineStr">
+        <is>
+          <t>Yr P&amp;L (Rs)</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" s="3" t="n">
+        <v>2025</v>
+      </c>
+      <c r="B5" s="6" t="n"/>
+      <c r="C5" s="6" t="n"/>
+      <c r="D5" s="6" t="n"/>
+      <c r="E5" s="6" t="n"/>
+      <c r="F5" s="6" t="n"/>
+      <c r="G5" s="6" t="n"/>
+      <c r="H5" s="6" t="n"/>
+      <c r="I5" s="6" t="n"/>
+      <c r="J5" s="6" t="n"/>
+      <c r="K5" s="6" t="n"/>
+      <c r="L5" s="6" t="n"/>
+      <c r="M5" s="15" t="n">
+        <v>-0.0355045</v>
+      </c>
+      <c r="N5" s="16" t="n">
+        <v>-0.03550450000000005</v>
+      </c>
+      <c r="O5" s="17" t="n">
+        <v>-710.09</v>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" s="3" t="n">
+        <v>2026</v>
+      </c>
+      <c r="B6" s="15" t="n">
+        <v>-0.01746560766742821</v>
+      </c>
+      <c r="C6" s="6" t="n"/>
+      <c r="D6" s="6" t="n"/>
+      <c r="E6" s="6" t="n"/>
+      <c r="F6" s="6" t="n"/>
+      <c r="G6" s="6" t="n"/>
+      <c r="H6" s="6" t="n"/>
+      <c r="I6" s="15" t="n">
+        <v>-0.02995409697673192</v>
+      </c>
+      <c r="J6" s="6" t="n"/>
+      <c r="K6" s="6" t="n"/>
+      <c r="L6" s="6" t="n"/>
+      <c r="M6" s="6" t="n"/>
+      <c r="N6" s="16" t="n">
+        <v>-0.04689653813833239</v>
+      </c>
+      <c r="O6" s="17" t="n">
+        <v>-904.63</v>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" s="3" t="inlineStr">
+        <is>
+          <t>Avg</t>
+        </is>
+      </c>
+      <c r="B7" s="16" t="n">
+        <v>-0.01746560766742821</v>
+      </c>
+      <c r="C7" s="6" t="n"/>
+      <c r="D7" s="6" t="n"/>
+      <c r="E7" s="6" t="n"/>
+      <c r="F7" s="6" t="n"/>
+      <c r="G7" s="6" t="n"/>
+      <c r="H7" s="6" t="n"/>
+      <c r="I7" s="16" t="n">
+        <v>-0.02995409697673192</v>
+      </c>
+      <c r="J7" s="6" t="n"/>
+      <c r="K7" s="6" t="n"/>
+      <c r="L7" s="6" t="n"/>
+      <c r="M7" s="16" t="n">
+        <v>-0.0355045</v>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" s="13" t="inlineStr">
+        <is>
+          <t>WEEKLY returns (% of capital at start of that week; weeks split at month edges)</t>
+        </is>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" s="2" t="inlineStr">
+        <is>
+          <t>Month</t>
+        </is>
+      </c>
+      <c r="B10" s="2" t="inlineStr">
+        <is>
+          <t>W1</t>
+        </is>
+      </c>
+      <c r="C10" s="2" t="inlineStr">
+        <is>
+          <t>W2</t>
+        </is>
+      </c>
+      <c r="D10" s="2" t="inlineStr">
+        <is>
+          <t>W3</t>
+        </is>
+      </c>
+      <c r="E10" s="2" t="inlineStr">
+        <is>
+          <t>W4</t>
+        </is>
+      </c>
+      <c r="F10" s="2" t="inlineStr">
+        <is>
+          <t>W5</t>
+        </is>
+      </c>
+      <c r="G10" s="2" t="inlineStr">
+        <is>
+          <t>W6</t>
+        </is>
+      </c>
+      <c r="H10" s="2" t="inlineStr">
+        <is>
+          <t>Month %</t>
+        </is>
+      </c>
+      <c r="I10" s="2" t="inlineStr">
+        <is>
+          <t>Month P&amp;L (Rs)</t>
+        </is>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" s="3" t="inlineStr">
+        <is>
+          <t>2025-Dec</t>
+        </is>
+      </c>
+      <c r="B11" s="15" t="n">
+        <v>-0.0355045</v>
+      </c>
+      <c r="C11" s="6" t="n"/>
+      <c r="D11" s="6" t="n"/>
+      <c r="E11" s="6" t="n"/>
+      <c r="F11" s="6" t="n"/>
+      <c r="G11" s="6" t="n"/>
+      <c r="H11" s="21" t="n">
+        <v>-0.0355045</v>
+      </c>
+      <c r="I11" s="17" t="n">
+        <v>-710.09</v>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" s="3" t="inlineStr">
+        <is>
+          <t>2026-Jan</t>
+        </is>
+      </c>
+      <c r="B12" s="15" t="n">
+        <v>-0.01746560766742821</v>
+      </c>
+      <c r="C12" s="6" t="n"/>
+      <c r="D12" s="6" t="n"/>
+      <c r="E12" s="6" t="n"/>
+      <c r="F12" s="6" t="n"/>
+      <c r="G12" s="6" t="n"/>
+      <c r="H12" s="21" t="n">
+        <v>-0.01746560766742821</v>
+      </c>
+      <c r="I12" s="17" t="n">
+        <v>-336.91</v>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" s="3" t="inlineStr">
+        <is>
+          <t>2026-Aug</t>
+        </is>
+      </c>
+      <c r="B13" s="15" t="n">
+        <v>-0.01872526776763573</v>
+      </c>
+      <c r="C13" s="15" t="n">
+        <v>-0.01144310440313796</v>
+      </c>
+      <c r="D13" s="6" t="n"/>
+      <c r="E13" s="6" t="n"/>
+      <c r="F13" s="6" t="n"/>
+      <c r="G13" s="6" t="n"/>
+      <c r="H13" s="21" t="n">
+        <v>-0.02995409697673192</v>
+      </c>
+      <c r="I13" s="17" t="n">
+        <v>-567.72</v>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" s="13" t="inlineStr">
+        <is>
+          <t>DAILY returns (% of capital at start of that day; blank = no trade that day)</t>
+        </is>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" s="2" t="inlineStr">
+        <is>
+          <t>Week starting (Mon)</t>
+        </is>
+      </c>
+      <c r="B16" s="2" t="inlineStr">
+        <is>
+          <t>Mon</t>
+        </is>
+      </c>
+      <c r="C16" s="2" t="inlineStr">
+        <is>
+          <t>Tue</t>
+        </is>
+      </c>
+      <c r="D16" s="2" t="inlineStr">
+        <is>
+          <t>Wed</t>
+        </is>
+      </c>
+      <c r="E16" s="2" t="inlineStr">
+        <is>
+          <t>Thu</t>
+        </is>
+      </c>
+      <c r="F16" s="2" t="inlineStr">
+        <is>
+          <t>Fri</t>
+        </is>
+      </c>
+      <c r="G16" s="2" t="inlineStr">
+        <is>
+          <t>Week %</t>
+        </is>
+      </c>
+      <c r="H16" s="2" t="inlineStr">
+        <is>
+          <t>Week P&amp;L (Rs)</t>
+        </is>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" s="3" t="inlineStr">
+        <is>
+          <t>29-Dec-2025</t>
+        </is>
+      </c>
+      <c r="B17" s="6" t="n"/>
+      <c r="C17" s="15" t="n">
+        <v>-0.0355045</v>
+      </c>
+      <c r="D17" s="6" t="n"/>
+      <c r="E17" s="6" t="n"/>
+      <c r="F17" s="6" t="n"/>
+      <c r="G17" s="21" t="n">
+        <v>-0.0355045</v>
+      </c>
+      <c r="H17" s="17" t="n">
+        <v>-710.09</v>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" s="3" t="inlineStr">
+        <is>
+          <t>26-Jan-2026</t>
+        </is>
+      </c>
+      <c r="B18" s="6" t="n"/>
+      <c r="C18" s="15" t="n">
+        <v>-0.01746560766742821</v>
+      </c>
+      <c r="D18" s="6" t="n"/>
+      <c r="E18" s="6" t="n"/>
+      <c r="F18" s="6" t="n"/>
+      <c r="G18" s="21" t="n">
+        <v>-0.01746560766742821</v>
+      </c>
+      <c r="H18" s="17" t="n">
+        <v>-336.91</v>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" s="3" t="inlineStr">
+        <is>
+          <t>10-Aug-2026</t>
+        </is>
+      </c>
+      <c r="B19" s="6" t="n"/>
+      <c r="C19" s="15" t="n">
+        <v>-0.01872526776763573</v>
+      </c>
+      <c r="D19" s="6" t="n"/>
+      <c r="E19" s="6" t="n"/>
+      <c r="F19" s="6" t="n"/>
+      <c r="G19" s="21" t="n">
+        <v>-0.01872526776763573</v>
+      </c>
+      <c r="H19" s="17" t="n">
+        <v>-354.9</v>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" s="3" t="inlineStr">
+        <is>
+          <t>24-Aug-2026</t>
+        </is>
+      </c>
+      <c r="B20" s="6" t="n"/>
+      <c r="C20" s="15" t="n">
+        <v>-0.01144310440313796</v>
+      </c>
+      <c r="D20" s="6" t="n"/>
+      <c r="E20" s="6" t="n"/>
+      <c r="F20" s="6" t="n"/>
+      <c r="G20" s="21" t="n">
+        <v>-0.01144310440313796</v>
+      </c>
+      <c r="H20" s="17" t="n">
+        <v>-212.82</v>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" s="13" t="inlineStr">
+        <is>
+          <t>STATISTICS (all trades for this index)</t>
+        </is>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" s="3" t="inlineStr">
+        <is>
+          <t>All trades</t>
+        </is>
+      </c>
+      <c r="B23" s="22" t="n">
+        <v>5</v>
+      </c>
+      <c r="C23" s="23" t="n"/>
+      <c r="D23" s="24" t="n"/>
+    </row>
+    <row r="24">
+      <c r="A24" s="3" t="inlineStr">
+        <is>
+          <t>Winners</t>
+        </is>
+      </c>
+      <c r="B24" s="25" t="inlineStr">
+        <is>
+          <t>0 (0.0%)</t>
+        </is>
+      </c>
+      <c r="C24" s="23" t="n"/>
+      <c r="D24" s="24" t="n"/>
+    </row>
+    <row r="25">
+      <c r="A25" s="3" t="inlineStr">
+        <is>
+          <t>Losers</t>
+        </is>
+      </c>
+      <c r="B25" s="25" t="inlineStr">
+        <is>
+          <t>5 (100.0%)</t>
+        </is>
+      </c>
+      <c r="C25" s="23" t="n"/>
+      <c r="D25" s="24" t="n"/>
+    </row>
+    <row r="26">
+      <c r="A26" s="3" t="inlineStr">
+        <is>
+          <t>Net P&amp;L (Rs)</t>
+        </is>
+      </c>
+      <c r="B26" s="27" t="n">
+        <v>-1614.72</v>
+      </c>
+      <c r="C26" s="23" t="n"/>
+      <c r="D26" s="24" t="n"/>
+    </row>
+    <row r="27">
+      <c r="A27" s="3" t="inlineStr">
+        <is>
+          <t>Total Profit (Rs)</t>
+        </is>
+      </c>
+      <c r="B27" s="26" t="n">
+        <v>0</v>
+      </c>
+      <c r="C27" s="23" t="n"/>
+      <c r="D27" s="24" t="n"/>
+    </row>
+    <row r="28">
+      <c r="A28" s="3" t="inlineStr">
+        <is>
+          <t>Total Loss (Rs)</t>
+        </is>
+      </c>
+      <c r="B28" s="27" t="n">
+        <v>-1614.72</v>
+      </c>
+      <c r="C28" s="23" t="n"/>
+      <c r="D28" s="24" t="n"/>
+    </row>
+    <row r="29">
+      <c r="A29" s="3" t="inlineStr">
+        <is>
+          <t>Transaction costs (Rs)</t>
+        </is>
+      </c>
+      <c r="B29" s="28" t="n">
+        <v>328.47</v>
+      </c>
+      <c r="C29" s="23" t="n"/>
+      <c r="D29" s="24" t="n"/>
+    </row>
+    <row r="30">
+      <c r="A30" s="3" t="inlineStr">
+        <is>
+          <t>Avg Profit/Loss per trade (Rs)</t>
+        </is>
+      </c>
+      <c r="B30" s="27" t="n">
+        <v>-322.94</v>
+      </c>
+      <c r="C30" s="23" t="n"/>
+      <c r="D30" s="24" t="n"/>
+    </row>
+    <row r="31">
+      <c r="A31" s="3" t="inlineStr">
+        <is>
+          <t>Avg Profit/Loss per trade (% of premium)</t>
+        </is>
+      </c>
+      <c r="B31" s="29" t="n">
+        <v>-14.84</v>
+      </c>
+      <c r="C31" s="23" t="n"/>
+      <c r="D31" s="24" t="n"/>
+    </row>
+    <row r="32">
+      <c r="A32" s="3" t="inlineStr">
+        <is>
+          <t>Avg Win (Rs)</t>
+        </is>
+      </c>
+      <c r="B32" s="26" t="n">
+        <v>0</v>
+      </c>
+      <c r="C32" s="23" t="n"/>
+      <c r="D32" s="24" t="n"/>
+    </row>
+    <row r="33">
+      <c r="A33" s="3" t="inlineStr">
+        <is>
+          <t>Avg Win (% of premium)</t>
+        </is>
+      </c>
+      <c r="B33" s="30" t="n">
+        <v>0</v>
+      </c>
+      <c r="C33" s="23" t="n"/>
+      <c r="D33" s="24" t="n"/>
+    </row>
+    <row r="34">
+      <c r="A34" s="3" t="inlineStr">
+        <is>
+          <t>Avg Loss (Rs)</t>
+        </is>
+      </c>
+      <c r="B34" s="27" t="n">
+        <v>-322.94</v>
+      </c>
+      <c r="C34" s="23" t="n"/>
+      <c r="D34" s="24" t="n"/>
+    </row>
+    <row r="35">
+      <c r="A35" s="3" t="inlineStr">
+        <is>
+          <t>Avg Loss (% of premium)</t>
+        </is>
+      </c>
+      <c r="B35" s="31" t="n">
+        <v>-14.84</v>
+      </c>
+      <c r="C35" s="23" t="n"/>
+      <c r="D35" s="24" t="n"/>
+    </row>
+    <row r="36">
+      <c r="A36" s="3" t="inlineStr">
+        <is>
+          <t>Largest Win (Rs)</t>
+        </is>
+      </c>
+      <c r="B36" s="26" t="n">
+        <v>-212.82</v>
+      </c>
+      <c r="C36" s="23" t="n"/>
+      <c r="D36" s="24" t="n"/>
+    </row>
+    <row r="37">
+      <c r="A37" s="3" t="inlineStr">
+        <is>
+          <t>Largest Loss (Rs)</t>
+        </is>
+      </c>
+      <c r="B37" s="27" t="n">
+        <v>-358.86</v>
+      </c>
+      <c r="C37" s="23" t="n"/>
+      <c r="D37" s="24" t="n"/>
+    </row>
+    <row r="38">
+      <c r="A38" s="3" t="inlineStr">
+        <is>
+          <t>Max Consecutive Wins</t>
+        </is>
+      </c>
+      <c r="B38" s="22" t="n">
+        <v>0</v>
+      </c>
+      <c r="C38" s="23" t="n"/>
+      <c r="D38" s="24" t="n"/>
+    </row>
+    <row r="39">
+      <c r="A39" s="3" t="inlineStr">
+        <is>
+          <t>Max Consecutive Losses</t>
+        </is>
+      </c>
+      <c r="B39" s="22" t="n">
+        <v>5</v>
+      </c>
+      <c r="C39" s="23" t="n"/>
+      <c r="D39" s="24" t="n"/>
+    </row>
+    <row r="40">
+      <c r="A40" s="3" t="inlineStr">
+        <is>
+          <t>Max trade drawdown (Rs)</t>
+        </is>
+      </c>
+      <c r="B40" s="27" t="n">
+        <v>-358.86</v>
+      </c>
+      <c r="C40" s="23" t="n"/>
+      <c r="D40" s="24" t="n"/>
+    </row>
+    <row r="41">
+      <c r="A41" s="3" t="inlineStr">
+        <is>
+          <t>Max system drawdown (Rs)</t>
+        </is>
+      </c>
+      <c r="B41" s="27" t="n">
+        <v>-1614.72</v>
+      </c>
+      <c r="C41" s="23" t="n"/>
+      <c r="D41" s="24" t="n"/>
+    </row>
+    <row r="42">
+      <c r="A42" s="3" t="inlineStr">
+        <is>
+          <t>Max system drawdown (%)</t>
+        </is>
+      </c>
+      <c r="B42" s="31" t="n">
+        <v>-8.07</v>
+      </c>
+      <c r="C42" s="23" t="n"/>
+      <c r="D42" s="24" t="n"/>
+    </row>
+    <row r="43">
+      <c r="A43" s="3" t="inlineStr">
+        <is>
+          <t>Recovery Factor</t>
+        </is>
+      </c>
+      <c r="B43" s="32" t="n">
+        <v>-1</v>
+      </c>
+      <c r="C43" s="23" t="n"/>
+      <c r="D43" s="24" t="n"/>
+    </row>
+    <row r="44">
+      <c r="A44" s="3" t="inlineStr">
+        <is>
+          <t>Profit Factor</t>
+        </is>
+      </c>
+      <c r="B44" s="32" t="n">
+        <v>0</v>
+      </c>
+      <c r="C44" s="23" t="n"/>
+      <c r="D44" s="24" t="n"/>
+    </row>
+    <row r="45">
+      <c r="A45" s="3" t="inlineStr">
+        <is>
+          <t>Payoff Ratio (avg win / avg loss)</t>
+        </is>
+      </c>
+      <c r="B45" s="25" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="C45" s="23" t="n"/>
+      <c r="D45" s="24" t="n"/>
+    </row>
+    <row r="46">
+      <c r="A46" s="3" t="inlineStr">
+        <is>
+          <t>Sharpe Ratio (annualized)</t>
+        </is>
+      </c>
+      <c r="B46" s="32" t="n">
+        <v>-36.94</v>
+      </c>
+      <c r="C46" s="23" t="n"/>
+      <c r="D46" s="24" t="n"/>
+    </row>
+    <row r="48">
+      <c r="A48" s="5" t="inlineStr">
+        <is>
+          <t>Caveat: with only a handful of trades these numbers (Sharpe, profit factor, drawdown %) are not statistically reliable. Watch this over weeks/months before drawing conclusions.</t>
+        </is>
+      </c>
+    </row>
+  </sheetData>
+  <mergeCells count="24">
+    <mergeCell ref="B42:D42"/>
+    <mergeCell ref="B23:D23"/>
+    <mergeCell ref="B44:D44"/>
+    <mergeCell ref="B29:D29"/>
+    <mergeCell ref="B38:D38"/>
+    <mergeCell ref="B34:D34"/>
+    <mergeCell ref="B28:D28"/>
+    <mergeCell ref="B37:D37"/>
+    <mergeCell ref="B40:D40"/>
+    <mergeCell ref="B30:D30"/>
+    <mergeCell ref="B24:D24"/>
+    <mergeCell ref="B33:D33"/>
+    <mergeCell ref="B36:D36"/>
+    <mergeCell ref="B45:D45"/>
+    <mergeCell ref="B41:D41"/>
+    <mergeCell ref="B32:D32"/>
+    <mergeCell ref="B35:D35"/>
+    <mergeCell ref="B26:D26"/>
+    <mergeCell ref="B25:D25"/>
+    <mergeCell ref="B31:D31"/>
+    <mergeCell ref="B46:D46"/>
+    <mergeCell ref="B27:D27"/>
+    <mergeCell ref="B43:D43"/>
+    <mergeCell ref="B39:D39"/>
+  </mergeCells>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+  <pageSetup orientation="landscape" fitToHeight="0" fitToWidth="1"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet9.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr fitToPage="1"/>
+  </sheetPr>
+  <dimension ref="A1:O49"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <cols>
+    <col width="40" customWidth="1" min="1" max="1"/>
+    <col width="10" customWidth="1" min="2" max="2"/>
+    <col width="10" customWidth="1" min="3" max="3"/>
+    <col width="10" customWidth="1" min="4" max="4"/>
+    <col width="10" customWidth="1" min="5" max="5"/>
+    <col width="10" customWidth="1" min="6" max="6"/>
+    <col width="10" customWidth="1" min="7" max="7"/>
+    <col width="15" customWidth="1" min="8" max="8"/>
+    <col width="15" customWidth="1" min="9" max="9"/>
+    <col width="10" customWidth="1" min="10" max="10"/>
+    <col width="10" customWidth="1" min="11" max="11"/>
+    <col width="10" customWidth="1" min="12" max="12"/>
+    <col width="10" customWidth="1" min="13" max="13"/>
+    <col width="10" customWidth="1" min="14" max="14"/>
+    <col width="15" customWidth="1" min="15" max="15"/>
+  </cols>
+  <sheetData>
+    <row r="1">
+      <c r="A1" s="1" t="inlineStr">
+        <is>
+          <t>BACKTEST FINNIFTY -- best: trend_scalp_nw (EMA8/21) [5m] -- PAPER TRADE, NOT REAL MONEY</t>
+        </is>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" s="13" t="inlineStr">
+        <is>
+          <t>MONTHLY returns (% of capital at start of month)</t>
+        </is>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" s="2" t="inlineStr">
+        <is>
+          <t>Year</t>
+        </is>
+      </c>
+      <c r="B4" s="2" t="inlineStr">
+        <is>
+          <t>Jan</t>
+        </is>
+      </c>
+      <c r="C4" s="2" t="inlineStr">
+        <is>
+          <t>Feb</t>
+        </is>
+      </c>
+      <c r="D4" s="2" t="inlineStr">
+        <is>
+          <t>Mar</t>
+        </is>
+      </c>
+      <c r="E4" s="2" t="inlineStr">
+        <is>
+          <t>Apr</t>
+        </is>
+      </c>
+      <c r="F4" s="2" t="inlineStr">
+        <is>
+          <t>May</t>
+        </is>
+      </c>
+      <c r="G4" s="2" t="inlineStr">
+        <is>
+          <t>Jun</t>
+        </is>
+      </c>
+      <c r="H4" s="2" t="inlineStr">
+        <is>
+          <t>Jul</t>
+        </is>
+      </c>
+      <c r="I4" s="2" t="inlineStr">
+        <is>
+          <t>Aug</t>
+        </is>
+      </c>
+      <c r="J4" s="2" t="inlineStr">
+        <is>
+          <t>Sep</t>
+        </is>
+      </c>
+      <c r="K4" s="2" t="inlineStr">
+        <is>
+          <t>Oct</t>
+        </is>
+      </c>
+      <c r="L4" s="2" t="inlineStr">
+        <is>
+          <t>Nov</t>
+        </is>
+      </c>
+      <c r="M4" s="2" t="inlineStr">
+        <is>
+          <t>Dec</t>
+        </is>
+      </c>
+      <c r="N4" s="2" t="inlineStr">
+        <is>
+          <t>Yr %</t>
+        </is>
+      </c>
+      <c r="O4" s="2" t="inlineStr">
+        <is>
+          <t>Yr P&amp;L (Rs)</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" s="3" t="n">
+        <v>2025</v>
+      </c>
+      <c r="B5" s="6" t="n"/>
+      <c r="C5" s="6" t="n"/>
+      <c r="D5" s="6" t="n"/>
+      <c r="E5" s="6" t="n"/>
+      <c r="F5" s="6" t="n"/>
+      <c r="G5" s="6" t="n"/>
+      <c r="H5" s="6" t="n"/>
+      <c r="I5" s="6" t="n"/>
+      <c r="J5" s="6" t="n"/>
+      <c r="K5" s="15" t="n">
+        <v>-0.0136185</v>
+      </c>
+      <c r="L5" s="6" t="n"/>
+      <c r="M5" s="15" t="n">
+        <v>-0.02744830473807548</v>
+      </c>
+      <c r="N5" s="16" t="n">
+        <v>-0.04069299999999998</v>
+      </c>
+      <c r="O5" s="17" t="n">
+        <v>-813.86</v>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" s="3" t="n">
+        <v>2026</v>
+      </c>
+      <c r="B6" s="15" t="n">
+        <v>-0.01495923619863089</v>
+      </c>
+      <c r="C6" s="6" t="n"/>
+      <c r="D6" s="6" t="n"/>
+      <c r="E6" s="6" t="n"/>
+      <c r="F6" s="6" t="n"/>
+      <c r="G6" s="6" t="n"/>
+      <c r="H6" s="6" t="n"/>
+      <c r="I6" s="6" t="n"/>
+      <c r="J6" s="15" t="n">
+        <v>-0.01223918772980555</v>
+      </c>
+      <c r="K6" s="6" t="n"/>
+      <c r="L6" s="6" t="n"/>
+      <c r="M6" s="6" t="n"/>
+      <c r="N6" s="16" t="n">
+        <v>-0.027015335028307</v>
+      </c>
+      <c r="O6" s="17" t="n">
+        <v>-518.3200000000001</v>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" s="3" t="inlineStr">
+        <is>
+          <t>Avg</t>
+        </is>
+      </c>
+      <c r="B7" s="16" t="n">
+        <v>-0.01495923619863089</v>
+      </c>
+      <c r="C7" s="6" t="n"/>
+      <c r="D7" s="6" t="n"/>
+      <c r="E7" s="6" t="n"/>
+      <c r="F7" s="6" t="n"/>
+      <c r="G7" s="6" t="n"/>
+      <c r="H7" s="6" t="n"/>
+      <c r="I7" s="6" t="n"/>
+      <c r="J7" s="16" t="n">
+        <v>-0.01223918772980555</v>
+      </c>
+      <c r="K7" s="16" t="n">
+        <v>-0.0136185</v>
+      </c>
+      <c r="L7" s="6" t="n"/>
+      <c r="M7" s="16" t="n">
+        <v>-0.02744830473807548</v>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" s="13" t="inlineStr">
+        <is>
+          <t>WEEKLY returns (% of capital at start of that week; weeks split at month edges)</t>
+        </is>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" s="2" t="inlineStr">
+        <is>
+          <t>Month</t>
+        </is>
+      </c>
+      <c r="B10" s="2" t="inlineStr">
+        <is>
+          <t>W1</t>
+        </is>
+      </c>
+      <c r="C10" s="2" t="inlineStr">
+        <is>
+          <t>W2</t>
+        </is>
+      </c>
+      <c r="D10" s="2" t="inlineStr">
+        <is>
+          <t>W3</t>
+        </is>
+      </c>
+      <c r="E10" s="2" t="inlineStr">
+        <is>
+          <t>W4</t>
+        </is>
+      </c>
+      <c r="F10" s="2" t="inlineStr">
+        <is>
+          <t>W5</t>
+        </is>
+      </c>
+      <c r="G10" s="2" t="inlineStr">
+        <is>
+          <t>W6</t>
+        </is>
+      </c>
+      <c r="H10" s="2" t="inlineStr">
+        <is>
+          <t>Month %</t>
+        </is>
+      </c>
+      <c r="I10" s="2" t="inlineStr">
+        <is>
+          <t>Month P&amp;L (Rs)</t>
+        </is>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" s="3" t="inlineStr">
+        <is>
+          <t>2025-Oct</t>
+        </is>
+      </c>
+      <c r="B11" s="15" t="n">
+        <v>-0.0136185</v>
+      </c>
+      <c r="C11" s="6" t="n"/>
+      <c r="D11" s="6" t="n"/>
+      <c r="E11" s="6" t="n"/>
+      <c r="F11" s="6" t="n"/>
+      <c r="G11" s="6" t="n"/>
+      <c r="H11" s="21" t="n">
+        <v>-0.0136185</v>
+      </c>
+      <c r="I11" s="17" t="n">
+        <v>-272.37</v>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" s="3" t="inlineStr">
+        <is>
+          <t>2025-Dec</t>
+        </is>
+      </c>
+      <c r="B12" s="15" t="n">
+        <v>-0.02744830473807548</v>
+      </c>
+      <c r="C12" s="6" t="n"/>
+      <c r="D12" s="6" t="n"/>
+      <c r="E12" s="6" t="n"/>
+      <c r="F12" s="6" t="n"/>
+      <c r="G12" s="6" t="n"/>
+      <c r="H12" s="21" t="n">
+        <v>-0.02744830473807548</v>
+      </c>
+      <c r="I12" s="17" t="n">
+        <v>-541.49</v>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" s="3" t="inlineStr">
+        <is>
+          <t>2026-Jan</t>
+        </is>
+      </c>
+      <c r="B13" s="15" t="n">
+        <v>-0.01495923619863089</v>
+      </c>
+      <c r="C13" s="6" t="n"/>
+      <c r="D13" s="6" t="n"/>
+      <c r="E13" s="6" t="n"/>
+      <c r="F13" s="6" t="n"/>
+      <c r="G13" s="6" t="n"/>
+      <c r="H13" s="21" t="n">
+        <v>-0.01495923619863089</v>
+      </c>
+      <c r="I13" s="17" t="n">
+        <v>-287.01</v>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" s="3" t="inlineStr">
+        <is>
+          <t>2026-Sep</t>
+        </is>
+      </c>
+      <c r="B14" s="15" t="n">
+        <v>-0.01223918772980555</v>
+      </c>
+      <c r="C14" s="6" t="n"/>
+      <c r="D14" s="6" t="n"/>
+      <c r="E14" s="6" t="n"/>
+      <c r="F14" s="6" t="n"/>
+      <c r="G14" s="6" t="n"/>
+      <c r="H14" s="21" t="n">
+        <v>-0.01223918772980555</v>
+      </c>
+      <c r="I14" s="17" t="n">
+        <v>-231.31</v>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" s="13" t="inlineStr">
+        <is>
+          <t>DAILY returns (% of capital at start of that day; blank = no trade that day)</t>
+        </is>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" s="2" t="inlineStr">
+        <is>
+          <t>Week starting (Mon)</t>
+        </is>
+      </c>
+      <c r="B17" s="2" t="inlineStr">
+        <is>
+          <t>Mon</t>
+        </is>
+      </c>
+      <c r="C17" s="2" t="inlineStr">
+        <is>
+          <t>Tue</t>
+        </is>
+      </c>
+      <c r="D17" s="2" t="inlineStr">
+        <is>
+          <t>Wed</t>
+        </is>
+      </c>
+      <c r="E17" s="2" t="inlineStr">
+        <is>
+          <t>Thu</t>
+        </is>
+      </c>
+      <c r="F17" s="2" t="inlineStr">
+        <is>
+          <t>Fri</t>
+        </is>
+      </c>
+      <c r="G17" s="2" t="inlineStr">
+        <is>
+          <t>Week %</t>
+        </is>
+      </c>
+      <c r="H17" s="2" t="inlineStr">
+        <is>
+          <t>Week P&amp;L (Rs)</t>
+        </is>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" s="3" t="inlineStr">
+        <is>
+          <t>13-Oct-2025</t>
+        </is>
+      </c>
+      <c r="B18" s="6" t="n"/>
+      <c r="C18" s="15" t="n">
+        <v>-0.0136185</v>
+      </c>
+      <c r="D18" s="6" t="n"/>
+      <c r="E18" s="6" t="n"/>
+      <c r="F18" s="6" t="n"/>
+      <c r="G18" s="21" t="n">
+        <v>-0.0136185</v>
+      </c>
+      <c r="H18" s="17" t="n">
+        <v>-272.37</v>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" s="3" t="inlineStr">
+        <is>
+          <t>08-Dec-2025</t>
+        </is>
+      </c>
+      <c r="B19" s="6" t="n"/>
+      <c r="C19" s="15" t="n">
+        <v>-0.02744830473807548</v>
+      </c>
+      <c r="D19" s="6" t="n"/>
+      <c r="E19" s="6" t="n"/>
+      <c r="F19" s="6" t="n"/>
+      <c r="G19" s="21" t="n">
+        <v>-0.02744830473807548</v>
+      </c>
+      <c r="H19" s="17" t="n">
+        <v>-541.49</v>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" s="3" t="inlineStr">
+        <is>
+          <t>26-Jan-2026</t>
+        </is>
+      </c>
+      <c r="B20" s="6" t="n"/>
+      <c r="C20" s="15" t="n">
+        <v>-0.01495923619863089</v>
+      </c>
+      <c r="D20" s="6" t="n"/>
+      <c r="E20" s="6" t="n"/>
+      <c r="F20" s="6" t="n"/>
+      <c r="G20" s="21" t="n">
+        <v>-0.01495923619863089</v>
+      </c>
+      <c r="H20" s="17" t="n">
+        <v>-287.01</v>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" s="3" t="inlineStr">
+        <is>
+          <t>07-Sep-2026</t>
+        </is>
+      </c>
+      <c r="B21" s="6" t="n"/>
+      <c r="C21" s="15" t="n">
+        <v>-0.01223918772980555</v>
+      </c>
+      <c r="D21" s="6" t="n"/>
+      <c r="E21" s="6" t="n"/>
+      <c r="F21" s="6" t="n"/>
+      <c r="G21" s="21" t="n">
+        <v>-0.01223918772980555</v>
+      </c>
+      <c r="H21" s="17" t="n">
+        <v>-231.31</v>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" s="13" t="inlineStr">
+        <is>
+          <t>STATISTICS (all trades for this index)</t>
+        </is>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24" s="3" t="inlineStr">
+        <is>
+          <t>All trades</t>
+        </is>
+      </c>
+      <c r="B24" s="22" t="n">
+        <v>5</v>
+      </c>
+      <c r="C24" s="23" t="n"/>
+      <c r="D24" s="24" t="n"/>
+    </row>
+    <row r="25">
+      <c r="A25" s="3" t="inlineStr">
+        <is>
+          <t>Winners</t>
+        </is>
+      </c>
+      <c r="B25" s="25" t="inlineStr">
+        <is>
+          <t>0 (0.0%)</t>
+        </is>
+      </c>
+      <c r="C25" s="23" t="n"/>
+      <c r="D25" s="24" t="n"/>
+    </row>
+    <row r="26">
+      <c r="A26" s="3" t="inlineStr">
+        <is>
+          <t>Losers</t>
+        </is>
+      </c>
+      <c r="B26" s="25" t="inlineStr">
+        <is>
+          <t>5 (100.0%)</t>
+        </is>
+      </c>
+      <c r="C26" s="23" t="n"/>
+      <c r="D26" s="24" t="n"/>
+    </row>
+    <row r="27">
+      <c r="A27" s="3" t="inlineStr">
+        <is>
+          <t>Net P&amp;L (Rs)</t>
+        </is>
+      </c>
+      <c r="B27" s="27" t="n">
+        <v>-1332.18</v>
+      </c>
+      <c r="C27" s="23" t="n"/>
+      <c r="D27" s="24" t="n"/>
+    </row>
+    <row r="28">
+      <c r="A28" s="3" t="inlineStr">
+        <is>
+          <t>Total Profit (Rs)</t>
+        </is>
+      </c>
+      <c r="B28" s="26" t="n">
+        <v>0</v>
+      </c>
+      <c r="C28" s="23" t="n"/>
+      <c r="D28" s="24" t="n"/>
+    </row>
+    <row r="29">
+      <c r="A29" s="3" t="inlineStr">
+        <is>
+          <t>Total Loss (Rs)</t>
+        </is>
+      </c>
+      <c r="B29" s="27" t="n">
+        <v>-1332.18</v>
+      </c>
+      <c r="C29" s="23" t="n"/>
+      <c r="D29" s="24" t="n"/>
+    </row>
+    <row r="30">
+      <c r="A30" s="3" t="inlineStr">
+        <is>
+          <t>Transaction costs (Rs)</t>
+        </is>
+      </c>
+      <c r="B30" s="28" t="n">
+        <v>271.38</v>
+      </c>
+      <c r="C30" s="23" t="n"/>
+      <c r="D30" s="24" t="n"/>
+    </row>
+    <row r="31">
+      <c r="A31" s="3" t="inlineStr">
+        <is>
+          <t>Avg Profit/Loss per trade (Rs)</t>
+        </is>
+      </c>
+      <c r="B31" s="27" t="n">
+        <v>-266.44</v>
+      </c>
+      <c r="C31" s="23" t="n"/>
+      <c r="D31" s="24" t="n"/>
+    </row>
+    <row r="32">
+      <c r="A32" s="3" t="inlineStr">
+        <is>
+          <t>Avg Profit/Loss per trade (% of premium)</t>
+        </is>
+      </c>
+      <c r="B32" s="29" t="n">
+        <v>-14.85</v>
+      </c>
+      <c r="C32" s="23" t="n"/>
+      <c r="D32" s="24" t="n"/>
+    </row>
+    <row r="33">
+      <c r="A33" s="3" t="inlineStr">
+        <is>
+          <t>Avg Win (Rs)</t>
+        </is>
+      </c>
+      <c r="B33" s="26" t="n">
+        <v>0</v>
+      </c>
+      <c r="C33" s="23" t="n"/>
+      <c r="D33" s="24" t="n"/>
+    </row>
+    <row r="34">
+      <c r="A34" s="3" t="inlineStr">
+        <is>
+          <t>Avg Win (% of premium)</t>
+        </is>
+      </c>
+      <c r="B34" s="30" t="n">
+        <v>0</v>
+      </c>
+      <c r="C34" s="23" t="n"/>
+      <c r="D34" s="24" t="n"/>
+    </row>
+    <row r="35">
+      <c r="A35" s="3" t="inlineStr">
+        <is>
+          <t>Avg Loss (Rs)</t>
+        </is>
+      </c>
+      <c r="B35" s="27" t="n">
+        <v>-266.44</v>
+      </c>
+      <c r="C35" s="23" t="n"/>
+      <c r="D35" s="24" t="n"/>
+    </row>
+    <row r="36">
+      <c r="A36" s="3" t="inlineStr">
+        <is>
+          <t>Avg Loss (% of premium)</t>
+        </is>
+      </c>
+      <c r="B36" s="31" t="n">
+        <v>-14.85</v>
+      </c>
+      <c r="C36" s="23" t="n"/>
+      <c r="D36" s="24" t="n"/>
+    </row>
+    <row r="37">
+      <c r="A37" s="3" t="inlineStr">
+        <is>
+          <t>Largest Win (Rs)</t>
+        </is>
+      </c>
+      <c r="B37" s="26" t="n">
+        <v>-231.31</v>
+      </c>
+      <c r="C37" s="23" t="n"/>
+      <c r="D37" s="24" t="n"/>
+    </row>
+    <row r="38">
+      <c r="A38" s="3" t="inlineStr">
+        <is>
+          <t>Largest Loss (Rs)</t>
+        </is>
+      </c>
+      <c r="B38" s="27" t="n">
+        <v>-295.95</v>
+      </c>
+      <c r="C38" s="23" t="n"/>
+      <c r="D38" s="24" t="n"/>
+    </row>
+    <row r="39">
+      <c r="A39" s="3" t="inlineStr">
+        <is>
+          <t>Max Consecutive Wins</t>
+        </is>
+      </c>
+      <c r="B39" s="22" t="n">
+        <v>0</v>
+      </c>
+      <c r="C39" s="23" t="n"/>
+      <c r="D39" s="24" t="n"/>
+    </row>
+    <row r="40">
+      <c r="A40" s="3" t="inlineStr">
+        <is>
+          <t>Max Consecutive Losses</t>
+        </is>
+      </c>
+      <c r="B40" s="22" t="n">
+        <v>5</v>
+      </c>
+      <c r="C40" s="23" t="n"/>
+      <c r="D40" s="24" t="n"/>
+    </row>
+    <row r="41">
+      <c r="A41" s="3" t="inlineStr">
+        <is>
+          <t>Max trade drawdown (Rs)</t>
+        </is>
+      </c>
+      <c r="B41" s="27" t="n">
+        <v>-295.95</v>
+      </c>
+      <c r="C41" s="23" t="n"/>
+      <c r="D41" s="24" t="n"/>
+    </row>
+    <row r="42">
+      <c r="A42" s="3" t="inlineStr">
+        <is>
+          <t>Max system drawdown (Rs)</t>
+        </is>
+      </c>
+      <c r="B42" s="27" t="n">
+        <v>-1332.18</v>
+      </c>
+      <c r="C42" s="23" t="n"/>
+      <c r="D42" s="24" t="n"/>
+    </row>
+    <row r="43">
+      <c r="A43" s="3" t="inlineStr">
+        <is>
+          <t>Max system drawdown (%)</t>
+        </is>
+      </c>
+      <c r="B43" s="31" t="n">
+        <v>-6.66</v>
+      </c>
+      <c r="C43" s="23" t="n"/>
+      <c r="D43" s="24" t="n"/>
+    </row>
+    <row r="44">
+      <c r="A44" s="3" t="inlineStr">
+        <is>
+          <t>Recovery Factor</t>
+        </is>
+      </c>
+      <c r="B44" s="32" t="n">
+        <v>-1</v>
+      </c>
+      <c r="C44" s="23" t="n"/>
+      <c r="D44" s="24" t="n"/>
+    </row>
+    <row r="45">
+      <c r="A45" s="3" t="inlineStr">
+        <is>
+          <t>Profit Factor</t>
+        </is>
+      </c>
+      <c r="B45" s="32" t="n">
+        <v>0</v>
+      </c>
+      <c r="C45" s="23" t="n"/>
+      <c r="D45" s="24" t="n"/>
+    </row>
+    <row r="46">
+      <c r="A46" s="3" t="inlineStr">
+        <is>
+          <t>Payoff Ratio (avg win / avg loss)</t>
+        </is>
+      </c>
+      <c r="B46" s="25" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="C46" s="23" t="n"/>
+      <c r="D46" s="24" t="n"/>
+    </row>
+    <row r="47">
+      <c r="A47" s="3" t="inlineStr">
+        <is>
+          <t>Sharpe Ratio (annualized)</t>
+        </is>
+      </c>
+      <c r="B47" s="32" t="n">
+        <v>-44.63</v>
+      </c>
+      <c r="C47" s="23" t="n"/>
+      <c r="D47" s="24" t="n"/>
+    </row>
+    <row r="49">
+      <c r="A49" s="5" t="inlineStr">
+        <is>
+          <t>Caveat: with only a handful of trades these numbers (Sharpe, profit factor, drawdown %) are not statistically reliable. Watch this over weeks/months before drawing conclusions.</t>
+        </is>
+      </c>
+    </row>
+  </sheetData>
+  <mergeCells count="24">
+    <mergeCell ref="B42:D42"/>
+    <mergeCell ref="B44:D44"/>
+    <mergeCell ref="B29:D29"/>
+    <mergeCell ref="B38:D38"/>
+    <mergeCell ref="B34:D34"/>
+    <mergeCell ref="B28:D28"/>
+    <mergeCell ref="B37:D37"/>
+    <mergeCell ref="B40:D40"/>
+    <mergeCell ref="B30:D30"/>
+    <mergeCell ref="B24:D24"/>
+    <mergeCell ref="B33:D33"/>
+    <mergeCell ref="B36:D36"/>
+    <mergeCell ref="B45:D45"/>
+    <mergeCell ref="B41:D41"/>
+    <mergeCell ref="B32:D32"/>
+    <mergeCell ref="B35:D35"/>
+    <mergeCell ref="B26:D26"/>
+    <mergeCell ref="B25:D25"/>
+    <mergeCell ref="B47:D47"/>
+    <mergeCell ref="B31:D31"/>
+    <mergeCell ref="B46:D46"/>
+    <mergeCell ref="B27:D27"/>
+    <mergeCell ref="B43:D43"/>
+    <mergeCell ref="B39:D39"/>
+  </mergeCells>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+  <pageSetup orientation="landscape" fitToHeight="0" fitToWidth="1"/>
+</worksheet>
 </file>
--- a/reports/dashboard.xlsx
+++ b/reports/dashboard.xlsx
@@ -196,12 +196,12 @@
     <xf numFmtId="0" fontId="3" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="164" fontId="6" fillId="3" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="164" fontId="7" fillId="4" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="164" fontId="7" fillId="0" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="166" fontId="7" fillId="0" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="164" fontId="6" fillId="0" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="166" fontId="6" fillId="0" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="164" fontId="7" fillId="0" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="164" fontId="8" fillId="3" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="164" fontId="9" fillId="4" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="166" fontId="7" fillId="0" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="1" fontId="4" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="right"/>
     </xf>
@@ -811,7 +811,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
-  <dimension ref="A1:O64"/>
+  <dimension ref="A1:O55"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="40" customWidth="1" min="1" max="1"/>
@@ -924,706 +924,611 @@
     </row>
     <row r="5">
       <c r="A5" s="3" t="n">
-        <v>2025</v>
-      </c>
-      <c r="B5" s="6" t="n"/>
+        <v>2026</v>
+      </c>
+      <c r="B5" s="14" t="n">
+        <v>0.007486499999999999</v>
+      </c>
       <c r="C5" s="6" t="n"/>
       <c r="D5" s="6" t="n"/>
-      <c r="E5" s="6" t="n"/>
-      <c r="F5" s="6" t="n"/>
+      <c r="E5" s="14" t="n">
+        <v>0.007542532827983304</v>
+      </c>
+      <c r="F5" s="14" t="n">
+        <v>0.05840394725370424</v>
+      </c>
       <c r="G5" s="6" t="n"/>
-      <c r="H5" s="6" t="n"/>
+      <c r="H5" s="15" t="n">
+        <v>-0.07320193545895015</v>
+      </c>
       <c r="I5" s="6" t="n"/>
-      <c r="J5" s="6" t="n"/>
-      <c r="K5" s="14" t="n">
-        <v>0.001868000000000001</v>
-      </c>
-      <c r="L5" s="15" t="n">
-        <v>-0.01919514347199431</v>
-      </c>
-      <c r="M5" s="15" t="n">
-        <v>-0.06368475846116115</v>
-      </c>
-      <c r="N5" s="16" t="n">
-        <v>-0.07994200000000007</v>
-      </c>
-      <c r="O5" s="17" t="n">
-        <v>-1598.84</v>
+      <c r="J5" s="15" t="n">
+        <v>-0.08522889614546995</v>
+      </c>
+      <c r="K5" s="6" t="n"/>
+      <c r="L5" s="6" t="n"/>
+      <c r="M5" s="6" t="n"/>
+      <c r="N5" s="18" t="n">
+        <v>-0.08914000000000022</v>
+      </c>
+      <c r="O5" s="21" t="n">
+        <v>-1782.8</v>
       </c>
     </row>
     <row r="6">
-      <c r="A6" s="3" t="n">
-        <v>2026</v>
-      </c>
-      <c r="B6" s="15" t="n">
-        <v>-0.03431848861702198</v>
-      </c>
-      <c r="C6" s="14" t="n">
-        <v>0.02423287783784272</v>
-      </c>
+      <c r="A6" s="3" t="inlineStr">
+        <is>
+          <t>Avg</t>
+        </is>
+      </c>
+      <c r="B6" s="16" t="n">
+        <v>0.007486499999999999</v>
+      </c>
+      <c r="C6" s="6" t="n"/>
       <c r="D6" s="6" t="n"/>
-      <c r="E6" s="15" t="n">
-        <v>-0.01347122872352993</v>
-      </c>
-      <c r="F6" s="6" t="n"/>
-      <c r="G6" s="14" t="n">
-        <v>0.03094387162637448</v>
-      </c>
-      <c r="H6" s="6" t="n"/>
-      <c r="I6" s="15" t="n">
-        <v>-0.05060049085150257</v>
-      </c>
-      <c r="J6" s="15" t="n">
-        <v>-0.01316202762711363</v>
+      <c r="E6" s="16" t="n">
+        <v>0.007542532827983304</v>
+      </c>
+      <c r="F6" s="16" t="n">
+        <v>0.05840394725370424</v>
+      </c>
+      <c r="G6" s="6" t="n"/>
+      <c r="H6" s="18" t="n">
+        <v>-0.07320193545895015</v>
+      </c>
+      <c r="I6" s="6" t="n"/>
+      <c r="J6" s="18" t="n">
+        <v>-0.08522889614546995</v>
       </c>
       <c r="K6" s="6" t="n"/>
       <c r="L6" s="6" t="n"/>
       <c r="M6" s="6" t="n"/>
-      <c r="N6" s="16" t="n">
-        <v>-0.05751974332052978</v>
-      </c>
-      <c r="O6" s="17" t="n">
-        <v>-1058.43</v>
-      </c>
-    </row>
-    <row r="7">
-      <c r="A7" s="3" t="inlineStr">
-        <is>
-          <t>Avg</t>
-        </is>
-      </c>
-      <c r="B7" s="16" t="n">
-        <v>-0.03431848861702198</v>
-      </c>
-      <c r="C7" s="18" t="n">
-        <v>0.02423287783784272</v>
-      </c>
-      <c r="D7" s="6" t="n"/>
-      <c r="E7" s="16" t="n">
-        <v>-0.01347122872352993</v>
-      </c>
-      <c r="F7" s="6" t="n"/>
-      <c r="G7" s="18" t="n">
-        <v>0.03094387162637448</v>
-      </c>
-      <c r="H7" s="6" t="n"/>
-      <c r="I7" s="16" t="n">
-        <v>-0.05060049085150257</v>
-      </c>
-      <c r="J7" s="16" t="n">
-        <v>-0.01316202762711363</v>
-      </c>
-      <c r="K7" s="18" t="n">
-        <v>0.001868000000000001</v>
-      </c>
-      <c r="L7" s="16" t="n">
-        <v>-0.01919514347199431</v>
-      </c>
-      <c r="M7" s="16" t="n">
-        <v>-0.06368475846116115</v>
+    </row>
+    <row r="8">
+      <c r="A8" s="13" t="inlineStr">
+        <is>
+          <t>WEEKLY returns (% of capital at start of that week; weeks split at month edges)</t>
+        </is>
       </c>
     </row>
     <row r="9">
-      <c r="A9" s="13" t="inlineStr">
-        <is>
-          <t>WEEKLY returns (% of capital at start of that week; weeks split at month edges)</t>
+      <c r="A9" s="2" t="inlineStr">
+        <is>
+          <t>Month</t>
+        </is>
+      </c>
+      <c r="B9" s="2" t="inlineStr">
+        <is>
+          <t>W1</t>
+        </is>
+      </c>
+      <c r="C9" s="2" t="inlineStr">
+        <is>
+          <t>W2</t>
+        </is>
+      </c>
+      <c r="D9" s="2" t="inlineStr">
+        <is>
+          <t>W3</t>
+        </is>
+      </c>
+      <c r="E9" s="2" t="inlineStr">
+        <is>
+          <t>W4</t>
+        </is>
+      </c>
+      <c r="F9" s="2" t="inlineStr">
+        <is>
+          <t>W5</t>
+        </is>
+      </c>
+      <c r="G9" s="2" t="inlineStr">
+        <is>
+          <t>W6</t>
+        </is>
+      </c>
+      <c r="H9" s="2" t="inlineStr">
+        <is>
+          <t>Month %</t>
+        </is>
+      </c>
+      <c r="I9" s="2" t="inlineStr">
+        <is>
+          <t>Month P&amp;L (Rs)</t>
         </is>
       </c>
     </row>
     <row r="10">
-      <c r="A10" s="2" t="inlineStr">
-        <is>
-          <t>Month</t>
-        </is>
-      </c>
-      <c r="B10" s="2" t="inlineStr">
-        <is>
-          <t>W1</t>
-        </is>
-      </c>
-      <c r="C10" s="2" t="inlineStr">
-        <is>
-          <t>W2</t>
-        </is>
-      </c>
-      <c r="D10" s="2" t="inlineStr">
-        <is>
-          <t>W3</t>
-        </is>
-      </c>
-      <c r="E10" s="2" t="inlineStr">
-        <is>
-          <t>W4</t>
-        </is>
-      </c>
-      <c r="F10" s="2" t="inlineStr">
-        <is>
-          <t>W5</t>
-        </is>
-      </c>
-      <c r="G10" s="2" t="inlineStr">
-        <is>
-          <t>W6</t>
-        </is>
-      </c>
-      <c r="H10" s="2" t="inlineStr">
-        <is>
-          <t>Month %</t>
-        </is>
-      </c>
-      <c r="I10" s="2" t="inlineStr">
-        <is>
-          <t>Month P&amp;L (Rs)</t>
-        </is>
+      <c r="A10" s="3" t="inlineStr">
+        <is>
+          <t>2026-Jan</t>
+        </is>
+      </c>
+      <c r="B10" s="14" t="n">
+        <v>0.007486499999999999</v>
+      </c>
+      <c r="C10" s="6" t="n"/>
+      <c r="D10" s="6" t="n"/>
+      <c r="E10" s="6" t="n"/>
+      <c r="F10" s="6" t="n"/>
+      <c r="G10" s="6" t="n"/>
+      <c r="H10" s="19" t="n">
+        <v>0.007486499999999999</v>
+      </c>
+      <c r="I10" s="17" t="n">
+        <v>149.73</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" s="3" t="inlineStr">
         <is>
-          <t>2025-Oct</t>
+          <t>2026-Apr</t>
         </is>
       </c>
       <c r="B11" s="14" t="n">
-        <v>0.0154865</v>
+        <v>0.02240377414486447</v>
       </c>
       <c r="C11" s="15" t="n">
-        <v>-0.0134108134376971</v>
+        <v>-0.01453558925808061</v>
       </c>
       <c r="D11" s="6" t="n"/>
       <c r="E11" s="6" t="n"/>
       <c r="F11" s="6" t="n"/>
       <c r="G11" s="6" t="n"/>
-      <c r="H11" s="20" t="n">
-        <v>0.001868000000000001</v>
-      </c>
-      <c r="I11" s="19" t="n">
-        <v>37.36</v>
+      <c r="H11" s="19" t="n">
+        <v>0.007542532827983304</v>
+      </c>
+      <c r="I11" s="17" t="n">
+        <v>151.98</v>
       </c>
     </row>
     <row r="12">
       <c r="A12" s="3" t="inlineStr">
         <is>
-          <t>2025-Nov</t>
-        </is>
-      </c>
-      <c r="B12" s="15" t="n">
-        <v>-0.01630703845217134</v>
-      </c>
-      <c r="C12" s="15" t="n">
-        <v>-0.002935982194361311</v>
-      </c>
+          <t>2026-May</t>
+        </is>
+      </c>
+      <c r="B12" s="14" t="n">
+        <v>0.05840394725370424</v>
+      </c>
+      <c r="C12" s="6" t="n"/>
       <c r="D12" s="6" t="n"/>
       <c r="E12" s="6" t="n"/>
       <c r="F12" s="6" t="n"/>
       <c r="G12" s="6" t="n"/>
-      <c r="H12" s="21" t="n">
-        <v>-0.01919514347199431</v>
+      <c r="H12" s="19" t="n">
+        <v>0.05840394725370424</v>
       </c>
       <c r="I12" s="17" t="n">
-        <v>-384.62</v>
+        <v>1185.7</v>
       </c>
     </row>
     <row r="13">
       <c r="A13" s="3" t="inlineStr">
         <is>
-          <t>2025-Dec</t>
+          <t>2026-Jul</t>
         </is>
       </c>
       <c r="B13" s="15" t="n">
-        <v>-0.02755290102041751</v>
+        <v>-0.01546998917040258</v>
       </c>
       <c r="C13" s="15" t="n">
-        <v>-0.03715560206684546</v>
-      </c>
-      <c r="D13" s="6" t="n"/>
+        <v>-0.04929992909477665</v>
+      </c>
+      <c r="D13" s="15" t="n">
+        <v>-0.009823459158335844</v>
+      </c>
       <c r="E13" s="6" t="n"/>
       <c r="F13" s="6" t="n"/>
       <c r="G13" s="6" t="n"/>
-      <c r="H13" s="21" t="n">
-        <v>-0.06368475846116115</v>
-      </c>
-      <c r="I13" s="17" t="n">
-        <v>-1251.58</v>
+      <c r="H13" s="20" t="n">
+        <v>-0.07320193545895015</v>
+      </c>
+      <c r="I13" s="21" t="n">
+        <v>-1572.92</v>
       </c>
     </row>
     <row r="14">
       <c r="A14" s="3" t="inlineStr">
         <is>
-          <t>2026-Jan</t>
-        </is>
-      </c>
-      <c r="B14" s="14" t="n">
-        <v>0.01397574935493198</v>
+          <t>2026-Sep</t>
+        </is>
+      </c>
+      <c r="B14" s="15" t="n">
+        <v>-0.02881419509111205</v>
       </c>
       <c r="C14" s="15" t="n">
-        <v>-0.04762859269827473</v>
-      </c>
-      <c r="D14" s="6" t="n"/>
+        <v>-0.009536898152959539</v>
+      </c>
+      <c r="D14" s="15" t="n">
+        <v>-0.0490190653479653</v>
+      </c>
       <c r="E14" s="6" t="n"/>
       <c r="F14" s="6" t="n"/>
       <c r="G14" s="6" t="n"/>
-      <c r="H14" s="21" t="n">
-        <v>-0.03431848861702198</v>
-      </c>
-      <c r="I14" s="17" t="n">
-        <v>-631.5</v>
-      </c>
-    </row>
-    <row r="15">
-      <c r="A15" s="3" t="inlineStr">
-        <is>
-          <t>2026-Feb</t>
-        </is>
-      </c>
-      <c r="B15" s="14" t="n">
-        <v>0.02423287783784272</v>
-      </c>
-      <c r="C15" s="6" t="n"/>
-      <c r="D15" s="6" t="n"/>
-      <c r="E15" s="6" t="n"/>
-      <c r="F15" s="6" t="n"/>
-      <c r="G15" s="6" t="n"/>
-      <c r="H15" s="20" t="n">
-        <v>0.02423287783784272</v>
-      </c>
-      <c r="I15" s="19" t="n">
-        <v>430.61</v>
+      <c r="H14" s="20" t="n">
+        <v>-0.08522889614546995</v>
+      </c>
+      <c r="I14" s="21" t="n">
+        <v>-1697.29</v>
       </c>
     </row>
     <row r="16">
-      <c r="A16" s="3" t="inlineStr">
-        <is>
-          <t>2026-Apr</t>
-        </is>
-      </c>
-      <c r="B16" s="15" t="n">
-        <v>-0.01347122872352993</v>
-      </c>
-      <c r="C16" s="6" t="n"/>
-      <c r="D16" s="6" t="n"/>
-      <c r="E16" s="6" t="n"/>
-      <c r="F16" s="6" t="n"/>
-      <c r="G16" s="6" t="n"/>
-      <c r="H16" s="21" t="n">
-        <v>-0.01347122872352993</v>
-      </c>
-      <c r="I16" s="17" t="n">
-        <v>-245.18</v>
+      <c r="A16" s="13" t="inlineStr">
+        <is>
+          <t>DAILY returns (% of capital at start of that day; blank = no trade that day)</t>
+        </is>
       </c>
     </row>
     <row r="17">
-      <c r="A17" s="3" t="inlineStr">
-        <is>
-          <t>2026-Jun</t>
-        </is>
-      </c>
-      <c r="B17" s="14" t="n">
-        <v>0.01436417194232945</v>
-      </c>
-      <c r="C17" s="14" t="n">
-        <v>0.01634491846483281</v>
-      </c>
-      <c r="D17" s="6" t="n"/>
-      <c r="E17" s="6" t="n"/>
-      <c r="F17" s="6" t="n"/>
-      <c r="G17" s="6" t="n"/>
-      <c r="H17" s="20" t="n">
-        <v>0.03094387162637448</v>
-      </c>
-      <c r="I17" s="19" t="n">
-        <v>555.6</v>
+      <c r="A17" s="2" t="inlineStr">
+        <is>
+          <t>Week starting (Mon)</t>
+        </is>
+      </c>
+      <c r="B17" s="2" t="inlineStr">
+        <is>
+          <t>Mon</t>
+        </is>
+      </c>
+      <c r="C17" s="2" t="inlineStr">
+        <is>
+          <t>Tue</t>
+        </is>
+      </c>
+      <c r="D17" s="2" t="inlineStr">
+        <is>
+          <t>Wed</t>
+        </is>
+      </c>
+      <c r="E17" s="2" t="inlineStr">
+        <is>
+          <t>Thu</t>
+        </is>
+      </c>
+      <c r="F17" s="2" t="inlineStr">
+        <is>
+          <t>Fri</t>
+        </is>
+      </c>
+      <c r="G17" s="2" t="inlineStr">
+        <is>
+          <t>Week %</t>
+        </is>
+      </c>
+      <c r="H17" s="2" t="inlineStr">
+        <is>
+          <t>Week P&amp;L (Rs)</t>
+        </is>
       </c>
     </row>
     <row r="18">
       <c r="A18" s="3" t="inlineStr">
         <is>
-          <t>2026-Aug</t>
-        </is>
-      </c>
-      <c r="B18" s="15" t="n">
-        <v>-0.03910335055041169</v>
-      </c>
-      <c r="C18" s="15" t="n">
-        <v>-0.01196501237430328</v>
+          <t>19-Jan-2026</t>
+        </is>
+      </c>
+      <c r="B18" s="6" t="n"/>
+      <c r="C18" s="14" t="n">
+        <v>0.007486499999999999</v>
       </c>
       <c r="D18" s="6" t="n"/>
       <c r="E18" s="6" t="n"/>
       <c r="F18" s="6" t="n"/>
-      <c r="G18" s="6" t="n"/>
-      <c r="H18" s="21" t="n">
-        <v>-0.05060049085150257</v>
-      </c>
-      <c r="I18" s="17" t="n">
-        <v>-936.65</v>
+      <c r="G18" s="19" t="n">
+        <v>0.007486499999999999</v>
+      </c>
+      <c r="H18" s="17" t="n">
+        <v>149.73</v>
       </c>
     </row>
     <row r="19">
       <c r="A19" s="3" t="inlineStr">
         <is>
-          <t>2026-Sep</t>
-        </is>
-      </c>
-      <c r="B19" s="15" t="n">
-        <v>-0.01316202762711363</v>
-      </c>
-      <c r="C19" s="6" t="n"/>
+          <t>06-Apr-2026</t>
+        </is>
+      </c>
+      <c r="B19" s="6" t="n"/>
+      <c r="C19" s="14" t="n">
+        <v>0.02240377414486447</v>
+      </c>
       <c r="D19" s="6" t="n"/>
       <c r="E19" s="6" t="n"/>
       <c r="F19" s="6" t="n"/>
-      <c r="G19" s="6" t="n"/>
-      <c r="H19" s="21" t="n">
-        <v>-0.01316202762711363</v>
-      </c>
-      <c r="I19" s="17" t="n">
-        <v>-231.31</v>
+      <c r="G19" s="19" t="n">
+        <v>0.02240377414486447</v>
+      </c>
+      <c r="H19" s="17" t="n">
+        <v>451.43</v>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" s="3" t="inlineStr">
+        <is>
+          <t>20-Apr-2026</t>
+        </is>
+      </c>
+      <c r="B20" s="6" t="n"/>
+      <c r="C20" s="15" t="n">
+        <v>-0.01453558925808061</v>
+      </c>
+      <c r="D20" s="6" t="n"/>
+      <c r="E20" s="6" t="n"/>
+      <c r="F20" s="6" t="n"/>
+      <c r="G20" s="20" t="n">
+        <v>-0.01453558925808061</v>
+      </c>
+      <c r="H20" s="21" t="n">
+        <v>-299.45</v>
       </c>
     </row>
     <row r="21">
-      <c r="A21" s="13" t="inlineStr">
-        <is>
-          <t>DAILY returns (% of capital at start of that day; blank = no trade that day)</t>
-        </is>
+      <c r="A21" s="3" t="inlineStr">
+        <is>
+          <t>11-May-2026</t>
+        </is>
+      </c>
+      <c r="B21" s="6" t="n"/>
+      <c r="C21" s="14" t="n">
+        <v>0.05840394725370424</v>
+      </c>
+      <c r="D21" s="6" t="n"/>
+      <c r="E21" s="6" t="n"/>
+      <c r="F21" s="6" t="n"/>
+      <c r="G21" s="19" t="n">
+        <v>0.05840394725370424</v>
+      </c>
+      <c r="H21" s="17" t="n">
+        <v>1185.7</v>
       </c>
     </row>
     <row r="22">
-      <c r="A22" s="2" t="inlineStr">
-        <is>
-          <t>Week starting (Mon)</t>
-        </is>
-      </c>
-      <c r="B22" s="2" t="inlineStr">
-        <is>
-          <t>Mon</t>
-        </is>
-      </c>
-      <c r="C22" s="2" t="inlineStr">
-        <is>
-          <t>Tue</t>
-        </is>
-      </c>
-      <c r="D22" s="2" t="inlineStr">
-        <is>
-          <t>Wed</t>
-        </is>
-      </c>
-      <c r="E22" s="2" t="inlineStr">
-        <is>
-          <t>Thu</t>
-        </is>
-      </c>
-      <c r="F22" s="2" t="inlineStr">
-        <is>
-          <t>Fri</t>
-        </is>
-      </c>
-      <c r="G22" s="2" t="inlineStr">
-        <is>
-          <t>Week %</t>
-        </is>
-      </c>
-      <c r="H22" s="2" t="inlineStr">
-        <is>
-          <t>Week P&amp;L (Rs)</t>
-        </is>
+      <c r="A22" s="3" t="inlineStr">
+        <is>
+          <t>06-Jul-2026</t>
+        </is>
+      </c>
+      <c r="B22" s="6" t="n"/>
+      <c r="C22" s="15" t="n">
+        <v>-0.01546998917040258</v>
+      </c>
+      <c r="D22" s="6" t="n"/>
+      <c r="E22" s="6" t="n"/>
+      <c r="F22" s="6" t="n"/>
+      <c r="G22" s="20" t="n">
+        <v>-0.01546998917040258</v>
+      </c>
+      <c r="H22" s="21" t="n">
+        <v>-332.41</v>
       </c>
     </row>
     <row r="23">
       <c r="A23" s="3" t="inlineStr">
         <is>
-          <t>06-Oct-2025</t>
-        </is>
-      </c>
-      <c r="B23" s="14" t="n">
-        <v>0.0154865</v>
-      </c>
-      <c r="C23" s="6" t="n"/>
+          <t>13-Jul-2026</t>
+        </is>
+      </c>
+      <c r="B23" s="6" t="n"/>
+      <c r="C23" s="15" t="n">
+        <v>-0.04929992909477665</v>
+      </c>
       <c r="D23" s="6" t="n"/>
       <c r="E23" s="6" t="n"/>
       <c r="F23" s="6" t="n"/>
       <c r="G23" s="20" t="n">
-        <v>0.0154865</v>
-      </c>
-      <c r="H23" s="19" t="n">
-        <v>309.73</v>
+        <v>-0.04929992909477665</v>
+      </c>
+      <c r="H23" s="21" t="n">
+        <v>-1042.94</v>
       </c>
     </row>
     <row r="24">
       <c r="A24" s="3" t="inlineStr">
         <is>
-          <t>13-Oct-2025</t>
+          <t>27-Jul-2026</t>
         </is>
       </c>
       <c r="B24" s="6" t="n"/>
       <c r="C24" s="15" t="n">
-        <v>-0.0134108134376971</v>
+        <v>-0.009823459158335844</v>
       </c>
       <c r="D24" s="6" t="n"/>
       <c r="E24" s="6" t="n"/>
       <c r="F24" s="6" t="n"/>
-      <c r="G24" s="21" t="n">
-        <v>-0.0134108134376971</v>
-      </c>
-      <c r="H24" s="17" t="n">
-        <v>-272.37</v>
+      <c r="G24" s="20" t="n">
+        <v>-0.009823459158335844</v>
+      </c>
+      <c r="H24" s="21" t="n">
+        <v>-197.57</v>
       </c>
     </row>
     <row r="25">
       <c r="A25" s="3" t="inlineStr">
         <is>
-          <t>10-Nov-2025</t>
+          <t>07-Sep-2026</t>
         </is>
       </c>
       <c r="B25" s="6" t="n"/>
       <c r="C25" s="15" t="n">
-        <v>-0.01630703845217134</v>
+        <v>-0.02881419509111205</v>
       </c>
       <c r="D25" s="6" t="n"/>
       <c r="E25" s="6" t="n"/>
       <c r="F25" s="6" t="n"/>
-      <c r="G25" s="21" t="n">
-        <v>-0.01630703845217134</v>
-      </c>
-      <c r="H25" s="17" t="n">
-        <v>-326.75</v>
+      <c r="G25" s="20" t="n">
+        <v>-0.02881419509111205</v>
+      </c>
+      <c r="H25" s="21" t="n">
+        <v>-573.8200000000001</v>
       </c>
     </row>
     <row r="26">
       <c r="A26" s="3" t="inlineStr">
         <is>
-          <t>24-Nov-2025</t>
-        </is>
-      </c>
-      <c r="B26" s="14" t="n">
-        <v>0.01547187022623856</v>
-      </c>
+          <t>14-Sep-2026</t>
+        </is>
+      </c>
+      <c r="B26" s="6" t="n"/>
       <c r="C26" s="15" t="n">
-        <v>-0.01812738782857545</v>
+        <v>-0.009536898152959539</v>
       </c>
       <c r="D26" s="6" t="n"/>
       <c r="E26" s="6" t="n"/>
       <c r="F26" s="6" t="n"/>
-      <c r="G26" s="21" t="n">
-        <v>-0.002935982194361311</v>
-      </c>
-      <c r="H26" s="17" t="n">
-        <v>-57.87</v>
+      <c r="G26" s="20" t="n">
+        <v>-0.009536898152959539</v>
+      </c>
+      <c r="H26" s="21" t="n">
+        <v>-184.45</v>
       </c>
     </row>
     <row r="27">
       <c r="A27" s="3" t="inlineStr">
         <is>
-          <t>08-Dec-2025</t>
+          <t>28-Sep-2026</t>
         </is>
       </c>
       <c r="B27" s="6" t="n"/>
       <c r="C27" s="15" t="n">
-        <v>-0.02755290102041751</v>
+        <v>-0.0490190653479653</v>
       </c>
       <c r="D27" s="6" t="n"/>
       <c r="E27" s="6" t="n"/>
       <c r="F27" s="6" t="n"/>
-      <c r="G27" s="21" t="n">
-        <v>-0.02755290102041751</v>
-      </c>
-      <c r="H27" s="17" t="n">
-        <v>-541.49</v>
-      </c>
-    </row>
-    <row r="28">
-      <c r="A28" s="3" t="inlineStr">
-        <is>
-          <t>29-Dec-2025</t>
-        </is>
-      </c>
-      <c r="B28" s="6" t="n"/>
-      <c r="C28" s="15" t="n">
-        <v>-0.03715560206684546</v>
-      </c>
-      <c r="D28" s="6" t="n"/>
-      <c r="E28" s="6" t="n"/>
-      <c r="F28" s="6" t="n"/>
-      <c r="G28" s="21" t="n">
-        <v>-0.03715560206684546</v>
-      </c>
-      <c r="H28" s="17" t="n">
-        <v>-710.09</v>
+      <c r="G27" s="20" t="n">
+        <v>-0.0490190653479653</v>
+      </c>
+      <c r="H27" s="21" t="n">
+        <v>-939.02</v>
       </c>
     </row>
     <row r="29">
-      <c r="A29" s="3" t="inlineStr">
-        <is>
-          <t>12-Jan-2026</t>
-        </is>
-      </c>
-      <c r="B29" s="14" t="n">
-        <v>0.01397574935493198</v>
-      </c>
-      <c r="C29" s="6" t="n"/>
-      <c r="D29" s="6" t="n"/>
-      <c r="E29" s="6" t="n"/>
-      <c r="F29" s="6" t="n"/>
-      <c r="G29" s="20" t="n">
-        <v>0.01397574935493198</v>
-      </c>
-      <c r="H29" s="19" t="n">
-        <v>257.17</v>
+      <c r="A29" s="13" t="inlineStr">
+        <is>
+          <t>STATISTICS (all trades for this index)</t>
+        </is>
       </c>
     </row>
     <row r="30">
       <c r="A30" s="3" t="inlineStr">
         <is>
-          <t>26-Jan-2026</t>
-        </is>
-      </c>
-      <c r="B30" s="6" t="n"/>
-      <c r="C30" s="15" t="n">
-        <v>-0.04762859269827473</v>
-      </c>
-      <c r="D30" s="6" t="n"/>
-      <c r="E30" s="6" t="n"/>
-      <c r="F30" s="6" t="n"/>
-      <c r="G30" s="21" t="n">
-        <v>-0.02454989272887767</v>
-      </c>
-      <c r="H30" s="17" t="n">
-        <v>-458.06</v>
-      </c>
+          <t>All trades</t>
+        </is>
+      </c>
+      <c r="B30" s="22" t="n">
+        <v>22</v>
+      </c>
+      <c r="C30" s="23" t="n"/>
+      <c r="D30" s="24" t="n"/>
     </row>
     <row r="31">
       <c r="A31" s="3" t="inlineStr">
         <is>
-          <t>20-Apr-2026</t>
-        </is>
-      </c>
-      <c r="B31" s="15" t="n">
-        <v>-0.01347122872352993</v>
-      </c>
-      <c r="C31" s="6" t="n"/>
-      <c r="D31" s="6" t="n"/>
-      <c r="E31" s="6" t="n"/>
-      <c r="F31" s="6" t="n"/>
-      <c r="G31" s="21" t="n">
-        <v>-0.01347122872352993</v>
-      </c>
-      <c r="H31" s="17" t="n">
-        <v>-245.18</v>
-      </c>
+          <t>Winners</t>
+        </is>
+      </c>
+      <c r="B31" s="25" t="inlineStr">
+        <is>
+          <t>5 (22.7%)</t>
+        </is>
+      </c>
+      <c r="C31" s="23" t="n"/>
+      <c r="D31" s="24" t="n"/>
     </row>
     <row r="32">
       <c r="A32" s="3" t="inlineStr">
         <is>
-          <t>01-Jun-2026</t>
-        </is>
-      </c>
-      <c r="B32" s="14" t="n">
-        <v>0.01436417194232945</v>
-      </c>
-      <c r="C32" s="6" t="n"/>
-      <c r="D32" s="6" t="n"/>
-      <c r="E32" s="6" t="n"/>
-      <c r="F32" s="6" t="n"/>
-      <c r="G32" s="20" t="n">
-        <v>0.01436417194232945</v>
-      </c>
-      <c r="H32" s="19" t="n">
-        <v>257.91</v>
-      </c>
+          <t>Losers</t>
+        </is>
+      </c>
+      <c r="B32" s="25" t="inlineStr">
+        <is>
+          <t>17 (77.3%)</t>
+        </is>
+      </c>
+      <c r="C32" s="23" t="n"/>
+      <c r="D32" s="24" t="n"/>
     </row>
     <row r="33">
       <c r="A33" s="3" t="inlineStr">
         <is>
-          <t>29-Jun-2026</t>
-        </is>
-      </c>
-      <c r="B33" s="14" t="n">
-        <v>0.01634491846483281</v>
-      </c>
-      <c r="C33" s="6" t="n"/>
-      <c r="D33" s="6" t="n"/>
-      <c r="E33" s="6" t="n"/>
-      <c r="F33" s="6" t="n"/>
-      <c r="G33" s="20" t="n">
-        <v>0.01634491846483281</v>
-      </c>
-      <c r="H33" s="19" t="n">
-        <v>297.69</v>
-      </c>
+          <t>Net P&amp;L (Rs)</t>
+        </is>
+      </c>
+      <c r="B33" s="27" t="n">
+        <v>-1782.8</v>
+      </c>
+      <c r="C33" s="23" t="n"/>
+      <c r="D33" s="24" t="n"/>
     </row>
     <row r="34">
       <c r="A34" s="3" t="inlineStr">
         <is>
-          <t>10-Aug-2026</t>
-        </is>
-      </c>
-      <c r="B34" s="6" t="n"/>
-      <c r="C34" s="15" t="n">
-        <v>-0.03910335055041169</v>
-      </c>
-      <c r="D34" s="6" t="n"/>
-      <c r="E34" s="6" t="n"/>
-      <c r="F34" s="6" t="n"/>
-      <c r="G34" s="21" t="n">
-        <v>-0.03910335055041169</v>
-      </c>
-      <c r="H34" s="17" t="n">
-        <v>-723.83</v>
-      </c>
+          <t>Total Profit (Rs)</t>
+        </is>
+      </c>
+      <c r="B34" s="26" t="n">
+        <v>2338.58</v>
+      </c>
+      <c r="C34" s="23" t="n"/>
+      <c r="D34" s="24" t="n"/>
     </row>
     <row r="35">
       <c r="A35" s="3" t="inlineStr">
         <is>
-          <t>24-Aug-2026</t>
-        </is>
-      </c>
-      <c r="B35" s="6" t="n"/>
-      <c r="C35" s="15" t="n">
-        <v>-0.01196501237430328</v>
-      </c>
-      <c r="D35" s="6" t="n"/>
-      <c r="E35" s="6" t="n"/>
-      <c r="F35" s="6" t="n"/>
-      <c r="G35" s="21" t="n">
-        <v>-0.01196501237430328</v>
-      </c>
-      <c r="H35" s="17" t="n">
-        <v>-212.82</v>
-      </c>
+          <t>Total Loss (Rs)</t>
+        </is>
+      </c>
+      <c r="B35" s="27" t="n">
+        <v>-4121.38</v>
+      </c>
+      <c r="C35" s="23" t="n"/>
+      <c r="D35" s="24" t="n"/>
     </row>
     <row r="36">
       <c r="A36" s="3" t="inlineStr">
         <is>
-          <t>07-Sep-2026</t>
-        </is>
-      </c>
-      <c r="B36" s="6" t="n"/>
-      <c r="C36" s="15" t="n">
-        <v>-0.01316202762711363</v>
-      </c>
-      <c r="D36" s="6" t="n"/>
-      <c r="E36" s="6" t="n"/>
-      <c r="F36" s="6" t="n"/>
-      <c r="G36" s="21" t="n">
-        <v>-0.01316202762711363</v>
-      </c>
-      <c r="H36" s="17" t="n">
-        <v>-231.31</v>
-      </c>
+          <t>Transaction costs (Rs)</t>
+        </is>
+      </c>
+      <c r="B36" s="28" t="n">
+        <v>842.95</v>
+      </c>
+      <c r="C36" s="23" t="n"/>
+      <c r="D36" s="24" t="n"/>
+    </row>
+    <row r="37">
+      <c r="A37" s="3" t="inlineStr">
+        <is>
+          <t>Avg Profit/Loss per trade (Rs)</t>
+        </is>
+      </c>
+      <c r="B37" s="27" t="n">
+        <v>-81.04000000000001</v>
+      </c>
+      <c r="C37" s="23" t="n"/>
+      <c r="D37" s="24" t="n"/>
     </row>
     <row r="38">
-      <c r="A38" s="13" t="inlineStr">
-        <is>
-          <t>STATISTICS (all trades for this index)</t>
-        </is>
-      </c>
+      <c r="A38" s="3" t="inlineStr">
+        <is>
+          <t>Avg Profit/Loss per trade (% of premium)</t>
+        </is>
+      </c>
+      <c r="B38" s="29" t="n">
+        <v>-3.56</v>
+      </c>
+      <c r="C38" s="23" t="n"/>
+      <c r="D38" s="24" t="n"/>
     </row>
     <row r="39">
       <c r="A39" s="3" t="inlineStr">
         <is>
-          <t>All trades</t>
-        </is>
-      </c>
-      <c r="B39" s="22" t="n">
-        <v>23</v>
+          <t>Avg Win (Rs)</t>
+        </is>
+      </c>
+      <c r="B39" s="26" t="n">
+        <v>467.72</v>
       </c>
       <c r="C39" s="23" t="n"/>
       <c r="D39" s="24" t="n"/>
@@ -1631,13 +1536,11 @@
     <row r="40">
       <c r="A40" s="3" t="inlineStr">
         <is>
-          <t>Winners</t>
-        </is>
-      </c>
-      <c r="B40" s="25" t="inlineStr">
-        <is>
-          <t>7 (30.4%)</t>
-        </is>
+          <t>Avg Win (% of premium)</t>
+        </is>
+      </c>
+      <c r="B40" s="30" t="n">
+        <v>54.93</v>
       </c>
       <c r="C40" s="23" t="n"/>
       <c r="D40" s="24" t="n"/>
@@ -1645,13 +1548,11 @@
     <row r="41">
       <c r="A41" s="3" t="inlineStr">
         <is>
-          <t>Losers</t>
-        </is>
-      </c>
-      <c r="B41" s="25" t="inlineStr">
-        <is>
-          <t>16 (69.6%)</t>
-        </is>
+          <t>Avg Loss (Rs)</t>
+        </is>
+      </c>
+      <c r="B41" s="27" t="n">
+        <v>-242.43</v>
       </c>
       <c r="C41" s="23" t="n"/>
       <c r="D41" s="24" t="n"/>
@@ -1659,11 +1560,11 @@
     <row r="42">
       <c r="A42" s="3" t="inlineStr">
         <is>
-          <t>Net P&amp;L (Rs)</t>
-        </is>
-      </c>
-      <c r="B42" s="27" t="n">
-        <v>-2657.27</v>
+          <t>Avg Loss (% of premium)</t>
+        </is>
+      </c>
+      <c r="B42" s="31" t="n">
+        <v>-20.76</v>
       </c>
       <c r="C42" s="23" t="n"/>
       <c r="D42" s="24" t="n"/>
@@ -1671,11 +1572,11 @@
     <row r="43">
       <c r="A43" s="3" t="inlineStr">
         <is>
-          <t>Total Profit (Rs)</t>
+          <t>Largest Win (Rs)</t>
         </is>
       </c>
       <c r="B43" s="26" t="n">
-        <v>2174.65</v>
+        <v>552.97</v>
       </c>
       <c r="C43" s="23" t="n"/>
       <c r="D43" s="24" t="n"/>
@@ -1683,11 +1584,11 @@
     <row r="44">
       <c r="A44" s="3" t="inlineStr">
         <is>
-          <t>Total Loss (Rs)</t>
+          <t>Largest Loss (Rs)</t>
         </is>
       </c>
       <c r="B44" s="27" t="n">
-        <v>-4831.92</v>
+        <v>-332.41</v>
       </c>
       <c r="C44" s="23" t="n"/>
       <c r="D44" s="24" t="n"/>
@@ -1695,11 +1596,11 @@
     <row r="45">
       <c r="A45" s="3" t="inlineStr">
         <is>
-          <t>Transaction costs (Rs)</t>
-        </is>
-      </c>
-      <c r="B45" s="28" t="n">
-        <v>1462.97</v>
+          <t>Max Consecutive Wins</t>
+        </is>
+      </c>
+      <c r="B45" s="22" t="n">
+        <v>3</v>
       </c>
       <c r="C45" s="23" t="n"/>
       <c r="D45" s="24" t="n"/>
@@ -1707,11 +1608,11 @@
     <row r="46">
       <c r="A46" s="3" t="inlineStr">
         <is>
-          <t>Avg Profit/Loss per trade (Rs)</t>
-        </is>
-      </c>
-      <c r="B46" s="27" t="n">
-        <v>-115.53</v>
+          <t>Max Consecutive Losses</t>
+        </is>
+      </c>
+      <c r="B46" s="22" t="n">
+        <v>14</v>
       </c>
       <c r="C46" s="23" t="n"/>
       <c r="D46" s="24" t="n"/>
@@ -1719,11 +1620,11 @@
     <row r="47">
       <c r="A47" s="3" t="inlineStr">
         <is>
-          <t>Avg Profit/Loss per trade (% of premium)</t>
-        </is>
-      </c>
-      <c r="B47" s="29" t="n">
-        <v>-5.45</v>
+          <t>Max trade drawdown (Rs)</t>
+        </is>
+      </c>
+      <c r="B47" s="27" t="n">
+        <v>-332.41</v>
       </c>
       <c r="C47" s="23" t="n"/>
       <c r="D47" s="24" t="n"/>
@@ -1731,11 +1632,11 @@
     <row r="48">
       <c r="A48" s="3" t="inlineStr">
         <is>
-          <t>Avg Win (Rs)</t>
-        </is>
-      </c>
-      <c r="B48" s="26" t="n">
-        <v>310.66</v>
+          <t>Max system drawdown (Rs)</t>
+        </is>
+      </c>
+      <c r="B48" s="27" t="n">
+        <v>-3501.72</v>
       </c>
       <c r="C48" s="23" t="n"/>
       <c r="D48" s="24" t="n"/>
@@ -1743,11 +1644,11 @@
     <row r="49">
       <c r="A49" s="3" t="inlineStr">
         <is>
-          <t>Avg Win (% of premium)</t>
-        </is>
-      </c>
-      <c r="B49" s="30" t="n">
-        <v>16.01</v>
+          <t>Max system drawdown (%)</t>
+        </is>
+      </c>
+      <c r="B49" s="31" t="n">
+        <v>-16.12</v>
       </c>
       <c r="C49" s="23" t="n"/>
       <c r="D49" s="24" t="n"/>
@@ -1755,11 +1656,11 @@
     <row r="50">
       <c r="A50" s="3" t="inlineStr">
         <is>
-          <t>Avg Loss (Rs)</t>
-        </is>
-      </c>
-      <c r="B50" s="27" t="n">
-        <v>-302</v>
+          <t>Recovery Factor</t>
+        </is>
+      </c>
+      <c r="B50" s="32" t="n">
+        <v>-0.51</v>
       </c>
       <c r="C50" s="23" t="n"/>
       <c r="D50" s="24" t="n"/>
@@ -1767,11 +1668,11 @@
     <row r="51">
       <c r="A51" s="3" t="inlineStr">
         <is>
-          <t>Avg Loss (% of premium)</t>
-        </is>
-      </c>
-      <c r="B51" s="31" t="n">
-        <v>-14.84</v>
+          <t>Profit Factor</t>
+        </is>
+      </c>
+      <c r="B51" s="32" t="n">
+        <v>0.57</v>
       </c>
       <c r="C51" s="23" t="n"/>
       <c r="D51" s="24" t="n"/>
@@ -1779,11 +1680,11 @@
     <row r="52">
       <c r="A52" s="3" t="inlineStr">
         <is>
-          <t>Largest Win (Rs)</t>
-        </is>
-      </c>
-      <c r="B52" s="26" t="n">
-        <v>406.75</v>
+          <t>Payoff Ratio (avg win / avg loss)</t>
+        </is>
+      </c>
+      <c r="B52" s="32" t="n">
+        <v>1.93</v>
       </c>
       <c r="C52" s="23" t="n"/>
       <c r="D52" s="24" t="n"/>
@@ -1791,125 +1692,17 @@
     <row r="53">
       <c r="A53" s="3" t="inlineStr">
         <is>
-          <t>Largest Loss (Rs)</t>
-        </is>
-      </c>
-      <c r="B53" s="27" t="n">
-        <v>-368.93</v>
+          <t>Sharpe Ratio (annualized)</t>
+        </is>
+      </c>
+      <c r="B53" s="32" t="n">
+        <v>-4.54</v>
       </c>
       <c r="C53" s="23" t="n"/>
       <c r="D53" s="24" t="n"/>
     </row>
-    <row r="54">
-      <c r="A54" s="3" t="inlineStr">
-        <is>
-          <t>Max Consecutive Wins</t>
-        </is>
-      </c>
-      <c r="B54" s="22" t="n">
-        <v>2</v>
-      </c>
-      <c r="C54" s="23" t="n"/>
-      <c r="D54" s="24" t="n"/>
-    </row>
     <row r="55">
-      <c r="A55" s="3" t="inlineStr">
-        <is>
-          <t>Max Consecutive Losses</t>
-        </is>
-      </c>
-      <c r="B55" s="22" t="n">
-        <v>11</v>
-      </c>
-      <c r="C55" s="23" t="n"/>
-      <c r="D55" s="24" t="n"/>
-    </row>
-    <row r="56">
-      <c r="A56" s="3" t="inlineStr">
-        <is>
-          <t>Max trade drawdown (Rs)</t>
-        </is>
-      </c>
-      <c r="B56" s="27" t="n">
-        <v>-368.93</v>
-      </c>
-      <c r="C56" s="23" t="n"/>
-      <c r="D56" s="24" t="n"/>
-    </row>
-    <row r="57">
-      <c r="A57" s="3" t="inlineStr">
-        <is>
-          <t>Max system drawdown (Rs)</t>
-        </is>
-      </c>
-      <c r="B57" s="27" t="n">
-        <v>-3321.99</v>
-      </c>
-      <c r="C57" s="23" t="n"/>
-      <c r="D57" s="24" t="n"/>
-    </row>
-    <row r="58">
-      <c r="A58" s="3" t="inlineStr">
-        <is>
-          <t>Max system drawdown (%)</t>
-        </is>
-      </c>
-      <c r="B58" s="31" t="n">
-        <v>-16.08</v>
-      </c>
-      <c r="C58" s="23" t="n"/>
-      <c r="D58" s="24" t="n"/>
-    </row>
-    <row r="59">
-      <c r="A59" s="3" t="inlineStr">
-        <is>
-          <t>Recovery Factor</t>
-        </is>
-      </c>
-      <c r="B59" s="32" t="n">
-        <v>-0.8</v>
-      </c>
-      <c r="C59" s="23" t="n"/>
-      <c r="D59" s="24" t="n"/>
-    </row>
-    <row r="60">
-      <c r="A60" s="3" t="inlineStr">
-        <is>
-          <t>Profit Factor</t>
-        </is>
-      </c>
-      <c r="B60" s="32" t="n">
-        <v>0.45</v>
-      </c>
-      <c r="C60" s="23" t="n"/>
-      <c r="D60" s="24" t="n"/>
-    </row>
-    <row r="61">
-      <c r="A61" s="3" t="inlineStr">
-        <is>
-          <t>Payoff Ratio (avg win / avg loss)</t>
-        </is>
-      </c>
-      <c r="B61" s="32" t="n">
-        <v>1.03</v>
-      </c>
-      <c r="C61" s="23" t="n"/>
-      <c r="D61" s="24" t="n"/>
-    </row>
-    <row r="62">
-      <c r="A62" s="3" t="inlineStr">
-        <is>
-          <t>Sharpe Ratio (annualized)</t>
-        </is>
-      </c>
-      <c r="B62" s="32" t="n">
-        <v>-6.22</v>
-      </c>
-      <c r="C62" s="23" t="n"/>
-      <c r="D62" s="24" t="n"/>
-    </row>
-    <row r="64">
-      <c r="A64" s="5" t="inlineStr">
+      <c r="A55" s="5" t="inlineStr">
         <is>
           <t>Caveat: with only a handful of trades these numbers (Sharpe, profit factor, drawdown %) are not statistically reliable. Watch this over weeks/months before drawing conclusions.</t>
         </is>
@@ -1918,25 +1711,25 @@
   </sheetData>
   <mergeCells count="24">
     <mergeCell ref="B42:D42"/>
-    <mergeCell ref="B60:D60"/>
-    <mergeCell ref="B61:D61"/>
-    <mergeCell ref="B57:D57"/>
     <mergeCell ref="B44:D44"/>
     <mergeCell ref="B53:D53"/>
+    <mergeCell ref="B38:D38"/>
+    <mergeCell ref="B34:D34"/>
+    <mergeCell ref="B37:D37"/>
     <mergeCell ref="B49:D49"/>
     <mergeCell ref="B40:D40"/>
-    <mergeCell ref="B55:D55"/>
+    <mergeCell ref="B30:D30"/>
     <mergeCell ref="B51:D51"/>
+    <mergeCell ref="B33:D33"/>
+    <mergeCell ref="B36:D36"/>
     <mergeCell ref="B45:D45"/>
     <mergeCell ref="B41:D41"/>
+    <mergeCell ref="B32:D32"/>
+    <mergeCell ref="B35:D35"/>
     <mergeCell ref="B50:D50"/>
-    <mergeCell ref="B62:D62"/>
     <mergeCell ref="B47:D47"/>
-    <mergeCell ref="B54:D54"/>
-    <mergeCell ref="B59:D59"/>
+    <mergeCell ref="B31:D31"/>
     <mergeCell ref="B46:D46"/>
-    <mergeCell ref="B56:D56"/>
-    <mergeCell ref="B58:D58"/>
     <mergeCell ref="B52:D52"/>
     <mergeCell ref="B43:D43"/>
     <mergeCell ref="B39:D39"/>
@@ -2201,23 +1994,23 @@
       </c>
       <c r="B4" s="6" t="inlineStr">
         <is>
-          <t>trend_scalp_nw (EMA5/21) [5m]</t>
+          <t>vwap_ema_momentum (EMA9/13) [60m]</t>
         </is>
       </c>
       <c r="C4" s="7" t="n">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="D4" s="8" t="n">
-        <v>0.5384615384615384</v>
+        <v>0.4166666666666667</v>
       </c>
       <c r="E4" s="9" t="n">
-        <v>289.63</v>
+        <v>714.63</v>
       </c>
       <c r="F4" s="10" t="n">
-        <v>1.15</v>
+        <v>1.44</v>
       </c>
       <c r="G4" s="11" t="n">
-        <v>-0.02718449608801872</v>
+        <v>-0.04624032870879385</v>
       </c>
     </row>
     <row r="5">
@@ -2228,7 +2021,7 @@
       </c>
       <c r="B5" s="6" t="inlineStr">
         <is>
-          <t>trend_scalp_nw (EMA5/21) [5m]</t>
+          <t>trend_scalp_nw (EMA5/21) [1m]</t>
         </is>
       </c>
       <c r="C5" s="7" t="n">
@@ -2238,13 +2031,13 @@
         <v>0</v>
       </c>
       <c r="E5" s="12" t="n">
-        <v>-1614.72</v>
+        <v>-1162.41</v>
       </c>
       <c r="F5" s="10" t="n">
         <v>0</v>
       </c>
       <c r="G5" s="11" t="n">
-        <v>-0.08073600000000006</v>
+        <v>-0.05812049999999982</v>
       </c>
     </row>
     <row r="6">
@@ -2255,7 +2048,7 @@
       </c>
       <c r="B6" s="6" t="inlineStr">
         <is>
-          <t>trend_scalp_nw (EMA8/21) [5m]</t>
+          <t>trend_scalp_nw (EMA9/21) [1m]</t>
         </is>
       </c>
       <c r="C6" s="7" t="n">
@@ -2265,13 +2058,13 @@
         <v>0</v>
       </c>
       <c r="E6" s="12" t="n">
-        <v>-1332.18</v>
+        <v>-1335.02</v>
       </c>
       <c r="F6" s="10" t="n">
         <v>0</v>
       </c>
       <c r="G6" s="11" t="n">
-        <v>-0.06660900000000002</v>
+        <v>-0.06675100000000002</v>
       </c>
     </row>
     <row r="7">
@@ -2286,19 +2079,19 @@
         </is>
       </c>
       <c r="C7" s="7" t="n">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="D7" s="8" t="n">
-        <v>0.3043478260869565</v>
+        <v>0.2272727272727273</v>
       </c>
       <c r="E7" s="12" t="n">
-        <v>-2657.27</v>
+        <v>-1782.8</v>
       </c>
       <c r="F7" s="10" t="n">
-        <v>0.45</v>
+        <v>0.57</v>
       </c>
       <c r="G7" s="11" t="n">
-        <v>-0.1607565938469046</v>
+        <v>-0.1612290113873062</v>
       </c>
     </row>
     <row r="9">
@@ -2320,7 +2113,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
-  <dimension ref="A1:O57"/>
+  <dimension ref="A1:O52"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="40" customWidth="1" min="1" max="1"/>
@@ -2343,7 +2136,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>BACKTEST NIFTY -- best: trend_scalp_nw (EMA5/21) [5m] -- PAPER TRADE, NOT REAL MONEY</t>
+          <t>BACKTEST NIFTY -- best: vwap_ema_momentum (EMA9/13) [60m] -- PAPER TRADE, NOT REAL MONEY</t>
         </is>
       </c>
     </row>
@@ -2433,550 +2226,497 @@
     </row>
     <row r="5">
       <c r="A5" s="3" t="n">
-        <v>2025</v>
-      </c>
-      <c r="B5" s="6" t="n"/>
+        <v>2026</v>
+      </c>
+      <c r="B5" s="14" t="n">
+        <v>0.007486499999999999</v>
+      </c>
       <c r="C5" s="6" t="n"/>
       <c r="D5" s="6" t="n"/>
-      <c r="E5" s="6" t="n"/>
-      <c r="F5" s="6" t="n"/>
+      <c r="E5" s="14" t="n">
+        <v>0.007542532827983304</v>
+      </c>
+      <c r="F5" s="14" t="n">
+        <v>0.05840394725370424</v>
+      </c>
       <c r="G5" s="6" t="n"/>
-      <c r="H5" s="6" t="n"/>
+      <c r="H5" s="15" t="n">
+        <v>-0.01546998917040258</v>
+      </c>
       <c r="I5" s="6" t="n"/>
-      <c r="J5" s="6" t="n"/>
-      <c r="K5" s="14" t="n">
-        <v>0.0154865</v>
-      </c>
-      <c r="L5" s="15" t="n">
-        <v>-0.01893772098398157</v>
-      </c>
+      <c r="J5" s="15" t="n">
+        <v>-0.02081635547151973</v>
+      </c>
+      <c r="K5" s="6" t="n"/>
+      <c r="L5" s="6" t="n"/>
       <c r="M5" s="6" t="n"/>
       <c r="N5" s="16" t="n">
-        <v>-0.003744500000000039</v>
+        <v>0.03573149999999981</v>
       </c>
       <c r="O5" s="17" t="n">
-        <v>-74.89</v>
+        <v>714.63</v>
       </c>
     </row>
     <row r="6">
-      <c r="A6" s="3" t="n">
-        <v>2026</v>
-      </c>
-      <c r="B6" s="15" t="n">
-        <v>-0.0003804244995385213</v>
-      </c>
-      <c r="C6" s="14" t="n">
-        <v>0.02161964862108907</v>
-      </c>
+      <c r="A6" s="3" t="inlineStr">
+        <is>
+          <t>Avg</t>
+        </is>
+      </c>
+      <c r="B6" s="16" t="n">
+        <v>0.007486499999999999</v>
+      </c>
+      <c r="C6" s="6" t="n"/>
       <c r="D6" s="6" t="n"/>
-      <c r="E6" s="15" t="n">
-        <v>-0.01204925855631031</v>
-      </c>
-      <c r="F6" s="6" t="n"/>
-      <c r="G6" s="14" t="n">
-        <v>0.02763772101222905</v>
-      </c>
-      <c r="H6" s="6" t="n"/>
-      <c r="I6" s="15" t="n">
-        <v>-0.01785845673657797</v>
-      </c>
-      <c r="J6" s="6" t="n"/>
+      <c r="E6" s="16" t="n">
+        <v>0.007542532827983304</v>
+      </c>
+      <c r="F6" s="16" t="n">
+        <v>0.05840394725370424</v>
+      </c>
+      <c r="G6" s="6" t="n"/>
+      <c r="H6" s="18" t="n">
+        <v>-0.01546998917040258</v>
+      </c>
+      <c r="I6" s="6" t="n"/>
+      <c r="J6" s="18" t="n">
+        <v>-0.02081635547151973</v>
+      </c>
       <c r="K6" s="6" t="n"/>
       <c r="L6" s="6" t="n"/>
       <c r="M6" s="6" t="n"/>
-      <c r="N6" s="18" t="n">
-        <v>0.01829450376936426</v>
-      </c>
-      <c r="O6" s="19" t="n">
-        <v>364.52</v>
-      </c>
-    </row>
-    <row r="7">
-      <c r="A7" s="3" t="inlineStr">
-        <is>
-          <t>Avg</t>
-        </is>
-      </c>
-      <c r="B7" s="16" t="n">
-        <v>-0.0003804244995385213</v>
-      </c>
-      <c r="C7" s="18" t="n">
-        <v>0.02161964862108907</v>
-      </c>
-      <c r="D7" s="6" t="n"/>
-      <c r="E7" s="16" t="n">
-        <v>-0.01204925855631031</v>
-      </c>
-      <c r="F7" s="6" t="n"/>
-      <c r="G7" s="18" t="n">
-        <v>0.02763772101222905</v>
-      </c>
-      <c r="H7" s="6" t="n"/>
-      <c r="I7" s="16" t="n">
-        <v>-0.01785845673657797</v>
-      </c>
-      <c r="J7" s="6" t="n"/>
-      <c r="K7" s="18" t="n">
-        <v>0.0154865</v>
-      </c>
-      <c r="L7" s="16" t="n">
-        <v>-0.01893772098398157</v>
-      </c>
-      <c r="M7" s="6" t="n"/>
+    </row>
+    <row r="8">
+      <c r="A8" s="13" t="inlineStr">
+        <is>
+          <t>WEEKLY returns (% of capital at start of that week; weeks split at month edges)</t>
+        </is>
+      </c>
     </row>
     <row r="9">
-      <c r="A9" s="13" t="inlineStr">
-        <is>
-          <t>WEEKLY returns (% of capital at start of that week; weeks split at month edges)</t>
+      <c r="A9" s="2" t="inlineStr">
+        <is>
+          <t>Month</t>
+        </is>
+      </c>
+      <c r="B9" s="2" t="inlineStr">
+        <is>
+          <t>W1</t>
+        </is>
+      </c>
+      <c r="C9" s="2" t="inlineStr">
+        <is>
+          <t>W2</t>
+        </is>
+      </c>
+      <c r="D9" s="2" t="inlineStr">
+        <is>
+          <t>W3</t>
+        </is>
+      </c>
+      <c r="E9" s="2" t="inlineStr">
+        <is>
+          <t>W4</t>
+        </is>
+      </c>
+      <c r="F9" s="2" t="inlineStr">
+        <is>
+          <t>W5</t>
+        </is>
+      </c>
+      <c r="G9" s="2" t="inlineStr">
+        <is>
+          <t>W6</t>
+        </is>
+      </c>
+      <c r="H9" s="2" t="inlineStr">
+        <is>
+          <t>Month %</t>
+        </is>
+      </c>
+      <c r="I9" s="2" t="inlineStr">
+        <is>
+          <t>Month P&amp;L (Rs)</t>
         </is>
       </c>
     </row>
     <row r="10">
-      <c r="A10" s="2" t="inlineStr">
-        <is>
-          <t>Month</t>
-        </is>
-      </c>
-      <c r="B10" s="2" t="inlineStr">
-        <is>
-          <t>W1</t>
-        </is>
-      </c>
-      <c r="C10" s="2" t="inlineStr">
-        <is>
-          <t>W2</t>
-        </is>
-      </c>
-      <c r="D10" s="2" t="inlineStr">
-        <is>
-          <t>W3</t>
-        </is>
-      </c>
-      <c r="E10" s="2" t="inlineStr">
-        <is>
-          <t>W4</t>
-        </is>
-      </c>
-      <c r="F10" s="2" t="inlineStr">
-        <is>
-          <t>W5</t>
-        </is>
-      </c>
-      <c r="G10" s="2" t="inlineStr">
-        <is>
-          <t>W6</t>
-        </is>
-      </c>
-      <c r="H10" s="2" t="inlineStr">
-        <is>
-          <t>Month %</t>
-        </is>
-      </c>
-      <c r="I10" s="2" t="inlineStr">
-        <is>
-          <t>Month P&amp;L (Rs)</t>
-        </is>
+      <c r="A10" s="3" t="inlineStr">
+        <is>
+          <t>2026-Jan</t>
+        </is>
+      </c>
+      <c r="B10" s="14" t="n">
+        <v>0.007486499999999999</v>
+      </c>
+      <c r="C10" s="6" t="n"/>
+      <c r="D10" s="6" t="n"/>
+      <c r="E10" s="6" t="n"/>
+      <c r="F10" s="6" t="n"/>
+      <c r="G10" s="6" t="n"/>
+      <c r="H10" s="19" t="n">
+        <v>0.007486499999999999</v>
+      </c>
+      <c r="I10" s="17" t="n">
+        <v>149.73</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" s="3" t="inlineStr">
         <is>
-          <t>2025-Oct</t>
+          <t>2026-Apr</t>
         </is>
       </c>
       <c r="B11" s="14" t="n">
-        <v>0.0154865</v>
-      </c>
-      <c r="C11" s="6" t="n"/>
+        <v>0.02240377414486447</v>
+      </c>
+      <c r="C11" s="15" t="n">
+        <v>-0.01453558925808061</v>
+      </c>
       <c r="D11" s="6" t="n"/>
       <c r="E11" s="6" t="n"/>
       <c r="F11" s="6" t="n"/>
       <c r="G11" s="6" t="n"/>
-      <c r="H11" s="20" t="n">
-        <v>0.0154865</v>
-      </c>
-      <c r="I11" s="19" t="n">
-        <v>309.73</v>
+      <c r="H11" s="19" t="n">
+        <v>0.007542532827983304</v>
+      </c>
+      <c r="I11" s="17" t="n">
+        <v>151.98</v>
       </c>
     </row>
     <row r="12">
       <c r="A12" s="3" t="inlineStr">
         <is>
-          <t>2025-Nov</t>
-        </is>
-      </c>
-      <c r="B12" s="15" t="n">
-        <v>-0.01608834780176792</v>
-      </c>
-      <c r="C12" s="15" t="n">
-        <v>-0.002895964465760363</v>
-      </c>
+          <t>2026-May</t>
+        </is>
+      </c>
+      <c r="B12" s="14" t="n">
+        <v>0.05840394725370424</v>
+      </c>
+      <c r="C12" s="6" t="n"/>
       <c r="D12" s="6" t="n"/>
       <c r="E12" s="6" t="n"/>
       <c r="F12" s="6" t="n"/>
       <c r="G12" s="6" t="n"/>
-      <c r="H12" s="21" t="n">
-        <v>-0.01893772098398157</v>
+      <c r="H12" s="19" t="n">
+        <v>0.05840394725370424</v>
       </c>
       <c r="I12" s="17" t="n">
-        <v>-384.62</v>
+        <v>1185.7</v>
       </c>
     </row>
     <row r="13">
       <c r="A13" s="3" t="inlineStr">
         <is>
-          <t>2026-Jan</t>
-        </is>
-      </c>
-      <c r="B13" s="14" t="n">
-        <v>0.01290682962352529</v>
-      </c>
-      <c r="C13" s="15" t="n">
-        <v>-0.01311794306688838</v>
-      </c>
+          <t>2026-Jul</t>
+        </is>
+      </c>
+      <c r="B13" s="15" t="n">
+        <v>-0.01546998917040258</v>
+      </c>
+      <c r="C13" s="6" t="n"/>
       <c r="D13" s="6" t="n"/>
       <c r="E13" s="6" t="n"/>
       <c r="F13" s="6" t="n"/>
       <c r="G13" s="6" t="n"/>
-      <c r="H13" s="21" t="n">
-        <v>-0.0003804244995385213</v>
-      </c>
-      <c r="I13" s="17" t="n">
-        <v>-7.58</v>
+      <c r="H13" s="20" t="n">
+        <v>-0.01546998917040258</v>
+      </c>
+      <c r="I13" s="21" t="n">
+        <v>-332.41</v>
       </c>
     </row>
     <row r="14">
       <c r="A14" s="3" t="inlineStr">
         <is>
-          <t>2026-Feb</t>
-        </is>
-      </c>
-      <c r="B14" s="14" t="n">
-        <v>0.02161964862108907</v>
-      </c>
-      <c r="C14" s="6" t="n"/>
+          <t>2026-Sep</t>
+        </is>
+      </c>
+      <c r="B14" s="15" t="n">
+        <v>-0.012097376506736</v>
+      </c>
+      <c r="C14" s="15" t="n">
+        <v>-0.008825747353472017</v>
+      </c>
       <c r="D14" s="6" t="n"/>
       <c r="E14" s="6" t="n"/>
       <c r="F14" s="6" t="n"/>
       <c r="G14" s="6" t="n"/>
       <c r="H14" s="20" t="n">
-        <v>0.02161964862108907</v>
-      </c>
-      <c r="I14" s="19" t="n">
-        <v>430.61</v>
-      </c>
-    </row>
-    <row r="15">
-      <c r="A15" s="3" t="inlineStr">
-        <is>
-          <t>2026-Apr</t>
-        </is>
-      </c>
-      <c r="B15" s="15" t="n">
-        <v>-0.01204925855631031</v>
-      </c>
-      <c r="C15" s="6" t="n"/>
-      <c r="D15" s="6" t="n"/>
-      <c r="E15" s="6" t="n"/>
-      <c r="F15" s="6" t="n"/>
-      <c r="G15" s="6" t="n"/>
-      <c r="H15" s="21" t="n">
-        <v>-0.01204925855631031</v>
-      </c>
-      <c r="I15" s="17" t="n">
-        <v>-245.18</v>
+        <v>-0.02081635547151973</v>
+      </c>
+      <c r="I14" s="21" t="n">
+        <v>-440.37</v>
       </c>
     </row>
     <row r="16">
-      <c r="A16" s="3" t="inlineStr">
-        <is>
-          <t>2026-Jun</t>
-        </is>
-      </c>
-      <c r="B16" s="14" t="n">
-        <v>0.01282945397095752</v>
-      </c>
-      <c r="C16" s="14" t="n">
-        <v>0.01462069155198182</v>
-      </c>
-      <c r="D16" s="6" t="n"/>
-      <c r="E16" s="6" t="n"/>
-      <c r="F16" s="6" t="n"/>
-      <c r="G16" s="6" t="n"/>
-      <c r="H16" s="20" t="n">
-        <v>0.02763772101222905</v>
-      </c>
-      <c r="I16" s="19" t="n">
-        <v>555.6</v>
+      <c r="A16" s="13" t="inlineStr">
+        <is>
+          <t>DAILY returns (% of capital at start of that day; blank = no trade that day)</t>
+        </is>
       </c>
     </row>
     <row r="17">
-      <c r="A17" s="3" t="inlineStr">
-        <is>
-          <t>2026-Aug</t>
-        </is>
-      </c>
-      <c r="B17" s="15" t="n">
-        <v>-0.01785845673657797</v>
-      </c>
-      <c r="C17" s="6" t="n"/>
-      <c r="D17" s="6" t="n"/>
-      <c r="E17" s="6" t="n"/>
-      <c r="F17" s="6" t="n"/>
-      <c r="G17" s="6" t="n"/>
-      <c r="H17" s="21" t="n">
-        <v>-0.01785845673657797</v>
-      </c>
-      <c r="I17" s="17" t="n">
-        <v>-368.93</v>
+      <c r="A17" s="2" t="inlineStr">
+        <is>
+          <t>Week starting (Mon)</t>
+        </is>
+      </c>
+      <c r="B17" s="2" t="inlineStr">
+        <is>
+          <t>Mon</t>
+        </is>
+      </c>
+      <c r="C17" s="2" t="inlineStr">
+        <is>
+          <t>Tue</t>
+        </is>
+      </c>
+      <c r="D17" s="2" t="inlineStr">
+        <is>
+          <t>Wed</t>
+        </is>
+      </c>
+      <c r="E17" s="2" t="inlineStr">
+        <is>
+          <t>Thu</t>
+        </is>
+      </c>
+      <c r="F17" s="2" t="inlineStr">
+        <is>
+          <t>Fri</t>
+        </is>
+      </c>
+      <c r="G17" s="2" t="inlineStr">
+        <is>
+          <t>Week %</t>
+        </is>
+      </c>
+      <c r="H17" s="2" t="inlineStr">
+        <is>
+          <t>Week P&amp;L (Rs)</t>
+        </is>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" s="3" t="inlineStr">
+        <is>
+          <t>19-Jan-2026</t>
+        </is>
+      </c>
+      <c r="B18" s="6" t="n"/>
+      <c r="C18" s="14" t="n">
+        <v>0.007486499999999999</v>
+      </c>
+      <c r="D18" s="6" t="n"/>
+      <c r="E18" s="6" t="n"/>
+      <c r="F18" s="6" t="n"/>
+      <c r="G18" s="19" t="n">
+        <v>0.007486499999999999</v>
+      </c>
+      <c r="H18" s="17" t="n">
+        <v>149.73</v>
       </c>
     </row>
     <row r="19">
-      <c r="A19" s="13" t="inlineStr">
-        <is>
-          <t>DAILY returns (% of capital at start of that day; blank = no trade that day)</t>
-        </is>
+      <c r="A19" s="3" t="inlineStr">
+        <is>
+          <t>06-Apr-2026</t>
+        </is>
+      </c>
+      <c r="B19" s="6" t="n"/>
+      <c r="C19" s="14" t="n">
+        <v>0.02240377414486447</v>
+      </c>
+      <c r="D19" s="6" t="n"/>
+      <c r="E19" s="6" t="n"/>
+      <c r="F19" s="6" t="n"/>
+      <c r="G19" s="19" t="n">
+        <v>0.02240377414486447</v>
+      </c>
+      <c r="H19" s="17" t="n">
+        <v>451.43</v>
       </c>
     </row>
     <row r="20">
-      <c r="A20" s="2" t="inlineStr">
-        <is>
-          <t>Week starting (Mon)</t>
-        </is>
-      </c>
-      <c r="B20" s="2" t="inlineStr">
-        <is>
-          <t>Mon</t>
-        </is>
-      </c>
-      <c r="C20" s="2" t="inlineStr">
-        <is>
-          <t>Tue</t>
-        </is>
-      </c>
-      <c r="D20" s="2" t="inlineStr">
-        <is>
-          <t>Wed</t>
-        </is>
-      </c>
-      <c r="E20" s="2" t="inlineStr">
-        <is>
-          <t>Thu</t>
-        </is>
-      </c>
-      <c r="F20" s="2" t="inlineStr">
-        <is>
-          <t>Fri</t>
-        </is>
-      </c>
-      <c r="G20" s="2" t="inlineStr">
-        <is>
-          <t>Week %</t>
-        </is>
-      </c>
-      <c r="H20" s="2" t="inlineStr">
-        <is>
-          <t>Week P&amp;L (Rs)</t>
-        </is>
+      <c r="A20" s="3" t="inlineStr">
+        <is>
+          <t>20-Apr-2026</t>
+        </is>
+      </c>
+      <c r="B20" s="6" t="n"/>
+      <c r="C20" s="15" t="n">
+        <v>-0.01453558925808061</v>
+      </c>
+      <c r="D20" s="6" t="n"/>
+      <c r="E20" s="6" t="n"/>
+      <c r="F20" s="6" t="n"/>
+      <c r="G20" s="20" t="n">
+        <v>-0.01453558925808061</v>
+      </c>
+      <c r="H20" s="21" t="n">
+        <v>-299.45</v>
       </c>
     </row>
     <row r="21">
       <c r="A21" s="3" t="inlineStr">
         <is>
-          <t>06-Oct-2025</t>
-        </is>
-      </c>
-      <c r="B21" s="14" t="n">
-        <v>0.0154865</v>
-      </c>
-      <c r="C21" s="6" t="n"/>
+          <t>11-May-2026</t>
+        </is>
+      </c>
+      <c r="B21" s="6" t="n"/>
+      <c r="C21" s="14" t="n">
+        <v>0.05840394725370424</v>
+      </c>
       <c r="D21" s="6" t="n"/>
       <c r="E21" s="6" t="n"/>
       <c r="F21" s="6" t="n"/>
-      <c r="G21" s="20" t="n">
-        <v>0.0154865</v>
-      </c>
-      <c r="H21" s="19" t="n">
-        <v>309.73</v>
+      <c r="G21" s="19" t="n">
+        <v>0.05840394725370424</v>
+      </c>
+      <c r="H21" s="17" t="n">
+        <v>1185.7</v>
       </c>
     </row>
     <row r="22">
       <c r="A22" s="3" t="inlineStr">
         <is>
-          <t>10-Nov-2025</t>
+          <t>06-Jul-2026</t>
         </is>
       </c>
       <c r="B22" s="6" t="n"/>
       <c r="C22" s="15" t="n">
-        <v>-0.01608834780176792</v>
+        <v>-0.01546998917040258</v>
       </c>
       <c r="D22" s="6" t="n"/>
       <c r="E22" s="6" t="n"/>
       <c r="F22" s="6" t="n"/>
-      <c r="G22" s="21" t="n">
-        <v>-0.01608834780176792</v>
-      </c>
-      <c r="H22" s="17" t="n">
-        <v>-326.75</v>
+      <c r="G22" s="20" t="n">
+        <v>-0.01546998917040258</v>
+      </c>
+      <c r="H22" s="21" t="n">
+        <v>-332.41</v>
       </c>
     </row>
     <row r="23">
       <c r="A23" s="3" t="inlineStr">
         <is>
-          <t>24-Nov-2025</t>
-        </is>
-      </c>
-      <c r="B23" s="14" t="n">
-        <v>0.01526098710002212</v>
-      </c>
+          <t>07-Sep-2026</t>
+        </is>
+      </c>
+      <c r="B23" s="6" t="n"/>
       <c r="C23" s="15" t="n">
-        <v>-0.01788402371063795</v>
+        <v>-0.012097376506736</v>
       </c>
       <c r="D23" s="6" t="n"/>
       <c r="E23" s="6" t="n"/>
       <c r="F23" s="6" t="n"/>
-      <c r="G23" s="21" t="n">
-        <v>-0.002895964465760363</v>
-      </c>
-      <c r="H23" s="17" t="n">
-        <v>-57.87</v>
+      <c r="G23" s="20" t="n">
+        <v>-0.012097376506736</v>
+      </c>
+      <c r="H23" s="21" t="n">
+        <v>-255.92</v>
       </c>
     </row>
     <row r="24">
       <c r="A24" s="3" t="inlineStr">
         <is>
-          <t>12-Jan-2026</t>
-        </is>
-      </c>
-      <c r="B24" s="14" t="n">
-        <v>0.01290682962352529</v>
-      </c>
-      <c r="C24" s="6" t="n"/>
+          <t>14-Sep-2026</t>
+        </is>
+      </c>
+      <c r="B24" s="6" t="n"/>
+      <c r="C24" s="15" t="n">
+        <v>-0.008825747353472017</v>
+      </c>
       <c r="D24" s="6" t="n"/>
       <c r="E24" s="6" t="n"/>
       <c r="F24" s="6" t="n"/>
       <c r="G24" s="20" t="n">
-        <v>0.01290682962352529</v>
-      </c>
-      <c r="H24" s="19" t="n">
-        <v>257.17</v>
-      </c>
-    </row>
-    <row r="25">
-      <c r="A25" s="3" t="inlineStr">
-        <is>
-          <t>26-Jan-2026</t>
-        </is>
-      </c>
-      <c r="B25" s="6" t="n"/>
-      <c r="C25" s="15" t="n">
-        <v>-0.01311794306688838</v>
-      </c>
-      <c r="D25" s="6" t="n"/>
-      <c r="E25" s="6" t="n"/>
-      <c r="F25" s="6" t="n"/>
-      <c r="G25" s="20" t="n">
-        <v>0.008218100234463109</v>
-      </c>
-      <c r="H25" s="19" t="n">
-        <v>165.86</v>
+        <v>-0.008825747353472017</v>
+      </c>
+      <c r="H24" s="21" t="n">
+        <v>-184.45</v>
       </c>
     </row>
     <row r="26">
-      <c r="A26" s="3" t="inlineStr">
-        <is>
-          <t>20-Apr-2026</t>
-        </is>
-      </c>
-      <c r="B26" s="15" t="n">
-        <v>-0.01204925855631031</v>
-      </c>
-      <c r="C26" s="6" t="n"/>
-      <c r="D26" s="6" t="n"/>
-      <c r="E26" s="6" t="n"/>
-      <c r="F26" s="6" t="n"/>
-      <c r="G26" s="21" t="n">
-        <v>-0.01204925855631031</v>
-      </c>
-      <c r="H26" s="17" t="n">
-        <v>-245.18</v>
+      <c r="A26" s="13" t="inlineStr">
+        <is>
+          <t>STATISTICS (all trades for this index)</t>
+        </is>
       </c>
     </row>
     <row r="27">
       <c r="A27" s="3" t="inlineStr">
         <is>
-          <t>01-Jun-2026</t>
-        </is>
-      </c>
-      <c r="B27" s="14" t="n">
-        <v>0.01282945397095752</v>
-      </c>
-      <c r="C27" s="6" t="n"/>
-      <c r="D27" s="6" t="n"/>
-      <c r="E27" s="6" t="n"/>
-      <c r="F27" s="6" t="n"/>
-      <c r="G27" s="20" t="n">
-        <v>0.01282945397095752</v>
-      </c>
-      <c r="H27" s="19" t="n">
-        <v>257.91</v>
-      </c>
+          <t>All trades</t>
+        </is>
+      </c>
+      <c r="B27" s="22" t="n">
+        <v>12</v>
+      </c>
+      <c r="C27" s="23" t="n"/>
+      <c r="D27" s="24" t="n"/>
     </row>
     <row r="28">
       <c r="A28" s="3" t="inlineStr">
         <is>
-          <t>29-Jun-2026</t>
-        </is>
-      </c>
-      <c r="B28" s="14" t="n">
-        <v>0.01462069155198182</v>
-      </c>
-      <c r="C28" s="6" t="n"/>
-      <c r="D28" s="6" t="n"/>
-      <c r="E28" s="6" t="n"/>
-      <c r="F28" s="6" t="n"/>
-      <c r="G28" s="20" t="n">
-        <v>0.01462069155198182</v>
-      </c>
-      <c r="H28" s="19" t="n">
-        <v>297.69</v>
-      </c>
+          <t>Winners</t>
+        </is>
+      </c>
+      <c r="B28" s="25" t="inlineStr">
+        <is>
+          <t>5 (41.7%)</t>
+        </is>
+      </c>
+      <c r="C28" s="23" t="n"/>
+      <c r="D28" s="24" t="n"/>
     </row>
     <row r="29">
       <c r="A29" s="3" t="inlineStr">
         <is>
-          <t>10-Aug-2026</t>
-        </is>
-      </c>
-      <c r="B29" s="6" t="n"/>
-      <c r="C29" s="15" t="n">
-        <v>-0.01785845673657797</v>
-      </c>
-      <c r="D29" s="6" t="n"/>
-      <c r="E29" s="6" t="n"/>
-      <c r="F29" s="6" t="n"/>
-      <c r="G29" s="21" t="n">
-        <v>-0.01785845673657797</v>
-      </c>
-      <c r="H29" s="17" t="n">
-        <v>-368.93</v>
-      </c>
+          <t>Losers</t>
+        </is>
+      </c>
+      <c r="B29" s="25" t="inlineStr">
+        <is>
+          <t>7 (58.3%)</t>
+        </is>
+      </c>
+      <c r="C29" s="23" t="n"/>
+      <c r="D29" s="24" t="n"/>
+    </row>
+    <row r="30">
+      <c r="A30" s="3" t="inlineStr">
+        <is>
+          <t>Net P&amp;L (Rs)</t>
+        </is>
+      </c>
+      <c r="B30" s="26" t="n">
+        <v>714.63</v>
+      </c>
+      <c r="C30" s="23" t="n"/>
+      <c r="D30" s="24" t="n"/>
     </row>
     <row r="31">
-      <c r="A31" s="13" t="inlineStr">
-        <is>
-          <t>STATISTICS (all trades for this index)</t>
-        </is>
-      </c>
+      <c r="A31" s="3" t="inlineStr">
+        <is>
+          <t>Total Profit (Rs)</t>
+        </is>
+      </c>
+      <c r="B31" s="26" t="n">
+        <v>2338.58</v>
+      </c>
+      <c r="C31" s="23" t="n"/>
+      <c r="D31" s="24" t="n"/>
     </row>
     <row r="32">
       <c r="A32" s="3" t="inlineStr">
         <is>
-          <t>All trades</t>
-        </is>
-      </c>
-      <c r="B32" s="22" t="n">
-        <v>13</v>
+          <t>Total Loss (Rs)</t>
+        </is>
+      </c>
+      <c r="B32" s="27" t="n">
+        <v>-1623.95</v>
       </c>
       <c r="C32" s="23" t="n"/>
       <c r="D32" s="24" t="n"/>
@@ -2984,13 +2724,11 @@
     <row r="33">
       <c r="A33" s="3" t="inlineStr">
         <is>
-          <t>Winners</t>
-        </is>
-      </c>
-      <c r="B33" s="25" t="inlineStr">
-        <is>
-          <t>7 (53.8%)</t>
-        </is>
+          <t>Transaction costs (Rs)</t>
+        </is>
+      </c>
+      <c r="B33" s="28" t="n">
+        <v>335.62</v>
       </c>
       <c r="C33" s="23" t="n"/>
       <c r="D33" s="24" t="n"/>
@@ -2998,13 +2736,11 @@
     <row r="34">
       <c r="A34" s="3" t="inlineStr">
         <is>
-          <t>Losers</t>
-        </is>
-      </c>
-      <c r="B34" s="25" t="inlineStr">
-        <is>
-          <t>6 (46.2%)</t>
-        </is>
+          <t>Avg Profit/Loss per trade (Rs)</t>
+        </is>
+      </c>
+      <c r="B34" s="26" t="n">
+        <v>59.55</v>
       </c>
       <c r="C34" s="23" t="n"/>
       <c r="D34" s="24" t="n"/>
@@ -3012,11 +2748,11 @@
     <row r="35">
       <c r="A35" s="3" t="inlineStr">
         <is>
-          <t>Net P&amp;L (Rs)</t>
-        </is>
-      </c>
-      <c r="B35" s="26" t="n">
-        <v>289.63</v>
+          <t>Avg Profit/Loss per trade (% of premium)</t>
+        </is>
+      </c>
+      <c r="B35" s="29" t="n">
+        <v>5.84</v>
       </c>
       <c r="C35" s="23" t="n"/>
       <c r="D35" s="24" t="n"/>
@@ -3024,11 +2760,11 @@
     <row r="36">
       <c r="A36" s="3" t="inlineStr">
         <is>
-          <t>Total Profit (Rs)</t>
+          <t>Avg Win (Rs)</t>
         </is>
       </c>
       <c r="B36" s="26" t="n">
-        <v>2174.65</v>
+        <v>467.72</v>
       </c>
       <c r="C36" s="23" t="n"/>
       <c r="D36" s="24" t="n"/>
@@ -3036,11 +2772,11 @@
     <row r="37">
       <c r="A37" s="3" t="inlineStr">
         <is>
-          <t>Total Loss (Rs)</t>
-        </is>
-      </c>
-      <c r="B37" s="27" t="n">
-        <v>-1885.02</v>
+          <t>Avg Win (% of premium)</t>
+        </is>
+      </c>
+      <c r="B37" s="30" t="n">
+        <v>54.93</v>
       </c>
       <c r="C37" s="23" t="n"/>
       <c r="D37" s="24" t="n"/>
@@ -3048,11 +2784,11 @@
     <row r="38">
       <c r="A38" s="3" t="inlineStr">
         <is>
-          <t>Transaction costs (Rs)</t>
-        </is>
-      </c>
-      <c r="B38" s="28" t="n">
-        <v>863.12</v>
+          <t>Avg Loss (Rs)</t>
+        </is>
+      </c>
+      <c r="B38" s="27" t="n">
+        <v>-231.99</v>
       </c>
       <c r="C38" s="23" t="n"/>
       <c r="D38" s="24" t="n"/>
@@ -3060,11 +2796,11 @@
     <row r="39">
       <c r="A39" s="3" t="inlineStr">
         <is>
-          <t>Avg Profit/Loss per trade (Rs)</t>
-        </is>
-      </c>
-      <c r="B39" s="26" t="n">
-        <v>22.28</v>
+          <t>Avg Loss (% of premium)</t>
+        </is>
+      </c>
+      <c r="B39" s="31" t="n">
+        <v>-29.23</v>
       </c>
       <c r="C39" s="23" t="n"/>
       <c r="D39" s="24" t="n"/>
@@ -3072,11 +2808,11 @@
     <row r="40">
       <c r="A40" s="3" t="inlineStr">
         <is>
-          <t>Avg Profit/Loss per trade (% of premium)</t>
-        </is>
-      </c>
-      <c r="B40" s="29" t="n">
-        <v>1.77</v>
+          <t>Largest Win (Rs)</t>
+        </is>
+      </c>
+      <c r="B40" s="26" t="n">
+        <v>552.97</v>
       </c>
       <c r="C40" s="23" t="n"/>
       <c r="D40" s="24" t="n"/>
@@ -3084,11 +2820,11 @@
     <row r="41">
       <c r="A41" s="3" t="inlineStr">
         <is>
-          <t>Avg Win (Rs)</t>
-        </is>
-      </c>
-      <c r="B41" s="26" t="n">
-        <v>310.66</v>
+          <t>Largest Loss (Rs)</t>
+        </is>
+      </c>
+      <c r="B41" s="27" t="n">
+        <v>-332.41</v>
       </c>
       <c r="C41" s="23" t="n"/>
       <c r="D41" s="24" t="n"/>
@@ -3096,11 +2832,11 @@
     <row r="42">
       <c r="A42" s="3" t="inlineStr">
         <is>
-          <t>Avg Win (% of premium)</t>
-        </is>
-      </c>
-      <c r="B42" s="30" t="n">
-        <v>16.01</v>
+          <t>Max Consecutive Wins</t>
+        </is>
+      </c>
+      <c r="B42" s="22" t="n">
+        <v>3</v>
       </c>
       <c r="C42" s="23" t="n"/>
       <c r="D42" s="24" t="n"/>
@@ -3108,11 +2844,11 @@
     <row r="43">
       <c r="A43" s="3" t="inlineStr">
         <is>
-          <t>Avg Loss (Rs)</t>
-        </is>
-      </c>
-      <c r="B43" s="27" t="n">
-        <v>-314.17</v>
+          <t>Max Consecutive Losses</t>
+        </is>
+      </c>
+      <c r="B43" s="22" t="n">
+        <v>4</v>
       </c>
       <c r="C43" s="23" t="n"/>
       <c r="D43" s="24" t="n"/>
@@ -3120,11 +2856,11 @@
     <row r="44">
       <c r="A44" s="3" t="inlineStr">
         <is>
-          <t>Avg Loss (% of premium)</t>
-        </is>
-      </c>
-      <c r="B44" s="31" t="n">
-        <v>-14.84</v>
+          <t>Max trade drawdown (Rs)</t>
+        </is>
+      </c>
+      <c r="B44" s="27" t="n">
+        <v>-332.41</v>
       </c>
       <c r="C44" s="23" t="n"/>
       <c r="D44" s="24" t="n"/>
@@ -3132,11 +2868,11 @@
     <row r="45">
       <c r="A45" s="3" t="inlineStr">
         <is>
-          <t>Largest Win (Rs)</t>
-        </is>
-      </c>
-      <c r="B45" s="26" t="n">
-        <v>406.75</v>
+          <t>Max system drawdown (Rs)</t>
+        </is>
+      </c>
+      <c r="B45" s="27" t="n">
+        <v>-1004.29</v>
       </c>
       <c r="C45" s="23" t="n"/>
       <c r="D45" s="24" t="n"/>
@@ -3144,11 +2880,11 @@
     <row r="46">
       <c r="A46" s="3" t="inlineStr">
         <is>
-          <t>Largest Loss (Rs)</t>
-        </is>
-      </c>
-      <c r="B46" s="27" t="n">
-        <v>-368.93</v>
+          <t>Max system drawdown (%)</t>
+        </is>
+      </c>
+      <c r="B46" s="31" t="n">
+        <v>-4.62</v>
       </c>
       <c r="C46" s="23" t="n"/>
       <c r="D46" s="24" t="n"/>
@@ -3156,11 +2892,11 @@
     <row r="47">
       <c r="A47" s="3" t="inlineStr">
         <is>
-          <t>Max Consecutive Wins</t>
-        </is>
-      </c>
-      <c r="B47" s="22" t="n">
-        <v>2</v>
+          <t>Recovery Factor</t>
+        </is>
+      </c>
+      <c r="B47" s="32" t="n">
+        <v>0.71</v>
       </c>
       <c r="C47" s="23" t="n"/>
       <c r="D47" s="24" t="n"/>
@@ -3168,11 +2904,11 @@
     <row r="48">
       <c r="A48" s="3" t="inlineStr">
         <is>
-          <t>Max Consecutive Losses</t>
-        </is>
-      </c>
-      <c r="B48" s="22" t="n">
-        <v>2</v>
+          <t>Profit Factor</t>
+        </is>
+      </c>
+      <c r="B48" s="32" t="n">
+        <v>1.44</v>
       </c>
       <c r="C48" s="23" t="n"/>
       <c r="D48" s="24" t="n"/>
@@ -3180,11 +2916,11 @@
     <row r="49">
       <c r="A49" s="3" t="inlineStr">
         <is>
-          <t>Max trade drawdown (Rs)</t>
-        </is>
-      </c>
-      <c r="B49" s="27" t="n">
-        <v>-368.93</v>
+          <t>Payoff Ratio (avg win / avg loss)</t>
+        </is>
+      </c>
+      <c r="B49" s="32" t="n">
+        <v>2.02</v>
       </c>
       <c r="C49" s="23" t="n"/>
       <c r="D49" s="24" t="n"/>
@@ -3192,77 +2928,17 @@
     <row r="50">
       <c r="A50" s="3" t="inlineStr">
         <is>
-          <t>Max system drawdown (Rs)</t>
-        </is>
-      </c>
-      <c r="B50" s="27" t="n">
-        <v>-561.76</v>
+          <t>Sharpe Ratio (annualized)</t>
+        </is>
+      </c>
+      <c r="B50" s="32" t="n">
+        <v>3.36</v>
       </c>
       <c r="C50" s="23" t="n"/>
       <c r="D50" s="24" t="n"/>
     </row>
-    <row r="51">
-      <c r="A51" s="3" t="inlineStr">
-        <is>
-          <t>Max system drawdown (%)</t>
-        </is>
-      </c>
-      <c r="B51" s="31" t="n">
-        <v>-2.72</v>
-      </c>
-      <c r="C51" s="23" t="n"/>
-      <c r="D51" s="24" t="n"/>
-    </row>
     <row r="52">
-      <c r="A52" s="3" t="inlineStr">
-        <is>
-          <t>Recovery Factor</t>
-        </is>
-      </c>
-      <c r="B52" s="32" t="n">
-        <v>0.52</v>
-      </c>
-      <c r="C52" s="23" t="n"/>
-      <c r="D52" s="24" t="n"/>
-    </row>
-    <row r="53">
-      <c r="A53" s="3" t="inlineStr">
-        <is>
-          <t>Profit Factor</t>
-        </is>
-      </c>
-      <c r="B53" s="32" t="n">
-        <v>1.15</v>
-      </c>
-      <c r="C53" s="23" t="n"/>
-      <c r="D53" s="24" t="n"/>
-    </row>
-    <row r="54">
-      <c r="A54" s="3" t="inlineStr">
-        <is>
-          <t>Payoff Ratio (avg win / avg loss)</t>
-        </is>
-      </c>
-      <c r="B54" s="32" t="n">
-        <v>0.99</v>
-      </c>
-      <c r="C54" s="23" t="n"/>
-      <c r="D54" s="24" t="n"/>
-    </row>
-    <row r="55">
-      <c r="A55" s="3" t="inlineStr">
-        <is>
-          <t>Sharpe Ratio (annualized)</t>
-        </is>
-      </c>
-      <c r="B55" s="32" t="n">
-        <v>1.45</v>
-      </c>
-      <c r="C55" s="23" t="n"/>
-      <c r="D55" s="24" t="n"/>
-    </row>
-    <row r="57">
-      <c r="A57" s="5" t="inlineStr">
+      <c r="A52" s="5" t="inlineStr">
         <is>
           <t>Caveat: with only a handful of trades these numbers (Sharpe, profit factor, drawdown %) are not statistically reliable. Watch this over weeks/months before drawing conclusions.</t>
         </is>
@@ -3272,25 +2948,25 @@
   <mergeCells count="24">
     <mergeCell ref="B42:D42"/>
     <mergeCell ref="B44:D44"/>
-    <mergeCell ref="B53:D53"/>
+    <mergeCell ref="B29:D29"/>
     <mergeCell ref="B38:D38"/>
     <mergeCell ref="B34:D34"/>
+    <mergeCell ref="B28:D28"/>
     <mergeCell ref="B37:D37"/>
     <mergeCell ref="B49:D49"/>
     <mergeCell ref="B40:D40"/>
-    <mergeCell ref="B55:D55"/>
-    <mergeCell ref="B51:D51"/>
+    <mergeCell ref="B30:D30"/>
     <mergeCell ref="B33:D33"/>
     <mergeCell ref="B36:D36"/>
     <mergeCell ref="B45:D45"/>
     <mergeCell ref="B41:D41"/>
+    <mergeCell ref="B32:D32"/>
     <mergeCell ref="B35:D35"/>
-    <mergeCell ref="B32:D32"/>
     <mergeCell ref="B50:D50"/>
     <mergeCell ref="B47:D47"/>
-    <mergeCell ref="B54:D54"/>
+    <mergeCell ref="B31:D31"/>
     <mergeCell ref="B46:D46"/>
-    <mergeCell ref="B52:D52"/>
+    <mergeCell ref="B27:D27"/>
     <mergeCell ref="B43:D43"/>
     <mergeCell ref="B39:D39"/>
     <mergeCell ref="B48:D48"/>
@@ -3306,7 +2982,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
-  <dimension ref="A1:O48"/>
+  <dimension ref="A1:O45"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="40" customWidth="1" min="1" max="1"/>
@@ -3329,7 +3005,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>BACKTEST BANKNIFTY -- best: trend_scalp_nw (EMA5/21) [5m] -- PAPER TRADE, NOT REAL MONEY</t>
+          <t>BACKTEST BANKNIFTY -- best: trend_scalp_nw (EMA5/21) [1m] -- PAPER TRADE, NOT REAL MONEY</t>
         </is>
       </c>
     </row>
@@ -3419,7 +3095,7 @@
     </row>
     <row r="5">
       <c r="A5" s="3" t="n">
-        <v>2025</v>
+        <v>2026</v>
       </c>
       <c r="B5" s="6" t="n"/>
       <c r="C5" s="6" t="n"/>
@@ -3427,336 +3103,308 @@
       <c r="E5" s="6" t="n"/>
       <c r="F5" s="6" t="n"/>
       <c r="G5" s="6" t="n"/>
-      <c r="H5" s="6" t="n"/>
+      <c r="H5" s="15" t="n">
+        <v>-0.0348495</v>
+      </c>
       <c r="I5" s="6" t="n"/>
-      <c r="J5" s="6" t="n"/>
+      <c r="J5" s="15" t="n">
+        <v>-0.02411126554874084</v>
+      </c>
       <c r="K5" s="6" t="n"/>
       <c r="L5" s="6" t="n"/>
-      <c r="M5" s="15" t="n">
-        <v>-0.0355045</v>
-      </c>
-      <c r="N5" s="16" t="n">
-        <v>-0.03550450000000005</v>
-      </c>
-      <c r="O5" s="17" t="n">
-        <v>-710.09</v>
+      <c r="M5" s="6" t="n"/>
+      <c r="N5" s="18" t="n">
+        <v>-0.05812050000000002</v>
+      </c>
+      <c r="O5" s="21" t="n">
+        <v>-1162.41</v>
       </c>
     </row>
     <row r="6">
-      <c r="A6" s="3" t="n">
-        <v>2026</v>
-      </c>
-      <c r="B6" s="15" t="n">
-        <v>-0.01746560766742821</v>
-      </c>
+      <c r="A6" s="3" t="inlineStr">
+        <is>
+          <t>Avg</t>
+        </is>
+      </c>
+      <c r="B6" s="6" t="n"/>
       <c r="C6" s="6" t="n"/>
       <c r="D6" s="6" t="n"/>
       <c r="E6" s="6" t="n"/>
       <c r="F6" s="6" t="n"/>
       <c r="G6" s="6" t="n"/>
-      <c r="H6" s="6" t="n"/>
-      <c r="I6" s="15" t="n">
-        <v>-0.02995409697673192</v>
-      </c>
-      <c r="J6" s="6" t="n"/>
+      <c r="H6" s="18" t="n">
+        <v>-0.0348495</v>
+      </c>
+      <c r="I6" s="6" t="n"/>
+      <c r="J6" s="18" t="n">
+        <v>-0.02411126554874084</v>
+      </c>
       <c r="K6" s="6" t="n"/>
       <c r="L6" s="6" t="n"/>
       <c r="M6" s="6" t="n"/>
-      <c r="N6" s="16" t="n">
-        <v>-0.04689653813833239</v>
-      </c>
-      <c r="O6" s="17" t="n">
-        <v>-904.63</v>
-      </c>
-    </row>
-    <row r="7">
-      <c r="A7" s="3" t="inlineStr">
-        <is>
-          <t>Avg</t>
-        </is>
-      </c>
-      <c r="B7" s="16" t="n">
-        <v>-0.01746560766742821</v>
-      </c>
-      <c r="C7" s="6" t="n"/>
-      <c r="D7" s="6" t="n"/>
-      <c r="E7" s="6" t="n"/>
-      <c r="F7" s="6" t="n"/>
-      <c r="G7" s="6" t="n"/>
-      <c r="H7" s="6" t="n"/>
-      <c r="I7" s="16" t="n">
-        <v>-0.02995409697673192</v>
-      </c>
-      <c r="J7" s="6" t="n"/>
-      <c r="K7" s="6" t="n"/>
-      <c r="L7" s="6" t="n"/>
-      <c r="M7" s="16" t="n">
-        <v>-0.0355045</v>
+    </row>
+    <row r="8">
+      <c r="A8" s="13" t="inlineStr">
+        <is>
+          <t>WEEKLY returns (% of capital at start of that week; weeks split at month edges)</t>
+        </is>
       </c>
     </row>
     <row r="9">
-      <c r="A9" s="13" t="inlineStr">
-        <is>
-          <t>WEEKLY returns (% of capital at start of that week; weeks split at month edges)</t>
+      <c r="A9" s="2" t="inlineStr">
+        <is>
+          <t>Month</t>
+        </is>
+      </c>
+      <c r="B9" s="2" t="inlineStr">
+        <is>
+          <t>W1</t>
+        </is>
+      </c>
+      <c r="C9" s="2" t="inlineStr">
+        <is>
+          <t>W2</t>
+        </is>
+      </c>
+      <c r="D9" s="2" t="inlineStr">
+        <is>
+          <t>W3</t>
+        </is>
+      </c>
+      <c r="E9" s="2" t="inlineStr">
+        <is>
+          <t>W4</t>
+        </is>
+      </c>
+      <c r="F9" s="2" t="inlineStr">
+        <is>
+          <t>W5</t>
+        </is>
+      </c>
+      <c r="G9" s="2" t="inlineStr">
+        <is>
+          <t>W6</t>
+        </is>
+      </c>
+      <c r="H9" s="2" t="inlineStr">
+        <is>
+          <t>Month %</t>
+        </is>
+      </c>
+      <c r="I9" s="2" t="inlineStr">
+        <is>
+          <t>Month P&amp;L (Rs)</t>
         </is>
       </c>
     </row>
     <row r="10">
-      <c r="A10" s="2" t="inlineStr">
-        <is>
-          <t>Month</t>
-        </is>
-      </c>
-      <c r="B10" s="2" t="inlineStr">
-        <is>
-          <t>W1</t>
-        </is>
-      </c>
-      <c r="C10" s="2" t="inlineStr">
-        <is>
-          <t>W2</t>
-        </is>
-      </c>
-      <c r="D10" s="2" t="inlineStr">
-        <is>
-          <t>W3</t>
-        </is>
-      </c>
-      <c r="E10" s="2" t="inlineStr">
-        <is>
-          <t>W4</t>
-        </is>
-      </c>
-      <c r="F10" s="2" t="inlineStr">
-        <is>
-          <t>W5</t>
-        </is>
-      </c>
-      <c r="G10" s="2" t="inlineStr">
-        <is>
-          <t>W6</t>
-        </is>
-      </c>
-      <c r="H10" s="2" t="inlineStr">
-        <is>
-          <t>Month %</t>
-        </is>
-      </c>
-      <c r="I10" s="2" t="inlineStr">
-        <is>
-          <t>Month P&amp;L (Rs)</t>
-        </is>
+      <c r="A10" s="3" t="inlineStr">
+        <is>
+          <t>2026-Jul</t>
+        </is>
+      </c>
+      <c r="B10" s="15" t="n">
+        <v>-0.024971</v>
+      </c>
+      <c r="C10" s="15" t="n">
+        <v>-0.01013149352480798</v>
+      </c>
+      <c r="D10" s="6" t="n"/>
+      <c r="E10" s="6" t="n"/>
+      <c r="F10" s="6" t="n"/>
+      <c r="G10" s="6" t="n"/>
+      <c r="H10" s="20" t="n">
+        <v>-0.0348495</v>
+      </c>
+      <c r="I10" s="21" t="n">
+        <v>-696.99</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" s="3" t="inlineStr">
         <is>
-          <t>2025-Dec</t>
+          <t>2026-Sep</t>
         </is>
       </c>
       <c r="B11" s="15" t="n">
-        <v>-0.0355045</v>
+        <v>-0.02411126554874084</v>
       </c>
       <c r="C11" s="6" t="n"/>
       <c r="D11" s="6" t="n"/>
       <c r="E11" s="6" t="n"/>
       <c r="F11" s="6" t="n"/>
       <c r="G11" s="6" t="n"/>
-      <c r="H11" s="21" t="n">
-        <v>-0.0355045</v>
-      </c>
-      <c r="I11" s="17" t="n">
-        <v>-710.09</v>
-      </c>
-    </row>
-    <row r="12">
-      <c r="A12" s="3" t="inlineStr">
-        <is>
-          <t>2026-Jan</t>
-        </is>
-      </c>
-      <c r="B12" s="15" t="n">
-        <v>-0.01746560766742821</v>
-      </c>
-      <c r="C12" s="6" t="n"/>
-      <c r="D12" s="6" t="n"/>
-      <c r="E12" s="6" t="n"/>
-      <c r="F12" s="6" t="n"/>
-      <c r="G12" s="6" t="n"/>
-      <c r="H12" s="21" t="n">
-        <v>-0.01746560766742821</v>
-      </c>
-      <c r="I12" s="17" t="n">
-        <v>-336.91</v>
+      <c r="H11" s="20" t="n">
+        <v>-0.02411126554874084</v>
+      </c>
+      <c r="I11" s="21" t="n">
+        <v>-465.42</v>
       </c>
     </row>
     <row r="13">
-      <c r="A13" s="3" t="inlineStr">
-        <is>
-          <t>2026-Aug</t>
-        </is>
-      </c>
-      <c r="B13" s="15" t="n">
-        <v>-0.01872526776763573</v>
-      </c>
-      <c r="C13" s="15" t="n">
-        <v>-0.01144310440313796</v>
-      </c>
-      <c r="D13" s="6" t="n"/>
-      <c r="E13" s="6" t="n"/>
-      <c r="F13" s="6" t="n"/>
-      <c r="G13" s="6" t="n"/>
-      <c r="H13" s="21" t="n">
-        <v>-0.02995409697673192</v>
-      </c>
-      <c r="I13" s="17" t="n">
-        <v>-567.72</v>
+      <c r="A13" s="13" t="inlineStr">
+        <is>
+          <t>DAILY returns (% of capital at start of that day; blank = no trade that day)</t>
+        </is>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" s="2" t="inlineStr">
+        <is>
+          <t>Week starting (Mon)</t>
+        </is>
+      </c>
+      <c r="B14" s="2" t="inlineStr">
+        <is>
+          <t>Mon</t>
+        </is>
+      </c>
+      <c r="C14" s="2" t="inlineStr">
+        <is>
+          <t>Tue</t>
+        </is>
+      </c>
+      <c r="D14" s="2" t="inlineStr">
+        <is>
+          <t>Wed</t>
+        </is>
+      </c>
+      <c r="E14" s="2" t="inlineStr">
+        <is>
+          <t>Thu</t>
+        </is>
+      </c>
+      <c r="F14" s="2" t="inlineStr">
+        <is>
+          <t>Fri</t>
+        </is>
+      </c>
+      <c r="G14" s="2" t="inlineStr">
+        <is>
+          <t>Week %</t>
+        </is>
+      </c>
+      <c r="H14" s="2" t="inlineStr">
+        <is>
+          <t>Week P&amp;L (Rs)</t>
+        </is>
       </c>
     </row>
     <row r="15">
-      <c r="A15" s="13" t="inlineStr">
-        <is>
-          <t>DAILY returns (% of capital at start of that day; blank = no trade that day)</t>
-        </is>
+      <c r="A15" s="3" t="inlineStr">
+        <is>
+          <t>13-Jul-2026</t>
+        </is>
+      </c>
+      <c r="B15" s="6" t="n"/>
+      <c r="C15" s="15" t="n">
+        <v>-0.024971</v>
+      </c>
+      <c r="D15" s="6" t="n"/>
+      <c r="E15" s="6" t="n"/>
+      <c r="F15" s="6" t="n"/>
+      <c r="G15" s="20" t="n">
+        <v>-0.024971</v>
+      </c>
+      <c r="H15" s="21" t="n">
+        <v>-499.42</v>
       </c>
     </row>
     <row r="16">
-      <c r="A16" s="2" t="inlineStr">
-        <is>
-          <t>Week starting (Mon)</t>
-        </is>
-      </c>
-      <c r="B16" s="2" t="inlineStr">
-        <is>
-          <t>Mon</t>
-        </is>
-      </c>
-      <c r="C16" s="2" t="inlineStr">
-        <is>
-          <t>Tue</t>
-        </is>
-      </c>
-      <c r="D16" s="2" t="inlineStr">
-        <is>
-          <t>Wed</t>
-        </is>
-      </c>
-      <c r="E16" s="2" t="inlineStr">
-        <is>
-          <t>Thu</t>
-        </is>
-      </c>
-      <c r="F16" s="2" t="inlineStr">
-        <is>
-          <t>Fri</t>
-        </is>
-      </c>
-      <c r="G16" s="2" t="inlineStr">
-        <is>
-          <t>Week %</t>
-        </is>
-      </c>
-      <c r="H16" s="2" t="inlineStr">
-        <is>
-          <t>Week P&amp;L (Rs)</t>
-        </is>
+      <c r="A16" s="3" t="inlineStr">
+        <is>
+          <t>27-Jul-2026</t>
+        </is>
+      </c>
+      <c r="B16" s="6" t="n"/>
+      <c r="C16" s="15" t="n">
+        <v>-0.01013149352480798</v>
+      </c>
+      <c r="D16" s="6" t="n"/>
+      <c r="E16" s="6" t="n"/>
+      <c r="F16" s="6" t="n"/>
+      <c r="G16" s="20" t="n">
+        <v>-0.01013149352480798</v>
+      </c>
+      <c r="H16" s="21" t="n">
+        <v>-197.57</v>
       </c>
     </row>
     <row r="17">
       <c r="A17" s="3" t="inlineStr">
         <is>
-          <t>29-Dec-2025</t>
+          <t>28-Sep-2026</t>
         </is>
       </c>
       <c r="B17" s="6" t="n"/>
       <c r="C17" s="15" t="n">
-        <v>-0.0355045</v>
+        <v>-0.02411126554874084</v>
       </c>
       <c r="D17" s="6" t="n"/>
       <c r="E17" s="6" t="n"/>
       <c r="F17" s="6" t="n"/>
-      <c r="G17" s="21" t="n">
-        <v>-0.0355045</v>
-      </c>
-      <c r="H17" s="17" t="n">
-        <v>-710.09</v>
-      </c>
-    </row>
-    <row r="18">
-      <c r="A18" s="3" t="inlineStr">
-        <is>
-          <t>26-Jan-2026</t>
-        </is>
-      </c>
-      <c r="B18" s="6" t="n"/>
-      <c r="C18" s="15" t="n">
-        <v>-0.01746560766742821</v>
-      </c>
-      <c r="D18" s="6" t="n"/>
-      <c r="E18" s="6" t="n"/>
-      <c r="F18" s="6" t="n"/>
-      <c r="G18" s="21" t="n">
-        <v>-0.01746560766742821</v>
-      </c>
-      <c r="H18" s="17" t="n">
-        <v>-336.91</v>
+      <c r="G17" s="20" t="n">
+        <v>-0.02411126554874084</v>
+      </c>
+      <c r="H17" s="21" t="n">
+        <v>-465.42</v>
       </c>
     </row>
     <row r="19">
-      <c r="A19" s="3" t="inlineStr">
-        <is>
-          <t>10-Aug-2026</t>
-        </is>
-      </c>
-      <c r="B19" s="6" t="n"/>
-      <c r="C19" s="15" t="n">
-        <v>-0.01872526776763573</v>
-      </c>
-      <c r="D19" s="6" t="n"/>
-      <c r="E19" s="6" t="n"/>
-      <c r="F19" s="6" t="n"/>
-      <c r="G19" s="21" t="n">
-        <v>-0.01872526776763573</v>
-      </c>
-      <c r="H19" s="17" t="n">
-        <v>-354.9</v>
+      <c r="A19" s="13" t="inlineStr">
+        <is>
+          <t>STATISTICS (all trades for this index)</t>
+        </is>
       </c>
     </row>
     <row r="20">
       <c r="A20" s="3" t="inlineStr">
         <is>
-          <t>24-Aug-2026</t>
-        </is>
-      </c>
-      <c r="B20" s="6" t="n"/>
-      <c r="C20" s="15" t="n">
-        <v>-0.01144310440313796</v>
-      </c>
-      <c r="D20" s="6" t="n"/>
-      <c r="E20" s="6" t="n"/>
-      <c r="F20" s="6" t="n"/>
-      <c r="G20" s="21" t="n">
-        <v>-0.01144310440313796</v>
-      </c>
-      <c r="H20" s="17" t="n">
-        <v>-212.82</v>
-      </c>
+          <t>All trades</t>
+        </is>
+      </c>
+      <c r="B20" s="22" t="n">
+        <v>5</v>
+      </c>
+      <c r="C20" s="23" t="n"/>
+      <c r="D20" s="24" t="n"/>
+    </row>
+    <row r="21">
+      <c r="A21" s="3" t="inlineStr">
+        <is>
+          <t>Winners</t>
+        </is>
+      </c>
+      <c r="B21" s="25" t="inlineStr">
+        <is>
+          <t>0 (0.0%)</t>
+        </is>
+      </c>
+      <c r="C21" s="23" t="n"/>
+      <c r="D21" s="24" t="n"/>
     </row>
     <row r="22">
-      <c r="A22" s="13" t="inlineStr">
-        <is>
-          <t>STATISTICS (all trades for this index)</t>
-        </is>
-      </c>
+      <c r="A22" s="3" t="inlineStr">
+        <is>
+          <t>Losers</t>
+        </is>
+      </c>
+      <c r="B22" s="25" t="inlineStr">
+        <is>
+          <t>5 (100.0%)</t>
+        </is>
+      </c>
+      <c r="C22" s="23" t="n"/>
+      <c r="D22" s="24" t="n"/>
     </row>
     <row r="23">
       <c r="A23" s="3" t="inlineStr">
         <is>
-          <t>All trades</t>
-        </is>
-      </c>
-      <c r="B23" s="22" t="n">
-        <v>5</v>
+          <t>Net P&amp;L (Rs)</t>
+        </is>
+      </c>
+      <c r="B23" s="27" t="n">
+        <v>-1162.41</v>
       </c>
       <c r="C23" s="23" t="n"/>
       <c r="D23" s="24" t="n"/>
@@ -3764,13 +3412,11 @@
     <row r="24">
       <c r="A24" s="3" t="inlineStr">
         <is>
-          <t>Winners</t>
-        </is>
-      </c>
-      <c r="B24" s="25" t="inlineStr">
-        <is>
-          <t>0 (0.0%)</t>
-        </is>
+          <t>Total Profit (Rs)</t>
+        </is>
+      </c>
+      <c r="B24" s="26" t="n">
+        <v>0</v>
       </c>
       <c r="C24" s="23" t="n"/>
       <c r="D24" s="24" t="n"/>
@@ -3778,13 +3424,11 @@
     <row r="25">
       <c r="A25" s="3" t="inlineStr">
         <is>
-          <t>Losers</t>
-        </is>
-      </c>
-      <c r="B25" s="25" t="inlineStr">
-        <is>
-          <t>5 (100.0%)</t>
-        </is>
+          <t>Total Loss (Rs)</t>
+        </is>
+      </c>
+      <c r="B25" s="27" t="n">
+        <v>-1162.41</v>
       </c>
       <c r="C25" s="23" t="n"/>
       <c r="D25" s="24" t="n"/>
@@ -3792,11 +3436,11 @@
     <row r="26">
       <c r="A26" s="3" t="inlineStr">
         <is>
-          <t>Net P&amp;L (Rs)</t>
-        </is>
-      </c>
-      <c r="B26" s="27" t="n">
-        <v>-1614.72</v>
+          <t>Transaction costs (Rs)</t>
+        </is>
+      </c>
+      <c r="B26" s="28" t="n">
+        <v>236.31</v>
       </c>
       <c r="C26" s="23" t="n"/>
       <c r="D26" s="24" t="n"/>
@@ -3804,11 +3448,11 @@
     <row r="27">
       <c r="A27" s="3" t="inlineStr">
         <is>
-          <t>Total Profit (Rs)</t>
-        </is>
-      </c>
-      <c r="B27" s="26" t="n">
-        <v>0</v>
+          <t>Avg Profit/Loss per trade (Rs)</t>
+        </is>
+      </c>
+      <c r="B27" s="27" t="n">
+        <v>-232.48</v>
       </c>
       <c r="C27" s="23" t="n"/>
       <c r="D27" s="24" t="n"/>
@@ -3816,11 +3460,11 @@
     <row r="28">
       <c r="A28" s="3" t="inlineStr">
         <is>
-          <t>Total Loss (Rs)</t>
-        </is>
-      </c>
-      <c r="B28" s="27" t="n">
-        <v>-1614.72</v>
+          <t>Avg Profit/Loss per trade (% of premium)</t>
+        </is>
+      </c>
+      <c r="B28" s="29" t="n">
+        <v>-14.84</v>
       </c>
       <c r="C28" s="23" t="n"/>
       <c r="D28" s="24" t="n"/>
@@ -3828,11 +3472,11 @@
     <row r="29">
       <c r="A29" s="3" t="inlineStr">
         <is>
-          <t>Transaction costs (Rs)</t>
-        </is>
-      </c>
-      <c r="B29" s="28" t="n">
-        <v>328.47</v>
+          <t>Avg Win (Rs)</t>
+        </is>
+      </c>
+      <c r="B29" s="26" t="n">
+        <v>0</v>
       </c>
       <c r="C29" s="23" t="n"/>
       <c r="D29" s="24" t="n"/>
@@ -3840,11 +3484,11 @@
     <row r="30">
       <c r="A30" s="3" t="inlineStr">
         <is>
-          <t>Avg Profit/Loss per trade (Rs)</t>
-        </is>
-      </c>
-      <c r="B30" s="27" t="n">
-        <v>-322.94</v>
+          <t>Avg Win (% of premium)</t>
+        </is>
+      </c>
+      <c r="B30" s="30" t="n">
+        <v>0</v>
       </c>
       <c r="C30" s="23" t="n"/>
       <c r="D30" s="24" t="n"/>
@@ -3852,11 +3496,11 @@
     <row r="31">
       <c r="A31" s="3" t="inlineStr">
         <is>
-          <t>Avg Profit/Loss per trade (% of premium)</t>
-        </is>
-      </c>
-      <c r="B31" s="29" t="n">
-        <v>-14.84</v>
+          <t>Avg Loss (Rs)</t>
+        </is>
+      </c>
+      <c r="B31" s="27" t="n">
+        <v>-232.48</v>
       </c>
       <c r="C31" s="23" t="n"/>
       <c r="D31" s="24" t="n"/>
@@ -3864,11 +3508,11 @@
     <row r="32">
       <c r="A32" s="3" t="inlineStr">
         <is>
-          <t>Avg Win (Rs)</t>
-        </is>
-      </c>
-      <c r="B32" s="26" t="n">
-        <v>0</v>
+          <t>Avg Loss (% of premium)</t>
+        </is>
+      </c>
+      <c r="B32" s="31" t="n">
+        <v>-14.84</v>
       </c>
       <c r="C32" s="23" t="n"/>
       <c r="D32" s="24" t="n"/>
@@ -3876,11 +3520,11 @@
     <row r="33">
       <c r="A33" s="3" t="inlineStr">
         <is>
-          <t>Avg Win (% of premium)</t>
-        </is>
-      </c>
-      <c r="B33" s="30" t="n">
-        <v>0</v>
+          <t>Largest Win (Rs)</t>
+        </is>
+      </c>
+      <c r="B33" s="26" t="n">
+        <v>-197.57</v>
       </c>
       <c r="C33" s="23" t="n"/>
       <c r="D33" s="24" t="n"/>
@@ -3888,11 +3532,11 @@
     <row r="34">
       <c r="A34" s="3" t="inlineStr">
         <is>
-          <t>Avg Loss (Rs)</t>
+          <t>Largest Loss (Rs)</t>
         </is>
       </c>
       <c r="B34" s="27" t="n">
-        <v>-322.94</v>
+        <v>-264.8</v>
       </c>
       <c r="C34" s="23" t="n"/>
       <c r="D34" s="24" t="n"/>
@@ -3900,11 +3544,11 @@
     <row r="35">
       <c r="A35" s="3" t="inlineStr">
         <is>
-          <t>Avg Loss (% of premium)</t>
-        </is>
-      </c>
-      <c r="B35" s="31" t="n">
-        <v>-14.84</v>
+          <t>Max Consecutive Wins</t>
+        </is>
+      </c>
+      <c r="B35" s="22" t="n">
+        <v>0</v>
       </c>
       <c r="C35" s="23" t="n"/>
       <c r="D35" s="24" t="n"/>
@@ -3912,11 +3556,11 @@
     <row r="36">
       <c r="A36" s="3" t="inlineStr">
         <is>
-          <t>Largest Win (Rs)</t>
-        </is>
-      </c>
-      <c r="B36" s="26" t="n">
-        <v>-212.82</v>
+          <t>Max Consecutive Losses</t>
+        </is>
+      </c>
+      <c r="B36" s="22" t="n">
+        <v>5</v>
       </c>
       <c r="C36" s="23" t="n"/>
       <c r="D36" s="24" t="n"/>
@@ -3924,11 +3568,11 @@
     <row r="37">
       <c r="A37" s="3" t="inlineStr">
         <is>
-          <t>Largest Loss (Rs)</t>
+          <t>Max trade drawdown (Rs)</t>
         </is>
       </c>
       <c r="B37" s="27" t="n">
-        <v>-358.86</v>
+        <v>-264.8</v>
       </c>
       <c r="C37" s="23" t="n"/>
       <c r="D37" s="24" t="n"/>
@@ -3936,11 +3580,11 @@
     <row r="38">
       <c r="A38" s="3" t="inlineStr">
         <is>
-          <t>Max Consecutive Wins</t>
-        </is>
-      </c>
-      <c r="B38" s="22" t="n">
-        <v>0</v>
+          <t>Max system drawdown (Rs)</t>
+        </is>
+      </c>
+      <c r="B38" s="27" t="n">
+        <v>-1162.41</v>
       </c>
       <c r="C38" s="23" t="n"/>
       <c r="D38" s="24" t="n"/>
@@ -3948,11 +3592,11 @@
     <row r="39">
       <c r="A39" s="3" t="inlineStr">
         <is>
-          <t>Max Consecutive Losses</t>
-        </is>
-      </c>
-      <c r="B39" s="22" t="n">
-        <v>5</v>
+          <t>Max system drawdown (%)</t>
+        </is>
+      </c>
+      <c r="B39" s="31" t="n">
+        <v>-5.81</v>
       </c>
       <c r="C39" s="23" t="n"/>
       <c r="D39" s="24" t="n"/>
@@ -3960,11 +3604,11 @@
     <row r="40">
       <c r="A40" s="3" t="inlineStr">
         <is>
-          <t>Max trade drawdown (Rs)</t>
-        </is>
-      </c>
-      <c r="B40" s="27" t="n">
-        <v>-358.86</v>
+          <t>Recovery Factor</t>
+        </is>
+      </c>
+      <c r="B40" s="32" t="n">
+        <v>-1</v>
       </c>
       <c r="C40" s="23" t="n"/>
       <c r="D40" s="24" t="n"/>
@@ -3972,11 +3616,11 @@
     <row r="41">
       <c r="A41" s="3" t="inlineStr">
         <is>
-          <t>Max system drawdown (Rs)</t>
-        </is>
-      </c>
-      <c r="B41" s="27" t="n">
-        <v>-1614.72</v>
+          <t>Profit Factor</t>
+        </is>
+      </c>
+      <c r="B41" s="32" t="n">
+        <v>0</v>
       </c>
       <c r="C41" s="23" t="n"/>
       <c r="D41" s="24" t="n"/>
@@ -3984,11 +3628,13 @@
     <row r="42">
       <c r="A42" s="3" t="inlineStr">
         <is>
-          <t>Max system drawdown (%)</t>
-        </is>
-      </c>
-      <c r="B42" s="31" t="n">
-        <v>-8.07</v>
+          <t>Payoff Ratio (avg win / avg loss)</t>
+        </is>
+      </c>
+      <c r="B42" s="25" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
       </c>
       <c r="C42" s="23" t="n"/>
       <c r="D42" s="24" t="n"/>
@@ -3996,55 +3642,17 @@
     <row r="43">
       <c r="A43" s="3" t="inlineStr">
         <is>
-          <t>Recovery Factor</t>
+          <t>Sharpe Ratio (annualized)</t>
         </is>
       </c>
       <c r="B43" s="32" t="n">
-        <v>-1</v>
+        <v>-46.07</v>
       </c>
       <c r="C43" s="23" t="n"/>
       <c r="D43" s="24" t="n"/>
     </row>
-    <row r="44">
-      <c r="A44" s="3" t="inlineStr">
-        <is>
-          <t>Profit Factor</t>
-        </is>
-      </c>
-      <c r="B44" s="32" t="n">
-        <v>0</v>
-      </c>
-      <c r="C44" s="23" t="n"/>
-      <c r="D44" s="24" t="n"/>
-    </row>
     <row r="45">
-      <c r="A45" s="3" t="inlineStr">
-        <is>
-          <t>Payoff Ratio (avg win / avg loss)</t>
-        </is>
-      </c>
-      <c r="B45" s="25" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="C45" s="23" t="n"/>
-      <c r="D45" s="24" t="n"/>
-    </row>
-    <row r="46">
-      <c r="A46" s="3" t="inlineStr">
-        <is>
-          <t>Sharpe Ratio (annualized)</t>
-        </is>
-      </c>
-      <c r="B46" s="32" t="n">
-        <v>-36.94</v>
-      </c>
-      <c r="C46" s="23" t="n"/>
-      <c r="D46" s="24" t="n"/>
-    </row>
-    <row r="48">
-      <c r="A48" s="5" t="inlineStr">
+      <c r="A45" s="5" t="inlineStr">
         <is>
           <t>Caveat: with only a handful of trades these numbers (Sharpe, profit factor, drawdown %) are not statistically reliable. Watch this over weeks/months before drawing conclusions.</t>
         </is>
@@ -4054,7 +3662,6 @@
   <mergeCells count="24">
     <mergeCell ref="B42:D42"/>
     <mergeCell ref="B23:D23"/>
-    <mergeCell ref="B44:D44"/>
     <mergeCell ref="B29:D29"/>
     <mergeCell ref="B38:D38"/>
     <mergeCell ref="B34:D34"/>
@@ -4063,17 +3670,18 @@
     <mergeCell ref="B40:D40"/>
     <mergeCell ref="B30:D30"/>
     <mergeCell ref="B24:D24"/>
+    <mergeCell ref="B20:D20"/>
     <mergeCell ref="B33:D33"/>
     <mergeCell ref="B36:D36"/>
-    <mergeCell ref="B45:D45"/>
     <mergeCell ref="B41:D41"/>
     <mergeCell ref="B32:D32"/>
     <mergeCell ref="B35:D35"/>
     <mergeCell ref="B26:D26"/>
     <mergeCell ref="B25:D25"/>
     <mergeCell ref="B31:D31"/>
-    <mergeCell ref="B46:D46"/>
+    <mergeCell ref="B22:D22"/>
     <mergeCell ref="B27:D27"/>
+    <mergeCell ref="B21:D21"/>
     <mergeCell ref="B43:D43"/>
     <mergeCell ref="B39:D39"/>
   </mergeCells>
@@ -4088,7 +3696,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
-  <dimension ref="A1:O49"/>
+  <dimension ref="A1:O45"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="40" customWidth="1" min="1" max="1"/>
@@ -4111,7 +3719,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>BACKTEST FINNIFTY -- best: trend_scalp_nw (EMA8/21) [5m] -- PAPER TRADE, NOT REAL MONEY</t>
+          <t>BACKTEST FINNIFTY -- best: trend_scalp_nw (EMA9/21) [1m] -- PAPER TRADE, NOT REAL MONEY</t>
         </is>
       </c>
     </row>
@@ -4201,7 +3809,7 @@
     </row>
     <row r="5">
       <c r="A5" s="3" t="n">
-        <v>2025</v>
+        <v>2026</v>
       </c>
       <c r="B5" s="6" t="n"/>
       <c r="C5" s="6" t="n"/>
@@ -4209,359 +3817,320 @@
       <c r="E5" s="6" t="n"/>
       <c r="F5" s="6" t="n"/>
       <c r="G5" s="6" t="n"/>
-      <c r="H5" s="6" t="n"/>
+      <c r="H5" s="15" t="n">
+        <v>-0.027176</v>
+      </c>
       <c r="I5" s="6" t="n"/>
-      <c r="J5" s="6" t="n"/>
-      <c r="K5" s="15" t="n">
-        <v>-0.0136185</v>
-      </c>
+      <c r="J5" s="15" t="n">
+        <v>-0.04068053419734711</v>
+      </c>
+      <c r="K5" s="6" t="n"/>
       <c r="L5" s="6" t="n"/>
-      <c r="M5" s="15" t="n">
-        <v>-0.02744830473807548</v>
-      </c>
-      <c r="N5" s="16" t="n">
-        <v>-0.04069299999999998</v>
-      </c>
-      <c r="O5" s="17" t="n">
-        <v>-813.86</v>
+      <c r="M5" s="6" t="n"/>
+      <c r="N5" s="18" t="n">
+        <v>-0.06675099999999989</v>
+      </c>
+      <c r="O5" s="21" t="n">
+        <v>-1335.02</v>
       </c>
     </row>
     <row r="6">
-      <c r="A6" s="3" t="n">
-        <v>2026</v>
-      </c>
-      <c r="B6" s="15" t="n">
-        <v>-0.01495923619863089</v>
-      </c>
+      <c r="A6" s="3" t="inlineStr">
+        <is>
+          <t>Avg</t>
+        </is>
+      </c>
+      <c r="B6" s="6" t="n"/>
       <c r="C6" s="6" t="n"/>
       <c r="D6" s="6" t="n"/>
       <c r="E6" s="6" t="n"/>
       <c r="F6" s="6" t="n"/>
       <c r="G6" s="6" t="n"/>
-      <c r="H6" s="6" t="n"/>
+      <c r="H6" s="18" t="n">
+        <v>-0.027176</v>
+      </c>
       <c r="I6" s="6" t="n"/>
-      <c r="J6" s="15" t="n">
-        <v>-0.01223918772980555</v>
+      <c r="J6" s="18" t="n">
+        <v>-0.04068053419734711</v>
       </c>
       <c r="K6" s="6" t="n"/>
       <c r="L6" s="6" t="n"/>
       <c r="M6" s="6" t="n"/>
-      <c r="N6" s="16" t="n">
-        <v>-0.027015335028307</v>
-      </c>
-      <c r="O6" s="17" t="n">
-        <v>-518.3200000000001</v>
-      </c>
-    </row>
-    <row r="7">
-      <c r="A7" s="3" t="inlineStr">
-        <is>
-          <t>Avg</t>
-        </is>
-      </c>
-      <c r="B7" s="16" t="n">
-        <v>-0.01495923619863089</v>
-      </c>
-      <c r="C7" s="6" t="n"/>
-      <c r="D7" s="6" t="n"/>
-      <c r="E7" s="6" t="n"/>
-      <c r="F7" s="6" t="n"/>
-      <c r="G7" s="6" t="n"/>
-      <c r="H7" s="6" t="n"/>
-      <c r="I7" s="6" t="n"/>
-      <c r="J7" s="16" t="n">
-        <v>-0.01223918772980555</v>
-      </c>
-      <c r="K7" s="16" t="n">
-        <v>-0.0136185</v>
-      </c>
-      <c r="L7" s="6" t="n"/>
-      <c r="M7" s="16" t="n">
-        <v>-0.02744830473807548</v>
+    </row>
+    <row r="8">
+      <c r="A8" s="13" t="inlineStr">
+        <is>
+          <t>WEEKLY returns (% of capital at start of that week; weeks split at month edges)</t>
+        </is>
       </c>
     </row>
     <row r="9">
-      <c r="A9" s="13" t="inlineStr">
-        <is>
-          <t>WEEKLY returns (% of capital at start of that week; weeks split at month edges)</t>
+      <c r="A9" s="2" t="inlineStr">
+        <is>
+          <t>Month</t>
+        </is>
+      </c>
+      <c r="B9" s="2" t="inlineStr">
+        <is>
+          <t>W1</t>
+        </is>
+      </c>
+      <c r="C9" s="2" t="inlineStr">
+        <is>
+          <t>W2</t>
+        </is>
+      </c>
+      <c r="D9" s="2" t="inlineStr">
+        <is>
+          <t>W3</t>
+        </is>
+      </c>
+      <c r="E9" s="2" t="inlineStr">
+        <is>
+          <t>W4</t>
+        </is>
+      </c>
+      <c r="F9" s="2" t="inlineStr">
+        <is>
+          <t>W5</t>
+        </is>
+      </c>
+      <c r="G9" s="2" t="inlineStr">
+        <is>
+          <t>W6</t>
+        </is>
+      </c>
+      <c r="H9" s="2" t="inlineStr">
+        <is>
+          <t>Month %</t>
+        </is>
+      </c>
+      <c r="I9" s="2" t="inlineStr">
+        <is>
+          <t>Month P&amp;L (Rs)</t>
         </is>
       </c>
     </row>
     <row r="10">
-      <c r="A10" s="2" t="inlineStr">
-        <is>
-          <t>Month</t>
-        </is>
-      </c>
-      <c r="B10" s="2" t="inlineStr">
-        <is>
-          <t>W1</t>
-        </is>
-      </c>
-      <c r="C10" s="2" t="inlineStr">
-        <is>
-          <t>W2</t>
-        </is>
-      </c>
-      <c r="D10" s="2" t="inlineStr">
-        <is>
-          <t>W3</t>
-        </is>
-      </c>
-      <c r="E10" s="2" t="inlineStr">
-        <is>
-          <t>W4</t>
-        </is>
-      </c>
-      <c r="F10" s="2" t="inlineStr">
-        <is>
-          <t>W5</t>
-        </is>
-      </c>
-      <c r="G10" s="2" t="inlineStr">
-        <is>
-          <t>W6</t>
-        </is>
-      </c>
-      <c r="H10" s="2" t="inlineStr">
-        <is>
-          <t>Month %</t>
-        </is>
-      </c>
-      <c r="I10" s="2" t="inlineStr">
-        <is>
-          <t>Month P&amp;L (Rs)</t>
-        </is>
+      <c r="A10" s="3" t="inlineStr">
+        <is>
+          <t>2026-Jul</t>
+        </is>
+      </c>
+      <c r="B10" s="15" t="n">
+        <v>-0.027176</v>
+      </c>
+      <c r="C10" s="6" t="n"/>
+      <c r="D10" s="6" t="n"/>
+      <c r="E10" s="6" t="n"/>
+      <c r="F10" s="6" t="n"/>
+      <c r="G10" s="6" t="n"/>
+      <c r="H10" s="20" t="n">
+        <v>-0.027176</v>
+      </c>
+      <c r="I10" s="21" t="n">
+        <v>-543.52</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" s="3" t="inlineStr">
         <is>
-          <t>2025-Oct</t>
+          <t>2026-Sep</t>
         </is>
       </c>
       <c r="B11" s="15" t="n">
-        <v>-0.0136185</v>
-      </c>
-      <c r="C11" s="6" t="n"/>
+        <v>-0.0163390294647336</v>
+      </c>
+      <c r="C11" s="15" t="n">
+        <v>-0.02474582753788421</v>
+      </c>
       <c r="D11" s="6" t="n"/>
       <c r="E11" s="6" t="n"/>
       <c r="F11" s="6" t="n"/>
       <c r="G11" s="6" t="n"/>
-      <c r="H11" s="21" t="n">
-        <v>-0.0136185</v>
-      </c>
-      <c r="I11" s="17" t="n">
-        <v>-272.37</v>
-      </c>
-    </row>
-    <row r="12">
-      <c r="A12" s="3" t="inlineStr">
-        <is>
-          <t>2025-Dec</t>
-        </is>
-      </c>
-      <c r="B12" s="15" t="n">
-        <v>-0.02744830473807548</v>
-      </c>
-      <c r="C12" s="6" t="n"/>
-      <c r="D12" s="6" t="n"/>
-      <c r="E12" s="6" t="n"/>
-      <c r="F12" s="6" t="n"/>
-      <c r="G12" s="6" t="n"/>
-      <c r="H12" s="21" t="n">
-        <v>-0.02744830473807548</v>
-      </c>
-      <c r="I12" s="17" t="n">
-        <v>-541.49</v>
+      <c r="H11" s="20" t="n">
+        <v>-0.04068053419734711</v>
+      </c>
+      <c r="I11" s="21" t="n">
+        <v>-791.5</v>
       </c>
     </row>
     <row r="13">
-      <c r="A13" s="3" t="inlineStr">
-        <is>
-          <t>2026-Jan</t>
-        </is>
-      </c>
-      <c r="B13" s="15" t="n">
-        <v>-0.01495923619863089</v>
-      </c>
-      <c r="C13" s="6" t="n"/>
-      <c r="D13" s="6" t="n"/>
-      <c r="E13" s="6" t="n"/>
-      <c r="F13" s="6" t="n"/>
-      <c r="G13" s="6" t="n"/>
-      <c r="H13" s="21" t="n">
-        <v>-0.01495923619863089</v>
-      </c>
-      <c r="I13" s="17" t="n">
-        <v>-287.01</v>
+      <c r="A13" s="13" t="inlineStr">
+        <is>
+          <t>DAILY returns (% of capital at start of that day; blank = no trade that day)</t>
+        </is>
       </c>
     </row>
     <row r="14">
-      <c r="A14" s="3" t="inlineStr">
-        <is>
-          <t>2026-Sep</t>
-        </is>
-      </c>
-      <c r="B14" s="15" t="n">
-        <v>-0.01223918772980555</v>
-      </c>
-      <c r="C14" s="6" t="n"/>
-      <c r="D14" s="6" t="n"/>
-      <c r="E14" s="6" t="n"/>
-      <c r="F14" s="6" t="n"/>
-      <c r="G14" s="6" t="n"/>
-      <c r="H14" s="21" t="n">
-        <v>-0.01223918772980555</v>
-      </c>
-      <c r="I14" s="17" t="n">
-        <v>-231.31</v>
+      <c r="A14" s="2" t="inlineStr">
+        <is>
+          <t>Week starting (Mon)</t>
+        </is>
+      </c>
+      <c r="B14" s="2" t="inlineStr">
+        <is>
+          <t>Mon</t>
+        </is>
+      </c>
+      <c r="C14" s="2" t="inlineStr">
+        <is>
+          <t>Tue</t>
+        </is>
+      </c>
+      <c r="D14" s="2" t="inlineStr">
+        <is>
+          <t>Wed</t>
+        </is>
+      </c>
+      <c r="E14" s="2" t="inlineStr">
+        <is>
+          <t>Thu</t>
+        </is>
+      </c>
+      <c r="F14" s="2" t="inlineStr">
+        <is>
+          <t>Fri</t>
+        </is>
+      </c>
+      <c r="G14" s="2" t="inlineStr">
+        <is>
+          <t>Week %</t>
+        </is>
+      </c>
+      <c r="H14" s="2" t="inlineStr">
+        <is>
+          <t>Week P&amp;L (Rs)</t>
+        </is>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" s="3" t="inlineStr">
+        <is>
+          <t>13-Jul-2026</t>
+        </is>
+      </c>
+      <c r="B15" s="6" t="n"/>
+      <c r="C15" s="15" t="n">
+        <v>-0.027176</v>
+      </c>
+      <c r="D15" s="6" t="n"/>
+      <c r="E15" s="6" t="n"/>
+      <c r="F15" s="6" t="n"/>
+      <c r="G15" s="20" t="n">
+        <v>-0.027176</v>
+      </c>
+      <c r="H15" s="21" t="n">
+        <v>-543.52</v>
       </c>
     </row>
     <row r="16">
-      <c r="A16" s="13" t="inlineStr">
-        <is>
-          <t>DAILY returns (% of capital at start of that day; blank = no trade that day)</t>
-        </is>
+      <c r="A16" s="3" t="inlineStr">
+        <is>
+          <t>07-Sep-2026</t>
+        </is>
+      </c>
+      <c r="B16" s="6" t="n"/>
+      <c r="C16" s="15" t="n">
+        <v>-0.0163390294647336</v>
+      </c>
+      <c r="D16" s="6" t="n"/>
+      <c r="E16" s="6" t="n"/>
+      <c r="F16" s="6" t="n"/>
+      <c r="G16" s="20" t="n">
+        <v>-0.0163390294647336</v>
+      </c>
+      <c r="H16" s="21" t="n">
+        <v>-317.9</v>
       </c>
     </row>
     <row r="17">
-      <c r="A17" s="2" t="inlineStr">
-        <is>
-          <t>Week starting (Mon)</t>
-        </is>
-      </c>
-      <c r="B17" s="2" t="inlineStr">
-        <is>
-          <t>Mon</t>
-        </is>
-      </c>
-      <c r="C17" s="2" t="inlineStr">
-        <is>
-          <t>Tue</t>
-        </is>
-      </c>
-      <c r="D17" s="2" t="inlineStr">
-        <is>
-          <t>Wed</t>
-        </is>
-      </c>
-      <c r="E17" s="2" t="inlineStr">
-        <is>
-          <t>Thu</t>
-        </is>
-      </c>
-      <c r="F17" s="2" t="inlineStr">
-        <is>
-          <t>Fri</t>
-        </is>
-      </c>
-      <c r="G17" s="2" t="inlineStr">
-        <is>
-          <t>Week %</t>
-        </is>
-      </c>
-      <c r="H17" s="2" t="inlineStr">
-        <is>
-          <t>Week P&amp;L (Rs)</t>
-        </is>
-      </c>
-    </row>
-    <row r="18">
-      <c r="A18" s="3" t="inlineStr">
-        <is>
-          <t>13-Oct-2025</t>
-        </is>
-      </c>
-      <c r="B18" s="6" t="n"/>
-      <c r="C18" s="15" t="n">
-        <v>-0.0136185</v>
-      </c>
-      <c r="D18" s="6" t="n"/>
-      <c r="E18" s="6" t="n"/>
-      <c r="F18" s="6" t="n"/>
-      <c r="G18" s="21" t="n">
-        <v>-0.0136185</v>
-      </c>
-      <c r="H18" s="17" t="n">
-        <v>-272.37</v>
+      <c r="A17" s="3" t="inlineStr">
+        <is>
+          <t>28-Sep-2026</t>
+        </is>
+      </c>
+      <c r="B17" s="6" t="n"/>
+      <c r="C17" s="15" t="n">
+        <v>-0.02474582753788421</v>
+      </c>
+      <c r="D17" s="6" t="n"/>
+      <c r="E17" s="6" t="n"/>
+      <c r="F17" s="6" t="n"/>
+      <c r="G17" s="20" t="n">
+        <v>-0.02474582753788421</v>
+      </c>
+      <c r="H17" s="21" t="n">
+        <v>-473.6</v>
       </c>
     </row>
     <row r="19">
-      <c r="A19" s="3" t="inlineStr">
-        <is>
-          <t>08-Dec-2025</t>
-        </is>
-      </c>
-      <c r="B19" s="6" t="n"/>
-      <c r="C19" s="15" t="n">
-        <v>-0.02744830473807548</v>
-      </c>
-      <c r="D19" s="6" t="n"/>
-      <c r="E19" s="6" t="n"/>
-      <c r="F19" s="6" t="n"/>
-      <c r="G19" s="21" t="n">
-        <v>-0.02744830473807548</v>
-      </c>
-      <c r="H19" s="17" t="n">
-        <v>-541.49</v>
+      <c r="A19" s="13" t="inlineStr">
+        <is>
+          <t>STATISTICS (all trades for this index)</t>
+        </is>
       </c>
     </row>
     <row r="20">
       <c r="A20" s="3" t="inlineStr">
         <is>
-          <t>26-Jan-2026</t>
-        </is>
-      </c>
-      <c r="B20" s="6" t="n"/>
-      <c r="C20" s="15" t="n">
-        <v>-0.01495923619863089</v>
-      </c>
-      <c r="D20" s="6" t="n"/>
-      <c r="E20" s="6" t="n"/>
-      <c r="F20" s="6" t="n"/>
-      <c r="G20" s="21" t="n">
-        <v>-0.01495923619863089</v>
-      </c>
-      <c r="H20" s="17" t="n">
-        <v>-287.01</v>
-      </c>
+          <t>All trades</t>
+        </is>
+      </c>
+      <c r="B20" s="22" t="n">
+        <v>5</v>
+      </c>
+      <c r="C20" s="23" t="n"/>
+      <c r="D20" s="24" t="n"/>
     </row>
     <row r="21">
       <c r="A21" s="3" t="inlineStr">
         <is>
-          <t>07-Sep-2026</t>
-        </is>
-      </c>
-      <c r="B21" s="6" t="n"/>
-      <c r="C21" s="15" t="n">
-        <v>-0.01223918772980555</v>
-      </c>
-      <c r="D21" s="6" t="n"/>
-      <c r="E21" s="6" t="n"/>
-      <c r="F21" s="6" t="n"/>
-      <c r="G21" s="21" t="n">
-        <v>-0.01223918772980555</v>
-      </c>
-      <c r="H21" s="17" t="n">
-        <v>-231.31</v>
-      </c>
+          <t>Winners</t>
+        </is>
+      </c>
+      <c r="B21" s="25" t="inlineStr">
+        <is>
+          <t>0 (0.0%)</t>
+        </is>
+      </c>
+      <c r="C21" s="23" t="n"/>
+      <c r="D21" s="24" t="n"/>
+    </row>
+    <row r="22">
+      <c r="A22" s="3" t="inlineStr">
+        <is>
+          <t>Losers</t>
+        </is>
+      </c>
+      <c r="B22" s="25" t="inlineStr">
+        <is>
+          <t>5 (100.0%)</t>
+        </is>
+      </c>
+      <c r="C22" s="23" t="n"/>
+      <c r="D22" s="24" t="n"/>
     </row>
     <row r="23">
-      <c r="A23" s="13" t="inlineStr">
-        <is>
-          <t>STATISTICS (all trades for this index)</t>
-        </is>
-      </c>
+      <c r="A23" s="3" t="inlineStr">
+        <is>
+          <t>Net P&amp;L (Rs)</t>
+        </is>
+      </c>
+      <c r="B23" s="27" t="n">
+        <v>-1335.02</v>
+      </c>
+      <c r="C23" s="23" t="n"/>
+      <c r="D23" s="24" t="n"/>
     </row>
     <row r="24">
       <c r="A24" s="3" t="inlineStr">
         <is>
-          <t>All trades</t>
-        </is>
-      </c>
-      <c r="B24" s="22" t="n">
-        <v>5</v>
+          <t>Total Profit (Rs)</t>
+        </is>
+      </c>
+      <c r="B24" s="26" t="n">
+        <v>0</v>
       </c>
       <c r="C24" s="23" t="n"/>
       <c r="D24" s="24" t="n"/>
@@ -4569,13 +4138,11 @@
     <row r="25">
       <c r="A25" s="3" t="inlineStr">
         <is>
-          <t>Winners</t>
-        </is>
-      </c>
-      <c r="B25" s="25" t="inlineStr">
-        <is>
-          <t>0 (0.0%)</t>
-        </is>
+          <t>Total Loss (Rs)</t>
+        </is>
+      </c>
+      <c r="B25" s="27" t="n">
+        <v>-1335.02</v>
       </c>
       <c r="C25" s="23" t="n"/>
       <c r="D25" s="24" t="n"/>
@@ -4583,13 +4150,11 @@
     <row r="26">
       <c r="A26" s="3" t="inlineStr">
         <is>
-          <t>Losers</t>
-        </is>
-      </c>
-      <c r="B26" s="25" t="inlineStr">
-        <is>
-          <t>5 (100.0%)</t>
-        </is>
+          <t>Transaction costs (Rs)</t>
+        </is>
+      </c>
+      <c r="B26" s="28" t="n">
+        <v>271.02</v>
       </c>
       <c r="C26" s="23" t="n"/>
       <c r="D26" s="24" t="n"/>
@@ -4597,11 +4162,11 @@
     <row r="27">
       <c r="A27" s="3" t="inlineStr">
         <is>
-          <t>Net P&amp;L (Rs)</t>
+          <t>Avg Profit/Loss per trade (Rs)</t>
         </is>
       </c>
       <c r="B27" s="27" t="n">
-        <v>-1332.18</v>
+        <v>-267</v>
       </c>
       <c r="C27" s="23" t="n"/>
       <c r="D27" s="24" t="n"/>
@@ -4609,11 +4174,11 @@
     <row r="28">
       <c r="A28" s="3" t="inlineStr">
         <is>
-          <t>Total Profit (Rs)</t>
-        </is>
-      </c>
-      <c r="B28" s="26" t="n">
-        <v>0</v>
+          <t>Avg Profit/Loss per trade (% of premium)</t>
+        </is>
+      </c>
+      <c r="B28" s="29" t="n">
+        <v>-14.84</v>
       </c>
       <c r="C28" s="23" t="n"/>
       <c r="D28" s="24" t="n"/>
@@ -4621,11 +4186,11 @@
     <row r="29">
       <c r="A29" s="3" t="inlineStr">
         <is>
-          <t>Total Loss (Rs)</t>
-        </is>
-      </c>
-      <c r="B29" s="27" t="n">
-        <v>-1332.18</v>
+          <t>Avg Win (Rs)</t>
+        </is>
+      </c>
+      <c r="B29" s="26" t="n">
+        <v>0</v>
       </c>
       <c r="C29" s="23" t="n"/>
       <c r="D29" s="24" t="n"/>
@@ -4633,11 +4198,11 @@
     <row r="30">
       <c r="A30" s="3" t="inlineStr">
         <is>
-          <t>Transaction costs (Rs)</t>
-        </is>
-      </c>
-      <c r="B30" s="28" t="n">
-        <v>271.38</v>
+          <t>Avg Win (% of premium)</t>
+        </is>
+      </c>
+      <c r="B30" s="30" t="n">
+        <v>0</v>
       </c>
       <c r="C30" s="23" t="n"/>
       <c r="D30" s="24" t="n"/>
@@ -4645,11 +4210,11 @@
     <row r="31">
       <c r="A31" s="3" t="inlineStr">
         <is>
-          <t>Avg Profit/Loss per trade (Rs)</t>
+          <t>Avg Loss (Rs)</t>
         </is>
       </c>
       <c r="B31" s="27" t="n">
-        <v>-266.44</v>
+        <v>-267</v>
       </c>
       <c r="C31" s="23" t="n"/>
       <c r="D31" s="24" t="n"/>
@@ -4657,11 +4222,11 @@
     <row r="32">
       <c r="A32" s="3" t="inlineStr">
         <is>
-          <t>Avg Profit/Loss per trade (% of premium)</t>
-        </is>
-      </c>
-      <c r="B32" s="29" t="n">
-        <v>-14.85</v>
+          <t>Avg Loss (% of premium)</t>
+        </is>
+      </c>
+      <c r="B32" s="31" t="n">
+        <v>-14.84</v>
       </c>
       <c r="C32" s="23" t="n"/>
       <c r="D32" s="24" t="n"/>
@@ -4669,11 +4234,11 @@
     <row r="33">
       <c r="A33" s="3" t="inlineStr">
         <is>
-          <t>Avg Win (Rs)</t>
+          <t>Largest Win (Rs)</t>
         </is>
       </c>
       <c r="B33" s="26" t="n">
-        <v>0</v>
+        <v>-216.68</v>
       </c>
       <c r="C33" s="23" t="n"/>
       <c r="D33" s="24" t="n"/>
@@ -4681,11 +4246,11 @@
     <row r="34">
       <c r="A34" s="3" t="inlineStr">
         <is>
-          <t>Avg Win (% of premium)</t>
-        </is>
-      </c>
-      <c r="B34" s="30" t="n">
-        <v>0</v>
+          <t>Largest Loss (Rs)</t>
+        </is>
+      </c>
+      <c r="B34" s="27" t="n">
+        <v>-317.9</v>
       </c>
       <c r="C34" s="23" t="n"/>
       <c r="D34" s="24" t="n"/>
@@ -4693,11 +4258,11 @@
     <row r="35">
       <c r="A35" s="3" t="inlineStr">
         <is>
-          <t>Avg Loss (Rs)</t>
-        </is>
-      </c>
-      <c r="B35" s="27" t="n">
-        <v>-266.44</v>
+          <t>Max Consecutive Wins</t>
+        </is>
+      </c>
+      <c r="B35" s="22" t="n">
+        <v>0</v>
       </c>
       <c r="C35" s="23" t="n"/>
       <c r="D35" s="24" t="n"/>
@@ -4705,11 +4270,11 @@
     <row r="36">
       <c r="A36" s="3" t="inlineStr">
         <is>
-          <t>Avg Loss (% of premium)</t>
-        </is>
-      </c>
-      <c r="B36" s="31" t="n">
-        <v>-14.85</v>
+          <t>Max Consecutive Losses</t>
+        </is>
+      </c>
+      <c r="B36" s="22" t="n">
+        <v>5</v>
       </c>
       <c r="C36" s="23" t="n"/>
       <c r="D36" s="24" t="n"/>
@@ -4717,11 +4282,11 @@
     <row r="37">
       <c r="A37" s="3" t="inlineStr">
         <is>
-          <t>Largest Win (Rs)</t>
-        </is>
-      </c>
-      <c r="B37" s="26" t="n">
-        <v>-231.31</v>
+          <t>Max trade drawdown (Rs)</t>
+        </is>
+      </c>
+      <c r="B37" s="27" t="n">
+        <v>-317.9</v>
       </c>
       <c r="C37" s="23" t="n"/>
       <c r="D37" s="24" t="n"/>
@@ -4729,11 +4294,11 @@
     <row r="38">
       <c r="A38" s="3" t="inlineStr">
         <is>
-          <t>Largest Loss (Rs)</t>
+          <t>Max system drawdown (Rs)</t>
         </is>
       </c>
       <c r="B38" s="27" t="n">
-        <v>-295.95</v>
+        <v>-1335.02</v>
       </c>
       <c r="C38" s="23" t="n"/>
       <c r="D38" s="24" t="n"/>
@@ -4741,11 +4306,11 @@
     <row r="39">
       <c r="A39" s="3" t="inlineStr">
         <is>
-          <t>Max Consecutive Wins</t>
-        </is>
-      </c>
-      <c r="B39" s="22" t="n">
-        <v>0</v>
+          <t>Max system drawdown (%)</t>
+        </is>
+      </c>
+      <c r="B39" s="31" t="n">
+        <v>-6.68</v>
       </c>
       <c r="C39" s="23" t="n"/>
       <c r="D39" s="24" t="n"/>
@@ -4753,11 +4318,11 @@
     <row r="40">
       <c r="A40" s="3" t="inlineStr">
         <is>
-          <t>Max Consecutive Losses</t>
-        </is>
-      </c>
-      <c r="B40" s="22" t="n">
-        <v>5</v>
+          <t>Recovery Factor</t>
+        </is>
+      </c>
+      <c r="B40" s="32" t="n">
+        <v>-1</v>
       </c>
       <c r="C40" s="23" t="n"/>
       <c r="D40" s="24" t="n"/>
@@ -4765,11 +4330,11 @@
     <row r="41">
       <c r="A41" s="3" t="inlineStr">
         <is>
-          <t>Max trade drawdown (Rs)</t>
-        </is>
-      </c>
-      <c r="B41" s="27" t="n">
-        <v>-295.95</v>
+          <t>Profit Factor</t>
+        </is>
+      </c>
+      <c r="B41" s="32" t="n">
+        <v>0</v>
       </c>
       <c r="C41" s="23" t="n"/>
       <c r="D41" s="24" t="n"/>
@@ -4777,11 +4342,13 @@
     <row r="42">
       <c r="A42" s="3" t="inlineStr">
         <is>
-          <t>Max system drawdown (Rs)</t>
-        </is>
-      </c>
-      <c r="B42" s="27" t="n">
-        <v>-1332.18</v>
+          <t>Payoff Ratio (avg win / avg loss)</t>
+        </is>
+      </c>
+      <c r="B42" s="25" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
       </c>
       <c r="C42" s="23" t="n"/>
       <c r="D42" s="24" t="n"/>
@@ -4789,67 +4356,17 @@
     <row r="43">
       <c r="A43" s="3" t="inlineStr">
         <is>
-          <t>Max system drawdown (%)</t>
-        </is>
-      </c>
-      <c r="B43" s="31" t="n">
-        <v>-6.66</v>
+          <t>Sharpe Ratio (annualized)</t>
+        </is>
+      </c>
+      <c r="B43" s="32" t="n">
+        <v>-77.79000000000001</v>
       </c>
       <c r="C43" s="23" t="n"/>
       <c r="D43" s="24" t="n"/>
     </row>
-    <row r="44">
-      <c r="A44" s="3" t="inlineStr">
-        <is>
-          <t>Recovery Factor</t>
-        </is>
-      </c>
-      <c r="B44" s="32" t="n">
-        <v>-1</v>
-      </c>
-      <c r="C44" s="23" t="n"/>
-      <c r="D44" s="24" t="n"/>
-    </row>
     <row r="45">
-      <c r="A45" s="3" t="inlineStr">
-        <is>
-          <t>Profit Factor</t>
-        </is>
-      </c>
-      <c r="B45" s="32" t="n">
-        <v>0</v>
-      </c>
-      <c r="C45" s="23" t="n"/>
-      <c r="D45" s="24" t="n"/>
-    </row>
-    <row r="46">
-      <c r="A46" s="3" t="inlineStr">
-        <is>
-          <t>Payoff Ratio (avg win / avg loss)</t>
-        </is>
-      </c>
-      <c r="B46" s="25" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="C46" s="23" t="n"/>
-      <c r="D46" s="24" t="n"/>
-    </row>
-    <row r="47">
-      <c r="A47" s="3" t="inlineStr">
-        <is>
-          <t>Sharpe Ratio (annualized)</t>
-        </is>
-      </c>
-      <c r="B47" s="32" t="n">
-        <v>-44.63</v>
-      </c>
-      <c r="C47" s="23" t="n"/>
-      <c r="D47" s="24" t="n"/>
-    </row>
-    <row r="49">
-      <c r="A49" s="5" t="inlineStr">
+      <c r="A45" s="5" t="inlineStr">
         <is>
           <t>Caveat: with only a handful of trades these numbers (Sharpe, profit factor, drawdown %) are not statistically reliable. Watch this over weeks/months before drawing conclusions.</t>
         </is>
@@ -4858,7 +4375,7 @@
   </sheetData>
   <mergeCells count="24">
     <mergeCell ref="B42:D42"/>
-    <mergeCell ref="B44:D44"/>
+    <mergeCell ref="B23:D23"/>
     <mergeCell ref="B29:D29"/>
     <mergeCell ref="B38:D38"/>
     <mergeCell ref="B34:D34"/>
@@ -4867,18 +4384,18 @@
     <mergeCell ref="B40:D40"/>
     <mergeCell ref="B30:D30"/>
     <mergeCell ref="B24:D24"/>
+    <mergeCell ref="B20:D20"/>
     <mergeCell ref="B33:D33"/>
     <mergeCell ref="B36:D36"/>
-    <mergeCell ref="B45:D45"/>
     <mergeCell ref="B41:D41"/>
     <mergeCell ref="B32:D32"/>
     <mergeCell ref="B35:D35"/>
     <mergeCell ref="B26:D26"/>
     <mergeCell ref="B25:D25"/>
-    <mergeCell ref="B47:D47"/>
     <mergeCell ref="B31:D31"/>
-    <mergeCell ref="B46:D46"/>
+    <mergeCell ref="B22:D22"/>
     <mergeCell ref="B27:D27"/>
+    <mergeCell ref="B21:D21"/>
     <mergeCell ref="B43:D43"/>
     <mergeCell ref="B39:D39"/>
   </mergeCells>

--- a/reports/dashboard.xlsx
+++ b/reports/dashboard.xlsx
@@ -73,12 +73,12 @@
     <font>
       <name val="Arial"/>
       <b val="1"/>
-      <color rgb="000B8A00"/>
+      <color rgb="00C00000"/>
     </font>
     <font>
       <name val="Arial"/>
       <b val="1"/>
-      <color rgb="00C00000"/>
+      <color rgb="000B8A00"/>
     </font>
   </fonts>
   <fills count="5">
@@ -96,14 +96,14 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="00E6F4EA"/>
-        <bgColor rgb="00E6F4EA"/>
+        <fgColor rgb="00FDE8E8"/>
+        <bgColor rgb="00FDE8E8"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="00FDE8E8"/>
-        <bgColor rgb="00FDE8E8"/>
+        <fgColor rgb="00E6F4EA"/>
+        <bgColor rgb="00E6F4EA"/>
       </patternFill>
     </fill>
   </fills>
@@ -194,14 +194,14 @@
     <xf numFmtId="10" fontId="4" fillId="0" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="165" fontId="7" fillId="0" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="164" fontId="6" fillId="3" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="164" fontId="7" fillId="4" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="164" fontId="7" fillId="3" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="164" fontId="6" fillId="4" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="164" fontId="6" fillId="0" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="166" fontId="6" fillId="0" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="164" fontId="7" fillId="0" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="164" fontId="8" fillId="3" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="166" fontId="7" fillId="0" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="164" fontId="9" fillId="4" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="166" fontId="7" fillId="0" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="1" fontId="4" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="right"/>
     </xf>
@@ -811,7 +811,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
-  <dimension ref="A1:O55"/>
+  <dimension ref="A1:O60"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="40" customWidth="1" min="1" max="1"/>
@@ -924,172 +924,188 @@
     </row>
     <row r="5">
       <c r="A5" s="3" t="n">
-        <v>2026</v>
-      </c>
-      <c r="B5" s="14" t="n">
-        <v>0.007486499999999999</v>
-      </c>
+        <v>2025</v>
+      </c>
+      <c r="B5" s="6" t="n"/>
       <c r="C5" s="6" t="n"/>
       <c r="D5" s="6" t="n"/>
-      <c r="E5" s="14" t="n">
-        <v>0.007542532827983304</v>
-      </c>
-      <c r="F5" s="14" t="n">
-        <v>0.05840394725370424</v>
-      </c>
+      <c r="E5" s="6" t="n"/>
+      <c r="F5" s="6" t="n"/>
       <c r="G5" s="6" t="n"/>
-      <c r="H5" s="15" t="n">
-        <v>-0.07320193545895015</v>
-      </c>
+      <c r="H5" s="6" t="n"/>
       <c r="I5" s="6" t="n"/>
-      <c r="J5" s="15" t="n">
-        <v>-0.08522889614546995</v>
-      </c>
+      <c r="J5" s="6" t="n"/>
       <c r="K5" s="6" t="n"/>
       <c r="L5" s="6" t="n"/>
-      <c r="M5" s="6" t="n"/>
+      <c r="M5" s="14" t="n">
+        <v>-0.082417</v>
+      </c>
       <c r="N5" s="18" t="n">
-        <v>-0.08914000000000022</v>
-      </c>
-      <c r="O5" s="21" t="n">
-        <v>-1782.8</v>
+        <v>-0.08241699999999996</v>
+      </c>
+      <c r="O5" s="20" t="n">
+        <v>-1648.34</v>
       </c>
     </row>
     <row r="6">
-      <c r="A6" s="3" t="inlineStr">
-        <is>
-          <t>Avg</t>
-        </is>
-      </c>
-      <c r="B6" s="16" t="n">
-        <v>0.007486499999999999</v>
+      <c r="A6" s="3" t="n">
+        <v>2026</v>
+      </c>
+      <c r="B6" s="14" t="n">
+        <v>-0.03399801434856575</v>
       </c>
       <c r="C6" s="6" t="n"/>
-      <c r="D6" s="6" t="n"/>
-      <c r="E6" s="16" t="n">
-        <v>0.007542532827983304</v>
-      </c>
-      <c r="F6" s="16" t="n">
-        <v>0.05840394725370424</v>
+      <c r="D6" s="14" t="n">
+        <v>-0.004249836696612201</v>
+      </c>
+      <c r="E6" s="15" t="n">
+        <v>0.01342480342616302</v>
+      </c>
+      <c r="F6" s="15" t="n">
+        <v>0.03063325839129137</v>
       </c>
       <c r="G6" s="6" t="n"/>
-      <c r="H6" s="18" t="n">
-        <v>-0.07320193545895015</v>
-      </c>
-      <c r="I6" s="6" t="n"/>
-      <c r="J6" s="18" t="n">
-        <v>-0.08522889614546995</v>
-      </c>
-      <c r="K6" s="6" t="n"/>
+      <c r="H6" s="6" t="n"/>
+      <c r="I6" s="14" t="n">
+        <v>-0.03079177692721151</v>
+      </c>
+      <c r="J6" s="14" t="n">
+        <v>-0.01294427932916501</v>
+      </c>
+      <c r="K6" s="14" t="n">
+        <v>-0.02117146945634402</v>
+      </c>
       <c r="L6" s="6" t="n"/>
       <c r="M6" s="6" t="n"/>
-    </row>
-    <row r="8">
-      <c r="A8" s="13" t="inlineStr">
+      <c r="N6" s="18" t="n">
+        <v>-0.05921698636526596</v>
+      </c>
+      <c r="O6" s="20" t="n">
+        <v>-1086.73</v>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" s="3" t="inlineStr">
+        <is>
+          <t>Avg</t>
+        </is>
+      </c>
+      <c r="B7" s="18" t="n">
+        <v>-0.03399801434856575</v>
+      </c>
+      <c r="C7" s="6" t="n"/>
+      <c r="D7" s="18" t="n">
+        <v>-0.004249836696612201</v>
+      </c>
+      <c r="E7" s="16" t="n">
+        <v>0.01342480342616302</v>
+      </c>
+      <c r="F7" s="16" t="n">
+        <v>0.03063325839129137</v>
+      </c>
+      <c r="G7" s="6" t="n"/>
+      <c r="H7" s="6" t="n"/>
+      <c r="I7" s="18" t="n">
+        <v>-0.03079177692721151</v>
+      </c>
+      <c r="J7" s="18" t="n">
+        <v>-0.01294427932916501</v>
+      </c>
+      <c r="K7" s="18" t="n">
+        <v>-0.02117146945634402</v>
+      </c>
+      <c r="L7" s="6" t="n"/>
+      <c r="M7" s="18" t="n">
+        <v>-0.082417</v>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" s="13" t="inlineStr">
         <is>
           <t>WEEKLY returns (% of capital at start of that week; weeks split at month edges)</t>
         </is>
       </c>
     </row>
-    <row r="9">
-      <c r="A9" s="2" t="inlineStr">
+    <row r="10">
+      <c r="A10" s="2" t="inlineStr">
         <is>
           <t>Month</t>
         </is>
       </c>
-      <c r="B9" s="2" t="inlineStr">
+      <c r="B10" s="2" t="inlineStr">
         <is>
           <t>W1</t>
         </is>
       </c>
-      <c r="C9" s="2" t="inlineStr">
+      <c r="C10" s="2" t="inlineStr">
         <is>
           <t>W2</t>
         </is>
       </c>
-      <c r="D9" s="2" t="inlineStr">
+      <c r="D10" s="2" t="inlineStr">
         <is>
           <t>W3</t>
         </is>
       </c>
-      <c r="E9" s="2" t="inlineStr">
+      <c r="E10" s="2" t="inlineStr">
         <is>
           <t>W4</t>
         </is>
       </c>
-      <c r="F9" s="2" t="inlineStr">
+      <c r="F10" s="2" t="inlineStr">
         <is>
           <t>W5</t>
         </is>
       </c>
-      <c r="G9" s="2" t="inlineStr">
+      <c r="G10" s="2" t="inlineStr">
         <is>
           <t>W6</t>
         </is>
       </c>
-      <c r="H9" s="2" t="inlineStr">
+      <c r="H10" s="2" t="inlineStr">
         <is>
           <t>Month %</t>
         </is>
       </c>
-      <c r="I9" s="2" t="inlineStr">
+      <c r="I10" s="2" t="inlineStr">
         <is>
           <t>Month P&amp;L (Rs)</t>
         </is>
-      </c>
-    </row>
-    <row r="10">
-      <c r="A10" s="3" t="inlineStr">
-        <is>
-          <t>2026-Jan</t>
-        </is>
-      </c>
-      <c r="B10" s="14" t="n">
-        <v>0.007486499999999999</v>
-      </c>
-      <c r="C10" s="6" t="n"/>
-      <c r="D10" s="6" t="n"/>
-      <c r="E10" s="6" t="n"/>
-      <c r="F10" s="6" t="n"/>
-      <c r="G10" s="6" t="n"/>
-      <c r="H10" s="19" t="n">
-        <v>0.007486499999999999</v>
-      </c>
-      <c r="I10" s="17" t="n">
-        <v>149.73</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" s="3" t="inlineStr">
         <is>
-          <t>2026-Apr</t>
+          <t>2025-Dec</t>
         </is>
       </c>
       <c r="B11" s="14" t="n">
-        <v>0.02240377414486447</v>
-      </c>
-      <c r="C11" s="15" t="n">
-        <v>-0.01453558925808061</v>
-      </c>
-      <c r="D11" s="6" t="n"/>
+        <v>-0.010346</v>
+      </c>
+      <c r="C11" s="14" t="n">
+        <v>-0.0369487719950609</v>
+      </c>
+      <c r="D11" s="14" t="n">
+        <v>-0.03725208860676486</v>
+      </c>
       <c r="E11" s="6" t="n"/>
       <c r="F11" s="6" t="n"/>
       <c r="G11" s="6" t="n"/>
       <c r="H11" s="19" t="n">
-        <v>0.007542532827983304</v>
-      </c>
-      <c r="I11" s="17" t="n">
-        <v>151.98</v>
+        <v>-0.082417</v>
+      </c>
+      <c r="I11" s="20" t="n">
+        <v>-1648.34</v>
       </c>
     </row>
     <row r="12">
       <c r="A12" s="3" t="inlineStr">
         <is>
-          <t>2026-May</t>
+          <t>2026-Jan</t>
         </is>
       </c>
       <c r="B12" s="14" t="n">
-        <v>0.05840394725370424</v>
+        <v>-0.03399801434856575</v>
       </c>
       <c r="C12" s="6" t="n"/>
       <c r="D12" s="6" t="n"/>
@@ -1097,390 +1113,424 @@
       <c r="F12" s="6" t="n"/>
       <c r="G12" s="6" t="n"/>
       <c r="H12" s="19" t="n">
-        <v>0.05840394725370424</v>
-      </c>
-      <c r="I12" s="17" t="n">
-        <v>1185.7</v>
+        <v>-0.03399801434856575</v>
+      </c>
+      <c r="I12" s="20" t="n">
+        <v>-623.92</v>
       </c>
     </row>
     <row r="13">
       <c r="A13" s="3" t="inlineStr">
         <is>
-          <t>2026-Jul</t>
-        </is>
-      </c>
-      <c r="B13" s="15" t="n">
-        <v>-0.01546998917040258</v>
-      </c>
-      <c r="C13" s="15" t="n">
-        <v>-0.04929992909477665</v>
-      </c>
-      <c r="D13" s="15" t="n">
-        <v>-0.009823459158335844</v>
-      </c>
+          <t>2026-Mar</t>
+        </is>
+      </c>
+      <c r="B13" s="14" t="n">
+        <v>-0.004249836696612201</v>
+      </c>
+      <c r="C13" s="6" t="n"/>
+      <c r="D13" s="6" t="n"/>
       <c r="E13" s="6" t="n"/>
       <c r="F13" s="6" t="n"/>
       <c r="G13" s="6" t="n"/>
-      <c r="H13" s="20" t="n">
-        <v>-0.07320193545895015</v>
-      </c>
-      <c r="I13" s="21" t="n">
-        <v>-1572.92</v>
+      <c r="H13" s="19" t="n">
+        <v>-0.004249836696612201</v>
+      </c>
+      <c r="I13" s="20" t="n">
+        <v>-75.34</v>
       </c>
     </row>
     <row r="14">
       <c r="A14" s="3" t="inlineStr">
         <is>
-          <t>2026-Sep</t>
+          <t>2026-Apr</t>
         </is>
       </c>
       <c r="B14" s="15" t="n">
-        <v>-0.02881419509111205</v>
-      </c>
-      <c r="C14" s="15" t="n">
-        <v>-0.009536898152959539</v>
-      </c>
-      <c r="D14" s="15" t="n">
-        <v>-0.0490190653479653</v>
-      </c>
+        <v>0.01342480342616302</v>
+      </c>
+      <c r="C14" s="6" t="n"/>
+      <c r="D14" s="6" t="n"/>
       <c r="E14" s="6" t="n"/>
       <c r="F14" s="6" t="n"/>
       <c r="G14" s="6" t="n"/>
-      <c r="H14" s="20" t="n">
-        <v>-0.08522889614546995</v>
-      </c>
-      <c r="I14" s="21" t="n">
-        <v>-1697.29</v>
+      <c r="H14" s="21" t="n">
+        <v>0.01342480342616302</v>
+      </c>
+      <c r="I14" s="17" t="n">
+        <v>236.98</v>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" s="3" t="inlineStr">
+        <is>
+          <t>2026-May</t>
+        </is>
+      </c>
+      <c r="B15" s="15" t="n">
+        <v>0.03063325839129137</v>
+      </c>
+      <c r="C15" s="6" t="n"/>
+      <c r="D15" s="6" t="n"/>
+      <c r="E15" s="6" t="n"/>
+      <c r="F15" s="6" t="n"/>
+      <c r="G15" s="6" t="n"/>
+      <c r="H15" s="21" t="n">
+        <v>0.03063325839129137</v>
+      </c>
+      <c r="I15" s="17" t="n">
+        <v>548.01</v>
       </c>
     </row>
     <row r="16">
-      <c r="A16" s="13" t="inlineStr">
-        <is>
-          <t>DAILY returns (% of capital at start of that day; blank = no trade that day)</t>
-        </is>
+      <c r="A16" s="3" t="inlineStr">
+        <is>
+          <t>2026-Aug</t>
+        </is>
+      </c>
+      <c r="B16" s="14" t="n">
+        <v>-0.01924892840038639</v>
+      </c>
+      <c r="C16" s="14" t="n">
+        <v>-0.01176939680320576</v>
+      </c>
+      <c r="D16" s="6" t="n"/>
+      <c r="E16" s="6" t="n"/>
+      <c r="F16" s="6" t="n"/>
+      <c r="G16" s="6" t="n"/>
+      <c r="H16" s="19" t="n">
+        <v>-0.03079177692721151</v>
+      </c>
+      <c r="I16" s="20" t="n">
+        <v>-567.72</v>
       </c>
     </row>
     <row r="17">
-      <c r="A17" s="2" t="inlineStr">
-        <is>
-          <t>Week starting (Mon)</t>
-        </is>
-      </c>
-      <c r="B17" s="2" t="inlineStr">
-        <is>
-          <t>Mon</t>
-        </is>
-      </c>
-      <c r="C17" s="2" t="inlineStr">
-        <is>
-          <t>Tue</t>
-        </is>
-      </c>
-      <c r="D17" s="2" t="inlineStr">
-        <is>
-          <t>Wed</t>
-        </is>
-      </c>
-      <c r="E17" s="2" t="inlineStr">
-        <is>
-          <t>Thu</t>
-        </is>
-      </c>
-      <c r="F17" s="2" t="inlineStr">
-        <is>
-          <t>Fri</t>
-        </is>
-      </c>
-      <c r="G17" s="2" t="inlineStr">
-        <is>
-          <t>Week %</t>
-        </is>
-      </c>
-      <c r="H17" s="2" t="inlineStr">
-        <is>
-          <t>Week P&amp;L (Rs)</t>
-        </is>
+      <c r="A17" s="3" t="inlineStr">
+        <is>
+          <t>2026-Sep</t>
+        </is>
+      </c>
+      <c r="B17" s="14" t="n">
+        <v>-0.01294427932916501</v>
+      </c>
+      <c r="C17" s="6" t="n"/>
+      <c r="D17" s="6" t="n"/>
+      <c r="E17" s="6" t="n"/>
+      <c r="F17" s="6" t="n"/>
+      <c r="G17" s="6" t="n"/>
+      <c r="H17" s="19" t="n">
+        <v>-0.01294427932916501</v>
+      </c>
+      <c r="I17" s="20" t="n">
+        <v>-231.31</v>
       </c>
     </row>
     <row r="18">
       <c r="A18" s="3" t="inlineStr">
         <is>
-          <t>19-Jan-2026</t>
-        </is>
-      </c>
-      <c r="B18" s="6" t="n"/>
-      <c r="C18" s="14" t="n">
-        <v>0.007486499999999999</v>
-      </c>
+          <t>2026-Oct</t>
+        </is>
+      </c>
+      <c r="B18" s="14" t="n">
+        <v>-0.02117146945634402</v>
+      </c>
+      <c r="C18" s="6" t="n"/>
       <c r="D18" s="6" t="n"/>
       <c r="E18" s="6" t="n"/>
       <c r="F18" s="6" t="n"/>
-      <c r="G18" s="19" t="n">
-        <v>0.007486499999999999</v>
-      </c>
-      <c r="H18" s="17" t="n">
-        <v>149.73</v>
-      </c>
-    </row>
-    <row r="19">
-      <c r="A19" s="3" t="inlineStr">
-        <is>
-          <t>06-Apr-2026</t>
-        </is>
-      </c>
-      <c r="B19" s="6" t="n"/>
-      <c r="C19" s="14" t="n">
-        <v>0.02240377414486447</v>
-      </c>
-      <c r="D19" s="6" t="n"/>
-      <c r="E19" s="6" t="n"/>
-      <c r="F19" s="6" t="n"/>
-      <c r="G19" s="19" t="n">
-        <v>0.02240377414486447</v>
-      </c>
-      <c r="H19" s="17" t="n">
-        <v>451.43</v>
+      <c r="G18" s="6" t="n"/>
+      <c r="H18" s="19" t="n">
+        <v>-0.02117146945634402</v>
+      </c>
+      <c r="I18" s="20" t="n">
+        <v>-373.43</v>
       </c>
     </row>
     <row r="20">
-      <c r="A20" s="3" t="inlineStr">
-        <is>
-          <t>20-Apr-2026</t>
-        </is>
-      </c>
-      <c r="B20" s="6" t="n"/>
-      <c r="C20" s="15" t="n">
-        <v>-0.01453558925808061</v>
-      </c>
-      <c r="D20" s="6" t="n"/>
-      <c r="E20" s="6" t="n"/>
-      <c r="F20" s="6" t="n"/>
-      <c r="G20" s="20" t="n">
-        <v>-0.01453558925808061</v>
-      </c>
-      <c r="H20" s="21" t="n">
-        <v>-299.45</v>
+      <c r="A20" s="13" t="inlineStr">
+        <is>
+          <t>DAILY returns (% of capital at start of that day; blank = no trade that day)</t>
+        </is>
       </c>
     </row>
     <row r="21">
-      <c r="A21" s="3" t="inlineStr">
-        <is>
-          <t>11-May-2026</t>
-        </is>
-      </c>
-      <c r="B21" s="6" t="n"/>
-      <c r="C21" s="14" t="n">
-        <v>0.05840394725370424</v>
-      </c>
-      <c r="D21" s="6" t="n"/>
-      <c r="E21" s="6" t="n"/>
-      <c r="F21" s="6" t="n"/>
-      <c r="G21" s="19" t="n">
-        <v>0.05840394725370424</v>
-      </c>
-      <c r="H21" s="17" t="n">
-        <v>1185.7</v>
+      <c r="A21" s="2" t="inlineStr">
+        <is>
+          <t>Week starting (Mon)</t>
+        </is>
+      </c>
+      <c r="B21" s="2" t="inlineStr">
+        <is>
+          <t>Mon</t>
+        </is>
+      </c>
+      <c r="C21" s="2" t="inlineStr">
+        <is>
+          <t>Tue</t>
+        </is>
+      </c>
+      <c r="D21" s="2" t="inlineStr">
+        <is>
+          <t>Wed</t>
+        </is>
+      </c>
+      <c r="E21" s="2" t="inlineStr">
+        <is>
+          <t>Thu</t>
+        </is>
+      </c>
+      <c r="F21" s="2" t="inlineStr">
+        <is>
+          <t>Fri</t>
+        </is>
+      </c>
+      <c r="G21" s="2" t="inlineStr">
+        <is>
+          <t>Week %</t>
+        </is>
+      </c>
+      <c r="H21" s="2" t="inlineStr">
+        <is>
+          <t>Week P&amp;L (Rs)</t>
+        </is>
       </c>
     </row>
     <row r="22">
       <c r="A22" s="3" t="inlineStr">
         <is>
-          <t>06-Jul-2026</t>
+          <t>01-Dec-2025</t>
         </is>
       </c>
       <c r="B22" s="6" t="n"/>
-      <c r="C22" s="15" t="n">
-        <v>-0.01546998917040258</v>
+      <c r="C22" s="14" t="n">
+        <v>-0.010346</v>
       </c>
       <c r="D22" s="6" t="n"/>
       <c r="E22" s="6" t="n"/>
       <c r="F22" s="6" t="n"/>
-      <c r="G22" s="20" t="n">
-        <v>-0.01546998917040258</v>
-      </c>
-      <c r="H22" s="21" t="n">
-        <v>-332.41</v>
+      <c r="G22" s="19" t="n">
+        <v>-0.010346</v>
+      </c>
+      <c r="H22" s="20" t="n">
+        <v>-206.92</v>
       </c>
     </row>
     <row r="23">
       <c r="A23" s="3" t="inlineStr">
         <is>
-          <t>13-Jul-2026</t>
+          <t>08-Dec-2025</t>
         </is>
       </c>
       <c r="B23" s="6" t="n"/>
-      <c r="C23" s="15" t="n">
-        <v>-0.04929992909477665</v>
+      <c r="C23" s="14" t="n">
+        <v>-0.0369487719950609</v>
       </c>
       <c r="D23" s="6" t="n"/>
       <c r="E23" s="6" t="n"/>
       <c r="F23" s="6" t="n"/>
-      <c r="G23" s="20" t="n">
-        <v>-0.04929992909477665</v>
-      </c>
-      <c r="H23" s="21" t="n">
-        <v>-1042.94</v>
+      <c r="G23" s="19" t="n">
+        <v>-0.0369487719950609</v>
+      </c>
+      <c r="H23" s="20" t="n">
+        <v>-731.33</v>
       </c>
     </row>
     <row r="24">
       <c r="A24" s="3" t="inlineStr">
         <is>
-          <t>27-Jul-2026</t>
+          <t>29-Dec-2025</t>
         </is>
       </c>
       <c r="B24" s="6" t="n"/>
-      <c r="C24" s="15" t="n">
-        <v>-0.009823459158335844</v>
+      <c r="C24" s="14" t="n">
+        <v>-0.03725208860676486</v>
       </c>
       <c r="D24" s="6" t="n"/>
       <c r="E24" s="6" t="n"/>
       <c r="F24" s="6" t="n"/>
-      <c r="G24" s="20" t="n">
-        <v>-0.009823459158335844</v>
-      </c>
-      <c r="H24" s="21" t="n">
-        <v>-197.57</v>
+      <c r="G24" s="19" t="n">
+        <v>-0.03725208860676486</v>
+      </c>
+      <c r="H24" s="20" t="n">
+        <v>-710.09</v>
       </c>
     </row>
     <row r="25">
       <c r="A25" s="3" t="inlineStr">
         <is>
-          <t>07-Sep-2026</t>
+          <t>26-Jan-2026</t>
         </is>
       </c>
       <c r="B25" s="6" t="n"/>
-      <c r="C25" s="15" t="n">
-        <v>-0.02881419509111205</v>
+      <c r="C25" s="14" t="n">
+        <v>-0.03399801434856575</v>
       </c>
       <c r="D25" s="6" t="n"/>
       <c r="E25" s="6" t="n"/>
       <c r="F25" s="6" t="n"/>
-      <c r="G25" s="20" t="n">
-        <v>-0.02881419509111205</v>
-      </c>
-      <c r="H25" s="21" t="n">
-        <v>-573.8200000000001</v>
+      <c r="G25" s="19" t="n">
+        <v>-0.03399801434856575</v>
+      </c>
+      <c r="H25" s="20" t="n">
+        <v>-623.92</v>
       </c>
     </row>
     <row r="26">
       <c r="A26" s="3" t="inlineStr">
         <is>
-          <t>14-Sep-2026</t>
+          <t>23-Mar-2026</t>
         </is>
       </c>
       <c r="B26" s="6" t="n"/>
-      <c r="C26" s="15" t="n">
-        <v>-0.009536898152959539</v>
+      <c r="C26" s="14" t="n">
+        <v>-0.004249836696612201</v>
       </c>
       <c r="D26" s="6" t="n"/>
       <c r="E26" s="6" t="n"/>
       <c r="F26" s="6" t="n"/>
-      <c r="G26" s="20" t="n">
-        <v>-0.009536898152959539</v>
-      </c>
-      <c r="H26" s="21" t="n">
-        <v>-184.45</v>
+      <c r="G26" s="19" t="n">
+        <v>-0.004249836696612201</v>
+      </c>
+      <c r="H26" s="20" t="n">
+        <v>-75.34</v>
       </c>
     </row>
     <row r="27">
       <c r="A27" s="3" t="inlineStr">
         <is>
-          <t>28-Sep-2026</t>
+          <t>06-Apr-2026</t>
         </is>
       </c>
       <c r="B27" s="6" t="n"/>
       <c r="C27" s="15" t="n">
-        <v>-0.0490190653479653</v>
+        <v>0.01342480342616302</v>
       </c>
       <c r="D27" s="6" t="n"/>
       <c r="E27" s="6" t="n"/>
       <c r="F27" s="6" t="n"/>
-      <c r="G27" s="20" t="n">
-        <v>-0.0490190653479653</v>
-      </c>
-      <c r="H27" s="21" t="n">
-        <v>-939.02</v>
+      <c r="G27" s="21" t="n">
+        <v>0.01342480342616302</v>
+      </c>
+      <c r="H27" s="17" t="n">
+        <v>236.98</v>
+      </c>
+    </row>
+    <row r="28">
+      <c r="A28" s="3" t="inlineStr">
+        <is>
+          <t>11-May-2026</t>
+        </is>
+      </c>
+      <c r="B28" s="6" t="n"/>
+      <c r="C28" s="15" t="n">
+        <v>0.03063325839129137</v>
+      </c>
+      <c r="D28" s="6" t="n"/>
+      <c r="E28" s="6" t="n"/>
+      <c r="F28" s="6" t="n"/>
+      <c r="G28" s="21" t="n">
+        <v>0.03063325839129137</v>
+      </c>
+      <c r="H28" s="17" t="n">
+        <v>548.01</v>
       </c>
     </row>
     <row r="29">
-      <c r="A29" s="13" t="inlineStr">
-        <is>
-          <t>STATISTICS (all trades for this index)</t>
-        </is>
+      <c r="A29" s="3" t="inlineStr">
+        <is>
+          <t>10-Aug-2026</t>
+        </is>
+      </c>
+      <c r="B29" s="6" t="n"/>
+      <c r="C29" s="14" t="n">
+        <v>-0.01924892840038639</v>
+      </c>
+      <c r="D29" s="6" t="n"/>
+      <c r="E29" s="6" t="n"/>
+      <c r="F29" s="6" t="n"/>
+      <c r="G29" s="19" t="n">
+        <v>-0.01924892840038639</v>
+      </c>
+      <c r="H29" s="20" t="n">
+        <v>-354.9</v>
       </c>
     </row>
     <row r="30">
       <c r="A30" s="3" t="inlineStr">
         <is>
-          <t>All trades</t>
-        </is>
-      </c>
-      <c r="B30" s="22" t="n">
-        <v>22</v>
-      </c>
-      <c r="C30" s="23" t="n"/>
-      <c r="D30" s="24" t="n"/>
+          <t>24-Aug-2026</t>
+        </is>
+      </c>
+      <c r="B30" s="6" t="n"/>
+      <c r="C30" s="14" t="n">
+        <v>-0.01176939680320576</v>
+      </c>
+      <c r="D30" s="6" t="n"/>
+      <c r="E30" s="6" t="n"/>
+      <c r="F30" s="6" t="n"/>
+      <c r="G30" s="19" t="n">
+        <v>-0.01176939680320576</v>
+      </c>
+      <c r="H30" s="20" t="n">
+        <v>-212.82</v>
+      </c>
     </row>
     <row r="31">
       <c r="A31" s="3" t="inlineStr">
         <is>
-          <t>Winners</t>
-        </is>
-      </c>
-      <c r="B31" s="25" t="inlineStr">
-        <is>
-          <t>5 (22.7%)</t>
-        </is>
-      </c>
-      <c r="C31" s="23" t="n"/>
-      <c r="D31" s="24" t="n"/>
+          <t>07-Sep-2026</t>
+        </is>
+      </c>
+      <c r="B31" s="6" t="n"/>
+      <c r="C31" s="14" t="n">
+        <v>-0.01294427932916501</v>
+      </c>
+      <c r="D31" s="6" t="n"/>
+      <c r="E31" s="6" t="n"/>
+      <c r="F31" s="6" t="n"/>
+      <c r="G31" s="19" t="n">
+        <v>-0.01294427932916501</v>
+      </c>
+      <c r="H31" s="20" t="n">
+        <v>-231.31</v>
+      </c>
     </row>
     <row r="32">
       <c r="A32" s="3" t="inlineStr">
         <is>
-          <t>Losers</t>
-        </is>
-      </c>
-      <c r="B32" s="25" t="inlineStr">
-        <is>
-          <t>17 (77.3%)</t>
-        </is>
-      </c>
-      <c r="C32" s="23" t="n"/>
-      <c r="D32" s="24" t="n"/>
-    </row>
-    <row r="33">
-      <c r="A33" s="3" t="inlineStr">
-        <is>
-          <t>Net P&amp;L (Rs)</t>
-        </is>
-      </c>
-      <c r="B33" s="27" t="n">
-        <v>-1782.8</v>
-      </c>
-      <c r="C33" s="23" t="n"/>
-      <c r="D33" s="24" t="n"/>
+          <t>12-Oct-2026</t>
+        </is>
+      </c>
+      <c r="B32" s="6" t="n"/>
+      <c r="C32" s="14" t="n">
+        <v>-0.02117146945634402</v>
+      </c>
+      <c r="D32" s="6" t="n"/>
+      <c r="E32" s="6" t="n"/>
+      <c r="F32" s="6" t="n"/>
+      <c r="G32" s="19" t="n">
+        <v>-0.02117146945634402</v>
+      </c>
+      <c r="H32" s="20" t="n">
+        <v>-373.43</v>
+      </c>
     </row>
     <row r="34">
-      <c r="A34" s="3" t="inlineStr">
-        <is>
-          <t>Total Profit (Rs)</t>
-        </is>
-      </c>
-      <c r="B34" s="26" t="n">
-        <v>2338.58</v>
-      </c>
-      <c r="C34" s="23" t="n"/>
-      <c r="D34" s="24" t="n"/>
+      <c r="A34" s="13" t="inlineStr">
+        <is>
+          <t>STATISTICS (all trades for this index)</t>
+        </is>
+      </c>
     </row>
     <row r="35">
       <c r="A35" s="3" t="inlineStr">
         <is>
-          <t>Total Loss (Rs)</t>
-        </is>
-      </c>
-      <c r="B35" s="27" t="n">
-        <v>-4121.38</v>
+          <t>All trades</t>
+        </is>
+      </c>
+      <c r="B35" s="22" t="n">
+        <v>18</v>
       </c>
       <c r="C35" s="23" t="n"/>
       <c r="D35" s="24" t="n"/>
@@ -1488,11 +1538,13 @@
     <row r="36">
       <c r="A36" s="3" t="inlineStr">
         <is>
-          <t>Transaction costs (Rs)</t>
-        </is>
-      </c>
-      <c r="B36" s="28" t="n">
-        <v>842.95</v>
+          <t>Winners</t>
+        </is>
+      </c>
+      <c r="B36" s="25" t="inlineStr">
+        <is>
+          <t>3 (16.7%)</t>
+        </is>
       </c>
       <c r="C36" s="23" t="n"/>
       <c r="D36" s="24" t="n"/>
@@ -1500,11 +1552,13 @@
     <row r="37">
       <c r="A37" s="3" t="inlineStr">
         <is>
-          <t>Avg Profit/Loss per trade (Rs)</t>
-        </is>
-      </c>
-      <c r="B37" s="27" t="n">
-        <v>-81.04000000000001</v>
+          <t>Losers</t>
+        </is>
+      </c>
+      <c r="B37" s="25" t="inlineStr">
+        <is>
+          <t>15 (83.3%)</t>
+        </is>
       </c>
       <c r="C37" s="23" t="n"/>
       <c r="D37" s="24" t="n"/>
@@ -1512,11 +1566,11 @@
     <row r="38">
       <c r="A38" s="3" t="inlineStr">
         <is>
-          <t>Avg Profit/Loss per trade (% of premium)</t>
-        </is>
-      </c>
-      <c r="B38" s="29" t="n">
-        <v>-3.56</v>
+          <t>Net P&amp;L (Rs)</t>
+        </is>
+      </c>
+      <c r="B38" s="27" t="n">
+        <v>-2735.07</v>
       </c>
       <c r="C38" s="23" t="n"/>
       <c r="D38" s="24" t="n"/>
@@ -1524,11 +1578,11 @@
     <row r="39">
       <c r="A39" s="3" t="inlineStr">
         <is>
-          <t>Avg Win (Rs)</t>
+          <t>Total Profit (Rs)</t>
         </is>
       </c>
       <c r="B39" s="26" t="n">
-        <v>467.72</v>
+        <v>1277.35</v>
       </c>
       <c r="C39" s="23" t="n"/>
       <c r="D39" s="24" t="n"/>
@@ -1536,11 +1590,11 @@
     <row r="40">
       <c r="A40" s="3" t="inlineStr">
         <is>
-          <t>Avg Win (% of premium)</t>
-        </is>
-      </c>
-      <c r="B40" s="30" t="n">
-        <v>54.93</v>
+          <t>Total Loss (Rs)</t>
+        </is>
+      </c>
+      <c r="B40" s="27" t="n">
+        <v>-4012.42</v>
       </c>
       <c r="C40" s="23" t="n"/>
       <c r="D40" s="24" t="n"/>
@@ -1548,11 +1602,11 @@
     <row r="41">
       <c r="A41" s="3" t="inlineStr">
         <is>
-          <t>Avg Loss (Rs)</t>
-        </is>
-      </c>
-      <c r="B41" s="27" t="n">
-        <v>-242.43</v>
+          <t>Transaction costs (Rs)</t>
+        </is>
+      </c>
+      <c r="B41" s="28" t="n">
+        <v>856.62</v>
       </c>
       <c r="C41" s="23" t="n"/>
       <c r="D41" s="24" t="n"/>
@@ -1560,11 +1614,11 @@
     <row r="42">
       <c r="A42" s="3" t="inlineStr">
         <is>
-          <t>Avg Loss (% of premium)</t>
-        </is>
-      </c>
-      <c r="B42" s="31" t="n">
-        <v>-20.76</v>
+          <t>Avg Profit/Loss per trade (Rs)</t>
+        </is>
+      </c>
+      <c r="B42" s="27" t="n">
+        <v>-151.95</v>
       </c>
       <c r="C42" s="23" t="n"/>
       <c r="D42" s="24" t="n"/>
@@ -1572,11 +1626,11 @@
     <row r="43">
       <c r="A43" s="3" t="inlineStr">
         <is>
-          <t>Largest Win (Rs)</t>
-        </is>
-      </c>
-      <c r="B43" s="26" t="n">
-        <v>552.97</v>
+          <t>Avg Profit/Loss per trade (% of premium)</t>
+        </is>
+      </c>
+      <c r="B43" s="29" t="n">
+        <v>-8.27</v>
       </c>
       <c r="C43" s="23" t="n"/>
       <c r="D43" s="24" t="n"/>
@@ -1584,11 +1638,11 @@
     <row r="44">
       <c r="A44" s="3" t="inlineStr">
         <is>
-          <t>Largest Loss (Rs)</t>
-        </is>
-      </c>
-      <c r="B44" s="27" t="n">
-        <v>-332.41</v>
+          <t>Avg Win (Rs)</t>
+        </is>
+      </c>
+      <c r="B44" s="26" t="n">
+        <v>425.78</v>
       </c>
       <c r="C44" s="23" t="n"/>
       <c r="D44" s="24" t="n"/>
@@ -1596,11 +1650,11 @@
     <row r="45">
       <c r="A45" s="3" t="inlineStr">
         <is>
-          <t>Max Consecutive Wins</t>
-        </is>
-      </c>
-      <c r="B45" s="22" t="n">
-        <v>3</v>
+          <t>Avg Win (% of premium)</t>
+        </is>
+      </c>
+      <c r="B45" s="30" t="n">
+        <v>42</v>
       </c>
       <c r="C45" s="23" t="n"/>
       <c r="D45" s="24" t="n"/>
@@ -1608,11 +1662,11 @@
     <row r="46">
       <c r="A46" s="3" t="inlineStr">
         <is>
-          <t>Max Consecutive Losses</t>
-        </is>
-      </c>
-      <c r="B46" s="22" t="n">
-        <v>14</v>
+          <t>Avg Loss (Rs)</t>
+        </is>
+      </c>
+      <c r="B46" s="27" t="n">
+        <v>-267.49</v>
       </c>
       <c r="C46" s="23" t="n"/>
       <c r="D46" s="24" t="n"/>
@@ -1620,11 +1674,11 @@
     <row r="47">
       <c r="A47" s="3" t="inlineStr">
         <is>
-          <t>Max trade drawdown (Rs)</t>
-        </is>
-      </c>
-      <c r="B47" s="27" t="n">
-        <v>-332.41</v>
+          <t>Avg Loss (% of premium)</t>
+        </is>
+      </c>
+      <c r="B47" s="31" t="n">
+        <v>-18.33</v>
       </c>
       <c r="C47" s="23" t="n"/>
       <c r="D47" s="24" t="n"/>
@@ -1632,11 +1686,11 @@
     <row r="48">
       <c r="A48" s="3" t="inlineStr">
         <is>
-          <t>Max system drawdown (Rs)</t>
-        </is>
-      </c>
-      <c r="B48" s="27" t="n">
-        <v>-3501.72</v>
+          <t>Largest Win (Rs)</t>
+        </is>
+      </c>
+      <c r="B48" s="26" t="n">
+        <v>548.01</v>
       </c>
       <c r="C48" s="23" t="n"/>
       <c r="D48" s="24" t="n"/>
@@ -1644,11 +1698,11 @@
     <row r="49">
       <c r="A49" s="3" t="inlineStr">
         <is>
-          <t>Max system drawdown (%)</t>
-        </is>
-      </c>
-      <c r="B49" s="31" t="n">
-        <v>-16.12</v>
+          <t>Largest Loss (Rs)</t>
+        </is>
+      </c>
+      <c r="B49" s="27" t="n">
+        <v>-358.86</v>
       </c>
       <c r="C49" s="23" t="n"/>
       <c r="D49" s="24" t="n"/>
@@ -1656,11 +1710,11 @@
     <row r="50">
       <c r="A50" s="3" t="inlineStr">
         <is>
-          <t>Recovery Factor</t>
-        </is>
-      </c>
-      <c r="B50" s="32" t="n">
-        <v>-0.51</v>
+          <t>Max Consecutive Wins</t>
+        </is>
+      </c>
+      <c r="B50" s="22" t="n">
+        <v>1</v>
       </c>
       <c r="C50" s="23" t="n"/>
       <c r="D50" s="24" t="n"/>
@@ -1668,11 +1722,11 @@
     <row r="51">
       <c r="A51" s="3" t="inlineStr">
         <is>
-          <t>Profit Factor</t>
-        </is>
-      </c>
-      <c r="B51" s="32" t="n">
-        <v>0.57</v>
+          <t>Max Consecutive Losses</t>
+        </is>
+      </c>
+      <c r="B51" s="22" t="n">
+        <v>12</v>
       </c>
       <c r="C51" s="23" t="n"/>
       <c r="D51" s="24" t="n"/>
@@ -1680,11 +1734,11 @@
     <row r="52">
       <c r="A52" s="3" t="inlineStr">
         <is>
-          <t>Payoff Ratio (avg win / avg loss)</t>
-        </is>
-      </c>
-      <c r="B52" s="32" t="n">
-        <v>1.93</v>
+          <t>Max trade drawdown (Rs)</t>
+        </is>
+      </c>
+      <c r="B52" s="27" t="n">
+        <v>-358.86</v>
       </c>
       <c r="C52" s="23" t="n"/>
       <c r="D52" s="24" t="n"/>
@@ -1692,17 +1746,77 @@
     <row r="53">
       <c r="A53" s="3" t="inlineStr">
         <is>
-          <t>Sharpe Ratio (annualized)</t>
-        </is>
-      </c>
-      <c r="B53" s="32" t="n">
-        <v>-4.54</v>
+          <t>Max system drawdown (Rs)</t>
+        </is>
+      </c>
+      <c r="B53" s="27" t="n">
+        <v>-3213.41</v>
       </c>
       <c r="C53" s="23" t="n"/>
       <c r="D53" s="24" t="n"/>
     </row>
+    <row r="54">
+      <c r="A54" s="3" t="inlineStr">
+        <is>
+          <t>Max system drawdown (%)</t>
+        </is>
+      </c>
+      <c r="B54" s="31" t="n">
+        <v>-15.7</v>
+      </c>
+      <c r="C54" s="23" t="n"/>
+      <c r="D54" s="24" t="n"/>
+    </row>
     <row r="55">
-      <c r="A55" s="5" t="inlineStr">
+      <c r="A55" s="3" t="inlineStr">
+        <is>
+          <t>Recovery Factor</t>
+        </is>
+      </c>
+      <c r="B55" s="32" t="n">
+        <v>-0.85</v>
+      </c>
+      <c r="C55" s="23" t="n"/>
+      <c r="D55" s="24" t="n"/>
+    </row>
+    <row r="56">
+      <c r="A56" s="3" t="inlineStr">
+        <is>
+          <t>Profit Factor</t>
+        </is>
+      </c>
+      <c r="B56" s="32" t="n">
+        <v>0.32</v>
+      </c>
+      <c r="C56" s="23" t="n"/>
+      <c r="D56" s="24" t="n"/>
+    </row>
+    <row r="57">
+      <c r="A57" s="3" t="inlineStr">
+        <is>
+          <t>Payoff Ratio (avg win / avg loss)</t>
+        </is>
+      </c>
+      <c r="B57" s="32" t="n">
+        <v>1.59</v>
+      </c>
+      <c r="C57" s="23" t="n"/>
+      <c r="D57" s="24" t="n"/>
+    </row>
+    <row r="58">
+      <c r="A58" s="3" t="inlineStr">
+        <is>
+          <t>Sharpe Ratio (annualized)</t>
+        </is>
+      </c>
+      <c r="B58" s="32" t="n">
+        <v>-10.39</v>
+      </c>
+      <c r="C58" s="23" t="n"/>
+      <c r="D58" s="24" t="n"/>
+    </row>
+    <row r="60">
+      <c r="A60" s="5" t="inlineStr">
         <is>
           <t>Caveat: with only a handful of trades these numbers (Sharpe, profit factor, drawdown %) are not statistically reliable. Watch this over weeks/months before drawing conclusions.</t>
         </is>
@@ -1711,25 +1825,25 @@
   </sheetData>
   <mergeCells count="24">
     <mergeCell ref="B42:D42"/>
+    <mergeCell ref="B57:D57"/>
     <mergeCell ref="B44:D44"/>
     <mergeCell ref="B53:D53"/>
     <mergeCell ref="B38:D38"/>
-    <mergeCell ref="B34:D34"/>
     <mergeCell ref="B37:D37"/>
     <mergeCell ref="B49:D49"/>
     <mergeCell ref="B40:D40"/>
-    <mergeCell ref="B30:D30"/>
+    <mergeCell ref="B55:D55"/>
     <mergeCell ref="B51:D51"/>
-    <mergeCell ref="B33:D33"/>
     <mergeCell ref="B36:D36"/>
     <mergeCell ref="B45:D45"/>
     <mergeCell ref="B41:D41"/>
-    <mergeCell ref="B32:D32"/>
     <mergeCell ref="B35:D35"/>
     <mergeCell ref="B50:D50"/>
     <mergeCell ref="B47:D47"/>
-    <mergeCell ref="B31:D31"/>
+    <mergeCell ref="B54:D54"/>
     <mergeCell ref="B46:D46"/>
+    <mergeCell ref="B56:D56"/>
+    <mergeCell ref="B58:D58"/>
     <mergeCell ref="B52:D52"/>
     <mergeCell ref="B43:D43"/>
     <mergeCell ref="B39:D39"/>
@@ -1994,23 +2108,23 @@
       </c>
       <c r="B4" s="6" t="inlineStr">
         <is>
-          <t>vwap_ema_momentum (EMA9/13) [60m]</t>
+          <t>vwap_ema_momentum (EMA9/13) [5m]</t>
         </is>
       </c>
       <c r="C4" s="7" t="n">
-        <v>12</v>
+        <v>5</v>
       </c>
       <c r="D4" s="8" t="n">
-        <v>0.4166666666666667</v>
+        <v>0.4</v>
       </c>
       <c r="E4" s="9" t="n">
-        <v>714.63</v>
+        <v>277.15</v>
       </c>
       <c r="F4" s="10" t="n">
-        <v>1.44</v>
+        <v>1.36</v>
       </c>
       <c r="G4" s="11" t="n">
-        <v>-0.04624032870879385</v>
+        <v>-0.01480658481386824</v>
       </c>
     </row>
     <row r="5">
@@ -2021,23 +2135,23 @@
       </c>
       <c r="B5" s="6" t="inlineStr">
         <is>
-          <t>trend_scalp_nw (EMA5/21) [1m]</t>
+          <t>trend_scalp_nw (EMA5/21) [5m]</t>
         </is>
       </c>
       <c r="C5" s="7" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="D5" s="8" t="n">
         <v>0</v>
       </c>
       <c r="E5" s="12" t="n">
-        <v>-1162.41</v>
+        <v>-1792.63</v>
       </c>
       <c r="F5" s="10" t="n">
         <v>0</v>
       </c>
       <c r="G5" s="11" t="n">
-        <v>-0.05812049999999982</v>
+        <v>-0.08963150000000004</v>
       </c>
     </row>
     <row r="6">
@@ -2048,23 +2162,23 @@
       </c>
       <c r="B6" s="6" t="inlineStr">
         <is>
-          <t>trend_scalp_nw (EMA9/21) [1m]</t>
+          <t>trend_scalp_nw (EMA9/26) [5m]</t>
         </is>
       </c>
       <c r="C6" s="7" t="n">
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="D6" s="8" t="n">
-        <v>0</v>
+        <v>0.1428571428571428</v>
       </c>
       <c r="E6" s="12" t="n">
-        <v>-1335.02</v>
+        <v>-1219.59</v>
       </c>
       <c r="F6" s="10" t="n">
-        <v>0</v>
+        <v>0.16</v>
       </c>
       <c r="G6" s="11" t="n">
-        <v>-0.06675100000000002</v>
+        <v>-0.06126299999999993</v>
       </c>
     </row>
     <row r="7">
@@ -2079,19 +2193,19 @@
         </is>
       </c>
       <c r="C7" s="7" t="n">
-        <v>22</v>
+        <v>18</v>
       </c>
       <c r="D7" s="8" t="n">
-        <v>0.2272727272727273</v>
+        <v>0.1666666666666667</v>
       </c>
       <c r="E7" s="12" t="n">
-        <v>-1782.8</v>
+        <v>-2735.07</v>
       </c>
       <c r="F7" s="10" t="n">
-        <v>0.57</v>
+        <v>0.32</v>
       </c>
       <c r="G7" s="11" t="n">
-        <v>-0.1612290113873062</v>
+        <v>-0.1569609630790708</v>
       </c>
     </row>
     <row r="9">
@@ -2113,7 +2227,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
-  <dimension ref="A1:O52"/>
+  <dimension ref="A1:O46"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="40" customWidth="1" min="1" max="1"/>
@@ -2136,7 +2250,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>BACKTEST NIFTY -- best: vwap_ema_momentum (EMA9/13) [60m] -- PAPER TRADE, NOT REAL MONEY</t>
+          <t>BACKTEST NIFTY -- best: vwap_ema_momentum (EMA9/13) [5m] -- PAPER TRADE, NOT REAL MONEY</t>
         </is>
       </c>
     </row>
@@ -2228,33 +2342,29 @@
       <c r="A5" s="3" t="n">
         <v>2026</v>
       </c>
-      <c r="B5" s="14" t="n">
-        <v>0.007486499999999999</v>
-      </c>
+      <c r="B5" s="6" t="n"/>
       <c r="C5" s="6" t="n"/>
-      <c r="D5" s="6" t="n"/>
-      <c r="E5" s="14" t="n">
-        <v>0.007542532827983304</v>
-      </c>
-      <c r="F5" s="14" t="n">
-        <v>0.05840394725370424</v>
+      <c r="D5" s="14" t="n">
+        <v>-0.003766999999999999</v>
+      </c>
+      <c r="E5" s="6" t="n"/>
+      <c r="F5" s="15" t="n">
+        <v>0.02750410797474085</v>
       </c>
       <c r="G5" s="6" t="n"/>
-      <c r="H5" s="15" t="n">
-        <v>-0.01546998917040258</v>
-      </c>
+      <c r="H5" s="6" t="n"/>
       <c r="I5" s="6" t="n"/>
-      <c r="J5" s="15" t="n">
-        <v>-0.02081635547151973</v>
-      </c>
-      <c r="K5" s="6" t="n"/>
+      <c r="J5" s="6" t="n"/>
+      <c r="K5" s="14" t="n">
+        <v>-0.009550293146912445</v>
+      </c>
       <c r="L5" s="6" t="n"/>
       <c r="M5" s="6" t="n"/>
       <c r="N5" s="16" t="n">
-        <v>0.03573149999999981</v>
+        <v>0.01385750000000008</v>
       </c>
       <c r="O5" s="17" t="n">
-        <v>714.63</v>
+        <v>277.15</v>
       </c>
     </row>
     <row r="6">
@@ -2263,26 +2373,22 @@
           <t>Avg</t>
         </is>
       </c>
-      <c r="B6" s="16" t="n">
-        <v>0.007486499999999999</v>
-      </c>
+      <c r="B6" s="6" t="n"/>
       <c r="C6" s="6" t="n"/>
-      <c r="D6" s="6" t="n"/>
-      <c r="E6" s="16" t="n">
-        <v>0.007542532827983304</v>
-      </c>
+      <c r="D6" s="18" t="n">
+        <v>-0.003766999999999999</v>
+      </c>
+      <c r="E6" s="6" t="n"/>
       <c r="F6" s="16" t="n">
-        <v>0.05840394725370424</v>
+        <v>0.02750410797474085</v>
       </c>
       <c r="G6" s="6" t="n"/>
-      <c r="H6" s="18" t="n">
-        <v>-0.01546998917040258</v>
-      </c>
+      <c r="H6" s="6" t="n"/>
       <c r="I6" s="6" t="n"/>
-      <c r="J6" s="18" t="n">
-        <v>-0.02081635547151973</v>
-      </c>
-      <c r="K6" s="6" t="n"/>
+      <c r="J6" s="6" t="n"/>
+      <c r="K6" s="18" t="n">
+        <v>-0.009550293146912445</v>
+      </c>
       <c r="L6" s="6" t="n"/>
       <c r="M6" s="6" t="n"/>
     </row>
@@ -2343,11 +2449,11 @@
     <row r="10">
       <c r="A10" s="3" t="inlineStr">
         <is>
-          <t>2026-Jan</t>
+          <t>2026-Mar</t>
         </is>
       </c>
       <c r="B10" s="14" t="n">
-        <v>0.007486499999999999</v>
+        <v>-0.003766999999999999</v>
       </c>
       <c r="C10" s="6" t="n"/>
       <c r="D10" s="6" t="n"/>
@@ -2355,43 +2461,41 @@
       <c r="F10" s="6" t="n"/>
       <c r="G10" s="6" t="n"/>
       <c r="H10" s="19" t="n">
-        <v>0.007486499999999999</v>
-      </c>
-      <c r="I10" s="17" t="n">
-        <v>149.73</v>
+        <v>-0.003766999999999999</v>
+      </c>
+      <c r="I10" s="20" t="n">
+        <v>-75.34</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" s="3" t="inlineStr">
         <is>
-          <t>2026-Apr</t>
-        </is>
-      </c>
-      <c r="B11" s="14" t="n">
-        <v>0.02240377414486447</v>
-      </c>
-      <c r="C11" s="15" t="n">
-        <v>-0.01453558925808061</v>
-      </c>
+          <t>2026-May</t>
+        </is>
+      </c>
+      <c r="B11" s="15" t="n">
+        <v>0.02750410797474085</v>
+      </c>
+      <c r="C11" s="6" t="n"/>
       <c r="D11" s="6" t="n"/>
       <c r="E11" s="6" t="n"/>
       <c r="F11" s="6" t="n"/>
       <c r="G11" s="6" t="n"/>
-      <c r="H11" s="19" t="n">
-        <v>0.007542532827983304</v>
+      <c r="H11" s="21" t="n">
+        <v>0.02750410797474085</v>
       </c>
       <c r="I11" s="17" t="n">
-        <v>151.98</v>
+        <v>548.01</v>
       </c>
     </row>
     <row r="12">
       <c r="A12" s="3" t="inlineStr">
         <is>
-          <t>2026-May</t>
+          <t>2026-Oct</t>
         </is>
       </c>
       <c r="B12" s="14" t="n">
-        <v>0.05840394725370424</v>
+        <v>-0.009550293146912445</v>
       </c>
       <c r="C12" s="6" t="n"/>
       <c r="D12" s="6" t="n"/>
@@ -2399,260 +2503,212 @@
       <c r="F12" s="6" t="n"/>
       <c r="G12" s="6" t="n"/>
       <c r="H12" s="19" t="n">
-        <v>0.05840394725370424</v>
-      </c>
-      <c r="I12" s="17" t="n">
-        <v>1185.7</v>
-      </c>
-    </row>
-    <row r="13">
-      <c r="A13" s="3" t="inlineStr">
-        <is>
-          <t>2026-Jul</t>
-        </is>
-      </c>
-      <c r="B13" s="15" t="n">
-        <v>-0.01546998917040258</v>
-      </c>
-      <c r="C13" s="6" t="n"/>
-      <c r="D13" s="6" t="n"/>
-      <c r="E13" s="6" t="n"/>
-      <c r="F13" s="6" t="n"/>
-      <c r="G13" s="6" t="n"/>
-      <c r="H13" s="20" t="n">
-        <v>-0.01546998917040258</v>
-      </c>
-      <c r="I13" s="21" t="n">
-        <v>-332.41</v>
+        <v>-0.009550293146912445</v>
+      </c>
+      <c r="I12" s="20" t="n">
+        <v>-195.52</v>
       </c>
     </row>
     <row r="14">
-      <c r="A14" s="3" t="inlineStr">
-        <is>
-          <t>2026-Sep</t>
-        </is>
-      </c>
-      <c r="B14" s="15" t="n">
-        <v>-0.012097376506736</v>
-      </c>
-      <c r="C14" s="15" t="n">
-        <v>-0.008825747353472017</v>
-      </c>
-      <c r="D14" s="6" t="n"/>
-      <c r="E14" s="6" t="n"/>
-      <c r="F14" s="6" t="n"/>
-      <c r="G14" s="6" t="n"/>
-      <c r="H14" s="20" t="n">
-        <v>-0.02081635547151973</v>
-      </c>
-      <c r="I14" s="21" t="n">
-        <v>-440.37</v>
+      <c r="A14" s="13" t="inlineStr">
+        <is>
+          <t>DAILY returns (% of capital at start of that day; blank = no trade that day)</t>
+        </is>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" s="2" t="inlineStr">
+        <is>
+          <t>Week starting (Mon)</t>
+        </is>
+      </c>
+      <c r="B15" s="2" t="inlineStr">
+        <is>
+          <t>Mon</t>
+        </is>
+      </c>
+      <c r="C15" s="2" t="inlineStr">
+        <is>
+          <t>Tue</t>
+        </is>
+      </c>
+      <c r="D15" s="2" t="inlineStr">
+        <is>
+          <t>Wed</t>
+        </is>
+      </c>
+      <c r="E15" s="2" t="inlineStr">
+        <is>
+          <t>Thu</t>
+        </is>
+      </c>
+      <c r="F15" s="2" t="inlineStr">
+        <is>
+          <t>Fri</t>
+        </is>
+      </c>
+      <c r="G15" s="2" t="inlineStr">
+        <is>
+          <t>Week %</t>
+        </is>
+      </c>
+      <c r="H15" s="2" t="inlineStr">
+        <is>
+          <t>Week P&amp;L (Rs)</t>
+        </is>
       </c>
     </row>
     <row r="16">
-      <c r="A16" s="13" t="inlineStr">
-        <is>
-          <t>DAILY returns (% of capital at start of that day; blank = no trade that day)</t>
-        </is>
+      <c r="A16" s="3" t="inlineStr">
+        <is>
+          <t>23-Mar-2026</t>
+        </is>
+      </c>
+      <c r="B16" s="6" t="n"/>
+      <c r="C16" s="14" t="n">
+        <v>-0.003766999999999999</v>
+      </c>
+      <c r="D16" s="6" t="n"/>
+      <c r="E16" s="6" t="n"/>
+      <c r="F16" s="6" t="n"/>
+      <c r="G16" s="19" t="n">
+        <v>-0.003766999999999999</v>
+      </c>
+      <c r="H16" s="20" t="n">
+        <v>-75.34</v>
       </c>
     </row>
     <row r="17">
-      <c r="A17" s="2" t="inlineStr">
-        <is>
-          <t>Week starting (Mon)</t>
-        </is>
-      </c>
-      <c r="B17" s="2" t="inlineStr">
-        <is>
-          <t>Mon</t>
-        </is>
-      </c>
-      <c r="C17" s="2" t="inlineStr">
-        <is>
-          <t>Tue</t>
-        </is>
-      </c>
-      <c r="D17" s="2" t="inlineStr">
-        <is>
-          <t>Wed</t>
-        </is>
-      </c>
-      <c r="E17" s="2" t="inlineStr">
-        <is>
-          <t>Thu</t>
-        </is>
-      </c>
-      <c r="F17" s="2" t="inlineStr">
-        <is>
-          <t>Fri</t>
-        </is>
-      </c>
-      <c r="G17" s="2" t="inlineStr">
-        <is>
-          <t>Week %</t>
-        </is>
-      </c>
-      <c r="H17" s="2" t="inlineStr">
-        <is>
-          <t>Week P&amp;L (Rs)</t>
-        </is>
+      <c r="A17" s="3" t="inlineStr">
+        <is>
+          <t>11-May-2026</t>
+        </is>
+      </c>
+      <c r="B17" s="6" t="n"/>
+      <c r="C17" s="15" t="n">
+        <v>0.02750410797474085</v>
+      </c>
+      <c r="D17" s="6" t="n"/>
+      <c r="E17" s="6" t="n"/>
+      <c r="F17" s="6" t="n"/>
+      <c r="G17" s="21" t="n">
+        <v>0.02750410797474085</v>
+      </c>
+      <c r="H17" s="17" t="n">
+        <v>548.01</v>
       </c>
     </row>
     <row r="18">
       <c r="A18" s="3" t="inlineStr">
         <is>
-          <t>19-Jan-2026</t>
+          <t>12-Oct-2026</t>
         </is>
       </c>
       <c r="B18" s="6" t="n"/>
       <c r="C18" s="14" t="n">
-        <v>0.007486499999999999</v>
+        <v>-0.009550293146912445</v>
       </c>
       <c r="D18" s="6" t="n"/>
       <c r="E18" s="6" t="n"/>
       <c r="F18" s="6" t="n"/>
       <c r="G18" s="19" t="n">
-        <v>0.007486499999999999</v>
-      </c>
-      <c r="H18" s="17" t="n">
-        <v>149.73</v>
-      </c>
-    </row>
-    <row r="19">
-      <c r="A19" s="3" t="inlineStr">
-        <is>
-          <t>06-Apr-2026</t>
-        </is>
-      </c>
-      <c r="B19" s="6" t="n"/>
-      <c r="C19" s="14" t="n">
-        <v>0.02240377414486447</v>
-      </c>
-      <c r="D19" s="6" t="n"/>
-      <c r="E19" s="6" t="n"/>
-      <c r="F19" s="6" t="n"/>
-      <c r="G19" s="19" t="n">
-        <v>0.02240377414486447</v>
-      </c>
-      <c r="H19" s="17" t="n">
-        <v>451.43</v>
+        <v>-0.009550293146912445</v>
+      </c>
+      <c r="H18" s="20" t="n">
+        <v>-195.52</v>
       </c>
     </row>
     <row r="20">
-      <c r="A20" s="3" t="inlineStr">
-        <is>
-          <t>20-Apr-2026</t>
-        </is>
-      </c>
-      <c r="B20" s="6" t="n"/>
-      <c r="C20" s="15" t="n">
-        <v>-0.01453558925808061</v>
-      </c>
-      <c r="D20" s="6" t="n"/>
-      <c r="E20" s="6" t="n"/>
-      <c r="F20" s="6" t="n"/>
-      <c r="G20" s="20" t="n">
-        <v>-0.01453558925808061</v>
-      </c>
-      <c r="H20" s="21" t="n">
-        <v>-299.45</v>
+      <c r="A20" s="13" t="inlineStr">
+        <is>
+          <t>STATISTICS (all trades for this index)</t>
+        </is>
       </c>
     </row>
     <row r="21">
       <c r="A21" s="3" t="inlineStr">
         <is>
-          <t>11-May-2026</t>
-        </is>
-      </c>
-      <c r="B21" s="6" t="n"/>
-      <c r="C21" s="14" t="n">
-        <v>0.05840394725370424</v>
-      </c>
-      <c r="D21" s="6" t="n"/>
-      <c r="E21" s="6" t="n"/>
-      <c r="F21" s="6" t="n"/>
-      <c r="G21" s="19" t="n">
-        <v>0.05840394725370424</v>
-      </c>
-      <c r="H21" s="17" t="n">
-        <v>1185.7</v>
-      </c>
+          <t>All trades</t>
+        </is>
+      </c>
+      <c r="B21" s="22" t="n">
+        <v>5</v>
+      </c>
+      <c r="C21" s="23" t="n"/>
+      <c r="D21" s="24" t="n"/>
     </row>
     <row r="22">
       <c r="A22" s="3" t="inlineStr">
         <is>
-          <t>06-Jul-2026</t>
-        </is>
-      </c>
-      <c r="B22" s="6" t="n"/>
-      <c r="C22" s="15" t="n">
-        <v>-0.01546998917040258</v>
-      </c>
-      <c r="D22" s="6" t="n"/>
-      <c r="E22" s="6" t="n"/>
-      <c r="F22" s="6" t="n"/>
-      <c r="G22" s="20" t="n">
-        <v>-0.01546998917040258</v>
-      </c>
-      <c r="H22" s="21" t="n">
-        <v>-332.41</v>
-      </c>
+          <t>Winners</t>
+        </is>
+      </c>
+      <c r="B22" s="25" t="inlineStr">
+        <is>
+          <t>2 (40.0%)</t>
+        </is>
+      </c>
+      <c r="C22" s="23" t="n"/>
+      <c r="D22" s="24" t="n"/>
     </row>
     <row r="23">
       <c r="A23" s="3" t="inlineStr">
         <is>
-          <t>07-Sep-2026</t>
-        </is>
-      </c>
-      <c r="B23" s="6" t="n"/>
-      <c r="C23" s="15" t="n">
-        <v>-0.012097376506736</v>
-      </c>
-      <c r="D23" s="6" t="n"/>
-      <c r="E23" s="6" t="n"/>
-      <c r="F23" s="6" t="n"/>
-      <c r="G23" s="20" t="n">
-        <v>-0.012097376506736</v>
-      </c>
-      <c r="H23" s="21" t="n">
-        <v>-255.92</v>
-      </c>
+          <t>Losers</t>
+        </is>
+      </c>
+      <c r="B23" s="25" t="inlineStr">
+        <is>
+          <t>3 (60.0%)</t>
+        </is>
+      </c>
+      <c r="C23" s="23" t="n"/>
+      <c r="D23" s="24" t="n"/>
     </row>
     <row r="24">
       <c r="A24" s="3" t="inlineStr">
         <is>
-          <t>14-Sep-2026</t>
-        </is>
-      </c>
-      <c r="B24" s="6" t="n"/>
-      <c r="C24" s="15" t="n">
-        <v>-0.008825747353472017</v>
-      </c>
-      <c r="D24" s="6" t="n"/>
-      <c r="E24" s="6" t="n"/>
-      <c r="F24" s="6" t="n"/>
-      <c r="G24" s="20" t="n">
-        <v>-0.008825747353472017</v>
-      </c>
-      <c r="H24" s="21" t="n">
-        <v>-184.45</v>
-      </c>
+          <t>Net P&amp;L (Rs)</t>
+        </is>
+      </c>
+      <c r="B24" s="26" t="n">
+        <v>277.15</v>
+      </c>
+      <c r="C24" s="23" t="n"/>
+      <c r="D24" s="24" t="n"/>
+    </row>
+    <row r="25">
+      <c r="A25" s="3" t="inlineStr">
+        <is>
+          <t>Total Profit (Rs)</t>
+        </is>
+      </c>
+      <c r="B25" s="26" t="n">
+        <v>1040.37</v>
+      </c>
+      <c r="C25" s="23" t="n"/>
+      <c r="D25" s="24" t="n"/>
     </row>
     <row r="26">
-      <c r="A26" s="13" t="inlineStr">
-        <is>
-          <t>STATISTICS (all trades for this index)</t>
-        </is>
-      </c>
+      <c r="A26" s="3" t="inlineStr">
+        <is>
+          <t>Total Loss (Rs)</t>
+        </is>
+      </c>
+      <c r="B26" s="27" t="n">
+        <v>-763.22</v>
+      </c>
+      <c r="C26" s="23" t="n"/>
+      <c r="D26" s="24" t="n"/>
     </row>
     <row r="27">
       <c r="A27" s="3" t="inlineStr">
         <is>
-          <t>All trades</t>
-        </is>
-      </c>
-      <c r="B27" s="22" t="n">
-        <v>12</v>
+          <t>Transaction costs (Rs)</t>
+        </is>
+      </c>
+      <c r="B27" s="28" t="n">
+        <v>143.6</v>
       </c>
       <c r="C27" s="23" t="n"/>
       <c r="D27" s="24" t="n"/>
@@ -2660,13 +2716,11 @@
     <row r="28">
       <c r="A28" s="3" t="inlineStr">
         <is>
-          <t>Winners</t>
-        </is>
-      </c>
-      <c r="B28" s="25" t="inlineStr">
-        <is>
-          <t>5 (41.7%)</t>
-        </is>
+          <t>Avg Profit/Loss per trade (Rs)</t>
+        </is>
+      </c>
+      <c r="B28" s="26" t="n">
+        <v>55.43</v>
       </c>
       <c r="C28" s="23" t="n"/>
       <c r="D28" s="24" t="n"/>
@@ -2674,13 +2728,11 @@
     <row r="29">
       <c r="A29" s="3" t="inlineStr">
         <is>
-          <t>Losers</t>
-        </is>
-      </c>
-      <c r="B29" s="25" t="inlineStr">
-        <is>
-          <t>7 (58.3%)</t>
-        </is>
+          <t>Avg Profit/Loss per trade (% of premium)</t>
+        </is>
+      </c>
+      <c r="B29" s="29" t="n">
+        <v>2.6</v>
       </c>
       <c r="C29" s="23" t="n"/>
       <c r="D29" s="24" t="n"/>
@@ -2688,11 +2740,11 @@
     <row r="30">
       <c r="A30" s="3" t="inlineStr">
         <is>
-          <t>Net P&amp;L (Rs)</t>
+          <t>Avg Win (Rs)</t>
         </is>
       </c>
       <c r="B30" s="26" t="n">
-        <v>714.63</v>
+        <v>520.1799999999999</v>
       </c>
       <c r="C30" s="23" t="n"/>
       <c r="D30" s="24" t="n"/>
@@ -2700,11 +2752,11 @@
     <row r="31">
       <c r="A31" s="3" t="inlineStr">
         <is>
-          <t>Total Profit (Rs)</t>
-        </is>
-      </c>
-      <c r="B31" s="26" t="n">
-        <v>2338.58</v>
+          <t>Avg Win (% of premium)</t>
+        </is>
+      </c>
+      <c r="B31" s="30" t="n">
+        <v>54.92</v>
       </c>
       <c r="C31" s="23" t="n"/>
       <c r="D31" s="24" t="n"/>
@@ -2712,11 +2764,11 @@
     <row r="32">
       <c r="A32" s="3" t="inlineStr">
         <is>
-          <t>Total Loss (Rs)</t>
+          <t>Avg Loss (Rs)</t>
         </is>
       </c>
       <c r="B32" s="27" t="n">
-        <v>-1623.95</v>
+        <v>-254.41</v>
       </c>
       <c r="C32" s="23" t="n"/>
       <c r="D32" s="24" t="n"/>
@@ -2724,11 +2776,11 @@
     <row r="33">
       <c r="A33" s="3" t="inlineStr">
         <is>
-          <t>Transaction costs (Rs)</t>
-        </is>
-      </c>
-      <c r="B33" s="28" t="n">
-        <v>335.62</v>
+          <t>Avg Loss (% of premium)</t>
+        </is>
+      </c>
+      <c r="B33" s="31" t="n">
+        <v>-32.27</v>
       </c>
       <c r="C33" s="23" t="n"/>
       <c r="D33" s="24" t="n"/>
@@ -2736,11 +2788,11 @@
     <row r="34">
       <c r="A34" s="3" t="inlineStr">
         <is>
-          <t>Avg Profit/Loss per trade (Rs)</t>
+          <t>Largest Win (Rs)</t>
         </is>
       </c>
       <c r="B34" s="26" t="n">
-        <v>59.55</v>
+        <v>548.01</v>
       </c>
       <c r="C34" s="23" t="n"/>
       <c r="D34" s="24" t="n"/>
@@ -2748,11 +2800,11 @@
     <row r="35">
       <c r="A35" s="3" t="inlineStr">
         <is>
-          <t>Avg Profit/Loss per trade (% of premium)</t>
-        </is>
-      </c>
-      <c r="B35" s="29" t="n">
-        <v>5.84</v>
+          <t>Largest Loss (Rs)</t>
+        </is>
+      </c>
+      <c r="B35" s="27" t="n">
+        <v>-299.45</v>
       </c>
       <c r="C35" s="23" t="n"/>
       <c r="D35" s="24" t="n"/>
@@ -2760,11 +2812,11 @@
     <row r="36">
       <c r="A36" s="3" t="inlineStr">
         <is>
-          <t>Avg Win (Rs)</t>
-        </is>
-      </c>
-      <c r="B36" s="26" t="n">
-        <v>467.72</v>
+          <t>Max Consecutive Wins</t>
+        </is>
+      </c>
+      <c r="B36" s="22" t="n">
+        <v>1</v>
       </c>
       <c r="C36" s="23" t="n"/>
       <c r="D36" s="24" t="n"/>
@@ -2772,11 +2824,11 @@
     <row r="37">
       <c r="A37" s="3" t="inlineStr">
         <is>
-          <t>Avg Win (% of premium)</t>
-        </is>
-      </c>
-      <c r="B37" s="30" t="n">
-        <v>54.93</v>
+          <t>Max Consecutive Losses</t>
+        </is>
+      </c>
+      <c r="B37" s="22" t="n">
+        <v>1</v>
       </c>
       <c r="C37" s="23" t="n"/>
       <c r="D37" s="24" t="n"/>
@@ -2784,11 +2836,11 @@
     <row r="38">
       <c r="A38" s="3" t="inlineStr">
         <is>
-          <t>Avg Loss (Rs)</t>
+          <t>Max trade drawdown (Rs)</t>
         </is>
       </c>
       <c r="B38" s="27" t="n">
-        <v>-231.99</v>
+        <v>-299.45</v>
       </c>
       <c r="C38" s="23" t="n"/>
       <c r="D38" s="24" t="n"/>
@@ -2796,11 +2848,11 @@
     <row r="39">
       <c r="A39" s="3" t="inlineStr">
         <is>
-          <t>Avg Loss (% of premium)</t>
-        </is>
-      </c>
-      <c r="B39" s="31" t="n">
-        <v>-29.23</v>
+          <t>Max system drawdown (Rs)</t>
+        </is>
+      </c>
+      <c r="B39" s="27" t="n">
+        <v>-299.45</v>
       </c>
       <c r="C39" s="23" t="n"/>
       <c r="D39" s="24" t="n"/>
@@ -2808,11 +2860,11 @@
     <row r="40">
       <c r="A40" s="3" t="inlineStr">
         <is>
-          <t>Largest Win (Rs)</t>
-        </is>
-      </c>
-      <c r="B40" s="26" t="n">
-        <v>552.97</v>
+          <t>Max system drawdown (%)</t>
+        </is>
+      </c>
+      <c r="B40" s="31" t="n">
+        <v>-1.48</v>
       </c>
       <c r="C40" s="23" t="n"/>
       <c r="D40" s="24" t="n"/>
@@ -2820,11 +2872,11 @@
     <row r="41">
       <c r="A41" s="3" t="inlineStr">
         <is>
-          <t>Largest Loss (Rs)</t>
-        </is>
-      </c>
-      <c r="B41" s="27" t="n">
-        <v>-332.41</v>
+          <t>Recovery Factor</t>
+        </is>
+      </c>
+      <c r="B41" s="32" t="n">
+        <v>0.93</v>
       </c>
       <c r="C41" s="23" t="n"/>
       <c r="D41" s="24" t="n"/>
@@ -2832,11 +2884,11 @@
     <row r="42">
       <c r="A42" s="3" t="inlineStr">
         <is>
-          <t>Max Consecutive Wins</t>
-        </is>
-      </c>
-      <c r="B42" s="22" t="n">
-        <v>3</v>
+          <t>Profit Factor</t>
+        </is>
+      </c>
+      <c r="B42" s="32" t="n">
+        <v>1.36</v>
       </c>
       <c r="C42" s="23" t="n"/>
       <c r="D42" s="24" t="n"/>
@@ -2844,11 +2896,11 @@
     <row r="43">
       <c r="A43" s="3" t="inlineStr">
         <is>
-          <t>Max Consecutive Losses</t>
-        </is>
-      </c>
-      <c r="B43" s="22" t="n">
-        <v>4</v>
+          <t>Payoff Ratio (avg win / avg loss)</t>
+        </is>
+      </c>
+      <c r="B43" s="32" t="n">
+        <v>2.04</v>
       </c>
       <c r="C43" s="23" t="n"/>
       <c r="D43" s="24" t="n"/>
@@ -2856,89 +2908,17 @@
     <row r="44">
       <c r="A44" s="3" t="inlineStr">
         <is>
-          <t>Max trade drawdown (Rs)</t>
-        </is>
-      </c>
-      <c r="B44" s="27" t="n">
-        <v>-332.41</v>
+          <t>Sharpe Ratio (annualized)</t>
+        </is>
+      </c>
+      <c r="B44" s="32" t="n">
+        <v>4.61</v>
       </c>
       <c r="C44" s="23" t="n"/>
       <c r="D44" s="24" t="n"/>
     </row>
-    <row r="45">
-      <c r="A45" s="3" t="inlineStr">
-        <is>
-          <t>Max system drawdown (Rs)</t>
-        </is>
-      </c>
-      <c r="B45" s="27" t="n">
-        <v>-1004.29</v>
-      </c>
-      <c r="C45" s="23" t="n"/>
-      <c r="D45" s="24" t="n"/>
-    </row>
     <row r="46">
-      <c r="A46" s="3" t="inlineStr">
-        <is>
-          <t>Max system drawdown (%)</t>
-        </is>
-      </c>
-      <c r="B46" s="31" t="n">
-        <v>-4.62</v>
-      </c>
-      <c r="C46" s="23" t="n"/>
-      <c r="D46" s="24" t="n"/>
-    </row>
-    <row r="47">
-      <c r="A47" s="3" t="inlineStr">
-        <is>
-          <t>Recovery Factor</t>
-        </is>
-      </c>
-      <c r="B47" s="32" t="n">
-        <v>0.71</v>
-      </c>
-      <c r="C47" s="23" t="n"/>
-      <c r="D47" s="24" t="n"/>
-    </row>
-    <row r="48">
-      <c r="A48" s="3" t="inlineStr">
-        <is>
-          <t>Profit Factor</t>
-        </is>
-      </c>
-      <c r="B48" s="32" t="n">
-        <v>1.44</v>
-      </c>
-      <c r="C48" s="23" t="n"/>
-      <c r="D48" s="24" t="n"/>
-    </row>
-    <row r="49">
-      <c r="A49" s="3" t="inlineStr">
-        <is>
-          <t>Payoff Ratio (avg win / avg loss)</t>
-        </is>
-      </c>
-      <c r="B49" s="32" t="n">
-        <v>2.02</v>
-      </c>
-      <c r="C49" s="23" t="n"/>
-      <c r="D49" s="24" t="n"/>
-    </row>
-    <row r="50">
-      <c r="A50" s="3" t="inlineStr">
-        <is>
-          <t>Sharpe Ratio (annualized)</t>
-        </is>
-      </c>
-      <c r="B50" s="32" t="n">
-        <v>3.36</v>
-      </c>
-      <c r="C50" s="23" t="n"/>
-      <c r="D50" s="24" t="n"/>
-    </row>
-    <row r="52">
-      <c r="A52" s="5" t="inlineStr">
+      <c r="A46" s="5" t="inlineStr">
         <is>
           <t>Caveat: with only a handful of trades these numbers (Sharpe, profit factor, drawdown %) are not statistically reliable. Watch this over weeks/months before drawing conclusions.</t>
         </is>
@@ -2947,29 +2927,29 @@
   </sheetData>
   <mergeCells count="24">
     <mergeCell ref="B42:D42"/>
+    <mergeCell ref="B23:D23"/>
     <mergeCell ref="B44:D44"/>
     <mergeCell ref="B29:D29"/>
     <mergeCell ref="B38:D38"/>
     <mergeCell ref="B34:D34"/>
     <mergeCell ref="B28:D28"/>
     <mergeCell ref="B37:D37"/>
-    <mergeCell ref="B49:D49"/>
     <mergeCell ref="B40:D40"/>
     <mergeCell ref="B30:D30"/>
+    <mergeCell ref="B24:D24"/>
     <mergeCell ref="B33:D33"/>
     <mergeCell ref="B36:D36"/>
-    <mergeCell ref="B45:D45"/>
     <mergeCell ref="B41:D41"/>
     <mergeCell ref="B32:D32"/>
     <mergeCell ref="B35:D35"/>
-    <mergeCell ref="B50:D50"/>
-    <mergeCell ref="B47:D47"/>
+    <mergeCell ref="B26:D26"/>
+    <mergeCell ref="B25:D25"/>
     <mergeCell ref="B31:D31"/>
-    <mergeCell ref="B46:D46"/>
+    <mergeCell ref="B22:D22"/>
     <mergeCell ref="B27:D27"/>
+    <mergeCell ref="B21:D21"/>
     <mergeCell ref="B43:D43"/>
     <mergeCell ref="B39:D39"/>
-    <mergeCell ref="B48:D48"/>
   </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
   <pageSetup orientation="landscape" fitToHeight="0" fitToWidth="1"/>
@@ -2982,7 +2962,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
-  <dimension ref="A1:O45"/>
+  <dimension ref="A1:O50"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="40" customWidth="1" min="1" max="1"/>
@@ -3005,7 +2985,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>BACKTEST BANKNIFTY -- best: trend_scalp_nw (EMA5/21) [1m] -- PAPER TRADE, NOT REAL MONEY</t>
+          <t>BACKTEST BANKNIFTY -- best: trend_scalp_nw (EMA5/21) [5m] -- PAPER TRADE, NOT REAL MONEY</t>
         </is>
       </c>
     </row>
@@ -3095,7 +3075,7 @@
     </row>
     <row r="5">
       <c r="A5" s="3" t="n">
-        <v>2026</v>
+        <v>2025</v>
       </c>
       <c r="B5" s="6" t="n"/>
       <c r="C5" s="6" t="n"/>
@@ -3103,332 +3083,381 @@
       <c r="E5" s="6" t="n"/>
       <c r="F5" s="6" t="n"/>
       <c r="G5" s="6" t="n"/>
-      <c r="H5" s="15" t="n">
-        <v>-0.0348495</v>
-      </c>
+      <c r="H5" s="6" t="n"/>
       <c r="I5" s="6" t="n"/>
-      <c r="J5" s="15" t="n">
-        <v>-0.02411126554874084</v>
-      </c>
+      <c r="J5" s="6" t="n"/>
       <c r="K5" s="6" t="n"/>
       <c r="L5" s="6" t="n"/>
-      <c r="M5" s="6" t="n"/>
+      <c r="M5" s="14" t="n">
+        <v>-0.0355045</v>
+      </c>
       <c r="N5" s="18" t="n">
-        <v>-0.05812050000000002</v>
-      </c>
-      <c r="O5" s="21" t="n">
-        <v>-1162.41</v>
+        <v>-0.03550450000000005</v>
+      </c>
+      <c r="O5" s="20" t="n">
+        <v>-710.09</v>
       </c>
     </row>
     <row r="6">
-      <c r="A6" s="3" t="inlineStr">
-        <is>
-          <t>Avg</t>
-        </is>
-      </c>
-      <c r="B6" s="6" t="n"/>
+      <c r="A6" s="3" t="n">
+        <v>2026</v>
+      </c>
+      <c r="B6" s="14" t="n">
+        <v>-0.01746560766742821</v>
+      </c>
       <c r="C6" s="6" t="n"/>
       <c r="D6" s="6" t="n"/>
       <c r="E6" s="6" t="n"/>
       <c r="F6" s="6" t="n"/>
       <c r="G6" s="6" t="n"/>
-      <c r="H6" s="18" t="n">
-        <v>-0.0348495</v>
-      </c>
-      <c r="I6" s="6" t="n"/>
-      <c r="J6" s="18" t="n">
-        <v>-0.02411126554874084</v>
-      </c>
-      <c r="K6" s="6" t="n"/>
+      <c r="H6" s="6" t="n"/>
+      <c r="I6" s="14" t="n">
+        <v>-0.02995409697673192</v>
+      </c>
+      <c r="J6" s="6" t="n"/>
+      <c r="K6" s="14" t="n">
+        <v>-0.009676763149650155</v>
+      </c>
       <c r="L6" s="6" t="n"/>
       <c r="M6" s="6" t="n"/>
-    </row>
-    <row r="8">
-      <c r="A8" s="13" t="inlineStr">
+      <c r="N6" s="18" t="n">
+        <v>-0.05611949459587939</v>
+      </c>
+      <c r="O6" s="20" t="n">
+        <v>-1082.54</v>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" s="3" t="inlineStr">
+        <is>
+          <t>Avg</t>
+        </is>
+      </c>
+      <c r="B7" s="18" t="n">
+        <v>-0.01746560766742821</v>
+      </c>
+      <c r="C7" s="6" t="n"/>
+      <c r="D7" s="6" t="n"/>
+      <c r="E7" s="6" t="n"/>
+      <c r="F7" s="6" t="n"/>
+      <c r="G7" s="6" t="n"/>
+      <c r="H7" s="6" t="n"/>
+      <c r="I7" s="18" t="n">
+        <v>-0.02995409697673192</v>
+      </c>
+      <c r="J7" s="6" t="n"/>
+      <c r="K7" s="18" t="n">
+        <v>-0.009676763149650155</v>
+      </c>
+      <c r="L7" s="6" t="n"/>
+      <c r="M7" s="18" t="n">
+        <v>-0.0355045</v>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" s="13" t="inlineStr">
         <is>
           <t>WEEKLY returns (% of capital at start of that week; weeks split at month edges)</t>
         </is>
       </c>
     </row>
-    <row r="9">
-      <c r="A9" s="2" t="inlineStr">
+    <row r="10">
+      <c r="A10" s="2" t="inlineStr">
         <is>
           <t>Month</t>
         </is>
       </c>
-      <c r="B9" s="2" t="inlineStr">
+      <c r="B10" s="2" t="inlineStr">
         <is>
           <t>W1</t>
         </is>
       </c>
-      <c r="C9" s="2" t="inlineStr">
+      <c r="C10" s="2" t="inlineStr">
         <is>
           <t>W2</t>
         </is>
       </c>
-      <c r="D9" s="2" t="inlineStr">
+      <c r="D10" s="2" t="inlineStr">
         <is>
           <t>W3</t>
         </is>
       </c>
-      <c r="E9" s="2" t="inlineStr">
+      <c r="E10" s="2" t="inlineStr">
         <is>
           <t>W4</t>
         </is>
       </c>
-      <c r="F9" s="2" t="inlineStr">
+      <c r="F10" s="2" t="inlineStr">
         <is>
           <t>W5</t>
         </is>
       </c>
-      <c r="G9" s="2" t="inlineStr">
+      <c r="G10" s="2" t="inlineStr">
         <is>
           <t>W6</t>
         </is>
       </c>
-      <c r="H9" s="2" t="inlineStr">
+      <c r="H10" s="2" t="inlineStr">
         <is>
           <t>Month %</t>
         </is>
       </c>
-      <c r="I9" s="2" t="inlineStr">
+      <c r="I10" s="2" t="inlineStr">
         <is>
           <t>Month P&amp;L (Rs)</t>
         </is>
-      </c>
-    </row>
-    <row r="10">
-      <c r="A10" s="3" t="inlineStr">
-        <is>
-          <t>2026-Jul</t>
-        </is>
-      </c>
-      <c r="B10" s="15" t="n">
-        <v>-0.024971</v>
-      </c>
-      <c r="C10" s="15" t="n">
-        <v>-0.01013149352480798</v>
-      </c>
-      <c r="D10" s="6" t="n"/>
-      <c r="E10" s="6" t="n"/>
-      <c r="F10" s="6" t="n"/>
-      <c r="G10" s="6" t="n"/>
-      <c r="H10" s="20" t="n">
-        <v>-0.0348495</v>
-      </c>
-      <c r="I10" s="21" t="n">
-        <v>-696.99</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" s="3" t="inlineStr">
         <is>
-          <t>2026-Sep</t>
-        </is>
-      </c>
-      <c r="B11" s="15" t="n">
-        <v>-0.02411126554874084</v>
+          <t>2025-Dec</t>
+        </is>
+      </c>
+      <c r="B11" s="14" t="n">
+        <v>-0.0355045</v>
       </c>
       <c r="C11" s="6" t="n"/>
       <c r="D11" s="6" t="n"/>
       <c r="E11" s="6" t="n"/>
       <c r="F11" s="6" t="n"/>
       <c r="G11" s="6" t="n"/>
-      <c r="H11" s="20" t="n">
-        <v>-0.02411126554874084</v>
-      </c>
-      <c r="I11" s="21" t="n">
-        <v>-465.42</v>
+      <c r="H11" s="19" t="n">
+        <v>-0.0355045</v>
+      </c>
+      <c r="I11" s="20" t="n">
+        <v>-710.09</v>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" s="3" t="inlineStr">
+        <is>
+          <t>2026-Jan</t>
+        </is>
+      </c>
+      <c r="B12" s="14" t="n">
+        <v>-0.01746560766742821</v>
+      </c>
+      <c r="C12" s="6" t="n"/>
+      <c r="D12" s="6" t="n"/>
+      <c r="E12" s="6" t="n"/>
+      <c r="F12" s="6" t="n"/>
+      <c r="G12" s="6" t="n"/>
+      <c r="H12" s="19" t="n">
+        <v>-0.01746560766742821</v>
+      </c>
+      <c r="I12" s="20" t="n">
+        <v>-336.91</v>
       </c>
     </row>
     <row r="13">
-      <c r="A13" s="13" t="inlineStr">
+      <c r="A13" s="3" t="inlineStr">
+        <is>
+          <t>2026-Aug</t>
+        </is>
+      </c>
+      <c r="B13" s="14" t="n">
+        <v>-0.01872526776763573</v>
+      </c>
+      <c r="C13" s="14" t="n">
+        <v>-0.01144310440313796</v>
+      </c>
+      <c r="D13" s="6" t="n"/>
+      <c r="E13" s="6" t="n"/>
+      <c r="F13" s="6" t="n"/>
+      <c r="G13" s="6" t="n"/>
+      <c r="H13" s="19" t="n">
+        <v>-0.02995409697673192</v>
+      </c>
+      <c r="I13" s="20" t="n">
+        <v>-567.72</v>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" s="3" t="inlineStr">
+        <is>
+          <t>2026-Oct</t>
+        </is>
+      </c>
+      <c r="B14" s="14" t="n">
+        <v>-0.009676763149650155</v>
+      </c>
+      <c r="C14" s="6" t="n"/>
+      <c r="D14" s="6" t="n"/>
+      <c r="E14" s="6" t="n"/>
+      <c r="F14" s="6" t="n"/>
+      <c r="G14" s="6" t="n"/>
+      <c r="H14" s="19" t="n">
+        <v>-0.009676763149650155</v>
+      </c>
+      <c r="I14" s="20" t="n">
+        <v>-177.91</v>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" s="13" t="inlineStr">
         <is>
           <t>DAILY returns (% of capital at start of that day; blank = no trade that day)</t>
         </is>
       </c>
     </row>
-    <row r="14">
-      <c r="A14" s="2" t="inlineStr">
+    <row r="17">
+      <c r="A17" s="2" t="inlineStr">
         <is>
           <t>Week starting (Mon)</t>
         </is>
       </c>
-      <c r="B14" s="2" t="inlineStr">
+      <c r="B17" s="2" t="inlineStr">
         <is>
           <t>Mon</t>
         </is>
       </c>
-      <c r="C14" s="2" t="inlineStr">
+      <c r="C17" s="2" t="inlineStr">
         <is>
           <t>Tue</t>
         </is>
       </c>
-      <c r="D14" s="2" t="inlineStr">
+      <c r="D17" s="2" t="inlineStr">
         <is>
           <t>Wed</t>
         </is>
       </c>
-      <c r="E14" s="2" t="inlineStr">
+      <c r="E17" s="2" t="inlineStr">
         <is>
           <t>Thu</t>
         </is>
       </c>
-      <c r="F14" s="2" t="inlineStr">
+      <c r="F17" s="2" t="inlineStr">
         <is>
           <t>Fri</t>
         </is>
       </c>
-      <c r="G14" s="2" t="inlineStr">
+      <c r="G17" s="2" t="inlineStr">
         <is>
           <t>Week %</t>
         </is>
       </c>
-      <c r="H14" s="2" t="inlineStr">
+      <c r="H17" s="2" t="inlineStr">
         <is>
           <t>Week P&amp;L (Rs)</t>
         </is>
       </c>
     </row>
-    <row r="15">
-      <c r="A15" s="3" t="inlineStr">
-        <is>
-          <t>13-Jul-2026</t>
-        </is>
-      </c>
-      <c r="B15" s="6" t="n"/>
-      <c r="C15" s="15" t="n">
-        <v>-0.024971</v>
-      </c>
-      <c r="D15" s="6" t="n"/>
-      <c r="E15" s="6" t="n"/>
-      <c r="F15" s="6" t="n"/>
-      <c r="G15" s="20" t="n">
-        <v>-0.024971</v>
-      </c>
-      <c r="H15" s="21" t="n">
-        <v>-499.42</v>
-      </c>
-    </row>
-    <row r="16">
-      <c r="A16" s="3" t="inlineStr">
-        <is>
-          <t>27-Jul-2026</t>
-        </is>
-      </c>
-      <c r="B16" s="6" t="n"/>
-      <c r="C16" s="15" t="n">
-        <v>-0.01013149352480798</v>
-      </c>
-      <c r="D16" s="6" t="n"/>
-      <c r="E16" s="6" t="n"/>
-      <c r="F16" s="6" t="n"/>
-      <c r="G16" s="20" t="n">
-        <v>-0.01013149352480798</v>
-      </c>
-      <c r="H16" s="21" t="n">
-        <v>-197.57</v>
-      </c>
-    </row>
-    <row r="17">
-      <c r="A17" s="3" t="inlineStr">
-        <is>
-          <t>28-Sep-2026</t>
-        </is>
-      </c>
-      <c r="B17" s="6" t="n"/>
-      <c r="C17" s="15" t="n">
-        <v>-0.02411126554874084</v>
-      </c>
-      <c r="D17" s="6" t="n"/>
-      <c r="E17" s="6" t="n"/>
-      <c r="F17" s="6" t="n"/>
-      <c r="G17" s="20" t="n">
-        <v>-0.02411126554874084</v>
-      </c>
-      <c r="H17" s="21" t="n">
-        <v>-465.42</v>
+    <row r="18">
+      <c r="A18" s="3" t="inlineStr">
+        <is>
+          <t>29-Dec-2025</t>
+        </is>
+      </c>
+      <c r="B18" s="6" t="n"/>
+      <c r="C18" s="14" t="n">
+        <v>-0.0355045</v>
+      </c>
+      <c r="D18" s="6" t="n"/>
+      <c r="E18" s="6" t="n"/>
+      <c r="F18" s="6" t="n"/>
+      <c r="G18" s="19" t="n">
+        <v>-0.0355045</v>
+      </c>
+      <c r="H18" s="20" t="n">
+        <v>-710.09</v>
       </c>
     </row>
     <row r="19">
-      <c r="A19" s="13" t="inlineStr">
-        <is>
-          <t>STATISTICS (all trades for this index)</t>
-        </is>
+      <c r="A19" s="3" t="inlineStr">
+        <is>
+          <t>26-Jan-2026</t>
+        </is>
+      </c>
+      <c r="B19" s="6" t="n"/>
+      <c r="C19" s="14" t="n">
+        <v>-0.01746560766742821</v>
+      </c>
+      <c r="D19" s="6" t="n"/>
+      <c r="E19" s="6" t="n"/>
+      <c r="F19" s="6" t="n"/>
+      <c r="G19" s="19" t="n">
+        <v>-0.01746560766742821</v>
+      </c>
+      <c r="H19" s="20" t="n">
+        <v>-336.91</v>
       </c>
     </row>
     <row r="20">
       <c r="A20" s="3" t="inlineStr">
         <is>
-          <t>All trades</t>
-        </is>
-      </c>
-      <c r="B20" s="22" t="n">
-        <v>5</v>
-      </c>
-      <c r="C20" s="23" t="n"/>
-      <c r="D20" s="24" t="n"/>
+          <t>10-Aug-2026</t>
+        </is>
+      </c>
+      <c r="B20" s="6" t="n"/>
+      <c r="C20" s="14" t="n">
+        <v>-0.01872526776763573</v>
+      </c>
+      <c r="D20" s="6" t="n"/>
+      <c r="E20" s="6" t="n"/>
+      <c r="F20" s="6" t="n"/>
+      <c r="G20" s="19" t="n">
+        <v>-0.01872526776763573</v>
+      </c>
+      <c r="H20" s="20" t="n">
+        <v>-354.9</v>
+      </c>
     </row>
     <row r="21">
       <c r="A21" s="3" t="inlineStr">
         <is>
-          <t>Winners</t>
-        </is>
-      </c>
-      <c r="B21" s="25" t="inlineStr">
-        <is>
-          <t>0 (0.0%)</t>
-        </is>
-      </c>
-      <c r="C21" s="23" t="n"/>
-      <c r="D21" s="24" t="n"/>
+          <t>24-Aug-2026</t>
+        </is>
+      </c>
+      <c r="B21" s="6" t="n"/>
+      <c r="C21" s="14" t="n">
+        <v>-0.01144310440313796</v>
+      </c>
+      <c r="D21" s="6" t="n"/>
+      <c r="E21" s="6" t="n"/>
+      <c r="F21" s="6" t="n"/>
+      <c r="G21" s="19" t="n">
+        <v>-0.01144310440313796</v>
+      </c>
+      <c r="H21" s="20" t="n">
+        <v>-212.82</v>
+      </c>
     </row>
     <row r="22">
       <c r="A22" s="3" t="inlineStr">
         <is>
-          <t>Losers</t>
-        </is>
-      </c>
-      <c r="B22" s="25" t="inlineStr">
-        <is>
-          <t>5 (100.0%)</t>
-        </is>
-      </c>
-      <c r="C22" s="23" t="n"/>
-      <c r="D22" s="24" t="n"/>
-    </row>
-    <row r="23">
-      <c r="A23" s="3" t="inlineStr">
-        <is>
-          <t>Net P&amp;L (Rs)</t>
-        </is>
-      </c>
-      <c r="B23" s="27" t="n">
-        <v>-1162.41</v>
-      </c>
-      <c r="C23" s="23" t="n"/>
-      <c r="D23" s="24" t="n"/>
+          <t>12-Oct-2026</t>
+        </is>
+      </c>
+      <c r="B22" s="6" t="n"/>
+      <c r="C22" s="14" t="n">
+        <v>-0.009676763149650155</v>
+      </c>
+      <c r="D22" s="6" t="n"/>
+      <c r="E22" s="6" t="n"/>
+      <c r="F22" s="6" t="n"/>
+      <c r="G22" s="19" t="n">
+        <v>-0.009676763149650155</v>
+      </c>
+      <c r="H22" s="20" t="n">
+        <v>-177.91</v>
+      </c>
     </row>
     <row r="24">
-      <c r="A24" s="3" t="inlineStr">
-        <is>
-          <t>Total Profit (Rs)</t>
-        </is>
-      </c>
-      <c r="B24" s="26" t="n">
-        <v>0</v>
-      </c>
-      <c r="C24" s="23" t="n"/>
-      <c r="D24" s="24" t="n"/>
+      <c r="A24" s="13" t="inlineStr">
+        <is>
+          <t>STATISTICS (all trades for this index)</t>
+        </is>
+      </c>
     </row>
     <row r="25">
       <c r="A25" s="3" t="inlineStr">
         <is>
-          <t>Total Loss (Rs)</t>
-        </is>
-      </c>
-      <c r="B25" s="27" t="n">
-        <v>-1162.41</v>
+          <t>All trades</t>
+        </is>
+      </c>
+      <c r="B25" s="22" t="n">
+        <v>6</v>
       </c>
       <c r="C25" s="23" t="n"/>
       <c r="D25" s="24" t="n"/>
@@ -3436,11 +3465,13 @@
     <row r="26">
       <c r="A26" s="3" t="inlineStr">
         <is>
-          <t>Transaction costs (Rs)</t>
-        </is>
-      </c>
-      <c r="B26" s="28" t="n">
-        <v>236.31</v>
+          <t>Winners</t>
+        </is>
+      </c>
+      <c r="B26" s="25" t="inlineStr">
+        <is>
+          <t>0 (0.0%)</t>
+        </is>
       </c>
       <c r="C26" s="23" t="n"/>
       <c r="D26" s="24" t="n"/>
@@ -3448,11 +3479,13 @@
     <row r="27">
       <c r="A27" s="3" t="inlineStr">
         <is>
-          <t>Avg Profit/Loss per trade (Rs)</t>
-        </is>
-      </c>
-      <c r="B27" s="27" t="n">
-        <v>-232.48</v>
+          <t>Losers</t>
+        </is>
+      </c>
+      <c r="B27" s="25" t="inlineStr">
+        <is>
+          <t>6 (100.0%)</t>
+        </is>
       </c>
       <c r="C27" s="23" t="n"/>
       <c r="D27" s="24" t="n"/>
@@ -3460,11 +3493,11 @@
     <row r="28">
       <c r="A28" s="3" t="inlineStr">
         <is>
-          <t>Avg Profit/Loss per trade (% of premium)</t>
-        </is>
-      </c>
-      <c r="B28" s="29" t="n">
-        <v>-14.84</v>
+          <t>Net P&amp;L (Rs)</t>
+        </is>
+      </c>
+      <c r="B28" s="27" t="n">
+        <v>-1792.63</v>
       </c>
       <c r="C28" s="23" t="n"/>
       <c r="D28" s="24" t="n"/>
@@ -3472,7 +3505,7 @@
     <row r="29">
       <c r="A29" s="3" t="inlineStr">
         <is>
-          <t>Avg Win (Rs)</t>
+          <t>Total Profit (Rs)</t>
         </is>
       </c>
       <c r="B29" s="26" t="n">
@@ -3484,11 +3517,11 @@
     <row r="30">
       <c r="A30" s="3" t="inlineStr">
         <is>
-          <t>Avg Win (% of premium)</t>
-        </is>
-      </c>
-      <c r="B30" s="30" t="n">
-        <v>0</v>
+          <t>Total Loss (Rs)</t>
+        </is>
+      </c>
+      <c r="B30" s="27" t="n">
+        <v>-1792.63</v>
       </c>
       <c r="C30" s="23" t="n"/>
       <c r="D30" s="24" t="n"/>
@@ -3496,11 +3529,11 @@
     <row r="31">
       <c r="A31" s="3" t="inlineStr">
         <is>
-          <t>Avg Loss (Rs)</t>
-        </is>
-      </c>
-      <c r="B31" s="27" t="n">
-        <v>-232.48</v>
+          <t>Transaction costs (Rs)</t>
+        </is>
+      </c>
+      <c r="B31" s="28" t="n">
+        <v>364.63</v>
       </c>
       <c r="C31" s="23" t="n"/>
       <c r="D31" s="24" t="n"/>
@@ -3508,11 +3541,11 @@
     <row r="32">
       <c r="A32" s="3" t="inlineStr">
         <is>
-          <t>Avg Loss (% of premium)</t>
-        </is>
-      </c>
-      <c r="B32" s="31" t="n">
-        <v>-14.84</v>
+          <t>Avg Profit/Loss per trade (Rs)</t>
+        </is>
+      </c>
+      <c r="B32" s="27" t="n">
+        <v>-298.77</v>
       </c>
       <c r="C32" s="23" t="n"/>
       <c r="D32" s="24" t="n"/>
@@ -3520,11 +3553,11 @@
     <row r="33">
       <c r="A33" s="3" t="inlineStr">
         <is>
-          <t>Largest Win (Rs)</t>
-        </is>
-      </c>
-      <c r="B33" s="26" t="n">
-        <v>-197.57</v>
+          <t>Avg Profit/Loss per trade (% of premium)</t>
+        </is>
+      </c>
+      <c r="B33" s="29" t="n">
+        <v>-14.84</v>
       </c>
       <c r="C33" s="23" t="n"/>
       <c r="D33" s="24" t="n"/>
@@ -3532,11 +3565,11 @@
     <row r="34">
       <c r="A34" s="3" t="inlineStr">
         <is>
-          <t>Largest Loss (Rs)</t>
-        </is>
-      </c>
-      <c r="B34" s="27" t="n">
-        <v>-264.8</v>
+          <t>Avg Win (Rs)</t>
+        </is>
+      </c>
+      <c r="B34" s="26" t="n">
+        <v>0</v>
       </c>
       <c r="C34" s="23" t="n"/>
       <c r="D34" s="24" t="n"/>
@@ -3544,10 +3577,10 @@
     <row r="35">
       <c r="A35" s="3" t="inlineStr">
         <is>
-          <t>Max Consecutive Wins</t>
-        </is>
-      </c>
-      <c r="B35" s="22" t="n">
+          <t>Avg Win (% of premium)</t>
+        </is>
+      </c>
+      <c r="B35" s="30" t="n">
         <v>0</v>
       </c>
       <c r="C35" s="23" t="n"/>
@@ -3556,11 +3589,11 @@
     <row r="36">
       <c r="A36" s="3" t="inlineStr">
         <is>
-          <t>Max Consecutive Losses</t>
-        </is>
-      </c>
-      <c r="B36" s="22" t="n">
-        <v>5</v>
+          <t>Avg Loss (Rs)</t>
+        </is>
+      </c>
+      <c r="B36" s="27" t="n">
+        <v>-298.77</v>
       </c>
       <c r="C36" s="23" t="n"/>
       <c r="D36" s="24" t="n"/>
@@ -3568,11 +3601,11 @@
     <row r="37">
       <c r="A37" s="3" t="inlineStr">
         <is>
-          <t>Max trade drawdown (Rs)</t>
-        </is>
-      </c>
-      <c r="B37" s="27" t="n">
-        <v>-264.8</v>
+          <t>Avg Loss (% of premium)</t>
+        </is>
+      </c>
+      <c r="B37" s="31" t="n">
+        <v>-14.84</v>
       </c>
       <c r="C37" s="23" t="n"/>
       <c r="D37" s="24" t="n"/>
@@ -3580,11 +3613,11 @@
     <row r="38">
       <c r="A38" s="3" t="inlineStr">
         <is>
-          <t>Max system drawdown (Rs)</t>
-        </is>
-      </c>
-      <c r="B38" s="27" t="n">
-        <v>-1162.41</v>
+          <t>Largest Win (Rs)</t>
+        </is>
+      </c>
+      <c r="B38" s="26" t="n">
+        <v>-177.91</v>
       </c>
       <c r="C38" s="23" t="n"/>
       <c r="D38" s="24" t="n"/>
@@ -3592,11 +3625,11 @@
     <row r="39">
       <c r="A39" s="3" t="inlineStr">
         <is>
-          <t>Max system drawdown (%)</t>
-        </is>
-      </c>
-      <c r="B39" s="31" t="n">
-        <v>-5.81</v>
+          <t>Largest Loss (Rs)</t>
+        </is>
+      </c>
+      <c r="B39" s="27" t="n">
+        <v>-358.86</v>
       </c>
       <c r="C39" s="23" t="n"/>
       <c r="D39" s="24" t="n"/>
@@ -3604,11 +3637,11 @@
     <row r="40">
       <c r="A40" s="3" t="inlineStr">
         <is>
-          <t>Recovery Factor</t>
-        </is>
-      </c>
-      <c r="B40" s="32" t="n">
-        <v>-1</v>
+          <t>Max Consecutive Wins</t>
+        </is>
+      </c>
+      <c r="B40" s="22" t="n">
+        <v>0</v>
       </c>
       <c r="C40" s="23" t="n"/>
       <c r="D40" s="24" t="n"/>
@@ -3616,11 +3649,11 @@
     <row r="41">
       <c r="A41" s="3" t="inlineStr">
         <is>
-          <t>Profit Factor</t>
-        </is>
-      </c>
-      <c r="B41" s="32" t="n">
-        <v>0</v>
+          <t>Max Consecutive Losses</t>
+        </is>
+      </c>
+      <c r="B41" s="22" t="n">
+        <v>6</v>
       </c>
       <c r="C41" s="23" t="n"/>
       <c r="D41" s="24" t="n"/>
@@ -3628,13 +3661,11 @@
     <row r="42">
       <c r="A42" s="3" t="inlineStr">
         <is>
-          <t>Payoff Ratio (avg win / avg loss)</t>
-        </is>
-      </c>
-      <c r="B42" s="25" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
+          <t>Max trade drawdown (Rs)</t>
+        </is>
+      </c>
+      <c r="B42" s="27" t="n">
+        <v>-358.86</v>
       </c>
       <c r="C42" s="23" t="n"/>
       <c r="D42" s="24" t="n"/>
@@ -3642,17 +3673,79 @@
     <row r="43">
       <c r="A43" s="3" t="inlineStr">
         <is>
-          <t>Sharpe Ratio (annualized)</t>
-        </is>
-      </c>
-      <c r="B43" s="32" t="n">
-        <v>-46.07</v>
+          <t>Max system drawdown (Rs)</t>
+        </is>
+      </c>
+      <c r="B43" s="27" t="n">
+        <v>-1792.63</v>
       </c>
       <c r="C43" s="23" t="n"/>
       <c r="D43" s="24" t="n"/>
     </row>
+    <row r="44">
+      <c r="A44" s="3" t="inlineStr">
+        <is>
+          <t>Max system drawdown (%)</t>
+        </is>
+      </c>
+      <c r="B44" s="31" t="n">
+        <v>-8.960000000000001</v>
+      </c>
+      <c r="C44" s="23" t="n"/>
+      <c r="D44" s="24" t="n"/>
+    </row>
     <row r="45">
-      <c r="A45" s="5" t="inlineStr">
+      <c r="A45" s="3" t="inlineStr">
+        <is>
+          <t>Recovery Factor</t>
+        </is>
+      </c>
+      <c r="B45" s="32" t="n">
+        <v>-1</v>
+      </c>
+      <c r="C45" s="23" t="n"/>
+      <c r="D45" s="24" t="n"/>
+    </row>
+    <row r="46">
+      <c r="A46" s="3" t="inlineStr">
+        <is>
+          <t>Profit Factor</t>
+        </is>
+      </c>
+      <c r="B46" s="32" t="n">
+        <v>0</v>
+      </c>
+      <c r="C46" s="23" t="n"/>
+      <c r="D46" s="24" t="n"/>
+    </row>
+    <row r="47">
+      <c r="A47" s="3" t="inlineStr">
+        <is>
+          <t>Payoff Ratio (avg win / avg loss)</t>
+        </is>
+      </c>
+      <c r="B47" s="25" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="C47" s="23" t="n"/>
+      <c r="D47" s="24" t="n"/>
+    </row>
+    <row r="48">
+      <c r="A48" s="3" t="inlineStr">
+        <is>
+          <t>Sharpe Ratio (annualized)</t>
+        </is>
+      </c>
+      <c r="B48" s="32" t="n">
+        <v>-32.23</v>
+      </c>
+      <c r="C48" s="23" t="n"/>
+      <c r="D48" s="24" t="n"/>
+    </row>
+    <row r="50">
+      <c r="A50" s="5" t="inlineStr">
         <is>
           <t>Caveat: with only a handful of trades these numbers (Sharpe, profit factor, drawdown %) are not statistically reliable. Watch this over weeks/months before drawing conclusions.</t>
         </is>
@@ -3661,7 +3754,7 @@
   </sheetData>
   <mergeCells count="24">
     <mergeCell ref="B42:D42"/>
-    <mergeCell ref="B23:D23"/>
+    <mergeCell ref="B44:D44"/>
     <mergeCell ref="B29:D29"/>
     <mergeCell ref="B38:D38"/>
     <mergeCell ref="B34:D34"/>
@@ -3669,21 +3762,21 @@
     <mergeCell ref="B37:D37"/>
     <mergeCell ref="B40:D40"/>
     <mergeCell ref="B30:D30"/>
-    <mergeCell ref="B24:D24"/>
-    <mergeCell ref="B20:D20"/>
     <mergeCell ref="B33:D33"/>
     <mergeCell ref="B36:D36"/>
+    <mergeCell ref="B45:D45"/>
     <mergeCell ref="B41:D41"/>
     <mergeCell ref="B32:D32"/>
     <mergeCell ref="B35:D35"/>
     <mergeCell ref="B26:D26"/>
     <mergeCell ref="B25:D25"/>
+    <mergeCell ref="B47:D47"/>
     <mergeCell ref="B31:D31"/>
-    <mergeCell ref="B22:D22"/>
+    <mergeCell ref="B46:D46"/>
     <mergeCell ref="B27:D27"/>
-    <mergeCell ref="B21:D21"/>
     <mergeCell ref="B43:D43"/>
     <mergeCell ref="B39:D39"/>
+    <mergeCell ref="B48:D48"/>
   </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
   <pageSetup orientation="landscape" fitToHeight="0" fitToWidth="1"/>
@@ -3696,7 +3789,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
-  <dimension ref="A1:O45"/>
+  <dimension ref="A1:O50"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="40" customWidth="1" min="1" max="1"/>
@@ -3719,7 +3812,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>BACKTEST FINNIFTY -- best: trend_scalp_nw (EMA9/21) [1m] -- PAPER TRADE, NOT REAL MONEY</t>
+          <t>BACKTEST FINNIFTY -- best: trend_scalp_nw (EMA9/26) [5m] -- PAPER TRADE, NOT REAL MONEY</t>
         </is>
       </c>
     </row>
@@ -3809,7 +3902,7 @@
     </row>
     <row r="5">
       <c r="A5" s="3" t="n">
-        <v>2026</v>
+        <v>2025</v>
       </c>
       <c r="B5" s="6" t="n"/>
       <c r="C5" s="6" t="n"/>
@@ -3817,332 +3910,381 @@
       <c r="E5" s="6" t="n"/>
       <c r="F5" s="6" t="n"/>
       <c r="G5" s="6" t="n"/>
-      <c r="H5" s="15" t="n">
-        <v>-0.027176</v>
-      </c>
+      <c r="H5" s="6" t="n"/>
       <c r="I5" s="6" t="n"/>
-      <c r="J5" s="15" t="n">
-        <v>-0.04068053419734711</v>
-      </c>
+      <c r="J5" s="6" t="n"/>
       <c r="K5" s="6" t="n"/>
       <c r="L5" s="6" t="n"/>
-      <c r="M5" s="6" t="n"/>
+      <c r="M5" s="14" t="n">
+        <v>-0.0469125</v>
+      </c>
       <c r="N5" s="18" t="n">
-        <v>-0.06675099999999989</v>
-      </c>
-      <c r="O5" s="21" t="n">
-        <v>-1335.02</v>
+        <v>-0.04691250000000002</v>
+      </c>
+      <c r="O5" s="20" t="n">
+        <v>-938.25</v>
       </c>
     </row>
     <row r="6">
-      <c r="A6" s="3" t="inlineStr">
-        <is>
-          <t>Avg</t>
-        </is>
-      </c>
-      <c r="B6" s="6" t="n"/>
+      <c r="A6" s="3" t="n">
+        <v>2026</v>
+      </c>
+      <c r="B6" s="14" t="n">
+        <v>-0.01505685469592246</v>
+      </c>
       <c r="C6" s="6" t="n"/>
       <c r="D6" s="6" t="n"/>
-      <c r="E6" s="6" t="n"/>
+      <c r="E6" s="15" t="n">
+        <v>0.01262227865738753</v>
+      </c>
       <c r="F6" s="6" t="n"/>
       <c r="G6" s="6" t="n"/>
-      <c r="H6" s="18" t="n">
-        <v>-0.027176</v>
-      </c>
+      <c r="H6" s="6" t="n"/>
       <c r="I6" s="6" t="n"/>
-      <c r="J6" s="18" t="n">
-        <v>-0.04068053419734711</v>
+      <c r="J6" s="14" t="n">
+        <v>-0.01216670559002552</v>
       </c>
       <c r="K6" s="6" t="n"/>
       <c r="L6" s="6" t="n"/>
       <c r="M6" s="6" t="n"/>
-    </row>
-    <row r="8">
-      <c r="A8" s="13" t="inlineStr">
+      <c r="N6" s="18" t="n">
+        <v>-0.01475940036985068</v>
+      </c>
+      <c r="O6" s="20" t="n">
+        <v>-281.34</v>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" s="3" t="inlineStr">
+        <is>
+          <t>Avg</t>
+        </is>
+      </c>
+      <c r="B7" s="18" t="n">
+        <v>-0.01505685469592246</v>
+      </c>
+      <c r="C7" s="6" t="n"/>
+      <c r="D7" s="6" t="n"/>
+      <c r="E7" s="16" t="n">
+        <v>0.01262227865738753</v>
+      </c>
+      <c r="F7" s="6" t="n"/>
+      <c r="G7" s="6" t="n"/>
+      <c r="H7" s="6" t="n"/>
+      <c r="I7" s="6" t="n"/>
+      <c r="J7" s="18" t="n">
+        <v>-0.01216670559002552</v>
+      </c>
+      <c r="K7" s="6" t="n"/>
+      <c r="L7" s="6" t="n"/>
+      <c r="M7" s="18" t="n">
+        <v>-0.0469125</v>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" s="13" t="inlineStr">
         <is>
           <t>WEEKLY returns (% of capital at start of that week; weeks split at month edges)</t>
         </is>
       </c>
     </row>
-    <row r="9">
-      <c r="A9" s="2" t="inlineStr">
+    <row r="10">
+      <c r="A10" s="2" t="inlineStr">
         <is>
           <t>Month</t>
         </is>
       </c>
-      <c r="B9" s="2" t="inlineStr">
+      <c r="B10" s="2" t="inlineStr">
         <is>
           <t>W1</t>
         </is>
       </c>
-      <c r="C9" s="2" t="inlineStr">
+      <c r="C10" s="2" t="inlineStr">
         <is>
           <t>W2</t>
         </is>
       </c>
-      <c r="D9" s="2" t="inlineStr">
+      <c r="D10" s="2" t="inlineStr">
         <is>
           <t>W3</t>
         </is>
       </c>
-      <c r="E9" s="2" t="inlineStr">
+      <c r="E10" s="2" t="inlineStr">
         <is>
           <t>W4</t>
         </is>
       </c>
-      <c r="F9" s="2" t="inlineStr">
+      <c r="F10" s="2" t="inlineStr">
         <is>
           <t>W5</t>
         </is>
       </c>
-      <c r="G9" s="2" t="inlineStr">
+      <c r="G10" s="2" t="inlineStr">
         <is>
           <t>W6</t>
         </is>
       </c>
-      <c r="H9" s="2" t="inlineStr">
+      <c r="H10" s="2" t="inlineStr">
         <is>
           <t>Month %</t>
         </is>
       </c>
-      <c r="I9" s="2" t="inlineStr">
+      <c r="I10" s="2" t="inlineStr">
         <is>
           <t>Month P&amp;L (Rs)</t>
         </is>
-      </c>
-    </row>
-    <row r="10">
-      <c r="A10" s="3" t="inlineStr">
-        <is>
-          <t>2026-Jul</t>
-        </is>
-      </c>
-      <c r="B10" s="15" t="n">
-        <v>-0.027176</v>
-      </c>
-      <c r="C10" s="6" t="n"/>
-      <c r="D10" s="6" t="n"/>
-      <c r="E10" s="6" t="n"/>
-      <c r="F10" s="6" t="n"/>
-      <c r="G10" s="6" t="n"/>
-      <c r="H10" s="20" t="n">
-        <v>-0.027176</v>
-      </c>
-      <c r="I10" s="21" t="n">
-        <v>-543.52</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" s="3" t="inlineStr">
         <is>
-          <t>2026-Sep</t>
-        </is>
-      </c>
-      <c r="B11" s="15" t="n">
-        <v>-0.0163390294647336</v>
-      </c>
-      <c r="C11" s="15" t="n">
-        <v>-0.02474582753788421</v>
+          <t>2025-Dec</t>
+        </is>
+      </c>
+      <c r="B11" s="14" t="n">
+        <v>-0.010346</v>
+      </c>
+      <c r="C11" s="14" t="n">
+        <v>-0.0369487719950609</v>
       </c>
       <c r="D11" s="6" t="n"/>
       <c r="E11" s="6" t="n"/>
       <c r="F11" s="6" t="n"/>
       <c r="G11" s="6" t="n"/>
-      <c r="H11" s="20" t="n">
-        <v>-0.04068053419734711</v>
-      </c>
-      <c r="I11" s="21" t="n">
-        <v>-791.5</v>
+      <c r="H11" s="19" t="n">
+        <v>-0.0469125</v>
+      </c>
+      <c r="I11" s="20" t="n">
+        <v>-938.25</v>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" s="3" t="inlineStr">
+        <is>
+          <t>2026-Jan</t>
+        </is>
+      </c>
+      <c r="B12" s="14" t="n">
+        <v>-0.01505685469592246</v>
+      </c>
+      <c r="C12" s="6" t="n"/>
+      <c r="D12" s="6" t="n"/>
+      <c r="E12" s="6" t="n"/>
+      <c r="F12" s="6" t="n"/>
+      <c r="G12" s="6" t="n"/>
+      <c r="H12" s="19" t="n">
+        <v>-0.01505685469592246</v>
+      </c>
+      <c r="I12" s="20" t="n">
+        <v>-287.01</v>
       </c>
     </row>
     <row r="13">
-      <c r="A13" s="13" t="inlineStr">
+      <c r="A13" s="3" t="inlineStr">
+        <is>
+          <t>2026-Apr</t>
+        </is>
+      </c>
+      <c r="B13" s="15" t="n">
+        <v>0.01262227865738753</v>
+      </c>
+      <c r="C13" s="6" t="n"/>
+      <c r="D13" s="6" t="n"/>
+      <c r="E13" s="6" t="n"/>
+      <c r="F13" s="6" t="n"/>
+      <c r="G13" s="6" t="n"/>
+      <c r="H13" s="21" t="n">
+        <v>0.01262227865738753</v>
+      </c>
+      <c r="I13" s="17" t="n">
+        <v>236.98</v>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" s="3" t="inlineStr">
+        <is>
+          <t>2026-Sep</t>
+        </is>
+      </c>
+      <c r="B14" s="14" t="n">
+        <v>-0.01216670559002552</v>
+      </c>
+      <c r="C14" s="6" t="n"/>
+      <c r="D14" s="6" t="n"/>
+      <c r="E14" s="6" t="n"/>
+      <c r="F14" s="6" t="n"/>
+      <c r="G14" s="6" t="n"/>
+      <c r="H14" s="19" t="n">
+        <v>-0.01216670559002552</v>
+      </c>
+      <c r="I14" s="20" t="n">
+        <v>-231.31</v>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" s="13" t="inlineStr">
         <is>
           <t>DAILY returns (% of capital at start of that day; blank = no trade that day)</t>
         </is>
       </c>
     </row>
-    <row r="14">
-      <c r="A14" s="2" t="inlineStr">
+    <row r="17">
+      <c r="A17" s="2" t="inlineStr">
         <is>
           <t>Week starting (Mon)</t>
         </is>
       </c>
-      <c r="B14" s="2" t="inlineStr">
+      <c r="B17" s="2" t="inlineStr">
         <is>
           <t>Mon</t>
         </is>
       </c>
-      <c r="C14" s="2" t="inlineStr">
+      <c r="C17" s="2" t="inlineStr">
         <is>
           <t>Tue</t>
         </is>
       </c>
-      <c r="D14" s="2" t="inlineStr">
+      <c r="D17" s="2" t="inlineStr">
         <is>
           <t>Wed</t>
         </is>
       </c>
-      <c r="E14" s="2" t="inlineStr">
+      <c r="E17" s="2" t="inlineStr">
         <is>
           <t>Thu</t>
         </is>
       </c>
-      <c r="F14" s="2" t="inlineStr">
+      <c r="F17" s="2" t="inlineStr">
         <is>
           <t>Fri</t>
         </is>
       </c>
-      <c r="G14" s="2" t="inlineStr">
+      <c r="G17" s="2" t="inlineStr">
         <is>
           <t>Week %</t>
         </is>
       </c>
-      <c r="H14" s="2" t="inlineStr">
+      <c r="H17" s="2" t="inlineStr">
         <is>
           <t>Week P&amp;L (Rs)</t>
         </is>
       </c>
     </row>
-    <row r="15">
-      <c r="A15" s="3" t="inlineStr">
-        <is>
-          <t>13-Jul-2026</t>
-        </is>
-      </c>
-      <c r="B15" s="6" t="n"/>
-      <c r="C15" s="15" t="n">
-        <v>-0.027176</v>
-      </c>
-      <c r="D15" s="6" t="n"/>
-      <c r="E15" s="6" t="n"/>
-      <c r="F15" s="6" t="n"/>
-      <c r="G15" s="20" t="n">
-        <v>-0.027176</v>
-      </c>
-      <c r="H15" s="21" t="n">
-        <v>-543.52</v>
-      </c>
-    </row>
-    <row r="16">
-      <c r="A16" s="3" t="inlineStr">
-        <is>
-          <t>07-Sep-2026</t>
-        </is>
-      </c>
-      <c r="B16" s="6" t="n"/>
-      <c r="C16" s="15" t="n">
-        <v>-0.0163390294647336</v>
-      </c>
-      <c r="D16" s="6" t="n"/>
-      <c r="E16" s="6" t="n"/>
-      <c r="F16" s="6" t="n"/>
-      <c r="G16" s="20" t="n">
-        <v>-0.0163390294647336</v>
-      </c>
-      <c r="H16" s="21" t="n">
-        <v>-317.9</v>
-      </c>
-    </row>
-    <row r="17">
-      <c r="A17" s="3" t="inlineStr">
-        <is>
-          <t>28-Sep-2026</t>
-        </is>
-      </c>
-      <c r="B17" s="6" t="n"/>
-      <c r="C17" s="15" t="n">
-        <v>-0.02474582753788421</v>
-      </c>
-      <c r="D17" s="6" t="n"/>
-      <c r="E17" s="6" t="n"/>
-      <c r="F17" s="6" t="n"/>
-      <c r="G17" s="20" t="n">
-        <v>-0.02474582753788421</v>
-      </c>
-      <c r="H17" s="21" t="n">
-        <v>-473.6</v>
+    <row r="18">
+      <c r="A18" s="3" t="inlineStr">
+        <is>
+          <t>01-Dec-2025</t>
+        </is>
+      </c>
+      <c r="B18" s="6" t="n"/>
+      <c r="C18" s="14" t="n">
+        <v>-0.010346</v>
+      </c>
+      <c r="D18" s="6" t="n"/>
+      <c r="E18" s="6" t="n"/>
+      <c r="F18" s="6" t="n"/>
+      <c r="G18" s="19" t="n">
+        <v>-0.010346</v>
+      </c>
+      <c r="H18" s="20" t="n">
+        <v>-206.92</v>
       </c>
     </row>
     <row r="19">
-      <c r="A19" s="13" t="inlineStr">
-        <is>
-          <t>STATISTICS (all trades for this index)</t>
-        </is>
+      <c r="A19" s="3" t="inlineStr">
+        <is>
+          <t>08-Dec-2025</t>
+        </is>
+      </c>
+      <c r="B19" s="6" t="n"/>
+      <c r="C19" s="14" t="n">
+        <v>-0.0369487719950609</v>
+      </c>
+      <c r="D19" s="6" t="n"/>
+      <c r="E19" s="6" t="n"/>
+      <c r="F19" s="6" t="n"/>
+      <c r="G19" s="19" t="n">
+        <v>-0.0369487719950609</v>
+      </c>
+      <c r="H19" s="20" t="n">
+        <v>-731.33</v>
       </c>
     </row>
     <row r="20">
       <c r="A20" s="3" t="inlineStr">
         <is>
-          <t>All trades</t>
-        </is>
-      </c>
-      <c r="B20" s="22" t="n">
-        <v>5</v>
-      </c>
-      <c r="C20" s="23" t="n"/>
-      <c r="D20" s="24" t="n"/>
+          <t>26-Jan-2026</t>
+        </is>
+      </c>
+      <c r="B20" s="6" t="n"/>
+      <c r="C20" s="14" t="n">
+        <v>-0.01505685469592246</v>
+      </c>
+      <c r="D20" s="6" t="n"/>
+      <c r="E20" s="6" t="n"/>
+      <c r="F20" s="6" t="n"/>
+      <c r="G20" s="19" t="n">
+        <v>-0.01505685469592246</v>
+      </c>
+      <c r="H20" s="20" t="n">
+        <v>-287.01</v>
+      </c>
     </row>
     <row r="21">
       <c r="A21" s="3" t="inlineStr">
         <is>
-          <t>Winners</t>
-        </is>
-      </c>
-      <c r="B21" s="25" t="inlineStr">
-        <is>
-          <t>0 (0.0%)</t>
-        </is>
-      </c>
-      <c r="C21" s="23" t="n"/>
-      <c r="D21" s="24" t="n"/>
+          <t>06-Apr-2026</t>
+        </is>
+      </c>
+      <c r="B21" s="6" t="n"/>
+      <c r="C21" s="15" t="n">
+        <v>0.01262227865738753</v>
+      </c>
+      <c r="D21" s="6" t="n"/>
+      <c r="E21" s="6" t="n"/>
+      <c r="F21" s="6" t="n"/>
+      <c r="G21" s="21" t="n">
+        <v>0.01262227865738753</v>
+      </c>
+      <c r="H21" s="17" t="n">
+        <v>236.98</v>
+      </c>
     </row>
     <row r="22">
       <c r="A22" s="3" t="inlineStr">
         <is>
-          <t>Losers</t>
-        </is>
-      </c>
-      <c r="B22" s="25" t="inlineStr">
-        <is>
-          <t>5 (100.0%)</t>
-        </is>
-      </c>
-      <c r="C22" s="23" t="n"/>
-      <c r="D22" s="24" t="n"/>
-    </row>
-    <row r="23">
-      <c r="A23" s="3" t="inlineStr">
-        <is>
-          <t>Net P&amp;L (Rs)</t>
-        </is>
-      </c>
-      <c r="B23" s="27" t="n">
-        <v>-1335.02</v>
-      </c>
-      <c r="C23" s="23" t="n"/>
-      <c r="D23" s="24" t="n"/>
+          <t>07-Sep-2026</t>
+        </is>
+      </c>
+      <c r="B22" s="6" t="n"/>
+      <c r="C22" s="14" t="n">
+        <v>-0.01216670559002552</v>
+      </c>
+      <c r="D22" s="6" t="n"/>
+      <c r="E22" s="6" t="n"/>
+      <c r="F22" s="6" t="n"/>
+      <c r="G22" s="19" t="n">
+        <v>-0.01216670559002552</v>
+      </c>
+      <c r="H22" s="20" t="n">
+        <v>-231.31</v>
+      </c>
     </row>
     <row r="24">
-      <c r="A24" s="3" t="inlineStr">
-        <is>
-          <t>Total Profit (Rs)</t>
-        </is>
-      </c>
-      <c r="B24" s="26" t="n">
-        <v>0</v>
-      </c>
-      <c r="C24" s="23" t="n"/>
-      <c r="D24" s="24" t="n"/>
+      <c r="A24" s="13" t="inlineStr">
+        <is>
+          <t>STATISTICS (all trades for this index)</t>
+        </is>
+      </c>
     </row>
     <row r="25">
       <c r="A25" s="3" t="inlineStr">
         <is>
-          <t>Total Loss (Rs)</t>
-        </is>
-      </c>
-      <c r="B25" s="27" t="n">
-        <v>-1335.02</v>
+          <t>All trades</t>
+        </is>
+      </c>
+      <c r="B25" s="22" t="n">
+        <v>7</v>
       </c>
       <c r="C25" s="23" t="n"/>
       <c r="D25" s="24" t="n"/>
@@ -4150,11 +4292,13 @@
     <row r="26">
       <c r="A26" s="3" t="inlineStr">
         <is>
-          <t>Transaction costs (Rs)</t>
-        </is>
-      </c>
-      <c r="B26" s="28" t="n">
-        <v>271.02</v>
+          <t>Winners</t>
+        </is>
+      </c>
+      <c r="B26" s="25" t="inlineStr">
+        <is>
+          <t>1 (14.3%)</t>
+        </is>
       </c>
       <c r="C26" s="23" t="n"/>
       <c r="D26" s="24" t="n"/>
@@ -4162,11 +4306,13 @@
     <row r="27">
       <c r="A27" s="3" t="inlineStr">
         <is>
-          <t>Avg Profit/Loss per trade (Rs)</t>
-        </is>
-      </c>
-      <c r="B27" s="27" t="n">
-        <v>-267</v>
+          <t>Losers</t>
+        </is>
+      </c>
+      <c r="B27" s="25" t="inlineStr">
+        <is>
+          <t>6 (85.7%)</t>
+        </is>
       </c>
       <c r="C27" s="23" t="n"/>
       <c r="D27" s="24" t="n"/>
@@ -4174,11 +4320,11 @@
     <row r="28">
       <c r="A28" s="3" t="inlineStr">
         <is>
-          <t>Avg Profit/Loss per trade (% of premium)</t>
-        </is>
-      </c>
-      <c r="B28" s="29" t="n">
-        <v>-14.84</v>
+          <t>Net P&amp;L (Rs)</t>
+        </is>
+      </c>
+      <c r="B28" s="27" t="n">
+        <v>-1219.59</v>
       </c>
       <c r="C28" s="23" t="n"/>
       <c r="D28" s="24" t="n"/>
@@ -4186,11 +4332,11 @@
     <row r="29">
       <c r="A29" s="3" t="inlineStr">
         <is>
-          <t>Avg Win (Rs)</t>
+          <t>Total Profit (Rs)</t>
         </is>
       </c>
       <c r="B29" s="26" t="n">
-        <v>0</v>
+        <v>236.98</v>
       </c>
       <c r="C29" s="23" t="n"/>
       <c r="D29" s="24" t="n"/>
@@ -4198,11 +4344,11 @@
     <row r="30">
       <c r="A30" s="3" t="inlineStr">
         <is>
-          <t>Avg Win (% of premium)</t>
-        </is>
-      </c>
-      <c r="B30" s="30" t="n">
-        <v>0</v>
+          <t>Total Loss (Rs)</t>
+        </is>
+      </c>
+      <c r="B30" s="27" t="n">
+        <v>-1456.57</v>
       </c>
       <c r="C30" s="23" t="n"/>
       <c r="D30" s="24" t="n"/>
@@ -4210,11 +4356,11 @@
     <row r="31">
       <c r="A31" s="3" t="inlineStr">
         <is>
-          <t>Avg Loss (Rs)</t>
-        </is>
-      </c>
-      <c r="B31" s="27" t="n">
-        <v>-267</v>
+          <t>Transaction costs (Rs)</t>
+        </is>
+      </c>
+      <c r="B31" s="28" t="n">
+        <v>348.39</v>
       </c>
       <c r="C31" s="23" t="n"/>
       <c r="D31" s="24" t="n"/>
@@ -4222,11 +4368,11 @@
     <row r="32">
       <c r="A32" s="3" t="inlineStr">
         <is>
-          <t>Avg Loss (% of premium)</t>
-        </is>
-      </c>
-      <c r="B32" s="31" t="n">
-        <v>-14.84</v>
+          <t>Avg Profit/Loss per trade (Rs)</t>
+        </is>
+      </c>
+      <c r="B32" s="27" t="n">
+        <v>-174.23</v>
       </c>
       <c r="C32" s="23" t="n"/>
       <c r="D32" s="24" t="n"/>
@@ -4234,11 +4380,11 @@
     <row r="33">
       <c r="A33" s="3" t="inlineStr">
         <is>
-          <t>Largest Win (Rs)</t>
-        </is>
-      </c>
-      <c r="B33" s="26" t="n">
-        <v>-216.68</v>
+          <t>Avg Profit/Loss per trade (% of premium)</t>
+        </is>
+      </c>
+      <c r="B33" s="29" t="n">
+        <v>-10.42</v>
       </c>
       <c r="C33" s="23" t="n"/>
       <c r="D33" s="24" t="n"/>
@@ -4246,11 +4392,11 @@
     <row r="34">
       <c r="A34" s="3" t="inlineStr">
         <is>
-          <t>Largest Loss (Rs)</t>
-        </is>
-      </c>
-      <c r="B34" s="27" t="n">
-        <v>-317.9</v>
+          <t>Avg Win (Rs)</t>
+        </is>
+      </c>
+      <c r="B34" s="26" t="n">
+        <v>236.98</v>
       </c>
       <c r="C34" s="23" t="n"/>
       <c r="D34" s="24" t="n"/>
@@ -4258,11 +4404,11 @@
     <row r="35">
       <c r="A35" s="3" t="inlineStr">
         <is>
-          <t>Max Consecutive Wins</t>
-        </is>
-      </c>
-      <c r="B35" s="22" t="n">
-        <v>0</v>
+          <t>Avg Win (% of premium)</t>
+        </is>
+      </c>
+      <c r="B35" s="30" t="n">
+        <v>16.17</v>
       </c>
       <c r="C35" s="23" t="n"/>
       <c r="D35" s="24" t="n"/>
@@ -4270,11 +4416,11 @@
     <row r="36">
       <c r="A36" s="3" t="inlineStr">
         <is>
-          <t>Max Consecutive Losses</t>
-        </is>
-      </c>
-      <c r="B36" s="22" t="n">
-        <v>5</v>
+          <t>Avg Loss (Rs)</t>
+        </is>
+      </c>
+      <c r="B36" s="27" t="n">
+        <v>-242.76</v>
       </c>
       <c r="C36" s="23" t="n"/>
       <c r="D36" s="24" t="n"/>
@@ -4282,11 +4428,11 @@
     <row r="37">
       <c r="A37" s="3" t="inlineStr">
         <is>
-          <t>Max trade drawdown (Rs)</t>
-        </is>
-      </c>
-      <c r="B37" s="27" t="n">
-        <v>-317.9</v>
+          <t>Avg Loss (% of premium)</t>
+        </is>
+      </c>
+      <c r="B37" s="31" t="n">
+        <v>-14.85</v>
       </c>
       <c r="C37" s="23" t="n"/>
       <c r="D37" s="24" t="n"/>
@@ -4294,11 +4440,11 @@
     <row r="38">
       <c r="A38" s="3" t="inlineStr">
         <is>
-          <t>Max system drawdown (Rs)</t>
-        </is>
-      </c>
-      <c r="B38" s="27" t="n">
-        <v>-1335.02</v>
+          <t>Largest Win (Rs)</t>
+        </is>
+      </c>
+      <c r="B38" s="26" t="n">
+        <v>236.98</v>
       </c>
       <c r="C38" s="23" t="n"/>
       <c r="D38" s="24" t="n"/>
@@ -4306,11 +4452,11 @@
     <row r="39">
       <c r="A39" s="3" t="inlineStr">
         <is>
-          <t>Max system drawdown (%)</t>
-        </is>
-      </c>
-      <c r="B39" s="31" t="n">
-        <v>-6.68</v>
+          <t>Largest Loss (Rs)</t>
+        </is>
+      </c>
+      <c r="B39" s="27" t="n">
+        <v>-295.95</v>
       </c>
       <c r="C39" s="23" t="n"/>
       <c r="D39" s="24" t="n"/>
@@ -4318,11 +4464,11 @@
     <row r="40">
       <c r="A40" s="3" t="inlineStr">
         <is>
-          <t>Recovery Factor</t>
-        </is>
-      </c>
-      <c r="B40" s="32" t="n">
-        <v>-1</v>
+          <t>Max Consecutive Wins</t>
+        </is>
+      </c>
+      <c r="B40" s="22" t="n">
+        <v>1</v>
       </c>
       <c r="C40" s="23" t="n"/>
       <c r="D40" s="24" t="n"/>
@@ -4330,11 +4476,11 @@
     <row r="41">
       <c r="A41" s="3" t="inlineStr">
         <is>
-          <t>Profit Factor</t>
-        </is>
-      </c>
-      <c r="B41" s="32" t="n">
-        <v>0</v>
+          <t>Max Consecutive Losses</t>
+        </is>
+      </c>
+      <c r="B41" s="22" t="n">
+        <v>5</v>
       </c>
       <c r="C41" s="23" t="n"/>
       <c r="D41" s="24" t="n"/>
@@ -4342,13 +4488,11 @@
     <row r="42">
       <c r="A42" s="3" t="inlineStr">
         <is>
-          <t>Payoff Ratio (avg win / avg loss)</t>
-        </is>
-      </c>
-      <c r="B42" s="25" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
+          <t>Max trade drawdown (Rs)</t>
+        </is>
+      </c>
+      <c r="B42" s="27" t="n">
+        <v>-295.95</v>
       </c>
       <c r="C42" s="23" t="n"/>
       <c r="D42" s="24" t="n"/>
@@ -4356,17 +4500,77 @@
     <row r="43">
       <c r="A43" s="3" t="inlineStr">
         <is>
-          <t>Sharpe Ratio (annualized)</t>
-        </is>
-      </c>
-      <c r="B43" s="32" t="n">
-        <v>-77.79000000000001</v>
+          <t>Max system drawdown (Rs)</t>
+        </is>
+      </c>
+      <c r="B43" s="27" t="n">
+        <v>-1225.26</v>
       </c>
       <c r="C43" s="23" t="n"/>
       <c r="D43" s="24" t="n"/>
     </row>
+    <row r="44">
+      <c r="A44" s="3" t="inlineStr">
+        <is>
+          <t>Max system drawdown (%)</t>
+        </is>
+      </c>
+      <c r="B44" s="31" t="n">
+        <v>-6.13</v>
+      </c>
+      <c r="C44" s="23" t="n"/>
+      <c r="D44" s="24" t="n"/>
+    </row>
     <row r="45">
-      <c r="A45" s="5" t="inlineStr">
+      <c r="A45" s="3" t="inlineStr">
+        <is>
+          <t>Recovery Factor</t>
+        </is>
+      </c>
+      <c r="B45" s="32" t="n">
+        <v>-1</v>
+      </c>
+      <c r="C45" s="23" t="n"/>
+      <c r="D45" s="24" t="n"/>
+    </row>
+    <row r="46">
+      <c r="A46" s="3" t="inlineStr">
+        <is>
+          <t>Profit Factor</t>
+        </is>
+      </c>
+      <c r="B46" s="32" t="n">
+        <v>0.16</v>
+      </c>
+      <c r="C46" s="23" t="n"/>
+      <c r="D46" s="24" t="n"/>
+    </row>
+    <row r="47">
+      <c r="A47" s="3" t="inlineStr">
+        <is>
+          <t>Payoff Ratio (avg win / avg loss)</t>
+        </is>
+      </c>
+      <c r="B47" s="32" t="n">
+        <v>0.98</v>
+      </c>
+      <c r="C47" s="23" t="n"/>
+      <c r="D47" s="24" t="n"/>
+    </row>
+    <row r="48">
+      <c r="A48" s="3" t="inlineStr">
+        <is>
+          <t>Sharpe Ratio (annualized)</t>
+        </is>
+      </c>
+      <c r="B48" s="32" t="n">
+        <v>-12.48</v>
+      </c>
+      <c r="C48" s="23" t="n"/>
+      <c r="D48" s="24" t="n"/>
+    </row>
+    <row r="50">
+      <c r="A50" s="5" t="inlineStr">
         <is>
           <t>Caveat: with only a handful of trades these numbers (Sharpe, profit factor, drawdown %) are not statistically reliable. Watch this over weeks/months before drawing conclusions.</t>
         </is>
@@ -4375,7 +4579,7 @@
   </sheetData>
   <mergeCells count="24">
     <mergeCell ref="B42:D42"/>
-    <mergeCell ref="B23:D23"/>
+    <mergeCell ref="B44:D44"/>
     <mergeCell ref="B29:D29"/>
     <mergeCell ref="B38:D38"/>
     <mergeCell ref="B34:D34"/>
@@ -4383,21 +4587,21 @@
     <mergeCell ref="B37:D37"/>
     <mergeCell ref="B40:D40"/>
     <mergeCell ref="B30:D30"/>
-    <mergeCell ref="B24:D24"/>
-    <mergeCell ref="B20:D20"/>
     <mergeCell ref="B33:D33"/>
     <mergeCell ref="B36:D36"/>
+    <mergeCell ref="B45:D45"/>
     <mergeCell ref="B41:D41"/>
     <mergeCell ref="B32:D32"/>
     <mergeCell ref="B35:D35"/>
     <mergeCell ref="B26:D26"/>
     <mergeCell ref="B25:D25"/>
+    <mergeCell ref="B47:D47"/>
     <mergeCell ref="B31:D31"/>
-    <mergeCell ref="B22:D22"/>
+    <mergeCell ref="B46:D46"/>
     <mergeCell ref="B27:D27"/>
-    <mergeCell ref="B21:D21"/>
     <mergeCell ref="B43:D43"/>
     <mergeCell ref="B39:D39"/>
+    <mergeCell ref="B48:D48"/>
   </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
   <pageSetup orientation="landscape" fitToHeight="0" fitToWidth="1"/>

--- a/reports/dashboard.xlsx
+++ b/reports/dashboard.xlsx
@@ -811,7 +811,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
-  <dimension ref="A1:O60"/>
+  <dimension ref="A1:O54"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="40" customWidth="1" min="1" max="1"/>
@@ -938,13 +938,13 @@
       <c r="K5" s="6" t="n"/>
       <c r="L5" s="6" t="n"/>
       <c r="M5" s="14" t="n">
-        <v>-0.082417</v>
+        <v>-0.0355045</v>
       </c>
       <c r="N5" s="18" t="n">
-        <v>-0.08241699999999996</v>
+        <v>-0.03550450000000005</v>
       </c>
       <c r="O5" s="20" t="n">
-        <v>-1648.34</v>
+        <v>-710.09</v>
       </c>
     </row>
     <row r="6">
@@ -952,36 +952,32 @@
         <v>2026</v>
       </c>
       <c r="B6" s="14" t="n">
-        <v>-0.03399801434856575</v>
+        <v>-0.01746560766742821</v>
       </c>
       <c r="C6" s="6" t="n"/>
       <c r="D6" s="14" t="n">
-        <v>-0.004249836696612201</v>
-      </c>
-      <c r="E6" s="15" t="n">
-        <v>0.01342480342616302</v>
-      </c>
+        <v>-0.00397509629082467</v>
+      </c>
+      <c r="E6" s="6" t="n"/>
       <c r="F6" s="15" t="n">
-        <v>0.03063325839129137</v>
+        <v>0.02902955133210366</v>
       </c>
       <c r="G6" s="6" t="n"/>
       <c r="H6" s="6" t="n"/>
       <c r="I6" s="14" t="n">
-        <v>-0.03079177692721151</v>
-      </c>
-      <c r="J6" s="14" t="n">
-        <v>-0.01294427932916501</v>
-      </c>
+        <v>-0.02922524679972429</v>
+      </c>
+      <c r="J6" s="6" t="n"/>
       <c r="K6" s="14" t="n">
-        <v>-0.02117146945634402</v>
+        <v>-0.01980225846393696</v>
       </c>
       <c r="L6" s="6" t="n"/>
       <c r="M6" s="6" t="n"/>
       <c r="N6" s="18" t="n">
-        <v>-0.05921698636526596</v>
+        <v>-0.04175187960959892</v>
       </c>
       <c r="O6" s="20" t="n">
-        <v>-1086.73</v>
+        <v>-805.39</v>
       </c>
     </row>
     <row r="7">
@@ -991,32 +987,28 @@
         </is>
       </c>
       <c r="B7" s="18" t="n">
-        <v>-0.03399801434856575</v>
+        <v>-0.01746560766742821</v>
       </c>
       <c r="C7" s="6" t="n"/>
       <c r="D7" s="18" t="n">
-        <v>-0.004249836696612201</v>
-      </c>
-      <c r="E7" s="16" t="n">
-        <v>0.01342480342616302</v>
-      </c>
+        <v>-0.00397509629082467</v>
+      </c>
+      <c r="E7" s="6" t="n"/>
       <c r="F7" s="16" t="n">
-        <v>0.03063325839129137</v>
+        <v>0.02902955133210366</v>
       </c>
       <c r="G7" s="6" t="n"/>
       <c r="H7" s="6" t="n"/>
       <c r="I7" s="18" t="n">
-        <v>-0.03079177692721151</v>
-      </c>
-      <c r="J7" s="18" t="n">
-        <v>-0.01294427932916501</v>
-      </c>
+        <v>-0.02922524679972429</v>
+      </c>
+      <c r="J7" s="6" t="n"/>
       <c r="K7" s="18" t="n">
-        <v>-0.02117146945634402</v>
+        <v>-0.01980225846393696</v>
       </c>
       <c r="L7" s="6" t="n"/>
       <c r="M7" s="18" t="n">
-        <v>-0.082417</v>
+        <v>-0.0355045</v>
       </c>
     </row>
     <row r="9">
@@ -1080,22 +1072,18 @@
         </is>
       </c>
       <c r="B11" s="14" t="n">
-        <v>-0.010346</v>
-      </c>
-      <c r="C11" s="14" t="n">
-        <v>-0.0369487719950609</v>
-      </c>
-      <c r="D11" s="14" t="n">
-        <v>-0.03725208860676486</v>
-      </c>
+        <v>-0.0355045</v>
+      </c>
+      <c r="C11" s="6" t="n"/>
+      <c r="D11" s="6" t="n"/>
       <c r="E11" s="6" t="n"/>
       <c r="F11" s="6" t="n"/>
       <c r="G11" s="6" t="n"/>
       <c r="H11" s="19" t="n">
-        <v>-0.082417</v>
+        <v>-0.0355045</v>
       </c>
       <c r="I11" s="20" t="n">
-        <v>-1648.34</v>
+        <v>-710.09</v>
       </c>
     </row>
     <row r="12">
@@ -1105,7 +1093,7 @@
         </is>
       </c>
       <c r="B12" s="14" t="n">
-        <v>-0.03399801434856575</v>
+        <v>-0.01746560766742821</v>
       </c>
       <c r="C12" s="6" t="n"/>
       <c r="D12" s="6" t="n"/>
@@ -1113,10 +1101,10 @@
       <c r="F12" s="6" t="n"/>
       <c r="G12" s="6" t="n"/>
       <c r="H12" s="19" t="n">
-        <v>-0.03399801434856575</v>
+        <v>-0.01746560766742821</v>
       </c>
       <c r="I12" s="20" t="n">
-        <v>-623.92</v>
+        <v>-336.91</v>
       </c>
     </row>
     <row r="13">
@@ -1126,7 +1114,7 @@
         </is>
       </c>
       <c r="B13" s="14" t="n">
-        <v>-0.004249836696612201</v>
+        <v>-0.00397509629082467</v>
       </c>
       <c r="C13" s="6" t="n"/>
       <c r="D13" s="6" t="n"/>
@@ -1134,7 +1122,7 @@
       <c r="F13" s="6" t="n"/>
       <c r="G13" s="6" t="n"/>
       <c r="H13" s="19" t="n">
-        <v>-0.004249836696612201</v>
+        <v>-0.00397509629082467</v>
       </c>
       <c r="I13" s="20" t="n">
         <v>-75.34</v>
@@ -1143,11 +1131,11 @@
     <row r="14">
       <c r="A14" s="3" t="inlineStr">
         <is>
-          <t>2026-Apr</t>
+          <t>2026-May</t>
         </is>
       </c>
       <c r="B14" s="15" t="n">
-        <v>0.01342480342616302</v>
+        <v>0.02902955133210366</v>
       </c>
       <c r="C14" s="6" t="n"/>
       <c r="D14" s="6" t="n"/>
@@ -1155,382 +1143,336 @@
       <c r="F14" s="6" t="n"/>
       <c r="G14" s="6" t="n"/>
       <c r="H14" s="21" t="n">
-        <v>0.01342480342616302</v>
+        <v>0.02902955133210366</v>
       </c>
       <c r="I14" s="17" t="n">
-        <v>236.98</v>
+        <v>548.01</v>
       </c>
     </row>
     <row r="15">
       <c r="A15" s="3" t="inlineStr">
         <is>
-          <t>2026-May</t>
-        </is>
-      </c>
-      <c r="B15" s="15" t="n">
-        <v>0.03063325839129137</v>
-      </c>
-      <c r="C15" s="6" t="n"/>
+          <t>2026-Aug</t>
+        </is>
+      </c>
+      <c r="B15" s="14" t="n">
+        <v>-0.01826964012052094</v>
+      </c>
+      <c r="C15" s="14" t="n">
+        <v>-0.01115948648114366</v>
+      </c>
       <c r="D15" s="6" t="n"/>
       <c r="E15" s="6" t="n"/>
       <c r="F15" s="6" t="n"/>
       <c r="G15" s="6" t="n"/>
-      <c r="H15" s="21" t="n">
-        <v>0.03063325839129137</v>
-      </c>
-      <c r="I15" s="17" t="n">
-        <v>548.01</v>
+      <c r="H15" s="19" t="n">
+        <v>-0.02922524679972429</v>
+      </c>
+      <c r="I15" s="20" t="n">
+        <v>-567.72</v>
       </c>
     </row>
     <row r="16">
       <c r="A16" s="3" t="inlineStr">
         <is>
-          <t>2026-Aug</t>
+          <t>2026-Oct</t>
         </is>
       </c>
       <c r="B16" s="14" t="n">
-        <v>-0.01924892840038639</v>
-      </c>
-      <c r="C16" s="14" t="n">
-        <v>-0.01176939680320576</v>
-      </c>
+        <v>-0.01980225846393696</v>
+      </c>
+      <c r="C16" s="6" t="n"/>
       <c r="D16" s="6" t="n"/>
       <c r="E16" s="6" t="n"/>
       <c r="F16" s="6" t="n"/>
       <c r="G16" s="6" t="n"/>
       <c r="H16" s="19" t="n">
-        <v>-0.03079177692721151</v>
+        <v>-0.01980225846393696</v>
       </c>
       <c r="I16" s="20" t="n">
-        <v>-567.72</v>
-      </c>
-    </row>
-    <row r="17">
-      <c r="A17" s="3" t="inlineStr">
-        <is>
-          <t>2026-Sep</t>
-        </is>
-      </c>
-      <c r="B17" s="14" t="n">
-        <v>-0.01294427932916501</v>
-      </c>
-      <c r="C17" s="6" t="n"/>
-      <c r="D17" s="6" t="n"/>
-      <c r="E17" s="6" t="n"/>
-      <c r="F17" s="6" t="n"/>
-      <c r="G17" s="6" t="n"/>
-      <c r="H17" s="19" t="n">
-        <v>-0.01294427932916501</v>
-      </c>
-      <c r="I17" s="20" t="n">
-        <v>-231.31</v>
+        <v>-373.43</v>
       </c>
     </row>
     <row r="18">
-      <c r="A18" s="3" t="inlineStr">
-        <is>
-          <t>2026-Oct</t>
-        </is>
-      </c>
-      <c r="B18" s="14" t="n">
-        <v>-0.02117146945634402</v>
-      </c>
-      <c r="C18" s="6" t="n"/>
-      <c r="D18" s="6" t="n"/>
-      <c r="E18" s="6" t="n"/>
-      <c r="F18" s="6" t="n"/>
-      <c r="G18" s="6" t="n"/>
-      <c r="H18" s="19" t="n">
-        <v>-0.02117146945634402</v>
-      </c>
-      <c r="I18" s="20" t="n">
-        <v>-373.43</v>
+      <c r="A18" s="13" t="inlineStr">
+        <is>
+          <t>DAILY returns (% of capital at start of that day; blank = no trade that day)</t>
+        </is>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" s="2" t="inlineStr">
+        <is>
+          <t>Week starting (Mon)</t>
+        </is>
+      </c>
+      <c r="B19" s="2" t="inlineStr">
+        <is>
+          <t>Mon</t>
+        </is>
+      </c>
+      <c r="C19" s="2" t="inlineStr">
+        <is>
+          <t>Tue</t>
+        </is>
+      </c>
+      <c r="D19" s="2" t="inlineStr">
+        <is>
+          <t>Wed</t>
+        </is>
+      </c>
+      <c r="E19" s="2" t="inlineStr">
+        <is>
+          <t>Thu</t>
+        </is>
+      </c>
+      <c r="F19" s="2" t="inlineStr">
+        <is>
+          <t>Fri</t>
+        </is>
+      </c>
+      <c r="G19" s="2" t="inlineStr">
+        <is>
+          <t>Week %</t>
+        </is>
+      </c>
+      <c r="H19" s="2" t="inlineStr">
+        <is>
+          <t>Week P&amp;L (Rs)</t>
+        </is>
       </c>
     </row>
     <row r="20">
-      <c r="A20" s="13" t="inlineStr">
-        <is>
-          <t>DAILY returns (% of capital at start of that day; blank = no trade that day)</t>
-        </is>
+      <c r="A20" s="3" t="inlineStr">
+        <is>
+          <t>29-Dec-2025</t>
+        </is>
+      </c>
+      <c r="B20" s="6" t="n"/>
+      <c r="C20" s="14" t="n">
+        <v>-0.0355045</v>
+      </c>
+      <c r="D20" s="6" t="n"/>
+      <c r="E20" s="6" t="n"/>
+      <c r="F20" s="6" t="n"/>
+      <c r="G20" s="19" t="n">
+        <v>-0.0355045</v>
+      </c>
+      <c r="H20" s="20" t="n">
+        <v>-710.09</v>
       </c>
     </row>
     <row r="21">
-      <c r="A21" s="2" t="inlineStr">
-        <is>
-          <t>Week starting (Mon)</t>
-        </is>
-      </c>
-      <c r="B21" s="2" t="inlineStr">
-        <is>
-          <t>Mon</t>
-        </is>
-      </c>
-      <c r="C21" s="2" t="inlineStr">
-        <is>
-          <t>Tue</t>
-        </is>
-      </c>
-      <c r="D21" s="2" t="inlineStr">
-        <is>
-          <t>Wed</t>
-        </is>
-      </c>
-      <c r="E21" s="2" t="inlineStr">
-        <is>
-          <t>Thu</t>
-        </is>
-      </c>
-      <c r="F21" s="2" t="inlineStr">
-        <is>
-          <t>Fri</t>
-        </is>
-      </c>
-      <c r="G21" s="2" t="inlineStr">
-        <is>
-          <t>Week %</t>
-        </is>
-      </c>
-      <c r="H21" s="2" t="inlineStr">
-        <is>
-          <t>Week P&amp;L (Rs)</t>
-        </is>
+      <c r="A21" s="3" t="inlineStr">
+        <is>
+          <t>26-Jan-2026</t>
+        </is>
+      </c>
+      <c r="B21" s="6" t="n"/>
+      <c r="C21" s="14" t="n">
+        <v>-0.01746560766742821</v>
+      </c>
+      <c r="D21" s="6" t="n"/>
+      <c r="E21" s="6" t="n"/>
+      <c r="F21" s="6" t="n"/>
+      <c r="G21" s="19" t="n">
+        <v>-0.01746560766742821</v>
+      </c>
+      <c r="H21" s="20" t="n">
+        <v>-336.91</v>
       </c>
     </row>
     <row r="22">
       <c r="A22" s="3" t="inlineStr">
         <is>
-          <t>01-Dec-2025</t>
+          <t>23-Mar-2026</t>
         </is>
       </c>
       <c r="B22" s="6" t="n"/>
       <c r="C22" s="14" t="n">
-        <v>-0.010346</v>
+        <v>-0.00397509629082467</v>
       </c>
       <c r="D22" s="6" t="n"/>
       <c r="E22" s="6" t="n"/>
       <c r="F22" s="6" t="n"/>
       <c r="G22" s="19" t="n">
-        <v>-0.010346</v>
+        <v>-0.00397509629082467</v>
       </c>
       <c r="H22" s="20" t="n">
-        <v>-206.92</v>
+        <v>-75.34</v>
       </c>
     </row>
     <row r="23">
       <c r="A23" s="3" t="inlineStr">
         <is>
-          <t>08-Dec-2025</t>
+          <t>11-May-2026</t>
         </is>
       </c>
       <c r="B23" s="6" t="n"/>
-      <c r="C23" s="14" t="n">
-        <v>-0.0369487719950609</v>
+      <c r="C23" s="15" t="n">
+        <v>0.02902955133210366</v>
       </c>
       <c r="D23" s="6" t="n"/>
       <c r="E23" s="6" t="n"/>
       <c r="F23" s="6" t="n"/>
-      <c r="G23" s="19" t="n">
-        <v>-0.0369487719950609</v>
-      </c>
-      <c r="H23" s="20" t="n">
-        <v>-731.33</v>
+      <c r="G23" s="21" t="n">
+        <v>0.02902955133210366</v>
+      </c>
+      <c r="H23" s="17" t="n">
+        <v>548.01</v>
       </c>
     </row>
     <row r="24">
       <c r="A24" s="3" t="inlineStr">
         <is>
-          <t>29-Dec-2025</t>
+          <t>10-Aug-2026</t>
         </is>
       </c>
       <c r="B24" s="6" t="n"/>
       <c r="C24" s="14" t="n">
-        <v>-0.03725208860676486</v>
+        <v>-0.01826964012052094</v>
       </c>
       <c r="D24" s="6" t="n"/>
       <c r="E24" s="6" t="n"/>
       <c r="F24" s="6" t="n"/>
       <c r="G24" s="19" t="n">
-        <v>-0.03725208860676486</v>
+        <v>-0.01826964012052094</v>
       </c>
       <c r="H24" s="20" t="n">
-        <v>-710.09</v>
+        <v>-354.9</v>
       </c>
     </row>
     <row r="25">
       <c r="A25" s="3" t="inlineStr">
         <is>
-          <t>26-Jan-2026</t>
+          <t>24-Aug-2026</t>
         </is>
       </c>
       <c r="B25" s="6" t="n"/>
       <c r="C25" s="14" t="n">
-        <v>-0.03399801434856575</v>
+        <v>-0.01115948648114366</v>
       </c>
       <c r="D25" s="6" t="n"/>
       <c r="E25" s="6" t="n"/>
       <c r="F25" s="6" t="n"/>
       <c r="G25" s="19" t="n">
-        <v>-0.03399801434856575</v>
+        <v>-0.01115948648114366</v>
       </c>
       <c r="H25" s="20" t="n">
-        <v>-623.92</v>
+        <v>-212.82</v>
       </c>
     </row>
     <row r="26">
       <c r="A26" s="3" t="inlineStr">
         <is>
-          <t>23-Mar-2026</t>
+          <t>12-Oct-2026</t>
         </is>
       </c>
       <c r="B26" s="6" t="n"/>
       <c r="C26" s="14" t="n">
-        <v>-0.004249836696612201</v>
+        <v>-0.01980225846393696</v>
       </c>
       <c r="D26" s="6" t="n"/>
       <c r="E26" s="6" t="n"/>
       <c r="F26" s="6" t="n"/>
       <c r="G26" s="19" t="n">
-        <v>-0.004249836696612201</v>
+        <v>-0.01980225846393696</v>
       </c>
       <c r="H26" s="20" t="n">
-        <v>-75.34</v>
-      </c>
-    </row>
-    <row r="27">
-      <c r="A27" s="3" t="inlineStr">
-        <is>
-          <t>06-Apr-2026</t>
-        </is>
-      </c>
-      <c r="B27" s="6" t="n"/>
-      <c r="C27" s="15" t="n">
-        <v>0.01342480342616302</v>
-      </c>
-      <c r="D27" s="6" t="n"/>
-      <c r="E27" s="6" t="n"/>
-      <c r="F27" s="6" t="n"/>
-      <c r="G27" s="21" t="n">
-        <v>0.01342480342616302</v>
-      </c>
-      <c r="H27" s="17" t="n">
-        <v>236.98</v>
+        <v>-373.43</v>
       </c>
     </row>
     <row r="28">
-      <c r="A28" s="3" t="inlineStr">
-        <is>
-          <t>11-May-2026</t>
-        </is>
-      </c>
-      <c r="B28" s="6" t="n"/>
-      <c r="C28" s="15" t="n">
-        <v>0.03063325839129137</v>
-      </c>
-      <c r="D28" s="6" t="n"/>
-      <c r="E28" s="6" t="n"/>
-      <c r="F28" s="6" t="n"/>
-      <c r="G28" s="21" t="n">
-        <v>0.03063325839129137</v>
-      </c>
-      <c r="H28" s="17" t="n">
-        <v>548.01</v>
+      <c r="A28" s="13" t="inlineStr">
+        <is>
+          <t>STATISTICS (all trades for this index)</t>
+        </is>
       </c>
     </row>
     <row r="29">
       <c r="A29" s="3" t="inlineStr">
         <is>
-          <t>10-Aug-2026</t>
-        </is>
-      </c>
-      <c r="B29" s="6" t="n"/>
-      <c r="C29" s="14" t="n">
-        <v>-0.01924892840038639</v>
-      </c>
-      <c r="D29" s="6" t="n"/>
-      <c r="E29" s="6" t="n"/>
-      <c r="F29" s="6" t="n"/>
-      <c r="G29" s="19" t="n">
-        <v>-0.01924892840038639</v>
-      </c>
-      <c r="H29" s="20" t="n">
-        <v>-354.9</v>
-      </c>
+          <t>All trades</t>
+        </is>
+      </c>
+      <c r="B29" s="22" t="n">
+        <v>11</v>
+      </c>
+      <c r="C29" s="23" t="n"/>
+      <c r="D29" s="24" t="n"/>
     </row>
     <row r="30">
       <c r="A30" s="3" t="inlineStr">
         <is>
-          <t>24-Aug-2026</t>
-        </is>
-      </c>
-      <c r="B30" s="6" t="n"/>
-      <c r="C30" s="14" t="n">
-        <v>-0.01176939680320576</v>
-      </c>
-      <c r="D30" s="6" t="n"/>
-      <c r="E30" s="6" t="n"/>
-      <c r="F30" s="6" t="n"/>
-      <c r="G30" s="19" t="n">
-        <v>-0.01176939680320576</v>
-      </c>
-      <c r="H30" s="20" t="n">
-        <v>-212.82</v>
-      </c>
+          <t>Winners</t>
+        </is>
+      </c>
+      <c r="B30" s="25" t="inlineStr">
+        <is>
+          <t>2 (18.2%)</t>
+        </is>
+      </c>
+      <c r="C30" s="23" t="n"/>
+      <c r="D30" s="24" t="n"/>
     </row>
     <row r="31">
       <c r="A31" s="3" t="inlineStr">
         <is>
-          <t>07-Sep-2026</t>
-        </is>
-      </c>
-      <c r="B31" s="6" t="n"/>
-      <c r="C31" s="14" t="n">
-        <v>-0.01294427932916501</v>
-      </c>
-      <c r="D31" s="6" t="n"/>
-      <c r="E31" s="6" t="n"/>
-      <c r="F31" s="6" t="n"/>
-      <c r="G31" s="19" t="n">
-        <v>-0.01294427932916501</v>
-      </c>
-      <c r="H31" s="20" t="n">
-        <v>-231.31</v>
-      </c>
+          <t>Losers</t>
+        </is>
+      </c>
+      <c r="B31" s="25" t="inlineStr">
+        <is>
+          <t>9 (81.8%)</t>
+        </is>
+      </c>
+      <c r="C31" s="23" t="n"/>
+      <c r="D31" s="24" t="n"/>
     </row>
     <row r="32">
       <c r="A32" s="3" t="inlineStr">
         <is>
-          <t>12-Oct-2026</t>
-        </is>
-      </c>
-      <c r="B32" s="6" t="n"/>
-      <c r="C32" s="14" t="n">
-        <v>-0.02117146945634402</v>
-      </c>
-      <c r="D32" s="6" t="n"/>
-      <c r="E32" s="6" t="n"/>
-      <c r="F32" s="6" t="n"/>
-      <c r="G32" s="19" t="n">
-        <v>-0.02117146945634402</v>
-      </c>
-      <c r="H32" s="20" t="n">
-        <v>-373.43</v>
-      </c>
+          <t>Net P&amp;L (Rs)</t>
+        </is>
+      </c>
+      <c r="B32" s="27" t="n">
+        <v>-1515.48</v>
+      </c>
+      <c r="C32" s="23" t="n"/>
+      <c r="D32" s="24" t="n"/>
+    </row>
+    <row r="33">
+      <c r="A33" s="3" t="inlineStr">
+        <is>
+          <t>Total Profit (Rs)</t>
+        </is>
+      </c>
+      <c r="B33" s="26" t="n">
+        <v>1040.37</v>
+      </c>
+      <c r="C33" s="23" t="n"/>
+      <c r="D33" s="24" t="n"/>
     </row>
     <row r="34">
-      <c r="A34" s="13" t="inlineStr">
-        <is>
-          <t>STATISTICS (all trades for this index)</t>
-        </is>
-      </c>
+      <c r="A34" s="3" t="inlineStr">
+        <is>
+          <t>Total Loss (Rs)</t>
+        </is>
+      </c>
+      <c r="B34" s="27" t="n">
+        <v>-2555.85</v>
+      </c>
+      <c r="C34" s="23" t="n"/>
+      <c r="D34" s="24" t="n"/>
     </row>
     <row r="35">
       <c r="A35" s="3" t="inlineStr">
         <is>
-          <t>All trades</t>
-        </is>
-      </c>
-      <c r="B35" s="22" t="n">
-        <v>18</v>
+          <t>Transaction costs (Rs)</t>
+        </is>
+      </c>
+      <c r="B35" s="28" t="n">
+        <v>508.23</v>
       </c>
       <c r="C35" s="23" t="n"/>
       <c r="D35" s="24" t="n"/>
@@ -1538,13 +1480,11 @@
     <row r="36">
       <c r="A36" s="3" t="inlineStr">
         <is>
-          <t>Winners</t>
-        </is>
-      </c>
-      <c r="B36" s="25" t="inlineStr">
-        <is>
-          <t>3 (16.7%)</t>
-        </is>
+          <t>Avg Profit/Loss per trade (Rs)</t>
+        </is>
+      </c>
+      <c r="B36" s="27" t="n">
+        <v>-137.77</v>
       </c>
       <c r="C36" s="23" t="n"/>
       <c r="D36" s="24" t="n"/>
@@ -1552,13 +1492,11 @@
     <row r="37">
       <c r="A37" s="3" t="inlineStr">
         <is>
-          <t>Losers</t>
-        </is>
-      </c>
-      <c r="B37" s="25" t="inlineStr">
-        <is>
-          <t>15 (83.3%)</t>
-        </is>
+          <t>Avg Profit/Loss per trade (% of premium)</t>
+        </is>
+      </c>
+      <c r="B37" s="29" t="n">
+        <v>-6.91</v>
       </c>
       <c r="C37" s="23" t="n"/>
       <c r="D37" s="24" t="n"/>
@@ -1566,11 +1504,11 @@
     <row r="38">
       <c r="A38" s="3" t="inlineStr">
         <is>
-          <t>Net P&amp;L (Rs)</t>
-        </is>
-      </c>
-      <c r="B38" s="27" t="n">
-        <v>-2735.07</v>
+          <t>Avg Win (Rs)</t>
+        </is>
+      </c>
+      <c r="B38" s="26" t="n">
+        <v>520.1799999999999</v>
       </c>
       <c r="C38" s="23" t="n"/>
       <c r="D38" s="24" t="n"/>
@@ -1578,11 +1516,11 @@
     <row r="39">
       <c r="A39" s="3" t="inlineStr">
         <is>
-          <t>Total Profit (Rs)</t>
-        </is>
-      </c>
-      <c r="B39" s="26" t="n">
-        <v>1277.35</v>
+          <t>Avg Win (% of premium)</t>
+        </is>
+      </c>
+      <c r="B39" s="30" t="n">
+        <v>54.92</v>
       </c>
       <c r="C39" s="23" t="n"/>
       <c r="D39" s="24" t="n"/>
@@ -1590,11 +1528,11 @@
     <row r="40">
       <c r="A40" s="3" t="inlineStr">
         <is>
-          <t>Total Loss (Rs)</t>
+          <t>Avg Loss (Rs)</t>
         </is>
       </c>
       <c r="B40" s="27" t="n">
-        <v>-4012.42</v>
+        <v>-283.98</v>
       </c>
       <c r="C40" s="23" t="n"/>
       <c r="D40" s="24" t="n"/>
@@ -1602,11 +1540,11 @@
     <row r="41">
       <c r="A41" s="3" t="inlineStr">
         <is>
-          <t>Transaction costs (Rs)</t>
-        </is>
-      </c>
-      <c r="B41" s="28" t="n">
-        <v>856.62</v>
+          <t>Avg Loss (% of premium)</t>
+        </is>
+      </c>
+      <c r="B41" s="31" t="n">
+        <v>-20.65</v>
       </c>
       <c r="C41" s="23" t="n"/>
       <c r="D41" s="24" t="n"/>
@@ -1614,11 +1552,11 @@
     <row r="42">
       <c r="A42" s="3" t="inlineStr">
         <is>
-          <t>Avg Profit/Loss per trade (Rs)</t>
-        </is>
-      </c>
-      <c r="B42" s="27" t="n">
-        <v>-151.95</v>
+          <t>Largest Win (Rs)</t>
+        </is>
+      </c>
+      <c r="B42" s="26" t="n">
+        <v>548.01</v>
       </c>
       <c r="C42" s="23" t="n"/>
       <c r="D42" s="24" t="n"/>
@@ -1626,11 +1564,11 @@
     <row r="43">
       <c r="A43" s="3" t="inlineStr">
         <is>
-          <t>Avg Profit/Loss per trade (% of premium)</t>
-        </is>
-      </c>
-      <c r="B43" s="29" t="n">
-        <v>-8.27</v>
+          <t>Largest Loss (Rs)</t>
+        </is>
+      </c>
+      <c r="B43" s="27" t="n">
+        <v>-358.86</v>
       </c>
       <c r="C43" s="23" t="n"/>
       <c r="D43" s="24" t="n"/>
@@ -1638,11 +1576,11 @@
     <row r="44">
       <c r="A44" s="3" t="inlineStr">
         <is>
-          <t>Avg Win (Rs)</t>
-        </is>
-      </c>
-      <c r="B44" s="26" t="n">
-        <v>425.78</v>
+          <t>Max Consecutive Wins</t>
+        </is>
+      </c>
+      <c r="B44" s="22" t="n">
+        <v>1</v>
       </c>
       <c r="C44" s="23" t="n"/>
       <c r="D44" s="24" t="n"/>
@@ -1650,11 +1588,11 @@
     <row r="45">
       <c r="A45" s="3" t="inlineStr">
         <is>
-          <t>Avg Win (% of premium)</t>
-        </is>
-      </c>
-      <c r="B45" s="30" t="n">
-        <v>42</v>
+          <t>Max Consecutive Losses</t>
+        </is>
+      </c>
+      <c r="B45" s="22" t="n">
+        <v>7</v>
       </c>
       <c r="C45" s="23" t="n"/>
       <c r="D45" s="24" t="n"/>
@@ -1662,11 +1600,11 @@
     <row r="46">
       <c r="A46" s="3" t="inlineStr">
         <is>
-          <t>Avg Loss (Rs)</t>
+          <t>Max trade drawdown (Rs)</t>
         </is>
       </c>
       <c r="B46" s="27" t="n">
-        <v>-267.49</v>
+        <v>-358.86</v>
       </c>
       <c r="C46" s="23" t="n"/>
       <c r="D46" s="24" t="n"/>
@@ -1674,11 +1612,11 @@
     <row r="47">
       <c r="A47" s="3" t="inlineStr">
         <is>
-          <t>Avg Loss (% of premium)</t>
-        </is>
-      </c>
-      <c r="B47" s="31" t="n">
-        <v>-18.33</v>
+          <t>Max system drawdown (Rs)</t>
+        </is>
+      </c>
+      <c r="B47" s="27" t="n">
+        <v>-1988.15</v>
       </c>
       <c r="C47" s="23" t="n"/>
       <c r="D47" s="24" t="n"/>
@@ -1686,11 +1624,11 @@
     <row r="48">
       <c r="A48" s="3" t="inlineStr">
         <is>
-          <t>Largest Win (Rs)</t>
-        </is>
-      </c>
-      <c r="B48" s="26" t="n">
-        <v>548.01</v>
+          <t>Max system drawdown (%)</t>
+        </is>
+      </c>
+      <c r="B48" s="31" t="n">
+        <v>-9.710000000000001</v>
       </c>
       <c r="C48" s="23" t="n"/>
       <c r="D48" s="24" t="n"/>
@@ -1698,11 +1636,11 @@
     <row r="49">
       <c r="A49" s="3" t="inlineStr">
         <is>
-          <t>Largest Loss (Rs)</t>
-        </is>
-      </c>
-      <c r="B49" s="27" t="n">
-        <v>-358.86</v>
+          <t>Recovery Factor</t>
+        </is>
+      </c>
+      <c r="B49" s="32" t="n">
+        <v>-0.76</v>
       </c>
       <c r="C49" s="23" t="n"/>
       <c r="D49" s="24" t="n"/>
@@ -1710,11 +1648,11 @@
     <row r="50">
       <c r="A50" s="3" t="inlineStr">
         <is>
-          <t>Max Consecutive Wins</t>
-        </is>
-      </c>
-      <c r="B50" s="22" t="n">
-        <v>1</v>
+          <t>Profit Factor</t>
+        </is>
+      </c>
+      <c r="B50" s="32" t="n">
+        <v>0.41</v>
       </c>
       <c r="C50" s="23" t="n"/>
       <c r="D50" s="24" t="n"/>
@@ -1722,11 +1660,11 @@
     <row r="51">
       <c r="A51" s="3" t="inlineStr">
         <is>
-          <t>Max Consecutive Losses</t>
-        </is>
-      </c>
-      <c r="B51" s="22" t="n">
-        <v>12</v>
+          <t>Payoff Ratio (avg win / avg loss)</t>
+        </is>
+      </c>
+      <c r="B51" s="32" t="n">
+        <v>1.83</v>
       </c>
       <c r="C51" s="23" t="n"/>
       <c r="D51" s="24" t="n"/>
@@ -1734,89 +1672,17 @@
     <row r="52">
       <c r="A52" s="3" t="inlineStr">
         <is>
-          <t>Max trade drawdown (Rs)</t>
-        </is>
-      </c>
-      <c r="B52" s="27" t="n">
-        <v>-358.86</v>
+          <t>Sharpe Ratio (annualized)</t>
+        </is>
+      </c>
+      <c r="B52" s="32" t="n">
+        <v>-9.4</v>
       </c>
       <c r="C52" s="23" t="n"/>
       <c r="D52" s="24" t="n"/>
     </row>
-    <row r="53">
-      <c r="A53" s="3" t="inlineStr">
-        <is>
-          <t>Max system drawdown (Rs)</t>
-        </is>
-      </c>
-      <c r="B53" s="27" t="n">
-        <v>-3213.41</v>
-      </c>
-      <c r="C53" s="23" t="n"/>
-      <c r="D53" s="24" t="n"/>
-    </row>
     <row r="54">
-      <c r="A54" s="3" t="inlineStr">
-        <is>
-          <t>Max system drawdown (%)</t>
-        </is>
-      </c>
-      <c r="B54" s="31" t="n">
-        <v>-15.7</v>
-      </c>
-      <c r="C54" s="23" t="n"/>
-      <c r="D54" s="24" t="n"/>
-    </row>
-    <row r="55">
-      <c r="A55" s="3" t="inlineStr">
-        <is>
-          <t>Recovery Factor</t>
-        </is>
-      </c>
-      <c r="B55" s="32" t="n">
-        <v>-0.85</v>
-      </c>
-      <c r="C55" s="23" t="n"/>
-      <c r="D55" s="24" t="n"/>
-    </row>
-    <row r="56">
-      <c r="A56" s="3" t="inlineStr">
-        <is>
-          <t>Profit Factor</t>
-        </is>
-      </c>
-      <c r="B56" s="32" t="n">
-        <v>0.32</v>
-      </c>
-      <c r="C56" s="23" t="n"/>
-      <c r="D56" s="24" t="n"/>
-    </row>
-    <row r="57">
-      <c r="A57" s="3" t="inlineStr">
-        <is>
-          <t>Payoff Ratio (avg win / avg loss)</t>
-        </is>
-      </c>
-      <c r="B57" s="32" t="n">
-        <v>1.59</v>
-      </c>
-      <c r="C57" s="23" t="n"/>
-      <c r="D57" s="24" t="n"/>
-    </row>
-    <row r="58">
-      <c r="A58" s="3" t="inlineStr">
-        <is>
-          <t>Sharpe Ratio (annualized)</t>
-        </is>
-      </c>
-      <c r="B58" s="32" t="n">
-        <v>-10.39</v>
-      </c>
-      <c r="C58" s="23" t="n"/>
-      <c r="D58" s="24" t="n"/>
-    </row>
-    <row r="60">
-      <c r="A60" s="5" t="inlineStr">
+      <c r="A54" s="5" t="inlineStr">
         <is>
           <t>Caveat: with only a handful of trades these numbers (Sharpe, profit factor, drawdown %) are not statistically reliable. Watch this over weeks/months before drawing conclusions.</t>
         </is>
@@ -1825,25 +1691,25 @@
   </sheetData>
   <mergeCells count="24">
     <mergeCell ref="B42:D42"/>
-    <mergeCell ref="B57:D57"/>
     <mergeCell ref="B44:D44"/>
-    <mergeCell ref="B53:D53"/>
+    <mergeCell ref="B29:D29"/>
     <mergeCell ref="B38:D38"/>
+    <mergeCell ref="B34:D34"/>
     <mergeCell ref="B37:D37"/>
     <mergeCell ref="B49:D49"/>
     <mergeCell ref="B40:D40"/>
-    <mergeCell ref="B55:D55"/>
+    <mergeCell ref="B30:D30"/>
     <mergeCell ref="B51:D51"/>
+    <mergeCell ref="B33:D33"/>
     <mergeCell ref="B36:D36"/>
     <mergeCell ref="B45:D45"/>
     <mergeCell ref="B41:D41"/>
+    <mergeCell ref="B32:D32"/>
     <mergeCell ref="B35:D35"/>
     <mergeCell ref="B50:D50"/>
     <mergeCell ref="B47:D47"/>
-    <mergeCell ref="B54:D54"/>
+    <mergeCell ref="B31:D31"/>
     <mergeCell ref="B46:D46"/>
-    <mergeCell ref="B56:D56"/>
-    <mergeCell ref="B58:D58"/>
     <mergeCell ref="B52:D52"/>
     <mergeCell ref="B43:D43"/>
     <mergeCell ref="B39:D39"/>
@@ -2162,23 +2028,31 @@
       </c>
       <c r="B6" s="6" t="inlineStr">
         <is>
-          <t>trend_scalp_nw (EMA9/26) [5m]</t>
-        </is>
-      </c>
-      <c r="C6" s="7" t="n">
-        <v>7</v>
-      </c>
-      <c r="D6" s="8" t="n">
-        <v>0.1428571428571428</v>
-      </c>
-      <c r="E6" s="12" t="n">
-        <v>-1219.59</v>
-      </c>
-      <c r="F6" s="10" t="n">
-        <v>0.16</v>
-      </c>
-      <c r="G6" s="11" t="n">
-        <v>-0.06126299999999993</v>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="C6" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="D6" s="4" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="E6" s="4" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="F6" s="4" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="G6" s="4" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
     </row>
     <row r="7">
@@ -2193,19 +2067,19 @@
         </is>
       </c>
       <c r="C7" s="7" t="n">
-        <v>18</v>
+        <v>11</v>
       </c>
       <c r="D7" s="8" t="n">
-        <v>0.1666666666666667</v>
+        <v>0.1818181818181818</v>
       </c>
       <c r="E7" s="12" t="n">
-        <v>-2735.07</v>
+        <v>-1515.48</v>
       </c>
       <c r="F7" s="10" t="n">
-        <v>0.32</v>
+        <v>0.41</v>
       </c>
       <c r="G7" s="11" t="n">
-        <v>-0.1569609630790708</v>
+        <v>-0.09711239423094309</v>
       </c>
     </row>
     <row r="9">
@@ -3789,7 +3663,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
-  <dimension ref="A1:O50"/>
+  <dimension ref="A1:A3"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="40" customWidth="1" min="1" max="1"/>
@@ -3812,797 +3686,18 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>BACKTEST FINNIFTY -- best: trend_scalp_nw (EMA9/26) [5m] -- PAPER TRADE, NOT REAL MONEY</t>
+          <t>BACKTEST FINNIFTY -- best:  -- PAPER TRADE, NOT REAL MONEY</t>
         </is>
       </c>
     </row>
     <row r="3">
-      <c r="A3" s="13" t="inlineStr">
-        <is>
-          <t>MONTHLY returns (% of capital at start of month)</t>
-        </is>
-      </c>
-    </row>
-    <row r="4">
-      <c r="A4" s="2" t="inlineStr">
-        <is>
-          <t>Year</t>
-        </is>
-      </c>
-      <c r="B4" s="2" t="inlineStr">
-        <is>
-          <t>Jan</t>
-        </is>
-      </c>
-      <c r="C4" s="2" t="inlineStr">
-        <is>
-          <t>Feb</t>
-        </is>
-      </c>
-      <c r="D4" s="2" t="inlineStr">
-        <is>
-          <t>Mar</t>
-        </is>
-      </c>
-      <c r="E4" s="2" t="inlineStr">
-        <is>
-          <t>Apr</t>
-        </is>
-      </c>
-      <c r="F4" s="2" t="inlineStr">
-        <is>
-          <t>May</t>
-        </is>
-      </c>
-      <c r="G4" s="2" t="inlineStr">
-        <is>
-          <t>Jun</t>
-        </is>
-      </c>
-      <c r="H4" s="2" t="inlineStr">
-        <is>
-          <t>Jul</t>
-        </is>
-      </c>
-      <c r="I4" s="2" t="inlineStr">
-        <is>
-          <t>Aug</t>
-        </is>
-      </c>
-      <c r="J4" s="2" t="inlineStr">
-        <is>
-          <t>Sep</t>
-        </is>
-      </c>
-      <c r="K4" s="2" t="inlineStr">
-        <is>
-          <t>Oct</t>
-        </is>
-      </c>
-      <c r="L4" s="2" t="inlineStr">
-        <is>
-          <t>Nov</t>
-        </is>
-      </c>
-      <c r="M4" s="2" t="inlineStr">
-        <is>
-          <t>Dec</t>
-        </is>
-      </c>
-      <c r="N4" s="2" t="inlineStr">
-        <is>
-          <t>Yr %</t>
-        </is>
-      </c>
-      <c r="O4" s="2" t="inlineStr">
-        <is>
-          <t>Yr P&amp;L (Rs)</t>
-        </is>
-      </c>
-    </row>
-    <row r="5">
-      <c r="A5" s="3" t="n">
-        <v>2025</v>
-      </c>
-      <c r="B5" s="6" t="n"/>
-      <c r="C5" s="6" t="n"/>
-      <c r="D5" s="6" t="n"/>
-      <c r="E5" s="6" t="n"/>
-      <c r="F5" s="6" t="n"/>
-      <c r="G5" s="6" t="n"/>
-      <c r="H5" s="6" t="n"/>
-      <c r="I5" s="6" t="n"/>
-      <c r="J5" s="6" t="n"/>
-      <c r="K5" s="6" t="n"/>
-      <c r="L5" s="6" t="n"/>
-      <c r="M5" s="14" t="n">
-        <v>-0.0469125</v>
-      </c>
-      <c r="N5" s="18" t="n">
-        <v>-0.04691250000000002</v>
-      </c>
-      <c r="O5" s="20" t="n">
-        <v>-938.25</v>
-      </c>
-    </row>
-    <row r="6">
-      <c r="A6" s="3" t="n">
-        <v>2026</v>
-      </c>
-      <c r="B6" s="14" t="n">
-        <v>-0.01505685469592246</v>
-      </c>
-      <c r="C6" s="6" t="n"/>
-      <c r="D6" s="6" t="n"/>
-      <c r="E6" s="15" t="n">
-        <v>0.01262227865738753</v>
-      </c>
-      <c r="F6" s="6" t="n"/>
-      <c r="G6" s="6" t="n"/>
-      <c r="H6" s="6" t="n"/>
-      <c r="I6" s="6" t="n"/>
-      <c r="J6" s="14" t="n">
-        <v>-0.01216670559002552</v>
-      </c>
-      <c r="K6" s="6" t="n"/>
-      <c r="L6" s="6" t="n"/>
-      <c r="M6" s="6" t="n"/>
-      <c r="N6" s="18" t="n">
-        <v>-0.01475940036985068</v>
-      </c>
-      <c r="O6" s="20" t="n">
-        <v>-281.34</v>
-      </c>
-    </row>
-    <row r="7">
-      <c r="A7" s="3" t="inlineStr">
-        <is>
-          <t>Avg</t>
-        </is>
-      </c>
-      <c r="B7" s="18" t="n">
-        <v>-0.01505685469592246</v>
-      </c>
-      <c r="C7" s="6" t="n"/>
-      <c r="D7" s="6" t="n"/>
-      <c r="E7" s="16" t="n">
-        <v>0.01262227865738753</v>
-      </c>
-      <c r="F7" s="6" t="n"/>
-      <c r="G7" s="6" t="n"/>
-      <c r="H7" s="6" t="n"/>
-      <c r="I7" s="6" t="n"/>
-      <c r="J7" s="18" t="n">
-        <v>-0.01216670559002552</v>
-      </c>
-      <c r="K7" s="6" t="n"/>
-      <c r="L7" s="6" t="n"/>
-      <c r="M7" s="18" t="n">
-        <v>-0.0469125</v>
-      </c>
-    </row>
-    <row r="9">
-      <c r="A9" s="13" t="inlineStr">
-        <is>
-          <t>WEEKLY returns (% of capital at start of that week; weeks split at month edges)</t>
-        </is>
-      </c>
-    </row>
-    <row r="10">
-      <c r="A10" s="2" t="inlineStr">
-        <is>
-          <t>Month</t>
-        </is>
-      </c>
-      <c r="B10" s="2" t="inlineStr">
-        <is>
-          <t>W1</t>
-        </is>
-      </c>
-      <c r="C10" s="2" t="inlineStr">
-        <is>
-          <t>W2</t>
-        </is>
-      </c>
-      <c r="D10" s="2" t="inlineStr">
-        <is>
-          <t>W3</t>
-        </is>
-      </c>
-      <c r="E10" s="2" t="inlineStr">
-        <is>
-          <t>W4</t>
-        </is>
-      </c>
-      <c r="F10" s="2" t="inlineStr">
-        <is>
-          <t>W5</t>
-        </is>
-      </c>
-      <c r="G10" s="2" t="inlineStr">
-        <is>
-          <t>W6</t>
-        </is>
-      </c>
-      <c r="H10" s="2" t="inlineStr">
-        <is>
-          <t>Month %</t>
-        </is>
-      </c>
-      <c r="I10" s="2" t="inlineStr">
-        <is>
-          <t>Month P&amp;L (Rs)</t>
-        </is>
-      </c>
-    </row>
-    <row r="11">
-      <c r="A11" s="3" t="inlineStr">
-        <is>
-          <t>2025-Dec</t>
-        </is>
-      </c>
-      <c r="B11" s="14" t="n">
-        <v>-0.010346</v>
-      </c>
-      <c r="C11" s="14" t="n">
-        <v>-0.0369487719950609</v>
-      </c>
-      <c r="D11" s="6" t="n"/>
-      <c r="E11" s="6" t="n"/>
-      <c r="F11" s="6" t="n"/>
-      <c r="G11" s="6" t="n"/>
-      <c r="H11" s="19" t="n">
-        <v>-0.0469125</v>
-      </c>
-      <c r="I11" s="20" t="n">
-        <v>-938.25</v>
-      </c>
-    </row>
-    <row r="12">
-      <c r="A12" s="3" t="inlineStr">
-        <is>
-          <t>2026-Jan</t>
-        </is>
-      </c>
-      <c r="B12" s="14" t="n">
-        <v>-0.01505685469592246</v>
-      </c>
-      <c r="C12" s="6" t="n"/>
-      <c r="D12" s="6" t="n"/>
-      <c r="E12" s="6" t="n"/>
-      <c r="F12" s="6" t="n"/>
-      <c r="G12" s="6" t="n"/>
-      <c r="H12" s="19" t="n">
-        <v>-0.01505685469592246</v>
-      </c>
-      <c r="I12" s="20" t="n">
-        <v>-287.01</v>
-      </c>
-    </row>
-    <row r="13">
-      <c r="A13" s="3" t="inlineStr">
-        <is>
-          <t>2026-Apr</t>
-        </is>
-      </c>
-      <c r="B13" s="15" t="n">
-        <v>0.01262227865738753</v>
-      </c>
-      <c r="C13" s="6" t="n"/>
-      <c r="D13" s="6" t="n"/>
-      <c r="E13" s="6" t="n"/>
-      <c r="F13" s="6" t="n"/>
-      <c r="G13" s="6" t="n"/>
-      <c r="H13" s="21" t="n">
-        <v>0.01262227865738753</v>
-      </c>
-      <c r="I13" s="17" t="n">
-        <v>236.98</v>
-      </c>
-    </row>
-    <row r="14">
-      <c r="A14" s="3" t="inlineStr">
-        <is>
-          <t>2026-Sep</t>
-        </is>
-      </c>
-      <c r="B14" s="14" t="n">
-        <v>-0.01216670559002552</v>
-      </c>
-      <c r="C14" s="6" t="n"/>
-      <c r="D14" s="6" t="n"/>
-      <c r="E14" s="6" t="n"/>
-      <c r="F14" s="6" t="n"/>
-      <c r="G14" s="6" t="n"/>
-      <c r="H14" s="19" t="n">
-        <v>-0.01216670559002552</v>
-      </c>
-      <c r="I14" s="20" t="n">
-        <v>-231.31</v>
-      </c>
-    </row>
-    <row r="16">
-      <c r="A16" s="13" t="inlineStr">
-        <is>
-          <t>DAILY returns (% of capital at start of that day; blank = no trade that day)</t>
-        </is>
-      </c>
-    </row>
-    <row r="17">
-      <c r="A17" s="2" t="inlineStr">
-        <is>
-          <t>Week starting (Mon)</t>
-        </is>
-      </c>
-      <c r="B17" s="2" t="inlineStr">
-        <is>
-          <t>Mon</t>
-        </is>
-      </c>
-      <c r="C17" s="2" t="inlineStr">
-        <is>
-          <t>Tue</t>
-        </is>
-      </c>
-      <c r="D17" s="2" t="inlineStr">
-        <is>
-          <t>Wed</t>
-        </is>
-      </c>
-      <c r="E17" s="2" t="inlineStr">
-        <is>
-          <t>Thu</t>
-        </is>
-      </c>
-      <c r="F17" s="2" t="inlineStr">
-        <is>
-          <t>Fri</t>
-        </is>
-      </c>
-      <c r="G17" s="2" t="inlineStr">
-        <is>
-          <t>Week %</t>
-        </is>
-      </c>
-      <c r="H17" s="2" t="inlineStr">
-        <is>
-          <t>Week P&amp;L (Rs)</t>
-        </is>
-      </c>
-    </row>
-    <row r="18">
-      <c r="A18" s="3" t="inlineStr">
-        <is>
-          <t>01-Dec-2025</t>
-        </is>
-      </c>
-      <c r="B18" s="6" t="n"/>
-      <c r="C18" s="14" t="n">
-        <v>-0.010346</v>
-      </c>
-      <c r="D18" s="6" t="n"/>
-      <c r="E18" s="6" t="n"/>
-      <c r="F18" s="6" t="n"/>
-      <c r="G18" s="19" t="n">
-        <v>-0.010346</v>
-      </c>
-      <c r="H18" s="20" t="n">
-        <v>-206.92</v>
-      </c>
-    </row>
-    <row r="19">
-      <c r="A19" s="3" t="inlineStr">
-        <is>
-          <t>08-Dec-2025</t>
-        </is>
-      </c>
-      <c r="B19" s="6" t="n"/>
-      <c r="C19" s="14" t="n">
-        <v>-0.0369487719950609</v>
-      </c>
-      <c r="D19" s="6" t="n"/>
-      <c r="E19" s="6" t="n"/>
-      <c r="F19" s="6" t="n"/>
-      <c r="G19" s="19" t="n">
-        <v>-0.0369487719950609</v>
-      </c>
-      <c r="H19" s="20" t="n">
-        <v>-731.33</v>
-      </c>
-    </row>
-    <row r="20">
-      <c r="A20" s="3" t="inlineStr">
-        <is>
-          <t>26-Jan-2026</t>
-        </is>
-      </c>
-      <c r="B20" s="6" t="n"/>
-      <c r="C20" s="14" t="n">
-        <v>-0.01505685469592246</v>
-      </c>
-      <c r="D20" s="6" t="n"/>
-      <c r="E20" s="6" t="n"/>
-      <c r="F20" s="6" t="n"/>
-      <c r="G20" s="19" t="n">
-        <v>-0.01505685469592246</v>
-      </c>
-      <c r="H20" s="20" t="n">
-        <v>-287.01</v>
-      </c>
-    </row>
-    <row r="21">
-      <c r="A21" s="3" t="inlineStr">
-        <is>
-          <t>06-Apr-2026</t>
-        </is>
-      </c>
-      <c r="B21" s="6" t="n"/>
-      <c r="C21" s="15" t="n">
-        <v>0.01262227865738753</v>
-      </c>
-      <c r="D21" s="6" t="n"/>
-      <c r="E21" s="6" t="n"/>
-      <c r="F21" s="6" t="n"/>
-      <c r="G21" s="21" t="n">
-        <v>0.01262227865738753</v>
-      </c>
-      <c r="H21" s="17" t="n">
-        <v>236.98</v>
-      </c>
-    </row>
-    <row r="22">
-      <c r="A22" s="3" t="inlineStr">
-        <is>
-          <t>07-Sep-2026</t>
-        </is>
-      </c>
-      <c r="B22" s="6" t="n"/>
-      <c r="C22" s="14" t="n">
-        <v>-0.01216670559002552</v>
-      </c>
-      <c r="D22" s="6" t="n"/>
-      <c r="E22" s="6" t="n"/>
-      <c r="F22" s="6" t="n"/>
-      <c r="G22" s="19" t="n">
-        <v>-0.01216670559002552</v>
-      </c>
-      <c r="H22" s="20" t="n">
-        <v>-231.31</v>
-      </c>
-    </row>
-    <row r="24">
-      <c r="A24" s="13" t="inlineStr">
-        <is>
-          <t>STATISTICS (all trades for this index)</t>
-        </is>
-      </c>
-    </row>
-    <row r="25">
-      <c r="A25" s="3" t="inlineStr">
-        <is>
-          <t>All trades</t>
-        </is>
-      </c>
-      <c r="B25" s="22" t="n">
-        <v>7</v>
-      </c>
-      <c r="C25" s="23" t="n"/>
-      <c r="D25" s="24" t="n"/>
-    </row>
-    <row r="26">
-      <c r="A26" s="3" t="inlineStr">
-        <is>
-          <t>Winners</t>
-        </is>
-      </c>
-      <c r="B26" s="25" t="inlineStr">
-        <is>
-          <t>1 (14.3%)</t>
-        </is>
-      </c>
-      <c r="C26" s="23" t="n"/>
-      <c r="D26" s="24" t="n"/>
-    </row>
-    <row r="27">
-      <c r="A27" s="3" t="inlineStr">
-        <is>
-          <t>Losers</t>
-        </is>
-      </c>
-      <c r="B27" s="25" t="inlineStr">
-        <is>
-          <t>6 (85.7%)</t>
-        </is>
-      </c>
-      <c r="C27" s="23" t="n"/>
-      <c r="D27" s="24" t="n"/>
-    </row>
-    <row r="28">
-      <c r="A28" s="3" t="inlineStr">
-        <is>
-          <t>Net P&amp;L (Rs)</t>
-        </is>
-      </c>
-      <c r="B28" s="27" t="n">
-        <v>-1219.59</v>
-      </c>
-      <c r="C28" s="23" t="n"/>
-      <c r="D28" s="24" t="n"/>
-    </row>
-    <row r="29">
-      <c r="A29" s="3" t="inlineStr">
-        <is>
-          <t>Total Profit (Rs)</t>
-        </is>
-      </c>
-      <c r="B29" s="26" t="n">
-        <v>236.98</v>
-      </c>
-      <c r="C29" s="23" t="n"/>
-      <c r="D29" s="24" t="n"/>
-    </row>
-    <row r="30">
-      <c r="A30" s="3" t="inlineStr">
-        <is>
-          <t>Total Loss (Rs)</t>
-        </is>
-      </c>
-      <c r="B30" s="27" t="n">
-        <v>-1456.57</v>
-      </c>
-      <c r="C30" s="23" t="n"/>
-      <c r="D30" s="24" t="n"/>
-    </row>
-    <row r="31">
-      <c r="A31" s="3" t="inlineStr">
-        <is>
-          <t>Transaction costs (Rs)</t>
-        </is>
-      </c>
-      <c r="B31" s="28" t="n">
-        <v>348.39</v>
-      </c>
-      <c r="C31" s="23" t="n"/>
-      <c r="D31" s="24" t="n"/>
-    </row>
-    <row r="32">
-      <c r="A32" s="3" t="inlineStr">
-        <is>
-          <t>Avg Profit/Loss per trade (Rs)</t>
-        </is>
-      </c>
-      <c r="B32" s="27" t="n">
-        <v>-174.23</v>
-      </c>
-      <c r="C32" s="23" t="n"/>
-      <c r="D32" s="24" t="n"/>
-    </row>
-    <row r="33">
-      <c r="A33" s="3" t="inlineStr">
-        <is>
-          <t>Avg Profit/Loss per trade (% of premium)</t>
-        </is>
-      </c>
-      <c r="B33" s="29" t="n">
-        <v>-10.42</v>
-      </c>
-      <c r="C33" s="23" t="n"/>
-      <c r="D33" s="24" t="n"/>
-    </row>
-    <row r="34">
-      <c r="A34" s="3" t="inlineStr">
-        <is>
-          <t>Avg Win (Rs)</t>
-        </is>
-      </c>
-      <c r="B34" s="26" t="n">
-        <v>236.98</v>
-      </c>
-      <c r="C34" s="23" t="n"/>
-      <c r="D34" s="24" t="n"/>
-    </row>
-    <row r="35">
-      <c r="A35" s="3" t="inlineStr">
-        <is>
-          <t>Avg Win (% of premium)</t>
-        </is>
-      </c>
-      <c r="B35" s="30" t="n">
-        <v>16.17</v>
-      </c>
-      <c r="C35" s="23" t="n"/>
-      <c r="D35" s="24" t="n"/>
-    </row>
-    <row r="36">
-      <c r="A36" s="3" t="inlineStr">
-        <is>
-          <t>Avg Loss (Rs)</t>
-        </is>
-      </c>
-      <c r="B36" s="27" t="n">
-        <v>-242.76</v>
-      </c>
-      <c r="C36" s="23" t="n"/>
-      <c r="D36" s="24" t="n"/>
-    </row>
-    <row r="37">
-      <c r="A37" s="3" t="inlineStr">
-        <is>
-          <t>Avg Loss (% of premium)</t>
-        </is>
-      </c>
-      <c r="B37" s="31" t="n">
-        <v>-14.85</v>
-      </c>
-      <c r="C37" s="23" t="n"/>
-      <c r="D37" s="24" t="n"/>
-    </row>
-    <row r="38">
-      <c r="A38" s="3" t="inlineStr">
-        <is>
-          <t>Largest Win (Rs)</t>
-        </is>
-      </c>
-      <c r="B38" s="26" t="n">
-        <v>236.98</v>
-      </c>
-      <c r="C38" s="23" t="n"/>
-      <c r="D38" s="24" t="n"/>
-    </row>
-    <row r="39">
-      <c r="A39" s="3" t="inlineStr">
-        <is>
-          <t>Largest Loss (Rs)</t>
-        </is>
-      </c>
-      <c r="B39" s="27" t="n">
-        <v>-295.95</v>
-      </c>
-      <c r="C39" s="23" t="n"/>
-      <c r="D39" s="24" t="n"/>
-    </row>
-    <row r="40">
-      <c r="A40" s="3" t="inlineStr">
-        <is>
-          <t>Max Consecutive Wins</t>
-        </is>
-      </c>
-      <c r="B40" s="22" t="n">
-        <v>1</v>
-      </c>
-      <c r="C40" s="23" t="n"/>
-      <c r="D40" s="24" t="n"/>
-    </row>
-    <row r="41">
-      <c r="A41" s="3" t="inlineStr">
-        <is>
-          <t>Max Consecutive Losses</t>
-        </is>
-      </c>
-      <c r="B41" s="22" t="n">
-        <v>5</v>
-      </c>
-      <c r="C41" s="23" t="n"/>
-      <c r="D41" s="24" t="n"/>
-    </row>
-    <row r="42">
-      <c r="A42" s="3" t="inlineStr">
-        <is>
-          <t>Max trade drawdown (Rs)</t>
-        </is>
-      </c>
-      <c r="B42" s="27" t="n">
-        <v>-295.95</v>
-      </c>
-      <c r="C42" s="23" t="n"/>
-      <c r="D42" s="24" t="n"/>
-    </row>
-    <row r="43">
-      <c r="A43" s="3" t="inlineStr">
-        <is>
-          <t>Max system drawdown (Rs)</t>
-        </is>
-      </c>
-      <c r="B43" s="27" t="n">
-        <v>-1225.26</v>
-      </c>
-      <c r="C43" s="23" t="n"/>
-      <c r="D43" s="24" t="n"/>
-    </row>
-    <row r="44">
-      <c r="A44" s="3" t="inlineStr">
-        <is>
-          <t>Max system drawdown (%)</t>
-        </is>
-      </c>
-      <c r="B44" s="31" t="n">
-        <v>-6.13</v>
-      </c>
-      <c r="C44" s="23" t="n"/>
-      <c r="D44" s="24" t="n"/>
-    </row>
-    <row r="45">
-      <c r="A45" s="3" t="inlineStr">
-        <is>
-          <t>Recovery Factor</t>
-        </is>
-      </c>
-      <c r="B45" s="32" t="n">
-        <v>-1</v>
-      </c>
-      <c r="C45" s="23" t="n"/>
-      <c r="D45" s="24" t="n"/>
-    </row>
-    <row r="46">
-      <c r="A46" s="3" t="inlineStr">
-        <is>
-          <t>Profit Factor</t>
-        </is>
-      </c>
-      <c r="B46" s="32" t="n">
-        <v>0.16</v>
-      </c>
-      <c r="C46" s="23" t="n"/>
-      <c r="D46" s="24" t="n"/>
-    </row>
-    <row r="47">
-      <c r="A47" s="3" t="inlineStr">
-        <is>
-          <t>Payoff Ratio (avg win / avg loss)</t>
-        </is>
-      </c>
-      <c r="B47" s="32" t="n">
-        <v>0.98</v>
-      </c>
-      <c r="C47" s="23" t="n"/>
-      <c r="D47" s="24" t="n"/>
-    </row>
-    <row r="48">
-      <c r="A48" s="3" t="inlineStr">
-        <is>
-          <t>Sharpe Ratio (annualized)</t>
-        </is>
-      </c>
-      <c r="B48" s="32" t="n">
-        <v>-12.48</v>
-      </c>
-      <c r="C48" s="23" t="n"/>
-      <c r="D48" s="24" t="n"/>
-    </row>
-    <row r="50">
-      <c r="A50" s="5" t="inlineStr">
-        <is>
-          <t>Caveat: with only a handful of trades these numbers (Sharpe, profit factor, drawdown %) are not statistically reliable. Watch this over weeks/months before drawing conclusions.</t>
+      <c r="A3" s="5" t="inlineStr">
+        <is>
+          <t>No trades yet for this index -- this fills in automatically as the bot trades.</t>
         </is>
       </c>
     </row>
   </sheetData>
-  <mergeCells count="24">
-    <mergeCell ref="B42:D42"/>
-    <mergeCell ref="B44:D44"/>
-    <mergeCell ref="B29:D29"/>
-    <mergeCell ref="B38:D38"/>
-    <mergeCell ref="B34:D34"/>
-    <mergeCell ref="B28:D28"/>
-    <mergeCell ref="B37:D37"/>
-    <mergeCell ref="B40:D40"/>
-    <mergeCell ref="B30:D30"/>
-    <mergeCell ref="B33:D33"/>
-    <mergeCell ref="B36:D36"/>
-    <mergeCell ref="B45:D45"/>
-    <mergeCell ref="B41:D41"/>
-    <mergeCell ref="B32:D32"/>
-    <mergeCell ref="B35:D35"/>
-    <mergeCell ref="B26:D26"/>
-    <mergeCell ref="B25:D25"/>
-    <mergeCell ref="B47:D47"/>
-    <mergeCell ref="B31:D31"/>
-    <mergeCell ref="B46:D46"/>
-    <mergeCell ref="B27:D27"/>
-    <mergeCell ref="B43:D43"/>
-    <mergeCell ref="B39:D39"/>
-    <mergeCell ref="B48:D48"/>
-  </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
   <pageSetup orientation="landscape" fitToHeight="0" fitToWidth="1"/>
 </worksheet>

--- a/reports/dashboard.xlsx
+++ b/reports/dashboard.xlsx
@@ -64,11 +64,11 @@
     </font>
     <font>
       <name val="Arial"/>
-      <color rgb="000B8A00"/>
+      <color rgb="00C00000"/>
     </font>
     <font>
       <name val="Arial"/>
-      <color rgb="00C00000"/>
+      <color rgb="000B8A00"/>
     </font>
     <font>
       <name val="Arial"/>
@@ -177,7 +177,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="33">
+  <cellXfs count="32">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="2" fillId="2" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
@@ -192,16 +192,15 @@
     <xf numFmtId="165" fontId="6" fillId="0" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="2" fontId="4" fillId="0" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="10" fontId="4" fillId="0" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="165" fontId="7" fillId="0" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="164" fontId="7" fillId="3" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="164" fontId="6" fillId="4" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="164" fontId="6" fillId="3" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="164" fontId="6" fillId="0" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="166" fontId="6" fillId="0" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="164" fontId="7" fillId="4" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="164" fontId="7" fillId="0" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="164" fontId="8" fillId="3" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="164" fontId="9" fillId="4" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="166" fontId="7" fillId="0" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="164" fontId="9" fillId="4" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="1" fontId="4" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="right"/>
     </xf>
@@ -222,10 +221,10 @@
     <xf numFmtId="167" fontId="4" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="right"/>
     </xf>
-    <xf numFmtId="167" fontId="6" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="167" fontId="7" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="right"/>
     </xf>
-    <xf numFmtId="167" fontId="7" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="167" fontId="6" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="right"/>
     </xf>
     <xf numFmtId="2" fontId="4" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
@@ -811,7 +810,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
-  <dimension ref="A1:O54"/>
+  <dimension ref="A1:O50"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="40" customWidth="1" min="1" max="1"/>
@@ -839,7 +838,7 @@
       </c>
     </row>
     <row r="3">
-      <c r="A3" s="13" t="inlineStr">
+      <c r="A3" s="12" t="inlineStr">
         <is>
           <t>MONTHLY returns (% of capital at start of month)</t>
         </is>
@@ -937,47 +936,43 @@
       <c r="J5" s="6" t="n"/>
       <c r="K5" s="6" t="n"/>
       <c r="L5" s="6" t="n"/>
-      <c r="M5" s="14" t="n">
-        <v>-0.0355045</v>
-      </c>
-      <c r="N5" s="18" t="n">
-        <v>-0.03550450000000005</v>
-      </c>
-      <c r="O5" s="20" t="n">
-        <v>-710.09</v>
+      <c r="M5" s="13" t="n">
+        <v>-0.0469125</v>
+      </c>
+      <c r="N5" s="14" t="n">
+        <v>-0.04691250000000002</v>
+      </c>
+      <c r="O5" s="15" t="n">
+        <v>-938.25</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" s="3" t="n">
         <v>2026</v>
       </c>
-      <c r="B6" s="14" t="n">
-        <v>-0.01746560766742821</v>
+      <c r="B6" s="13" t="n">
+        <v>-0.01505685469592246</v>
       </c>
       <c r="C6" s="6" t="n"/>
-      <c r="D6" s="14" t="n">
-        <v>-0.00397509629082467</v>
-      </c>
-      <c r="E6" s="6" t="n"/>
-      <c r="F6" s="15" t="n">
-        <v>0.02902955133210366</v>
-      </c>
+      <c r="D6" s="6" t="n"/>
+      <c r="E6" s="16" t="n">
+        <v>0.01262227865738753</v>
+      </c>
+      <c r="F6" s="6" t="n"/>
       <c r="G6" s="6" t="n"/>
       <c r="H6" s="6" t="n"/>
-      <c r="I6" s="14" t="n">
-        <v>-0.02922524679972429</v>
-      </c>
-      <c r="J6" s="6" t="n"/>
-      <c r="K6" s="14" t="n">
-        <v>-0.01980225846393696</v>
-      </c>
+      <c r="I6" s="6" t="n"/>
+      <c r="J6" s="13" t="n">
+        <v>-0.01216670559002552</v>
+      </c>
+      <c r="K6" s="6" t="n"/>
       <c r="L6" s="6" t="n"/>
       <c r="M6" s="6" t="n"/>
-      <c r="N6" s="18" t="n">
-        <v>-0.04175187960959892</v>
-      </c>
-      <c r="O6" s="20" t="n">
-        <v>-805.39</v>
+      <c r="N6" s="14" t="n">
+        <v>-0.01475940036985068</v>
+      </c>
+      <c r="O6" s="15" t="n">
+        <v>-281.34</v>
       </c>
     </row>
     <row r="7">
@@ -986,33 +981,29 @@
           <t>Avg</t>
         </is>
       </c>
-      <c r="B7" s="18" t="n">
-        <v>-0.01746560766742821</v>
+      <c r="B7" s="14" t="n">
+        <v>-0.01505685469592246</v>
       </c>
       <c r="C7" s="6" t="n"/>
-      <c r="D7" s="18" t="n">
-        <v>-0.00397509629082467</v>
-      </c>
-      <c r="E7" s="6" t="n"/>
-      <c r="F7" s="16" t="n">
-        <v>0.02902955133210366</v>
-      </c>
+      <c r="D7" s="6" t="n"/>
+      <c r="E7" s="17" t="n">
+        <v>0.01262227865738753</v>
+      </c>
+      <c r="F7" s="6" t="n"/>
       <c r="G7" s="6" t="n"/>
       <c r="H7" s="6" t="n"/>
-      <c r="I7" s="18" t="n">
-        <v>-0.02922524679972429</v>
-      </c>
-      <c r="J7" s="6" t="n"/>
-      <c r="K7" s="18" t="n">
-        <v>-0.01980225846393696</v>
-      </c>
+      <c r="I7" s="6" t="n"/>
+      <c r="J7" s="14" t="n">
+        <v>-0.01216670559002552</v>
+      </c>
+      <c r="K7" s="6" t="n"/>
       <c r="L7" s="6" t="n"/>
-      <c r="M7" s="18" t="n">
-        <v>-0.0355045</v>
+      <c r="M7" s="14" t="n">
+        <v>-0.0469125</v>
       </c>
     </row>
     <row r="9">
-      <c r="A9" s="13" t="inlineStr">
+      <c r="A9" s="12" t="inlineStr">
         <is>
           <t>WEEKLY returns (% of capital at start of that week; weeks split at month edges)</t>
         </is>
@@ -1071,19 +1062,21 @@
           <t>2025-Dec</t>
         </is>
       </c>
-      <c r="B11" s="14" t="n">
-        <v>-0.0355045</v>
-      </c>
-      <c r="C11" s="6" t="n"/>
+      <c r="B11" s="13" t="n">
+        <v>-0.010346</v>
+      </c>
+      <c r="C11" s="13" t="n">
+        <v>-0.0369487719950609</v>
+      </c>
       <c r="D11" s="6" t="n"/>
       <c r="E11" s="6" t="n"/>
       <c r="F11" s="6" t="n"/>
       <c r="G11" s="6" t="n"/>
-      <c r="H11" s="19" t="n">
-        <v>-0.0355045</v>
-      </c>
-      <c r="I11" s="20" t="n">
-        <v>-710.09</v>
+      <c r="H11" s="18" t="n">
+        <v>-0.0469125</v>
+      </c>
+      <c r="I11" s="15" t="n">
+        <v>-938.25</v>
       </c>
     </row>
     <row r="12">
@@ -1092,29 +1085,29 @@
           <t>2026-Jan</t>
         </is>
       </c>
-      <c r="B12" s="14" t="n">
-        <v>-0.01746560766742821</v>
+      <c r="B12" s="13" t="n">
+        <v>-0.01505685469592246</v>
       </c>
       <c r="C12" s="6" t="n"/>
       <c r="D12" s="6" t="n"/>
       <c r="E12" s="6" t="n"/>
       <c r="F12" s="6" t="n"/>
       <c r="G12" s="6" t="n"/>
-      <c r="H12" s="19" t="n">
-        <v>-0.01746560766742821</v>
-      </c>
-      <c r="I12" s="20" t="n">
-        <v>-336.91</v>
+      <c r="H12" s="18" t="n">
+        <v>-0.01505685469592246</v>
+      </c>
+      <c r="I12" s="15" t="n">
+        <v>-287.01</v>
       </c>
     </row>
     <row r="13">
       <c r="A13" s="3" t="inlineStr">
         <is>
-          <t>2026-Mar</t>
-        </is>
-      </c>
-      <c r="B13" s="14" t="n">
-        <v>-0.00397509629082467</v>
+          <t>2026-Apr</t>
+        </is>
+      </c>
+      <c r="B13" s="16" t="n">
+        <v>0.01262227865738753</v>
       </c>
       <c r="C13" s="6" t="n"/>
       <c r="D13" s="6" t="n"/>
@@ -1122,567 +1115,483 @@
       <c r="F13" s="6" t="n"/>
       <c r="G13" s="6" t="n"/>
       <c r="H13" s="19" t="n">
-        <v>-0.00397509629082467</v>
+        <v>0.01262227865738753</v>
       </c>
       <c r="I13" s="20" t="n">
-        <v>-75.34</v>
+        <v>236.98</v>
       </c>
     </row>
     <row r="14">
       <c r="A14" s="3" t="inlineStr">
         <is>
-          <t>2026-May</t>
-        </is>
-      </c>
-      <c r="B14" s="15" t="n">
-        <v>0.02902955133210366</v>
+          <t>2026-Sep</t>
+        </is>
+      </c>
+      <c r="B14" s="13" t="n">
+        <v>-0.01216670559002552</v>
       </c>
       <c r="C14" s="6" t="n"/>
       <c r="D14" s="6" t="n"/>
       <c r="E14" s="6" t="n"/>
       <c r="F14" s="6" t="n"/>
       <c r="G14" s="6" t="n"/>
-      <c r="H14" s="21" t="n">
-        <v>0.02902955133210366</v>
-      </c>
-      <c r="I14" s="17" t="n">
-        <v>548.01</v>
-      </c>
-    </row>
-    <row r="15">
-      <c r="A15" s="3" t="inlineStr">
-        <is>
-          <t>2026-Aug</t>
-        </is>
-      </c>
-      <c r="B15" s="14" t="n">
-        <v>-0.01826964012052094</v>
-      </c>
-      <c r="C15" s="14" t="n">
-        <v>-0.01115948648114366</v>
-      </c>
-      <c r="D15" s="6" t="n"/>
-      <c r="E15" s="6" t="n"/>
-      <c r="F15" s="6" t="n"/>
-      <c r="G15" s="6" t="n"/>
-      <c r="H15" s="19" t="n">
-        <v>-0.02922524679972429</v>
-      </c>
-      <c r="I15" s="20" t="n">
-        <v>-567.72</v>
+      <c r="H14" s="18" t="n">
+        <v>-0.01216670559002552</v>
+      </c>
+      <c r="I14" s="15" t="n">
+        <v>-231.31</v>
       </c>
     </row>
     <row r="16">
-      <c r="A16" s="3" t="inlineStr">
-        <is>
-          <t>2026-Oct</t>
-        </is>
-      </c>
-      <c r="B16" s="14" t="n">
-        <v>-0.01980225846393696</v>
-      </c>
-      <c r="C16" s="6" t="n"/>
-      <c r="D16" s="6" t="n"/>
-      <c r="E16" s="6" t="n"/>
-      <c r="F16" s="6" t="n"/>
-      <c r="G16" s="6" t="n"/>
-      <c r="H16" s="19" t="n">
-        <v>-0.01980225846393696</v>
-      </c>
-      <c r="I16" s="20" t="n">
-        <v>-373.43</v>
+      <c r="A16" s="12" t="inlineStr">
+        <is>
+          <t>DAILY returns (% of capital at start of that day; blank = no trade that day)</t>
+        </is>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" s="2" t="inlineStr">
+        <is>
+          <t>Week starting (Mon)</t>
+        </is>
+      </c>
+      <c r="B17" s="2" t="inlineStr">
+        <is>
+          <t>Mon</t>
+        </is>
+      </c>
+      <c r="C17" s="2" t="inlineStr">
+        <is>
+          <t>Tue</t>
+        </is>
+      </c>
+      <c r="D17" s="2" t="inlineStr">
+        <is>
+          <t>Wed</t>
+        </is>
+      </c>
+      <c r="E17" s="2" t="inlineStr">
+        <is>
+          <t>Thu</t>
+        </is>
+      </c>
+      <c r="F17" s="2" t="inlineStr">
+        <is>
+          <t>Fri</t>
+        </is>
+      </c>
+      <c r="G17" s="2" t="inlineStr">
+        <is>
+          <t>Week %</t>
+        </is>
+      </c>
+      <c r="H17" s="2" t="inlineStr">
+        <is>
+          <t>Week P&amp;L (Rs)</t>
+        </is>
       </c>
     </row>
     <row r="18">
-      <c r="A18" s="13" t="inlineStr">
-        <is>
-          <t>DAILY returns (% of capital at start of that day; blank = no trade that day)</t>
-        </is>
+      <c r="A18" s="3" t="inlineStr">
+        <is>
+          <t>01-Dec-2025</t>
+        </is>
+      </c>
+      <c r="B18" s="6" t="n"/>
+      <c r="C18" s="13" t="n">
+        <v>-0.010346</v>
+      </c>
+      <c r="D18" s="6" t="n"/>
+      <c r="E18" s="6" t="n"/>
+      <c r="F18" s="6" t="n"/>
+      <c r="G18" s="18" t="n">
+        <v>-0.010346</v>
+      </c>
+      <c r="H18" s="15" t="n">
+        <v>-206.92</v>
       </c>
     </row>
     <row r="19">
-      <c r="A19" s="2" t="inlineStr">
-        <is>
-          <t>Week starting (Mon)</t>
-        </is>
-      </c>
-      <c r="B19" s="2" t="inlineStr">
-        <is>
-          <t>Mon</t>
-        </is>
-      </c>
-      <c r="C19" s="2" t="inlineStr">
-        <is>
-          <t>Tue</t>
-        </is>
-      </c>
-      <c r="D19" s="2" t="inlineStr">
-        <is>
-          <t>Wed</t>
-        </is>
-      </c>
-      <c r="E19" s="2" t="inlineStr">
-        <is>
-          <t>Thu</t>
-        </is>
-      </c>
-      <c r="F19" s="2" t="inlineStr">
-        <is>
-          <t>Fri</t>
-        </is>
-      </c>
-      <c r="G19" s="2" t="inlineStr">
-        <is>
-          <t>Week %</t>
-        </is>
-      </c>
-      <c r="H19" s="2" t="inlineStr">
-        <is>
-          <t>Week P&amp;L (Rs)</t>
-        </is>
+      <c r="A19" s="3" t="inlineStr">
+        <is>
+          <t>08-Dec-2025</t>
+        </is>
+      </c>
+      <c r="B19" s="6" t="n"/>
+      <c r="C19" s="13" t="n">
+        <v>-0.0369487719950609</v>
+      </c>
+      <c r="D19" s="6" t="n"/>
+      <c r="E19" s="6" t="n"/>
+      <c r="F19" s="6" t="n"/>
+      <c r="G19" s="18" t="n">
+        <v>-0.0369487719950609</v>
+      </c>
+      <c r="H19" s="15" t="n">
+        <v>-731.33</v>
       </c>
     </row>
     <row r="20">
       <c r="A20" s="3" t="inlineStr">
         <is>
-          <t>29-Dec-2025</t>
+          <t>26-Jan-2026</t>
         </is>
       </c>
       <c r="B20" s="6" t="n"/>
-      <c r="C20" s="14" t="n">
-        <v>-0.0355045</v>
+      <c r="C20" s="13" t="n">
+        <v>-0.01505685469592246</v>
       </c>
       <c r="D20" s="6" t="n"/>
       <c r="E20" s="6" t="n"/>
       <c r="F20" s="6" t="n"/>
-      <c r="G20" s="19" t="n">
-        <v>-0.0355045</v>
-      </c>
-      <c r="H20" s="20" t="n">
-        <v>-710.09</v>
+      <c r="G20" s="18" t="n">
+        <v>-0.01505685469592246</v>
+      </c>
+      <c r="H20" s="15" t="n">
+        <v>-287.01</v>
       </c>
     </row>
     <row r="21">
       <c r="A21" s="3" t="inlineStr">
         <is>
-          <t>26-Jan-2026</t>
+          <t>06-Apr-2026</t>
         </is>
       </c>
       <c r="B21" s="6" t="n"/>
-      <c r="C21" s="14" t="n">
-        <v>-0.01746560766742821</v>
+      <c r="C21" s="16" t="n">
+        <v>0.01262227865738753</v>
       </c>
       <c r="D21" s="6" t="n"/>
       <c r="E21" s="6" t="n"/>
       <c r="F21" s="6" t="n"/>
       <c r="G21" s="19" t="n">
-        <v>-0.01746560766742821</v>
+        <v>0.01262227865738753</v>
       </c>
       <c r="H21" s="20" t="n">
-        <v>-336.91</v>
+        <v>236.98</v>
       </c>
     </row>
     <row r="22">
       <c r="A22" s="3" t="inlineStr">
         <is>
-          <t>23-Mar-2026</t>
+          <t>07-Sep-2026</t>
         </is>
       </c>
       <c r="B22" s="6" t="n"/>
-      <c r="C22" s="14" t="n">
-        <v>-0.00397509629082467</v>
+      <c r="C22" s="13" t="n">
+        <v>-0.01216670559002552</v>
       </c>
       <c r="D22" s="6" t="n"/>
       <c r="E22" s="6" t="n"/>
       <c r="F22" s="6" t="n"/>
-      <c r="G22" s="19" t="n">
-        <v>-0.00397509629082467</v>
-      </c>
-      <c r="H22" s="20" t="n">
-        <v>-75.34</v>
-      </c>
-    </row>
-    <row r="23">
-      <c r="A23" s="3" t="inlineStr">
-        <is>
-          <t>11-May-2026</t>
-        </is>
-      </c>
-      <c r="B23" s="6" t="n"/>
-      <c r="C23" s="15" t="n">
-        <v>0.02902955133210366</v>
-      </c>
-      <c r="D23" s="6" t="n"/>
-      <c r="E23" s="6" t="n"/>
-      <c r="F23" s="6" t="n"/>
-      <c r="G23" s="21" t="n">
-        <v>0.02902955133210366</v>
-      </c>
-      <c r="H23" s="17" t="n">
-        <v>548.01</v>
+      <c r="G22" s="18" t="n">
+        <v>-0.01216670559002552</v>
+      </c>
+      <c r="H22" s="15" t="n">
+        <v>-231.31</v>
       </c>
     </row>
     <row r="24">
-      <c r="A24" s="3" t="inlineStr">
-        <is>
-          <t>10-Aug-2026</t>
-        </is>
-      </c>
-      <c r="B24" s="6" t="n"/>
-      <c r="C24" s="14" t="n">
-        <v>-0.01826964012052094</v>
-      </c>
-      <c r="D24" s="6" t="n"/>
-      <c r="E24" s="6" t="n"/>
-      <c r="F24" s="6" t="n"/>
-      <c r="G24" s="19" t="n">
-        <v>-0.01826964012052094</v>
-      </c>
-      <c r="H24" s="20" t="n">
-        <v>-354.9</v>
+      <c r="A24" s="12" t="inlineStr">
+        <is>
+          <t>STATISTICS (all trades for this index)</t>
+        </is>
       </c>
     </row>
     <row r="25">
       <c r="A25" s="3" t="inlineStr">
         <is>
-          <t>24-Aug-2026</t>
-        </is>
-      </c>
-      <c r="B25" s="6" t="n"/>
-      <c r="C25" s="14" t="n">
-        <v>-0.01115948648114366</v>
-      </c>
-      <c r="D25" s="6" t="n"/>
-      <c r="E25" s="6" t="n"/>
-      <c r="F25" s="6" t="n"/>
-      <c r="G25" s="19" t="n">
-        <v>-0.01115948648114366</v>
-      </c>
-      <c r="H25" s="20" t="n">
-        <v>-212.82</v>
-      </c>
+          <t>All trades</t>
+        </is>
+      </c>
+      <c r="B25" s="21" t="n">
+        <v>7</v>
+      </c>
+      <c r="C25" s="22" t="n"/>
+      <c r="D25" s="23" t="n"/>
     </row>
     <row r="26">
       <c r="A26" s="3" t="inlineStr">
         <is>
-          <t>12-Oct-2026</t>
-        </is>
-      </c>
-      <c r="B26" s="6" t="n"/>
-      <c r="C26" s="14" t="n">
-        <v>-0.01980225846393696</v>
-      </c>
-      <c r="D26" s="6" t="n"/>
-      <c r="E26" s="6" t="n"/>
-      <c r="F26" s="6" t="n"/>
-      <c r="G26" s="19" t="n">
-        <v>-0.01980225846393696</v>
-      </c>
-      <c r="H26" s="20" t="n">
-        <v>-373.43</v>
-      </c>
+          <t>Winners</t>
+        </is>
+      </c>
+      <c r="B26" s="24" t="inlineStr">
+        <is>
+          <t>1 (14.3%)</t>
+        </is>
+      </c>
+      <c r="C26" s="22" t="n"/>
+      <c r="D26" s="23" t="n"/>
+    </row>
+    <row r="27">
+      <c r="A27" s="3" t="inlineStr">
+        <is>
+          <t>Losers</t>
+        </is>
+      </c>
+      <c r="B27" s="24" t="inlineStr">
+        <is>
+          <t>6 (85.7%)</t>
+        </is>
+      </c>
+      <c r="C27" s="22" t="n"/>
+      <c r="D27" s="23" t="n"/>
     </row>
     <row r="28">
-      <c r="A28" s="13" t="inlineStr">
-        <is>
-          <t>STATISTICS (all trades for this index)</t>
-        </is>
-      </c>
+      <c r="A28" s="3" t="inlineStr">
+        <is>
+          <t>Net P&amp;L (Rs)</t>
+        </is>
+      </c>
+      <c r="B28" s="25" t="n">
+        <v>-1219.59</v>
+      </c>
+      <c r="C28" s="22" t="n"/>
+      <c r="D28" s="23" t="n"/>
     </row>
     <row r="29">
       <c r="A29" s="3" t="inlineStr">
         <is>
-          <t>All trades</t>
-        </is>
-      </c>
-      <c r="B29" s="22" t="n">
-        <v>11</v>
-      </c>
-      <c r="C29" s="23" t="n"/>
-      <c r="D29" s="24" t="n"/>
+          <t>Total Profit (Rs)</t>
+        </is>
+      </c>
+      <c r="B29" s="26" t="n">
+        <v>236.98</v>
+      </c>
+      <c r="C29" s="22" t="n"/>
+      <c r="D29" s="23" t="n"/>
     </row>
     <row r="30">
       <c r="A30" s="3" t="inlineStr">
         <is>
-          <t>Winners</t>
-        </is>
-      </c>
-      <c r="B30" s="25" t="inlineStr">
-        <is>
-          <t>2 (18.2%)</t>
-        </is>
-      </c>
-      <c r="C30" s="23" t="n"/>
-      <c r="D30" s="24" t="n"/>
+          <t>Total Loss (Rs)</t>
+        </is>
+      </c>
+      <c r="B30" s="25" t="n">
+        <v>-1456.57</v>
+      </c>
+      <c r="C30" s="22" t="n"/>
+      <c r="D30" s="23" t="n"/>
     </row>
     <row r="31">
       <c r="A31" s="3" t="inlineStr">
         <is>
-          <t>Losers</t>
-        </is>
-      </c>
-      <c r="B31" s="25" t="inlineStr">
-        <is>
-          <t>9 (81.8%)</t>
-        </is>
-      </c>
-      <c r="C31" s="23" t="n"/>
-      <c r="D31" s="24" t="n"/>
+          <t>Transaction costs (Rs)</t>
+        </is>
+      </c>
+      <c r="B31" s="27" t="n">
+        <v>348.39</v>
+      </c>
+      <c r="C31" s="22" t="n"/>
+      <c r="D31" s="23" t="n"/>
     </row>
     <row r="32">
       <c r="A32" s="3" t="inlineStr">
         <is>
-          <t>Net P&amp;L (Rs)</t>
-        </is>
-      </c>
-      <c r="B32" s="27" t="n">
-        <v>-1515.48</v>
-      </c>
-      <c r="C32" s="23" t="n"/>
-      <c r="D32" s="24" t="n"/>
+          <t>Avg Profit/Loss per trade (Rs)</t>
+        </is>
+      </c>
+      <c r="B32" s="25" t="n">
+        <v>-174.23</v>
+      </c>
+      <c r="C32" s="22" t="n"/>
+      <c r="D32" s="23" t="n"/>
     </row>
     <row r="33">
       <c r="A33" s="3" t="inlineStr">
         <is>
-          <t>Total Profit (Rs)</t>
-        </is>
-      </c>
-      <c r="B33" s="26" t="n">
-        <v>1040.37</v>
-      </c>
-      <c r="C33" s="23" t="n"/>
-      <c r="D33" s="24" t="n"/>
+          <t>Avg Profit/Loss per trade (% of premium)</t>
+        </is>
+      </c>
+      <c r="B33" s="28" t="n">
+        <v>-10.42</v>
+      </c>
+      <c r="C33" s="22" t="n"/>
+      <c r="D33" s="23" t="n"/>
     </row>
     <row r="34">
       <c r="A34" s="3" t="inlineStr">
         <is>
-          <t>Total Loss (Rs)</t>
-        </is>
-      </c>
-      <c r="B34" s="27" t="n">
-        <v>-2555.85</v>
-      </c>
-      <c r="C34" s="23" t="n"/>
-      <c r="D34" s="24" t="n"/>
+          <t>Avg Win (Rs)</t>
+        </is>
+      </c>
+      <c r="B34" s="26" t="n">
+        <v>236.98</v>
+      </c>
+      <c r="C34" s="22" t="n"/>
+      <c r="D34" s="23" t="n"/>
     </row>
     <row r="35">
       <c r="A35" s="3" t="inlineStr">
         <is>
-          <t>Transaction costs (Rs)</t>
-        </is>
-      </c>
-      <c r="B35" s="28" t="n">
-        <v>508.23</v>
-      </c>
-      <c r="C35" s="23" t="n"/>
-      <c r="D35" s="24" t="n"/>
+          <t>Avg Win (% of premium)</t>
+        </is>
+      </c>
+      <c r="B35" s="29" t="n">
+        <v>16.17</v>
+      </c>
+      <c r="C35" s="22" t="n"/>
+      <c r="D35" s="23" t="n"/>
     </row>
     <row r="36">
       <c r="A36" s="3" t="inlineStr">
         <is>
-          <t>Avg Profit/Loss per trade (Rs)</t>
-        </is>
-      </c>
-      <c r="B36" s="27" t="n">
-        <v>-137.77</v>
-      </c>
-      <c r="C36" s="23" t="n"/>
-      <c r="D36" s="24" t="n"/>
+          <t>Avg Loss (Rs)</t>
+        </is>
+      </c>
+      <c r="B36" s="25" t="n">
+        <v>-242.76</v>
+      </c>
+      <c r="C36" s="22" t="n"/>
+      <c r="D36" s="23" t="n"/>
     </row>
     <row r="37">
       <c r="A37" s="3" t="inlineStr">
         <is>
-          <t>Avg Profit/Loss per trade (% of premium)</t>
-        </is>
-      </c>
-      <c r="B37" s="29" t="n">
-        <v>-6.91</v>
-      </c>
-      <c r="C37" s="23" t="n"/>
-      <c r="D37" s="24" t="n"/>
+          <t>Avg Loss (% of premium)</t>
+        </is>
+      </c>
+      <c r="B37" s="30" t="n">
+        <v>-14.85</v>
+      </c>
+      <c r="C37" s="22" t="n"/>
+      <c r="D37" s="23" t="n"/>
     </row>
     <row r="38">
       <c r="A38" s="3" t="inlineStr">
         <is>
-          <t>Avg Win (Rs)</t>
+          <t>Largest Win (Rs)</t>
         </is>
       </c>
       <c r="B38" s="26" t="n">
-        <v>520.1799999999999</v>
-      </c>
-      <c r="C38" s="23" t="n"/>
-      <c r="D38" s="24" t="n"/>
+        <v>236.98</v>
+      </c>
+      <c r="C38" s="22" t="n"/>
+      <c r="D38" s="23" t="n"/>
     </row>
     <row r="39">
       <c r="A39" s="3" t="inlineStr">
         <is>
-          <t>Avg Win (% of premium)</t>
-        </is>
-      </c>
-      <c r="B39" s="30" t="n">
-        <v>54.92</v>
-      </c>
-      <c r="C39" s="23" t="n"/>
-      <c r="D39" s="24" t="n"/>
+          <t>Largest Loss (Rs)</t>
+        </is>
+      </c>
+      <c r="B39" s="25" t="n">
+        <v>-295.95</v>
+      </c>
+      <c r="C39" s="22" t="n"/>
+      <c r="D39" s="23" t="n"/>
     </row>
     <row r="40">
       <c r="A40" s="3" t="inlineStr">
         <is>
-          <t>Avg Loss (Rs)</t>
-        </is>
-      </c>
-      <c r="B40" s="27" t="n">
-        <v>-283.98</v>
-      </c>
-      <c r="C40" s="23" t="n"/>
-      <c r="D40" s="24" t="n"/>
+          <t>Max Consecutive Wins</t>
+        </is>
+      </c>
+      <c r="B40" s="21" t="n">
+        <v>1</v>
+      </c>
+      <c r="C40" s="22" t="n"/>
+      <c r="D40" s="23" t="n"/>
     </row>
     <row r="41">
       <c r="A41" s="3" t="inlineStr">
         <is>
-          <t>Avg Loss (% of premium)</t>
-        </is>
-      </c>
-      <c r="B41" s="31" t="n">
-        <v>-20.65</v>
-      </c>
-      <c r="C41" s="23" t="n"/>
-      <c r="D41" s="24" t="n"/>
+          <t>Max Consecutive Losses</t>
+        </is>
+      </c>
+      <c r="B41" s="21" t="n">
+        <v>5</v>
+      </c>
+      <c r="C41" s="22" t="n"/>
+      <c r="D41" s="23" t="n"/>
     </row>
     <row r="42">
       <c r="A42" s="3" t="inlineStr">
         <is>
-          <t>Largest Win (Rs)</t>
-        </is>
-      </c>
-      <c r="B42" s="26" t="n">
-        <v>548.01</v>
-      </c>
-      <c r="C42" s="23" t="n"/>
-      <c r="D42" s="24" t="n"/>
+          <t>Max trade drawdown (Rs)</t>
+        </is>
+      </c>
+      <c r="B42" s="25" t="n">
+        <v>-295.95</v>
+      </c>
+      <c r="C42" s="22" t="n"/>
+      <c r="D42" s="23" t="n"/>
     </row>
     <row r="43">
       <c r="A43" s="3" t="inlineStr">
         <is>
-          <t>Largest Loss (Rs)</t>
-        </is>
-      </c>
-      <c r="B43" s="27" t="n">
-        <v>-358.86</v>
-      </c>
-      <c r="C43" s="23" t="n"/>
-      <c r="D43" s="24" t="n"/>
+          <t>Max system drawdown (Rs)</t>
+        </is>
+      </c>
+      <c r="B43" s="25" t="n">
+        <v>-1225.26</v>
+      </c>
+      <c r="C43" s="22" t="n"/>
+      <c r="D43" s="23" t="n"/>
     </row>
     <row r="44">
       <c r="A44" s="3" t="inlineStr">
         <is>
-          <t>Max Consecutive Wins</t>
-        </is>
-      </c>
-      <c r="B44" s="22" t="n">
-        <v>1</v>
-      </c>
-      <c r="C44" s="23" t="n"/>
-      <c r="D44" s="24" t="n"/>
+          <t>Max system drawdown (%)</t>
+        </is>
+      </c>
+      <c r="B44" s="30" t="n">
+        <v>-6.13</v>
+      </c>
+      <c r="C44" s="22" t="n"/>
+      <c r="D44" s="23" t="n"/>
     </row>
     <row r="45">
       <c r="A45" s="3" t="inlineStr">
         <is>
-          <t>Max Consecutive Losses</t>
-        </is>
-      </c>
-      <c r="B45" s="22" t="n">
-        <v>7</v>
-      </c>
-      <c r="C45" s="23" t="n"/>
-      <c r="D45" s="24" t="n"/>
+          <t>Recovery Factor</t>
+        </is>
+      </c>
+      <c r="B45" s="31" t="n">
+        <v>-1</v>
+      </c>
+      <c r="C45" s="22" t="n"/>
+      <c r="D45" s="23" t="n"/>
     </row>
     <row r="46">
       <c r="A46" s="3" t="inlineStr">
         <is>
-          <t>Max trade drawdown (Rs)</t>
-        </is>
-      </c>
-      <c r="B46" s="27" t="n">
-        <v>-358.86</v>
-      </c>
-      <c r="C46" s="23" t="n"/>
-      <c r="D46" s="24" t="n"/>
+          <t>Profit Factor</t>
+        </is>
+      </c>
+      <c r="B46" s="31" t="n">
+        <v>0.16</v>
+      </c>
+      <c r="C46" s="22" t="n"/>
+      <c r="D46" s="23" t="n"/>
     </row>
     <row r="47">
       <c r="A47" s="3" t="inlineStr">
         <is>
-          <t>Max system drawdown (Rs)</t>
-        </is>
-      </c>
-      <c r="B47" s="27" t="n">
-        <v>-1988.15</v>
-      </c>
-      <c r="C47" s="23" t="n"/>
-      <c r="D47" s="24" t="n"/>
+          <t>Payoff Ratio (avg win / avg loss)</t>
+        </is>
+      </c>
+      <c r="B47" s="31" t="n">
+        <v>0.98</v>
+      </c>
+      <c r="C47" s="22" t="n"/>
+      <c r="D47" s="23" t="n"/>
     </row>
     <row r="48">
       <c r="A48" s="3" t="inlineStr">
         <is>
-          <t>Max system drawdown (%)</t>
+          <t>Sharpe Ratio (annualized)</t>
         </is>
       </c>
       <c r="B48" s="31" t="n">
-        <v>-9.710000000000001</v>
-      </c>
-      <c r="C48" s="23" t="n"/>
-      <c r="D48" s="24" t="n"/>
-    </row>
-    <row r="49">
-      <c r="A49" s="3" t="inlineStr">
-        <is>
-          <t>Recovery Factor</t>
-        </is>
-      </c>
-      <c r="B49" s="32" t="n">
-        <v>-0.76</v>
-      </c>
-      <c r="C49" s="23" t="n"/>
-      <c r="D49" s="24" t="n"/>
+        <v>-12.48</v>
+      </c>
+      <c r="C48" s="22" t="n"/>
+      <c r="D48" s="23" t="n"/>
     </row>
     <row r="50">
-      <c r="A50" s="3" t="inlineStr">
-        <is>
-          <t>Profit Factor</t>
-        </is>
-      </c>
-      <c r="B50" s="32" t="n">
-        <v>0.41</v>
-      </c>
-      <c r="C50" s="23" t="n"/>
-      <c r="D50" s="24" t="n"/>
-    </row>
-    <row r="51">
-      <c r="A51" s="3" t="inlineStr">
-        <is>
-          <t>Payoff Ratio (avg win / avg loss)</t>
-        </is>
-      </c>
-      <c r="B51" s="32" t="n">
-        <v>1.83</v>
-      </c>
-      <c r="C51" s="23" t="n"/>
-      <c r="D51" s="24" t="n"/>
-    </row>
-    <row r="52">
-      <c r="A52" s="3" t="inlineStr">
-        <is>
-          <t>Sharpe Ratio (annualized)</t>
-        </is>
-      </c>
-      <c r="B52" s="32" t="n">
-        <v>-9.4</v>
-      </c>
-      <c r="C52" s="23" t="n"/>
-      <c r="D52" s="24" t="n"/>
-    </row>
-    <row r="54">
-      <c r="A54" s="5" t="inlineStr">
+      <c r="A50" s="5" t="inlineStr">
         <is>
           <t>Caveat: with only a handful of trades these numbers (Sharpe, profit factor, drawdown %) are not statistically reliable. Watch this over weeks/months before drawing conclusions.</t>
         </is>
@@ -1695,22 +1604,22 @@
     <mergeCell ref="B29:D29"/>
     <mergeCell ref="B38:D38"/>
     <mergeCell ref="B34:D34"/>
+    <mergeCell ref="B28:D28"/>
     <mergeCell ref="B37:D37"/>
-    <mergeCell ref="B49:D49"/>
     <mergeCell ref="B40:D40"/>
     <mergeCell ref="B30:D30"/>
-    <mergeCell ref="B51:D51"/>
     <mergeCell ref="B33:D33"/>
     <mergeCell ref="B36:D36"/>
     <mergeCell ref="B45:D45"/>
     <mergeCell ref="B41:D41"/>
     <mergeCell ref="B32:D32"/>
     <mergeCell ref="B35:D35"/>
-    <mergeCell ref="B50:D50"/>
+    <mergeCell ref="B26:D26"/>
+    <mergeCell ref="B25:D25"/>
     <mergeCell ref="B47:D47"/>
     <mergeCell ref="B31:D31"/>
     <mergeCell ref="B46:D46"/>
-    <mergeCell ref="B52:D52"/>
+    <mergeCell ref="B27:D27"/>
     <mergeCell ref="B43:D43"/>
     <mergeCell ref="B39:D39"/>
     <mergeCell ref="B48:D48"/>
@@ -1974,23 +1883,31 @@
       </c>
       <c r="B4" s="6" t="inlineStr">
         <is>
-          <t>vwap_ema_momentum (EMA9/13) [5m]</t>
-        </is>
-      </c>
-      <c r="C4" s="7" t="n">
-        <v>5</v>
-      </c>
-      <c r="D4" s="8" t="n">
-        <v>0.4</v>
-      </c>
-      <c r="E4" s="9" t="n">
-        <v>277.15</v>
-      </c>
-      <c r="F4" s="10" t="n">
-        <v>1.36</v>
-      </c>
-      <c r="G4" s="11" t="n">
-        <v>-0.01480658481386824</v>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="C4" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="D4" s="4" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="E4" s="4" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="F4" s="4" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="G4" s="4" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
     </row>
     <row r="5">
@@ -2001,23 +1918,31 @@
       </c>
       <c r="B5" s="6" t="inlineStr">
         <is>
-          <t>trend_scalp_nw (EMA5/21) [5m]</t>
-        </is>
-      </c>
-      <c r="C5" s="7" t="n">
-        <v>6</v>
-      </c>
-      <c r="D5" s="8" t="n">
+          <t>-</t>
+        </is>
+      </c>
+      <c r="C5" s="4" t="n">
         <v>0</v>
       </c>
-      <c r="E5" s="12" t="n">
-        <v>-1792.63</v>
-      </c>
-      <c r="F5" s="10" t="n">
-        <v>0</v>
-      </c>
-      <c r="G5" s="11" t="n">
-        <v>-0.08963150000000004</v>
+      <c r="D5" s="4" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="E5" s="4" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="F5" s="4" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="G5" s="4" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
     </row>
     <row r="6">
@@ -2028,31 +1953,23 @@
       </c>
       <c r="B6" s="6" t="inlineStr">
         <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="C6" s="4" t="n">
-        <v>0</v>
-      </c>
-      <c r="D6" s="4" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="E6" s="4" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="F6" s="4" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="G6" s="4" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+          <t>trend_scalp_nw (EMA9/26) [5m]</t>
+        </is>
+      </c>
+      <c r="C6" s="7" t="n">
+        <v>7</v>
+      </c>
+      <c r="D6" s="8" t="n">
+        <v>0.1428571428571428</v>
+      </c>
+      <c r="E6" s="9" t="n">
+        <v>-1219.59</v>
+      </c>
+      <c r="F6" s="10" t="n">
+        <v>0.16</v>
+      </c>
+      <c r="G6" s="11" t="n">
+        <v>-0.06126299999999993</v>
       </c>
     </row>
     <row r="7">
@@ -2067,19 +1984,19 @@
         </is>
       </c>
       <c r="C7" s="7" t="n">
-        <v>11</v>
+        <v>7</v>
       </c>
       <c r="D7" s="8" t="n">
-        <v>0.1818181818181818</v>
-      </c>
-      <c r="E7" s="12" t="n">
-        <v>-1515.48</v>
+        <v>0.1428571428571428</v>
+      </c>
+      <c r="E7" s="9" t="n">
+        <v>-1219.59</v>
       </c>
       <c r="F7" s="10" t="n">
-        <v>0.41</v>
+        <v>0.16</v>
       </c>
       <c r="G7" s="11" t="n">
-        <v>-0.09711239423094309</v>
+        <v>-0.06126299999999993</v>
       </c>
     </row>
     <row r="9">
@@ -2101,7 +2018,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
-  <dimension ref="A1:O46"/>
+  <dimension ref="A1:A3"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="40" customWidth="1" min="1" max="1"/>
@@ -2124,713 +2041,70 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>BACKTEST NIFTY -- best: vwap_ema_momentum (EMA9/13) [5m] -- PAPER TRADE, NOT REAL MONEY</t>
+          <t>BACKTEST NIFTY -- best:  -- PAPER TRADE, NOT REAL MONEY</t>
         </is>
       </c>
     </row>
     <row r="3">
-      <c r="A3" s="13" t="inlineStr">
-        <is>
-          <t>MONTHLY returns (% of capital at start of month)</t>
-        </is>
-      </c>
-    </row>
-    <row r="4">
-      <c r="A4" s="2" t="inlineStr">
-        <is>
-          <t>Year</t>
-        </is>
-      </c>
-      <c r="B4" s="2" t="inlineStr">
-        <is>
-          <t>Jan</t>
-        </is>
-      </c>
-      <c r="C4" s="2" t="inlineStr">
-        <is>
-          <t>Feb</t>
-        </is>
-      </c>
-      <c r="D4" s="2" t="inlineStr">
-        <is>
-          <t>Mar</t>
-        </is>
-      </c>
-      <c r="E4" s="2" t="inlineStr">
-        <is>
-          <t>Apr</t>
-        </is>
-      </c>
-      <c r="F4" s="2" t="inlineStr">
-        <is>
-          <t>May</t>
-        </is>
-      </c>
-      <c r="G4" s="2" t="inlineStr">
-        <is>
-          <t>Jun</t>
-        </is>
-      </c>
-      <c r="H4" s="2" t="inlineStr">
-        <is>
-          <t>Jul</t>
-        </is>
-      </c>
-      <c r="I4" s="2" t="inlineStr">
-        <is>
-          <t>Aug</t>
-        </is>
-      </c>
-      <c r="J4" s="2" t="inlineStr">
-        <is>
-          <t>Sep</t>
-        </is>
-      </c>
-      <c r="K4" s="2" t="inlineStr">
-        <is>
-          <t>Oct</t>
-        </is>
-      </c>
-      <c r="L4" s="2" t="inlineStr">
-        <is>
-          <t>Nov</t>
-        </is>
-      </c>
-      <c r="M4" s="2" t="inlineStr">
-        <is>
-          <t>Dec</t>
-        </is>
-      </c>
-      <c r="N4" s="2" t="inlineStr">
-        <is>
-          <t>Yr %</t>
-        </is>
-      </c>
-      <c r="O4" s="2" t="inlineStr">
-        <is>
-          <t>Yr P&amp;L (Rs)</t>
-        </is>
-      </c>
-    </row>
-    <row r="5">
-      <c r="A5" s="3" t="n">
-        <v>2026</v>
-      </c>
-      <c r="B5" s="6" t="n"/>
-      <c r="C5" s="6" t="n"/>
-      <c r="D5" s="14" t="n">
-        <v>-0.003766999999999999</v>
-      </c>
-      <c r="E5" s="6" t="n"/>
-      <c r="F5" s="15" t="n">
-        <v>0.02750410797474085</v>
-      </c>
-      <c r="G5" s="6" t="n"/>
-      <c r="H5" s="6" t="n"/>
-      <c r="I5" s="6" t="n"/>
-      <c r="J5" s="6" t="n"/>
-      <c r="K5" s="14" t="n">
-        <v>-0.009550293146912445</v>
-      </c>
-      <c r="L5" s="6" t="n"/>
-      <c r="M5" s="6" t="n"/>
-      <c r="N5" s="16" t="n">
-        <v>0.01385750000000008</v>
-      </c>
-      <c r="O5" s="17" t="n">
-        <v>277.15</v>
-      </c>
-    </row>
-    <row r="6">
-      <c r="A6" s="3" t="inlineStr">
-        <is>
-          <t>Avg</t>
-        </is>
-      </c>
-      <c r="B6" s="6" t="n"/>
-      <c r="C6" s="6" t="n"/>
-      <c r="D6" s="18" t="n">
-        <v>-0.003766999999999999</v>
-      </c>
-      <c r="E6" s="6" t="n"/>
-      <c r="F6" s="16" t="n">
-        <v>0.02750410797474085</v>
-      </c>
-      <c r="G6" s="6" t="n"/>
-      <c r="H6" s="6" t="n"/>
-      <c r="I6" s="6" t="n"/>
-      <c r="J6" s="6" t="n"/>
-      <c r="K6" s="18" t="n">
-        <v>-0.009550293146912445</v>
-      </c>
-      <c r="L6" s="6" t="n"/>
-      <c r="M6" s="6" t="n"/>
-    </row>
-    <row r="8">
-      <c r="A8" s="13" t="inlineStr">
-        <is>
-          <t>WEEKLY returns (% of capital at start of that week; weeks split at month edges)</t>
-        </is>
-      </c>
-    </row>
-    <row r="9">
-      <c r="A9" s="2" t="inlineStr">
-        <is>
-          <t>Month</t>
-        </is>
-      </c>
-      <c r="B9" s="2" t="inlineStr">
-        <is>
-          <t>W1</t>
-        </is>
-      </c>
-      <c r="C9" s="2" t="inlineStr">
-        <is>
-          <t>W2</t>
-        </is>
-      </c>
-      <c r="D9" s="2" t="inlineStr">
-        <is>
-          <t>W3</t>
-        </is>
-      </c>
-      <c r="E9" s="2" t="inlineStr">
-        <is>
-          <t>W4</t>
-        </is>
-      </c>
-      <c r="F9" s="2" t="inlineStr">
-        <is>
-          <t>W5</t>
-        </is>
-      </c>
-      <c r="G9" s="2" t="inlineStr">
-        <is>
-          <t>W6</t>
-        </is>
-      </c>
-      <c r="H9" s="2" t="inlineStr">
-        <is>
-          <t>Month %</t>
-        </is>
-      </c>
-      <c r="I9" s="2" t="inlineStr">
-        <is>
-          <t>Month P&amp;L (Rs)</t>
-        </is>
-      </c>
-    </row>
-    <row r="10">
-      <c r="A10" s="3" t="inlineStr">
-        <is>
-          <t>2026-Mar</t>
-        </is>
-      </c>
-      <c r="B10" s="14" t="n">
-        <v>-0.003766999999999999</v>
-      </c>
-      <c r="C10" s="6" t="n"/>
-      <c r="D10" s="6" t="n"/>
-      <c r="E10" s="6" t="n"/>
-      <c r="F10" s="6" t="n"/>
-      <c r="G10" s="6" t="n"/>
-      <c r="H10" s="19" t="n">
-        <v>-0.003766999999999999</v>
-      </c>
-      <c r="I10" s="20" t="n">
-        <v>-75.34</v>
-      </c>
-    </row>
-    <row r="11">
-      <c r="A11" s="3" t="inlineStr">
-        <is>
-          <t>2026-May</t>
-        </is>
-      </c>
-      <c r="B11" s="15" t="n">
-        <v>0.02750410797474085</v>
-      </c>
-      <c r="C11" s="6" t="n"/>
-      <c r="D11" s="6" t="n"/>
-      <c r="E11" s="6" t="n"/>
-      <c r="F11" s="6" t="n"/>
-      <c r="G11" s="6" t="n"/>
-      <c r="H11" s="21" t="n">
-        <v>0.02750410797474085</v>
-      </c>
-      <c r="I11" s="17" t="n">
-        <v>548.01</v>
-      </c>
-    </row>
-    <row r="12">
-      <c r="A12" s="3" t="inlineStr">
-        <is>
-          <t>2026-Oct</t>
-        </is>
-      </c>
-      <c r="B12" s="14" t="n">
-        <v>-0.009550293146912445</v>
-      </c>
-      <c r="C12" s="6" t="n"/>
-      <c r="D12" s="6" t="n"/>
-      <c r="E12" s="6" t="n"/>
-      <c r="F12" s="6" t="n"/>
-      <c r="G12" s="6" t="n"/>
-      <c r="H12" s="19" t="n">
-        <v>-0.009550293146912445</v>
-      </c>
-      <c r="I12" s="20" t="n">
-        <v>-195.52</v>
-      </c>
-    </row>
-    <row r="14">
-      <c r="A14" s="13" t="inlineStr">
-        <is>
-          <t>DAILY returns (% of capital at start of that day; blank = no trade that day)</t>
-        </is>
-      </c>
-    </row>
-    <row r="15">
-      <c r="A15" s="2" t="inlineStr">
-        <is>
-          <t>Week starting (Mon)</t>
-        </is>
-      </c>
-      <c r="B15" s="2" t="inlineStr">
-        <is>
-          <t>Mon</t>
-        </is>
-      </c>
-      <c r="C15" s="2" t="inlineStr">
-        <is>
-          <t>Tue</t>
-        </is>
-      </c>
-      <c r="D15" s="2" t="inlineStr">
-        <is>
-          <t>Wed</t>
-        </is>
-      </c>
-      <c r="E15" s="2" t="inlineStr">
-        <is>
-          <t>Thu</t>
-        </is>
-      </c>
-      <c r="F15" s="2" t="inlineStr">
-        <is>
-          <t>Fri</t>
-        </is>
-      </c>
-      <c r="G15" s="2" t="inlineStr">
-        <is>
-          <t>Week %</t>
-        </is>
-      </c>
-      <c r="H15" s="2" t="inlineStr">
-        <is>
-          <t>Week P&amp;L (Rs)</t>
-        </is>
-      </c>
-    </row>
-    <row r="16">
-      <c r="A16" s="3" t="inlineStr">
-        <is>
-          <t>23-Mar-2026</t>
-        </is>
-      </c>
-      <c r="B16" s="6" t="n"/>
-      <c r="C16" s="14" t="n">
-        <v>-0.003766999999999999</v>
-      </c>
-      <c r="D16" s="6" t="n"/>
-      <c r="E16" s="6" t="n"/>
-      <c r="F16" s="6" t="n"/>
-      <c r="G16" s="19" t="n">
-        <v>-0.003766999999999999</v>
-      </c>
-      <c r="H16" s="20" t="n">
-        <v>-75.34</v>
-      </c>
-    </row>
-    <row r="17">
-      <c r="A17" s="3" t="inlineStr">
-        <is>
-          <t>11-May-2026</t>
-        </is>
-      </c>
-      <c r="B17" s="6" t="n"/>
-      <c r="C17" s="15" t="n">
-        <v>0.02750410797474085</v>
-      </c>
-      <c r="D17" s="6" t="n"/>
-      <c r="E17" s="6" t="n"/>
-      <c r="F17" s="6" t="n"/>
-      <c r="G17" s="21" t="n">
-        <v>0.02750410797474085</v>
-      </c>
-      <c r="H17" s="17" t="n">
-        <v>548.01</v>
-      </c>
-    </row>
-    <row r="18">
-      <c r="A18" s="3" t="inlineStr">
-        <is>
-          <t>12-Oct-2026</t>
-        </is>
-      </c>
-      <c r="B18" s="6" t="n"/>
-      <c r="C18" s="14" t="n">
-        <v>-0.009550293146912445</v>
-      </c>
-      <c r="D18" s="6" t="n"/>
-      <c r="E18" s="6" t="n"/>
-      <c r="F18" s="6" t="n"/>
-      <c r="G18" s="19" t="n">
-        <v>-0.009550293146912445</v>
-      </c>
-      <c r="H18" s="20" t="n">
-        <v>-195.52</v>
-      </c>
-    </row>
-    <row r="20">
-      <c r="A20" s="13" t="inlineStr">
-        <is>
-          <t>STATISTICS (all trades for this index)</t>
-        </is>
-      </c>
-    </row>
-    <row r="21">
-      <c r="A21" s="3" t="inlineStr">
-        <is>
-          <t>All trades</t>
-        </is>
-      </c>
-      <c r="B21" s="22" t="n">
-        <v>5</v>
-      </c>
-      <c r="C21" s="23" t="n"/>
-      <c r="D21" s="24" t="n"/>
-    </row>
-    <row r="22">
-      <c r="A22" s="3" t="inlineStr">
-        <is>
-          <t>Winners</t>
-        </is>
-      </c>
-      <c r="B22" s="25" t="inlineStr">
-        <is>
-          <t>2 (40.0%)</t>
-        </is>
-      </c>
-      <c r="C22" s="23" t="n"/>
-      <c r="D22" s="24" t="n"/>
-    </row>
-    <row r="23">
-      <c r="A23" s="3" t="inlineStr">
-        <is>
-          <t>Losers</t>
-        </is>
-      </c>
-      <c r="B23" s="25" t="inlineStr">
-        <is>
-          <t>3 (60.0%)</t>
-        </is>
-      </c>
-      <c r="C23" s="23" t="n"/>
-      <c r="D23" s="24" t="n"/>
-    </row>
-    <row r="24">
-      <c r="A24" s="3" t="inlineStr">
-        <is>
-          <t>Net P&amp;L (Rs)</t>
-        </is>
-      </c>
-      <c r="B24" s="26" t="n">
-        <v>277.15</v>
-      </c>
-      <c r="C24" s="23" t="n"/>
-      <c r="D24" s="24" t="n"/>
-    </row>
-    <row r="25">
-      <c r="A25" s="3" t="inlineStr">
-        <is>
-          <t>Total Profit (Rs)</t>
-        </is>
-      </c>
-      <c r="B25" s="26" t="n">
-        <v>1040.37</v>
-      </c>
-      <c r="C25" s="23" t="n"/>
-      <c r="D25" s="24" t="n"/>
-    </row>
-    <row r="26">
-      <c r="A26" s="3" t="inlineStr">
-        <is>
-          <t>Total Loss (Rs)</t>
-        </is>
-      </c>
-      <c r="B26" s="27" t="n">
-        <v>-763.22</v>
-      </c>
-      <c r="C26" s="23" t="n"/>
-      <c r="D26" s="24" t="n"/>
-    </row>
-    <row r="27">
-      <c r="A27" s="3" t="inlineStr">
-        <is>
-          <t>Transaction costs (Rs)</t>
-        </is>
-      </c>
-      <c r="B27" s="28" t="n">
-        <v>143.6</v>
-      </c>
-      <c r="C27" s="23" t="n"/>
-      <c r="D27" s="24" t="n"/>
-    </row>
-    <row r="28">
-      <c r="A28" s="3" t="inlineStr">
-        <is>
-          <t>Avg Profit/Loss per trade (Rs)</t>
-        </is>
-      </c>
-      <c r="B28" s="26" t="n">
-        <v>55.43</v>
-      </c>
-      <c r="C28" s="23" t="n"/>
-      <c r="D28" s="24" t="n"/>
-    </row>
-    <row r="29">
-      <c r="A29" s="3" t="inlineStr">
-        <is>
-          <t>Avg Profit/Loss per trade (% of premium)</t>
-        </is>
-      </c>
-      <c r="B29" s="29" t="n">
-        <v>2.6</v>
-      </c>
-      <c r="C29" s="23" t="n"/>
-      <c r="D29" s="24" t="n"/>
-    </row>
-    <row r="30">
-      <c r="A30" s="3" t="inlineStr">
-        <is>
-          <t>Avg Win (Rs)</t>
-        </is>
-      </c>
-      <c r="B30" s="26" t="n">
-        <v>520.1799999999999</v>
-      </c>
-      <c r="C30" s="23" t="n"/>
-      <c r="D30" s="24" t="n"/>
-    </row>
-    <row r="31">
-      <c r="A31" s="3" t="inlineStr">
-        <is>
-          <t>Avg Win (% of premium)</t>
-        </is>
-      </c>
-      <c r="B31" s="30" t="n">
-        <v>54.92</v>
-      </c>
-      <c r="C31" s="23" t="n"/>
-      <c r="D31" s="24" t="n"/>
-    </row>
-    <row r="32">
-      <c r="A32" s="3" t="inlineStr">
-        <is>
-          <t>Avg Loss (Rs)</t>
-        </is>
-      </c>
-      <c r="B32" s="27" t="n">
-        <v>-254.41</v>
-      </c>
-      <c r="C32" s="23" t="n"/>
-      <c r="D32" s="24" t="n"/>
-    </row>
-    <row r="33">
-      <c r="A33" s="3" t="inlineStr">
-        <is>
-          <t>Avg Loss (% of premium)</t>
-        </is>
-      </c>
-      <c r="B33" s="31" t="n">
-        <v>-32.27</v>
-      </c>
-      <c r="C33" s="23" t="n"/>
-      <c r="D33" s="24" t="n"/>
-    </row>
-    <row r="34">
-      <c r="A34" s="3" t="inlineStr">
-        <is>
-          <t>Largest Win (Rs)</t>
-        </is>
-      </c>
-      <c r="B34" s="26" t="n">
-        <v>548.01</v>
-      </c>
-      <c r="C34" s="23" t="n"/>
-      <c r="D34" s="24" t="n"/>
-    </row>
-    <row r="35">
-      <c r="A35" s="3" t="inlineStr">
-        <is>
-          <t>Largest Loss (Rs)</t>
-        </is>
-      </c>
-      <c r="B35" s="27" t="n">
-        <v>-299.45</v>
-      </c>
-      <c r="C35" s="23" t="n"/>
-      <c r="D35" s="24" t="n"/>
-    </row>
-    <row r="36">
-      <c r="A36" s="3" t="inlineStr">
-        <is>
-          <t>Max Consecutive Wins</t>
-        </is>
-      </c>
-      <c r="B36" s="22" t="n">
-        <v>1</v>
-      </c>
-      <c r="C36" s="23" t="n"/>
-      <c r="D36" s="24" t="n"/>
-    </row>
-    <row r="37">
-      <c r="A37" s="3" t="inlineStr">
-        <is>
-          <t>Max Consecutive Losses</t>
-        </is>
-      </c>
-      <c r="B37" s="22" t="n">
-        <v>1</v>
-      </c>
-      <c r="C37" s="23" t="n"/>
-      <c r="D37" s="24" t="n"/>
-    </row>
-    <row r="38">
-      <c r="A38" s="3" t="inlineStr">
-        <is>
-          <t>Max trade drawdown (Rs)</t>
-        </is>
-      </c>
-      <c r="B38" s="27" t="n">
-        <v>-299.45</v>
-      </c>
-      <c r="C38" s="23" t="n"/>
-      <c r="D38" s="24" t="n"/>
-    </row>
-    <row r="39">
-      <c r="A39" s="3" t="inlineStr">
-        <is>
-          <t>Max system drawdown (Rs)</t>
-        </is>
-      </c>
-      <c r="B39" s="27" t="n">
-        <v>-299.45</v>
-      </c>
-      <c r="C39" s="23" t="n"/>
-      <c r="D39" s="24" t="n"/>
-    </row>
-    <row r="40">
-      <c r="A40" s="3" t="inlineStr">
-        <is>
-          <t>Max system drawdown (%)</t>
-        </is>
-      </c>
-      <c r="B40" s="31" t="n">
-        <v>-1.48</v>
-      </c>
-      <c r="C40" s="23" t="n"/>
-      <c r="D40" s="24" t="n"/>
-    </row>
-    <row r="41">
-      <c r="A41" s="3" t="inlineStr">
-        <is>
-          <t>Recovery Factor</t>
-        </is>
-      </c>
-      <c r="B41" s="32" t="n">
-        <v>0.93</v>
-      </c>
-      <c r="C41" s="23" t="n"/>
-      <c r="D41" s="24" t="n"/>
-    </row>
-    <row r="42">
-      <c r="A42" s="3" t="inlineStr">
-        <is>
-          <t>Profit Factor</t>
-        </is>
-      </c>
-      <c r="B42" s="32" t="n">
-        <v>1.36</v>
-      </c>
-      <c r="C42" s="23" t="n"/>
-      <c r="D42" s="24" t="n"/>
-    </row>
-    <row r="43">
-      <c r="A43" s="3" t="inlineStr">
-        <is>
-          <t>Payoff Ratio (avg win / avg loss)</t>
-        </is>
-      </c>
-      <c r="B43" s="32" t="n">
-        <v>2.04</v>
-      </c>
-      <c r="C43" s="23" t="n"/>
-      <c r="D43" s="24" t="n"/>
-    </row>
-    <row r="44">
-      <c r="A44" s="3" t="inlineStr">
-        <is>
-          <t>Sharpe Ratio (annualized)</t>
-        </is>
-      </c>
-      <c r="B44" s="32" t="n">
-        <v>4.61</v>
-      </c>
-      <c r="C44" s="23" t="n"/>
-      <c r="D44" s="24" t="n"/>
-    </row>
-    <row r="46">
-      <c r="A46" s="5" t="inlineStr">
-        <is>
-          <t>Caveat: with only a handful of trades these numbers (Sharpe, profit factor, drawdown %) are not statistically reliable. Watch this over weeks/months before drawing conclusions.</t>
+      <c r="A3" s="5" t="inlineStr">
+        <is>
+          <t>No trades yet for this index -- this fills in automatically as the bot trades.</t>
         </is>
       </c>
     </row>
   </sheetData>
-  <mergeCells count="24">
-    <mergeCell ref="B42:D42"/>
-    <mergeCell ref="B23:D23"/>
-    <mergeCell ref="B44:D44"/>
-    <mergeCell ref="B29:D29"/>
-    <mergeCell ref="B38:D38"/>
-    <mergeCell ref="B34:D34"/>
-    <mergeCell ref="B28:D28"/>
-    <mergeCell ref="B37:D37"/>
-    <mergeCell ref="B40:D40"/>
-    <mergeCell ref="B30:D30"/>
-    <mergeCell ref="B24:D24"/>
-    <mergeCell ref="B33:D33"/>
-    <mergeCell ref="B36:D36"/>
-    <mergeCell ref="B41:D41"/>
-    <mergeCell ref="B32:D32"/>
-    <mergeCell ref="B35:D35"/>
-    <mergeCell ref="B26:D26"/>
-    <mergeCell ref="B25:D25"/>
-    <mergeCell ref="B31:D31"/>
-    <mergeCell ref="B22:D22"/>
-    <mergeCell ref="B27:D27"/>
-    <mergeCell ref="B21:D21"/>
-    <mergeCell ref="B43:D43"/>
-    <mergeCell ref="B39:D39"/>
-  </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
   <pageSetup orientation="landscape" fitToHeight="0" fitToWidth="1"/>
 </worksheet>
 </file>
 
 <file path=xl/worksheets/sheet8.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr fitToPage="1"/>
+  </sheetPr>
+  <dimension ref="A1:A3"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <cols>
+    <col width="40" customWidth="1" min="1" max="1"/>
+    <col width="10" customWidth="1" min="2" max="2"/>
+    <col width="10" customWidth="1" min="3" max="3"/>
+    <col width="10" customWidth="1" min="4" max="4"/>
+    <col width="10" customWidth="1" min="5" max="5"/>
+    <col width="10" customWidth="1" min="6" max="6"/>
+    <col width="10" customWidth="1" min="7" max="7"/>
+    <col width="15" customWidth="1" min="8" max="8"/>
+    <col width="15" customWidth="1" min="9" max="9"/>
+    <col width="10" customWidth="1" min="10" max="10"/>
+    <col width="10" customWidth="1" min="11" max="11"/>
+    <col width="10" customWidth="1" min="12" max="12"/>
+    <col width="10" customWidth="1" min="13" max="13"/>
+    <col width="10" customWidth="1" min="14" max="14"/>
+    <col width="15" customWidth="1" min="15" max="15"/>
+  </cols>
+  <sheetData>
+    <row r="1">
+      <c r="A1" s="1" t="inlineStr">
+        <is>
+          <t>BACKTEST BANKNIFTY -- best:  -- PAPER TRADE, NOT REAL MONEY</t>
+        </is>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" s="5" t="inlineStr">
+        <is>
+          <t>No trades yet for this index -- this fills in automatically as the bot trades.</t>
+        </is>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+  <pageSetup orientation="landscape" fitToHeight="0" fitToWidth="1"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet9.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr>
     <outlinePr summaryBelow="1" summaryRight="1"/>
@@ -2859,12 +2133,12 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>BACKTEST BANKNIFTY -- best: trend_scalp_nw (EMA5/21) [5m] -- PAPER TRADE, NOT REAL MONEY</t>
+          <t>BACKTEST FINNIFTY -- best: trend_scalp_nw (EMA9/26) [5m] -- PAPER TRADE, NOT REAL MONEY</t>
         </is>
       </c>
     </row>
     <row r="3">
-      <c r="A3" s="13" t="inlineStr">
+      <c r="A3" s="12" t="inlineStr">
         <is>
           <t>MONTHLY returns (% of capital at start of month)</t>
         </is>
@@ -2962,43 +2236,43 @@
       <c r="J5" s="6" t="n"/>
       <c r="K5" s="6" t="n"/>
       <c r="L5" s="6" t="n"/>
-      <c r="M5" s="14" t="n">
-        <v>-0.0355045</v>
-      </c>
-      <c r="N5" s="18" t="n">
-        <v>-0.03550450000000005</v>
-      </c>
-      <c r="O5" s="20" t="n">
-        <v>-710.09</v>
+      <c r="M5" s="13" t="n">
+        <v>-0.0469125</v>
+      </c>
+      <c r="N5" s="14" t="n">
+        <v>-0.04691250000000002</v>
+      </c>
+      <c r="O5" s="15" t="n">
+        <v>-938.25</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" s="3" t="n">
         <v>2026</v>
       </c>
-      <c r="B6" s="14" t="n">
-        <v>-0.01746560766742821</v>
+      <c r="B6" s="13" t="n">
+        <v>-0.01505685469592246</v>
       </c>
       <c r="C6" s="6" t="n"/>
       <c r="D6" s="6" t="n"/>
-      <c r="E6" s="6" t="n"/>
+      <c r="E6" s="16" t="n">
+        <v>0.01262227865738753</v>
+      </c>
       <c r="F6" s="6" t="n"/>
       <c r="G6" s="6" t="n"/>
       <c r="H6" s="6" t="n"/>
-      <c r="I6" s="14" t="n">
-        <v>-0.02995409697673192</v>
-      </c>
-      <c r="J6" s="6" t="n"/>
-      <c r="K6" s="14" t="n">
-        <v>-0.009676763149650155</v>
-      </c>
+      <c r="I6" s="6" t="n"/>
+      <c r="J6" s="13" t="n">
+        <v>-0.01216670559002552</v>
+      </c>
+      <c r="K6" s="6" t="n"/>
       <c r="L6" s="6" t="n"/>
       <c r="M6" s="6" t="n"/>
-      <c r="N6" s="18" t="n">
-        <v>-0.05611949459587939</v>
-      </c>
-      <c r="O6" s="20" t="n">
-        <v>-1082.54</v>
+      <c r="N6" s="14" t="n">
+        <v>-0.01475940036985068</v>
+      </c>
+      <c r="O6" s="15" t="n">
+        <v>-281.34</v>
       </c>
     </row>
     <row r="7">
@@ -3007,29 +2281,29 @@
           <t>Avg</t>
         </is>
       </c>
-      <c r="B7" s="18" t="n">
-        <v>-0.01746560766742821</v>
+      <c r="B7" s="14" t="n">
+        <v>-0.01505685469592246</v>
       </c>
       <c r="C7" s="6" t="n"/>
       <c r="D7" s="6" t="n"/>
-      <c r="E7" s="6" t="n"/>
+      <c r="E7" s="17" t="n">
+        <v>0.01262227865738753</v>
+      </c>
       <c r="F7" s="6" t="n"/>
       <c r="G7" s="6" t="n"/>
       <c r="H7" s="6" t="n"/>
-      <c r="I7" s="18" t="n">
-        <v>-0.02995409697673192</v>
-      </c>
-      <c r="J7" s="6" t="n"/>
-      <c r="K7" s="18" t="n">
-        <v>-0.009676763149650155</v>
-      </c>
+      <c r="I7" s="6" t="n"/>
+      <c r="J7" s="14" t="n">
+        <v>-0.01216670559002552</v>
+      </c>
+      <c r="K7" s="6" t="n"/>
       <c r="L7" s="6" t="n"/>
-      <c r="M7" s="18" t="n">
-        <v>-0.0355045</v>
+      <c r="M7" s="14" t="n">
+        <v>-0.0469125</v>
       </c>
     </row>
     <row r="9">
-      <c r="A9" s="13" t="inlineStr">
+      <c r="A9" s="12" t="inlineStr">
         <is>
           <t>WEEKLY returns (% of capital at start of that week; weeks split at month edges)</t>
         </is>
@@ -3088,19 +2362,21 @@
           <t>2025-Dec</t>
         </is>
       </c>
-      <c r="B11" s="14" t="n">
-        <v>-0.0355045</v>
-      </c>
-      <c r="C11" s="6" t="n"/>
+      <c r="B11" s="13" t="n">
+        <v>-0.010346</v>
+      </c>
+      <c r="C11" s="13" t="n">
+        <v>-0.0369487719950609</v>
+      </c>
       <c r="D11" s="6" t="n"/>
       <c r="E11" s="6" t="n"/>
       <c r="F11" s="6" t="n"/>
       <c r="G11" s="6" t="n"/>
-      <c r="H11" s="19" t="n">
-        <v>-0.0355045</v>
-      </c>
-      <c r="I11" s="20" t="n">
-        <v>-710.09</v>
+      <c r="H11" s="18" t="n">
+        <v>-0.0469125</v>
+      </c>
+      <c r="I11" s="15" t="n">
+        <v>-938.25</v>
       </c>
     </row>
     <row r="12">
@@ -3109,67 +2385,65 @@
           <t>2026-Jan</t>
         </is>
       </c>
-      <c r="B12" s="14" t="n">
-        <v>-0.01746560766742821</v>
+      <c r="B12" s="13" t="n">
+        <v>-0.01505685469592246</v>
       </c>
       <c r="C12" s="6" t="n"/>
       <c r="D12" s="6" t="n"/>
       <c r="E12" s="6" t="n"/>
       <c r="F12" s="6" t="n"/>
       <c r="G12" s="6" t="n"/>
-      <c r="H12" s="19" t="n">
-        <v>-0.01746560766742821</v>
-      </c>
-      <c r="I12" s="20" t="n">
-        <v>-336.91</v>
+      <c r="H12" s="18" t="n">
+        <v>-0.01505685469592246</v>
+      </c>
+      <c r="I12" s="15" t="n">
+        <v>-287.01</v>
       </c>
     </row>
     <row r="13">
       <c r="A13" s="3" t="inlineStr">
         <is>
-          <t>2026-Aug</t>
-        </is>
-      </c>
-      <c r="B13" s="14" t="n">
-        <v>-0.01872526776763573</v>
-      </c>
-      <c r="C13" s="14" t="n">
-        <v>-0.01144310440313796</v>
-      </c>
+          <t>2026-Apr</t>
+        </is>
+      </c>
+      <c r="B13" s="16" t="n">
+        <v>0.01262227865738753</v>
+      </c>
+      <c r="C13" s="6" t="n"/>
       <c r="D13" s="6" t="n"/>
       <c r="E13" s="6" t="n"/>
       <c r="F13" s="6" t="n"/>
       <c r="G13" s="6" t="n"/>
       <c r="H13" s="19" t="n">
-        <v>-0.02995409697673192</v>
+        <v>0.01262227865738753</v>
       </c>
       <c r="I13" s="20" t="n">
-        <v>-567.72</v>
+        <v>236.98</v>
       </c>
     </row>
     <row r="14">
       <c r="A14" s="3" t="inlineStr">
         <is>
-          <t>2026-Oct</t>
-        </is>
-      </c>
-      <c r="B14" s="14" t="n">
-        <v>-0.009676763149650155</v>
+          <t>2026-Sep</t>
+        </is>
+      </c>
+      <c r="B14" s="13" t="n">
+        <v>-0.01216670559002552</v>
       </c>
       <c r="C14" s="6" t="n"/>
       <c r="D14" s="6" t="n"/>
       <c r="E14" s="6" t="n"/>
       <c r="F14" s="6" t="n"/>
       <c r="G14" s="6" t="n"/>
-      <c r="H14" s="19" t="n">
-        <v>-0.009676763149650155</v>
-      </c>
-      <c r="I14" s="20" t="n">
-        <v>-177.91</v>
+      <c r="H14" s="18" t="n">
+        <v>-0.01216670559002552</v>
+      </c>
+      <c r="I14" s="15" t="n">
+        <v>-231.31</v>
       </c>
     </row>
     <row r="16">
-      <c r="A16" s="13" t="inlineStr">
+      <c r="A16" s="12" t="inlineStr">
         <is>
           <t>DAILY returns (% of capital at start of that day; blank = no trade that day)</t>
         </is>
@@ -3220,105 +2494,105 @@
     <row r="18">
       <c r="A18" s="3" t="inlineStr">
         <is>
-          <t>29-Dec-2025</t>
+          <t>01-Dec-2025</t>
         </is>
       </c>
       <c r="B18" s="6" t="n"/>
-      <c r="C18" s="14" t="n">
-        <v>-0.0355045</v>
+      <c r="C18" s="13" t="n">
+        <v>-0.010346</v>
       </c>
       <c r="D18" s="6" t="n"/>
       <c r="E18" s="6" t="n"/>
       <c r="F18" s="6" t="n"/>
-      <c r="G18" s="19" t="n">
-        <v>-0.0355045</v>
-      </c>
-      <c r="H18" s="20" t="n">
-        <v>-710.09</v>
+      <c r="G18" s="18" t="n">
+        <v>-0.010346</v>
+      </c>
+      <c r="H18" s="15" t="n">
+        <v>-206.92</v>
       </c>
     </row>
     <row r="19">
       <c r="A19" s="3" t="inlineStr">
         <is>
-          <t>26-Jan-2026</t>
+          <t>08-Dec-2025</t>
         </is>
       </c>
       <c r="B19" s="6" t="n"/>
-      <c r="C19" s="14" t="n">
-        <v>-0.01746560766742821</v>
+      <c r="C19" s="13" t="n">
+        <v>-0.0369487719950609</v>
       </c>
       <c r="D19" s="6" t="n"/>
       <c r="E19" s="6" t="n"/>
       <c r="F19" s="6" t="n"/>
-      <c r="G19" s="19" t="n">
-        <v>-0.01746560766742821</v>
-      </c>
-      <c r="H19" s="20" t="n">
-        <v>-336.91</v>
+      <c r="G19" s="18" t="n">
+        <v>-0.0369487719950609</v>
+      </c>
+      <c r="H19" s="15" t="n">
+        <v>-731.33</v>
       </c>
     </row>
     <row r="20">
       <c r="A20" s="3" t="inlineStr">
         <is>
-          <t>10-Aug-2026</t>
+          <t>26-Jan-2026</t>
         </is>
       </c>
       <c r="B20" s="6" t="n"/>
-      <c r="C20" s="14" t="n">
-        <v>-0.01872526776763573</v>
+      <c r="C20" s="13" t="n">
+        <v>-0.01505685469592246</v>
       </c>
       <c r="D20" s="6" t="n"/>
       <c r="E20" s="6" t="n"/>
       <c r="F20" s="6" t="n"/>
-      <c r="G20" s="19" t="n">
-        <v>-0.01872526776763573</v>
-      </c>
-      <c r="H20" s="20" t="n">
-        <v>-354.9</v>
+      <c r="G20" s="18" t="n">
+        <v>-0.01505685469592246</v>
+      </c>
+      <c r="H20" s="15" t="n">
+        <v>-287.01</v>
       </c>
     </row>
     <row r="21">
       <c r="A21" s="3" t="inlineStr">
         <is>
-          <t>24-Aug-2026</t>
+          <t>06-Apr-2026</t>
         </is>
       </c>
       <c r="B21" s="6" t="n"/>
-      <c r="C21" s="14" t="n">
-        <v>-0.01144310440313796</v>
+      <c r="C21" s="16" t="n">
+        <v>0.01262227865738753</v>
       </c>
       <c r="D21" s="6" t="n"/>
       <c r="E21" s="6" t="n"/>
       <c r="F21" s="6" t="n"/>
       <c r="G21" s="19" t="n">
-        <v>-0.01144310440313796</v>
+        <v>0.01262227865738753</v>
       </c>
       <c r="H21" s="20" t="n">
-        <v>-212.82</v>
+        <v>236.98</v>
       </c>
     </row>
     <row r="22">
       <c r="A22" s="3" t="inlineStr">
         <is>
-          <t>12-Oct-2026</t>
+          <t>07-Sep-2026</t>
         </is>
       </c>
       <c r="B22" s="6" t="n"/>
-      <c r="C22" s="14" t="n">
-        <v>-0.009676763149650155</v>
+      <c r="C22" s="13" t="n">
+        <v>-0.01216670559002552</v>
       </c>
       <c r="D22" s="6" t="n"/>
       <c r="E22" s="6" t="n"/>
       <c r="F22" s="6" t="n"/>
-      <c r="G22" s="19" t="n">
-        <v>-0.009676763149650155</v>
-      </c>
-      <c r="H22" s="20" t="n">
-        <v>-177.91</v>
+      <c r="G22" s="18" t="n">
+        <v>-0.01216670559002552</v>
+      </c>
+      <c r="H22" s="15" t="n">
+        <v>-231.31</v>
       </c>
     </row>
     <row r="24">
-      <c r="A24" s="13" t="inlineStr">
+      <c r="A24" s="12" t="inlineStr">
         <is>
           <t>STATISTICS (all trades for this index)</t>
         </is>
@@ -3330,11 +2604,11 @@
           <t>All trades</t>
         </is>
       </c>
-      <c r="B25" s="22" t="n">
-        <v>6</v>
-      </c>
-      <c r="C25" s="23" t="n"/>
-      <c r="D25" s="24" t="n"/>
+      <c r="B25" s="21" t="n">
+        <v>7</v>
+      </c>
+      <c r="C25" s="22" t="n"/>
+      <c r="D25" s="23" t="n"/>
     </row>
     <row r="26">
       <c r="A26" s="3" t="inlineStr">
@@ -3342,13 +2616,13 @@
           <t>Winners</t>
         </is>
       </c>
-      <c r="B26" s="25" t="inlineStr">
-        <is>
-          <t>0 (0.0%)</t>
-        </is>
-      </c>
-      <c r="C26" s="23" t="n"/>
-      <c r="D26" s="24" t="n"/>
+      <c r="B26" s="24" t="inlineStr">
+        <is>
+          <t>1 (14.3%)</t>
+        </is>
+      </c>
+      <c r="C26" s="22" t="n"/>
+      <c r="D26" s="23" t="n"/>
     </row>
     <row r="27">
       <c r="A27" s="3" t="inlineStr">
@@ -3356,13 +2630,13 @@
           <t>Losers</t>
         </is>
       </c>
-      <c r="B27" s="25" t="inlineStr">
-        <is>
-          <t>6 (100.0%)</t>
-        </is>
-      </c>
-      <c r="C27" s="23" t="n"/>
-      <c r="D27" s="24" t="n"/>
+      <c r="B27" s="24" t="inlineStr">
+        <is>
+          <t>6 (85.7%)</t>
+        </is>
+      </c>
+      <c r="C27" s="22" t="n"/>
+      <c r="D27" s="23" t="n"/>
     </row>
     <row r="28">
       <c r="A28" s="3" t="inlineStr">
@@ -3370,11 +2644,11 @@
           <t>Net P&amp;L (Rs)</t>
         </is>
       </c>
-      <c r="B28" s="27" t="n">
-        <v>-1792.63</v>
-      </c>
-      <c r="C28" s="23" t="n"/>
-      <c r="D28" s="24" t="n"/>
+      <c r="B28" s="25" t="n">
+        <v>-1219.59</v>
+      </c>
+      <c r="C28" s="22" t="n"/>
+      <c r="D28" s="23" t="n"/>
     </row>
     <row r="29">
       <c r="A29" s="3" t="inlineStr">
@@ -3383,10 +2657,10 @@
         </is>
       </c>
       <c r="B29" s="26" t="n">
-        <v>0</v>
-      </c>
-      <c r="C29" s="23" t="n"/>
-      <c r="D29" s="24" t="n"/>
+        <v>236.98</v>
+      </c>
+      <c r="C29" s="22" t="n"/>
+      <c r="D29" s="23" t="n"/>
     </row>
     <row r="30">
       <c r="A30" s="3" t="inlineStr">
@@ -3394,11 +2668,11 @@
           <t>Total Loss (Rs)</t>
         </is>
       </c>
-      <c r="B30" s="27" t="n">
-        <v>-1792.63</v>
-      </c>
-      <c r="C30" s="23" t="n"/>
-      <c r="D30" s="24" t="n"/>
+      <c r="B30" s="25" t="n">
+        <v>-1456.57</v>
+      </c>
+      <c r="C30" s="22" t="n"/>
+      <c r="D30" s="23" t="n"/>
     </row>
     <row r="31">
       <c r="A31" s="3" t="inlineStr">
@@ -3406,11 +2680,11 @@
           <t>Transaction costs (Rs)</t>
         </is>
       </c>
-      <c r="B31" s="28" t="n">
-        <v>364.63</v>
-      </c>
-      <c r="C31" s="23" t="n"/>
-      <c r="D31" s="24" t="n"/>
+      <c r="B31" s="27" t="n">
+        <v>348.39</v>
+      </c>
+      <c r="C31" s="22" t="n"/>
+      <c r="D31" s="23" t="n"/>
     </row>
     <row r="32">
       <c r="A32" s="3" t="inlineStr">
@@ -3418,11 +2692,11 @@
           <t>Avg Profit/Loss per trade (Rs)</t>
         </is>
       </c>
-      <c r="B32" s="27" t="n">
-        <v>-298.77</v>
-      </c>
-      <c r="C32" s="23" t="n"/>
-      <c r="D32" s="24" t="n"/>
+      <c r="B32" s="25" t="n">
+        <v>-174.23</v>
+      </c>
+      <c r="C32" s="22" t="n"/>
+      <c r="D32" s="23" t="n"/>
     </row>
     <row r="33">
       <c r="A33" s="3" t="inlineStr">
@@ -3430,11 +2704,11 @@
           <t>Avg Profit/Loss per trade (% of premium)</t>
         </is>
       </c>
-      <c r="B33" s="29" t="n">
-        <v>-14.84</v>
-      </c>
-      <c r="C33" s="23" t="n"/>
-      <c r="D33" s="24" t="n"/>
+      <c r="B33" s="28" t="n">
+        <v>-10.42</v>
+      </c>
+      <c r="C33" s="22" t="n"/>
+      <c r="D33" s="23" t="n"/>
     </row>
     <row r="34">
       <c r="A34" s="3" t="inlineStr">
@@ -3443,10 +2717,10 @@
         </is>
       </c>
       <c r="B34" s="26" t="n">
-        <v>0</v>
-      </c>
-      <c r="C34" s="23" t="n"/>
-      <c r="D34" s="24" t="n"/>
+        <v>236.98</v>
+      </c>
+      <c r="C34" s="22" t="n"/>
+      <c r="D34" s="23" t="n"/>
     </row>
     <row r="35">
       <c r="A35" s="3" t="inlineStr">
@@ -3454,11 +2728,11 @@
           <t>Avg Win (% of premium)</t>
         </is>
       </c>
-      <c r="B35" s="30" t="n">
-        <v>0</v>
-      </c>
-      <c r="C35" s="23" t="n"/>
-      <c r="D35" s="24" t="n"/>
+      <c r="B35" s="29" t="n">
+        <v>16.17</v>
+      </c>
+      <c r="C35" s="22" t="n"/>
+      <c r="D35" s="23" t="n"/>
     </row>
     <row r="36">
       <c r="A36" s="3" t="inlineStr">
@@ -3466,11 +2740,11 @@
           <t>Avg Loss (Rs)</t>
         </is>
       </c>
-      <c r="B36" s="27" t="n">
-        <v>-298.77</v>
-      </c>
-      <c r="C36" s="23" t="n"/>
-      <c r="D36" s="24" t="n"/>
+      <c r="B36" s="25" t="n">
+        <v>-242.76</v>
+      </c>
+      <c r="C36" s="22" t="n"/>
+      <c r="D36" s="23" t="n"/>
     </row>
     <row r="37">
       <c r="A37" s="3" t="inlineStr">
@@ -3478,11 +2752,11 @@
           <t>Avg Loss (% of premium)</t>
         </is>
       </c>
-      <c r="B37" s="31" t="n">
-        <v>-14.84</v>
-      </c>
-      <c r="C37" s="23" t="n"/>
-      <c r="D37" s="24" t="n"/>
+      <c r="B37" s="30" t="n">
+        <v>-14.85</v>
+      </c>
+      <c r="C37" s="22" t="n"/>
+      <c r="D37" s="23" t="n"/>
     </row>
     <row r="38">
       <c r="A38" s="3" t="inlineStr">
@@ -3491,10 +2765,10 @@
         </is>
       </c>
       <c r="B38" s="26" t="n">
-        <v>-177.91</v>
-      </c>
-      <c r="C38" s="23" t="n"/>
-      <c r="D38" s="24" t="n"/>
+        <v>236.98</v>
+      </c>
+      <c r="C38" s="22" t="n"/>
+      <c r="D38" s="23" t="n"/>
     </row>
     <row r="39">
       <c r="A39" s="3" t="inlineStr">
@@ -3502,11 +2776,11 @@
           <t>Largest Loss (Rs)</t>
         </is>
       </c>
-      <c r="B39" s="27" t="n">
-        <v>-358.86</v>
-      </c>
-      <c r="C39" s="23" t="n"/>
-      <c r="D39" s="24" t="n"/>
+      <c r="B39" s="25" t="n">
+        <v>-295.95</v>
+      </c>
+      <c r="C39" s="22" t="n"/>
+      <c r="D39" s="23" t="n"/>
     </row>
     <row r="40">
       <c r="A40" s="3" t="inlineStr">
@@ -3514,11 +2788,11 @@
           <t>Max Consecutive Wins</t>
         </is>
       </c>
-      <c r="B40" s="22" t="n">
-        <v>0</v>
-      </c>
-      <c r="C40" s="23" t="n"/>
-      <c r="D40" s="24" t="n"/>
+      <c r="B40" s="21" t="n">
+        <v>1</v>
+      </c>
+      <c r="C40" s="22" t="n"/>
+      <c r="D40" s="23" t="n"/>
     </row>
     <row r="41">
       <c r="A41" s="3" t="inlineStr">
@@ -3526,11 +2800,11 @@
           <t>Max Consecutive Losses</t>
         </is>
       </c>
-      <c r="B41" s="22" t="n">
-        <v>6</v>
-      </c>
-      <c r="C41" s="23" t="n"/>
-      <c r="D41" s="24" t="n"/>
+      <c r="B41" s="21" t="n">
+        <v>5</v>
+      </c>
+      <c r="C41" s="22" t="n"/>
+      <c r="D41" s="23" t="n"/>
     </row>
     <row r="42">
       <c r="A42" s="3" t="inlineStr">
@@ -3538,11 +2812,11 @@
           <t>Max trade drawdown (Rs)</t>
         </is>
       </c>
-      <c r="B42" s="27" t="n">
-        <v>-358.86</v>
-      </c>
-      <c r="C42" s="23" t="n"/>
-      <c r="D42" s="24" t="n"/>
+      <c r="B42" s="25" t="n">
+        <v>-295.95</v>
+      </c>
+      <c r="C42" s="22" t="n"/>
+      <c r="D42" s="23" t="n"/>
     </row>
     <row r="43">
       <c r="A43" s="3" t="inlineStr">
@@ -3550,11 +2824,11 @@
           <t>Max system drawdown (Rs)</t>
         </is>
       </c>
-      <c r="B43" s="27" t="n">
-        <v>-1792.63</v>
-      </c>
-      <c r="C43" s="23" t="n"/>
-      <c r="D43" s="24" t="n"/>
+      <c r="B43" s="25" t="n">
+        <v>-1225.26</v>
+      </c>
+      <c r="C43" s="22" t="n"/>
+      <c r="D43" s="23" t="n"/>
     </row>
     <row r="44">
       <c r="A44" s="3" t="inlineStr">
@@ -3562,11 +2836,11 @@
           <t>Max system drawdown (%)</t>
         </is>
       </c>
-      <c r="B44" s="31" t="n">
-        <v>-8.960000000000001</v>
-      </c>
-      <c r="C44" s="23" t="n"/>
-      <c r="D44" s="24" t="n"/>
+      <c r="B44" s="30" t="n">
+        <v>-6.13</v>
+      </c>
+      <c r="C44" s="22" t="n"/>
+      <c r="D44" s="23" t="n"/>
     </row>
     <row r="45">
       <c r="A45" s="3" t="inlineStr">
@@ -3574,11 +2848,11 @@
           <t>Recovery Factor</t>
         </is>
       </c>
-      <c r="B45" s="32" t="n">
+      <c r="B45" s="31" t="n">
         <v>-1</v>
       </c>
-      <c r="C45" s="23" t="n"/>
-      <c r="D45" s="24" t="n"/>
+      <c r="C45" s="22" t="n"/>
+      <c r="D45" s="23" t="n"/>
     </row>
     <row r="46">
       <c r="A46" s="3" t="inlineStr">
@@ -3586,11 +2860,11 @@
           <t>Profit Factor</t>
         </is>
       </c>
-      <c r="B46" s="32" t="n">
-        <v>0</v>
-      </c>
-      <c r="C46" s="23" t="n"/>
-      <c r="D46" s="24" t="n"/>
+      <c r="B46" s="31" t="n">
+        <v>0.16</v>
+      </c>
+      <c r="C46" s="22" t="n"/>
+      <c r="D46" s="23" t="n"/>
     </row>
     <row r="47">
       <c r="A47" s="3" t="inlineStr">
@@ -3598,13 +2872,11 @@
           <t>Payoff Ratio (avg win / avg loss)</t>
         </is>
       </c>
-      <c r="B47" s="25" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="C47" s="23" t="n"/>
-      <c r="D47" s="24" t="n"/>
+      <c r="B47" s="31" t="n">
+        <v>0.98</v>
+      </c>
+      <c r="C47" s="22" t="n"/>
+      <c r="D47" s="23" t="n"/>
     </row>
     <row r="48">
       <c r="A48" s="3" t="inlineStr">
@@ -3612,11 +2884,11 @@
           <t>Sharpe Ratio (annualized)</t>
         </is>
       </c>
-      <c r="B48" s="32" t="n">
-        <v>-32.23</v>
-      </c>
-      <c r="C48" s="23" t="n"/>
-      <c r="D48" s="24" t="n"/>
+      <c r="B48" s="31" t="n">
+        <v>-12.48</v>
+      </c>
+      <c r="C48" s="22" t="n"/>
+      <c r="D48" s="23" t="n"/>
     </row>
     <row r="50">
       <c r="A50" s="5" t="inlineStr">
@@ -3655,50 +2927,4 @@
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
   <pageSetup orientation="landscape" fitToHeight="0" fitToWidth="1"/>
 </worksheet>
-</file>
-
-<file path=xl/worksheets/sheet9.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <sheetPr>
-    <outlinePr summaryBelow="1" summaryRight="1"/>
-    <pageSetUpPr fitToPage="1"/>
-  </sheetPr>
-  <dimension ref="A1:A3"/>
-  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
-  <cols>
-    <col width="40" customWidth="1" min="1" max="1"/>
-    <col width="10" customWidth="1" min="2" max="2"/>
-    <col width="10" customWidth="1" min="3" max="3"/>
-    <col width="10" customWidth="1" min="4" max="4"/>
-    <col width="10" customWidth="1" min="5" max="5"/>
-    <col width="10" customWidth="1" min="6" max="6"/>
-    <col width="10" customWidth="1" min="7" max="7"/>
-    <col width="15" customWidth="1" min="8" max="8"/>
-    <col width="15" customWidth="1" min="9" max="9"/>
-    <col width="10" customWidth="1" min="10" max="10"/>
-    <col width="10" customWidth="1" min="11" max="11"/>
-    <col width="10" customWidth="1" min="12" max="12"/>
-    <col width="10" customWidth="1" min="13" max="13"/>
-    <col width="10" customWidth="1" min="14" max="14"/>
-    <col width="15" customWidth="1" min="15" max="15"/>
-  </cols>
-  <sheetData>
-    <row r="1">
-      <c r="A1" s="1" t="inlineStr">
-        <is>
-          <t>BACKTEST FINNIFTY -- best:  -- PAPER TRADE, NOT REAL MONEY</t>
-        </is>
-      </c>
-    </row>
-    <row r="3">
-      <c r="A3" s="5" t="inlineStr">
-        <is>
-          <t>No trades yet for this index -- this fills in automatically as the bot trades.</t>
-        </is>
-      </c>
-    </row>
-  </sheetData>
-  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
-  <pageSetup orientation="landscape" fitToHeight="0" fitToWidth="1"/>
-</worksheet>
 </file>
--- a/reports/dashboard.xlsx
+++ b/reports/dashboard.xlsx
@@ -58,9 +58,18 @@
     </font>
     <font>
       <name val="Arial"/>
+      <color rgb="000B8A00"/>
+    </font>
+    <font>
+      <name val="Arial"/>
       <i val="1"/>
       <color rgb="00666666"/>
       <sz val="9"/>
+    </font>
+    <font>
+      <name val="Arial"/>
+      <b val="1"/>
+      <color rgb="000B8A00"/>
     </font>
     <font>
       <name val="Arial"/>
@@ -68,17 +77,8 @@
     </font>
     <font>
       <name val="Arial"/>
-      <color rgb="000B8A00"/>
-    </font>
-    <font>
-      <name val="Arial"/>
       <b val="1"/>
       <color rgb="00C00000"/>
-    </font>
-    <font>
-      <name val="Arial"/>
-      <b val="1"/>
-      <color rgb="000B8A00"/>
     </font>
   </fonts>
   <fills count="5">
@@ -96,14 +96,14 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="00FDE8E8"/>
-        <bgColor rgb="00FDE8E8"/>
+        <fgColor rgb="00E6F4EA"/>
+        <bgColor rgb="00E6F4EA"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="00E6F4EA"/>
-        <bgColor rgb="00E6F4EA"/>
+        <fgColor rgb="00FDE8E8"/>
+        <bgColor rgb="00FDE8E8"/>
       </patternFill>
     </fill>
   </fills>
@@ -177,30 +177,27 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="32">
+  <cellXfs count="34">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="2" fillId="2" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="1" fontId="4" fillId="0" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="164" fontId="4" fillId="0" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="165" fontId="6" fillId="0" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="165" fontId="5" fillId="0" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="2" fontId="4" fillId="0" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="10" fontId="4" fillId="0" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="165" fontId="4" fillId="0" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="164" fontId="6" fillId="3" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="164" fontId="6" fillId="0" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="166" fontId="6" fillId="0" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="164" fontId="7" fillId="4" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="164" fontId="7" fillId="0" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="164" fontId="8" fillId="3" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="164" fontId="9" fillId="4" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="166" fontId="7" fillId="0" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="164" fontId="5" fillId="3" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="164" fontId="5" fillId="0" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="166" fontId="5" fillId="0" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="164" fontId="7" fillId="3" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="1" fontId="4" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="right"/>
     </xf>
@@ -209,10 +206,10 @@
     <xf numFmtId="0" fontId="4" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="right"/>
     </xf>
-    <xf numFmtId="165" fontId="6" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="165" fontId="5" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="right"/>
     </xf>
-    <xf numFmtId="165" fontId="7" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="165" fontId="8" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="right"/>
     </xf>
     <xf numFmtId="165" fontId="4" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
@@ -221,15 +218,20 @@
     <xf numFmtId="167" fontId="4" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="right"/>
     </xf>
-    <xf numFmtId="167" fontId="7" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="167" fontId="5" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="right"/>
     </xf>
-    <xf numFmtId="167" fontId="6" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="167" fontId="8" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="right"/>
     </xf>
     <xf numFmtId="2" fontId="4" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="right"/>
     </xf>
+    <xf numFmtId="165" fontId="8" fillId="0" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="164" fontId="8" fillId="4" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="164" fontId="8" fillId="0" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="166" fontId="8" fillId="0" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="164" fontId="9" fillId="4" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0" hidden="0"/>
@@ -658,32 +660,22 @@
         </is>
       </c>
       <c r="B4" s="4" t="n">
-        <v>0</v>
-      </c>
-      <c r="C4" s="4" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="D4" s="4" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="E4" s="4" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="F4" s="4" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="G4" s="4" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+        <v>2</v>
+      </c>
+      <c r="C4" s="5" t="n">
+        <v>0.5</v>
+      </c>
+      <c r="D4" s="6" t="n">
+        <v>402.32</v>
+      </c>
+      <c r="E4" s="7" t="n">
+        <v>2.8</v>
+      </c>
+      <c r="F4" s="8" t="n">
+        <v>-0.01084792207143678</v>
+      </c>
+      <c r="G4" s="9" t="n">
+        <v>201.16</v>
       </c>
     </row>
     <row r="5">
@@ -692,30 +684,30 @@
           <t>BANKNIFTY</t>
         </is>
       </c>
-      <c r="B5" s="4" t="n">
+      <c r="B5" s="10" t="n">
         <v>0</v>
       </c>
-      <c r="C5" s="4" t="inlineStr">
+      <c r="C5" s="10" t="inlineStr">
         <is>
           <t>-</t>
         </is>
       </c>
-      <c r="D5" s="4" t="inlineStr">
+      <c r="D5" s="10" t="inlineStr">
         <is>
           <t>-</t>
         </is>
       </c>
-      <c r="E5" s="4" t="inlineStr">
+      <c r="E5" s="10" t="inlineStr">
         <is>
           <t>-</t>
         </is>
       </c>
-      <c r="F5" s="4" t="inlineStr">
+      <c r="F5" s="10" t="inlineStr">
         <is>
           <t>-</t>
         </is>
       </c>
-      <c r="G5" s="4" t="inlineStr">
+      <c r="G5" s="10" t="inlineStr">
         <is>
           <t>-</t>
         </is>
@@ -727,30 +719,30 @@
           <t>FINNIFTY</t>
         </is>
       </c>
-      <c r="B6" s="4" t="n">
+      <c r="B6" s="10" t="n">
         <v>0</v>
       </c>
-      <c r="C6" s="4" t="inlineStr">
+      <c r="C6" s="10" t="inlineStr">
         <is>
           <t>-</t>
         </is>
       </c>
-      <c r="D6" s="4" t="inlineStr">
+      <c r="D6" s="10" t="inlineStr">
         <is>
           <t>-</t>
         </is>
       </c>
-      <c r="E6" s="4" t="inlineStr">
+      <c r="E6" s="10" t="inlineStr">
         <is>
           <t>-</t>
         </is>
       </c>
-      <c r="F6" s="4" t="inlineStr">
+      <c r="F6" s="10" t="inlineStr">
         <is>
           <t>-</t>
         </is>
       </c>
-      <c r="G6" s="4" t="inlineStr">
+      <c r="G6" s="10" t="inlineStr">
         <is>
           <t>-</t>
         </is>
@@ -763,36 +755,26 @@
         </is>
       </c>
       <c r="B7" s="4" t="n">
-        <v>0</v>
-      </c>
-      <c r="C7" s="4" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="D7" s="4" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="E7" s="4" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="F7" s="4" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="G7" s="4" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+        <v>2</v>
+      </c>
+      <c r="C7" s="5" t="n">
+        <v>0.5</v>
+      </c>
+      <c r="D7" s="6" t="n">
+        <v>402.32</v>
+      </c>
+      <c r="E7" s="7" t="n">
+        <v>2.8</v>
+      </c>
+      <c r="F7" s="8" t="n">
+        <v>-0.01084792207143678</v>
+      </c>
+      <c r="G7" s="9" t="n">
+        <v>201.16</v>
       </c>
     </row>
     <row r="9">
-      <c r="A9" s="5" t="inlineStr">
+      <c r="A9" s="11" t="inlineStr">
         <is>
           <t>Each index has its own sheet with the monthly-returns grid and full statistics.</t>
         </is>
@@ -925,24 +907,24 @@
       <c r="A5" s="3" t="n">
         <v>2025</v>
       </c>
-      <c r="B5" s="6" t="n"/>
-      <c r="C5" s="6" t="n"/>
-      <c r="D5" s="6" t="n"/>
-      <c r="E5" s="6" t="n"/>
-      <c r="F5" s="6" t="n"/>
-      <c r="G5" s="6" t="n"/>
-      <c r="H5" s="6" t="n"/>
-      <c r="I5" s="6" t="n"/>
-      <c r="J5" s="6" t="n"/>
-      <c r="K5" s="6" t="n"/>
-      <c r="L5" s="6" t="n"/>
-      <c r="M5" s="13" t="n">
+      <c r="B5" s="13" t="n"/>
+      <c r="C5" s="13" t="n"/>
+      <c r="D5" s="13" t="n"/>
+      <c r="E5" s="13" t="n"/>
+      <c r="F5" s="13" t="n"/>
+      <c r="G5" s="13" t="n"/>
+      <c r="H5" s="13" t="n"/>
+      <c r="I5" s="13" t="n"/>
+      <c r="J5" s="13" t="n"/>
+      <c r="K5" s="13" t="n"/>
+      <c r="L5" s="13" t="n"/>
+      <c r="M5" s="30" t="n">
         <v>-0.0469125</v>
       </c>
-      <c r="N5" s="14" t="n">
+      <c r="N5" s="31" t="n">
         <v>-0.04691250000000002</v>
       </c>
-      <c r="O5" s="15" t="n">
+      <c r="O5" s="32" t="n">
         <v>-938.25</v>
       </c>
     </row>
@@ -950,28 +932,28 @@
       <c r="A6" s="3" t="n">
         <v>2026</v>
       </c>
-      <c r="B6" s="13" t="n">
+      <c r="B6" s="30" t="n">
         <v>-0.01505685469592246</v>
       </c>
-      <c r="C6" s="6" t="n"/>
-      <c r="D6" s="6" t="n"/>
-      <c r="E6" s="16" t="n">
+      <c r="C6" s="13" t="n"/>
+      <c r="D6" s="13" t="n"/>
+      <c r="E6" s="14" t="n">
         <v>0.01262227865738753</v>
       </c>
-      <c r="F6" s="6" t="n"/>
-      <c r="G6" s="6" t="n"/>
-      <c r="H6" s="6" t="n"/>
-      <c r="I6" s="6" t="n"/>
-      <c r="J6" s="13" t="n">
+      <c r="F6" s="13" t="n"/>
+      <c r="G6" s="13" t="n"/>
+      <c r="H6" s="13" t="n"/>
+      <c r="I6" s="13" t="n"/>
+      <c r="J6" s="30" t="n">
         <v>-0.01216670559002552</v>
       </c>
-      <c r="K6" s="6" t="n"/>
-      <c r="L6" s="6" t="n"/>
-      <c r="M6" s="6" t="n"/>
-      <c r="N6" s="14" t="n">
+      <c r="K6" s="13" t="n"/>
+      <c r="L6" s="13" t="n"/>
+      <c r="M6" s="13" t="n"/>
+      <c r="N6" s="31" t="n">
         <v>-0.01475940036985068</v>
       </c>
-      <c r="O6" s="15" t="n">
+      <c r="O6" s="32" t="n">
         <v>-281.34</v>
       </c>
     </row>
@@ -981,24 +963,24 @@
           <t>Avg</t>
         </is>
       </c>
-      <c r="B7" s="14" t="n">
+      <c r="B7" s="31" t="n">
         <v>-0.01505685469592246</v>
       </c>
-      <c r="C7" s="6" t="n"/>
-      <c r="D7" s="6" t="n"/>
-      <c r="E7" s="17" t="n">
+      <c r="C7" s="13" t="n"/>
+      <c r="D7" s="13" t="n"/>
+      <c r="E7" s="15" t="n">
         <v>0.01262227865738753</v>
       </c>
-      <c r="F7" s="6" t="n"/>
-      <c r="G7" s="6" t="n"/>
-      <c r="H7" s="6" t="n"/>
-      <c r="I7" s="6" t="n"/>
-      <c r="J7" s="14" t="n">
+      <c r="F7" s="13" t="n"/>
+      <c r="G7" s="13" t="n"/>
+      <c r="H7" s="13" t="n"/>
+      <c r="I7" s="13" t="n"/>
+      <c r="J7" s="31" t="n">
         <v>-0.01216670559002552</v>
       </c>
-      <c r="K7" s="6" t="n"/>
-      <c r="L7" s="6" t="n"/>
-      <c r="M7" s="14" t="n">
+      <c r="K7" s="13" t="n"/>
+      <c r="L7" s="13" t="n"/>
+      <c r="M7" s="31" t="n">
         <v>-0.0469125</v>
       </c>
     </row>
@@ -1062,20 +1044,20 @@
           <t>2025-Dec</t>
         </is>
       </c>
-      <c r="B11" s="13" t="n">
+      <c r="B11" s="30" t="n">
         <v>-0.010346</v>
       </c>
-      <c r="C11" s="13" t="n">
+      <c r="C11" s="30" t="n">
         <v>-0.0369487719950609</v>
       </c>
-      <c r="D11" s="6" t="n"/>
-      <c r="E11" s="6" t="n"/>
-      <c r="F11" s="6" t="n"/>
-      <c r="G11" s="6" t="n"/>
-      <c r="H11" s="18" t="n">
+      <c r="D11" s="13" t="n"/>
+      <c r="E11" s="13" t="n"/>
+      <c r="F11" s="13" t="n"/>
+      <c r="G11" s="13" t="n"/>
+      <c r="H11" s="33" t="n">
         <v>-0.0469125</v>
       </c>
-      <c r="I11" s="15" t="n">
+      <c r="I11" s="32" t="n">
         <v>-938.25</v>
       </c>
     </row>
@@ -1085,18 +1067,18 @@
           <t>2026-Jan</t>
         </is>
       </c>
-      <c r="B12" s="13" t="n">
+      <c r="B12" s="30" t="n">
         <v>-0.01505685469592246</v>
       </c>
-      <c r="C12" s="6" t="n"/>
-      <c r="D12" s="6" t="n"/>
-      <c r="E12" s="6" t="n"/>
-      <c r="F12" s="6" t="n"/>
-      <c r="G12" s="6" t="n"/>
-      <c r="H12" s="18" t="n">
+      <c r="C12" s="13" t="n"/>
+      <c r="D12" s="13" t="n"/>
+      <c r="E12" s="13" t="n"/>
+      <c r="F12" s="13" t="n"/>
+      <c r="G12" s="13" t="n"/>
+      <c r="H12" s="33" t="n">
         <v>-0.01505685469592246</v>
       </c>
-      <c r="I12" s="15" t="n">
+      <c r="I12" s="32" t="n">
         <v>-287.01</v>
       </c>
     </row>
@@ -1106,18 +1088,18 @@
           <t>2026-Apr</t>
         </is>
       </c>
-      <c r="B13" s="16" t="n">
+      <c r="B13" s="14" t="n">
         <v>0.01262227865738753</v>
       </c>
-      <c r="C13" s="6" t="n"/>
-      <c r="D13" s="6" t="n"/>
-      <c r="E13" s="6" t="n"/>
-      <c r="F13" s="6" t="n"/>
-      <c r="G13" s="6" t="n"/>
-      <c r="H13" s="19" t="n">
+      <c r="C13" s="13" t="n"/>
+      <c r="D13" s="13" t="n"/>
+      <c r="E13" s="13" t="n"/>
+      <c r="F13" s="13" t="n"/>
+      <c r="G13" s="13" t="n"/>
+      <c r="H13" s="17" t="n">
         <v>0.01262227865738753</v>
       </c>
-      <c r="I13" s="20" t="n">
+      <c r="I13" s="16" t="n">
         <v>236.98</v>
       </c>
     </row>
@@ -1127,18 +1109,18 @@
           <t>2026-Sep</t>
         </is>
       </c>
-      <c r="B14" s="13" t="n">
+      <c r="B14" s="30" t="n">
         <v>-0.01216670559002552</v>
       </c>
-      <c r="C14" s="6" t="n"/>
-      <c r="D14" s="6" t="n"/>
-      <c r="E14" s="6" t="n"/>
-      <c r="F14" s="6" t="n"/>
-      <c r="G14" s="6" t="n"/>
-      <c r="H14" s="18" t="n">
+      <c r="C14" s="13" t="n"/>
+      <c r="D14" s="13" t="n"/>
+      <c r="E14" s="13" t="n"/>
+      <c r="F14" s="13" t="n"/>
+      <c r="G14" s="13" t="n"/>
+      <c r="H14" s="33" t="n">
         <v>-0.01216670559002552</v>
       </c>
-      <c r="I14" s="15" t="n">
+      <c r="I14" s="32" t="n">
         <v>-231.31</v>
       </c>
     </row>
@@ -1197,17 +1179,17 @@
           <t>01-Dec-2025</t>
         </is>
       </c>
-      <c r="B18" s="6" t="n"/>
-      <c r="C18" s="13" t="n">
+      <c r="B18" s="13" t="n"/>
+      <c r="C18" s="30" t="n">
         <v>-0.010346</v>
       </c>
-      <c r="D18" s="6" t="n"/>
-      <c r="E18" s="6" t="n"/>
-      <c r="F18" s="6" t="n"/>
-      <c r="G18" s="18" t="n">
+      <c r="D18" s="13" t="n"/>
+      <c r="E18" s="13" t="n"/>
+      <c r="F18" s="13" t="n"/>
+      <c r="G18" s="33" t="n">
         <v>-0.010346</v>
       </c>
-      <c r="H18" s="15" t="n">
+      <c r="H18" s="32" t="n">
         <v>-206.92</v>
       </c>
     </row>
@@ -1217,17 +1199,17 @@
           <t>08-Dec-2025</t>
         </is>
       </c>
-      <c r="B19" s="6" t="n"/>
-      <c r="C19" s="13" t="n">
+      <c r="B19" s="13" t="n"/>
+      <c r="C19" s="30" t="n">
         <v>-0.0369487719950609</v>
       </c>
-      <c r="D19" s="6" t="n"/>
-      <c r="E19" s="6" t="n"/>
-      <c r="F19" s="6" t="n"/>
-      <c r="G19" s="18" t="n">
+      <c r="D19" s="13" t="n"/>
+      <c r="E19" s="13" t="n"/>
+      <c r="F19" s="13" t="n"/>
+      <c r="G19" s="33" t="n">
         <v>-0.0369487719950609</v>
       </c>
-      <c r="H19" s="15" t="n">
+      <c r="H19" s="32" t="n">
         <v>-731.33</v>
       </c>
     </row>
@@ -1237,17 +1219,17 @@
           <t>26-Jan-2026</t>
         </is>
       </c>
-      <c r="B20" s="6" t="n"/>
-      <c r="C20" s="13" t="n">
+      <c r="B20" s="13" t="n"/>
+      <c r="C20" s="30" t="n">
         <v>-0.01505685469592246</v>
       </c>
-      <c r="D20" s="6" t="n"/>
-      <c r="E20" s="6" t="n"/>
-      <c r="F20" s="6" t="n"/>
-      <c r="G20" s="18" t="n">
+      <c r="D20" s="13" t="n"/>
+      <c r="E20" s="13" t="n"/>
+      <c r="F20" s="13" t="n"/>
+      <c r="G20" s="33" t="n">
         <v>-0.01505685469592246</v>
       </c>
-      <c r="H20" s="15" t="n">
+      <c r="H20" s="32" t="n">
         <v>-287.01</v>
       </c>
     </row>
@@ -1257,17 +1239,17 @@
           <t>06-Apr-2026</t>
         </is>
       </c>
-      <c r="B21" s="6" t="n"/>
-      <c r="C21" s="16" t="n">
+      <c r="B21" s="13" t="n"/>
+      <c r="C21" s="14" t="n">
         <v>0.01262227865738753</v>
       </c>
-      <c r="D21" s="6" t="n"/>
-      <c r="E21" s="6" t="n"/>
-      <c r="F21" s="6" t="n"/>
-      <c r="G21" s="19" t="n">
+      <c r="D21" s="13" t="n"/>
+      <c r="E21" s="13" t="n"/>
+      <c r="F21" s="13" t="n"/>
+      <c r="G21" s="17" t="n">
         <v>0.01262227865738753</v>
       </c>
-      <c r="H21" s="20" t="n">
+      <c r="H21" s="16" t="n">
         <v>236.98</v>
       </c>
     </row>
@@ -1277,17 +1259,17 @@
           <t>07-Sep-2026</t>
         </is>
       </c>
-      <c r="B22" s="6" t="n"/>
-      <c r="C22" s="13" t="n">
+      <c r="B22" s="13" t="n"/>
+      <c r="C22" s="30" t="n">
         <v>-0.01216670559002552</v>
       </c>
-      <c r="D22" s="6" t="n"/>
-      <c r="E22" s="6" t="n"/>
-      <c r="F22" s="6" t="n"/>
-      <c r="G22" s="18" t="n">
+      <c r="D22" s="13" t="n"/>
+      <c r="E22" s="13" t="n"/>
+      <c r="F22" s="13" t="n"/>
+      <c r="G22" s="33" t="n">
         <v>-0.01216670559002552</v>
       </c>
-      <c r="H22" s="15" t="n">
+      <c r="H22" s="32" t="n">
         <v>-231.31</v>
       </c>
     </row>
@@ -1304,11 +1286,11 @@
           <t>All trades</t>
         </is>
       </c>
-      <c r="B25" s="21" t="n">
+      <c r="B25" s="18" t="n">
         <v>7</v>
       </c>
-      <c r="C25" s="22" t="n"/>
-      <c r="D25" s="23" t="n"/>
+      <c r="C25" s="19" t="n"/>
+      <c r="D25" s="20" t="n"/>
     </row>
     <row r="26">
       <c r="A26" s="3" t="inlineStr">
@@ -1316,13 +1298,13 @@
           <t>Winners</t>
         </is>
       </c>
-      <c r="B26" s="24" t="inlineStr">
+      <c r="B26" s="21" t="inlineStr">
         <is>
           <t>1 (14.3%)</t>
         </is>
       </c>
-      <c r="C26" s="22" t="n"/>
-      <c r="D26" s="23" t="n"/>
+      <c r="C26" s="19" t="n"/>
+      <c r="D26" s="20" t="n"/>
     </row>
     <row r="27">
       <c r="A27" s="3" t="inlineStr">
@@ -1330,13 +1312,13 @@
           <t>Losers</t>
         </is>
       </c>
-      <c r="B27" s="24" t="inlineStr">
+      <c r="B27" s="21" t="inlineStr">
         <is>
           <t>6 (85.7%)</t>
         </is>
       </c>
-      <c r="C27" s="22" t="n"/>
-      <c r="D27" s="23" t="n"/>
+      <c r="C27" s="19" t="n"/>
+      <c r="D27" s="20" t="n"/>
     </row>
     <row r="28">
       <c r="A28" s="3" t="inlineStr">
@@ -1344,11 +1326,11 @@
           <t>Net P&amp;L (Rs)</t>
         </is>
       </c>
-      <c r="B28" s="25" t="n">
+      <c r="B28" s="23" t="n">
         <v>-1219.59</v>
       </c>
-      <c r="C28" s="22" t="n"/>
-      <c r="D28" s="23" t="n"/>
+      <c r="C28" s="19" t="n"/>
+      <c r="D28" s="20" t="n"/>
     </row>
     <row r="29">
       <c r="A29" s="3" t="inlineStr">
@@ -1356,11 +1338,11 @@
           <t>Total Profit (Rs)</t>
         </is>
       </c>
-      <c r="B29" s="26" t="n">
+      <c r="B29" s="22" t="n">
         <v>236.98</v>
       </c>
-      <c r="C29" s="22" t="n"/>
-      <c r="D29" s="23" t="n"/>
+      <c r="C29" s="19" t="n"/>
+      <c r="D29" s="20" t="n"/>
     </row>
     <row r="30">
       <c r="A30" s="3" t="inlineStr">
@@ -1368,11 +1350,11 @@
           <t>Total Loss (Rs)</t>
         </is>
       </c>
-      <c r="B30" s="25" t="n">
+      <c r="B30" s="23" t="n">
         <v>-1456.57</v>
       </c>
-      <c r="C30" s="22" t="n"/>
-      <c r="D30" s="23" t="n"/>
+      <c r="C30" s="19" t="n"/>
+      <c r="D30" s="20" t="n"/>
     </row>
     <row r="31">
       <c r="A31" s="3" t="inlineStr">
@@ -1380,11 +1362,11 @@
           <t>Transaction costs (Rs)</t>
         </is>
       </c>
-      <c r="B31" s="27" t="n">
+      <c r="B31" s="24" t="n">
         <v>348.39</v>
       </c>
-      <c r="C31" s="22" t="n"/>
-      <c r="D31" s="23" t="n"/>
+      <c r="C31" s="19" t="n"/>
+      <c r="D31" s="20" t="n"/>
     </row>
     <row r="32">
       <c r="A32" s="3" t="inlineStr">
@@ -1392,11 +1374,11 @@
           <t>Avg Profit/Loss per trade (Rs)</t>
         </is>
       </c>
-      <c r="B32" s="25" t="n">
+      <c r="B32" s="23" t="n">
         <v>-174.23</v>
       </c>
-      <c r="C32" s="22" t="n"/>
-      <c r="D32" s="23" t="n"/>
+      <c r="C32" s="19" t="n"/>
+      <c r="D32" s="20" t="n"/>
     </row>
     <row r="33">
       <c r="A33" s="3" t="inlineStr">
@@ -1404,11 +1386,11 @@
           <t>Avg Profit/Loss per trade (% of premium)</t>
         </is>
       </c>
-      <c r="B33" s="28" t="n">
+      <c r="B33" s="25" t="n">
         <v>-10.42</v>
       </c>
-      <c r="C33" s="22" t="n"/>
-      <c r="D33" s="23" t="n"/>
+      <c r="C33" s="19" t="n"/>
+      <c r="D33" s="20" t="n"/>
     </row>
     <row r="34">
       <c r="A34" s="3" t="inlineStr">
@@ -1416,11 +1398,11 @@
           <t>Avg Win (Rs)</t>
         </is>
       </c>
-      <c r="B34" s="26" t="n">
+      <c r="B34" s="22" t="n">
         <v>236.98</v>
       </c>
-      <c r="C34" s="22" t="n"/>
-      <c r="D34" s="23" t="n"/>
+      <c r="C34" s="19" t="n"/>
+      <c r="D34" s="20" t="n"/>
     </row>
     <row r="35">
       <c r="A35" s="3" t="inlineStr">
@@ -1428,11 +1410,11 @@
           <t>Avg Win (% of premium)</t>
         </is>
       </c>
-      <c r="B35" s="29" t="n">
+      <c r="B35" s="26" t="n">
         <v>16.17</v>
       </c>
-      <c r="C35" s="22" t="n"/>
-      <c r="D35" s="23" t="n"/>
+      <c r="C35" s="19" t="n"/>
+      <c r="D35" s="20" t="n"/>
     </row>
     <row r="36">
       <c r="A36" s="3" t="inlineStr">
@@ -1440,11 +1422,11 @@
           <t>Avg Loss (Rs)</t>
         </is>
       </c>
-      <c r="B36" s="25" t="n">
+      <c r="B36" s="23" t="n">
         <v>-242.76</v>
       </c>
-      <c r="C36" s="22" t="n"/>
-      <c r="D36" s="23" t="n"/>
+      <c r="C36" s="19" t="n"/>
+      <c r="D36" s="20" t="n"/>
     </row>
     <row r="37">
       <c r="A37" s="3" t="inlineStr">
@@ -1452,11 +1434,11 @@
           <t>Avg Loss (% of premium)</t>
         </is>
       </c>
-      <c r="B37" s="30" t="n">
+      <c r="B37" s="27" t="n">
         <v>-14.85</v>
       </c>
-      <c r="C37" s="22" t="n"/>
-      <c r="D37" s="23" t="n"/>
+      <c r="C37" s="19" t="n"/>
+      <c r="D37" s="20" t="n"/>
     </row>
     <row r="38">
       <c r="A38" s="3" t="inlineStr">
@@ -1464,11 +1446,11 @@
           <t>Largest Win (Rs)</t>
         </is>
       </c>
-      <c r="B38" s="26" t="n">
+      <c r="B38" s="22" t="n">
         <v>236.98</v>
       </c>
-      <c r="C38" s="22" t="n"/>
-      <c r="D38" s="23" t="n"/>
+      <c r="C38" s="19" t="n"/>
+      <c r="D38" s="20" t="n"/>
     </row>
     <row r="39">
       <c r="A39" s="3" t="inlineStr">
@@ -1476,11 +1458,11 @@
           <t>Largest Loss (Rs)</t>
         </is>
       </c>
-      <c r="B39" s="25" t="n">
+      <c r="B39" s="23" t="n">
         <v>-295.95</v>
       </c>
-      <c r="C39" s="22" t="n"/>
-      <c r="D39" s="23" t="n"/>
+      <c r="C39" s="19" t="n"/>
+      <c r="D39" s="20" t="n"/>
     </row>
     <row r="40">
       <c r="A40" s="3" t="inlineStr">
@@ -1488,11 +1470,11 @@
           <t>Max Consecutive Wins</t>
         </is>
       </c>
-      <c r="B40" s="21" t="n">
+      <c r="B40" s="18" t="n">
         <v>1</v>
       </c>
-      <c r="C40" s="22" t="n"/>
-      <c r="D40" s="23" t="n"/>
+      <c r="C40" s="19" t="n"/>
+      <c r="D40" s="20" t="n"/>
     </row>
     <row r="41">
       <c r="A41" s="3" t="inlineStr">
@@ -1500,11 +1482,11 @@
           <t>Max Consecutive Losses</t>
         </is>
       </c>
-      <c r="B41" s="21" t="n">
+      <c r="B41" s="18" t="n">
         <v>5</v>
       </c>
-      <c r="C41" s="22" t="n"/>
-      <c r="D41" s="23" t="n"/>
+      <c r="C41" s="19" t="n"/>
+      <c r="D41" s="20" t="n"/>
     </row>
     <row r="42">
       <c r="A42" s="3" t="inlineStr">
@@ -1512,11 +1494,11 @@
           <t>Max trade drawdown (Rs)</t>
         </is>
       </c>
-      <c r="B42" s="25" t="n">
+      <c r="B42" s="23" t="n">
         <v>-295.95</v>
       </c>
-      <c r="C42" s="22" t="n"/>
-      <c r="D42" s="23" t="n"/>
+      <c r="C42" s="19" t="n"/>
+      <c r="D42" s="20" t="n"/>
     </row>
     <row r="43">
       <c r="A43" s="3" t="inlineStr">
@@ -1524,11 +1506,11 @@
           <t>Max system drawdown (Rs)</t>
         </is>
       </c>
-      <c r="B43" s="25" t="n">
+      <c r="B43" s="23" t="n">
         <v>-1225.26</v>
       </c>
-      <c r="C43" s="22" t="n"/>
-      <c r="D43" s="23" t="n"/>
+      <c r="C43" s="19" t="n"/>
+      <c r="D43" s="20" t="n"/>
     </row>
     <row r="44">
       <c r="A44" s="3" t="inlineStr">
@@ -1536,11 +1518,11 @@
           <t>Max system drawdown (%)</t>
         </is>
       </c>
-      <c r="B44" s="30" t="n">
+      <c r="B44" s="27" t="n">
         <v>-6.13</v>
       </c>
-      <c r="C44" s="22" t="n"/>
-      <c r="D44" s="23" t="n"/>
+      <c r="C44" s="19" t="n"/>
+      <c r="D44" s="20" t="n"/>
     </row>
     <row r="45">
       <c r="A45" s="3" t="inlineStr">
@@ -1548,11 +1530,11 @@
           <t>Recovery Factor</t>
         </is>
       </c>
-      <c r="B45" s="31" t="n">
+      <c r="B45" s="28" t="n">
         <v>-1</v>
       </c>
-      <c r="C45" s="22" t="n"/>
-      <c r="D45" s="23" t="n"/>
+      <c r="C45" s="19" t="n"/>
+      <c r="D45" s="20" t="n"/>
     </row>
     <row r="46">
       <c r="A46" s="3" t="inlineStr">
@@ -1560,11 +1542,11 @@
           <t>Profit Factor</t>
         </is>
       </c>
-      <c r="B46" s="31" t="n">
+      <c r="B46" s="28" t="n">
         <v>0.16</v>
       </c>
-      <c r="C46" s="22" t="n"/>
-      <c r="D46" s="23" t="n"/>
+      <c r="C46" s="19" t="n"/>
+      <c r="D46" s="20" t="n"/>
     </row>
     <row r="47">
       <c r="A47" s="3" t="inlineStr">
@@ -1572,11 +1554,11 @@
           <t>Payoff Ratio (avg win / avg loss)</t>
         </is>
       </c>
-      <c r="B47" s="31" t="n">
+      <c r="B47" s="28" t="n">
         <v>0.98</v>
       </c>
-      <c r="C47" s="22" t="n"/>
-      <c r="D47" s="23" t="n"/>
+      <c r="C47" s="19" t="n"/>
+      <c r="D47" s="20" t="n"/>
     </row>
     <row r="48">
       <c r="A48" s="3" t="inlineStr">
@@ -1584,14 +1566,14 @@
           <t>Sharpe Ratio (annualized)</t>
         </is>
       </c>
-      <c r="B48" s="31" t="n">
+      <c r="B48" s="28" t="n">
         <v>-12.48</v>
       </c>
-      <c r="C48" s="22" t="n"/>
-      <c r="D48" s="23" t="n"/>
+      <c r="C48" s="19" t="n"/>
+      <c r="D48" s="20" t="n"/>
     </row>
     <row r="50">
-      <c r="A50" s="5" t="inlineStr">
+      <c r="A50" s="11" t="inlineStr">
         <is>
           <t>Caveat: with only a handful of trades these numbers (Sharpe, profit factor, drawdown %) are not statistically reliable. Watch this over weeks/months before drawing conclusions.</t>
         </is>
@@ -1635,7 +1617,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
-  <dimension ref="A1:A3"/>
+  <dimension ref="A1:O42"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="40" customWidth="1" min="1" max="1"/>
@@ -1663,13 +1645,614 @@
       </c>
     </row>
     <row r="3">
-      <c r="A3" s="5" t="inlineStr">
-        <is>
-          <t>No trades yet for this index -- this fills in automatically as the bot trades.</t>
+      <c r="A3" s="12" t="inlineStr">
+        <is>
+          <t>MONTHLY returns (% of capital at start of month)</t>
+        </is>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" s="2" t="inlineStr">
+        <is>
+          <t>Year</t>
+        </is>
+      </c>
+      <c r="B4" s="2" t="inlineStr">
+        <is>
+          <t>Jan</t>
+        </is>
+      </c>
+      <c r="C4" s="2" t="inlineStr">
+        <is>
+          <t>Feb</t>
+        </is>
+      </c>
+      <c r="D4" s="2" t="inlineStr">
+        <is>
+          <t>Mar</t>
+        </is>
+      </c>
+      <c r="E4" s="2" t="inlineStr">
+        <is>
+          <t>Apr</t>
+        </is>
+      </c>
+      <c r="F4" s="2" t="inlineStr">
+        <is>
+          <t>May</t>
+        </is>
+      </c>
+      <c r="G4" s="2" t="inlineStr">
+        <is>
+          <t>Jun</t>
+        </is>
+      </c>
+      <c r="H4" s="2" t="inlineStr">
+        <is>
+          <t>Jul</t>
+        </is>
+      </c>
+      <c r="I4" s="2" t="inlineStr">
+        <is>
+          <t>Aug</t>
+        </is>
+      </c>
+      <c r="J4" s="2" t="inlineStr">
+        <is>
+          <t>Sep</t>
+        </is>
+      </c>
+      <c r="K4" s="2" t="inlineStr">
+        <is>
+          <t>Oct</t>
+        </is>
+      </c>
+      <c r="L4" s="2" t="inlineStr">
+        <is>
+          <t>Nov</t>
+        </is>
+      </c>
+      <c r="M4" s="2" t="inlineStr">
+        <is>
+          <t>Dec</t>
+        </is>
+      </c>
+      <c r="N4" s="2" t="inlineStr">
+        <is>
+          <t>Yr %</t>
+        </is>
+      </c>
+      <c r="O4" s="2" t="inlineStr">
+        <is>
+          <t>Yr P&amp;L (Rs)</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" s="3" t="n">
+        <v>2026</v>
+      </c>
+      <c r="B5" s="13" t="n"/>
+      <c r="C5" s="13" t="n"/>
+      <c r="D5" s="13" t="n"/>
+      <c r="E5" s="13" t="n"/>
+      <c r="F5" s="13" t="n"/>
+      <c r="G5" s="13" t="n"/>
+      <c r="H5" s="13" t="n"/>
+      <c r="I5" s="13" t="n"/>
+      <c r="J5" s="13" t="n"/>
+      <c r="K5" s="14" t="n">
+        <v>0.020116</v>
+      </c>
+      <c r="L5" s="13" t="n"/>
+      <c r="M5" s="13" t="n"/>
+      <c r="N5" s="15" t="n">
+        <v>0.02011600000000002</v>
+      </c>
+      <c r="O5" s="16" t="n">
+        <v>402.32</v>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" s="3" t="inlineStr">
+        <is>
+          <t>Avg</t>
+        </is>
+      </c>
+      <c r="B6" s="13" t="n"/>
+      <c r="C6" s="13" t="n"/>
+      <c r="D6" s="13" t="n"/>
+      <c r="E6" s="13" t="n"/>
+      <c r="F6" s="13" t="n"/>
+      <c r="G6" s="13" t="n"/>
+      <c r="H6" s="13" t="n"/>
+      <c r="I6" s="13" t="n"/>
+      <c r="J6" s="13" t="n"/>
+      <c r="K6" s="15" t="n">
+        <v>0.020116</v>
+      </c>
+      <c r="L6" s="13" t="n"/>
+      <c r="M6" s="13" t="n"/>
+    </row>
+    <row r="8">
+      <c r="A8" s="12" t="inlineStr">
+        <is>
+          <t>WEEKLY returns (% of capital at start of that week; weeks split at month edges)</t>
+        </is>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" s="2" t="inlineStr">
+        <is>
+          <t>Month</t>
+        </is>
+      </c>
+      <c r="B9" s="2" t="inlineStr">
+        <is>
+          <t>W1</t>
+        </is>
+      </c>
+      <c r="C9" s="2" t="inlineStr">
+        <is>
+          <t>W2</t>
+        </is>
+      </c>
+      <c r="D9" s="2" t="inlineStr">
+        <is>
+          <t>W3</t>
+        </is>
+      </c>
+      <c r="E9" s="2" t="inlineStr">
+        <is>
+          <t>W4</t>
+        </is>
+      </c>
+      <c r="F9" s="2" t="inlineStr">
+        <is>
+          <t>W5</t>
+        </is>
+      </c>
+      <c r="G9" s="2" t="inlineStr">
+        <is>
+          <t>W6</t>
+        </is>
+      </c>
+      <c r="H9" s="2" t="inlineStr">
+        <is>
+          <t>Month %</t>
+        </is>
+      </c>
+      <c r="I9" s="2" t="inlineStr">
+        <is>
+          <t>Month P&amp;L (Rs)</t>
+        </is>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" s="3" t="inlineStr">
+        <is>
+          <t>2026-Oct</t>
+        </is>
+      </c>
+      <c r="B10" s="14" t="n">
+        <v>0.020116</v>
+      </c>
+      <c r="C10" s="13" t="n"/>
+      <c r="D10" s="13" t="n"/>
+      <c r="E10" s="13" t="n"/>
+      <c r="F10" s="13" t="n"/>
+      <c r="G10" s="13" t="n"/>
+      <c r="H10" s="17" t="n">
+        <v>0.020116</v>
+      </c>
+      <c r="I10" s="16" t="n">
+        <v>402.32</v>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" s="12" t="inlineStr">
+        <is>
+          <t>DAILY returns (% of capital at start of that day; blank = no trade that day)</t>
+        </is>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" s="2" t="inlineStr">
+        <is>
+          <t>Week starting (Mon)</t>
+        </is>
+      </c>
+      <c r="B13" s="2" t="inlineStr">
+        <is>
+          <t>Mon</t>
+        </is>
+      </c>
+      <c r="C13" s="2" t="inlineStr">
+        <is>
+          <t>Tue</t>
+        </is>
+      </c>
+      <c r="D13" s="2" t="inlineStr">
+        <is>
+          <t>Wed</t>
+        </is>
+      </c>
+      <c r="E13" s="2" t="inlineStr">
+        <is>
+          <t>Thu</t>
+        </is>
+      </c>
+      <c r="F13" s="2" t="inlineStr">
+        <is>
+          <t>Fri</t>
+        </is>
+      </c>
+      <c r="G13" s="2" t="inlineStr">
+        <is>
+          <t>Week %</t>
+        </is>
+      </c>
+      <c r="H13" s="2" t="inlineStr">
+        <is>
+          <t>Week P&amp;L (Rs)</t>
+        </is>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" s="3" t="inlineStr">
+        <is>
+          <t>19-Oct-2026</t>
+        </is>
+      </c>
+      <c r="B14" s="14" t="n">
+        <v>0.020116</v>
+      </c>
+      <c r="C14" s="13" t="n"/>
+      <c r="D14" s="13" t="n"/>
+      <c r="E14" s="13" t="n"/>
+      <c r="F14" s="13" t="n"/>
+      <c r="G14" s="17" t="n">
+        <v>0.020116</v>
+      </c>
+      <c r="H14" s="16" t="n">
+        <v>402.32</v>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" s="12" t="inlineStr">
+        <is>
+          <t>STATISTICS (all trades for this index)</t>
+        </is>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" s="3" t="inlineStr">
+        <is>
+          <t>All trades</t>
+        </is>
+      </c>
+      <c r="B17" s="18" t="n">
+        <v>2</v>
+      </c>
+      <c r="C17" s="19" t="n"/>
+      <c r="D17" s="20" t="n"/>
+    </row>
+    <row r="18">
+      <c r="A18" s="3" t="inlineStr">
+        <is>
+          <t>Winners</t>
+        </is>
+      </c>
+      <c r="B18" s="21" t="inlineStr">
+        <is>
+          <t>1 (50.0%)</t>
+        </is>
+      </c>
+      <c r="C18" s="19" t="n"/>
+      <c r="D18" s="20" t="n"/>
+    </row>
+    <row r="19">
+      <c r="A19" s="3" t="inlineStr">
+        <is>
+          <t>Losers</t>
+        </is>
+      </c>
+      <c r="B19" s="21" t="inlineStr">
+        <is>
+          <t>1 (50.0%)</t>
+        </is>
+      </c>
+      <c r="C19" s="19" t="n"/>
+      <c r="D19" s="20" t="n"/>
+    </row>
+    <row r="20">
+      <c r="A20" s="3" t="inlineStr">
+        <is>
+          <t>Net P&amp;L (Rs)</t>
+        </is>
+      </c>
+      <c r="B20" s="22" t="n">
+        <v>402.32</v>
+      </c>
+      <c r="C20" s="19" t="n"/>
+      <c r="D20" s="20" t="n"/>
+    </row>
+    <row r="21">
+      <c r="A21" s="3" t="inlineStr">
+        <is>
+          <t>Total Profit (Rs)</t>
+        </is>
+      </c>
+      <c r="B21" s="22" t="n">
+        <v>626.0700000000001</v>
+      </c>
+      <c r="C21" s="19" t="n"/>
+      <c r="D21" s="20" t="n"/>
+    </row>
+    <row r="22">
+      <c r="A22" s="3" t="inlineStr">
+        <is>
+          <t>Total Loss (Rs)</t>
+        </is>
+      </c>
+      <c r="B22" s="23" t="n">
+        <v>-223.75</v>
+      </c>
+      <c r="C22" s="19" t="n"/>
+      <c r="D22" s="20" t="n"/>
+    </row>
+    <row r="23">
+      <c r="A23" s="3" t="inlineStr">
+        <is>
+          <t>Transaction costs (Rs)</t>
+        </is>
+      </c>
+      <c r="B23" s="24" t="n">
+        <v>47.68</v>
+      </c>
+      <c r="C23" s="19" t="n"/>
+      <c r="D23" s="20" t="n"/>
+    </row>
+    <row r="24">
+      <c r="A24" s="3" t="inlineStr">
+        <is>
+          <t>Avg Profit/Loss per trade (Rs)</t>
+        </is>
+      </c>
+      <c r="B24" s="22" t="n">
+        <v>201.16</v>
+      </c>
+      <c r="C24" s="19" t="n"/>
+      <c r="D24" s="20" t="n"/>
+    </row>
+    <row r="25">
+      <c r="A25" s="3" t="inlineStr">
+        <is>
+          <t>Avg Profit/Loss per trade (% of premium)</t>
+        </is>
+      </c>
+      <c r="B25" s="25" t="n">
+        <v>30.69</v>
+      </c>
+      <c r="C25" s="19" t="n"/>
+      <c r="D25" s="20" t="n"/>
+    </row>
+    <row r="26">
+      <c r="A26" s="3" t="inlineStr">
+        <is>
+          <t>Avg Win (Rs)</t>
+        </is>
+      </c>
+      <c r="B26" s="22" t="n">
+        <v>626.0700000000001</v>
+      </c>
+      <c r="C26" s="19" t="n"/>
+      <c r="D26" s="20" t="n"/>
+    </row>
+    <row r="27">
+      <c r="A27" s="3" t="inlineStr">
+        <is>
+          <t>Avg Win (% of premium)</t>
+        </is>
+      </c>
+      <c r="B27" s="26" t="n">
+        <v>97.90000000000001</v>
+      </c>
+      <c r="C27" s="19" t="n"/>
+      <c r="D27" s="20" t="n"/>
+    </row>
+    <row r="28">
+      <c r="A28" s="3" t="inlineStr">
+        <is>
+          <t>Avg Loss (Rs)</t>
+        </is>
+      </c>
+      <c r="B28" s="23" t="n">
+        <v>-223.75</v>
+      </c>
+      <c r="C28" s="19" t="n"/>
+      <c r="D28" s="20" t="n"/>
+    </row>
+    <row r="29">
+      <c r="A29" s="3" t="inlineStr">
+        <is>
+          <t>Avg Loss (% of premium)</t>
+        </is>
+      </c>
+      <c r="B29" s="27" t="n">
+        <v>-36.52</v>
+      </c>
+      <c r="C29" s="19" t="n"/>
+      <c r="D29" s="20" t="n"/>
+    </row>
+    <row r="30">
+      <c r="A30" s="3" t="inlineStr">
+        <is>
+          <t>Largest Win (Rs)</t>
+        </is>
+      </c>
+      <c r="B30" s="22" t="n">
+        <v>626.0700000000001</v>
+      </c>
+      <c r="C30" s="19" t="n"/>
+      <c r="D30" s="20" t="n"/>
+    </row>
+    <row r="31">
+      <c r="A31" s="3" t="inlineStr">
+        <is>
+          <t>Largest Loss (Rs)</t>
+        </is>
+      </c>
+      <c r="B31" s="23" t="n">
+        <v>-223.75</v>
+      </c>
+      <c r="C31" s="19" t="n"/>
+      <c r="D31" s="20" t="n"/>
+    </row>
+    <row r="32">
+      <c r="A32" s="3" t="inlineStr">
+        <is>
+          <t>Max Consecutive Wins</t>
+        </is>
+      </c>
+      <c r="B32" s="18" t="n">
+        <v>1</v>
+      </c>
+      <c r="C32" s="19" t="n"/>
+      <c r="D32" s="20" t="n"/>
+    </row>
+    <row r="33">
+      <c r="A33" s="3" t="inlineStr">
+        <is>
+          <t>Max Consecutive Losses</t>
+        </is>
+      </c>
+      <c r="B33" s="18" t="n">
+        <v>1</v>
+      </c>
+      <c r="C33" s="19" t="n"/>
+      <c r="D33" s="20" t="n"/>
+    </row>
+    <row r="34">
+      <c r="A34" s="3" t="inlineStr">
+        <is>
+          <t>Max trade drawdown (Rs)</t>
+        </is>
+      </c>
+      <c r="B34" s="23" t="n">
+        <v>-223.75</v>
+      </c>
+      <c r="C34" s="19" t="n"/>
+      <c r="D34" s="20" t="n"/>
+    </row>
+    <row r="35">
+      <c r="A35" s="3" t="inlineStr">
+        <is>
+          <t>Max system drawdown (Rs)</t>
+        </is>
+      </c>
+      <c r="B35" s="23" t="n">
+        <v>-223.75</v>
+      </c>
+      <c r="C35" s="19" t="n"/>
+      <c r="D35" s="20" t="n"/>
+    </row>
+    <row r="36">
+      <c r="A36" s="3" t="inlineStr">
+        <is>
+          <t>Max system drawdown (%)</t>
+        </is>
+      </c>
+      <c r="B36" s="27" t="n">
+        <v>-1.08</v>
+      </c>
+      <c r="C36" s="19" t="n"/>
+      <c r="D36" s="20" t="n"/>
+    </row>
+    <row r="37">
+      <c r="A37" s="3" t="inlineStr">
+        <is>
+          <t>Recovery Factor</t>
+        </is>
+      </c>
+      <c r="B37" s="28" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="C37" s="19" t="n"/>
+      <c r="D37" s="20" t="n"/>
+    </row>
+    <row r="38">
+      <c r="A38" s="3" t="inlineStr">
+        <is>
+          <t>Profit Factor</t>
+        </is>
+      </c>
+      <c r="B38" s="28" t="n">
+        <v>2.8</v>
+      </c>
+      <c r="C38" s="19" t="n"/>
+      <c r="D38" s="20" t="n"/>
+    </row>
+    <row r="39">
+      <c r="A39" s="3" t="inlineStr">
+        <is>
+          <t>Payoff Ratio (avg win / avg loss)</t>
+        </is>
+      </c>
+      <c r="B39" s="28" t="n">
+        <v>2.8</v>
+      </c>
+      <c r="C39" s="19" t="n"/>
+      <c r="D39" s="20" t="n"/>
+    </row>
+    <row r="40">
+      <c r="A40" s="3" t="inlineStr">
+        <is>
+          <t>Sharpe Ratio (annualized)</t>
+        </is>
+      </c>
+      <c r="B40" s="21" t="inlineStr">
+        <is>
+          <t>N/A (needs 2+ trading days)</t>
+        </is>
+      </c>
+      <c r="C40" s="19" t="n"/>
+      <c r="D40" s="20" t="n"/>
+    </row>
+    <row r="42">
+      <c r="A42" s="11" t="inlineStr">
+        <is>
+          <t>Caveat: with only a handful of trades these numbers (Sharpe, profit factor, drawdown %) are not statistically reliable. Watch this over weeks/months before drawing conclusions.</t>
         </is>
       </c>
     </row>
   </sheetData>
+  <mergeCells count="24">
+    <mergeCell ref="B23:D23"/>
+    <mergeCell ref="B17:D17"/>
+    <mergeCell ref="B29:D29"/>
+    <mergeCell ref="B38:D38"/>
+    <mergeCell ref="B34:D34"/>
+    <mergeCell ref="B28:D28"/>
+    <mergeCell ref="B19:D19"/>
+    <mergeCell ref="B37:D37"/>
+    <mergeCell ref="B40:D40"/>
+    <mergeCell ref="B30:D30"/>
+    <mergeCell ref="B24:D24"/>
+    <mergeCell ref="B20:D20"/>
+    <mergeCell ref="B33:D33"/>
+    <mergeCell ref="B36:D36"/>
+    <mergeCell ref="B32:D32"/>
+    <mergeCell ref="B35:D35"/>
+    <mergeCell ref="B26:D26"/>
+    <mergeCell ref="B25:D25"/>
+    <mergeCell ref="B31:D31"/>
+    <mergeCell ref="B22:D22"/>
+    <mergeCell ref="B18:D18"/>
+    <mergeCell ref="B27:D27"/>
+    <mergeCell ref="B21:D21"/>
+    <mergeCell ref="B39:D39"/>
+  </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
   <pageSetup orientation="landscape" fitToHeight="0" fitToWidth="1"/>
 </worksheet>
@@ -1709,7 +2292,7 @@
       </c>
     </row>
     <row r="3">
-      <c r="A3" s="5" t="inlineStr">
+      <c r="A3" s="11" t="inlineStr">
         <is>
           <t>No trades yet for this index -- this fills in automatically as the bot trades.</t>
         </is>
@@ -1755,7 +2338,7 @@
       </c>
     </row>
     <row r="3">
-      <c r="A3" s="5" t="inlineStr">
+      <c r="A3" s="11" t="inlineStr">
         <is>
           <t>No trades yet for this index -- this fills in automatically as the bot trades.</t>
         </is>
@@ -1773,7 +2356,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
-  <dimension ref="A1:A3"/>
+  <dimension ref="A1:O42"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="40" customWidth="1" min="1" max="1"/>
@@ -1801,13 +2384,614 @@
       </c>
     </row>
     <row r="3">
-      <c r="A3" s="5" t="inlineStr">
-        <is>
-          <t>No trades yet for this index -- this fills in automatically as the bot trades.</t>
+      <c r="A3" s="12" t="inlineStr">
+        <is>
+          <t>MONTHLY returns (% of capital at start of month)</t>
+        </is>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" s="2" t="inlineStr">
+        <is>
+          <t>Year</t>
+        </is>
+      </c>
+      <c r="B4" s="2" t="inlineStr">
+        <is>
+          <t>Jan</t>
+        </is>
+      </c>
+      <c r="C4" s="2" t="inlineStr">
+        <is>
+          <t>Feb</t>
+        </is>
+      </c>
+      <c r="D4" s="2" t="inlineStr">
+        <is>
+          <t>Mar</t>
+        </is>
+      </c>
+      <c r="E4" s="2" t="inlineStr">
+        <is>
+          <t>Apr</t>
+        </is>
+      </c>
+      <c r="F4" s="2" t="inlineStr">
+        <is>
+          <t>May</t>
+        </is>
+      </c>
+      <c r="G4" s="2" t="inlineStr">
+        <is>
+          <t>Jun</t>
+        </is>
+      </c>
+      <c r="H4" s="2" t="inlineStr">
+        <is>
+          <t>Jul</t>
+        </is>
+      </c>
+      <c r="I4" s="2" t="inlineStr">
+        <is>
+          <t>Aug</t>
+        </is>
+      </c>
+      <c r="J4" s="2" t="inlineStr">
+        <is>
+          <t>Sep</t>
+        </is>
+      </c>
+      <c r="K4" s="2" t="inlineStr">
+        <is>
+          <t>Oct</t>
+        </is>
+      </c>
+      <c r="L4" s="2" t="inlineStr">
+        <is>
+          <t>Nov</t>
+        </is>
+      </c>
+      <c r="M4" s="2" t="inlineStr">
+        <is>
+          <t>Dec</t>
+        </is>
+      </c>
+      <c r="N4" s="2" t="inlineStr">
+        <is>
+          <t>Yr %</t>
+        </is>
+      </c>
+      <c r="O4" s="2" t="inlineStr">
+        <is>
+          <t>Yr P&amp;L (Rs)</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" s="3" t="n">
+        <v>2026</v>
+      </c>
+      <c r="B5" s="13" t="n"/>
+      <c r="C5" s="13" t="n"/>
+      <c r="D5" s="13" t="n"/>
+      <c r="E5" s="13" t="n"/>
+      <c r="F5" s="13" t="n"/>
+      <c r="G5" s="13" t="n"/>
+      <c r="H5" s="13" t="n"/>
+      <c r="I5" s="13" t="n"/>
+      <c r="J5" s="13" t="n"/>
+      <c r="K5" s="14" t="n">
+        <v>0.020116</v>
+      </c>
+      <c r="L5" s="13" t="n"/>
+      <c r="M5" s="13" t="n"/>
+      <c r="N5" s="15" t="n">
+        <v>0.02011600000000002</v>
+      </c>
+      <c r="O5" s="16" t="n">
+        <v>402.32</v>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" s="3" t="inlineStr">
+        <is>
+          <t>Avg</t>
+        </is>
+      </c>
+      <c r="B6" s="13" t="n"/>
+      <c r="C6" s="13" t="n"/>
+      <c r="D6" s="13" t="n"/>
+      <c r="E6" s="13" t="n"/>
+      <c r="F6" s="13" t="n"/>
+      <c r="G6" s="13" t="n"/>
+      <c r="H6" s="13" t="n"/>
+      <c r="I6" s="13" t="n"/>
+      <c r="J6" s="13" t="n"/>
+      <c r="K6" s="15" t="n">
+        <v>0.020116</v>
+      </c>
+      <c r="L6" s="13" t="n"/>
+      <c r="M6" s="13" t="n"/>
+    </row>
+    <row r="8">
+      <c r="A8" s="12" t="inlineStr">
+        <is>
+          <t>WEEKLY returns (% of capital at start of that week; weeks split at month edges)</t>
+        </is>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" s="2" t="inlineStr">
+        <is>
+          <t>Month</t>
+        </is>
+      </c>
+      <c r="B9" s="2" t="inlineStr">
+        <is>
+          <t>W1</t>
+        </is>
+      </c>
+      <c r="C9" s="2" t="inlineStr">
+        <is>
+          <t>W2</t>
+        </is>
+      </c>
+      <c r="D9" s="2" t="inlineStr">
+        <is>
+          <t>W3</t>
+        </is>
+      </c>
+      <c r="E9" s="2" t="inlineStr">
+        <is>
+          <t>W4</t>
+        </is>
+      </c>
+      <c r="F9" s="2" t="inlineStr">
+        <is>
+          <t>W5</t>
+        </is>
+      </c>
+      <c r="G9" s="2" t="inlineStr">
+        <is>
+          <t>W6</t>
+        </is>
+      </c>
+      <c r="H9" s="2" t="inlineStr">
+        <is>
+          <t>Month %</t>
+        </is>
+      </c>
+      <c r="I9" s="2" t="inlineStr">
+        <is>
+          <t>Month P&amp;L (Rs)</t>
+        </is>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" s="3" t="inlineStr">
+        <is>
+          <t>2026-Oct</t>
+        </is>
+      </c>
+      <c r="B10" s="14" t="n">
+        <v>0.020116</v>
+      </c>
+      <c r="C10" s="13" t="n"/>
+      <c r="D10" s="13" t="n"/>
+      <c r="E10" s="13" t="n"/>
+      <c r="F10" s="13" t="n"/>
+      <c r="G10" s="13" t="n"/>
+      <c r="H10" s="17" t="n">
+        <v>0.020116</v>
+      </c>
+      <c r="I10" s="16" t="n">
+        <v>402.32</v>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" s="12" t="inlineStr">
+        <is>
+          <t>DAILY returns (% of capital at start of that day; blank = no trade that day)</t>
+        </is>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" s="2" t="inlineStr">
+        <is>
+          <t>Week starting (Mon)</t>
+        </is>
+      </c>
+      <c r="B13" s="2" t="inlineStr">
+        <is>
+          <t>Mon</t>
+        </is>
+      </c>
+      <c r="C13" s="2" t="inlineStr">
+        <is>
+          <t>Tue</t>
+        </is>
+      </c>
+      <c r="D13" s="2" t="inlineStr">
+        <is>
+          <t>Wed</t>
+        </is>
+      </c>
+      <c r="E13" s="2" t="inlineStr">
+        <is>
+          <t>Thu</t>
+        </is>
+      </c>
+      <c r="F13" s="2" t="inlineStr">
+        <is>
+          <t>Fri</t>
+        </is>
+      </c>
+      <c r="G13" s="2" t="inlineStr">
+        <is>
+          <t>Week %</t>
+        </is>
+      </c>
+      <c r="H13" s="2" t="inlineStr">
+        <is>
+          <t>Week P&amp;L (Rs)</t>
+        </is>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" s="3" t="inlineStr">
+        <is>
+          <t>19-Oct-2026</t>
+        </is>
+      </c>
+      <c r="B14" s="14" t="n">
+        <v>0.020116</v>
+      </c>
+      <c r="C14" s="13" t="n"/>
+      <c r="D14" s="13" t="n"/>
+      <c r="E14" s="13" t="n"/>
+      <c r="F14" s="13" t="n"/>
+      <c r="G14" s="17" t="n">
+        <v>0.020116</v>
+      </c>
+      <c r="H14" s="16" t="n">
+        <v>402.32</v>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" s="12" t="inlineStr">
+        <is>
+          <t>STATISTICS (all trades for this index)</t>
+        </is>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" s="3" t="inlineStr">
+        <is>
+          <t>All trades</t>
+        </is>
+      </c>
+      <c r="B17" s="18" t="n">
+        <v>2</v>
+      </c>
+      <c r="C17" s="19" t="n"/>
+      <c r="D17" s="20" t="n"/>
+    </row>
+    <row r="18">
+      <c r="A18" s="3" t="inlineStr">
+        <is>
+          <t>Winners</t>
+        </is>
+      </c>
+      <c r="B18" s="21" t="inlineStr">
+        <is>
+          <t>1 (50.0%)</t>
+        </is>
+      </c>
+      <c r="C18" s="19" t="n"/>
+      <c r="D18" s="20" t="n"/>
+    </row>
+    <row r="19">
+      <c r="A19" s="3" t="inlineStr">
+        <is>
+          <t>Losers</t>
+        </is>
+      </c>
+      <c r="B19" s="21" t="inlineStr">
+        <is>
+          <t>1 (50.0%)</t>
+        </is>
+      </c>
+      <c r="C19" s="19" t="n"/>
+      <c r="D19" s="20" t="n"/>
+    </row>
+    <row r="20">
+      <c r="A20" s="3" t="inlineStr">
+        <is>
+          <t>Net P&amp;L (Rs)</t>
+        </is>
+      </c>
+      <c r="B20" s="22" t="n">
+        <v>402.32</v>
+      </c>
+      <c r="C20" s="19" t="n"/>
+      <c r="D20" s="20" t="n"/>
+    </row>
+    <row r="21">
+      <c r="A21" s="3" t="inlineStr">
+        <is>
+          <t>Total Profit (Rs)</t>
+        </is>
+      </c>
+      <c r="B21" s="22" t="n">
+        <v>626.0700000000001</v>
+      </c>
+      <c r="C21" s="19" t="n"/>
+      <c r="D21" s="20" t="n"/>
+    </row>
+    <row r="22">
+      <c r="A22" s="3" t="inlineStr">
+        <is>
+          <t>Total Loss (Rs)</t>
+        </is>
+      </c>
+      <c r="B22" s="23" t="n">
+        <v>-223.75</v>
+      </c>
+      <c r="C22" s="19" t="n"/>
+      <c r="D22" s="20" t="n"/>
+    </row>
+    <row r="23">
+      <c r="A23" s="3" t="inlineStr">
+        <is>
+          <t>Transaction costs (Rs)</t>
+        </is>
+      </c>
+      <c r="B23" s="24" t="n">
+        <v>47.68</v>
+      </c>
+      <c r="C23" s="19" t="n"/>
+      <c r="D23" s="20" t="n"/>
+    </row>
+    <row r="24">
+      <c r="A24" s="3" t="inlineStr">
+        <is>
+          <t>Avg Profit/Loss per trade (Rs)</t>
+        </is>
+      </c>
+      <c r="B24" s="22" t="n">
+        <v>201.16</v>
+      </c>
+      <c r="C24" s="19" t="n"/>
+      <c r="D24" s="20" t="n"/>
+    </row>
+    <row r="25">
+      <c r="A25" s="3" t="inlineStr">
+        <is>
+          <t>Avg Profit/Loss per trade (% of premium)</t>
+        </is>
+      </c>
+      <c r="B25" s="25" t="n">
+        <v>30.69</v>
+      </c>
+      <c r="C25" s="19" t="n"/>
+      <c r="D25" s="20" t="n"/>
+    </row>
+    <row r="26">
+      <c r="A26" s="3" t="inlineStr">
+        <is>
+          <t>Avg Win (Rs)</t>
+        </is>
+      </c>
+      <c r="B26" s="22" t="n">
+        <v>626.0700000000001</v>
+      </c>
+      <c r="C26" s="19" t="n"/>
+      <c r="D26" s="20" t="n"/>
+    </row>
+    <row r="27">
+      <c r="A27" s="3" t="inlineStr">
+        <is>
+          <t>Avg Win (% of premium)</t>
+        </is>
+      </c>
+      <c r="B27" s="26" t="n">
+        <v>97.90000000000001</v>
+      </c>
+      <c r="C27" s="19" t="n"/>
+      <c r="D27" s="20" t="n"/>
+    </row>
+    <row r="28">
+      <c r="A28" s="3" t="inlineStr">
+        <is>
+          <t>Avg Loss (Rs)</t>
+        </is>
+      </c>
+      <c r="B28" s="23" t="n">
+        <v>-223.75</v>
+      </c>
+      <c r="C28" s="19" t="n"/>
+      <c r="D28" s="20" t="n"/>
+    </row>
+    <row r="29">
+      <c r="A29" s="3" t="inlineStr">
+        <is>
+          <t>Avg Loss (% of premium)</t>
+        </is>
+      </c>
+      <c r="B29" s="27" t="n">
+        <v>-36.52</v>
+      </c>
+      <c r="C29" s="19" t="n"/>
+      <c r="D29" s="20" t="n"/>
+    </row>
+    <row r="30">
+      <c r="A30" s="3" t="inlineStr">
+        <is>
+          <t>Largest Win (Rs)</t>
+        </is>
+      </c>
+      <c r="B30" s="22" t="n">
+        <v>626.0700000000001</v>
+      </c>
+      <c r="C30" s="19" t="n"/>
+      <c r="D30" s="20" t="n"/>
+    </row>
+    <row r="31">
+      <c r="A31" s="3" t="inlineStr">
+        <is>
+          <t>Largest Loss (Rs)</t>
+        </is>
+      </c>
+      <c r="B31" s="23" t="n">
+        <v>-223.75</v>
+      </c>
+      <c r="C31" s="19" t="n"/>
+      <c r="D31" s="20" t="n"/>
+    </row>
+    <row r="32">
+      <c r="A32" s="3" t="inlineStr">
+        <is>
+          <t>Max Consecutive Wins</t>
+        </is>
+      </c>
+      <c r="B32" s="18" t="n">
+        <v>1</v>
+      </c>
+      <c r="C32" s="19" t="n"/>
+      <c r="D32" s="20" t="n"/>
+    </row>
+    <row r="33">
+      <c r="A33" s="3" t="inlineStr">
+        <is>
+          <t>Max Consecutive Losses</t>
+        </is>
+      </c>
+      <c r="B33" s="18" t="n">
+        <v>1</v>
+      </c>
+      <c r="C33" s="19" t="n"/>
+      <c r="D33" s="20" t="n"/>
+    </row>
+    <row r="34">
+      <c r="A34" s="3" t="inlineStr">
+        <is>
+          <t>Max trade drawdown (Rs)</t>
+        </is>
+      </c>
+      <c r="B34" s="23" t="n">
+        <v>-223.75</v>
+      </c>
+      <c r="C34" s="19" t="n"/>
+      <c r="D34" s="20" t="n"/>
+    </row>
+    <row r="35">
+      <c r="A35" s="3" t="inlineStr">
+        <is>
+          <t>Max system drawdown (Rs)</t>
+        </is>
+      </c>
+      <c r="B35" s="23" t="n">
+        <v>-223.75</v>
+      </c>
+      <c r="C35" s="19" t="n"/>
+      <c r="D35" s="20" t="n"/>
+    </row>
+    <row r="36">
+      <c r="A36" s="3" t="inlineStr">
+        <is>
+          <t>Max system drawdown (%)</t>
+        </is>
+      </c>
+      <c r="B36" s="27" t="n">
+        <v>-1.08</v>
+      </c>
+      <c r="C36" s="19" t="n"/>
+      <c r="D36" s="20" t="n"/>
+    </row>
+    <row r="37">
+      <c r="A37" s="3" t="inlineStr">
+        <is>
+          <t>Recovery Factor</t>
+        </is>
+      </c>
+      <c r="B37" s="28" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="C37" s="19" t="n"/>
+      <c r="D37" s="20" t="n"/>
+    </row>
+    <row r="38">
+      <c r="A38" s="3" t="inlineStr">
+        <is>
+          <t>Profit Factor</t>
+        </is>
+      </c>
+      <c r="B38" s="28" t="n">
+        <v>2.8</v>
+      </c>
+      <c r="C38" s="19" t="n"/>
+      <c r="D38" s="20" t="n"/>
+    </row>
+    <row r="39">
+      <c r="A39" s="3" t="inlineStr">
+        <is>
+          <t>Payoff Ratio (avg win / avg loss)</t>
+        </is>
+      </c>
+      <c r="B39" s="28" t="n">
+        <v>2.8</v>
+      </c>
+      <c r="C39" s="19" t="n"/>
+      <c r="D39" s="20" t="n"/>
+    </row>
+    <row r="40">
+      <c r="A40" s="3" t="inlineStr">
+        <is>
+          <t>Sharpe Ratio (annualized)</t>
+        </is>
+      </c>
+      <c r="B40" s="21" t="inlineStr">
+        <is>
+          <t>N/A (needs 2+ trading days)</t>
+        </is>
+      </c>
+      <c r="C40" s="19" t="n"/>
+      <c r="D40" s="20" t="n"/>
+    </row>
+    <row r="42">
+      <c r="A42" s="11" t="inlineStr">
+        <is>
+          <t>Caveat: with only a handful of trades these numbers (Sharpe, profit factor, drawdown %) are not statistically reliable. Watch this over weeks/months before drawing conclusions.</t>
         </is>
       </c>
     </row>
   </sheetData>
+  <mergeCells count="24">
+    <mergeCell ref="B23:D23"/>
+    <mergeCell ref="B17:D17"/>
+    <mergeCell ref="B29:D29"/>
+    <mergeCell ref="B38:D38"/>
+    <mergeCell ref="B34:D34"/>
+    <mergeCell ref="B28:D28"/>
+    <mergeCell ref="B19:D19"/>
+    <mergeCell ref="B37:D37"/>
+    <mergeCell ref="B40:D40"/>
+    <mergeCell ref="B30:D30"/>
+    <mergeCell ref="B24:D24"/>
+    <mergeCell ref="B20:D20"/>
+    <mergeCell ref="B33:D33"/>
+    <mergeCell ref="B36:D36"/>
+    <mergeCell ref="B32:D32"/>
+    <mergeCell ref="B35:D35"/>
+    <mergeCell ref="B26:D26"/>
+    <mergeCell ref="B25:D25"/>
+    <mergeCell ref="B31:D31"/>
+    <mergeCell ref="B22:D22"/>
+    <mergeCell ref="B18:D18"/>
+    <mergeCell ref="B27:D27"/>
+    <mergeCell ref="B21:D21"/>
+    <mergeCell ref="B39:D39"/>
+  </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
   <pageSetup orientation="landscape" fitToHeight="0" fitToWidth="1"/>
 </worksheet>
@@ -1881,30 +3065,30 @@
           <t>NIFTY</t>
         </is>
       </c>
-      <c r="B4" s="6" t="inlineStr">
+      <c r="B4" s="13" t="inlineStr">
         <is>
           <t>-</t>
         </is>
       </c>
-      <c r="C4" s="4" t="n">
+      <c r="C4" s="10" t="n">
         <v>0</v>
       </c>
-      <c r="D4" s="4" t="inlineStr">
+      <c r="D4" s="10" t="inlineStr">
         <is>
           <t>-</t>
         </is>
       </c>
-      <c r="E4" s="4" t="inlineStr">
+      <c r="E4" s="10" t="inlineStr">
         <is>
           <t>-</t>
         </is>
       </c>
-      <c r="F4" s="4" t="inlineStr">
+      <c r="F4" s="10" t="inlineStr">
         <is>
           <t>-</t>
         </is>
       </c>
-      <c r="G4" s="4" t="inlineStr">
+      <c r="G4" s="10" t="inlineStr">
         <is>
           <t>-</t>
         </is>
@@ -1916,30 +3100,30 @@
           <t>BANKNIFTY</t>
         </is>
       </c>
-      <c r="B5" s="6" t="inlineStr">
+      <c r="B5" s="13" t="inlineStr">
         <is>
           <t>-</t>
         </is>
       </c>
-      <c r="C5" s="4" t="n">
+      <c r="C5" s="10" t="n">
         <v>0</v>
       </c>
-      <c r="D5" s="4" t="inlineStr">
+      <c r="D5" s="10" t="inlineStr">
         <is>
           <t>-</t>
         </is>
       </c>
-      <c r="E5" s="4" t="inlineStr">
+      <c r="E5" s="10" t="inlineStr">
         <is>
           <t>-</t>
         </is>
       </c>
-      <c r="F5" s="4" t="inlineStr">
+      <c r="F5" s="10" t="inlineStr">
         <is>
           <t>-</t>
         </is>
       </c>
-      <c r="G5" s="4" t="inlineStr">
+      <c r="G5" s="10" t="inlineStr">
         <is>
           <t>-</t>
         </is>
@@ -1951,24 +3135,24 @@
           <t>FINNIFTY</t>
         </is>
       </c>
-      <c r="B6" s="6" t="inlineStr">
+      <c r="B6" s="13" t="inlineStr">
         <is>
           <t>trend_scalp_nw (EMA9/26) [5m]</t>
         </is>
       </c>
-      <c r="C6" s="7" t="n">
+      <c r="C6" s="4" t="n">
         <v>7</v>
       </c>
-      <c r="D6" s="8" t="n">
+      <c r="D6" s="5" t="n">
         <v>0.1428571428571428</v>
       </c>
-      <c r="E6" s="9" t="n">
+      <c r="E6" s="29" t="n">
         <v>-1219.59</v>
       </c>
-      <c r="F6" s="10" t="n">
+      <c r="F6" s="7" t="n">
         <v>0.16</v>
       </c>
-      <c r="G6" s="11" t="n">
+      <c r="G6" s="8" t="n">
         <v>-0.06126299999999993</v>
       </c>
     </row>
@@ -1978,29 +3162,29 @@
           <t>ALL INDICES</t>
         </is>
       </c>
-      <c r="B7" s="6" t="inlineStr">
+      <c r="B7" s="13" t="inlineStr">
         <is>
           <t>(combined)</t>
         </is>
       </c>
-      <c r="C7" s="7" t="n">
+      <c r="C7" s="4" t="n">
         <v>7</v>
       </c>
-      <c r="D7" s="8" t="n">
+      <c r="D7" s="5" t="n">
         <v>0.1428571428571428</v>
       </c>
-      <c r="E7" s="9" t="n">
+      <c r="E7" s="29" t="n">
         <v>-1219.59</v>
       </c>
-      <c r="F7" s="10" t="n">
+      <c r="F7" s="7" t="n">
         <v>0.16</v>
       </c>
-      <c r="G7" s="11" t="n">
+      <c r="G7" s="8" t="n">
         <v>-0.06126299999999993</v>
       </c>
     </row>
     <row r="9">
-      <c r="A9" s="5" t="inlineStr">
+      <c r="A9" s="11" t="inlineStr">
         <is>
           <t>BT- sheets are from the BACKTEST (each index's single best combo, so time periods aren't double-counted across competing strategies). Plain-named sheets are LIVE paper trades. See latest_backtest_summary.xlsx for every combo tested.</t>
         </is>
@@ -2046,7 +3230,7 @@
       </c>
     </row>
     <row r="3">
-      <c r="A3" s="5" t="inlineStr">
+      <c r="A3" s="11" t="inlineStr">
         <is>
           <t>No trades yet for this index -- this fills in automatically as the bot trades.</t>
         </is>
@@ -2092,7 +3276,7 @@
       </c>
     </row>
     <row r="3">
-      <c r="A3" s="5" t="inlineStr">
+      <c r="A3" s="11" t="inlineStr">
         <is>
           <t>No trades yet for this index -- this fills in automatically as the bot trades.</t>
         </is>
@@ -2225,24 +3409,24 @@
       <c r="A5" s="3" t="n">
         <v>2025</v>
       </c>
-      <c r="B5" s="6" t="n"/>
-      <c r="C5" s="6" t="n"/>
-      <c r="D5" s="6" t="n"/>
-      <c r="E5" s="6" t="n"/>
-      <c r="F5" s="6" t="n"/>
-      <c r="G5" s="6" t="n"/>
-      <c r="H5" s="6" t="n"/>
-      <c r="I5" s="6" t="n"/>
-      <c r="J5" s="6" t="n"/>
-      <c r="K5" s="6" t="n"/>
-      <c r="L5" s="6" t="n"/>
-      <c r="M5" s="13" t="n">
+      <c r="B5" s="13" t="n"/>
+      <c r="C5" s="13" t="n"/>
+      <c r="D5" s="13" t="n"/>
+      <c r="E5" s="13" t="n"/>
+      <c r="F5" s="13" t="n"/>
+      <c r="G5" s="13" t="n"/>
+      <c r="H5" s="13" t="n"/>
+      <c r="I5" s="13" t="n"/>
+      <c r="J5" s="13" t="n"/>
+      <c r="K5" s="13" t="n"/>
+      <c r="L5" s="13" t="n"/>
+      <c r="M5" s="30" t="n">
         <v>-0.0469125</v>
       </c>
-      <c r="N5" s="14" t="n">
+      <c r="N5" s="31" t="n">
         <v>-0.04691250000000002</v>
       </c>
-      <c r="O5" s="15" t="n">
+      <c r="O5" s="32" t="n">
         <v>-938.25</v>
       </c>
     </row>
@@ -2250,28 +3434,28 @@
       <c r="A6" s="3" t="n">
         <v>2026</v>
       </c>
-      <c r="B6" s="13" t="n">
+      <c r="B6" s="30" t="n">
         <v>-0.01505685469592246</v>
       </c>
-      <c r="C6" s="6" t="n"/>
-      <c r="D6" s="6" t="n"/>
-      <c r="E6" s="16" t="n">
+      <c r="C6" s="13" t="n"/>
+      <c r="D6" s="13" t="n"/>
+      <c r="E6" s="14" t="n">
         <v>0.01262227865738753</v>
       </c>
-      <c r="F6" s="6" t="n"/>
-      <c r="G6" s="6" t="n"/>
-      <c r="H6" s="6" t="n"/>
-      <c r="I6" s="6" t="n"/>
-      <c r="J6" s="13" t="n">
+      <c r="F6" s="13" t="n"/>
+      <c r="G6" s="13" t="n"/>
+      <c r="H6" s="13" t="n"/>
+      <c r="I6" s="13" t="n"/>
+      <c r="J6" s="30" t="n">
         <v>-0.01216670559002552</v>
       </c>
-      <c r="K6" s="6" t="n"/>
-      <c r="L6" s="6" t="n"/>
-      <c r="M6" s="6" t="n"/>
-      <c r="N6" s="14" t="n">
+      <c r="K6" s="13" t="n"/>
+      <c r="L6" s="13" t="n"/>
+      <c r="M6" s="13" t="n"/>
+      <c r="N6" s="31" t="n">
         <v>-0.01475940036985068</v>
       </c>
-      <c r="O6" s="15" t="n">
+      <c r="O6" s="32" t="n">
         <v>-281.34</v>
       </c>
     </row>
@@ -2281,24 +3465,24 @@
           <t>Avg</t>
         </is>
       </c>
-      <c r="B7" s="14" t="n">
+      <c r="B7" s="31" t="n">
         <v>-0.01505685469592246</v>
       </c>
-      <c r="C7" s="6" t="n"/>
-      <c r="D7" s="6" t="n"/>
-      <c r="E7" s="17" t="n">
+      <c r="C7" s="13" t="n"/>
+      <c r="D7" s="13" t="n"/>
+      <c r="E7" s="15" t="n">
         <v>0.01262227865738753</v>
       </c>
-      <c r="F7" s="6" t="n"/>
-      <c r="G7" s="6" t="n"/>
-      <c r="H7" s="6" t="n"/>
-      <c r="I7" s="6" t="n"/>
-      <c r="J7" s="14" t="n">
+      <c r="F7" s="13" t="n"/>
+      <c r="G7" s="13" t="n"/>
+      <c r="H7" s="13" t="n"/>
+      <c r="I7" s="13" t="n"/>
+      <c r="J7" s="31" t="n">
         <v>-0.01216670559002552</v>
       </c>
-      <c r="K7" s="6" t="n"/>
-      <c r="L7" s="6" t="n"/>
-      <c r="M7" s="14" t="n">
+      <c r="K7" s="13" t="n"/>
+      <c r="L7" s="13" t="n"/>
+      <c r="M7" s="31" t="n">
         <v>-0.0469125</v>
       </c>
     </row>
@@ -2362,20 +3546,20 @@
           <t>2025-Dec</t>
         </is>
       </c>
-      <c r="B11" s="13" t="n">
+      <c r="B11" s="30" t="n">
         <v>-0.010346</v>
       </c>
-      <c r="C11" s="13" t="n">
+      <c r="C11" s="30" t="n">
         <v>-0.0369487719950609</v>
       </c>
-      <c r="D11" s="6" t="n"/>
-      <c r="E11" s="6" t="n"/>
-      <c r="F11" s="6" t="n"/>
-      <c r="G11" s="6" t="n"/>
-      <c r="H11" s="18" t="n">
+      <c r="D11" s="13" t="n"/>
+      <c r="E11" s="13" t="n"/>
+      <c r="F11" s="13" t="n"/>
+      <c r="G11" s="13" t="n"/>
+      <c r="H11" s="33" t="n">
         <v>-0.0469125</v>
       </c>
-      <c r="I11" s="15" t="n">
+      <c r="I11" s="32" t="n">
         <v>-938.25</v>
       </c>
     </row>
@@ -2385,18 +3569,18 @@
           <t>2026-Jan</t>
         </is>
       </c>
-      <c r="B12" s="13" t="n">
+      <c r="B12" s="30" t="n">
         <v>-0.01505685469592246</v>
       </c>
-      <c r="C12" s="6" t="n"/>
-      <c r="D12" s="6" t="n"/>
-      <c r="E12" s="6" t="n"/>
-      <c r="F12" s="6" t="n"/>
-      <c r="G12" s="6" t="n"/>
-      <c r="H12" s="18" t="n">
+      <c r="C12" s="13" t="n"/>
+      <c r="D12" s="13" t="n"/>
+      <c r="E12" s="13" t="n"/>
+      <c r="F12" s="13" t="n"/>
+      <c r="G12" s="13" t="n"/>
+      <c r="H12" s="33" t="n">
         <v>-0.01505685469592246</v>
       </c>
-      <c r="I12" s="15" t="n">
+      <c r="I12" s="32" t="n">
         <v>-287.01</v>
       </c>
     </row>
@@ -2406,18 +3590,18 @@
           <t>2026-Apr</t>
         </is>
       </c>
-      <c r="B13" s="16" t="n">
+      <c r="B13" s="14" t="n">
         <v>0.01262227865738753</v>
       </c>
-      <c r="C13" s="6" t="n"/>
-      <c r="D13" s="6" t="n"/>
-      <c r="E13" s="6" t="n"/>
-      <c r="F13" s="6" t="n"/>
-      <c r="G13" s="6" t="n"/>
-      <c r="H13" s="19" t="n">
+      <c r="C13" s="13" t="n"/>
+      <c r="D13" s="13" t="n"/>
+      <c r="E13" s="13" t="n"/>
+      <c r="F13" s="13" t="n"/>
+      <c r="G13" s="13" t="n"/>
+      <c r="H13" s="17" t="n">
         <v>0.01262227865738753</v>
       </c>
-      <c r="I13" s="20" t="n">
+      <c r="I13" s="16" t="n">
         <v>236.98</v>
       </c>
     </row>
@@ -2427,18 +3611,18 @@
           <t>2026-Sep</t>
         </is>
       </c>
-      <c r="B14" s="13" t="n">
+      <c r="B14" s="30" t="n">
         <v>-0.01216670559002552</v>
       </c>
-      <c r="C14" s="6" t="n"/>
-      <c r="D14" s="6" t="n"/>
-      <c r="E14" s="6" t="n"/>
-      <c r="F14" s="6" t="n"/>
-      <c r="G14" s="6" t="n"/>
-      <c r="H14" s="18" t="n">
+      <c r="C14" s="13" t="n"/>
+      <c r="D14" s="13" t="n"/>
+      <c r="E14" s="13" t="n"/>
+      <c r="F14" s="13" t="n"/>
+      <c r="G14" s="13" t="n"/>
+      <c r="H14" s="33" t="n">
         <v>-0.01216670559002552</v>
       </c>
-      <c r="I14" s="15" t="n">
+      <c r="I14" s="32" t="n">
         <v>-231.31</v>
       </c>
     </row>
@@ -2497,17 +3681,17 @@
           <t>01-Dec-2025</t>
         </is>
       </c>
-      <c r="B18" s="6" t="n"/>
-      <c r="C18" s="13" t="n">
+      <c r="B18" s="13" t="n"/>
+      <c r="C18" s="30" t="n">
         <v>-0.010346</v>
       </c>
-      <c r="D18" s="6" t="n"/>
-      <c r="E18" s="6" t="n"/>
-      <c r="F18" s="6" t="n"/>
-      <c r="G18" s="18" t="n">
+      <c r="D18" s="13" t="n"/>
+      <c r="E18" s="13" t="n"/>
+      <c r="F18" s="13" t="n"/>
+      <c r="G18" s="33" t="n">
         <v>-0.010346</v>
       </c>
-      <c r="H18" s="15" t="n">
+      <c r="H18" s="32" t="n">
         <v>-206.92</v>
       </c>
     </row>
@@ -2517,17 +3701,17 @@
           <t>08-Dec-2025</t>
         </is>
       </c>
-      <c r="B19" s="6" t="n"/>
-      <c r="C19" s="13" t="n">
+      <c r="B19" s="13" t="n"/>
+      <c r="C19" s="30" t="n">
         <v>-0.0369487719950609</v>
       </c>
-      <c r="D19" s="6" t="n"/>
-      <c r="E19" s="6" t="n"/>
-      <c r="F19" s="6" t="n"/>
-      <c r="G19" s="18" t="n">
+      <c r="D19" s="13" t="n"/>
+      <c r="E19" s="13" t="n"/>
+      <c r="F19" s="13" t="n"/>
+      <c r="G19" s="33" t="n">
         <v>-0.0369487719950609</v>
       </c>
-      <c r="H19" s="15" t="n">
+      <c r="H19" s="32" t="n">
         <v>-731.33</v>
       </c>
     </row>
@@ -2537,17 +3721,17 @@
           <t>26-Jan-2026</t>
         </is>
       </c>
-      <c r="B20" s="6" t="n"/>
-      <c r="C20" s="13" t="n">
+      <c r="B20" s="13" t="n"/>
+      <c r="C20" s="30" t="n">
         <v>-0.01505685469592246</v>
       </c>
-      <c r="D20" s="6" t="n"/>
-      <c r="E20" s="6" t="n"/>
-      <c r="F20" s="6" t="n"/>
-      <c r="G20" s="18" t="n">
+      <c r="D20" s="13" t="n"/>
+      <c r="E20" s="13" t="n"/>
+      <c r="F20" s="13" t="n"/>
+      <c r="G20" s="33" t="n">
         <v>-0.01505685469592246</v>
       </c>
-      <c r="H20" s="15" t="n">
+      <c r="H20" s="32" t="n">
         <v>-287.01</v>
       </c>
     </row>
@@ -2557,17 +3741,17 @@
           <t>06-Apr-2026</t>
         </is>
       </c>
-      <c r="B21" s="6" t="n"/>
-      <c r="C21" s="16" t="n">
+      <c r="B21" s="13" t="n"/>
+      <c r="C21" s="14" t="n">
         <v>0.01262227865738753</v>
       </c>
-      <c r="D21" s="6" t="n"/>
-      <c r="E21" s="6" t="n"/>
-      <c r="F21" s="6" t="n"/>
-      <c r="G21" s="19" t="n">
+      <c r="D21" s="13" t="n"/>
+      <c r="E21" s="13" t="n"/>
+      <c r="F21" s="13" t="n"/>
+      <c r="G21" s="17" t="n">
         <v>0.01262227865738753</v>
       </c>
-      <c r="H21" s="20" t="n">
+      <c r="H21" s="16" t="n">
         <v>236.98</v>
       </c>
     </row>
@@ -2577,17 +3761,17 @@
           <t>07-Sep-2026</t>
         </is>
       </c>
-      <c r="B22" s="6" t="n"/>
-      <c r="C22" s="13" t="n">
+      <c r="B22" s="13" t="n"/>
+      <c r="C22" s="30" t="n">
         <v>-0.01216670559002552</v>
       </c>
-      <c r="D22" s="6" t="n"/>
-      <c r="E22" s="6" t="n"/>
-      <c r="F22" s="6" t="n"/>
-      <c r="G22" s="18" t="n">
+      <c r="D22" s="13" t="n"/>
+      <c r="E22" s="13" t="n"/>
+      <c r="F22" s="13" t="n"/>
+      <c r="G22" s="33" t="n">
         <v>-0.01216670559002552</v>
       </c>
-      <c r="H22" s="15" t="n">
+      <c r="H22" s="32" t="n">
         <v>-231.31</v>
       </c>
     </row>
@@ -2604,11 +3788,11 @@
           <t>All trades</t>
         </is>
       </c>
-      <c r="B25" s="21" t="n">
+      <c r="B25" s="18" t="n">
         <v>7</v>
       </c>
-      <c r="C25" s="22" t="n"/>
-      <c r="D25" s="23" t="n"/>
+      <c r="C25" s="19" t="n"/>
+      <c r="D25" s="20" t="n"/>
     </row>
     <row r="26">
       <c r="A26" s="3" t="inlineStr">
@@ -2616,13 +3800,13 @@
           <t>Winners</t>
         </is>
       </c>
-      <c r="B26" s="24" t="inlineStr">
+      <c r="B26" s="21" t="inlineStr">
         <is>
           <t>1 (14.3%)</t>
         </is>
       </c>
-      <c r="C26" s="22" t="n"/>
-      <c r="D26" s="23" t="n"/>
+      <c r="C26" s="19" t="n"/>
+      <c r="D26" s="20" t="n"/>
     </row>
     <row r="27">
       <c r="A27" s="3" t="inlineStr">
@@ -2630,13 +3814,13 @@
           <t>Losers</t>
         </is>
       </c>
-      <c r="B27" s="24" t="inlineStr">
+      <c r="B27" s="21" t="inlineStr">
         <is>
           <t>6 (85.7%)</t>
         </is>
       </c>
-      <c r="C27" s="22" t="n"/>
-      <c r="D27" s="23" t="n"/>
+      <c r="C27" s="19" t="n"/>
+      <c r="D27" s="20" t="n"/>
     </row>
     <row r="28">
       <c r="A28" s="3" t="inlineStr">
@@ -2644,11 +3828,11 @@
           <t>Net P&amp;L (Rs)</t>
         </is>
       </c>
-      <c r="B28" s="25" t="n">
+      <c r="B28" s="23" t="n">
         <v>-1219.59</v>
       </c>
-      <c r="C28" s="22" t="n"/>
-      <c r="D28" s="23" t="n"/>
+      <c r="C28" s="19" t="n"/>
+      <c r="D28" s="20" t="n"/>
     </row>
     <row r="29">
       <c r="A29" s="3" t="inlineStr">
@@ -2656,11 +3840,11 @@
           <t>Total Profit (Rs)</t>
         </is>
       </c>
-      <c r="B29" s="26" t="n">
+      <c r="B29" s="22" t="n">
         <v>236.98</v>
       </c>
-      <c r="C29" s="22" t="n"/>
-      <c r="D29" s="23" t="n"/>
+      <c r="C29" s="19" t="n"/>
+      <c r="D29" s="20" t="n"/>
     </row>
     <row r="30">
       <c r="A30" s="3" t="inlineStr">
@@ -2668,11 +3852,11 @@
           <t>Total Loss (Rs)</t>
         </is>
       </c>
-      <c r="B30" s="25" t="n">
+      <c r="B30" s="23" t="n">
         <v>-1456.57</v>
       </c>
-      <c r="C30" s="22" t="n"/>
-      <c r="D30" s="23" t="n"/>
+      <c r="C30" s="19" t="n"/>
+      <c r="D30" s="20" t="n"/>
     </row>
     <row r="31">
       <c r="A31" s="3" t="inlineStr">
@@ -2680,11 +3864,11 @@
           <t>Transaction costs (Rs)</t>
         </is>
       </c>
-      <c r="B31" s="27" t="n">
+      <c r="B31" s="24" t="n">
         <v>348.39</v>
       </c>
-      <c r="C31" s="22" t="n"/>
-      <c r="D31" s="23" t="n"/>
+      <c r="C31" s="19" t="n"/>
+      <c r="D31" s="20" t="n"/>
     </row>
     <row r="32">
       <c r="A32" s="3" t="inlineStr">
@@ -2692,11 +3876,11 @@
           <t>Avg Profit/Loss per trade (Rs)</t>
         </is>
       </c>
-      <c r="B32" s="25" t="n">
+      <c r="B32" s="23" t="n">
         <v>-174.23</v>
       </c>
-      <c r="C32" s="22" t="n"/>
-      <c r="D32" s="23" t="n"/>
+      <c r="C32" s="19" t="n"/>
+      <c r="D32" s="20" t="n"/>
     </row>
     <row r="33">
       <c r="A33" s="3" t="inlineStr">
@@ -2704,11 +3888,11 @@
           <t>Avg Profit/Loss per trade (% of premium)</t>
         </is>
       </c>
-      <c r="B33" s="28" t="n">
+      <c r="B33" s="25" t="n">
         <v>-10.42</v>
       </c>
-      <c r="C33" s="22" t="n"/>
-      <c r="D33" s="23" t="n"/>
+      <c r="C33" s="19" t="n"/>
+      <c r="D33" s="20" t="n"/>
     </row>
     <row r="34">
       <c r="A34" s="3" t="inlineStr">
@@ -2716,11 +3900,11 @@
           <t>Avg Win (Rs)</t>
         </is>
       </c>
-      <c r="B34" s="26" t="n">
+      <c r="B34" s="22" t="n">
         <v>236.98</v>
       </c>
-      <c r="C34" s="22" t="n"/>
-      <c r="D34" s="23" t="n"/>
+      <c r="C34" s="19" t="n"/>
+      <c r="D34" s="20" t="n"/>
     </row>
     <row r="35">
       <c r="A35" s="3" t="inlineStr">
@@ -2728,11 +3912,11 @@
           <t>Avg Win (% of premium)</t>
         </is>
       </c>
-      <c r="B35" s="29" t="n">
+      <c r="B35" s="26" t="n">
         <v>16.17</v>
       </c>
-      <c r="C35" s="22" t="n"/>
-      <c r="D35" s="23" t="n"/>
+      <c r="C35" s="19" t="n"/>
+      <c r="D35" s="20" t="n"/>
     </row>
     <row r="36">
       <c r="A36" s="3" t="inlineStr">
@@ -2740,11 +3924,11 @@
           <t>Avg Loss (Rs)</t>
         </is>
       </c>
-      <c r="B36" s="25" t="n">
+      <c r="B36" s="23" t="n">
         <v>-242.76</v>
       </c>
-      <c r="C36" s="22" t="n"/>
-      <c r="D36" s="23" t="n"/>
+      <c r="C36" s="19" t="n"/>
+      <c r="D36" s="20" t="n"/>
     </row>
     <row r="37">
       <c r="A37" s="3" t="inlineStr">
@@ -2752,11 +3936,11 @@
           <t>Avg Loss (% of premium)</t>
         </is>
       </c>
-      <c r="B37" s="30" t="n">
+      <c r="B37" s="27" t="n">
         <v>-14.85</v>
       </c>
-      <c r="C37" s="22" t="n"/>
-      <c r="D37" s="23" t="n"/>
+      <c r="C37" s="19" t="n"/>
+      <c r="D37" s="20" t="n"/>
     </row>
     <row r="38">
       <c r="A38" s="3" t="inlineStr">
@@ -2764,11 +3948,11 @@
           <t>Largest Win (Rs)</t>
         </is>
       </c>
-      <c r="B38" s="26" t="n">
+      <c r="B38" s="22" t="n">
         <v>236.98</v>
       </c>
-      <c r="C38" s="22" t="n"/>
-      <c r="D38" s="23" t="n"/>
+      <c r="C38" s="19" t="n"/>
+      <c r="D38" s="20" t="n"/>
     </row>
     <row r="39">
       <c r="A39" s="3" t="inlineStr">
@@ -2776,11 +3960,11 @@
           <t>Largest Loss (Rs)</t>
         </is>
       </c>
-      <c r="B39" s="25" t="n">
+      <c r="B39" s="23" t="n">
         <v>-295.95</v>
       </c>
-      <c r="C39" s="22" t="n"/>
-      <c r="D39" s="23" t="n"/>
+      <c r="C39" s="19" t="n"/>
+      <c r="D39" s="20" t="n"/>
     </row>
     <row r="40">
       <c r="A40" s="3" t="inlineStr">
@@ -2788,11 +3972,11 @@
           <t>Max Consecutive Wins</t>
         </is>
       </c>
-      <c r="B40" s="21" t="n">
+      <c r="B40" s="18" t="n">
         <v>1</v>
       </c>
-      <c r="C40" s="22" t="n"/>
-      <c r="D40" s="23" t="n"/>
+      <c r="C40" s="19" t="n"/>
+      <c r="D40" s="20" t="n"/>
     </row>
     <row r="41">
       <c r="A41" s="3" t="inlineStr">
@@ -2800,11 +3984,11 @@
           <t>Max Consecutive Losses</t>
         </is>
       </c>
-      <c r="B41" s="21" t="n">
+      <c r="B41" s="18" t="n">
         <v>5</v>
       </c>
-      <c r="C41" s="22" t="n"/>
-      <c r="D41" s="23" t="n"/>
+      <c r="C41" s="19" t="n"/>
+      <c r="D41" s="20" t="n"/>
     </row>
     <row r="42">
       <c r="A42" s="3" t="inlineStr">
@@ -2812,11 +3996,11 @@
           <t>Max trade drawdown (Rs)</t>
         </is>
       </c>
-      <c r="B42" s="25" t="n">
+      <c r="B42" s="23" t="n">
         <v>-295.95</v>
       </c>
-      <c r="C42" s="22" t="n"/>
-      <c r="D42" s="23" t="n"/>
+      <c r="C42" s="19" t="n"/>
+      <c r="D42" s="20" t="n"/>
     </row>
     <row r="43">
       <c r="A43" s="3" t="inlineStr">
@@ -2824,11 +4008,11 @@
           <t>Max system drawdown (Rs)</t>
         </is>
       </c>
-      <c r="B43" s="25" t="n">
+      <c r="B43" s="23" t="n">
         <v>-1225.26</v>
       </c>
-      <c r="C43" s="22" t="n"/>
-      <c r="D43" s="23" t="n"/>
+      <c r="C43" s="19" t="n"/>
+      <c r="D43" s="20" t="n"/>
     </row>
     <row r="44">
       <c r="A44" s="3" t="inlineStr">
@@ -2836,11 +4020,11 @@
           <t>Max system drawdown (%)</t>
         </is>
       </c>
-      <c r="B44" s="30" t="n">
+      <c r="B44" s="27" t="n">
         <v>-6.13</v>
       </c>
-      <c r="C44" s="22" t="n"/>
-      <c r="D44" s="23" t="n"/>
+      <c r="C44" s="19" t="n"/>
+      <c r="D44" s="20" t="n"/>
     </row>
     <row r="45">
       <c r="A45" s="3" t="inlineStr">
@@ -2848,11 +4032,11 @@
           <t>Recovery Factor</t>
         </is>
       </c>
-      <c r="B45" s="31" t="n">
+      <c r="B45" s="28" t="n">
         <v>-1</v>
       </c>
-      <c r="C45" s="22" t="n"/>
-      <c r="D45" s="23" t="n"/>
+      <c r="C45" s="19" t="n"/>
+      <c r="D45" s="20" t="n"/>
     </row>
     <row r="46">
       <c r="A46" s="3" t="inlineStr">
@@ -2860,11 +4044,11 @@
           <t>Profit Factor</t>
         </is>
       </c>
-      <c r="B46" s="31" t="n">
+      <c r="B46" s="28" t="n">
         <v>0.16</v>
       </c>
-      <c r="C46" s="22" t="n"/>
-      <c r="D46" s="23" t="n"/>
+      <c r="C46" s="19" t="n"/>
+      <c r="D46" s="20" t="n"/>
     </row>
     <row r="47">
       <c r="A47" s="3" t="inlineStr">
@@ -2872,11 +4056,11 @@
           <t>Payoff Ratio (avg win / avg loss)</t>
         </is>
       </c>
-      <c r="B47" s="31" t="n">
+      <c r="B47" s="28" t="n">
         <v>0.98</v>
       </c>
-      <c r="C47" s="22" t="n"/>
-      <c r="D47" s="23" t="n"/>
+      <c r="C47" s="19" t="n"/>
+      <c r="D47" s="20" t="n"/>
     </row>
     <row r="48">
       <c r="A48" s="3" t="inlineStr">
@@ -2884,14 +4068,14 @@
           <t>Sharpe Ratio (annualized)</t>
         </is>
       </c>
-      <c r="B48" s="31" t="n">
+      <c r="B48" s="28" t="n">
         <v>-12.48</v>
       </c>
-      <c r="C48" s="22" t="n"/>
-      <c r="D48" s="23" t="n"/>
+      <c r="C48" s="19" t="n"/>
+      <c r="D48" s="20" t="n"/>
     </row>
     <row r="50">
-      <c r="A50" s="5" t="inlineStr">
+      <c r="A50" s="11" t="inlineStr">
         <is>
           <t>Caveat: with only a handful of trades these numbers (Sharpe, profit factor, drawdown %) are not statistically reliable. Watch this over weeks/months before drawing conclusions.</t>
         </is>

--- a/reports/dashboard.xlsx
+++ b/reports/dashboard.xlsx
@@ -12,11 +12,6 @@
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="BANKNIFTY" sheetId="3" state="visible" r:id="rId3"/>
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="FINNIFTY" sheetId="4" state="visible" r:id="rId4"/>
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="ALL INDICES" sheetId="5" state="visible" r:id="rId5"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="BT-Summary" sheetId="6" state="visible" r:id="rId6"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="BT-NIFTY" sheetId="7" state="visible" r:id="rId7"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="BT-BANKNIFTY" sheetId="8" state="visible" r:id="rId8"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="BT-FINNIFTY" sheetId="9" state="visible" r:id="rId9"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="BT-ALL INDICES" sheetId="10" state="visible" r:id="rId10"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -31,7 +26,7 @@
     <numFmt numFmtId="166" formatCode="#,##0;-#,##0"/>
     <numFmt numFmtId="167" formatCode="0.00&quot;%&quot;"/>
   </numFmts>
-  <fonts count="10">
+  <fonts count="9">
     <font>
       <name val="Calibri"/>
       <family val="2"/>
@@ -75,13 +70,8 @@
       <name val="Arial"/>
       <color rgb="00C00000"/>
     </font>
-    <font>
-      <name val="Arial"/>
-      <b val="1"/>
-      <color rgb="00C00000"/>
-    </font>
   </fonts>
-  <fills count="5">
+  <fills count="4">
     <fill>
       <patternFill/>
     </fill>
@@ -98,12 +88,6 @@
       <patternFill patternType="solid">
         <fgColor rgb="00E6F4EA"/>
         <bgColor rgb="00E6F4EA"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="00FDE8E8"/>
-        <bgColor rgb="00FDE8E8"/>
       </patternFill>
     </fill>
   </fills>
@@ -177,7 +161,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="34">
+  <cellXfs count="29">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="2" fillId="2" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
@@ -227,11 +211,6 @@
     <xf numFmtId="2" fontId="4" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="right"/>
     </xf>
-    <xf numFmtId="165" fontId="8" fillId="0" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="164" fontId="8" fillId="4" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="164" fontId="8" fillId="0" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="166" fontId="8" fillId="0" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="164" fontId="9" fillId="4" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0" hidden="0"/>
@@ -786,831 +765,6 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet10.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <sheetPr>
-    <outlinePr summaryBelow="1" summaryRight="1"/>
-    <pageSetUpPr fitToPage="1"/>
-  </sheetPr>
-  <dimension ref="A1:O50"/>
-  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
-  <cols>
-    <col width="40" customWidth="1" min="1" max="1"/>
-    <col width="10" customWidth="1" min="2" max="2"/>
-    <col width="10" customWidth="1" min="3" max="3"/>
-    <col width="10" customWidth="1" min="4" max="4"/>
-    <col width="10" customWidth="1" min="5" max="5"/>
-    <col width="10" customWidth="1" min="6" max="6"/>
-    <col width="10" customWidth="1" min="7" max="7"/>
-    <col width="15" customWidth="1" min="8" max="8"/>
-    <col width="15" customWidth="1" min="9" max="9"/>
-    <col width="10" customWidth="1" min="10" max="10"/>
-    <col width="10" customWidth="1" min="11" max="11"/>
-    <col width="10" customWidth="1" min="12" max="12"/>
-    <col width="10" customWidth="1" min="13" max="13"/>
-    <col width="10" customWidth="1" min="14" max="14"/>
-    <col width="15" customWidth="1" min="15" max="15"/>
-  </cols>
-  <sheetData>
-    <row r="1">
-      <c r="A1" s="1" t="inlineStr">
-        <is>
-          <t>BACKTEST ALL INDICES -- PAPER TRADE, NOT REAL MONEY</t>
-        </is>
-      </c>
-    </row>
-    <row r="3">
-      <c r="A3" s="12" t="inlineStr">
-        <is>
-          <t>MONTHLY returns (% of capital at start of month)</t>
-        </is>
-      </c>
-    </row>
-    <row r="4">
-      <c r="A4" s="2" t="inlineStr">
-        <is>
-          <t>Year</t>
-        </is>
-      </c>
-      <c r="B4" s="2" t="inlineStr">
-        <is>
-          <t>Jan</t>
-        </is>
-      </c>
-      <c r="C4" s="2" t="inlineStr">
-        <is>
-          <t>Feb</t>
-        </is>
-      </c>
-      <c r="D4" s="2" t="inlineStr">
-        <is>
-          <t>Mar</t>
-        </is>
-      </c>
-      <c r="E4" s="2" t="inlineStr">
-        <is>
-          <t>Apr</t>
-        </is>
-      </c>
-      <c r="F4" s="2" t="inlineStr">
-        <is>
-          <t>May</t>
-        </is>
-      </c>
-      <c r="G4" s="2" t="inlineStr">
-        <is>
-          <t>Jun</t>
-        </is>
-      </c>
-      <c r="H4" s="2" t="inlineStr">
-        <is>
-          <t>Jul</t>
-        </is>
-      </c>
-      <c r="I4" s="2" t="inlineStr">
-        <is>
-          <t>Aug</t>
-        </is>
-      </c>
-      <c r="J4" s="2" t="inlineStr">
-        <is>
-          <t>Sep</t>
-        </is>
-      </c>
-      <c r="K4" s="2" t="inlineStr">
-        <is>
-          <t>Oct</t>
-        </is>
-      </c>
-      <c r="L4" s="2" t="inlineStr">
-        <is>
-          <t>Nov</t>
-        </is>
-      </c>
-      <c r="M4" s="2" t="inlineStr">
-        <is>
-          <t>Dec</t>
-        </is>
-      </c>
-      <c r="N4" s="2" t="inlineStr">
-        <is>
-          <t>Yr %</t>
-        </is>
-      </c>
-      <c r="O4" s="2" t="inlineStr">
-        <is>
-          <t>Yr P&amp;L (Rs)</t>
-        </is>
-      </c>
-    </row>
-    <row r="5">
-      <c r="A5" s="3" t="n">
-        <v>2025</v>
-      </c>
-      <c r="B5" s="13" t="n"/>
-      <c r="C5" s="13" t="n"/>
-      <c r="D5" s="13" t="n"/>
-      <c r="E5" s="13" t="n"/>
-      <c r="F5" s="13" t="n"/>
-      <c r="G5" s="13" t="n"/>
-      <c r="H5" s="13" t="n"/>
-      <c r="I5" s="13" t="n"/>
-      <c r="J5" s="13" t="n"/>
-      <c r="K5" s="13" t="n"/>
-      <c r="L5" s="13" t="n"/>
-      <c r="M5" s="30" t="n">
-        <v>-0.0469125</v>
-      </c>
-      <c r="N5" s="31" t="n">
-        <v>-0.04691250000000002</v>
-      </c>
-      <c r="O5" s="32" t="n">
-        <v>-938.25</v>
-      </c>
-    </row>
-    <row r="6">
-      <c r="A6" s="3" t="n">
-        <v>2026</v>
-      </c>
-      <c r="B6" s="30" t="n">
-        <v>-0.01505685469592246</v>
-      </c>
-      <c r="C6" s="13" t="n"/>
-      <c r="D6" s="13" t="n"/>
-      <c r="E6" s="14" t="n">
-        <v>0.01262227865738753</v>
-      </c>
-      <c r="F6" s="13" t="n"/>
-      <c r="G6" s="13" t="n"/>
-      <c r="H6" s="13" t="n"/>
-      <c r="I6" s="13" t="n"/>
-      <c r="J6" s="30" t="n">
-        <v>-0.01216670559002552</v>
-      </c>
-      <c r="K6" s="13" t="n"/>
-      <c r="L6" s="13" t="n"/>
-      <c r="M6" s="13" t="n"/>
-      <c r="N6" s="31" t="n">
-        <v>-0.01475940036985068</v>
-      </c>
-      <c r="O6" s="32" t="n">
-        <v>-281.34</v>
-      </c>
-    </row>
-    <row r="7">
-      <c r="A7" s="3" t="inlineStr">
-        <is>
-          <t>Avg</t>
-        </is>
-      </c>
-      <c r="B7" s="31" t="n">
-        <v>-0.01505685469592246</v>
-      </c>
-      <c r="C7" s="13" t="n"/>
-      <c r="D7" s="13" t="n"/>
-      <c r="E7" s="15" t="n">
-        <v>0.01262227865738753</v>
-      </c>
-      <c r="F7" s="13" t="n"/>
-      <c r="G7" s="13" t="n"/>
-      <c r="H7" s="13" t="n"/>
-      <c r="I7" s="13" t="n"/>
-      <c r="J7" s="31" t="n">
-        <v>-0.01216670559002552</v>
-      </c>
-      <c r="K7" s="13" t="n"/>
-      <c r="L7" s="13" t="n"/>
-      <c r="M7" s="31" t="n">
-        <v>-0.0469125</v>
-      </c>
-    </row>
-    <row r="9">
-      <c r="A9" s="12" t="inlineStr">
-        <is>
-          <t>WEEKLY returns (% of capital at start of that week; weeks split at month edges)</t>
-        </is>
-      </c>
-    </row>
-    <row r="10">
-      <c r="A10" s="2" t="inlineStr">
-        <is>
-          <t>Month</t>
-        </is>
-      </c>
-      <c r="B10" s="2" t="inlineStr">
-        <is>
-          <t>W1</t>
-        </is>
-      </c>
-      <c r="C10" s="2" t="inlineStr">
-        <is>
-          <t>W2</t>
-        </is>
-      </c>
-      <c r="D10" s="2" t="inlineStr">
-        <is>
-          <t>W3</t>
-        </is>
-      </c>
-      <c r="E10" s="2" t="inlineStr">
-        <is>
-          <t>W4</t>
-        </is>
-      </c>
-      <c r="F10" s="2" t="inlineStr">
-        <is>
-          <t>W5</t>
-        </is>
-      </c>
-      <c r="G10" s="2" t="inlineStr">
-        <is>
-          <t>W6</t>
-        </is>
-      </c>
-      <c r="H10" s="2" t="inlineStr">
-        <is>
-          <t>Month %</t>
-        </is>
-      </c>
-      <c r="I10" s="2" t="inlineStr">
-        <is>
-          <t>Month P&amp;L (Rs)</t>
-        </is>
-      </c>
-    </row>
-    <row r="11">
-      <c r="A11" s="3" t="inlineStr">
-        <is>
-          <t>2025-Dec</t>
-        </is>
-      </c>
-      <c r="B11" s="30" t="n">
-        <v>-0.010346</v>
-      </c>
-      <c r="C11" s="30" t="n">
-        <v>-0.0369487719950609</v>
-      </c>
-      <c r="D11" s="13" t="n"/>
-      <c r="E11" s="13" t="n"/>
-      <c r="F11" s="13" t="n"/>
-      <c r="G11" s="13" t="n"/>
-      <c r="H11" s="33" t="n">
-        <v>-0.0469125</v>
-      </c>
-      <c r="I11" s="32" t="n">
-        <v>-938.25</v>
-      </c>
-    </row>
-    <row r="12">
-      <c r="A12" s="3" t="inlineStr">
-        <is>
-          <t>2026-Jan</t>
-        </is>
-      </c>
-      <c r="B12" s="30" t="n">
-        <v>-0.01505685469592246</v>
-      </c>
-      <c r="C12" s="13" t="n"/>
-      <c r="D12" s="13" t="n"/>
-      <c r="E12" s="13" t="n"/>
-      <c r="F12" s="13" t="n"/>
-      <c r="G12" s="13" t="n"/>
-      <c r="H12" s="33" t="n">
-        <v>-0.01505685469592246</v>
-      </c>
-      <c r="I12" s="32" t="n">
-        <v>-287.01</v>
-      </c>
-    </row>
-    <row r="13">
-      <c r="A13" s="3" t="inlineStr">
-        <is>
-          <t>2026-Apr</t>
-        </is>
-      </c>
-      <c r="B13" s="14" t="n">
-        <v>0.01262227865738753</v>
-      </c>
-      <c r="C13" s="13" t="n"/>
-      <c r="D13" s="13" t="n"/>
-      <c r="E13" s="13" t="n"/>
-      <c r="F13" s="13" t="n"/>
-      <c r="G13" s="13" t="n"/>
-      <c r="H13" s="17" t="n">
-        <v>0.01262227865738753</v>
-      </c>
-      <c r="I13" s="16" t="n">
-        <v>236.98</v>
-      </c>
-    </row>
-    <row r="14">
-      <c r="A14" s="3" t="inlineStr">
-        <is>
-          <t>2026-Sep</t>
-        </is>
-      </c>
-      <c r="B14" s="30" t="n">
-        <v>-0.01216670559002552</v>
-      </c>
-      <c r="C14" s="13" t="n"/>
-      <c r="D14" s="13" t="n"/>
-      <c r="E14" s="13" t="n"/>
-      <c r="F14" s="13" t="n"/>
-      <c r="G14" s="13" t="n"/>
-      <c r="H14" s="33" t="n">
-        <v>-0.01216670559002552</v>
-      </c>
-      <c r="I14" s="32" t="n">
-        <v>-231.31</v>
-      </c>
-    </row>
-    <row r="16">
-      <c r="A16" s="12" t="inlineStr">
-        <is>
-          <t>DAILY returns (% of capital at start of that day; blank = no trade that day)</t>
-        </is>
-      </c>
-    </row>
-    <row r="17">
-      <c r="A17" s="2" t="inlineStr">
-        <is>
-          <t>Week starting (Mon)</t>
-        </is>
-      </c>
-      <c r="B17" s="2" t="inlineStr">
-        <is>
-          <t>Mon</t>
-        </is>
-      </c>
-      <c r="C17" s="2" t="inlineStr">
-        <is>
-          <t>Tue</t>
-        </is>
-      </c>
-      <c r="D17" s="2" t="inlineStr">
-        <is>
-          <t>Wed</t>
-        </is>
-      </c>
-      <c r="E17" s="2" t="inlineStr">
-        <is>
-          <t>Thu</t>
-        </is>
-      </c>
-      <c r="F17" s="2" t="inlineStr">
-        <is>
-          <t>Fri</t>
-        </is>
-      </c>
-      <c r="G17" s="2" t="inlineStr">
-        <is>
-          <t>Week %</t>
-        </is>
-      </c>
-      <c r="H17" s="2" t="inlineStr">
-        <is>
-          <t>Week P&amp;L (Rs)</t>
-        </is>
-      </c>
-    </row>
-    <row r="18">
-      <c r="A18" s="3" t="inlineStr">
-        <is>
-          <t>01-Dec-2025</t>
-        </is>
-      </c>
-      <c r="B18" s="13" t="n"/>
-      <c r="C18" s="30" t="n">
-        <v>-0.010346</v>
-      </c>
-      <c r="D18" s="13" t="n"/>
-      <c r="E18" s="13" t="n"/>
-      <c r="F18" s="13" t="n"/>
-      <c r="G18" s="33" t="n">
-        <v>-0.010346</v>
-      </c>
-      <c r="H18" s="32" t="n">
-        <v>-206.92</v>
-      </c>
-    </row>
-    <row r="19">
-      <c r="A19" s="3" t="inlineStr">
-        <is>
-          <t>08-Dec-2025</t>
-        </is>
-      </c>
-      <c r="B19" s="13" t="n"/>
-      <c r="C19" s="30" t="n">
-        <v>-0.0369487719950609</v>
-      </c>
-      <c r="D19" s="13" t="n"/>
-      <c r="E19" s="13" t="n"/>
-      <c r="F19" s="13" t="n"/>
-      <c r="G19" s="33" t="n">
-        <v>-0.0369487719950609</v>
-      </c>
-      <c r="H19" s="32" t="n">
-        <v>-731.33</v>
-      </c>
-    </row>
-    <row r="20">
-      <c r="A20" s="3" t="inlineStr">
-        <is>
-          <t>26-Jan-2026</t>
-        </is>
-      </c>
-      <c r="B20" s="13" t="n"/>
-      <c r="C20" s="30" t="n">
-        <v>-0.01505685469592246</v>
-      </c>
-      <c r="D20" s="13" t="n"/>
-      <c r="E20" s="13" t="n"/>
-      <c r="F20" s="13" t="n"/>
-      <c r="G20" s="33" t="n">
-        <v>-0.01505685469592246</v>
-      </c>
-      <c r="H20" s="32" t="n">
-        <v>-287.01</v>
-      </c>
-    </row>
-    <row r="21">
-      <c r="A21" s="3" t="inlineStr">
-        <is>
-          <t>06-Apr-2026</t>
-        </is>
-      </c>
-      <c r="B21" s="13" t="n"/>
-      <c r="C21" s="14" t="n">
-        <v>0.01262227865738753</v>
-      </c>
-      <c r="D21" s="13" t="n"/>
-      <c r="E21" s="13" t="n"/>
-      <c r="F21" s="13" t="n"/>
-      <c r="G21" s="17" t="n">
-        <v>0.01262227865738753</v>
-      </c>
-      <c r="H21" s="16" t="n">
-        <v>236.98</v>
-      </c>
-    </row>
-    <row r="22">
-      <c r="A22" s="3" t="inlineStr">
-        <is>
-          <t>07-Sep-2026</t>
-        </is>
-      </c>
-      <c r="B22" s="13" t="n"/>
-      <c r="C22" s="30" t="n">
-        <v>-0.01216670559002552</v>
-      </c>
-      <c r="D22" s="13" t="n"/>
-      <c r="E22" s="13" t="n"/>
-      <c r="F22" s="13" t="n"/>
-      <c r="G22" s="33" t="n">
-        <v>-0.01216670559002552</v>
-      </c>
-      <c r="H22" s="32" t="n">
-        <v>-231.31</v>
-      </c>
-    </row>
-    <row r="24">
-      <c r="A24" s="12" t="inlineStr">
-        <is>
-          <t>STATISTICS (all trades for this index)</t>
-        </is>
-      </c>
-    </row>
-    <row r="25">
-      <c r="A25" s="3" t="inlineStr">
-        <is>
-          <t>All trades</t>
-        </is>
-      </c>
-      <c r="B25" s="18" t="n">
-        <v>7</v>
-      </c>
-      <c r="C25" s="19" t="n"/>
-      <c r="D25" s="20" t="n"/>
-    </row>
-    <row r="26">
-      <c r="A26" s="3" t="inlineStr">
-        <is>
-          <t>Winners</t>
-        </is>
-      </c>
-      <c r="B26" s="21" t="inlineStr">
-        <is>
-          <t>1 (14.3%)</t>
-        </is>
-      </c>
-      <c r="C26" s="19" t="n"/>
-      <c r="D26" s="20" t="n"/>
-    </row>
-    <row r="27">
-      <c r="A27" s="3" t="inlineStr">
-        <is>
-          <t>Losers</t>
-        </is>
-      </c>
-      <c r="B27" s="21" t="inlineStr">
-        <is>
-          <t>6 (85.7%)</t>
-        </is>
-      </c>
-      <c r="C27" s="19" t="n"/>
-      <c r="D27" s="20" t="n"/>
-    </row>
-    <row r="28">
-      <c r="A28" s="3" t="inlineStr">
-        <is>
-          <t>Net P&amp;L (Rs)</t>
-        </is>
-      </c>
-      <c r="B28" s="23" t="n">
-        <v>-1219.59</v>
-      </c>
-      <c r="C28" s="19" t="n"/>
-      <c r="D28" s="20" t="n"/>
-    </row>
-    <row r="29">
-      <c r="A29" s="3" t="inlineStr">
-        <is>
-          <t>Total Profit (Rs)</t>
-        </is>
-      </c>
-      <c r="B29" s="22" t="n">
-        <v>236.98</v>
-      </c>
-      <c r="C29" s="19" t="n"/>
-      <c r="D29" s="20" t="n"/>
-    </row>
-    <row r="30">
-      <c r="A30" s="3" t="inlineStr">
-        <is>
-          <t>Total Loss (Rs)</t>
-        </is>
-      </c>
-      <c r="B30" s="23" t="n">
-        <v>-1456.57</v>
-      </c>
-      <c r="C30" s="19" t="n"/>
-      <c r="D30" s="20" t="n"/>
-    </row>
-    <row r="31">
-      <c r="A31" s="3" t="inlineStr">
-        <is>
-          <t>Transaction costs (Rs)</t>
-        </is>
-      </c>
-      <c r="B31" s="24" t="n">
-        <v>348.39</v>
-      </c>
-      <c r="C31" s="19" t="n"/>
-      <c r="D31" s="20" t="n"/>
-    </row>
-    <row r="32">
-      <c r="A32" s="3" t="inlineStr">
-        <is>
-          <t>Avg Profit/Loss per trade (Rs)</t>
-        </is>
-      </c>
-      <c r="B32" s="23" t="n">
-        <v>-174.23</v>
-      </c>
-      <c r="C32" s="19" t="n"/>
-      <c r="D32" s="20" t="n"/>
-    </row>
-    <row r="33">
-      <c r="A33" s="3" t="inlineStr">
-        <is>
-          <t>Avg Profit/Loss per trade (% of premium)</t>
-        </is>
-      </c>
-      <c r="B33" s="25" t="n">
-        <v>-10.42</v>
-      </c>
-      <c r="C33" s="19" t="n"/>
-      <c r="D33" s="20" t="n"/>
-    </row>
-    <row r="34">
-      <c r="A34" s="3" t="inlineStr">
-        <is>
-          <t>Avg Win (Rs)</t>
-        </is>
-      </c>
-      <c r="B34" s="22" t="n">
-        <v>236.98</v>
-      </c>
-      <c r="C34" s="19" t="n"/>
-      <c r="D34" s="20" t="n"/>
-    </row>
-    <row r="35">
-      <c r="A35" s="3" t="inlineStr">
-        <is>
-          <t>Avg Win (% of premium)</t>
-        </is>
-      </c>
-      <c r="B35" s="26" t="n">
-        <v>16.17</v>
-      </c>
-      <c r="C35" s="19" t="n"/>
-      <c r="D35" s="20" t="n"/>
-    </row>
-    <row r="36">
-      <c r="A36" s="3" t="inlineStr">
-        <is>
-          <t>Avg Loss (Rs)</t>
-        </is>
-      </c>
-      <c r="B36" s="23" t="n">
-        <v>-242.76</v>
-      </c>
-      <c r="C36" s="19" t="n"/>
-      <c r="D36" s="20" t="n"/>
-    </row>
-    <row r="37">
-      <c r="A37" s="3" t="inlineStr">
-        <is>
-          <t>Avg Loss (% of premium)</t>
-        </is>
-      </c>
-      <c r="B37" s="27" t="n">
-        <v>-14.85</v>
-      </c>
-      <c r="C37" s="19" t="n"/>
-      <c r="D37" s="20" t="n"/>
-    </row>
-    <row r="38">
-      <c r="A38" s="3" t="inlineStr">
-        <is>
-          <t>Largest Win (Rs)</t>
-        </is>
-      </c>
-      <c r="B38" s="22" t="n">
-        <v>236.98</v>
-      </c>
-      <c r="C38" s="19" t="n"/>
-      <c r="D38" s="20" t="n"/>
-    </row>
-    <row r="39">
-      <c r="A39" s="3" t="inlineStr">
-        <is>
-          <t>Largest Loss (Rs)</t>
-        </is>
-      </c>
-      <c r="B39" s="23" t="n">
-        <v>-295.95</v>
-      </c>
-      <c r="C39" s="19" t="n"/>
-      <c r="D39" s="20" t="n"/>
-    </row>
-    <row r="40">
-      <c r="A40" s="3" t="inlineStr">
-        <is>
-          <t>Max Consecutive Wins</t>
-        </is>
-      </c>
-      <c r="B40" s="18" t="n">
-        <v>1</v>
-      </c>
-      <c r="C40" s="19" t="n"/>
-      <c r="D40" s="20" t="n"/>
-    </row>
-    <row r="41">
-      <c r="A41" s="3" t="inlineStr">
-        <is>
-          <t>Max Consecutive Losses</t>
-        </is>
-      </c>
-      <c r="B41" s="18" t="n">
-        <v>5</v>
-      </c>
-      <c r="C41" s="19" t="n"/>
-      <c r="D41" s="20" t="n"/>
-    </row>
-    <row r="42">
-      <c r="A42" s="3" t="inlineStr">
-        <is>
-          <t>Max trade drawdown (Rs)</t>
-        </is>
-      </c>
-      <c r="B42" s="23" t="n">
-        <v>-295.95</v>
-      </c>
-      <c r="C42" s="19" t="n"/>
-      <c r="D42" s="20" t="n"/>
-    </row>
-    <row r="43">
-      <c r="A43" s="3" t="inlineStr">
-        <is>
-          <t>Max system drawdown (Rs)</t>
-        </is>
-      </c>
-      <c r="B43" s="23" t="n">
-        <v>-1225.26</v>
-      </c>
-      <c r="C43" s="19" t="n"/>
-      <c r="D43" s="20" t="n"/>
-    </row>
-    <row r="44">
-      <c r="A44" s="3" t="inlineStr">
-        <is>
-          <t>Max system drawdown (%)</t>
-        </is>
-      </c>
-      <c r="B44" s="27" t="n">
-        <v>-6.13</v>
-      </c>
-      <c r="C44" s="19" t="n"/>
-      <c r="D44" s="20" t="n"/>
-    </row>
-    <row r="45">
-      <c r="A45" s="3" t="inlineStr">
-        <is>
-          <t>Recovery Factor</t>
-        </is>
-      </c>
-      <c r="B45" s="28" t="n">
-        <v>-1</v>
-      </c>
-      <c r="C45" s="19" t="n"/>
-      <c r="D45" s="20" t="n"/>
-    </row>
-    <row r="46">
-      <c r="A46" s="3" t="inlineStr">
-        <is>
-          <t>Profit Factor</t>
-        </is>
-      </c>
-      <c r="B46" s="28" t="n">
-        <v>0.16</v>
-      </c>
-      <c r="C46" s="19" t="n"/>
-      <c r="D46" s="20" t="n"/>
-    </row>
-    <row r="47">
-      <c r="A47" s="3" t="inlineStr">
-        <is>
-          <t>Payoff Ratio (avg win / avg loss)</t>
-        </is>
-      </c>
-      <c r="B47" s="28" t="n">
-        <v>0.98</v>
-      </c>
-      <c r="C47" s="19" t="n"/>
-      <c r="D47" s="20" t="n"/>
-    </row>
-    <row r="48">
-      <c r="A48" s="3" t="inlineStr">
-        <is>
-          <t>Sharpe Ratio (annualized)</t>
-        </is>
-      </c>
-      <c r="B48" s="28" t="n">
-        <v>-12.48</v>
-      </c>
-      <c r="C48" s="19" t="n"/>
-      <c r="D48" s="20" t="n"/>
-    </row>
-    <row r="50">
-      <c r="A50" s="11" t="inlineStr">
-        <is>
-          <t>Caveat: with only a handful of trades these numbers (Sharpe, profit factor, drawdown %) are not statistically reliable. Watch this over weeks/months before drawing conclusions.</t>
-        </is>
-      </c>
-    </row>
-  </sheetData>
-  <mergeCells count="24">
-    <mergeCell ref="B42:D42"/>
-    <mergeCell ref="B44:D44"/>
-    <mergeCell ref="B29:D29"/>
-    <mergeCell ref="B38:D38"/>
-    <mergeCell ref="B34:D34"/>
-    <mergeCell ref="B28:D28"/>
-    <mergeCell ref="B37:D37"/>
-    <mergeCell ref="B40:D40"/>
-    <mergeCell ref="B30:D30"/>
-    <mergeCell ref="B33:D33"/>
-    <mergeCell ref="B36:D36"/>
-    <mergeCell ref="B45:D45"/>
-    <mergeCell ref="B41:D41"/>
-    <mergeCell ref="B32:D32"/>
-    <mergeCell ref="B35:D35"/>
-    <mergeCell ref="B26:D26"/>
-    <mergeCell ref="B25:D25"/>
-    <mergeCell ref="B47:D47"/>
-    <mergeCell ref="B31:D31"/>
-    <mergeCell ref="B46:D46"/>
-    <mergeCell ref="B27:D27"/>
-    <mergeCell ref="B43:D43"/>
-    <mergeCell ref="B39:D39"/>
-    <mergeCell ref="B48:D48"/>
-  </mergeCells>
-  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
-  <pageSetup orientation="landscape" fitToHeight="0" fitToWidth="1"/>
-</worksheet>
-</file>
-
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr>
@@ -2995,1120 +2149,4 @@
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
   <pageSetup orientation="landscape" fitToHeight="0" fitToWidth="1"/>
 </worksheet>
-</file>
-
-<file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <sheetPr>
-    <outlinePr summaryBelow="1" summaryRight="1"/>
-    <pageSetUpPr fitToPage="1"/>
-  </sheetPr>
-  <dimension ref="A1:G9"/>
-  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
-  <cols>
-    <col width="15" customWidth="1" min="1" max="1"/>
-    <col width="22" customWidth="1" min="2" max="2"/>
-    <col width="15" customWidth="1" min="3" max="3"/>
-    <col width="15" customWidth="1" min="4" max="4"/>
-    <col width="15" customWidth="1" min="5" max="5"/>
-    <col width="15" customWidth="1" min="6" max="6"/>
-    <col width="15" customWidth="1" min="7" max="7"/>
-  </cols>
-  <sheetData>
-    <row r="1">
-      <c r="A1" s="1" t="inlineStr">
-        <is>
-          <t>BACKTEST summary by index (best strategy per index) -- PAPER TRADE, NOT REAL MONEY</t>
-        </is>
-      </c>
-    </row>
-    <row r="3">
-      <c r="A3" s="2" t="inlineStr">
-        <is>
-          <t>Index</t>
-        </is>
-      </c>
-      <c r="B3" s="2" t="inlineStr">
-        <is>
-          <t>Best Strategy</t>
-        </is>
-      </c>
-      <c r="C3" s="2" t="inlineStr">
-        <is>
-          <t>Trades</t>
-        </is>
-      </c>
-      <c r="D3" s="2" t="inlineStr">
-        <is>
-          <t>Win %</t>
-        </is>
-      </c>
-      <c r="E3" s="2" t="inlineStr">
-        <is>
-          <t>Net P&amp;L (Rs)</t>
-        </is>
-      </c>
-      <c r="F3" s="2" t="inlineStr">
-        <is>
-          <t>Profit Factor</t>
-        </is>
-      </c>
-      <c r="G3" s="2" t="inlineStr">
-        <is>
-          <t>Max DD (%)</t>
-        </is>
-      </c>
-    </row>
-    <row r="4">
-      <c r="A4" s="3" t="inlineStr">
-        <is>
-          <t>NIFTY</t>
-        </is>
-      </c>
-      <c r="B4" s="13" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="C4" s="10" t="n">
-        <v>0</v>
-      </c>
-      <c r="D4" s="10" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="E4" s="10" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="F4" s="10" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="G4" s="10" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-    </row>
-    <row r="5">
-      <c r="A5" s="3" t="inlineStr">
-        <is>
-          <t>BANKNIFTY</t>
-        </is>
-      </c>
-      <c r="B5" s="13" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="C5" s="10" t="n">
-        <v>0</v>
-      </c>
-      <c r="D5" s="10" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="E5" s="10" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="F5" s="10" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="G5" s="10" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-    </row>
-    <row r="6">
-      <c r="A6" s="3" t="inlineStr">
-        <is>
-          <t>FINNIFTY</t>
-        </is>
-      </c>
-      <c r="B6" s="13" t="inlineStr">
-        <is>
-          <t>trend_scalp_nw (EMA9/26) [5m]</t>
-        </is>
-      </c>
-      <c r="C6" s="4" t="n">
-        <v>7</v>
-      </c>
-      <c r="D6" s="5" t="n">
-        <v>0.1428571428571428</v>
-      </c>
-      <c r="E6" s="29" t="n">
-        <v>-1219.59</v>
-      </c>
-      <c r="F6" s="7" t="n">
-        <v>0.16</v>
-      </c>
-      <c r="G6" s="8" t="n">
-        <v>-0.06126299999999993</v>
-      </c>
-    </row>
-    <row r="7">
-      <c r="A7" s="3" t="inlineStr">
-        <is>
-          <t>ALL INDICES</t>
-        </is>
-      </c>
-      <c r="B7" s="13" t="inlineStr">
-        <is>
-          <t>(combined)</t>
-        </is>
-      </c>
-      <c r="C7" s="4" t="n">
-        <v>7</v>
-      </c>
-      <c r="D7" s="5" t="n">
-        <v>0.1428571428571428</v>
-      </c>
-      <c r="E7" s="29" t="n">
-        <v>-1219.59</v>
-      </c>
-      <c r="F7" s="7" t="n">
-        <v>0.16</v>
-      </c>
-      <c r="G7" s="8" t="n">
-        <v>-0.06126299999999993</v>
-      </c>
-    </row>
-    <row r="9">
-      <c r="A9" s="11" t="inlineStr">
-        <is>
-          <t>BT- sheets are from the BACKTEST (each index's single best combo, so time periods aren't double-counted across competing strategies). Plain-named sheets are LIVE paper trades. See latest_backtest_summary.xlsx for every combo tested.</t>
-        </is>
-      </c>
-    </row>
-  </sheetData>
-  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
-  <pageSetup orientation="landscape" fitToHeight="0" fitToWidth="1"/>
-</worksheet>
-</file>
-
-<file path=xl/worksheets/sheet7.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <sheetPr>
-    <outlinePr summaryBelow="1" summaryRight="1"/>
-    <pageSetUpPr fitToPage="1"/>
-  </sheetPr>
-  <dimension ref="A1:A3"/>
-  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
-  <cols>
-    <col width="40" customWidth="1" min="1" max="1"/>
-    <col width="10" customWidth="1" min="2" max="2"/>
-    <col width="10" customWidth="1" min="3" max="3"/>
-    <col width="10" customWidth="1" min="4" max="4"/>
-    <col width="10" customWidth="1" min="5" max="5"/>
-    <col width="10" customWidth="1" min="6" max="6"/>
-    <col width="10" customWidth="1" min="7" max="7"/>
-    <col width="15" customWidth="1" min="8" max="8"/>
-    <col width="15" customWidth="1" min="9" max="9"/>
-    <col width="10" customWidth="1" min="10" max="10"/>
-    <col width="10" customWidth="1" min="11" max="11"/>
-    <col width="10" customWidth="1" min="12" max="12"/>
-    <col width="10" customWidth="1" min="13" max="13"/>
-    <col width="10" customWidth="1" min="14" max="14"/>
-    <col width="15" customWidth="1" min="15" max="15"/>
-  </cols>
-  <sheetData>
-    <row r="1">
-      <c r="A1" s="1" t="inlineStr">
-        <is>
-          <t>BACKTEST NIFTY -- best:  -- PAPER TRADE, NOT REAL MONEY</t>
-        </is>
-      </c>
-    </row>
-    <row r="3">
-      <c r="A3" s="11" t="inlineStr">
-        <is>
-          <t>No trades yet for this index -- this fills in automatically as the bot trades.</t>
-        </is>
-      </c>
-    </row>
-  </sheetData>
-  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
-  <pageSetup orientation="landscape" fitToHeight="0" fitToWidth="1"/>
-</worksheet>
-</file>
-
-<file path=xl/worksheets/sheet8.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <sheetPr>
-    <outlinePr summaryBelow="1" summaryRight="1"/>
-    <pageSetUpPr fitToPage="1"/>
-  </sheetPr>
-  <dimension ref="A1:A3"/>
-  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
-  <cols>
-    <col width="40" customWidth="1" min="1" max="1"/>
-    <col width="10" customWidth="1" min="2" max="2"/>
-    <col width="10" customWidth="1" min="3" max="3"/>
-    <col width="10" customWidth="1" min="4" max="4"/>
-    <col width="10" customWidth="1" min="5" max="5"/>
-    <col width="10" customWidth="1" min="6" max="6"/>
-    <col width="10" customWidth="1" min="7" max="7"/>
-    <col width="15" customWidth="1" min="8" max="8"/>
-    <col width="15" customWidth="1" min="9" max="9"/>
-    <col width="10" customWidth="1" min="10" max="10"/>
-    <col width="10" customWidth="1" min="11" max="11"/>
-    <col width="10" customWidth="1" min="12" max="12"/>
-    <col width="10" customWidth="1" min="13" max="13"/>
-    <col width="10" customWidth="1" min="14" max="14"/>
-    <col width="15" customWidth="1" min="15" max="15"/>
-  </cols>
-  <sheetData>
-    <row r="1">
-      <c r="A1" s="1" t="inlineStr">
-        <is>
-          <t>BACKTEST BANKNIFTY -- best:  -- PAPER TRADE, NOT REAL MONEY</t>
-        </is>
-      </c>
-    </row>
-    <row r="3">
-      <c r="A3" s="11" t="inlineStr">
-        <is>
-          <t>No trades yet for this index -- this fills in automatically as the bot trades.</t>
-        </is>
-      </c>
-    </row>
-  </sheetData>
-  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
-  <pageSetup orientation="landscape" fitToHeight="0" fitToWidth="1"/>
-</worksheet>
-</file>
-
-<file path=xl/worksheets/sheet9.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <sheetPr>
-    <outlinePr summaryBelow="1" summaryRight="1"/>
-    <pageSetUpPr fitToPage="1"/>
-  </sheetPr>
-  <dimension ref="A1:O50"/>
-  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
-  <cols>
-    <col width="40" customWidth="1" min="1" max="1"/>
-    <col width="10" customWidth="1" min="2" max="2"/>
-    <col width="10" customWidth="1" min="3" max="3"/>
-    <col width="10" customWidth="1" min="4" max="4"/>
-    <col width="10" customWidth="1" min="5" max="5"/>
-    <col width="10" customWidth="1" min="6" max="6"/>
-    <col width="10" customWidth="1" min="7" max="7"/>
-    <col width="15" customWidth="1" min="8" max="8"/>
-    <col width="15" customWidth="1" min="9" max="9"/>
-    <col width="10" customWidth="1" min="10" max="10"/>
-    <col width="10" customWidth="1" min="11" max="11"/>
-    <col width="10" customWidth="1" min="12" max="12"/>
-    <col width="10" customWidth="1" min="13" max="13"/>
-    <col width="10" customWidth="1" min="14" max="14"/>
-    <col width="15" customWidth="1" min="15" max="15"/>
-  </cols>
-  <sheetData>
-    <row r="1">
-      <c r="A1" s="1" t="inlineStr">
-        <is>
-          <t>BACKTEST FINNIFTY -- best: trend_scalp_nw (EMA9/26) [5m] -- PAPER TRADE, NOT REAL MONEY</t>
-        </is>
-      </c>
-    </row>
-    <row r="3">
-      <c r="A3" s="12" t="inlineStr">
-        <is>
-          <t>MONTHLY returns (% of capital at start of month)</t>
-        </is>
-      </c>
-    </row>
-    <row r="4">
-      <c r="A4" s="2" t="inlineStr">
-        <is>
-          <t>Year</t>
-        </is>
-      </c>
-      <c r="B4" s="2" t="inlineStr">
-        <is>
-          <t>Jan</t>
-        </is>
-      </c>
-      <c r="C4" s="2" t="inlineStr">
-        <is>
-          <t>Feb</t>
-        </is>
-      </c>
-      <c r="D4" s="2" t="inlineStr">
-        <is>
-          <t>Mar</t>
-        </is>
-      </c>
-      <c r="E4" s="2" t="inlineStr">
-        <is>
-          <t>Apr</t>
-        </is>
-      </c>
-      <c r="F4" s="2" t="inlineStr">
-        <is>
-          <t>May</t>
-        </is>
-      </c>
-      <c r="G4" s="2" t="inlineStr">
-        <is>
-          <t>Jun</t>
-        </is>
-      </c>
-      <c r="H4" s="2" t="inlineStr">
-        <is>
-          <t>Jul</t>
-        </is>
-      </c>
-      <c r="I4" s="2" t="inlineStr">
-        <is>
-          <t>Aug</t>
-        </is>
-      </c>
-      <c r="J4" s="2" t="inlineStr">
-        <is>
-          <t>Sep</t>
-        </is>
-      </c>
-      <c r="K4" s="2" t="inlineStr">
-        <is>
-          <t>Oct</t>
-        </is>
-      </c>
-      <c r="L4" s="2" t="inlineStr">
-        <is>
-          <t>Nov</t>
-        </is>
-      </c>
-      <c r="M4" s="2" t="inlineStr">
-        <is>
-          <t>Dec</t>
-        </is>
-      </c>
-      <c r="N4" s="2" t="inlineStr">
-        <is>
-          <t>Yr %</t>
-        </is>
-      </c>
-      <c r="O4" s="2" t="inlineStr">
-        <is>
-          <t>Yr P&amp;L (Rs)</t>
-        </is>
-      </c>
-    </row>
-    <row r="5">
-      <c r="A5" s="3" t="n">
-        <v>2025</v>
-      </c>
-      <c r="B5" s="13" t="n"/>
-      <c r="C5" s="13" t="n"/>
-      <c r="D5" s="13" t="n"/>
-      <c r="E5" s="13" t="n"/>
-      <c r="F5" s="13" t="n"/>
-      <c r="G5" s="13" t="n"/>
-      <c r="H5" s="13" t="n"/>
-      <c r="I5" s="13" t="n"/>
-      <c r="J5" s="13" t="n"/>
-      <c r="K5" s="13" t="n"/>
-      <c r="L5" s="13" t="n"/>
-      <c r="M5" s="30" t="n">
-        <v>-0.0469125</v>
-      </c>
-      <c r="N5" s="31" t="n">
-        <v>-0.04691250000000002</v>
-      </c>
-      <c r="O5" s="32" t="n">
-        <v>-938.25</v>
-      </c>
-    </row>
-    <row r="6">
-      <c r="A6" s="3" t="n">
-        <v>2026</v>
-      </c>
-      <c r="B6" s="30" t="n">
-        <v>-0.01505685469592246</v>
-      </c>
-      <c r="C6" s="13" t="n"/>
-      <c r="D6" s="13" t="n"/>
-      <c r="E6" s="14" t="n">
-        <v>0.01262227865738753</v>
-      </c>
-      <c r="F6" s="13" t="n"/>
-      <c r="G6" s="13" t="n"/>
-      <c r="H6" s="13" t="n"/>
-      <c r="I6" s="13" t="n"/>
-      <c r="J6" s="30" t="n">
-        <v>-0.01216670559002552</v>
-      </c>
-      <c r="K6" s="13" t="n"/>
-      <c r="L6" s="13" t="n"/>
-      <c r="M6" s="13" t="n"/>
-      <c r="N6" s="31" t="n">
-        <v>-0.01475940036985068</v>
-      </c>
-      <c r="O6" s="32" t="n">
-        <v>-281.34</v>
-      </c>
-    </row>
-    <row r="7">
-      <c r="A7" s="3" t="inlineStr">
-        <is>
-          <t>Avg</t>
-        </is>
-      </c>
-      <c r="B7" s="31" t="n">
-        <v>-0.01505685469592246</v>
-      </c>
-      <c r="C7" s="13" t="n"/>
-      <c r="D7" s="13" t="n"/>
-      <c r="E7" s="15" t="n">
-        <v>0.01262227865738753</v>
-      </c>
-      <c r="F7" s="13" t="n"/>
-      <c r="G7" s="13" t="n"/>
-      <c r="H7" s="13" t="n"/>
-      <c r="I7" s="13" t="n"/>
-      <c r="J7" s="31" t="n">
-        <v>-0.01216670559002552</v>
-      </c>
-      <c r="K7" s="13" t="n"/>
-      <c r="L7" s="13" t="n"/>
-      <c r="M7" s="31" t="n">
-        <v>-0.0469125</v>
-      </c>
-    </row>
-    <row r="9">
-      <c r="A9" s="12" t="inlineStr">
-        <is>
-          <t>WEEKLY returns (% of capital at start of that week; weeks split at month edges)</t>
-        </is>
-      </c>
-    </row>
-    <row r="10">
-      <c r="A10" s="2" t="inlineStr">
-        <is>
-          <t>Month</t>
-        </is>
-      </c>
-      <c r="B10" s="2" t="inlineStr">
-        <is>
-          <t>W1</t>
-        </is>
-      </c>
-      <c r="C10" s="2" t="inlineStr">
-        <is>
-          <t>W2</t>
-        </is>
-      </c>
-      <c r="D10" s="2" t="inlineStr">
-        <is>
-          <t>W3</t>
-        </is>
-      </c>
-      <c r="E10" s="2" t="inlineStr">
-        <is>
-          <t>W4</t>
-        </is>
-      </c>
-      <c r="F10" s="2" t="inlineStr">
-        <is>
-          <t>W5</t>
-        </is>
-      </c>
-      <c r="G10" s="2" t="inlineStr">
-        <is>
-          <t>W6</t>
-        </is>
-      </c>
-      <c r="H10" s="2" t="inlineStr">
-        <is>
-          <t>Month %</t>
-        </is>
-      </c>
-      <c r="I10" s="2" t="inlineStr">
-        <is>
-          <t>Month P&amp;L (Rs)</t>
-        </is>
-      </c>
-    </row>
-    <row r="11">
-      <c r="A11" s="3" t="inlineStr">
-        <is>
-          <t>2025-Dec</t>
-        </is>
-      </c>
-      <c r="B11" s="30" t="n">
-        <v>-0.010346</v>
-      </c>
-      <c r="C11" s="30" t="n">
-        <v>-0.0369487719950609</v>
-      </c>
-      <c r="D11" s="13" t="n"/>
-      <c r="E11" s="13" t="n"/>
-      <c r="F11" s="13" t="n"/>
-      <c r="G11" s="13" t="n"/>
-      <c r="H11" s="33" t="n">
-        <v>-0.0469125</v>
-      </c>
-      <c r="I11" s="32" t="n">
-        <v>-938.25</v>
-      </c>
-    </row>
-    <row r="12">
-      <c r="A12" s="3" t="inlineStr">
-        <is>
-          <t>2026-Jan</t>
-        </is>
-      </c>
-      <c r="B12" s="30" t="n">
-        <v>-0.01505685469592246</v>
-      </c>
-      <c r="C12" s="13" t="n"/>
-      <c r="D12" s="13" t="n"/>
-      <c r="E12" s="13" t="n"/>
-      <c r="F12" s="13" t="n"/>
-      <c r="G12" s="13" t="n"/>
-      <c r="H12" s="33" t="n">
-        <v>-0.01505685469592246</v>
-      </c>
-      <c r="I12" s="32" t="n">
-        <v>-287.01</v>
-      </c>
-    </row>
-    <row r="13">
-      <c r="A13" s="3" t="inlineStr">
-        <is>
-          <t>2026-Apr</t>
-        </is>
-      </c>
-      <c r="B13" s="14" t="n">
-        <v>0.01262227865738753</v>
-      </c>
-      <c r="C13" s="13" t="n"/>
-      <c r="D13" s="13" t="n"/>
-      <c r="E13" s="13" t="n"/>
-      <c r="F13" s="13" t="n"/>
-      <c r="G13" s="13" t="n"/>
-      <c r="H13" s="17" t="n">
-        <v>0.01262227865738753</v>
-      </c>
-      <c r="I13" s="16" t="n">
-        <v>236.98</v>
-      </c>
-    </row>
-    <row r="14">
-      <c r="A14" s="3" t="inlineStr">
-        <is>
-          <t>2026-Sep</t>
-        </is>
-      </c>
-      <c r="B14" s="30" t="n">
-        <v>-0.01216670559002552</v>
-      </c>
-      <c r="C14" s="13" t="n"/>
-      <c r="D14" s="13" t="n"/>
-      <c r="E14" s="13" t="n"/>
-      <c r="F14" s="13" t="n"/>
-      <c r="G14" s="13" t="n"/>
-      <c r="H14" s="33" t="n">
-        <v>-0.01216670559002552</v>
-      </c>
-      <c r="I14" s="32" t="n">
-        <v>-231.31</v>
-      </c>
-    </row>
-    <row r="16">
-      <c r="A16" s="12" t="inlineStr">
-        <is>
-          <t>DAILY returns (% of capital at start of that day; blank = no trade that day)</t>
-        </is>
-      </c>
-    </row>
-    <row r="17">
-      <c r="A17" s="2" t="inlineStr">
-        <is>
-          <t>Week starting (Mon)</t>
-        </is>
-      </c>
-      <c r="B17" s="2" t="inlineStr">
-        <is>
-          <t>Mon</t>
-        </is>
-      </c>
-      <c r="C17" s="2" t="inlineStr">
-        <is>
-          <t>Tue</t>
-        </is>
-      </c>
-      <c r="D17" s="2" t="inlineStr">
-        <is>
-          <t>Wed</t>
-        </is>
-      </c>
-      <c r="E17" s="2" t="inlineStr">
-        <is>
-          <t>Thu</t>
-        </is>
-      </c>
-      <c r="F17" s="2" t="inlineStr">
-        <is>
-          <t>Fri</t>
-        </is>
-      </c>
-      <c r="G17" s="2" t="inlineStr">
-        <is>
-          <t>Week %</t>
-        </is>
-      </c>
-      <c r="H17" s="2" t="inlineStr">
-        <is>
-          <t>Week P&amp;L (Rs)</t>
-        </is>
-      </c>
-    </row>
-    <row r="18">
-      <c r="A18" s="3" t="inlineStr">
-        <is>
-          <t>01-Dec-2025</t>
-        </is>
-      </c>
-      <c r="B18" s="13" t="n"/>
-      <c r="C18" s="30" t="n">
-        <v>-0.010346</v>
-      </c>
-      <c r="D18" s="13" t="n"/>
-      <c r="E18" s="13" t="n"/>
-      <c r="F18" s="13" t="n"/>
-      <c r="G18" s="33" t="n">
-        <v>-0.010346</v>
-      </c>
-      <c r="H18" s="32" t="n">
-        <v>-206.92</v>
-      </c>
-    </row>
-    <row r="19">
-      <c r="A19" s="3" t="inlineStr">
-        <is>
-          <t>08-Dec-2025</t>
-        </is>
-      </c>
-      <c r="B19" s="13" t="n"/>
-      <c r="C19" s="30" t="n">
-        <v>-0.0369487719950609</v>
-      </c>
-      <c r="D19" s="13" t="n"/>
-      <c r="E19" s="13" t="n"/>
-      <c r="F19" s="13" t="n"/>
-      <c r="G19" s="33" t="n">
-        <v>-0.0369487719950609</v>
-      </c>
-      <c r="H19" s="32" t="n">
-        <v>-731.33</v>
-      </c>
-    </row>
-    <row r="20">
-      <c r="A20" s="3" t="inlineStr">
-        <is>
-          <t>26-Jan-2026</t>
-        </is>
-      </c>
-      <c r="B20" s="13" t="n"/>
-      <c r="C20" s="30" t="n">
-        <v>-0.01505685469592246</v>
-      </c>
-      <c r="D20" s="13" t="n"/>
-      <c r="E20" s="13" t="n"/>
-      <c r="F20" s="13" t="n"/>
-      <c r="G20" s="33" t="n">
-        <v>-0.01505685469592246</v>
-      </c>
-      <c r="H20" s="32" t="n">
-        <v>-287.01</v>
-      </c>
-    </row>
-    <row r="21">
-      <c r="A21" s="3" t="inlineStr">
-        <is>
-          <t>06-Apr-2026</t>
-        </is>
-      </c>
-      <c r="B21" s="13" t="n"/>
-      <c r="C21" s="14" t="n">
-        <v>0.01262227865738753</v>
-      </c>
-      <c r="D21" s="13" t="n"/>
-      <c r="E21" s="13" t="n"/>
-      <c r="F21" s="13" t="n"/>
-      <c r="G21" s="17" t="n">
-        <v>0.01262227865738753</v>
-      </c>
-      <c r="H21" s="16" t="n">
-        <v>236.98</v>
-      </c>
-    </row>
-    <row r="22">
-      <c r="A22" s="3" t="inlineStr">
-        <is>
-          <t>07-Sep-2026</t>
-        </is>
-      </c>
-      <c r="B22" s="13" t="n"/>
-      <c r="C22" s="30" t="n">
-        <v>-0.01216670559002552</v>
-      </c>
-      <c r="D22" s="13" t="n"/>
-      <c r="E22" s="13" t="n"/>
-      <c r="F22" s="13" t="n"/>
-      <c r="G22" s="33" t="n">
-        <v>-0.01216670559002552</v>
-      </c>
-      <c r="H22" s="32" t="n">
-        <v>-231.31</v>
-      </c>
-    </row>
-    <row r="24">
-      <c r="A24" s="12" t="inlineStr">
-        <is>
-          <t>STATISTICS (all trades for this index)</t>
-        </is>
-      </c>
-    </row>
-    <row r="25">
-      <c r="A25" s="3" t="inlineStr">
-        <is>
-          <t>All trades</t>
-        </is>
-      </c>
-      <c r="B25" s="18" t="n">
-        <v>7</v>
-      </c>
-      <c r="C25" s="19" t="n"/>
-      <c r="D25" s="20" t="n"/>
-    </row>
-    <row r="26">
-      <c r="A26" s="3" t="inlineStr">
-        <is>
-          <t>Winners</t>
-        </is>
-      </c>
-      <c r="B26" s="21" t="inlineStr">
-        <is>
-          <t>1 (14.3%)</t>
-        </is>
-      </c>
-      <c r="C26" s="19" t="n"/>
-      <c r="D26" s="20" t="n"/>
-    </row>
-    <row r="27">
-      <c r="A27" s="3" t="inlineStr">
-        <is>
-          <t>Losers</t>
-        </is>
-      </c>
-      <c r="B27" s="21" t="inlineStr">
-        <is>
-          <t>6 (85.7%)</t>
-        </is>
-      </c>
-      <c r="C27" s="19" t="n"/>
-      <c r="D27" s="20" t="n"/>
-    </row>
-    <row r="28">
-      <c r="A28" s="3" t="inlineStr">
-        <is>
-          <t>Net P&amp;L (Rs)</t>
-        </is>
-      </c>
-      <c r="B28" s="23" t="n">
-        <v>-1219.59</v>
-      </c>
-      <c r="C28" s="19" t="n"/>
-      <c r="D28" s="20" t="n"/>
-    </row>
-    <row r="29">
-      <c r="A29" s="3" t="inlineStr">
-        <is>
-          <t>Total Profit (Rs)</t>
-        </is>
-      </c>
-      <c r="B29" s="22" t="n">
-        <v>236.98</v>
-      </c>
-      <c r="C29" s="19" t="n"/>
-      <c r="D29" s="20" t="n"/>
-    </row>
-    <row r="30">
-      <c r="A30" s="3" t="inlineStr">
-        <is>
-          <t>Total Loss (Rs)</t>
-        </is>
-      </c>
-      <c r="B30" s="23" t="n">
-        <v>-1456.57</v>
-      </c>
-      <c r="C30" s="19" t="n"/>
-      <c r="D30" s="20" t="n"/>
-    </row>
-    <row r="31">
-      <c r="A31" s="3" t="inlineStr">
-        <is>
-          <t>Transaction costs (Rs)</t>
-        </is>
-      </c>
-      <c r="B31" s="24" t="n">
-        <v>348.39</v>
-      </c>
-      <c r="C31" s="19" t="n"/>
-      <c r="D31" s="20" t="n"/>
-    </row>
-    <row r="32">
-      <c r="A32" s="3" t="inlineStr">
-        <is>
-          <t>Avg Profit/Loss per trade (Rs)</t>
-        </is>
-      </c>
-      <c r="B32" s="23" t="n">
-        <v>-174.23</v>
-      </c>
-      <c r="C32" s="19" t="n"/>
-      <c r="D32" s="20" t="n"/>
-    </row>
-    <row r="33">
-      <c r="A33" s="3" t="inlineStr">
-        <is>
-          <t>Avg Profit/Loss per trade (% of premium)</t>
-        </is>
-      </c>
-      <c r="B33" s="25" t="n">
-        <v>-10.42</v>
-      </c>
-      <c r="C33" s="19" t="n"/>
-      <c r="D33" s="20" t="n"/>
-    </row>
-    <row r="34">
-      <c r="A34" s="3" t="inlineStr">
-        <is>
-          <t>Avg Win (Rs)</t>
-        </is>
-      </c>
-      <c r="B34" s="22" t="n">
-        <v>236.98</v>
-      </c>
-      <c r="C34" s="19" t="n"/>
-      <c r="D34" s="20" t="n"/>
-    </row>
-    <row r="35">
-      <c r="A35" s="3" t="inlineStr">
-        <is>
-          <t>Avg Win (% of premium)</t>
-        </is>
-      </c>
-      <c r="B35" s="26" t="n">
-        <v>16.17</v>
-      </c>
-      <c r="C35" s="19" t="n"/>
-      <c r="D35" s="20" t="n"/>
-    </row>
-    <row r="36">
-      <c r="A36" s="3" t="inlineStr">
-        <is>
-          <t>Avg Loss (Rs)</t>
-        </is>
-      </c>
-      <c r="B36" s="23" t="n">
-        <v>-242.76</v>
-      </c>
-      <c r="C36" s="19" t="n"/>
-      <c r="D36" s="20" t="n"/>
-    </row>
-    <row r="37">
-      <c r="A37" s="3" t="inlineStr">
-        <is>
-          <t>Avg Loss (% of premium)</t>
-        </is>
-      </c>
-      <c r="B37" s="27" t="n">
-        <v>-14.85</v>
-      </c>
-      <c r="C37" s="19" t="n"/>
-      <c r="D37" s="20" t="n"/>
-    </row>
-    <row r="38">
-      <c r="A38" s="3" t="inlineStr">
-        <is>
-          <t>Largest Win (Rs)</t>
-        </is>
-      </c>
-      <c r="B38" s="22" t="n">
-        <v>236.98</v>
-      </c>
-      <c r="C38" s="19" t="n"/>
-      <c r="D38" s="20" t="n"/>
-    </row>
-    <row r="39">
-      <c r="A39" s="3" t="inlineStr">
-        <is>
-          <t>Largest Loss (Rs)</t>
-        </is>
-      </c>
-      <c r="B39" s="23" t="n">
-        <v>-295.95</v>
-      </c>
-      <c r="C39" s="19" t="n"/>
-      <c r="D39" s="20" t="n"/>
-    </row>
-    <row r="40">
-      <c r="A40" s="3" t="inlineStr">
-        <is>
-          <t>Max Consecutive Wins</t>
-        </is>
-      </c>
-      <c r="B40" s="18" t="n">
-        <v>1</v>
-      </c>
-      <c r="C40" s="19" t="n"/>
-      <c r="D40" s="20" t="n"/>
-    </row>
-    <row r="41">
-      <c r="A41" s="3" t="inlineStr">
-        <is>
-          <t>Max Consecutive Losses</t>
-        </is>
-      </c>
-      <c r="B41" s="18" t="n">
-        <v>5</v>
-      </c>
-      <c r="C41" s="19" t="n"/>
-      <c r="D41" s="20" t="n"/>
-    </row>
-    <row r="42">
-      <c r="A42" s="3" t="inlineStr">
-        <is>
-          <t>Max trade drawdown (Rs)</t>
-        </is>
-      </c>
-      <c r="B42" s="23" t="n">
-        <v>-295.95</v>
-      </c>
-      <c r="C42" s="19" t="n"/>
-      <c r="D42" s="20" t="n"/>
-    </row>
-    <row r="43">
-      <c r="A43" s="3" t="inlineStr">
-        <is>
-          <t>Max system drawdown (Rs)</t>
-        </is>
-      </c>
-      <c r="B43" s="23" t="n">
-        <v>-1225.26</v>
-      </c>
-      <c r="C43" s="19" t="n"/>
-      <c r="D43" s="20" t="n"/>
-    </row>
-    <row r="44">
-      <c r="A44" s="3" t="inlineStr">
-        <is>
-          <t>Max system drawdown (%)</t>
-        </is>
-      </c>
-      <c r="B44" s="27" t="n">
-        <v>-6.13</v>
-      </c>
-      <c r="C44" s="19" t="n"/>
-      <c r="D44" s="20" t="n"/>
-    </row>
-    <row r="45">
-      <c r="A45" s="3" t="inlineStr">
-        <is>
-          <t>Recovery Factor</t>
-        </is>
-      </c>
-      <c r="B45" s="28" t="n">
-        <v>-1</v>
-      </c>
-      <c r="C45" s="19" t="n"/>
-      <c r="D45" s="20" t="n"/>
-    </row>
-    <row r="46">
-      <c r="A46" s="3" t="inlineStr">
-        <is>
-          <t>Profit Factor</t>
-        </is>
-      </c>
-      <c r="B46" s="28" t="n">
-        <v>0.16</v>
-      </c>
-      <c r="C46" s="19" t="n"/>
-      <c r="D46" s="20" t="n"/>
-    </row>
-    <row r="47">
-      <c r="A47" s="3" t="inlineStr">
-        <is>
-          <t>Payoff Ratio (avg win / avg loss)</t>
-        </is>
-      </c>
-      <c r="B47" s="28" t="n">
-        <v>0.98</v>
-      </c>
-      <c r="C47" s="19" t="n"/>
-      <c r="D47" s="20" t="n"/>
-    </row>
-    <row r="48">
-      <c r="A48" s="3" t="inlineStr">
-        <is>
-          <t>Sharpe Ratio (annualized)</t>
-        </is>
-      </c>
-      <c r="B48" s="28" t="n">
-        <v>-12.48</v>
-      </c>
-      <c r="C48" s="19" t="n"/>
-      <c r="D48" s="20" t="n"/>
-    </row>
-    <row r="50">
-      <c r="A50" s="11" t="inlineStr">
-        <is>
-          <t>Caveat: with only a handful of trades these numbers (Sharpe, profit factor, drawdown %) are not statistically reliable. Watch this over weeks/months before drawing conclusions.</t>
-        </is>
-      </c>
-    </row>
-  </sheetData>
-  <mergeCells count="24">
-    <mergeCell ref="B42:D42"/>
-    <mergeCell ref="B44:D44"/>
-    <mergeCell ref="B29:D29"/>
-    <mergeCell ref="B38:D38"/>
-    <mergeCell ref="B34:D34"/>
-    <mergeCell ref="B28:D28"/>
-    <mergeCell ref="B37:D37"/>
-    <mergeCell ref="B40:D40"/>
-    <mergeCell ref="B30:D30"/>
-    <mergeCell ref="B33:D33"/>
-    <mergeCell ref="B36:D36"/>
-    <mergeCell ref="B45:D45"/>
-    <mergeCell ref="B41:D41"/>
-    <mergeCell ref="B32:D32"/>
-    <mergeCell ref="B35:D35"/>
-    <mergeCell ref="B26:D26"/>
-    <mergeCell ref="B25:D25"/>
-    <mergeCell ref="B47:D47"/>
-    <mergeCell ref="B31:D31"/>
-    <mergeCell ref="B46:D46"/>
-    <mergeCell ref="B27:D27"/>
-    <mergeCell ref="B43:D43"/>
-    <mergeCell ref="B39:D39"/>
-    <mergeCell ref="B48:D48"/>
-  </mergeCells>
-  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
-  <pageSetup orientation="landscape" fitToHeight="0" fitToWidth="1"/>
-</worksheet>
 </file>
--- a/reports/dashboard.xlsx
+++ b/reports/dashboard.xlsx
@@ -12,6 +12,11 @@
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="BANKNIFTY" sheetId="3" state="visible" r:id="rId3"/>
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="FINNIFTY" sheetId="4" state="visible" r:id="rId4"/>
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="ALL INDICES" sheetId="5" state="visible" r:id="rId5"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="BT-Summary" sheetId="6" state="visible" r:id="rId6"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="BT-NIFTY" sheetId="7" state="visible" r:id="rId7"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="BT-BANKNIFTY" sheetId="8" state="visible" r:id="rId8"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="BT-FINNIFTY" sheetId="9" state="visible" r:id="rId9"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="BT-ALL INDICES" sheetId="10" state="visible" r:id="rId10"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -26,7 +31,7 @@
     <numFmt numFmtId="166" formatCode="#,##0;-#,##0"/>
     <numFmt numFmtId="167" formatCode="0.00&quot;%&quot;"/>
   </numFmts>
-  <fonts count="9">
+  <fonts count="10">
     <font>
       <name val="Calibri"/>
       <family val="2"/>
@@ -70,8 +75,13 @@
       <name val="Arial"/>
       <color rgb="00C00000"/>
     </font>
+    <font>
+      <name val="Arial"/>
+      <b val="1"/>
+      <color rgb="00C00000"/>
+    </font>
   </fonts>
-  <fills count="4">
+  <fills count="5">
     <fill>
       <patternFill/>
     </fill>
@@ -88,6 +98,12 @@
       <patternFill patternType="solid">
         <fgColor rgb="00E6F4EA"/>
         <bgColor rgb="00E6F4EA"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="00FDE8E8"/>
+        <bgColor rgb="00FDE8E8"/>
       </patternFill>
     </fill>
   </fills>
@@ -161,7 +177,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="29">
+  <cellXfs count="33">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="2" fillId="2" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
@@ -211,6 +227,10 @@
     <xf numFmtId="2" fontId="4" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="right"/>
     </xf>
+    <xf numFmtId="164" fontId="8" fillId="4" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="164" fontId="8" fillId="0" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="164" fontId="9" fillId="4" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="166" fontId="8" fillId="0" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0" hidden="0"/>
@@ -765,6 +785,741 @@
 </worksheet>
 </file>
 
+<file path=xl/worksheets/sheet10.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr fitToPage="1"/>
+  </sheetPr>
+  <dimension ref="A1:O46"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <cols>
+    <col width="40" customWidth="1" min="1" max="1"/>
+    <col width="10" customWidth="1" min="2" max="2"/>
+    <col width="10" customWidth="1" min="3" max="3"/>
+    <col width="10" customWidth="1" min="4" max="4"/>
+    <col width="10" customWidth="1" min="5" max="5"/>
+    <col width="10" customWidth="1" min="6" max="6"/>
+    <col width="10" customWidth="1" min="7" max="7"/>
+    <col width="15" customWidth="1" min="8" max="8"/>
+    <col width="15" customWidth="1" min="9" max="9"/>
+    <col width="10" customWidth="1" min="10" max="10"/>
+    <col width="10" customWidth="1" min="11" max="11"/>
+    <col width="10" customWidth="1" min="12" max="12"/>
+    <col width="10" customWidth="1" min="13" max="13"/>
+    <col width="10" customWidth="1" min="14" max="14"/>
+    <col width="15" customWidth="1" min="15" max="15"/>
+  </cols>
+  <sheetData>
+    <row r="1">
+      <c r="A1" s="1" t="inlineStr">
+        <is>
+          <t>BACKTEST ALL INDICES -- PAPER TRADE, NOT REAL MONEY</t>
+        </is>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" s="12" t="inlineStr">
+        <is>
+          <t>MONTHLY returns (% of capital at start of month)</t>
+        </is>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" s="2" t="inlineStr">
+        <is>
+          <t>Year</t>
+        </is>
+      </c>
+      <c r="B4" s="2" t="inlineStr">
+        <is>
+          <t>Jan</t>
+        </is>
+      </c>
+      <c r="C4" s="2" t="inlineStr">
+        <is>
+          <t>Feb</t>
+        </is>
+      </c>
+      <c r="D4" s="2" t="inlineStr">
+        <is>
+          <t>Mar</t>
+        </is>
+      </c>
+      <c r="E4" s="2" t="inlineStr">
+        <is>
+          <t>Apr</t>
+        </is>
+      </c>
+      <c r="F4" s="2" t="inlineStr">
+        <is>
+          <t>May</t>
+        </is>
+      </c>
+      <c r="G4" s="2" t="inlineStr">
+        <is>
+          <t>Jun</t>
+        </is>
+      </c>
+      <c r="H4" s="2" t="inlineStr">
+        <is>
+          <t>Jul</t>
+        </is>
+      </c>
+      <c r="I4" s="2" t="inlineStr">
+        <is>
+          <t>Aug</t>
+        </is>
+      </c>
+      <c r="J4" s="2" t="inlineStr">
+        <is>
+          <t>Sep</t>
+        </is>
+      </c>
+      <c r="K4" s="2" t="inlineStr">
+        <is>
+          <t>Oct</t>
+        </is>
+      </c>
+      <c r="L4" s="2" t="inlineStr">
+        <is>
+          <t>Nov</t>
+        </is>
+      </c>
+      <c r="M4" s="2" t="inlineStr">
+        <is>
+          <t>Dec</t>
+        </is>
+      </c>
+      <c r="N4" s="2" t="inlineStr">
+        <is>
+          <t>Yr %</t>
+        </is>
+      </c>
+      <c r="O4" s="2" t="inlineStr">
+        <is>
+          <t>Yr P&amp;L (Rs)</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" s="3" t="n">
+        <v>2026</v>
+      </c>
+      <c r="B5" s="13" t="n"/>
+      <c r="C5" s="13" t="n"/>
+      <c r="D5" s="29" t="n">
+        <v>-0.003766999999999999</v>
+      </c>
+      <c r="E5" s="13" t="n"/>
+      <c r="F5" s="14" t="n">
+        <v>0.02750410797474085</v>
+      </c>
+      <c r="G5" s="13" t="n"/>
+      <c r="H5" s="13" t="n"/>
+      <c r="I5" s="13" t="n"/>
+      <c r="J5" s="13" t="n"/>
+      <c r="K5" s="29" t="n">
+        <v>-0.009550293146912445</v>
+      </c>
+      <c r="L5" s="13" t="n"/>
+      <c r="M5" s="13" t="n"/>
+      <c r="N5" s="15" t="n">
+        <v>0.01385750000000008</v>
+      </c>
+      <c r="O5" s="16" t="n">
+        <v>277.15</v>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" s="3" t="inlineStr">
+        <is>
+          <t>Avg</t>
+        </is>
+      </c>
+      <c r="B6" s="13" t="n"/>
+      <c r="C6" s="13" t="n"/>
+      <c r="D6" s="30" t="n">
+        <v>-0.003766999999999999</v>
+      </c>
+      <c r="E6" s="13" t="n"/>
+      <c r="F6" s="15" t="n">
+        <v>0.02750410797474085</v>
+      </c>
+      <c r="G6" s="13" t="n"/>
+      <c r="H6" s="13" t="n"/>
+      <c r="I6" s="13" t="n"/>
+      <c r="J6" s="13" t="n"/>
+      <c r="K6" s="30" t="n">
+        <v>-0.009550293146912445</v>
+      </c>
+      <c r="L6" s="13" t="n"/>
+      <c r="M6" s="13" t="n"/>
+    </row>
+    <row r="8">
+      <c r="A8" s="12" t="inlineStr">
+        <is>
+          <t>WEEKLY returns (% of capital at start of that week; weeks split at month edges)</t>
+        </is>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" s="2" t="inlineStr">
+        <is>
+          <t>Month</t>
+        </is>
+      </c>
+      <c r="B9" s="2" t="inlineStr">
+        <is>
+          <t>W1</t>
+        </is>
+      </c>
+      <c r="C9" s="2" t="inlineStr">
+        <is>
+          <t>W2</t>
+        </is>
+      </c>
+      <c r="D9" s="2" t="inlineStr">
+        <is>
+          <t>W3</t>
+        </is>
+      </c>
+      <c r="E9" s="2" t="inlineStr">
+        <is>
+          <t>W4</t>
+        </is>
+      </c>
+      <c r="F9" s="2" t="inlineStr">
+        <is>
+          <t>W5</t>
+        </is>
+      </c>
+      <c r="G9" s="2" t="inlineStr">
+        <is>
+          <t>W6</t>
+        </is>
+      </c>
+      <c r="H9" s="2" t="inlineStr">
+        <is>
+          <t>Month %</t>
+        </is>
+      </c>
+      <c r="I9" s="2" t="inlineStr">
+        <is>
+          <t>Month P&amp;L (Rs)</t>
+        </is>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" s="3" t="inlineStr">
+        <is>
+          <t>2026-Mar</t>
+        </is>
+      </c>
+      <c r="B10" s="29" t="n">
+        <v>-0.003766999999999999</v>
+      </c>
+      <c r="C10" s="13" t="n"/>
+      <c r="D10" s="13" t="n"/>
+      <c r="E10" s="13" t="n"/>
+      <c r="F10" s="13" t="n"/>
+      <c r="G10" s="13" t="n"/>
+      <c r="H10" s="31" t="n">
+        <v>-0.003766999999999999</v>
+      </c>
+      <c r="I10" s="32" t="n">
+        <v>-75.34</v>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" s="3" t="inlineStr">
+        <is>
+          <t>2026-May</t>
+        </is>
+      </c>
+      <c r="B11" s="14" t="n">
+        <v>0.02750410797474085</v>
+      </c>
+      <c r="C11" s="13" t="n"/>
+      <c r="D11" s="13" t="n"/>
+      <c r="E11" s="13" t="n"/>
+      <c r="F11" s="13" t="n"/>
+      <c r="G11" s="13" t="n"/>
+      <c r="H11" s="17" t="n">
+        <v>0.02750410797474085</v>
+      </c>
+      <c r="I11" s="16" t="n">
+        <v>548.01</v>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" s="3" t="inlineStr">
+        <is>
+          <t>2026-Oct</t>
+        </is>
+      </c>
+      <c r="B12" s="29" t="n">
+        <v>-0.009550293146912445</v>
+      </c>
+      <c r="C12" s="13" t="n"/>
+      <c r="D12" s="13" t="n"/>
+      <c r="E12" s="13" t="n"/>
+      <c r="F12" s="13" t="n"/>
+      <c r="G12" s="13" t="n"/>
+      <c r="H12" s="31" t="n">
+        <v>-0.009550293146912445</v>
+      </c>
+      <c r="I12" s="32" t="n">
+        <v>-195.52</v>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" s="12" t="inlineStr">
+        <is>
+          <t>DAILY returns (% of capital at start of that day; blank = no trade that day)</t>
+        </is>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" s="2" t="inlineStr">
+        <is>
+          <t>Week starting (Mon)</t>
+        </is>
+      </c>
+      <c r="B15" s="2" t="inlineStr">
+        <is>
+          <t>Mon</t>
+        </is>
+      </c>
+      <c r="C15" s="2" t="inlineStr">
+        <is>
+          <t>Tue</t>
+        </is>
+      </c>
+      <c r="D15" s="2" t="inlineStr">
+        <is>
+          <t>Wed</t>
+        </is>
+      </c>
+      <c r="E15" s="2" t="inlineStr">
+        <is>
+          <t>Thu</t>
+        </is>
+      </c>
+      <c r="F15" s="2" t="inlineStr">
+        <is>
+          <t>Fri</t>
+        </is>
+      </c>
+      <c r="G15" s="2" t="inlineStr">
+        <is>
+          <t>Week %</t>
+        </is>
+      </c>
+      <c r="H15" s="2" t="inlineStr">
+        <is>
+          <t>Week P&amp;L (Rs)</t>
+        </is>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" s="3" t="inlineStr">
+        <is>
+          <t>23-Mar-2026</t>
+        </is>
+      </c>
+      <c r="B16" s="13" t="n"/>
+      <c r="C16" s="29" t="n">
+        <v>-0.003766999999999999</v>
+      </c>
+      <c r="D16" s="13" t="n"/>
+      <c r="E16" s="13" t="n"/>
+      <c r="F16" s="13" t="n"/>
+      <c r="G16" s="31" t="n">
+        <v>-0.003766999999999999</v>
+      </c>
+      <c r="H16" s="32" t="n">
+        <v>-75.34</v>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" s="3" t="inlineStr">
+        <is>
+          <t>11-May-2026</t>
+        </is>
+      </c>
+      <c r="B17" s="13" t="n"/>
+      <c r="C17" s="14" t="n">
+        <v>0.02750410797474085</v>
+      </c>
+      <c r="D17" s="13" t="n"/>
+      <c r="E17" s="13" t="n"/>
+      <c r="F17" s="13" t="n"/>
+      <c r="G17" s="17" t="n">
+        <v>0.02750410797474085</v>
+      </c>
+      <c r="H17" s="16" t="n">
+        <v>548.01</v>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" s="3" t="inlineStr">
+        <is>
+          <t>12-Oct-2026</t>
+        </is>
+      </c>
+      <c r="B18" s="13" t="n"/>
+      <c r="C18" s="29" t="n">
+        <v>-0.009550293146912445</v>
+      </c>
+      <c r="D18" s="13" t="n"/>
+      <c r="E18" s="13" t="n"/>
+      <c r="F18" s="13" t="n"/>
+      <c r="G18" s="31" t="n">
+        <v>-0.009550293146912445</v>
+      </c>
+      <c r="H18" s="32" t="n">
+        <v>-195.52</v>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" s="12" t="inlineStr">
+        <is>
+          <t>STATISTICS (all trades for this index)</t>
+        </is>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" s="3" t="inlineStr">
+        <is>
+          <t>All trades</t>
+        </is>
+      </c>
+      <c r="B21" s="18" t="n">
+        <v>5</v>
+      </c>
+      <c r="C21" s="19" t="n"/>
+      <c r="D21" s="20" t="n"/>
+    </row>
+    <row r="22">
+      <c r="A22" s="3" t="inlineStr">
+        <is>
+          <t>Winners</t>
+        </is>
+      </c>
+      <c r="B22" s="21" t="inlineStr">
+        <is>
+          <t>2 (40.0%)</t>
+        </is>
+      </c>
+      <c r="C22" s="19" t="n"/>
+      <c r="D22" s="20" t="n"/>
+    </row>
+    <row r="23">
+      <c r="A23" s="3" t="inlineStr">
+        <is>
+          <t>Losers</t>
+        </is>
+      </c>
+      <c r="B23" s="21" t="inlineStr">
+        <is>
+          <t>3 (60.0%)</t>
+        </is>
+      </c>
+      <c r="C23" s="19" t="n"/>
+      <c r="D23" s="20" t="n"/>
+    </row>
+    <row r="24">
+      <c r="A24" s="3" t="inlineStr">
+        <is>
+          <t>Net P&amp;L (Rs)</t>
+        </is>
+      </c>
+      <c r="B24" s="22" t="n">
+        <v>277.15</v>
+      </c>
+      <c r="C24" s="19" t="n"/>
+      <c r="D24" s="20" t="n"/>
+    </row>
+    <row r="25">
+      <c r="A25" s="3" t="inlineStr">
+        <is>
+          <t>Total Profit (Rs)</t>
+        </is>
+      </c>
+      <c r="B25" s="22" t="n">
+        <v>1040.37</v>
+      </c>
+      <c r="C25" s="19" t="n"/>
+      <c r="D25" s="20" t="n"/>
+    </row>
+    <row r="26">
+      <c r="A26" s="3" t="inlineStr">
+        <is>
+          <t>Total Loss (Rs)</t>
+        </is>
+      </c>
+      <c r="B26" s="23" t="n">
+        <v>-763.22</v>
+      </c>
+      <c r="C26" s="19" t="n"/>
+      <c r="D26" s="20" t="n"/>
+    </row>
+    <row r="27">
+      <c r="A27" s="3" t="inlineStr">
+        <is>
+          <t>Transaction costs (Rs)</t>
+        </is>
+      </c>
+      <c r="B27" s="24" t="n">
+        <v>143.6</v>
+      </c>
+      <c r="C27" s="19" t="n"/>
+      <c r="D27" s="20" t="n"/>
+    </row>
+    <row r="28">
+      <c r="A28" s="3" t="inlineStr">
+        <is>
+          <t>Avg Profit/Loss per trade (Rs)</t>
+        </is>
+      </c>
+      <c r="B28" s="22" t="n">
+        <v>55.43</v>
+      </c>
+      <c r="C28" s="19" t="n"/>
+      <c r="D28" s="20" t="n"/>
+    </row>
+    <row r="29">
+      <c r="A29" s="3" t="inlineStr">
+        <is>
+          <t>Avg Profit/Loss per trade (% of premium)</t>
+        </is>
+      </c>
+      <c r="B29" s="25" t="n">
+        <v>2.6</v>
+      </c>
+      <c r="C29" s="19" t="n"/>
+      <c r="D29" s="20" t="n"/>
+    </row>
+    <row r="30">
+      <c r="A30" s="3" t="inlineStr">
+        <is>
+          <t>Avg Win (Rs)</t>
+        </is>
+      </c>
+      <c r="B30" s="22" t="n">
+        <v>520.1799999999999</v>
+      </c>
+      <c r="C30" s="19" t="n"/>
+      <c r="D30" s="20" t="n"/>
+    </row>
+    <row r="31">
+      <c r="A31" s="3" t="inlineStr">
+        <is>
+          <t>Avg Win (% of premium)</t>
+        </is>
+      </c>
+      <c r="B31" s="26" t="n">
+        <v>54.92</v>
+      </c>
+      <c r="C31" s="19" t="n"/>
+      <c r="D31" s="20" t="n"/>
+    </row>
+    <row r="32">
+      <c r="A32" s="3" t="inlineStr">
+        <is>
+          <t>Avg Loss (Rs)</t>
+        </is>
+      </c>
+      <c r="B32" s="23" t="n">
+        <v>-254.41</v>
+      </c>
+      <c r="C32" s="19" t="n"/>
+      <c r="D32" s="20" t="n"/>
+    </row>
+    <row r="33">
+      <c r="A33" s="3" t="inlineStr">
+        <is>
+          <t>Avg Loss (% of premium)</t>
+        </is>
+      </c>
+      <c r="B33" s="27" t="n">
+        <v>-32.27</v>
+      </c>
+      <c r="C33" s="19" t="n"/>
+      <c r="D33" s="20" t="n"/>
+    </row>
+    <row r="34">
+      <c r="A34" s="3" t="inlineStr">
+        <is>
+          <t>Largest Win (Rs)</t>
+        </is>
+      </c>
+      <c r="B34" s="22" t="n">
+        <v>548.01</v>
+      </c>
+      <c r="C34" s="19" t="n"/>
+      <c r="D34" s="20" t="n"/>
+    </row>
+    <row r="35">
+      <c r="A35" s="3" t="inlineStr">
+        <is>
+          <t>Largest Loss (Rs)</t>
+        </is>
+      </c>
+      <c r="B35" s="23" t="n">
+        <v>-299.45</v>
+      </c>
+      <c r="C35" s="19" t="n"/>
+      <c r="D35" s="20" t="n"/>
+    </row>
+    <row r="36">
+      <c r="A36" s="3" t="inlineStr">
+        <is>
+          <t>Max Consecutive Wins</t>
+        </is>
+      </c>
+      <c r="B36" s="18" t="n">
+        <v>1</v>
+      </c>
+      <c r="C36" s="19" t="n"/>
+      <c r="D36" s="20" t="n"/>
+    </row>
+    <row r="37">
+      <c r="A37" s="3" t="inlineStr">
+        <is>
+          <t>Max Consecutive Losses</t>
+        </is>
+      </c>
+      <c r="B37" s="18" t="n">
+        <v>1</v>
+      </c>
+      <c r="C37" s="19" t="n"/>
+      <c r="D37" s="20" t="n"/>
+    </row>
+    <row r="38">
+      <c r="A38" s="3" t="inlineStr">
+        <is>
+          <t>Max trade drawdown (Rs)</t>
+        </is>
+      </c>
+      <c r="B38" s="23" t="n">
+        <v>-299.45</v>
+      </c>
+      <c r="C38" s="19" t="n"/>
+      <c r="D38" s="20" t="n"/>
+    </row>
+    <row r="39">
+      <c r="A39" s="3" t="inlineStr">
+        <is>
+          <t>Max system drawdown (Rs)</t>
+        </is>
+      </c>
+      <c r="B39" s="23" t="n">
+        <v>-299.45</v>
+      </c>
+      <c r="C39" s="19" t="n"/>
+      <c r="D39" s="20" t="n"/>
+    </row>
+    <row r="40">
+      <c r="A40" s="3" t="inlineStr">
+        <is>
+          <t>Max system drawdown (%)</t>
+        </is>
+      </c>
+      <c r="B40" s="27" t="n">
+        <v>-1.48</v>
+      </c>
+      <c r="C40" s="19" t="n"/>
+      <c r="D40" s="20" t="n"/>
+    </row>
+    <row r="41">
+      <c r="A41" s="3" t="inlineStr">
+        <is>
+          <t>Recovery Factor</t>
+        </is>
+      </c>
+      <c r="B41" s="28" t="n">
+        <v>0.93</v>
+      </c>
+      <c r="C41" s="19" t="n"/>
+      <c r="D41" s="20" t="n"/>
+    </row>
+    <row r="42">
+      <c r="A42" s="3" t="inlineStr">
+        <is>
+          <t>Profit Factor</t>
+        </is>
+      </c>
+      <c r="B42" s="28" t="n">
+        <v>1.36</v>
+      </c>
+      <c r="C42" s="19" t="n"/>
+      <c r="D42" s="20" t="n"/>
+    </row>
+    <row r="43">
+      <c r="A43" s="3" t="inlineStr">
+        <is>
+          <t>Payoff Ratio (avg win / avg loss)</t>
+        </is>
+      </c>
+      <c r="B43" s="28" t="n">
+        <v>2.04</v>
+      </c>
+      <c r="C43" s="19" t="n"/>
+      <c r="D43" s="20" t="n"/>
+    </row>
+    <row r="44">
+      <c r="A44" s="3" t="inlineStr">
+        <is>
+          <t>Sharpe Ratio (annualized)</t>
+        </is>
+      </c>
+      <c r="B44" s="28" t="n">
+        <v>4.61</v>
+      </c>
+      <c r="C44" s="19" t="n"/>
+      <c r="D44" s="20" t="n"/>
+    </row>
+    <row r="46">
+      <c r="A46" s="11" t="inlineStr">
+        <is>
+          <t>Caveat: with only a handful of trades these numbers (Sharpe, profit factor, drawdown %) are not statistically reliable. Watch this over weeks/months before drawing conclusions.</t>
+        </is>
+      </c>
+    </row>
+  </sheetData>
+  <mergeCells count="24">
+    <mergeCell ref="B42:D42"/>
+    <mergeCell ref="B23:D23"/>
+    <mergeCell ref="B44:D44"/>
+    <mergeCell ref="B29:D29"/>
+    <mergeCell ref="B38:D38"/>
+    <mergeCell ref="B34:D34"/>
+    <mergeCell ref="B28:D28"/>
+    <mergeCell ref="B37:D37"/>
+    <mergeCell ref="B40:D40"/>
+    <mergeCell ref="B30:D30"/>
+    <mergeCell ref="B24:D24"/>
+    <mergeCell ref="B33:D33"/>
+    <mergeCell ref="B36:D36"/>
+    <mergeCell ref="B41:D41"/>
+    <mergeCell ref="B32:D32"/>
+    <mergeCell ref="B35:D35"/>
+    <mergeCell ref="B26:D26"/>
+    <mergeCell ref="B25:D25"/>
+    <mergeCell ref="B31:D31"/>
+    <mergeCell ref="B22:D22"/>
+    <mergeCell ref="B27:D27"/>
+    <mergeCell ref="B21:D21"/>
+    <mergeCell ref="B43:D43"/>
+    <mergeCell ref="B39:D39"/>
+  </mergeCells>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+  <pageSetup orientation="landscape" fitToHeight="0" fitToWidth="1"/>
+</worksheet>
+</file>
+
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr>
@@ -2149,4 +2904,1030 @@
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
   <pageSetup orientation="landscape" fitToHeight="0" fitToWidth="1"/>
 </worksheet>
+</file>
+
+<file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr fitToPage="1"/>
+  </sheetPr>
+  <dimension ref="A1:G9"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <cols>
+    <col width="15" customWidth="1" min="1" max="1"/>
+    <col width="22" customWidth="1" min="2" max="2"/>
+    <col width="15" customWidth="1" min="3" max="3"/>
+    <col width="15" customWidth="1" min="4" max="4"/>
+    <col width="15" customWidth="1" min="5" max="5"/>
+    <col width="15" customWidth="1" min="6" max="6"/>
+    <col width="15" customWidth="1" min="7" max="7"/>
+  </cols>
+  <sheetData>
+    <row r="1">
+      <c r="A1" s="1" t="inlineStr">
+        <is>
+          <t>BACKTEST summary by index (best strategy per index) -- PAPER TRADE, NOT REAL MONEY</t>
+        </is>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" s="2" t="inlineStr">
+        <is>
+          <t>Index</t>
+        </is>
+      </c>
+      <c r="B3" s="2" t="inlineStr">
+        <is>
+          <t>Best Strategy</t>
+        </is>
+      </c>
+      <c r="C3" s="2" t="inlineStr">
+        <is>
+          <t>Trades</t>
+        </is>
+      </c>
+      <c r="D3" s="2" t="inlineStr">
+        <is>
+          <t>Win %</t>
+        </is>
+      </c>
+      <c r="E3" s="2" t="inlineStr">
+        <is>
+          <t>Net P&amp;L (Rs)</t>
+        </is>
+      </c>
+      <c r="F3" s="2" t="inlineStr">
+        <is>
+          <t>Profit Factor</t>
+        </is>
+      </c>
+      <c r="G3" s="2" t="inlineStr">
+        <is>
+          <t>Max DD (%)</t>
+        </is>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" s="3" t="inlineStr">
+        <is>
+          <t>NIFTY</t>
+        </is>
+      </c>
+      <c r="B4" s="13" t="inlineStr">
+        <is>
+          <t>vwap_ema_momentum (EMA9/13) [5m]</t>
+        </is>
+      </c>
+      <c r="C4" s="4" t="n">
+        <v>5</v>
+      </c>
+      <c r="D4" s="5" t="n">
+        <v>0.4</v>
+      </c>
+      <c r="E4" s="6" t="n">
+        <v>277.15</v>
+      </c>
+      <c r="F4" s="7" t="n">
+        <v>1.36</v>
+      </c>
+      <c r="G4" s="8" t="n">
+        <v>-0.01480658481386824</v>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" s="3" t="inlineStr">
+        <is>
+          <t>BANKNIFTY</t>
+        </is>
+      </c>
+      <c r="B5" s="13" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="C5" s="10" t="n">
+        <v>0</v>
+      </c>
+      <c r="D5" s="10" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="E5" s="10" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="F5" s="10" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="G5" s="10" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" s="3" t="inlineStr">
+        <is>
+          <t>FINNIFTY</t>
+        </is>
+      </c>
+      <c r="B6" s="13" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="C6" s="10" t="n">
+        <v>0</v>
+      </c>
+      <c r="D6" s="10" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="E6" s="10" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="F6" s="10" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="G6" s="10" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" s="3" t="inlineStr">
+        <is>
+          <t>ALL INDICES</t>
+        </is>
+      </c>
+      <c r="B7" s="13" t="inlineStr">
+        <is>
+          <t>(combined)</t>
+        </is>
+      </c>
+      <c r="C7" s="4" t="n">
+        <v>5</v>
+      </c>
+      <c r="D7" s="5" t="n">
+        <v>0.4</v>
+      </c>
+      <c r="E7" s="6" t="n">
+        <v>277.15</v>
+      </c>
+      <c r="F7" s="7" t="n">
+        <v>1.36</v>
+      </c>
+      <c r="G7" s="8" t="n">
+        <v>-0.01480658481386824</v>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" s="11" t="inlineStr">
+        <is>
+          <t>BT- sheets are from the BACKTEST (each index's single best combo, so time periods aren't double-counted across competing strategies). Plain-named sheets are LIVE paper trades. See latest_backtest_summary.xlsx for every combo tested.</t>
+        </is>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+  <pageSetup orientation="landscape" fitToHeight="0" fitToWidth="1"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet7.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr fitToPage="1"/>
+  </sheetPr>
+  <dimension ref="A1:O46"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <cols>
+    <col width="40" customWidth="1" min="1" max="1"/>
+    <col width="10" customWidth="1" min="2" max="2"/>
+    <col width="10" customWidth="1" min="3" max="3"/>
+    <col width="10" customWidth="1" min="4" max="4"/>
+    <col width="10" customWidth="1" min="5" max="5"/>
+    <col width="10" customWidth="1" min="6" max="6"/>
+    <col width="10" customWidth="1" min="7" max="7"/>
+    <col width="15" customWidth="1" min="8" max="8"/>
+    <col width="15" customWidth="1" min="9" max="9"/>
+    <col width="10" customWidth="1" min="10" max="10"/>
+    <col width="10" customWidth="1" min="11" max="11"/>
+    <col width="10" customWidth="1" min="12" max="12"/>
+    <col width="10" customWidth="1" min="13" max="13"/>
+    <col width="10" customWidth="1" min="14" max="14"/>
+    <col width="15" customWidth="1" min="15" max="15"/>
+  </cols>
+  <sheetData>
+    <row r="1">
+      <c r="A1" s="1" t="inlineStr">
+        <is>
+          <t>BACKTEST NIFTY -- best: vwap_ema_momentum (EMA9/13) [5m] -- PAPER TRADE, NOT REAL MONEY</t>
+        </is>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" s="12" t="inlineStr">
+        <is>
+          <t>MONTHLY returns (% of capital at start of month)</t>
+        </is>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" s="2" t="inlineStr">
+        <is>
+          <t>Year</t>
+        </is>
+      </c>
+      <c r="B4" s="2" t="inlineStr">
+        <is>
+          <t>Jan</t>
+        </is>
+      </c>
+      <c r="C4" s="2" t="inlineStr">
+        <is>
+          <t>Feb</t>
+        </is>
+      </c>
+      <c r="D4" s="2" t="inlineStr">
+        <is>
+          <t>Mar</t>
+        </is>
+      </c>
+      <c r="E4" s="2" t="inlineStr">
+        <is>
+          <t>Apr</t>
+        </is>
+      </c>
+      <c r="F4" s="2" t="inlineStr">
+        <is>
+          <t>May</t>
+        </is>
+      </c>
+      <c r="G4" s="2" t="inlineStr">
+        <is>
+          <t>Jun</t>
+        </is>
+      </c>
+      <c r="H4" s="2" t="inlineStr">
+        <is>
+          <t>Jul</t>
+        </is>
+      </c>
+      <c r="I4" s="2" t="inlineStr">
+        <is>
+          <t>Aug</t>
+        </is>
+      </c>
+      <c r="J4" s="2" t="inlineStr">
+        <is>
+          <t>Sep</t>
+        </is>
+      </c>
+      <c r="K4" s="2" t="inlineStr">
+        <is>
+          <t>Oct</t>
+        </is>
+      </c>
+      <c r="L4" s="2" t="inlineStr">
+        <is>
+          <t>Nov</t>
+        </is>
+      </c>
+      <c r="M4" s="2" t="inlineStr">
+        <is>
+          <t>Dec</t>
+        </is>
+      </c>
+      <c r="N4" s="2" t="inlineStr">
+        <is>
+          <t>Yr %</t>
+        </is>
+      </c>
+      <c r="O4" s="2" t="inlineStr">
+        <is>
+          <t>Yr P&amp;L (Rs)</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" s="3" t="n">
+        <v>2026</v>
+      </c>
+      <c r="B5" s="13" t="n"/>
+      <c r="C5" s="13" t="n"/>
+      <c r="D5" s="29" t="n">
+        <v>-0.003766999999999999</v>
+      </c>
+      <c r="E5" s="13" t="n"/>
+      <c r="F5" s="14" t="n">
+        <v>0.02750410797474085</v>
+      </c>
+      <c r="G5" s="13" t="n"/>
+      <c r="H5" s="13" t="n"/>
+      <c r="I5" s="13" t="n"/>
+      <c r="J5" s="13" t="n"/>
+      <c r="K5" s="29" t="n">
+        <v>-0.009550293146912445</v>
+      </c>
+      <c r="L5" s="13" t="n"/>
+      <c r="M5" s="13" t="n"/>
+      <c r="N5" s="15" t="n">
+        <v>0.01385750000000008</v>
+      </c>
+      <c r="O5" s="16" t="n">
+        <v>277.15</v>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" s="3" t="inlineStr">
+        <is>
+          <t>Avg</t>
+        </is>
+      </c>
+      <c r="B6" s="13" t="n"/>
+      <c r="C6" s="13" t="n"/>
+      <c r="D6" s="30" t="n">
+        <v>-0.003766999999999999</v>
+      </c>
+      <c r="E6" s="13" t="n"/>
+      <c r="F6" s="15" t="n">
+        <v>0.02750410797474085</v>
+      </c>
+      <c r="G6" s="13" t="n"/>
+      <c r="H6" s="13" t="n"/>
+      <c r="I6" s="13" t="n"/>
+      <c r="J6" s="13" t="n"/>
+      <c r="K6" s="30" t="n">
+        <v>-0.009550293146912445</v>
+      </c>
+      <c r="L6" s="13" t="n"/>
+      <c r="M6" s="13" t="n"/>
+    </row>
+    <row r="8">
+      <c r="A8" s="12" t="inlineStr">
+        <is>
+          <t>WEEKLY returns (% of capital at start of that week; weeks split at month edges)</t>
+        </is>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" s="2" t="inlineStr">
+        <is>
+          <t>Month</t>
+        </is>
+      </c>
+      <c r="B9" s="2" t="inlineStr">
+        <is>
+          <t>W1</t>
+        </is>
+      </c>
+      <c r="C9" s="2" t="inlineStr">
+        <is>
+          <t>W2</t>
+        </is>
+      </c>
+      <c r="D9" s="2" t="inlineStr">
+        <is>
+          <t>W3</t>
+        </is>
+      </c>
+      <c r="E9" s="2" t="inlineStr">
+        <is>
+          <t>W4</t>
+        </is>
+      </c>
+      <c r="F9" s="2" t="inlineStr">
+        <is>
+          <t>W5</t>
+        </is>
+      </c>
+      <c r="G9" s="2" t="inlineStr">
+        <is>
+          <t>W6</t>
+        </is>
+      </c>
+      <c r="H9" s="2" t="inlineStr">
+        <is>
+          <t>Month %</t>
+        </is>
+      </c>
+      <c r="I9" s="2" t="inlineStr">
+        <is>
+          <t>Month P&amp;L (Rs)</t>
+        </is>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" s="3" t="inlineStr">
+        <is>
+          <t>2026-Mar</t>
+        </is>
+      </c>
+      <c r="B10" s="29" t="n">
+        <v>-0.003766999999999999</v>
+      </c>
+      <c r="C10" s="13" t="n"/>
+      <c r="D10" s="13" t="n"/>
+      <c r="E10" s="13" t="n"/>
+      <c r="F10" s="13" t="n"/>
+      <c r="G10" s="13" t="n"/>
+      <c r="H10" s="31" t="n">
+        <v>-0.003766999999999999</v>
+      </c>
+      <c r="I10" s="32" t="n">
+        <v>-75.34</v>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" s="3" t="inlineStr">
+        <is>
+          <t>2026-May</t>
+        </is>
+      </c>
+      <c r="B11" s="14" t="n">
+        <v>0.02750410797474085</v>
+      </c>
+      <c r="C11" s="13" t="n"/>
+      <c r="D11" s="13" t="n"/>
+      <c r="E11" s="13" t="n"/>
+      <c r="F11" s="13" t="n"/>
+      <c r="G11" s="13" t="n"/>
+      <c r="H11" s="17" t="n">
+        <v>0.02750410797474085</v>
+      </c>
+      <c r="I11" s="16" t="n">
+        <v>548.01</v>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" s="3" t="inlineStr">
+        <is>
+          <t>2026-Oct</t>
+        </is>
+      </c>
+      <c r="B12" s="29" t="n">
+        <v>-0.009550293146912445</v>
+      </c>
+      <c r="C12" s="13" t="n"/>
+      <c r="D12" s="13" t="n"/>
+      <c r="E12" s="13" t="n"/>
+      <c r="F12" s="13" t="n"/>
+      <c r="G12" s="13" t="n"/>
+      <c r="H12" s="31" t="n">
+        <v>-0.009550293146912445</v>
+      </c>
+      <c r="I12" s="32" t="n">
+        <v>-195.52</v>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" s="12" t="inlineStr">
+        <is>
+          <t>DAILY returns (% of capital at start of that day; blank = no trade that day)</t>
+        </is>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" s="2" t="inlineStr">
+        <is>
+          <t>Week starting (Mon)</t>
+        </is>
+      </c>
+      <c r="B15" s="2" t="inlineStr">
+        <is>
+          <t>Mon</t>
+        </is>
+      </c>
+      <c r="C15" s="2" t="inlineStr">
+        <is>
+          <t>Tue</t>
+        </is>
+      </c>
+      <c r="D15" s="2" t="inlineStr">
+        <is>
+          <t>Wed</t>
+        </is>
+      </c>
+      <c r="E15" s="2" t="inlineStr">
+        <is>
+          <t>Thu</t>
+        </is>
+      </c>
+      <c r="F15" s="2" t="inlineStr">
+        <is>
+          <t>Fri</t>
+        </is>
+      </c>
+      <c r="G15" s="2" t="inlineStr">
+        <is>
+          <t>Week %</t>
+        </is>
+      </c>
+      <c r="H15" s="2" t="inlineStr">
+        <is>
+          <t>Week P&amp;L (Rs)</t>
+        </is>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" s="3" t="inlineStr">
+        <is>
+          <t>23-Mar-2026</t>
+        </is>
+      </c>
+      <c r="B16" s="13" t="n"/>
+      <c r="C16" s="29" t="n">
+        <v>-0.003766999999999999</v>
+      </c>
+      <c r="D16" s="13" t="n"/>
+      <c r="E16" s="13" t="n"/>
+      <c r="F16" s="13" t="n"/>
+      <c r="G16" s="31" t="n">
+        <v>-0.003766999999999999</v>
+      </c>
+      <c r="H16" s="32" t="n">
+        <v>-75.34</v>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" s="3" t="inlineStr">
+        <is>
+          <t>11-May-2026</t>
+        </is>
+      </c>
+      <c r="B17" s="13" t="n"/>
+      <c r="C17" s="14" t="n">
+        <v>0.02750410797474085</v>
+      </c>
+      <c r="D17" s="13" t="n"/>
+      <c r="E17" s="13" t="n"/>
+      <c r="F17" s="13" t="n"/>
+      <c r="G17" s="17" t="n">
+        <v>0.02750410797474085</v>
+      </c>
+      <c r="H17" s="16" t="n">
+        <v>548.01</v>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" s="3" t="inlineStr">
+        <is>
+          <t>12-Oct-2026</t>
+        </is>
+      </c>
+      <c r="B18" s="13" t="n"/>
+      <c r="C18" s="29" t="n">
+        <v>-0.009550293146912445</v>
+      </c>
+      <c r="D18" s="13" t="n"/>
+      <c r="E18" s="13" t="n"/>
+      <c r="F18" s="13" t="n"/>
+      <c r="G18" s="31" t="n">
+        <v>-0.009550293146912445</v>
+      </c>
+      <c r="H18" s="32" t="n">
+        <v>-195.52</v>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" s="12" t="inlineStr">
+        <is>
+          <t>STATISTICS (all trades for this index)</t>
+        </is>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" s="3" t="inlineStr">
+        <is>
+          <t>All trades</t>
+        </is>
+      </c>
+      <c r="B21" s="18" t="n">
+        <v>5</v>
+      </c>
+      <c r="C21" s="19" t="n"/>
+      <c r="D21" s="20" t="n"/>
+    </row>
+    <row r="22">
+      <c r="A22" s="3" t="inlineStr">
+        <is>
+          <t>Winners</t>
+        </is>
+      </c>
+      <c r="B22" s="21" t="inlineStr">
+        <is>
+          <t>2 (40.0%)</t>
+        </is>
+      </c>
+      <c r="C22" s="19" t="n"/>
+      <c r="D22" s="20" t="n"/>
+    </row>
+    <row r="23">
+      <c r="A23" s="3" t="inlineStr">
+        <is>
+          <t>Losers</t>
+        </is>
+      </c>
+      <c r="B23" s="21" t="inlineStr">
+        <is>
+          <t>3 (60.0%)</t>
+        </is>
+      </c>
+      <c r="C23" s="19" t="n"/>
+      <c r="D23" s="20" t="n"/>
+    </row>
+    <row r="24">
+      <c r="A24" s="3" t="inlineStr">
+        <is>
+          <t>Net P&amp;L (Rs)</t>
+        </is>
+      </c>
+      <c r="B24" s="22" t="n">
+        <v>277.15</v>
+      </c>
+      <c r="C24" s="19" t="n"/>
+      <c r="D24" s="20" t="n"/>
+    </row>
+    <row r="25">
+      <c r="A25" s="3" t="inlineStr">
+        <is>
+          <t>Total Profit (Rs)</t>
+        </is>
+      </c>
+      <c r="B25" s="22" t="n">
+        <v>1040.37</v>
+      </c>
+      <c r="C25" s="19" t="n"/>
+      <c r="D25" s="20" t="n"/>
+    </row>
+    <row r="26">
+      <c r="A26" s="3" t="inlineStr">
+        <is>
+          <t>Total Loss (Rs)</t>
+        </is>
+      </c>
+      <c r="B26" s="23" t="n">
+        <v>-763.22</v>
+      </c>
+      <c r="C26" s="19" t="n"/>
+      <c r="D26" s="20" t="n"/>
+    </row>
+    <row r="27">
+      <c r="A27" s="3" t="inlineStr">
+        <is>
+          <t>Transaction costs (Rs)</t>
+        </is>
+      </c>
+      <c r="B27" s="24" t="n">
+        <v>143.6</v>
+      </c>
+      <c r="C27" s="19" t="n"/>
+      <c r="D27" s="20" t="n"/>
+    </row>
+    <row r="28">
+      <c r="A28" s="3" t="inlineStr">
+        <is>
+          <t>Avg Profit/Loss per trade (Rs)</t>
+        </is>
+      </c>
+      <c r="B28" s="22" t="n">
+        <v>55.43</v>
+      </c>
+      <c r="C28" s="19" t="n"/>
+      <c r="D28" s="20" t="n"/>
+    </row>
+    <row r="29">
+      <c r="A29" s="3" t="inlineStr">
+        <is>
+          <t>Avg Profit/Loss per trade (% of premium)</t>
+        </is>
+      </c>
+      <c r="B29" s="25" t="n">
+        <v>2.6</v>
+      </c>
+      <c r="C29" s="19" t="n"/>
+      <c r="D29" s="20" t="n"/>
+    </row>
+    <row r="30">
+      <c r="A30" s="3" t="inlineStr">
+        <is>
+          <t>Avg Win (Rs)</t>
+        </is>
+      </c>
+      <c r="B30" s="22" t="n">
+        <v>520.1799999999999</v>
+      </c>
+      <c r="C30" s="19" t="n"/>
+      <c r="D30" s="20" t="n"/>
+    </row>
+    <row r="31">
+      <c r="A31" s="3" t="inlineStr">
+        <is>
+          <t>Avg Win (% of premium)</t>
+        </is>
+      </c>
+      <c r="B31" s="26" t="n">
+        <v>54.92</v>
+      </c>
+      <c r="C31" s="19" t="n"/>
+      <c r="D31" s="20" t="n"/>
+    </row>
+    <row r="32">
+      <c r="A32" s="3" t="inlineStr">
+        <is>
+          <t>Avg Loss (Rs)</t>
+        </is>
+      </c>
+      <c r="B32" s="23" t="n">
+        <v>-254.41</v>
+      </c>
+      <c r="C32" s="19" t="n"/>
+      <c r="D32" s="20" t="n"/>
+    </row>
+    <row r="33">
+      <c r="A33" s="3" t="inlineStr">
+        <is>
+          <t>Avg Loss (% of premium)</t>
+        </is>
+      </c>
+      <c r="B33" s="27" t="n">
+        <v>-32.27</v>
+      </c>
+      <c r="C33" s="19" t="n"/>
+      <c r="D33" s="20" t="n"/>
+    </row>
+    <row r="34">
+      <c r="A34" s="3" t="inlineStr">
+        <is>
+          <t>Largest Win (Rs)</t>
+        </is>
+      </c>
+      <c r="B34" s="22" t="n">
+        <v>548.01</v>
+      </c>
+      <c r="C34" s="19" t="n"/>
+      <c r="D34" s="20" t="n"/>
+    </row>
+    <row r="35">
+      <c r="A35" s="3" t="inlineStr">
+        <is>
+          <t>Largest Loss (Rs)</t>
+        </is>
+      </c>
+      <c r="B35" s="23" t="n">
+        <v>-299.45</v>
+      </c>
+      <c r="C35" s="19" t="n"/>
+      <c r="D35" s="20" t="n"/>
+    </row>
+    <row r="36">
+      <c r="A36" s="3" t="inlineStr">
+        <is>
+          <t>Max Consecutive Wins</t>
+        </is>
+      </c>
+      <c r="B36" s="18" t="n">
+        <v>1</v>
+      </c>
+      <c r="C36" s="19" t="n"/>
+      <c r="D36" s="20" t="n"/>
+    </row>
+    <row r="37">
+      <c r="A37" s="3" t="inlineStr">
+        <is>
+          <t>Max Consecutive Losses</t>
+        </is>
+      </c>
+      <c r="B37" s="18" t="n">
+        <v>1</v>
+      </c>
+      <c r="C37" s="19" t="n"/>
+      <c r="D37" s="20" t="n"/>
+    </row>
+    <row r="38">
+      <c r="A38" s="3" t="inlineStr">
+        <is>
+          <t>Max trade drawdown (Rs)</t>
+        </is>
+      </c>
+      <c r="B38" s="23" t="n">
+        <v>-299.45</v>
+      </c>
+      <c r="C38" s="19" t="n"/>
+      <c r="D38" s="20" t="n"/>
+    </row>
+    <row r="39">
+      <c r="A39" s="3" t="inlineStr">
+        <is>
+          <t>Max system drawdown (Rs)</t>
+        </is>
+      </c>
+      <c r="B39" s="23" t="n">
+        <v>-299.45</v>
+      </c>
+      <c r="C39" s="19" t="n"/>
+      <c r="D39" s="20" t="n"/>
+    </row>
+    <row r="40">
+      <c r="A40" s="3" t="inlineStr">
+        <is>
+          <t>Max system drawdown (%)</t>
+        </is>
+      </c>
+      <c r="B40" s="27" t="n">
+        <v>-1.48</v>
+      </c>
+      <c r="C40" s="19" t="n"/>
+      <c r="D40" s="20" t="n"/>
+    </row>
+    <row r="41">
+      <c r="A41" s="3" t="inlineStr">
+        <is>
+          <t>Recovery Factor</t>
+        </is>
+      </c>
+      <c r="B41" s="28" t="n">
+        <v>0.93</v>
+      </c>
+      <c r="C41" s="19" t="n"/>
+      <c r="D41" s="20" t="n"/>
+    </row>
+    <row r="42">
+      <c r="A42" s="3" t="inlineStr">
+        <is>
+          <t>Profit Factor</t>
+        </is>
+      </c>
+      <c r="B42" s="28" t="n">
+        <v>1.36</v>
+      </c>
+      <c r="C42" s="19" t="n"/>
+      <c r="D42" s="20" t="n"/>
+    </row>
+    <row r="43">
+      <c r="A43" s="3" t="inlineStr">
+        <is>
+          <t>Payoff Ratio (avg win / avg loss)</t>
+        </is>
+      </c>
+      <c r="B43" s="28" t="n">
+        <v>2.04</v>
+      </c>
+      <c r="C43" s="19" t="n"/>
+      <c r="D43" s="20" t="n"/>
+    </row>
+    <row r="44">
+      <c r="A44" s="3" t="inlineStr">
+        <is>
+          <t>Sharpe Ratio (annualized)</t>
+        </is>
+      </c>
+      <c r="B44" s="28" t="n">
+        <v>4.61</v>
+      </c>
+      <c r="C44" s="19" t="n"/>
+      <c r="D44" s="20" t="n"/>
+    </row>
+    <row r="46">
+      <c r="A46" s="11" t="inlineStr">
+        <is>
+          <t>Caveat: with only a handful of trades these numbers (Sharpe, profit factor, drawdown %) are not statistically reliable. Watch this over weeks/months before drawing conclusions.</t>
+        </is>
+      </c>
+    </row>
+  </sheetData>
+  <mergeCells count="24">
+    <mergeCell ref="B42:D42"/>
+    <mergeCell ref="B23:D23"/>
+    <mergeCell ref="B44:D44"/>
+    <mergeCell ref="B29:D29"/>
+    <mergeCell ref="B38:D38"/>
+    <mergeCell ref="B34:D34"/>
+    <mergeCell ref="B28:D28"/>
+    <mergeCell ref="B37:D37"/>
+    <mergeCell ref="B40:D40"/>
+    <mergeCell ref="B30:D30"/>
+    <mergeCell ref="B24:D24"/>
+    <mergeCell ref="B33:D33"/>
+    <mergeCell ref="B36:D36"/>
+    <mergeCell ref="B41:D41"/>
+    <mergeCell ref="B32:D32"/>
+    <mergeCell ref="B35:D35"/>
+    <mergeCell ref="B26:D26"/>
+    <mergeCell ref="B25:D25"/>
+    <mergeCell ref="B31:D31"/>
+    <mergeCell ref="B22:D22"/>
+    <mergeCell ref="B27:D27"/>
+    <mergeCell ref="B21:D21"/>
+    <mergeCell ref="B43:D43"/>
+    <mergeCell ref="B39:D39"/>
+  </mergeCells>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+  <pageSetup orientation="landscape" fitToHeight="0" fitToWidth="1"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet8.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr fitToPage="1"/>
+  </sheetPr>
+  <dimension ref="A1:A3"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <cols>
+    <col width="40" customWidth="1" min="1" max="1"/>
+    <col width="10" customWidth="1" min="2" max="2"/>
+    <col width="10" customWidth="1" min="3" max="3"/>
+    <col width="10" customWidth="1" min="4" max="4"/>
+    <col width="10" customWidth="1" min="5" max="5"/>
+    <col width="10" customWidth="1" min="6" max="6"/>
+    <col width="10" customWidth="1" min="7" max="7"/>
+    <col width="15" customWidth="1" min="8" max="8"/>
+    <col width="15" customWidth="1" min="9" max="9"/>
+    <col width="10" customWidth="1" min="10" max="10"/>
+    <col width="10" customWidth="1" min="11" max="11"/>
+    <col width="10" customWidth="1" min="12" max="12"/>
+    <col width="10" customWidth="1" min="13" max="13"/>
+    <col width="10" customWidth="1" min="14" max="14"/>
+    <col width="15" customWidth="1" min="15" max="15"/>
+  </cols>
+  <sheetData>
+    <row r="1">
+      <c r="A1" s="1" t="inlineStr">
+        <is>
+          <t>BACKTEST BANKNIFTY -- best:  -- PAPER TRADE, NOT REAL MONEY</t>
+        </is>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" s="11" t="inlineStr">
+        <is>
+          <t>No trades yet for this index -- this fills in automatically as the bot trades.</t>
+        </is>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+  <pageSetup orientation="landscape" fitToHeight="0" fitToWidth="1"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet9.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr fitToPage="1"/>
+  </sheetPr>
+  <dimension ref="A1:A3"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <cols>
+    <col width="40" customWidth="1" min="1" max="1"/>
+    <col width="10" customWidth="1" min="2" max="2"/>
+    <col width="10" customWidth="1" min="3" max="3"/>
+    <col width="10" customWidth="1" min="4" max="4"/>
+    <col width="10" customWidth="1" min="5" max="5"/>
+    <col width="10" customWidth="1" min="6" max="6"/>
+    <col width="10" customWidth="1" min="7" max="7"/>
+    <col width="15" customWidth="1" min="8" max="8"/>
+    <col width="15" customWidth="1" min="9" max="9"/>
+    <col width="10" customWidth="1" min="10" max="10"/>
+    <col width="10" customWidth="1" min="11" max="11"/>
+    <col width="10" customWidth="1" min="12" max="12"/>
+    <col width="10" customWidth="1" min="13" max="13"/>
+    <col width="10" customWidth="1" min="14" max="14"/>
+    <col width="15" customWidth="1" min="15" max="15"/>
+  </cols>
+  <sheetData>
+    <row r="1">
+      <c r="A1" s="1" t="inlineStr">
+        <is>
+          <t>BACKTEST FINNIFTY -- best:  -- PAPER TRADE, NOT REAL MONEY</t>
+        </is>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" s="11" t="inlineStr">
+        <is>
+          <t>No trades yet for this index -- this fills in automatically as the bot trades.</t>
+        </is>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+  <pageSetup orientation="landscape" fitToHeight="0" fitToWidth="1"/>
+</worksheet>
 </file>
--- a/reports/dashboard.xlsx
+++ b/reports/dashboard.xlsx
@@ -12,11 +12,6 @@
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="BANKNIFTY" sheetId="3" state="visible" r:id="rId3"/>
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="FINNIFTY" sheetId="4" state="visible" r:id="rId4"/>
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="ALL INDICES" sheetId="5" state="visible" r:id="rId5"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="BT-Summary" sheetId="6" state="visible" r:id="rId6"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="BT-NIFTY" sheetId="7" state="visible" r:id="rId7"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="BT-BANKNIFTY" sheetId="8" state="visible" r:id="rId8"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="BT-FINNIFTY" sheetId="9" state="visible" r:id="rId9"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="BT-ALL INDICES" sheetId="10" state="visible" r:id="rId10"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -31,7 +26,7 @@
     <numFmt numFmtId="166" formatCode="#,##0;-#,##0"/>
     <numFmt numFmtId="167" formatCode="0.00&quot;%&quot;"/>
   </numFmts>
-  <fonts count="10">
+  <fonts count="9">
     <font>
       <name val="Calibri"/>
       <family val="2"/>
@@ -75,13 +70,8 @@
       <name val="Arial"/>
       <color rgb="00C00000"/>
     </font>
-    <font>
-      <name val="Arial"/>
-      <b val="1"/>
-      <color rgb="00C00000"/>
-    </font>
   </fonts>
-  <fills count="5">
+  <fills count="4">
     <fill>
       <patternFill/>
     </fill>
@@ -98,12 +88,6 @@
       <patternFill patternType="solid">
         <fgColor rgb="00E6F4EA"/>
         <bgColor rgb="00E6F4EA"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="00FDE8E8"/>
-        <bgColor rgb="00FDE8E8"/>
       </patternFill>
     </fill>
   </fills>
@@ -177,7 +161,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="33">
+  <cellXfs count="29">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="2" fillId="2" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
@@ -227,10 +211,6 @@
     <xf numFmtId="2" fontId="4" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="right"/>
     </xf>
-    <xf numFmtId="164" fontId="8" fillId="4" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="164" fontId="8" fillId="0" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="164" fontId="9" fillId="4" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="166" fontId="8" fillId="0" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0" hidden="0"/>
@@ -785,741 +765,6 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet10.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <sheetPr>
-    <outlinePr summaryBelow="1" summaryRight="1"/>
-    <pageSetUpPr fitToPage="1"/>
-  </sheetPr>
-  <dimension ref="A1:O46"/>
-  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
-  <cols>
-    <col width="40" customWidth="1" min="1" max="1"/>
-    <col width="10" customWidth="1" min="2" max="2"/>
-    <col width="10" customWidth="1" min="3" max="3"/>
-    <col width="10" customWidth="1" min="4" max="4"/>
-    <col width="10" customWidth="1" min="5" max="5"/>
-    <col width="10" customWidth="1" min="6" max="6"/>
-    <col width="10" customWidth="1" min="7" max="7"/>
-    <col width="15" customWidth="1" min="8" max="8"/>
-    <col width="15" customWidth="1" min="9" max="9"/>
-    <col width="10" customWidth="1" min="10" max="10"/>
-    <col width="10" customWidth="1" min="11" max="11"/>
-    <col width="10" customWidth="1" min="12" max="12"/>
-    <col width="10" customWidth="1" min="13" max="13"/>
-    <col width="10" customWidth="1" min="14" max="14"/>
-    <col width="15" customWidth="1" min="15" max="15"/>
-  </cols>
-  <sheetData>
-    <row r="1">
-      <c r="A1" s="1" t="inlineStr">
-        <is>
-          <t>BACKTEST ALL INDICES -- PAPER TRADE, NOT REAL MONEY</t>
-        </is>
-      </c>
-    </row>
-    <row r="3">
-      <c r="A3" s="12" t="inlineStr">
-        <is>
-          <t>MONTHLY returns (% of capital at start of month)</t>
-        </is>
-      </c>
-    </row>
-    <row r="4">
-      <c r="A4" s="2" t="inlineStr">
-        <is>
-          <t>Year</t>
-        </is>
-      </c>
-      <c r="B4" s="2" t="inlineStr">
-        <is>
-          <t>Jan</t>
-        </is>
-      </c>
-      <c r="C4" s="2" t="inlineStr">
-        <is>
-          <t>Feb</t>
-        </is>
-      </c>
-      <c r="D4" s="2" t="inlineStr">
-        <is>
-          <t>Mar</t>
-        </is>
-      </c>
-      <c r="E4" s="2" t="inlineStr">
-        <is>
-          <t>Apr</t>
-        </is>
-      </c>
-      <c r="F4" s="2" t="inlineStr">
-        <is>
-          <t>May</t>
-        </is>
-      </c>
-      <c r="G4" s="2" t="inlineStr">
-        <is>
-          <t>Jun</t>
-        </is>
-      </c>
-      <c r="H4" s="2" t="inlineStr">
-        <is>
-          <t>Jul</t>
-        </is>
-      </c>
-      <c r="I4" s="2" t="inlineStr">
-        <is>
-          <t>Aug</t>
-        </is>
-      </c>
-      <c r="J4" s="2" t="inlineStr">
-        <is>
-          <t>Sep</t>
-        </is>
-      </c>
-      <c r="K4" s="2" t="inlineStr">
-        <is>
-          <t>Oct</t>
-        </is>
-      </c>
-      <c r="L4" s="2" t="inlineStr">
-        <is>
-          <t>Nov</t>
-        </is>
-      </c>
-      <c r="M4" s="2" t="inlineStr">
-        <is>
-          <t>Dec</t>
-        </is>
-      </c>
-      <c r="N4" s="2" t="inlineStr">
-        <is>
-          <t>Yr %</t>
-        </is>
-      </c>
-      <c r="O4" s="2" t="inlineStr">
-        <is>
-          <t>Yr P&amp;L (Rs)</t>
-        </is>
-      </c>
-    </row>
-    <row r="5">
-      <c r="A5" s="3" t="n">
-        <v>2026</v>
-      </c>
-      <c r="B5" s="13" t="n"/>
-      <c r="C5" s="13" t="n"/>
-      <c r="D5" s="29" t="n">
-        <v>-0.003766999999999999</v>
-      </c>
-      <c r="E5" s="13" t="n"/>
-      <c r="F5" s="14" t="n">
-        <v>0.02750410797474085</v>
-      </c>
-      <c r="G5" s="13" t="n"/>
-      <c r="H5" s="13" t="n"/>
-      <c r="I5" s="13" t="n"/>
-      <c r="J5" s="13" t="n"/>
-      <c r="K5" s="29" t="n">
-        <v>-0.009550293146912445</v>
-      </c>
-      <c r="L5" s="13" t="n"/>
-      <c r="M5" s="13" t="n"/>
-      <c r="N5" s="15" t="n">
-        <v>0.01385750000000008</v>
-      </c>
-      <c r="O5" s="16" t="n">
-        <v>277.15</v>
-      </c>
-    </row>
-    <row r="6">
-      <c r="A6" s="3" t="inlineStr">
-        <is>
-          <t>Avg</t>
-        </is>
-      </c>
-      <c r="B6" s="13" t="n"/>
-      <c r="C6" s="13" t="n"/>
-      <c r="D6" s="30" t="n">
-        <v>-0.003766999999999999</v>
-      </c>
-      <c r="E6" s="13" t="n"/>
-      <c r="F6" s="15" t="n">
-        <v>0.02750410797474085</v>
-      </c>
-      <c r="G6" s="13" t="n"/>
-      <c r="H6" s="13" t="n"/>
-      <c r="I6" s="13" t="n"/>
-      <c r="J6" s="13" t="n"/>
-      <c r="K6" s="30" t="n">
-        <v>-0.009550293146912445</v>
-      </c>
-      <c r="L6" s="13" t="n"/>
-      <c r="M6" s="13" t="n"/>
-    </row>
-    <row r="8">
-      <c r="A8" s="12" t="inlineStr">
-        <is>
-          <t>WEEKLY returns (% of capital at start of that week; weeks split at month edges)</t>
-        </is>
-      </c>
-    </row>
-    <row r="9">
-      <c r="A9" s="2" t="inlineStr">
-        <is>
-          <t>Month</t>
-        </is>
-      </c>
-      <c r="B9" s="2" t="inlineStr">
-        <is>
-          <t>W1</t>
-        </is>
-      </c>
-      <c r="C9" s="2" t="inlineStr">
-        <is>
-          <t>W2</t>
-        </is>
-      </c>
-      <c r="D9" s="2" t="inlineStr">
-        <is>
-          <t>W3</t>
-        </is>
-      </c>
-      <c r="E9" s="2" t="inlineStr">
-        <is>
-          <t>W4</t>
-        </is>
-      </c>
-      <c r="F9" s="2" t="inlineStr">
-        <is>
-          <t>W5</t>
-        </is>
-      </c>
-      <c r="G9" s="2" t="inlineStr">
-        <is>
-          <t>W6</t>
-        </is>
-      </c>
-      <c r="H9" s="2" t="inlineStr">
-        <is>
-          <t>Month %</t>
-        </is>
-      </c>
-      <c r="I9" s="2" t="inlineStr">
-        <is>
-          <t>Month P&amp;L (Rs)</t>
-        </is>
-      </c>
-    </row>
-    <row r="10">
-      <c r="A10" s="3" t="inlineStr">
-        <is>
-          <t>2026-Mar</t>
-        </is>
-      </c>
-      <c r="B10" s="29" t="n">
-        <v>-0.003766999999999999</v>
-      </c>
-      <c r="C10" s="13" t="n"/>
-      <c r="D10" s="13" t="n"/>
-      <c r="E10" s="13" t="n"/>
-      <c r="F10" s="13" t="n"/>
-      <c r="G10" s="13" t="n"/>
-      <c r="H10" s="31" t="n">
-        <v>-0.003766999999999999</v>
-      </c>
-      <c r="I10" s="32" t="n">
-        <v>-75.34</v>
-      </c>
-    </row>
-    <row r="11">
-      <c r="A11" s="3" t="inlineStr">
-        <is>
-          <t>2026-May</t>
-        </is>
-      </c>
-      <c r="B11" s="14" t="n">
-        <v>0.02750410797474085</v>
-      </c>
-      <c r="C11" s="13" t="n"/>
-      <c r="D11" s="13" t="n"/>
-      <c r="E11" s="13" t="n"/>
-      <c r="F11" s="13" t="n"/>
-      <c r="G11" s="13" t="n"/>
-      <c r="H11" s="17" t="n">
-        <v>0.02750410797474085</v>
-      </c>
-      <c r="I11" s="16" t="n">
-        <v>548.01</v>
-      </c>
-    </row>
-    <row r="12">
-      <c r="A12" s="3" t="inlineStr">
-        <is>
-          <t>2026-Oct</t>
-        </is>
-      </c>
-      <c r="B12" s="29" t="n">
-        <v>-0.009550293146912445</v>
-      </c>
-      <c r="C12" s="13" t="n"/>
-      <c r="D12" s="13" t="n"/>
-      <c r="E12" s="13" t="n"/>
-      <c r="F12" s="13" t="n"/>
-      <c r="G12" s="13" t="n"/>
-      <c r="H12" s="31" t="n">
-        <v>-0.009550293146912445</v>
-      </c>
-      <c r="I12" s="32" t="n">
-        <v>-195.52</v>
-      </c>
-    </row>
-    <row r="14">
-      <c r="A14" s="12" t="inlineStr">
-        <is>
-          <t>DAILY returns (% of capital at start of that day; blank = no trade that day)</t>
-        </is>
-      </c>
-    </row>
-    <row r="15">
-      <c r="A15" s="2" t="inlineStr">
-        <is>
-          <t>Week starting (Mon)</t>
-        </is>
-      </c>
-      <c r="B15" s="2" t="inlineStr">
-        <is>
-          <t>Mon</t>
-        </is>
-      </c>
-      <c r="C15" s="2" t="inlineStr">
-        <is>
-          <t>Tue</t>
-        </is>
-      </c>
-      <c r="D15" s="2" t="inlineStr">
-        <is>
-          <t>Wed</t>
-        </is>
-      </c>
-      <c r="E15" s="2" t="inlineStr">
-        <is>
-          <t>Thu</t>
-        </is>
-      </c>
-      <c r="F15" s="2" t="inlineStr">
-        <is>
-          <t>Fri</t>
-        </is>
-      </c>
-      <c r="G15" s="2" t="inlineStr">
-        <is>
-          <t>Week %</t>
-        </is>
-      </c>
-      <c r="H15" s="2" t="inlineStr">
-        <is>
-          <t>Week P&amp;L (Rs)</t>
-        </is>
-      </c>
-    </row>
-    <row r="16">
-      <c r="A16" s="3" t="inlineStr">
-        <is>
-          <t>23-Mar-2026</t>
-        </is>
-      </c>
-      <c r="B16" s="13" t="n"/>
-      <c r="C16" s="29" t="n">
-        <v>-0.003766999999999999</v>
-      </c>
-      <c r="D16" s="13" t="n"/>
-      <c r="E16" s="13" t="n"/>
-      <c r="F16" s="13" t="n"/>
-      <c r="G16" s="31" t="n">
-        <v>-0.003766999999999999</v>
-      </c>
-      <c r="H16" s="32" t="n">
-        <v>-75.34</v>
-      </c>
-    </row>
-    <row r="17">
-      <c r="A17" s="3" t="inlineStr">
-        <is>
-          <t>11-May-2026</t>
-        </is>
-      </c>
-      <c r="B17" s="13" t="n"/>
-      <c r="C17" s="14" t="n">
-        <v>0.02750410797474085</v>
-      </c>
-      <c r="D17" s="13" t="n"/>
-      <c r="E17" s="13" t="n"/>
-      <c r="F17" s="13" t="n"/>
-      <c r="G17" s="17" t="n">
-        <v>0.02750410797474085</v>
-      </c>
-      <c r="H17" s="16" t="n">
-        <v>548.01</v>
-      </c>
-    </row>
-    <row r="18">
-      <c r="A18" s="3" t="inlineStr">
-        <is>
-          <t>12-Oct-2026</t>
-        </is>
-      </c>
-      <c r="B18" s="13" t="n"/>
-      <c r="C18" s="29" t="n">
-        <v>-0.009550293146912445</v>
-      </c>
-      <c r="D18" s="13" t="n"/>
-      <c r="E18" s="13" t="n"/>
-      <c r="F18" s="13" t="n"/>
-      <c r="G18" s="31" t="n">
-        <v>-0.009550293146912445</v>
-      </c>
-      <c r="H18" s="32" t="n">
-        <v>-195.52</v>
-      </c>
-    </row>
-    <row r="20">
-      <c r="A20" s="12" t="inlineStr">
-        <is>
-          <t>STATISTICS (all trades for this index)</t>
-        </is>
-      </c>
-    </row>
-    <row r="21">
-      <c r="A21" s="3" t="inlineStr">
-        <is>
-          <t>All trades</t>
-        </is>
-      </c>
-      <c r="B21" s="18" t="n">
-        <v>5</v>
-      </c>
-      <c r="C21" s="19" t="n"/>
-      <c r="D21" s="20" t="n"/>
-    </row>
-    <row r="22">
-      <c r="A22" s="3" t="inlineStr">
-        <is>
-          <t>Winners</t>
-        </is>
-      </c>
-      <c r="B22" s="21" t="inlineStr">
-        <is>
-          <t>2 (40.0%)</t>
-        </is>
-      </c>
-      <c r="C22" s="19" t="n"/>
-      <c r="D22" s="20" t="n"/>
-    </row>
-    <row r="23">
-      <c r="A23" s="3" t="inlineStr">
-        <is>
-          <t>Losers</t>
-        </is>
-      </c>
-      <c r="B23" s="21" t="inlineStr">
-        <is>
-          <t>3 (60.0%)</t>
-        </is>
-      </c>
-      <c r="C23" s="19" t="n"/>
-      <c r="D23" s="20" t="n"/>
-    </row>
-    <row r="24">
-      <c r="A24" s="3" t="inlineStr">
-        <is>
-          <t>Net P&amp;L (Rs)</t>
-        </is>
-      </c>
-      <c r="B24" s="22" t="n">
-        <v>277.15</v>
-      </c>
-      <c r="C24" s="19" t="n"/>
-      <c r="D24" s="20" t="n"/>
-    </row>
-    <row r="25">
-      <c r="A25" s="3" t="inlineStr">
-        <is>
-          <t>Total Profit (Rs)</t>
-        </is>
-      </c>
-      <c r="B25" s="22" t="n">
-        <v>1040.37</v>
-      </c>
-      <c r="C25" s="19" t="n"/>
-      <c r="D25" s="20" t="n"/>
-    </row>
-    <row r="26">
-      <c r="A26" s="3" t="inlineStr">
-        <is>
-          <t>Total Loss (Rs)</t>
-        </is>
-      </c>
-      <c r="B26" s="23" t="n">
-        <v>-763.22</v>
-      </c>
-      <c r="C26" s="19" t="n"/>
-      <c r="D26" s="20" t="n"/>
-    </row>
-    <row r="27">
-      <c r="A27" s="3" t="inlineStr">
-        <is>
-          <t>Transaction costs (Rs)</t>
-        </is>
-      </c>
-      <c r="B27" s="24" t="n">
-        <v>143.6</v>
-      </c>
-      <c r="C27" s="19" t="n"/>
-      <c r="D27" s="20" t="n"/>
-    </row>
-    <row r="28">
-      <c r="A28" s="3" t="inlineStr">
-        <is>
-          <t>Avg Profit/Loss per trade (Rs)</t>
-        </is>
-      </c>
-      <c r="B28" s="22" t="n">
-        <v>55.43</v>
-      </c>
-      <c r="C28" s="19" t="n"/>
-      <c r="D28" s="20" t="n"/>
-    </row>
-    <row r="29">
-      <c r="A29" s="3" t="inlineStr">
-        <is>
-          <t>Avg Profit/Loss per trade (% of premium)</t>
-        </is>
-      </c>
-      <c r="B29" s="25" t="n">
-        <v>2.6</v>
-      </c>
-      <c r="C29" s="19" t="n"/>
-      <c r="D29" s="20" t="n"/>
-    </row>
-    <row r="30">
-      <c r="A30" s="3" t="inlineStr">
-        <is>
-          <t>Avg Win (Rs)</t>
-        </is>
-      </c>
-      <c r="B30" s="22" t="n">
-        <v>520.1799999999999</v>
-      </c>
-      <c r="C30" s="19" t="n"/>
-      <c r="D30" s="20" t="n"/>
-    </row>
-    <row r="31">
-      <c r="A31" s="3" t="inlineStr">
-        <is>
-          <t>Avg Win (% of premium)</t>
-        </is>
-      </c>
-      <c r="B31" s="26" t="n">
-        <v>54.92</v>
-      </c>
-      <c r="C31" s="19" t="n"/>
-      <c r="D31" s="20" t="n"/>
-    </row>
-    <row r="32">
-      <c r="A32" s="3" t="inlineStr">
-        <is>
-          <t>Avg Loss (Rs)</t>
-        </is>
-      </c>
-      <c r="B32" s="23" t="n">
-        <v>-254.41</v>
-      </c>
-      <c r="C32" s="19" t="n"/>
-      <c r="D32" s="20" t="n"/>
-    </row>
-    <row r="33">
-      <c r="A33" s="3" t="inlineStr">
-        <is>
-          <t>Avg Loss (% of premium)</t>
-        </is>
-      </c>
-      <c r="B33" s="27" t="n">
-        <v>-32.27</v>
-      </c>
-      <c r="C33" s="19" t="n"/>
-      <c r="D33" s="20" t="n"/>
-    </row>
-    <row r="34">
-      <c r="A34" s="3" t="inlineStr">
-        <is>
-          <t>Largest Win (Rs)</t>
-        </is>
-      </c>
-      <c r="B34" s="22" t="n">
-        <v>548.01</v>
-      </c>
-      <c r="C34" s="19" t="n"/>
-      <c r="D34" s="20" t="n"/>
-    </row>
-    <row r="35">
-      <c r="A35" s="3" t="inlineStr">
-        <is>
-          <t>Largest Loss (Rs)</t>
-        </is>
-      </c>
-      <c r="B35" s="23" t="n">
-        <v>-299.45</v>
-      </c>
-      <c r="C35" s="19" t="n"/>
-      <c r="D35" s="20" t="n"/>
-    </row>
-    <row r="36">
-      <c r="A36" s="3" t="inlineStr">
-        <is>
-          <t>Max Consecutive Wins</t>
-        </is>
-      </c>
-      <c r="B36" s="18" t="n">
-        <v>1</v>
-      </c>
-      <c r="C36" s="19" t="n"/>
-      <c r="D36" s="20" t="n"/>
-    </row>
-    <row r="37">
-      <c r="A37" s="3" t="inlineStr">
-        <is>
-          <t>Max Consecutive Losses</t>
-        </is>
-      </c>
-      <c r="B37" s="18" t="n">
-        <v>1</v>
-      </c>
-      <c r="C37" s="19" t="n"/>
-      <c r="D37" s="20" t="n"/>
-    </row>
-    <row r="38">
-      <c r="A38" s="3" t="inlineStr">
-        <is>
-          <t>Max trade drawdown (Rs)</t>
-        </is>
-      </c>
-      <c r="B38" s="23" t="n">
-        <v>-299.45</v>
-      </c>
-      <c r="C38" s="19" t="n"/>
-      <c r="D38" s="20" t="n"/>
-    </row>
-    <row r="39">
-      <c r="A39" s="3" t="inlineStr">
-        <is>
-          <t>Max system drawdown (Rs)</t>
-        </is>
-      </c>
-      <c r="B39" s="23" t="n">
-        <v>-299.45</v>
-      </c>
-      <c r="C39" s="19" t="n"/>
-      <c r="D39" s="20" t="n"/>
-    </row>
-    <row r="40">
-      <c r="A40" s="3" t="inlineStr">
-        <is>
-          <t>Max system drawdown (%)</t>
-        </is>
-      </c>
-      <c r="B40" s="27" t="n">
-        <v>-1.48</v>
-      </c>
-      <c r="C40" s="19" t="n"/>
-      <c r="D40" s="20" t="n"/>
-    </row>
-    <row r="41">
-      <c r="A41" s="3" t="inlineStr">
-        <is>
-          <t>Recovery Factor</t>
-        </is>
-      </c>
-      <c r="B41" s="28" t="n">
-        <v>0.93</v>
-      </c>
-      <c r="C41" s="19" t="n"/>
-      <c r="D41" s="20" t="n"/>
-    </row>
-    <row r="42">
-      <c r="A42" s="3" t="inlineStr">
-        <is>
-          <t>Profit Factor</t>
-        </is>
-      </c>
-      <c r="B42" s="28" t="n">
-        <v>1.36</v>
-      </c>
-      <c r="C42" s="19" t="n"/>
-      <c r="D42" s="20" t="n"/>
-    </row>
-    <row r="43">
-      <c r="A43" s="3" t="inlineStr">
-        <is>
-          <t>Payoff Ratio (avg win / avg loss)</t>
-        </is>
-      </c>
-      <c r="B43" s="28" t="n">
-        <v>2.04</v>
-      </c>
-      <c r="C43" s="19" t="n"/>
-      <c r="D43" s="20" t="n"/>
-    </row>
-    <row r="44">
-      <c r="A44" s="3" t="inlineStr">
-        <is>
-          <t>Sharpe Ratio (annualized)</t>
-        </is>
-      </c>
-      <c r="B44" s="28" t="n">
-        <v>4.61</v>
-      </c>
-      <c r="C44" s="19" t="n"/>
-      <c r="D44" s="20" t="n"/>
-    </row>
-    <row r="46">
-      <c r="A46" s="11" t="inlineStr">
-        <is>
-          <t>Caveat: with only a handful of trades these numbers (Sharpe, profit factor, drawdown %) are not statistically reliable. Watch this over weeks/months before drawing conclusions.</t>
-        </is>
-      </c>
-    </row>
-  </sheetData>
-  <mergeCells count="24">
-    <mergeCell ref="B42:D42"/>
-    <mergeCell ref="B23:D23"/>
-    <mergeCell ref="B44:D44"/>
-    <mergeCell ref="B29:D29"/>
-    <mergeCell ref="B38:D38"/>
-    <mergeCell ref="B34:D34"/>
-    <mergeCell ref="B28:D28"/>
-    <mergeCell ref="B37:D37"/>
-    <mergeCell ref="B40:D40"/>
-    <mergeCell ref="B30:D30"/>
-    <mergeCell ref="B24:D24"/>
-    <mergeCell ref="B33:D33"/>
-    <mergeCell ref="B36:D36"/>
-    <mergeCell ref="B41:D41"/>
-    <mergeCell ref="B32:D32"/>
-    <mergeCell ref="B35:D35"/>
-    <mergeCell ref="B26:D26"/>
-    <mergeCell ref="B25:D25"/>
-    <mergeCell ref="B31:D31"/>
-    <mergeCell ref="B22:D22"/>
-    <mergeCell ref="B27:D27"/>
-    <mergeCell ref="B21:D21"/>
-    <mergeCell ref="B43:D43"/>
-    <mergeCell ref="B39:D39"/>
-  </mergeCells>
-  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
-  <pageSetup orientation="landscape" fitToHeight="0" fitToWidth="1"/>
-</worksheet>
-</file>
-
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr>
@@ -2904,1030 +2149,4 @@
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
   <pageSetup orientation="landscape" fitToHeight="0" fitToWidth="1"/>
 </worksheet>
-</file>
-
-<file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <sheetPr>
-    <outlinePr summaryBelow="1" summaryRight="1"/>
-    <pageSetUpPr fitToPage="1"/>
-  </sheetPr>
-  <dimension ref="A1:G9"/>
-  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
-  <cols>
-    <col width="15" customWidth="1" min="1" max="1"/>
-    <col width="22" customWidth="1" min="2" max="2"/>
-    <col width="15" customWidth="1" min="3" max="3"/>
-    <col width="15" customWidth="1" min="4" max="4"/>
-    <col width="15" customWidth="1" min="5" max="5"/>
-    <col width="15" customWidth="1" min="6" max="6"/>
-    <col width="15" customWidth="1" min="7" max="7"/>
-  </cols>
-  <sheetData>
-    <row r="1">
-      <c r="A1" s="1" t="inlineStr">
-        <is>
-          <t>BACKTEST summary by index (best strategy per index) -- PAPER TRADE, NOT REAL MONEY</t>
-        </is>
-      </c>
-    </row>
-    <row r="3">
-      <c r="A3" s="2" t="inlineStr">
-        <is>
-          <t>Index</t>
-        </is>
-      </c>
-      <c r="B3" s="2" t="inlineStr">
-        <is>
-          <t>Best Strategy</t>
-        </is>
-      </c>
-      <c r="C3" s="2" t="inlineStr">
-        <is>
-          <t>Trades</t>
-        </is>
-      </c>
-      <c r="D3" s="2" t="inlineStr">
-        <is>
-          <t>Win %</t>
-        </is>
-      </c>
-      <c r="E3" s="2" t="inlineStr">
-        <is>
-          <t>Net P&amp;L (Rs)</t>
-        </is>
-      </c>
-      <c r="F3" s="2" t="inlineStr">
-        <is>
-          <t>Profit Factor</t>
-        </is>
-      </c>
-      <c r="G3" s="2" t="inlineStr">
-        <is>
-          <t>Max DD (%)</t>
-        </is>
-      </c>
-    </row>
-    <row r="4">
-      <c r="A4" s="3" t="inlineStr">
-        <is>
-          <t>NIFTY</t>
-        </is>
-      </c>
-      <c r="B4" s="13" t="inlineStr">
-        <is>
-          <t>vwap_ema_momentum (EMA9/13) [5m]</t>
-        </is>
-      </c>
-      <c r="C4" s="4" t="n">
-        <v>5</v>
-      </c>
-      <c r="D4" s="5" t="n">
-        <v>0.4</v>
-      </c>
-      <c r="E4" s="6" t="n">
-        <v>277.15</v>
-      </c>
-      <c r="F4" s="7" t="n">
-        <v>1.36</v>
-      </c>
-      <c r="G4" s="8" t="n">
-        <v>-0.01480658481386824</v>
-      </c>
-    </row>
-    <row r="5">
-      <c r="A5" s="3" t="inlineStr">
-        <is>
-          <t>BANKNIFTY</t>
-        </is>
-      </c>
-      <c r="B5" s="13" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="C5" s="10" t="n">
-        <v>0</v>
-      </c>
-      <c r="D5" s="10" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="E5" s="10" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="F5" s="10" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="G5" s="10" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-    </row>
-    <row r="6">
-      <c r="A6" s="3" t="inlineStr">
-        <is>
-          <t>FINNIFTY</t>
-        </is>
-      </c>
-      <c r="B6" s="13" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="C6" s="10" t="n">
-        <v>0</v>
-      </c>
-      <c r="D6" s="10" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="E6" s="10" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="F6" s="10" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="G6" s="10" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-    </row>
-    <row r="7">
-      <c r="A7" s="3" t="inlineStr">
-        <is>
-          <t>ALL INDICES</t>
-        </is>
-      </c>
-      <c r="B7" s="13" t="inlineStr">
-        <is>
-          <t>(combined)</t>
-        </is>
-      </c>
-      <c r="C7" s="4" t="n">
-        <v>5</v>
-      </c>
-      <c r="D7" s="5" t="n">
-        <v>0.4</v>
-      </c>
-      <c r="E7" s="6" t="n">
-        <v>277.15</v>
-      </c>
-      <c r="F7" s="7" t="n">
-        <v>1.36</v>
-      </c>
-      <c r="G7" s="8" t="n">
-        <v>-0.01480658481386824</v>
-      </c>
-    </row>
-    <row r="9">
-      <c r="A9" s="11" t="inlineStr">
-        <is>
-          <t>BT- sheets are from the BACKTEST (each index's single best combo, so time periods aren't double-counted across competing strategies). Plain-named sheets are LIVE paper trades. See latest_backtest_summary.xlsx for every combo tested.</t>
-        </is>
-      </c>
-    </row>
-  </sheetData>
-  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
-  <pageSetup orientation="landscape" fitToHeight="0" fitToWidth="1"/>
-</worksheet>
-</file>
-
-<file path=xl/worksheets/sheet7.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <sheetPr>
-    <outlinePr summaryBelow="1" summaryRight="1"/>
-    <pageSetUpPr fitToPage="1"/>
-  </sheetPr>
-  <dimension ref="A1:O46"/>
-  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
-  <cols>
-    <col width="40" customWidth="1" min="1" max="1"/>
-    <col width="10" customWidth="1" min="2" max="2"/>
-    <col width="10" customWidth="1" min="3" max="3"/>
-    <col width="10" customWidth="1" min="4" max="4"/>
-    <col width="10" customWidth="1" min="5" max="5"/>
-    <col width="10" customWidth="1" min="6" max="6"/>
-    <col width="10" customWidth="1" min="7" max="7"/>
-    <col width="15" customWidth="1" min="8" max="8"/>
-    <col width="15" customWidth="1" min="9" max="9"/>
-    <col width="10" customWidth="1" min="10" max="10"/>
-    <col width="10" customWidth="1" min="11" max="11"/>
-    <col width="10" customWidth="1" min="12" max="12"/>
-    <col width="10" customWidth="1" min="13" max="13"/>
-    <col width="10" customWidth="1" min="14" max="14"/>
-    <col width="15" customWidth="1" min="15" max="15"/>
-  </cols>
-  <sheetData>
-    <row r="1">
-      <c r="A1" s="1" t="inlineStr">
-        <is>
-          <t>BACKTEST NIFTY -- best: vwap_ema_momentum (EMA9/13) [5m] -- PAPER TRADE, NOT REAL MONEY</t>
-        </is>
-      </c>
-    </row>
-    <row r="3">
-      <c r="A3" s="12" t="inlineStr">
-        <is>
-          <t>MONTHLY returns (% of capital at start of month)</t>
-        </is>
-      </c>
-    </row>
-    <row r="4">
-      <c r="A4" s="2" t="inlineStr">
-        <is>
-          <t>Year</t>
-        </is>
-      </c>
-      <c r="B4" s="2" t="inlineStr">
-        <is>
-          <t>Jan</t>
-        </is>
-      </c>
-      <c r="C4" s="2" t="inlineStr">
-        <is>
-          <t>Feb</t>
-        </is>
-      </c>
-      <c r="D4" s="2" t="inlineStr">
-        <is>
-          <t>Mar</t>
-        </is>
-      </c>
-      <c r="E4" s="2" t="inlineStr">
-        <is>
-          <t>Apr</t>
-        </is>
-      </c>
-      <c r="F4" s="2" t="inlineStr">
-        <is>
-          <t>May</t>
-        </is>
-      </c>
-      <c r="G4" s="2" t="inlineStr">
-        <is>
-          <t>Jun</t>
-        </is>
-      </c>
-      <c r="H4" s="2" t="inlineStr">
-        <is>
-          <t>Jul</t>
-        </is>
-      </c>
-      <c r="I4" s="2" t="inlineStr">
-        <is>
-          <t>Aug</t>
-        </is>
-      </c>
-      <c r="J4" s="2" t="inlineStr">
-        <is>
-          <t>Sep</t>
-        </is>
-      </c>
-      <c r="K4" s="2" t="inlineStr">
-        <is>
-          <t>Oct</t>
-        </is>
-      </c>
-      <c r="L4" s="2" t="inlineStr">
-        <is>
-          <t>Nov</t>
-        </is>
-      </c>
-      <c r="M4" s="2" t="inlineStr">
-        <is>
-          <t>Dec</t>
-        </is>
-      </c>
-      <c r="N4" s="2" t="inlineStr">
-        <is>
-          <t>Yr %</t>
-        </is>
-      </c>
-      <c r="O4" s="2" t="inlineStr">
-        <is>
-          <t>Yr P&amp;L (Rs)</t>
-        </is>
-      </c>
-    </row>
-    <row r="5">
-      <c r="A5" s="3" t="n">
-        <v>2026</v>
-      </c>
-      <c r="B5" s="13" t="n"/>
-      <c r="C5" s="13" t="n"/>
-      <c r="D5" s="29" t="n">
-        <v>-0.003766999999999999</v>
-      </c>
-      <c r="E5" s="13" t="n"/>
-      <c r="F5" s="14" t="n">
-        <v>0.02750410797474085</v>
-      </c>
-      <c r="G5" s="13" t="n"/>
-      <c r="H5" s="13" t="n"/>
-      <c r="I5" s="13" t="n"/>
-      <c r="J5" s="13" t="n"/>
-      <c r="K5" s="29" t="n">
-        <v>-0.009550293146912445</v>
-      </c>
-      <c r="L5" s="13" t="n"/>
-      <c r="M5" s="13" t="n"/>
-      <c r="N5" s="15" t="n">
-        <v>0.01385750000000008</v>
-      </c>
-      <c r="O5" s="16" t="n">
-        <v>277.15</v>
-      </c>
-    </row>
-    <row r="6">
-      <c r="A6" s="3" t="inlineStr">
-        <is>
-          <t>Avg</t>
-        </is>
-      </c>
-      <c r="B6" s="13" t="n"/>
-      <c r="C6" s="13" t="n"/>
-      <c r="D6" s="30" t="n">
-        <v>-0.003766999999999999</v>
-      </c>
-      <c r="E6" s="13" t="n"/>
-      <c r="F6" s="15" t="n">
-        <v>0.02750410797474085</v>
-      </c>
-      <c r="G6" s="13" t="n"/>
-      <c r="H6" s="13" t="n"/>
-      <c r="I6" s="13" t="n"/>
-      <c r="J6" s="13" t="n"/>
-      <c r="K6" s="30" t="n">
-        <v>-0.009550293146912445</v>
-      </c>
-      <c r="L6" s="13" t="n"/>
-      <c r="M6" s="13" t="n"/>
-    </row>
-    <row r="8">
-      <c r="A8" s="12" t="inlineStr">
-        <is>
-          <t>WEEKLY returns (% of capital at start of that week; weeks split at month edges)</t>
-        </is>
-      </c>
-    </row>
-    <row r="9">
-      <c r="A9" s="2" t="inlineStr">
-        <is>
-          <t>Month</t>
-        </is>
-      </c>
-      <c r="B9" s="2" t="inlineStr">
-        <is>
-          <t>W1</t>
-        </is>
-      </c>
-      <c r="C9" s="2" t="inlineStr">
-        <is>
-          <t>W2</t>
-        </is>
-      </c>
-      <c r="D9" s="2" t="inlineStr">
-        <is>
-          <t>W3</t>
-        </is>
-      </c>
-      <c r="E9" s="2" t="inlineStr">
-        <is>
-          <t>W4</t>
-        </is>
-      </c>
-      <c r="F9" s="2" t="inlineStr">
-        <is>
-          <t>W5</t>
-        </is>
-      </c>
-      <c r="G9" s="2" t="inlineStr">
-        <is>
-          <t>W6</t>
-        </is>
-      </c>
-      <c r="H9" s="2" t="inlineStr">
-        <is>
-          <t>Month %</t>
-        </is>
-      </c>
-      <c r="I9" s="2" t="inlineStr">
-        <is>
-          <t>Month P&amp;L (Rs)</t>
-        </is>
-      </c>
-    </row>
-    <row r="10">
-      <c r="A10" s="3" t="inlineStr">
-        <is>
-          <t>2026-Mar</t>
-        </is>
-      </c>
-      <c r="B10" s="29" t="n">
-        <v>-0.003766999999999999</v>
-      </c>
-      <c r="C10" s="13" t="n"/>
-      <c r="D10" s="13" t="n"/>
-      <c r="E10" s="13" t="n"/>
-      <c r="F10" s="13" t="n"/>
-      <c r="G10" s="13" t="n"/>
-      <c r="H10" s="31" t="n">
-        <v>-0.003766999999999999</v>
-      </c>
-      <c r="I10" s="32" t="n">
-        <v>-75.34</v>
-      </c>
-    </row>
-    <row r="11">
-      <c r="A11" s="3" t="inlineStr">
-        <is>
-          <t>2026-May</t>
-        </is>
-      </c>
-      <c r="B11" s="14" t="n">
-        <v>0.02750410797474085</v>
-      </c>
-      <c r="C11" s="13" t="n"/>
-      <c r="D11" s="13" t="n"/>
-      <c r="E11" s="13" t="n"/>
-      <c r="F11" s="13" t="n"/>
-      <c r="G11" s="13" t="n"/>
-      <c r="H11" s="17" t="n">
-        <v>0.02750410797474085</v>
-      </c>
-      <c r="I11" s="16" t="n">
-        <v>548.01</v>
-      </c>
-    </row>
-    <row r="12">
-      <c r="A12" s="3" t="inlineStr">
-        <is>
-          <t>2026-Oct</t>
-        </is>
-      </c>
-      <c r="B12" s="29" t="n">
-        <v>-0.009550293146912445</v>
-      </c>
-      <c r="C12" s="13" t="n"/>
-      <c r="D12" s="13" t="n"/>
-      <c r="E12" s="13" t="n"/>
-      <c r="F12" s="13" t="n"/>
-      <c r="G12" s="13" t="n"/>
-      <c r="H12" s="31" t="n">
-        <v>-0.009550293146912445</v>
-      </c>
-      <c r="I12" s="32" t="n">
-        <v>-195.52</v>
-      </c>
-    </row>
-    <row r="14">
-      <c r="A14" s="12" t="inlineStr">
-        <is>
-          <t>DAILY returns (% of capital at start of that day; blank = no trade that day)</t>
-        </is>
-      </c>
-    </row>
-    <row r="15">
-      <c r="A15" s="2" t="inlineStr">
-        <is>
-          <t>Week starting (Mon)</t>
-        </is>
-      </c>
-      <c r="B15" s="2" t="inlineStr">
-        <is>
-          <t>Mon</t>
-        </is>
-      </c>
-      <c r="C15" s="2" t="inlineStr">
-        <is>
-          <t>Tue</t>
-        </is>
-      </c>
-      <c r="D15" s="2" t="inlineStr">
-        <is>
-          <t>Wed</t>
-        </is>
-      </c>
-      <c r="E15" s="2" t="inlineStr">
-        <is>
-          <t>Thu</t>
-        </is>
-      </c>
-      <c r="F15" s="2" t="inlineStr">
-        <is>
-          <t>Fri</t>
-        </is>
-      </c>
-      <c r="G15" s="2" t="inlineStr">
-        <is>
-          <t>Week %</t>
-        </is>
-      </c>
-      <c r="H15" s="2" t="inlineStr">
-        <is>
-          <t>Week P&amp;L (Rs)</t>
-        </is>
-      </c>
-    </row>
-    <row r="16">
-      <c r="A16" s="3" t="inlineStr">
-        <is>
-          <t>23-Mar-2026</t>
-        </is>
-      </c>
-      <c r="B16" s="13" t="n"/>
-      <c r="C16" s="29" t="n">
-        <v>-0.003766999999999999</v>
-      </c>
-      <c r="D16" s="13" t="n"/>
-      <c r="E16" s="13" t="n"/>
-      <c r="F16" s="13" t="n"/>
-      <c r="G16" s="31" t="n">
-        <v>-0.003766999999999999</v>
-      </c>
-      <c r="H16" s="32" t="n">
-        <v>-75.34</v>
-      </c>
-    </row>
-    <row r="17">
-      <c r="A17" s="3" t="inlineStr">
-        <is>
-          <t>11-May-2026</t>
-        </is>
-      </c>
-      <c r="B17" s="13" t="n"/>
-      <c r="C17" s="14" t="n">
-        <v>0.02750410797474085</v>
-      </c>
-      <c r="D17" s="13" t="n"/>
-      <c r="E17" s="13" t="n"/>
-      <c r="F17" s="13" t="n"/>
-      <c r="G17" s="17" t="n">
-        <v>0.02750410797474085</v>
-      </c>
-      <c r="H17" s="16" t="n">
-        <v>548.01</v>
-      </c>
-    </row>
-    <row r="18">
-      <c r="A18" s="3" t="inlineStr">
-        <is>
-          <t>12-Oct-2026</t>
-        </is>
-      </c>
-      <c r="B18" s="13" t="n"/>
-      <c r="C18" s="29" t="n">
-        <v>-0.009550293146912445</v>
-      </c>
-      <c r="D18" s="13" t="n"/>
-      <c r="E18" s="13" t="n"/>
-      <c r="F18" s="13" t="n"/>
-      <c r="G18" s="31" t="n">
-        <v>-0.009550293146912445</v>
-      </c>
-      <c r="H18" s="32" t="n">
-        <v>-195.52</v>
-      </c>
-    </row>
-    <row r="20">
-      <c r="A20" s="12" t="inlineStr">
-        <is>
-          <t>STATISTICS (all trades for this index)</t>
-        </is>
-      </c>
-    </row>
-    <row r="21">
-      <c r="A21" s="3" t="inlineStr">
-        <is>
-          <t>All trades</t>
-        </is>
-      </c>
-      <c r="B21" s="18" t="n">
-        <v>5</v>
-      </c>
-      <c r="C21" s="19" t="n"/>
-      <c r="D21" s="20" t="n"/>
-    </row>
-    <row r="22">
-      <c r="A22" s="3" t="inlineStr">
-        <is>
-          <t>Winners</t>
-        </is>
-      </c>
-      <c r="B22" s="21" t="inlineStr">
-        <is>
-          <t>2 (40.0%)</t>
-        </is>
-      </c>
-      <c r="C22" s="19" t="n"/>
-      <c r="D22" s="20" t="n"/>
-    </row>
-    <row r="23">
-      <c r="A23" s="3" t="inlineStr">
-        <is>
-          <t>Losers</t>
-        </is>
-      </c>
-      <c r="B23" s="21" t="inlineStr">
-        <is>
-          <t>3 (60.0%)</t>
-        </is>
-      </c>
-      <c r="C23" s="19" t="n"/>
-      <c r="D23" s="20" t="n"/>
-    </row>
-    <row r="24">
-      <c r="A24" s="3" t="inlineStr">
-        <is>
-          <t>Net P&amp;L (Rs)</t>
-        </is>
-      </c>
-      <c r="B24" s="22" t="n">
-        <v>277.15</v>
-      </c>
-      <c r="C24" s="19" t="n"/>
-      <c r="D24" s="20" t="n"/>
-    </row>
-    <row r="25">
-      <c r="A25" s="3" t="inlineStr">
-        <is>
-          <t>Total Profit (Rs)</t>
-        </is>
-      </c>
-      <c r="B25" s="22" t="n">
-        <v>1040.37</v>
-      </c>
-      <c r="C25" s="19" t="n"/>
-      <c r="D25" s="20" t="n"/>
-    </row>
-    <row r="26">
-      <c r="A26" s="3" t="inlineStr">
-        <is>
-          <t>Total Loss (Rs)</t>
-        </is>
-      </c>
-      <c r="B26" s="23" t="n">
-        <v>-763.22</v>
-      </c>
-      <c r="C26" s="19" t="n"/>
-      <c r="D26" s="20" t="n"/>
-    </row>
-    <row r="27">
-      <c r="A27" s="3" t="inlineStr">
-        <is>
-          <t>Transaction costs (Rs)</t>
-        </is>
-      </c>
-      <c r="B27" s="24" t="n">
-        <v>143.6</v>
-      </c>
-      <c r="C27" s="19" t="n"/>
-      <c r="D27" s="20" t="n"/>
-    </row>
-    <row r="28">
-      <c r="A28" s="3" t="inlineStr">
-        <is>
-          <t>Avg Profit/Loss per trade (Rs)</t>
-        </is>
-      </c>
-      <c r="B28" s="22" t="n">
-        <v>55.43</v>
-      </c>
-      <c r="C28" s="19" t="n"/>
-      <c r="D28" s="20" t="n"/>
-    </row>
-    <row r="29">
-      <c r="A29" s="3" t="inlineStr">
-        <is>
-          <t>Avg Profit/Loss per trade (% of premium)</t>
-        </is>
-      </c>
-      <c r="B29" s="25" t="n">
-        <v>2.6</v>
-      </c>
-      <c r="C29" s="19" t="n"/>
-      <c r="D29" s="20" t="n"/>
-    </row>
-    <row r="30">
-      <c r="A30" s="3" t="inlineStr">
-        <is>
-          <t>Avg Win (Rs)</t>
-        </is>
-      </c>
-      <c r="B30" s="22" t="n">
-        <v>520.1799999999999</v>
-      </c>
-      <c r="C30" s="19" t="n"/>
-      <c r="D30" s="20" t="n"/>
-    </row>
-    <row r="31">
-      <c r="A31" s="3" t="inlineStr">
-        <is>
-          <t>Avg Win (% of premium)</t>
-        </is>
-      </c>
-      <c r="B31" s="26" t="n">
-        <v>54.92</v>
-      </c>
-      <c r="C31" s="19" t="n"/>
-      <c r="D31" s="20" t="n"/>
-    </row>
-    <row r="32">
-      <c r="A32" s="3" t="inlineStr">
-        <is>
-          <t>Avg Loss (Rs)</t>
-        </is>
-      </c>
-      <c r="B32" s="23" t="n">
-        <v>-254.41</v>
-      </c>
-      <c r="C32" s="19" t="n"/>
-      <c r="D32" s="20" t="n"/>
-    </row>
-    <row r="33">
-      <c r="A33" s="3" t="inlineStr">
-        <is>
-          <t>Avg Loss (% of premium)</t>
-        </is>
-      </c>
-      <c r="B33" s="27" t="n">
-        <v>-32.27</v>
-      </c>
-      <c r="C33" s="19" t="n"/>
-      <c r="D33" s="20" t="n"/>
-    </row>
-    <row r="34">
-      <c r="A34" s="3" t="inlineStr">
-        <is>
-          <t>Largest Win (Rs)</t>
-        </is>
-      </c>
-      <c r="B34" s="22" t="n">
-        <v>548.01</v>
-      </c>
-      <c r="C34" s="19" t="n"/>
-      <c r="D34" s="20" t="n"/>
-    </row>
-    <row r="35">
-      <c r="A35" s="3" t="inlineStr">
-        <is>
-          <t>Largest Loss (Rs)</t>
-        </is>
-      </c>
-      <c r="B35" s="23" t="n">
-        <v>-299.45</v>
-      </c>
-      <c r="C35" s="19" t="n"/>
-      <c r="D35" s="20" t="n"/>
-    </row>
-    <row r="36">
-      <c r="A36" s="3" t="inlineStr">
-        <is>
-          <t>Max Consecutive Wins</t>
-        </is>
-      </c>
-      <c r="B36" s="18" t="n">
-        <v>1</v>
-      </c>
-      <c r="C36" s="19" t="n"/>
-      <c r="D36" s="20" t="n"/>
-    </row>
-    <row r="37">
-      <c r="A37" s="3" t="inlineStr">
-        <is>
-          <t>Max Consecutive Losses</t>
-        </is>
-      </c>
-      <c r="B37" s="18" t="n">
-        <v>1</v>
-      </c>
-      <c r="C37" s="19" t="n"/>
-      <c r="D37" s="20" t="n"/>
-    </row>
-    <row r="38">
-      <c r="A38" s="3" t="inlineStr">
-        <is>
-          <t>Max trade drawdown (Rs)</t>
-        </is>
-      </c>
-      <c r="B38" s="23" t="n">
-        <v>-299.45</v>
-      </c>
-      <c r="C38" s="19" t="n"/>
-      <c r="D38" s="20" t="n"/>
-    </row>
-    <row r="39">
-      <c r="A39" s="3" t="inlineStr">
-        <is>
-          <t>Max system drawdown (Rs)</t>
-        </is>
-      </c>
-      <c r="B39" s="23" t="n">
-        <v>-299.45</v>
-      </c>
-      <c r="C39" s="19" t="n"/>
-      <c r="D39" s="20" t="n"/>
-    </row>
-    <row r="40">
-      <c r="A40" s="3" t="inlineStr">
-        <is>
-          <t>Max system drawdown (%)</t>
-        </is>
-      </c>
-      <c r="B40" s="27" t="n">
-        <v>-1.48</v>
-      </c>
-      <c r="C40" s="19" t="n"/>
-      <c r="D40" s="20" t="n"/>
-    </row>
-    <row r="41">
-      <c r="A41" s="3" t="inlineStr">
-        <is>
-          <t>Recovery Factor</t>
-        </is>
-      </c>
-      <c r="B41" s="28" t="n">
-        <v>0.93</v>
-      </c>
-      <c r="C41" s="19" t="n"/>
-      <c r="D41" s="20" t="n"/>
-    </row>
-    <row r="42">
-      <c r="A42" s="3" t="inlineStr">
-        <is>
-          <t>Profit Factor</t>
-        </is>
-      </c>
-      <c r="B42" s="28" t="n">
-        <v>1.36</v>
-      </c>
-      <c r="C42" s="19" t="n"/>
-      <c r="D42" s="20" t="n"/>
-    </row>
-    <row r="43">
-      <c r="A43" s="3" t="inlineStr">
-        <is>
-          <t>Payoff Ratio (avg win / avg loss)</t>
-        </is>
-      </c>
-      <c r="B43" s="28" t="n">
-        <v>2.04</v>
-      </c>
-      <c r="C43" s="19" t="n"/>
-      <c r="D43" s="20" t="n"/>
-    </row>
-    <row r="44">
-      <c r="A44" s="3" t="inlineStr">
-        <is>
-          <t>Sharpe Ratio (annualized)</t>
-        </is>
-      </c>
-      <c r="B44" s="28" t="n">
-        <v>4.61</v>
-      </c>
-      <c r="C44" s="19" t="n"/>
-      <c r="D44" s="20" t="n"/>
-    </row>
-    <row r="46">
-      <c r="A46" s="11" t="inlineStr">
-        <is>
-          <t>Caveat: with only a handful of trades these numbers (Sharpe, profit factor, drawdown %) are not statistically reliable. Watch this over weeks/months before drawing conclusions.</t>
-        </is>
-      </c>
-    </row>
-  </sheetData>
-  <mergeCells count="24">
-    <mergeCell ref="B42:D42"/>
-    <mergeCell ref="B23:D23"/>
-    <mergeCell ref="B44:D44"/>
-    <mergeCell ref="B29:D29"/>
-    <mergeCell ref="B38:D38"/>
-    <mergeCell ref="B34:D34"/>
-    <mergeCell ref="B28:D28"/>
-    <mergeCell ref="B37:D37"/>
-    <mergeCell ref="B40:D40"/>
-    <mergeCell ref="B30:D30"/>
-    <mergeCell ref="B24:D24"/>
-    <mergeCell ref="B33:D33"/>
-    <mergeCell ref="B36:D36"/>
-    <mergeCell ref="B41:D41"/>
-    <mergeCell ref="B32:D32"/>
-    <mergeCell ref="B35:D35"/>
-    <mergeCell ref="B26:D26"/>
-    <mergeCell ref="B25:D25"/>
-    <mergeCell ref="B31:D31"/>
-    <mergeCell ref="B22:D22"/>
-    <mergeCell ref="B27:D27"/>
-    <mergeCell ref="B21:D21"/>
-    <mergeCell ref="B43:D43"/>
-    <mergeCell ref="B39:D39"/>
-  </mergeCells>
-  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
-  <pageSetup orientation="landscape" fitToHeight="0" fitToWidth="1"/>
-</worksheet>
-</file>
-
-<file path=xl/worksheets/sheet8.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <sheetPr>
-    <outlinePr summaryBelow="1" summaryRight="1"/>
-    <pageSetUpPr fitToPage="1"/>
-  </sheetPr>
-  <dimension ref="A1:A3"/>
-  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
-  <cols>
-    <col width="40" customWidth="1" min="1" max="1"/>
-    <col width="10" customWidth="1" min="2" max="2"/>
-    <col width="10" customWidth="1" min="3" max="3"/>
-    <col width="10" customWidth="1" min="4" max="4"/>
-    <col width="10" customWidth="1" min="5" max="5"/>
-    <col width="10" customWidth="1" min="6" max="6"/>
-    <col width="10" customWidth="1" min="7" max="7"/>
-    <col width="15" customWidth="1" min="8" max="8"/>
-    <col width="15" customWidth="1" min="9" max="9"/>
-    <col width="10" customWidth="1" min="10" max="10"/>
-    <col width="10" customWidth="1" min="11" max="11"/>
-    <col width="10" customWidth="1" min="12" max="12"/>
-    <col width="10" customWidth="1" min="13" max="13"/>
-    <col width="10" customWidth="1" min="14" max="14"/>
-    <col width="15" customWidth="1" min="15" max="15"/>
-  </cols>
-  <sheetData>
-    <row r="1">
-      <c r="A1" s="1" t="inlineStr">
-        <is>
-          <t>BACKTEST BANKNIFTY -- best:  -- PAPER TRADE, NOT REAL MONEY</t>
-        </is>
-      </c>
-    </row>
-    <row r="3">
-      <c r="A3" s="11" t="inlineStr">
-        <is>
-          <t>No trades yet for this index -- this fills in automatically as the bot trades.</t>
-        </is>
-      </c>
-    </row>
-  </sheetData>
-  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
-  <pageSetup orientation="landscape" fitToHeight="0" fitToWidth="1"/>
-</worksheet>
-</file>
-
-<file path=xl/worksheets/sheet9.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <sheetPr>
-    <outlinePr summaryBelow="1" summaryRight="1"/>
-    <pageSetUpPr fitToPage="1"/>
-  </sheetPr>
-  <dimension ref="A1:A3"/>
-  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
-  <cols>
-    <col width="40" customWidth="1" min="1" max="1"/>
-    <col width="10" customWidth="1" min="2" max="2"/>
-    <col width="10" customWidth="1" min="3" max="3"/>
-    <col width="10" customWidth="1" min="4" max="4"/>
-    <col width="10" customWidth="1" min="5" max="5"/>
-    <col width="10" customWidth="1" min="6" max="6"/>
-    <col width="10" customWidth="1" min="7" max="7"/>
-    <col width="15" customWidth="1" min="8" max="8"/>
-    <col width="15" customWidth="1" min="9" max="9"/>
-    <col width="10" customWidth="1" min="10" max="10"/>
-    <col width="10" customWidth="1" min="11" max="11"/>
-    <col width="10" customWidth="1" min="12" max="12"/>
-    <col width="10" customWidth="1" min="13" max="13"/>
-    <col width="10" customWidth="1" min="14" max="14"/>
-    <col width="15" customWidth="1" min="15" max="15"/>
-  </cols>
-  <sheetData>
-    <row r="1">
-      <c r="A1" s="1" t="inlineStr">
-        <is>
-          <t>BACKTEST FINNIFTY -- best:  -- PAPER TRADE, NOT REAL MONEY</t>
-        </is>
-      </c>
-    </row>
-    <row r="3">
-      <c r="A3" s="11" t="inlineStr">
-        <is>
-          <t>No trades yet for this index -- this fills in automatically as the bot trades.</t>
-        </is>
-      </c>
-    </row>
-  </sheetData>
-  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
-  <pageSetup orientation="landscape" fitToHeight="0" fitToWidth="1"/>
-</worksheet>
 </file>
--- a/reports/dashboard.xlsx
+++ b/reports/dashboard.xlsx
@@ -639,22 +639,22 @@
         </is>
       </c>
       <c r="B4" s="4" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="C4" s="5" t="n">
-        <v>0.5</v>
+        <v>0.6666666666666666</v>
       </c>
       <c r="D4" s="6" t="n">
-        <v>402.32</v>
+        <v>551.04</v>
       </c>
       <c r="E4" s="7" t="n">
-        <v>2.8</v>
+        <v>3.46</v>
       </c>
       <c r="F4" s="8" t="n">
         <v>-0.01084792207143678</v>
       </c>
       <c r="G4" s="9" t="n">
-        <v>201.16</v>
+        <v>183.68</v>
       </c>
     </row>
     <row r="5">
@@ -734,22 +734,22 @@
         </is>
       </c>
       <c r="B7" s="4" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="C7" s="5" t="n">
-        <v>0.5</v>
+        <v>0.6666666666666666</v>
       </c>
       <c r="D7" s="6" t="n">
-        <v>402.32</v>
+        <v>551.04</v>
       </c>
       <c r="E7" s="7" t="n">
-        <v>2.8</v>
+        <v>3.46</v>
       </c>
       <c r="F7" s="8" t="n">
         <v>-0.01084792207143678</v>
       </c>
       <c r="G7" s="9" t="n">
-        <v>201.16</v>
+        <v>183.68</v>
       </c>
     </row>
     <row r="9">
@@ -771,7 +771,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
-  <dimension ref="A1:O42"/>
+  <dimension ref="A1:O43"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="40" customWidth="1" min="1" max="1"/>
@@ -896,15 +896,15 @@
       <c r="I5" s="13" t="n"/>
       <c r="J5" s="13" t="n"/>
       <c r="K5" s="14" t="n">
-        <v>0.020116</v>
+        <v>0.027552</v>
       </c>
       <c r="L5" s="13" t="n"/>
       <c r="M5" s="13" t="n"/>
       <c r="N5" s="15" t="n">
-        <v>0.02011600000000002</v>
+        <v>0.02755200000000002</v>
       </c>
       <c r="O5" s="16" t="n">
-        <v>402.32</v>
+        <v>551.04</v>
       </c>
     </row>
     <row r="6">
@@ -923,7 +923,7 @@
       <c r="I6" s="13" t="n"/>
       <c r="J6" s="13" t="n"/>
       <c r="K6" s="15" t="n">
-        <v>0.020116</v>
+        <v>0.027552</v>
       </c>
       <c r="L6" s="13" t="n"/>
       <c r="M6" s="13" t="n"/>
@@ -991,16 +991,18 @@
       <c r="B10" s="14" t="n">
         <v>0.020116</v>
       </c>
-      <c r="C10" s="13" t="n"/>
+      <c r="C10" s="14" t="n">
+        <v>0.007289367091585663</v>
+      </c>
       <c r="D10" s="13" t="n"/>
       <c r="E10" s="13" t="n"/>
       <c r="F10" s="13" t="n"/>
       <c r="G10" s="13" t="n"/>
       <c r="H10" s="17" t="n">
-        <v>0.020116</v>
+        <v>0.027552</v>
       </c>
       <c r="I10" s="16" t="n">
-        <v>402.32</v>
+        <v>551.04</v>
       </c>
     </row>
     <row r="12">
@@ -1072,35 +1074,41 @@
         <v>402.32</v>
       </c>
     </row>
-    <row r="16">
-      <c r="A16" s="12" t="inlineStr">
+    <row r="15">
+      <c r="A15" s="3" t="inlineStr">
+        <is>
+          <t>26-Oct-2026</t>
+        </is>
+      </c>
+      <c r="B15" s="13" t="n"/>
+      <c r="C15" s="14" t="n">
+        <v>0.007289367091585663</v>
+      </c>
+      <c r="D15" s="13" t="n"/>
+      <c r="E15" s="13" t="n"/>
+      <c r="F15" s="13" t="n"/>
+      <c r="G15" s="17" t="n">
+        <v>0.007289367091585663</v>
+      </c>
+      <c r="H15" s="16" t="n">
+        <v>148.72</v>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" s="12" t="inlineStr">
         <is>
           <t>STATISTICS (all trades for this index)</t>
         </is>
       </c>
-    </row>
-    <row r="17">
-      <c r="A17" s="3" t="inlineStr">
-        <is>
-          <t>All trades</t>
-        </is>
-      </c>
-      <c r="B17" s="18" t="n">
-        <v>2</v>
-      </c>
-      <c r="C17" s="19" t="n"/>
-      <c r="D17" s="20" t="n"/>
     </row>
     <row r="18">
       <c r="A18" s="3" t="inlineStr">
         <is>
-          <t>Winners</t>
-        </is>
-      </c>
-      <c r="B18" s="21" t="inlineStr">
-        <is>
-          <t>1 (50.0%)</t>
-        </is>
+          <t>All trades</t>
+        </is>
+      </c>
+      <c r="B18" s="18" t="n">
+        <v>3</v>
       </c>
       <c r="C18" s="19" t="n"/>
       <c r="D18" s="20" t="n"/>
@@ -1108,12 +1116,12 @@
     <row r="19">
       <c r="A19" s="3" t="inlineStr">
         <is>
-          <t>Losers</t>
+          <t>Winners</t>
         </is>
       </c>
       <c r="B19" s="21" t="inlineStr">
         <is>
-          <t>1 (50.0%)</t>
+          <t>2 (66.7%)</t>
         </is>
       </c>
       <c r="C19" s="19" t="n"/>
@@ -1122,11 +1130,13 @@
     <row r="20">
       <c r="A20" s="3" t="inlineStr">
         <is>
-          <t>Net P&amp;L (Rs)</t>
-        </is>
-      </c>
-      <c r="B20" s="22" t="n">
-        <v>402.32</v>
+          <t>Losers</t>
+        </is>
+      </c>
+      <c r="B20" s="21" t="inlineStr">
+        <is>
+          <t>1 (33.3%)</t>
+        </is>
       </c>
       <c r="C20" s="19" t="n"/>
       <c r="D20" s="20" t="n"/>
@@ -1134,11 +1144,11 @@
     <row r="21">
       <c r="A21" s="3" t="inlineStr">
         <is>
-          <t>Total Profit (Rs)</t>
+          <t>Net P&amp;L (Rs)</t>
         </is>
       </c>
       <c r="B21" s="22" t="n">
-        <v>626.0700000000001</v>
+        <v>551.04</v>
       </c>
       <c r="C21" s="19" t="n"/>
       <c r="D21" s="20" t="n"/>
@@ -1146,11 +1156,11 @@
     <row r="22">
       <c r="A22" s="3" t="inlineStr">
         <is>
-          <t>Total Loss (Rs)</t>
-        </is>
-      </c>
-      <c r="B22" s="23" t="n">
-        <v>-223.75</v>
+          <t>Total Profit (Rs)</t>
+        </is>
+      </c>
+      <c r="B22" s="22" t="n">
+        <v>774.79</v>
       </c>
       <c r="C22" s="19" t="n"/>
       <c r="D22" s="20" t="n"/>
@@ -1158,11 +1168,11 @@
     <row r="23">
       <c r="A23" s="3" t="inlineStr">
         <is>
-          <t>Transaction costs (Rs)</t>
-        </is>
-      </c>
-      <c r="B23" s="24" t="n">
-        <v>47.68</v>
+          <t>Total Loss (Rs)</t>
+        </is>
+      </c>
+      <c r="B23" s="23" t="n">
+        <v>-223.75</v>
       </c>
       <c r="C23" s="19" t="n"/>
       <c r="D23" s="20" t="n"/>
@@ -1170,11 +1180,11 @@
     <row r="24">
       <c r="A24" s="3" t="inlineStr">
         <is>
-          <t>Avg Profit/Loss per trade (Rs)</t>
-        </is>
-      </c>
-      <c r="B24" s="22" t="n">
-        <v>201.16</v>
+          <t>Transaction costs (Rs)</t>
+        </is>
+      </c>
+      <c r="B24" s="24" t="n">
+        <v>72.45999999999999</v>
       </c>
       <c r="C24" s="19" t="n"/>
       <c r="D24" s="20" t="n"/>
@@ -1182,11 +1192,11 @@
     <row r="25">
       <c r="A25" s="3" t="inlineStr">
         <is>
-          <t>Avg Profit/Loss per trade (% of premium)</t>
-        </is>
-      </c>
-      <c r="B25" s="25" t="n">
-        <v>30.69</v>
+          <t>Avg Profit/Loss per trade (Rs)</t>
+        </is>
+      </c>
+      <c r="B25" s="22" t="n">
+        <v>183.68</v>
       </c>
       <c r="C25" s="19" t="n"/>
       <c r="D25" s="20" t="n"/>
@@ -1194,11 +1204,11 @@
     <row r="26">
       <c r="A26" s="3" t="inlineStr">
         <is>
-          <t>Avg Win (Rs)</t>
-        </is>
-      </c>
-      <c r="B26" s="22" t="n">
-        <v>626.0700000000001</v>
+          <t>Avg Profit/Loss per trade (% of premium)</t>
+        </is>
+      </c>
+      <c r="B26" s="25" t="n">
+        <v>27.7</v>
       </c>
       <c r="C26" s="19" t="n"/>
       <c r="D26" s="20" t="n"/>
@@ -1206,11 +1216,11 @@
     <row r="27">
       <c r="A27" s="3" t="inlineStr">
         <is>
-          <t>Avg Win (% of premium)</t>
-        </is>
-      </c>
-      <c r="B27" s="26" t="n">
-        <v>97.90000000000001</v>
+          <t>Avg Win (Rs)</t>
+        </is>
+      </c>
+      <c r="B27" s="22" t="n">
+        <v>387.4</v>
       </c>
       <c r="C27" s="19" t="n"/>
       <c r="D27" s="20" t="n"/>
@@ -1218,11 +1228,11 @@
     <row r="28">
       <c r="A28" s="3" t="inlineStr">
         <is>
-          <t>Avg Loss (Rs)</t>
-        </is>
-      </c>
-      <c r="B28" s="23" t="n">
-        <v>-223.75</v>
+          <t>Avg Win (% of premium)</t>
+        </is>
+      </c>
+      <c r="B28" s="26" t="n">
+        <v>59.8</v>
       </c>
       <c r="C28" s="19" t="n"/>
       <c r="D28" s="20" t="n"/>
@@ -1230,11 +1240,11 @@
     <row r="29">
       <c r="A29" s="3" t="inlineStr">
         <is>
-          <t>Avg Loss (% of premium)</t>
-        </is>
-      </c>
-      <c r="B29" s="27" t="n">
-        <v>-36.52</v>
+          <t>Avg Loss (Rs)</t>
+        </is>
+      </c>
+      <c r="B29" s="23" t="n">
+        <v>-223.75</v>
       </c>
       <c r="C29" s="19" t="n"/>
       <c r="D29" s="20" t="n"/>
@@ -1242,11 +1252,11 @@
     <row r="30">
       <c r="A30" s="3" t="inlineStr">
         <is>
-          <t>Largest Win (Rs)</t>
-        </is>
-      </c>
-      <c r="B30" s="22" t="n">
-        <v>626.0700000000001</v>
+          <t>Avg Loss (% of premium)</t>
+        </is>
+      </c>
+      <c r="B30" s="27" t="n">
+        <v>-36.52</v>
       </c>
       <c r="C30" s="19" t="n"/>
       <c r="D30" s="20" t="n"/>
@@ -1254,11 +1264,11 @@
     <row r="31">
       <c r="A31" s="3" t="inlineStr">
         <is>
-          <t>Largest Loss (Rs)</t>
-        </is>
-      </c>
-      <c r="B31" s="23" t="n">
-        <v>-223.75</v>
+          <t>Largest Win (Rs)</t>
+        </is>
+      </c>
+      <c r="B31" s="22" t="n">
+        <v>626.0700000000001</v>
       </c>
       <c r="C31" s="19" t="n"/>
       <c r="D31" s="20" t="n"/>
@@ -1266,11 +1276,11 @@
     <row r="32">
       <c r="A32" s="3" t="inlineStr">
         <is>
-          <t>Max Consecutive Wins</t>
-        </is>
-      </c>
-      <c r="B32" s="18" t="n">
-        <v>1</v>
+          <t>Largest Loss (Rs)</t>
+        </is>
+      </c>
+      <c r="B32" s="23" t="n">
+        <v>-223.75</v>
       </c>
       <c r="C32" s="19" t="n"/>
       <c r="D32" s="20" t="n"/>
@@ -1278,7 +1288,7 @@
     <row r="33">
       <c r="A33" s="3" t="inlineStr">
         <is>
-          <t>Max Consecutive Losses</t>
+          <t>Max Consecutive Wins</t>
         </is>
       </c>
       <c r="B33" s="18" t="n">
@@ -1290,11 +1300,11 @@
     <row r="34">
       <c r="A34" s="3" t="inlineStr">
         <is>
-          <t>Max trade drawdown (Rs)</t>
-        </is>
-      </c>
-      <c r="B34" s="23" t="n">
-        <v>-223.75</v>
+          <t>Max Consecutive Losses</t>
+        </is>
+      </c>
+      <c r="B34" s="18" t="n">
+        <v>1</v>
       </c>
       <c r="C34" s="19" t="n"/>
       <c r="D34" s="20" t="n"/>
@@ -1302,7 +1312,7 @@
     <row r="35">
       <c r="A35" s="3" t="inlineStr">
         <is>
-          <t>Max system drawdown (Rs)</t>
+          <t>Max trade drawdown (Rs)</t>
         </is>
       </c>
       <c r="B35" s="23" t="n">
@@ -1314,11 +1324,11 @@
     <row r="36">
       <c r="A36" s="3" t="inlineStr">
         <is>
-          <t>Max system drawdown (%)</t>
-        </is>
-      </c>
-      <c r="B36" s="27" t="n">
-        <v>-1.08</v>
+          <t>Max system drawdown (Rs)</t>
+        </is>
+      </c>
+      <c r="B36" s="23" t="n">
+        <v>-223.75</v>
       </c>
       <c r="C36" s="19" t="n"/>
       <c r="D36" s="20" t="n"/>
@@ -1326,11 +1336,11 @@
     <row r="37">
       <c r="A37" s="3" t="inlineStr">
         <is>
-          <t>Recovery Factor</t>
-        </is>
-      </c>
-      <c r="B37" s="28" t="n">
-        <v>1.8</v>
+          <t>Max system drawdown (%)</t>
+        </is>
+      </c>
+      <c r="B37" s="27" t="n">
+        <v>-1.08</v>
       </c>
       <c r="C37" s="19" t="n"/>
       <c r="D37" s="20" t="n"/>
@@ -1338,11 +1348,11 @@
     <row r="38">
       <c r="A38" s="3" t="inlineStr">
         <is>
-          <t>Profit Factor</t>
+          <t>Recovery Factor</t>
         </is>
       </c>
       <c r="B38" s="28" t="n">
-        <v>2.8</v>
+        <v>2.46</v>
       </c>
       <c r="C38" s="19" t="n"/>
       <c r="D38" s="20" t="n"/>
@@ -1350,11 +1360,11 @@
     <row r="39">
       <c r="A39" s="3" t="inlineStr">
         <is>
-          <t>Payoff Ratio (avg win / avg loss)</t>
+          <t>Profit Factor</t>
         </is>
       </c>
       <c r="B39" s="28" t="n">
-        <v>2.8</v>
+        <v>3.46</v>
       </c>
       <c r="C39" s="19" t="n"/>
       <c r="D39" s="20" t="n"/>
@@ -1362,19 +1372,29 @@
     <row r="40">
       <c r="A40" s="3" t="inlineStr">
         <is>
-          <t>Sharpe Ratio (annualized)</t>
-        </is>
-      </c>
-      <c r="B40" s="21" t="inlineStr">
-        <is>
-          <t>N/A (needs 2+ trading days)</t>
-        </is>
+          <t>Payoff Ratio (avg win / avg loss)</t>
+        </is>
+      </c>
+      <c r="B40" s="28" t="n">
+        <v>1.73</v>
       </c>
       <c r="C40" s="19" t="n"/>
       <c r="D40" s="20" t="n"/>
     </row>
-    <row r="42">
-      <c r="A42" s="11" t="inlineStr">
+    <row r="41">
+      <c r="A41" s="3" t="inlineStr">
+        <is>
+          <t>Sharpe Ratio (annualized)</t>
+        </is>
+      </c>
+      <c r="B41" s="28" t="n">
+        <v>33.92</v>
+      </c>
+      <c r="C41" s="19" t="n"/>
+      <c r="D41" s="20" t="n"/>
+    </row>
+    <row r="43">
+      <c r="A43" s="11" t="inlineStr">
         <is>
           <t>Caveat: with only a handful of trades these numbers (Sharpe, profit factor, drawdown %) are not statistically reliable. Watch this over weeks/months before drawing conclusions.</t>
         </is>
@@ -1383,7 +1403,6 @@
   </sheetData>
   <mergeCells count="24">
     <mergeCell ref="B23:D23"/>
-    <mergeCell ref="B17:D17"/>
     <mergeCell ref="B29:D29"/>
     <mergeCell ref="B38:D38"/>
     <mergeCell ref="B34:D34"/>
@@ -1396,6 +1415,7 @@
     <mergeCell ref="B20:D20"/>
     <mergeCell ref="B33:D33"/>
     <mergeCell ref="B36:D36"/>
+    <mergeCell ref="B41:D41"/>
     <mergeCell ref="B32:D32"/>
     <mergeCell ref="B35:D35"/>
     <mergeCell ref="B26:D26"/>
@@ -1510,7 +1530,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
-  <dimension ref="A1:O42"/>
+  <dimension ref="A1:O43"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="40" customWidth="1" min="1" max="1"/>
@@ -1635,15 +1655,15 @@
       <c r="I5" s="13" t="n"/>
       <c r="J5" s="13" t="n"/>
       <c r="K5" s="14" t="n">
-        <v>0.020116</v>
+        <v>0.027552</v>
       </c>
       <c r="L5" s="13" t="n"/>
       <c r="M5" s="13" t="n"/>
       <c r="N5" s="15" t="n">
-        <v>0.02011600000000002</v>
+        <v>0.02755200000000002</v>
       </c>
       <c r="O5" s="16" t="n">
-        <v>402.32</v>
+        <v>551.04</v>
       </c>
     </row>
     <row r="6">
@@ -1662,7 +1682,7 @@
       <c r="I6" s="13" t="n"/>
       <c r="J6" s="13" t="n"/>
       <c r="K6" s="15" t="n">
-        <v>0.020116</v>
+        <v>0.027552</v>
       </c>
       <c r="L6" s="13" t="n"/>
       <c r="M6" s="13" t="n"/>
@@ -1730,16 +1750,18 @@
       <c r="B10" s="14" t="n">
         <v>0.020116</v>
       </c>
-      <c r="C10" s="13" t="n"/>
+      <c r="C10" s="14" t="n">
+        <v>0.007289367091585663</v>
+      </c>
       <c r="D10" s="13" t="n"/>
       <c r="E10" s="13" t="n"/>
       <c r="F10" s="13" t="n"/>
       <c r="G10" s="13" t="n"/>
       <c r="H10" s="17" t="n">
-        <v>0.020116</v>
+        <v>0.027552</v>
       </c>
       <c r="I10" s="16" t="n">
-        <v>402.32</v>
+        <v>551.04</v>
       </c>
     </row>
     <row r="12">
@@ -1811,35 +1833,41 @@
         <v>402.32</v>
       </c>
     </row>
-    <row r="16">
-      <c r="A16" s="12" t="inlineStr">
+    <row r="15">
+      <c r="A15" s="3" t="inlineStr">
+        <is>
+          <t>26-Oct-2026</t>
+        </is>
+      </c>
+      <c r="B15" s="13" t="n"/>
+      <c r="C15" s="14" t="n">
+        <v>0.007289367091585663</v>
+      </c>
+      <c r="D15" s="13" t="n"/>
+      <c r="E15" s="13" t="n"/>
+      <c r="F15" s="13" t="n"/>
+      <c r="G15" s="17" t="n">
+        <v>0.007289367091585663</v>
+      </c>
+      <c r="H15" s="16" t="n">
+        <v>148.72</v>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" s="12" t="inlineStr">
         <is>
           <t>STATISTICS (all trades for this index)</t>
         </is>
       </c>
-    </row>
-    <row r="17">
-      <c r="A17" s="3" t="inlineStr">
-        <is>
-          <t>All trades</t>
-        </is>
-      </c>
-      <c r="B17" s="18" t="n">
-        <v>2</v>
-      </c>
-      <c r="C17" s="19" t="n"/>
-      <c r="D17" s="20" t="n"/>
     </row>
     <row r="18">
       <c r="A18" s="3" t="inlineStr">
         <is>
-          <t>Winners</t>
-        </is>
-      </c>
-      <c r="B18" s="21" t="inlineStr">
-        <is>
-          <t>1 (50.0%)</t>
-        </is>
+          <t>All trades</t>
+        </is>
+      </c>
+      <c r="B18" s="18" t="n">
+        <v>3</v>
       </c>
       <c r="C18" s="19" t="n"/>
       <c r="D18" s="20" t="n"/>
@@ -1847,12 +1875,12 @@
     <row r="19">
       <c r="A19" s="3" t="inlineStr">
         <is>
-          <t>Losers</t>
+          <t>Winners</t>
         </is>
       </c>
       <c r="B19" s="21" t="inlineStr">
         <is>
-          <t>1 (50.0%)</t>
+          <t>2 (66.7%)</t>
         </is>
       </c>
       <c r="C19" s="19" t="n"/>
@@ -1861,11 +1889,13 @@
     <row r="20">
       <c r="A20" s="3" t="inlineStr">
         <is>
-          <t>Net P&amp;L (Rs)</t>
-        </is>
-      </c>
-      <c r="B20" s="22" t="n">
-        <v>402.32</v>
+          <t>Losers</t>
+        </is>
+      </c>
+      <c r="B20" s="21" t="inlineStr">
+        <is>
+          <t>1 (33.3%)</t>
+        </is>
       </c>
       <c r="C20" s="19" t="n"/>
       <c r="D20" s="20" t="n"/>
@@ -1873,11 +1903,11 @@
     <row r="21">
       <c r="A21" s="3" t="inlineStr">
         <is>
-          <t>Total Profit (Rs)</t>
+          <t>Net P&amp;L (Rs)</t>
         </is>
       </c>
       <c r="B21" s="22" t="n">
-        <v>626.0700000000001</v>
+        <v>551.04</v>
       </c>
       <c r="C21" s="19" t="n"/>
       <c r="D21" s="20" t="n"/>
@@ -1885,11 +1915,11 @@
     <row r="22">
       <c r="A22" s="3" t="inlineStr">
         <is>
-          <t>Total Loss (Rs)</t>
-        </is>
-      </c>
-      <c r="B22" s="23" t="n">
-        <v>-223.75</v>
+          <t>Total Profit (Rs)</t>
+        </is>
+      </c>
+      <c r="B22" s="22" t="n">
+        <v>774.79</v>
       </c>
       <c r="C22" s="19" t="n"/>
       <c r="D22" s="20" t="n"/>
@@ -1897,11 +1927,11 @@
     <row r="23">
       <c r="A23" s="3" t="inlineStr">
         <is>
-          <t>Transaction costs (Rs)</t>
-        </is>
-      </c>
-      <c r="B23" s="24" t="n">
-        <v>47.68</v>
+          <t>Total Loss (Rs)</t>
+        </is>
+      </c>
+      <c r="B23" s="23" t="n">
+        <v>-223.75</v>
       </c>
       <c r="C23" s="19" t="n"/>
       <c r="D23" s="20" t="n"/>
@@ -1909,11 +1939,11 @@
     <row r="24">
       <c r="A24" s="3" t="inlineStr">
         <is>
-          <t>Avg Profit/Loss per trade (Rs)</t>
-        </is>
-      </c>
-      <c r="B24" s="22" t="n">
-        <v>201.16</v>
+          <t>Transaction costs (Rs)</t>
+        </is>
+      </c>
+      <c r="B24" s="24" t="n">
+        <v>72.45999999999999</v>
       </c>
       <c r="C24" s="19" t="n"/>
       <c r="D24" s="20" t="n"/>
@@ -1921,11 +1951,11 @@
     <row r="25">
       <c r="A25" s="3" t="inlineStr">
         <is>
-          <t>Avg Profit/Loss per trade (% of premium)</t>
-        </is>
-      </c>
-      <c r="B25" s="25" t="n">
-        <v>30.69</v>
+          <t>Avg Profit/Loss per trade (Rs)</t>
+        </is>
+      </c>
+      <c r="B25" s="22" t="n">
+        <v>183.68</v>
       </c>
       <c r="C25" s="19" t="n"/>
       <c r="D25" s="20" t="n"/>
@@ -1933,11 +1963,11 @@
     <row r="26">
       <c r="A26" s="3" t="inlineStr">
         <is>
-          <t>Avg Win (Rs)</t>
-        </is>
-      </c>
-      <c r="B26" s="22" t="n">
-        <v>626.0700000000001</v>
+          <t>Avg Profit/Loss per trade (% of premium)</t>
+        </is>
+      </c>
+      <c r="B26" s="25" t="n">
+        <v>27.7</v>
       </c>
       <c r="C26" s="19" t="n"/>
       <c r="D26" s="20" t="n"/>
@@ -1945,11 +1975,11 @@
     <row r="27">
       <c r="A27" s="3" t="inlineStr">
         <is>
-          <t>Avg Win (% of premium)</t>
-        </is>
-      </c>
-      <c r="B27" s="26" t="n">
-        <v>97.90000000000001</v>
+          <t>Avg Win (Rs)</t>
+        </is>
+      </c>
+      <c r="B27" s="22" t="n">
+        <v>387.4</v>
       </c>
       <c r="C27" s="19" t="n"/>
       <c r="D27" s="20" t="n"/>
@@ -1957,11 +1987,11 @@
     <row r="28">
       <c r="A28" s="3" t="inlineStr">
         <is>
-          <t>Avg Loss (Rs)</t>
-        </is>
-      </c>
-      <c r="B28" s="23" t="n">
-        <v>-223.75</v>
+          <t>Avg Win (% of premium)</t>
+        </is>
+      </c>
+      <c r="B28" s="26" t="n">
+        <v>59.8</v>
       </c>
       <c r="C28" s="19" t="n"/>
       <c r="D28" s="20" t="n"/>
@@ -1969,11 +1999,11 @@
     <row r="29">
       <c r="A29" s="3" t="inlineStr">
         <is>
-          <t>Avg Loss (% of premium)</t>
-        </is>
-      </c>
-      <c r="B29" s="27" t="n">
-        <v>-36.52</v>
+          <t>Avg Loss (Rs)</t>
+        </is>
+      </c>
+      <c r="B29" s="23" t="n">
+        <v>-223.75</v>
       </c>
       <c r="C29" s="19" t="n"/>
       <c r="D29" s="20" t="n"/>
@@ -1981,11 +2011,11 @@
     <row r="30">
       <c r="A30" s="3" t="inlineStr">
         <is>
-          <t>Largest Win (Rs)</t>
-        </is>
-      </c>
-      <c r="B30" s="22" t="n">
-        <v>626.0700000000001</v>
+          <t>Avg Loss (% of premium)</t>
+        </is>
+      </c>
+      <c r="B30" s="27" t="n">
+        <v>-36.52</v>
       </c>
       <c r="C30" s="19" t="n"/>
       <c r="D30" s="20" t="n"/>
@@ -1993,11 +2023,11 @@
     <row r="31">
       <c r="A31" s="3" t="inlineStr">
         <is>
-          <t>Largest Loss (Rs)</t>
-        </is>
-      </c>
-      <c r="B31" s="23" t="n">
-        <v>-223.75</v>
+          <t>Largest Win (Rs)</t>
+        </is>
+      </c>
+      <c r="B31" s="22" t="n">
+        <v>626.0700000000001</v>
       </c>
       <c r="C31" s="19" t="n"/>
       <c r="D31" s="20" t="n"/>
@@ -2005,11 +2035,11 @@
     <row r="32">
       <c r="A32" s="3" t="inlineStr">
         <is>
-          <t>Max Consecutive Wins</t>
-        </is>
-      </c>
-      <c r="B32" s="18" t="n">
-        <v>1</v>
+          <t>Largest Loss (Rs)</t>
+        </is>
+      </c>
+      <c r="B32" s="23" t="n">
+        <v>-223.75</v>
       </c>
       <c r="C32" s="19" t="n"/>
       <c r="D32" s="20" t="n"/>
@@ -2017,7 +2047,7 @@
     <row r="33">
       <c r="A33" s="3" t="inlineStr">
         <is>
-          <t>Max Consecutive Losses</t>
+          <t>Max Consecutive Wins</t>
         </is>
       </c>
       <c r="B33" s="18" t="n">
@@ -2029,11 +2059,11 @@
     <row r="34">
       <c r="A34" s="3" t="inlineStr">
         <is>
-          <t>Max trade drawdown (Rs)</t>
-        </is>
-      </c>
-      <c r="B34" s="23" t="n">
-        <v>-223.75</v>
+          <t>Max Consecutive Losses</t>
+        </is>
+      </c>
+      <c r="B34" s="18" t="n">
+        <v>1</v>
       </c>
       <c r="C34" s="19" t="n"/>
       <c r="D34" s="20" t="n"/>
@@ -2041,7 +2071,7 @@
     <row r="35">
       <c r="A35" s="3" t="inlineStr">
         <is>
-          <t>Max system drawdown (Rs)</t>
+          <t>Max trade drawdown (Rs)</t>
         </is>
       </c>
       <c r="B35" s="23" t="n">
@@ -2053,11 +2083,11 @@
     <row r="36">
       <c r="A36" s="3" t="inlineStr">
         <is>
-          <t>Max system drawdown (%)</t>
-        </is>
-      </c>
-      <c r="B36" s="27" t="n">
-        <v>-1.08</v>
+          <t>Max system drawdown (Rs)</t>
+        </is>
+      </c>
+      <c r="B36" s="23" t="n">
+        <v>-223.75</v>
       </c>
       <c r="C36" s="19" t="n"/>
       <c r="D36" s="20" t="n"/>
@@ -2065,11 +2095,11 @@
     <row r="37">
       <c r="A37" s="3" t="inlineStr">
         <is>
-          <t>Recovery Factor</t>
-        </is>
-      </c>
-      <c r="B37" s="28" t="n">
-        <v>1.8</v>
+          <t>Max system drawdown (%)</t>
+        </is>
+      </c>
+      <c r="B37" s="27" t="n">
+        <v>-1.08</v>
       </c>
       <c r="C37" s="19" t="n"/>
       <c r="D37" s="20" t="n"/>
@@ -2077,11 +2107,11 @@
     <row r="38">
       <c r="A38" s="3" t="inlineStr">
         <is>
-          <t>Profit Factor</t>
+          <t>Recovery Factor</t>
         </is>
       </c>
       <c r="B38" s="28" t="n">
-        <v>2.8</v>
+        <v>2.46</v>
       </c>
       <c r="C38" s="19" t="n"/>
       <c r="D38" s="20" t="n"/>
@@ -2089,11 +2119,11 @@
     <row r="39">
       <c r="A39" s="3" t="inlineStr">
         <is>
-          <t>Payoff Ratio (avg win / avg loss)</t>
+          <t>Profit Factor</t>
         </is>
       </c>
       <c r="B39" s="28" t="n">
-        <v>2.8</v>
+        <v>3.46</v>
       </c>
       <c r="C39" s="19" t="n"/>
       <c r="D39" s="20" t="n"/>
@@ -2101,19 +2131,29 @@
     <row r="40">
       <c r="A40" s="3" t="inlineStr">
         <is>
-          <t>Sharpe Ratio (annualized)</t>
-        </is>
-      </c>
-      <c r="B40" s="21" t="inlineStr">
-        <is>
-          <t>N/A (needs 2+ trading days)</t>
-        </is>
+          <t>Payoff Ratio (avg win / avg loss)</t>
+        </is>
+      </c>
+      <c r="B40" s="28" t="n">
+        <v>1.73</v>
       </c>
       <c r="C40" s="19" t="n"/>
       <c r="D40" s="20" t="n"/>
     </row>
-    <row r="42">
-      <c r="A42" s="11" t="inlineStr">
+    <row r="41">
+      <c r="A41" s="3" t="inlineStr">
+        <is>
+          <t>Sharpe Ratio (annualized)</t>
+        </is>
+      </c>
+      <c r="B41" s="28" t="n">
+        <v>33.92</v>
+      </c>
+      <c r="C41" s="19" t="n"/>
+      <c r="D41" s="20" t="n"/>
+    </row>
+    <row r="43">
+      <c r="A43" s="11" t="inlineStr">
         <is>
           <t>Caveat: with only a handful of trades these numbers (Sharpe, profit factor, drawdown %) are not statistically reliable. Watch this over weeks/months before drawing conclusions.</t>
         </is>
@@ -2122,7 +2162,6 @@
   </sheetData>
   <mergeCells count="24">
     <mergeCell ref="B23:D23"/>
-    <mergeCell ref="B17:D17"/>
     <mergeCell ref="B29:D29"/>
     <mergeCell ref="B38:D38"/>
     <mergeCell ref="B34:D34"/>
@@ -2135,6 +2174,7 @@
     <mergeCell ref="B20:D20"/>
     <mergeCell ref="B33:D33"/>
     <mergeCell ref="B36:D36"/>
+    <mergeCell ref="B41:D41"/>
     <mergeCell ref="B32:D32"/>
     <mergeCell ref="B35:D35"/>
     <mergeCell ref="B26:D26"/>
